--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="175">
   <si>
     <t>CodCliente</t>
   </si>
@@ -241,6 +241,9 @@
     <t>Folha Mensal/Pró-Labore</t>
   </si>
   <si>
+    <t>FOPAG Impressão PDF</t>
+  </si>
+  <si>
     <t>Rebto planilha/Resumo de Folha (01)</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>02/09/2026</t>
   </si>
   <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
     <t>04/09/2026</t>
   </si>
   <si>
@@ -334,6 +340,9 @@
     <t>Mikael Teixeira</t>
   </si>
   <si>
+    <t>Kaique Souza</t>
+  </si>
+  <si>
     <t>Santos Karina</t>
   </si>
   <si>
@@ -356,6 +365,9 @@
   </si>
   <si>
     <t>Karina Santos</t>
+  </si>
+  <si>
+    <t>Sara Cavalheiro</t>
   </si>
   <si>
     <t>Leandro Matos</t>
@@ -419,6 +431,13 @@
 será enviado ao cliente - Data Comentário: 31/08/2026 11:06 - Data Comentário: 01/09/2026 18:34</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/09/2026 
+aguardando cliente - Data Comentário: 31/08/2026 11:10</t>
+  </si>
+  <si>
+    <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/09/2026 - Data Comentário: 01/09/2026 17:03</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 04/09/2026 
 Previsão para finalizar em 04/09 - Data Comentário: 01/09/2026 11:28</t>
   </si>
@@ -491,10 +510,19 @@
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[7237]. - Data Comentário: 01/09/2026 06:04</t>
   </si>
   <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 02/09/2026 15:55:47. - Data Comentário: 02/09/2026 15:50</t>
+  </si>
+  <si>
     <t>Baixado via rotina MGC x Analise Balanço em 01/09/2026 05:10:58. - Data Comentário: 01/09/2026 05:09</t>
   </si>
   <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 02/09/2026 15:53:59. - Data Comentário: 02/09/2026 15:49</t>
+  </si>
+  <si>
     <t>Baixado via rotina MGC x Analise Balanço em 01/09/2026 05:10:39. - Data Comentário: 01/09/2026 05:09</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 02/09/2026 16:10:07. - Data Comentário: 02/09/2026 16:05</t>
   </si>
   <si>
     <t>Baixado via rotina MGC x Analise Balanço em 01/09/2026 05:10:19. - Data Comentário: 01/09/2026 05:09</t>
@@ -851,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI70"/>
+  <dimension ref="A1:AI78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1005,13 +1033,13 @@
         <v>18096486</v>
       </c>
       <c r="S2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V2" s="1">
         <v>46266.57730150463</v>
@@ -1020,22 +1048,22 @@
         <v>8</v>
       </c>
       <c r="X2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="Y2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AH2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1082,13 +1110,13 @@
         <v>18254143</v>
       </c>
       <c r="S3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V3" s="1">
         <v>46266.41668148148</v>
@@ -1097,22 +1125,22 @@
         <v>8</v>
       </c>
       <c r="X3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AB3">
         <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1159,13 +1187,13 @@
         <v>17968041</v>
       </c>
       <c r="S4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V4" s="1">
         <v>46267.4463130787</v>
@@ -1174,19 +1202,19 @@
         <v>-12</v>
       </c>
       <c r="X4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AB4">
         <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1233,13 +1261,13 @@
         <v>17042643</v>
       </c>
       <c r="S5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V5" s="1">
         <v>46267.44631975694</v>
@@ -1248,19 +1276,19 @@
         <v>-12</v>
       </c>
       <c r="X5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AB5">
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AH5" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1307,13 +1335,13 @@
         <v>16960110</v>
       </c>
       <c r="S6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V6" s="1">
         <v>46267.44632179398</v>
@@ -1322,19 +1350,19 @@
         <v>-12</v>
       </c>
       <c r="X6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AB6">
         <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AH6" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI6" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1381,13 +1409,13 @@
         <v>18163699</v>
       </c>
       <c r="S7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V7" s="1">
         <v>46267.44634035879</v>
@@ -1396,19 +1424,19 @@
         <v>-12</v>
       </c>
       <c r="X7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AB7">
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AH7" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI7" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1455,13 +1483,13 @@
         <v>18178308</v>
       </c>
       <c r="S8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V8" s="1">
         <v>46267.44634128473</v>
@@ -1470,19 +1498,19 @@
         <v>-12</v>
       </c>
       <c r="X8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AB8">
         <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH8" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1529,13 +1557,13 @@
         <v>18187978</v>
       </c>
       <c r="S9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V9" s="1">
         <v>46267.44634366898</v>
@@ -1544,19 +1572,19 @@
         <v>-12</v>
       </c>
       <c r="X9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AB9">
         <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AH9" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1603,13 +1631,13 @@
         <v>18241249</v>
       </c>
       <c r="S10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V10" s="1">
         <v>46267.44634548611</v>
@@ -1618,19 +1646,19 @@
         <v>-12</v>
       </c>
       <c r="X10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AB10">
         <v>0</v>
       </c>
       <c r="AC10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AH10" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI10" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1677,13 +1705,13 @@
         <v>17955421</v>
       </c>
       <c r="S11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V11" s="1">
         <v>46267.47365627315</v>
@@ -1692,19 +1720,19 @@
         <v>-26</v>
       </c>
       <c r="X11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB11">
         <v>0</v>
       </c>
       <c r="AC11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI11" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -1751,13 +1779,13 @@
         <v>17399423</v>
       </c>
       <c r="S12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="U12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V12" s="1">
         <v>46266.47620831019</v>
@@ -1766,19 +1794,19 @@
         <v>-16</v>
       </c>
       <c r="X12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AB12">
         <v>0</v>
       </c>
       <c r="AC12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="AH12" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI12" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -1825,13 +1853,13 @@
         <v>18152557</v>
       </c>
       <c r="S13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="U13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V13" s="1">
         <v>46267.57586420139</v>
@@ -1840,19 +1868,19 @@
         <v>-16</v>
       </c>
       <c r="X13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AB13">
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="AH13" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI13" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -1890,7 +1918,7 @@
         <v>46232</v>
       </c>
       <c r="O14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -1902,7 +1930,7 @@
         <v>17688641</v>
       </c>
       <c r="U14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V14" s="1">
         <v>46266.44145744213</v>
@@ -1911,19 +1939,19 @@
         <v>35</v>
       </c>
       <c r="X14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AB14">
         <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI14" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -1970,7 +1998,7 @@
         <v>17688645</v>
       </c>
       <c r="U15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V15" s="1">
         <v>46266.44156952546</v>
@@ -1979,16 +2007,16 @@
         <v>-23</v>
       </c>
       <c r="X15" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AB15">
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI15" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2026,7 +2054,7 @@
         <v>46260</v>
       </c>
       <c r="O16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -2038,7 +2066,7 @@
         <v>17688891</v>
       </c>
       <c r="U16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V16" s="1">
         <v>46266.44152346065</v>
@@ -2047,19 +2075,19 @@
         <v>7</v>
       </c>
       <c r="X16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AB16">
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2106,13 +2134,13 @@
         <v>16962141</v>
       </c>
       <c r="S17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V17" s="1">
         <v>46266.37634084491</v>
@@ -2121,19 +2149,19 @@
         <v>-19</v>
       </c>
       <c r="X17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AB17">
         <v>0</v>
       </c>
       <c r="AC17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AH17" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI17" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2180,13 +2208,13 @@
         <v>17955384</v>
       </c>
       <c r="S18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V18" s="1">
         <v>46267.47452163194</v>
@@ -2195,19 +2223,19 @@
         <v>-19</v>
       </c>
       <c r="X18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB18">
         <v>0</v>
       </c>
       <c r="AC18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH18" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI18" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2254,13 +2282,13 @@
         <v>17955238</v>
       </c>
       <c r="S19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V19" s="1">
         <v>46267.4745221412</v>
@@ -2269,19 +2297,19 @@
         <v>-19</v>
       </c>
       <c r="X19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB19">
         <v>0</v>
       </c>
       <c r="AC19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH19" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI19" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2328,13 +2356,13 @@
         <v>18056729</v>
       </c>
       <c r="S20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V20" s="1">
         <v>46267.47452299768</v>
@@ -2343,19 +2371,19 @@
         <v>-19</v>
       </c>
       <c r="X20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB20">
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH20" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI20" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2402,13 +2430,13 @@
         <v>17399444</v>
       </c>
       <c r="S21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="U21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V21" s="1">
         <v>46267.4462272338</v>
@@ -2417,19 +2445,19 @@
         <v>-12</v>
       </c>
       <c r="X21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AH21" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI21" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2476,13 +2504,13 @@
         <v>17955434</v>
       </c>
       <c r="S22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V22" s="1">
         <v>46267.44632673611</v>
@@ -2491,19 +2519,19 @@
         <v>-12</v>
       </c>
       <c r="X22" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB22">
         <v>0</v>
       </c>
       <c r="AC22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH22" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI22" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2550,13 +2578,13 @@
         <v>17955274</v>
       </c>
       <c r="S23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V23" s="1">
         <v>46267.44632704861</v>
@@ -2565,19 +2593,19 @@
         <v>-12</v>
       </c>
       <c r="X23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB23">
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH23" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI23" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2624,13 +2652,13 @@
         <v>18056832</v>
       </c>
       <c r="S24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U24" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V24" s="1">
         <v>46267.44633364584</v>
@@ -2639,19 +2667,19 @@
         <v>-12</v>
       </c>
       <c r="X24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AH24" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI24" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -2689,7 +2717,7 @@
         <v>46266</v>
       </c>
       <c r="O25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -2701,10 +2729,10 @@
         <v>18248555</v>
       </c>
       <c r="S25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="U25" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V25" s="1">
         <v>46267.55838734953</v>
@@ -2713,42 +2741,42 @@
         <v>1</v>
       </c>
       <c r="X25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Y25" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AH25" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="AI25" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:35">
       <c r="A26">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
         <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26">
         <v>5905</v>
@@ -2766,7 +2794,7 @@
         <v>46269</v>
       </c>
       <c r="O26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P26">
         <v>8</v>
@@ -2775,54 +2803,51 @@
         <v>2026</v>
       </c>
       <c r="R26">
-        <v>18179132</v>
+        <v>17399096</v>
       </c>
       <c r="S26" t="s">
-        <v>106</v>
-      </c>
-      <c r="T26" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="U26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V26" s="1">
-        <v>46267.4478849537</v>
+        <v>46267.66088636574</v>
       </c>
       <c r="W26">
         <v>-2</v>
       </c>
       <c r="X26" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Y26" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AB26">
         <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AH26" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="AI26" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:35">
       <c r="A27">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
@@ -2831,7 +2856,7 @@
         <v>56</v>
       </c>
       <c r="G27">
-        <v>5838</v>
+        <v>5905</v>
       </c>
       <c r="H27">
         <v>5784</v>
@@ -2840,13 +2865,13 @@
         <v>61</v>
       </c>
       <c r="J27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N27" s="1">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -2855,40 +2880,40 @@
         <v>2026</v>
       </c>
       <c r="R27">
-        <v>18157807</v>
+        <v>18090219</v>
       </c>
       <c r="S27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U27" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="V27" s="1">
-        <v>46267.35832805555</v>
+        <v>46267.64795916666</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="X27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Y27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AB27">
         <v>0</v>
       </c>
       <c r="AC27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="AI27" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -2911,7 +2936,7 @@
         <v>57</v>
       </c>
       <c r="G28">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="H28">
         <v>5784</v>
@@ -2920,13 +2945,13 @@
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N28" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="O28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P28">
         <v>8</v>
@@ -2935,48 +2960,48 @@
         <v>2026</v>
       </c>
       <c r="R28">
-        <v>18179139</v>
+        <v>18179132</v>
       </c>
       <c r="S28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="U28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V28" s="1">
-        <v>46267.44799793982</v>
+        <v>46267.4478849537</v>
       </c>
       <c r="W28">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="X28" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Y28" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AB28">
         <v>0</v>
       </c>
       <c r="AC28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AH28" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="AI28" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:35">
       <c r="A29">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
         <v>50</v>
@@ -2985,13 +3010,13 @@
         <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29">
-        <v>5907</v>
+        <v>5853</v>
       </c>
       <c r="H29">
         <v>5784</v>
@@ -3000,7 +3025,7 @@
         <v>61</v>
       </c>
       <c r="J29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N29" s="1">
         <v>46273</v>
@@ -3012,45 +3037,45 @@
         <v>2026</v>
       </c>
       <c r="R29">
-        <v>18179146</v>
+        <v>18090158</v>
       </c>
       <c r="S29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T29" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="U29" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V29" s="1">
-        <v>46267.44824061343</v>
+        <v>46267.64761306713</v>
       </c>
       <c r="W29">
         <v>-6</v>
       </c>
       <c r="X29" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="AB29">
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI29" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:35">
       <c r="A30">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>50</v>
@@ -3065,19 +3090,22 @@
         <v>56</v>
       </c>
       <c r="G30">
-        <v>6883</v>
+        <v>5838</v>
       </c>
       <c r="H30">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N30" s="1">
-        <v>46275</v>
+        <v>46266</v>
+      </c>
+      <c r="O30" t="s">
+        <v>96</v>
       </c>
       <c r="P30">
         <v>8</v>
@@ -3086,51 +3114,54 @@
         <v>2026</v>
       </c>
       <c r="R30">
-        <v>17399250</v>
+        <v>18157807</v>
       </c>
       <c r="S30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T30" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="U30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V30" s="1">
-        <v>46266.37636392361</v>
+        <v>46267.35832805555</v>
       </c>
       <c r="W30">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="X30" t="s">
-        <v>125</v>
+        <v>130</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>141</v>
       </c>
       <c r="AB30">
         <v>0</v>
       </c>
       <c r="AC30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AH30" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI30" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:35">
       <c r="A31">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
         <v>55</v>
@@ -3139,19 +3170,22 @@
         <v>56</v>
       </c>
       <c r="G31">
-        <v>1836</v>
+        <v>5906</v>
       </c>
       <c r="H31">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N31" s="1">
-        <v>46268</v>
+        <v>46273</v>
+      </c>
+      <c r="O31" t="s">
+        <v>98</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -3160,25 +3194,28 @@
         <v>2026</v>
       </c>
       <c r="R31">
-        <v>17398975</v>
+        <v>18090229</v>
       </c>
       <c r="S31" t="s">
         <v>108</v>
       </c>
       <c r="T31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V31" s="1">
-        <v>46266.37598834491</v>
+        <v>46267.64800344907</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="X31" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>142</v>
       </c>
       <c r="AB31">
         <v>0</v>
@@ -3187,45 +3224,48 @@
         <v>108</v>
       </c>
       <c r="AH31" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI31" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:35">
       <c r="A32">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
         <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32">
-        <v>1836</v>
+        <v>5906</v>
       </c>
       <c r="H32">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N32" s="1">
-        <v>46268</v>
+        <v>46273</v>
+      </c>
+      <c r="O32" t="s">
+        <v>98</v>
       </c>
       <c r="P32">
         <v>8</v>
@@ -3234,51 +3274,54 @@
         <v>2026</v>
       </c>
       <c r="R32">
-        <v>18085220</v>
+        <v>18179139</v>
       </c>
       <c r="S32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V32" s="1">
-        <v>46266.45957881944</v>
+        <v>46267.44799793982</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="X32" t="s">
-        <v>124</v>
+        <v>126</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>142</v>
       </c>
       <c r="AB32">
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH32" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI32" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:35">
       <c r="A33">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
         <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
         <v>55</v>
@@ -3287,19 +3330,19 @@
         <v>56</v>
       </c>
       <c r="G33">
-        <v>6802</v>
+        <v>5907</v>
       </c>
       <c r="H33">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N33" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="P33">
         <v>8</v>
@@ -3308,25 +3351,25 @@
         <v>2026</v>
       </c>
       <c r="R33">
-        <v>17399220</v>
+        <v>18090239</v>
       </c>
       <c r="S33" t="s">
         <v>108</v>
       </c>
       <c r="T33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V33" s="1">
-        <v>46266.37645462963</v>
+        <v>46267.648038125</v>
       </c>
       <c r="W33">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="X33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AB33">
         <v>0</v>
@@ -3335,45 +3378,45 @@
         <v>108</v>
       </c>
       <c r="AH33" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI33" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:35">
       <c r="A34">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
         <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G34">
-        <v>6801</v>
+        <v>5907</v>
       </c>
       <c r="H34">
-        <v>1796</v>
+        <v>5784</v>
       </c>
       <c r="I34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N34" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="P34">
         <v>8</v>
@@ -3382,37 +3425,37 @@
         <v>2026</v>
       </c>
       <c r="R34">
-        <v>17399210</v>
+        <v>18179146</v>
       </c>
       <c r="S34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V34" s="1">
-        <v>46266.37649475694</v>
+        <v>46267.44824061343</v>
       </c>
       <c r="W34">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="X34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AB34">
         <v>0</v>
       </c>
       <c r="AC34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH34" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI34" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3435,7 +3478,7 @@
         <v>56</v>
       </c>
       <c r="G35">
-        <v>6014</v>
+        <v>6883</v>
       </c>
       <c r="H35">
         <v>1788</v>
@@ -3444,10 +3487,10 @@
         <v>62</v>
       </c>
       <c r="J35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N35" s="1">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3456,45 +3499,45 @@
         <v>2026</v>
       </c>
       <c r="R35">
-        <v>17399136</v>
+        <v>17399250</v>
       </c>
       <c r="S35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T35" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V35" s="1">
-        <v>46266.37591180555</v>
+        <v>46266.37636392361</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="X35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AB35">
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH35" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI35" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:35">
       <c r="A36">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
         <v>50</v>
@@ -3509,7 +3552,7 @@
         <v>56</v>
       </c>
       <c r="G36">
-        <v>6014</v>
+        <v>1836</v>
       </c>
       <c r="H36">
         <v>1788</v>
@@ -3518,7 +3561,7 @@
         <v>62</v>
       </c>
       <c r="J36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N36" s="1">
         <v>46268</v>
@@ -3530,45 +3573,45 @@
         <v>2026</v>
       </c>
       <c r="R36">
-        <v>18085231</v>
+        <v>17398975</v>
       </c>
       <c r="S36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V36" s="1">
-        <v>46266.45946195602</v>
+        <v>46266.37598834491</v>
       </c>
       <c r="W36">
         <v>-1</v>
       </c>
       <c r="X36" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AB36">
         <v>0</v>
       </c>
       <c r="AC36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH36" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI36" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:35">
       <c r="A37">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>50</v>
@@ -3583,16 +3626,16 @@
         <v>56</v>
       </c>
       <c r="G37">
-        <v>6233</v>
+        <v>1836</v>
       </c>
       <c r="H37">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I37" t="s">
         <v>62</v>
       </c>
       <c r="J37" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N37" s="1">
         <v>46268</v>
@@ -3604,51 +3647,51 @@
         <v>2026</v>
       </c>
       <c r="R37">
-        <v>17399176</v>
+        <v>18085220</v>
       </c>
       <c r="S37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T37" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V37" s="1">
-        <v>46266.37538684028</v>
+        <v>46266.45957881944</v>
       </c>
       <c r="W37">
         <v>-1</v>
       </c>
       <c r="X37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AB37">
         <v>0</v>
       </c>
       <c r="AC37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH37" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI37" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="A38">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
         <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
         <v>55</v>
@@ -3657,19 +3700,19 @@
         <v>56</v>
       </c>
       <c r="G38">
-        <v>6233</v>
+        <v>6802</v>
       </c>
       <c r="H38">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I38" t="s">
         <v>62</v>
       </c>
       <c r="J38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N38" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3678,51 +3721,51 @@
         <v>2026</v>
       </c>
       <c r="R38">
-        <v>16962294</v>
+        <v>17399220</v>
       </c>
       <c r="S38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V38" s="1">
-        <v>46266.37538506944</v>
+        <v>46266.37645462963</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AB38">
         <v>0</v>
       </c>
       <c r="AC38" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH38" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI38" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="A39">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
         <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
         <v>55</v>
@@ -3731,19 +3774,19 @@
         <v>56</v>
       </c>
       <c r="G39">
-        <v>6233</v>
+        <v>6801</v>
       </c>
       <c r="H39">
-        <v>6232</v>
+        <v>1796</v>
       </c>
       <c r="I39" t="s">
         <v>62</v>
       </c>
       <c r="J39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N39" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -3752,22 +3795,22 @@
         <v>2026</v>
       </c>
       <c r="R39">
-        <v>17948844</v>
+        <v>17399210</v>
       </c>
       <c r="S39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T39" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U39" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V39" s="1">
-        <v>46266.45895332176</v>
+        <v>46266.37649475694</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X39" t="s">
         <v>129</v>
@@ -3776,21 +3819,21 @@
         <v>0</v>
       </c>
       <c r="AC39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH39" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI39" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:35">
       <c r="A40">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
         <v>50</v>
@@ -3805,10 +3848,10 @@
         <v>56</v>
       </c>
       <c r="G40">
-        <v>6233</v>
+        <v>6014</v>
       </c>
       <c r="H40">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I40" t="s">
         <v>62</v>
@@ -3826,51 +3869,51 @@
         <v>2026</v>
       </c>
       <c r="R40">
-        <v>18085264</v>
+        <v>17399136</v>
       </c>
       <c r="S40" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U40" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V40" s="1">
-        <v>46266.45874105324</v>
+        <v>46266.37591180555</v>
       </c>
       <c r="W40">
         <v>-1</v>
       </c>
       <c r="X40" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AB40">
         <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH40" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI40" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:35">
       <c r="A41">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
         <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>55</v>
@@ -3879,10 +3922,10 @@
         <v>56</v>
       </c>
       <c r="G41">
-        <v>6233</v>
+        <v>6014</v>
       </c>
       <c r="H41">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I41" t="s">
         <v>62</v>
@@ -3900,51 +3943,51 @@
         <v>2026</v>
       </c>
       <c r="R41">
-        <v>17948989</v>
+        <v>18085231</v>
       </c>
       <c r="S41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T41" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U41" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V41" s="1">
-        <v>46266.45873584491</v>
+        <v>46266.45946195602</v>
       </c>
       <c r="W41">
         <v>-1</v>
       </c>
       <c r="X41" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH41" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI41" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:35">
       <c r="A42">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
         <v>55</v>
@@ -3953,10 +3996,10 @@
         <v>56</v>
       </c>
       <c r="G42">
-        <v>11303</v>
+        <v>6233</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I42" t="s">
         <v>62</v>
@@ -3965,7 +4008,7 @@
         <v>84</v>
       </c>
       <c r="N42" s="1">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="P42">
         <v>8</v>
@@ -3974,72 +4017,72 @@
         <v>2026</v>
       </c>
       <c r="R42">
-        <v>17949079</v>
+        <v>17399176</v>
       </c>
       <c r="S42" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="T42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U42" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V42" s="1">
-        <v>46267.44505795139</v>
+        <v>46266.37538684028</v>
       </c>
       <c r="W42">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="X42" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AB42">
         <v>0</v>
       </c>
       <c r="AC42" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH42" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AI42" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:35">
       <c r="A43">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
         <v>56</v>
       </c>
       <c r="G43">
-        <v>945</v>
+        <v>6233</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N43" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P43">
         <v>8</v>
@@ -4048,51 +4091,51 @@
         <v>2026</v>
       </c>
       <c r="R43">
-        <v>16959938</v>
+        <v>16962294</v>
       </c>
       <c r="S43" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="T43" t="s">
+        <v>120</v>
       </c>
       <c r="U43" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V43" s="1">
-        <v>46266.04180934028</v>
+        <v>46266.37538506944</v>
       </c>
       <c r="W43">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="X43" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AB43">
         <v>0</v>
       </c>
       <c r="AC43" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH43" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AI43" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:35">
       <c r="A44">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
         <v>55</v>
@@ -4101,19 +4144,19 @@
         <v>56</v>
       </c>
       <c r="G44">
-        <v>945</v>
+        <v>6233</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N44" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P44">
         <v>8</v>
@@ -4122,72 +4165,72 @@
         <v>2026</v>
       </c>
       <c r="R44">
-        <v>18056695</v>
+        <v>17948844</v>
       </c>
       <c r="S44" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="T44" t="s">
+        <v>120</v>
       </c>
       <c r="U44" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V44" s="1">
-        <v>46266.08343295139</v>
+        <v>46266.45895332176</v>
       </c>
       <c r="W44">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="X44" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AB44">
         <v>0</v>
       </c>
       <c r="AC44" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH44" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AI44" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:35">
       <c r="A45">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45">
-        <v>945</v>
+        <v>6233</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N45" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P45">
         <v>8</v>
@@ -4196,51 +4239,51 @@
         <v>2026</v>
       </c>
       <c r="R45">
-        <v>18164487</v>
+        <v>18085264</v>
       </c>
       <c r="S45" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="T45" t="s">
+        <v>120</v>
       </c>
       <c r="U45" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V45" s="1">
-        <v>46266.08344398148</v>
+        <v>46266.45874105324</v>
       </c>
       <c r="W45">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="X45" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="AB45">
         <v>0</v>
       </c>
       <c r="AC45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH45" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AI45" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:35">
       <c r="A46">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
@@ -4249,19 +4292,19 @@
         <v>56</v>
       </c>
       <c r="G46">
-        <v>946</v>
+        <v>6233</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N46" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P46">
         <v>8</v>
@@ -4270,51 +4313,51 @@
         <v>2026</v>
       </c>
       <c r="R46">
-        <v>17398869</v>
+        <v>17948989</v>
       </c>
       <c r="S46" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="T46" t="s">
+        <v>120</v>
       </c>
       <c r="U46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V46" s="1">
-        <v>46266.25077376157</v>
+        <v>46266.45873584491</v>
       </c>
       <c r="W46">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="X46" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="AB46">
         <v>0</v>
       </c>
       <c r="AC46" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH46" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AI46" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:35">
       <c r="A47">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
         <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
@@ -4323,19 +4366,19 @@
         <v>56</v>
       </c>
       <c r="G47">
-        <v>946</v>
+        <v>11303</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N47" s="1">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="P47">
         <v>8</v>
@@ -4344,60 +4387,60 @@
         <v>2026</v>
       </c>
       <c r="R47">
-        <v>16962093</v>
+        <v>17949079</v>
       </c>
       <c r="S47" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="T47" t="s">
+        <v>120</v>
       </c>
       <c r="U47" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V47" s="1">
-        <v>46266.25004302083</v>
+        <v>46267.44505795139</v>
       </c>
       <c r="W47">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="X47" t="s">
         <v>128</v>
       </c>
-      <c r="Y47" t="s">
-        <v>141</v>
-      </c>
       <c r="AB47">
         <v>0</v>
       </c>
       <c r="AC47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH47" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AI47" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="A48">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F48" t="s">
         <v>56</v>
       </c>
       <c r="G48">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -4418,51 +4461,51 @@
         <v>2026</v>
       </c>
       <c r="R48">
-        <v>17941132</v>
+        <v>16959938</v>
       </c>
       <c r="S48" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V48" s="1">
-        <v>46266.25135543982</v>
+        <v>46266.04180934028</v>
       </c>
       <c r="W48">
         <v>-16</v>
       </c>
       <c r="X48" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="Y48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB48">
         <v>0</v>
       </c>
       <c r="AC48" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH48" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI48" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:35">
       <c r="A49">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
         <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E49" t="s">
         <v>55</v>
@@ -4471,7 +4514,7 @@
         <v>56</v>
       </c>
       <c r="G49">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -4480,10 +4523,10 @@
         <v>63</v>
       </c>
       <c r="J49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N49" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P49">
         <v>8</v>
@@ -4492,60 +4535,60 @@
         <v>2026</v>
       </c>
       <c r="R49">
-        <v>17941146</v>
+        <v>18056695</v>
       </c>
       <c r="S49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U49" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V49" s="1">
-        <v>46266.25232241898</v>
+        <v>46266.08343295139</v>
       </c>
       <c r="W49">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="X49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AB49">
         <v>0</v>
       </c>
       <c r="AC49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH49" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI49" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:35">
       <c r="A50">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
         <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F50" t="s">
         <v>57</v>
       </c>
       <c r="G50">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4554,10 +4597,10 @@
         <v>63</v>
       </c>
       <c r="J50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N50" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P50">
         <v>8</v>
@@ -4566,45 +4609,45 @@
         <v>2026</v>
       </c>
       <c r="R50">
-        <v>18178132</v>
+        <v>18164487</v>
       </c>
       <c r="S50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U50" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V50" s="1">
-        <v>46266.25258784722</v>
+        <v>46266.08344398148</v>
       </c>
       <c r="W50">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="X50" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="Y50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB50">
         <v>0</v>
       </c>
       <c r="AC50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH50" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI50" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:35">
       <c r="A51">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
         <v>50</v>
@@ -4619,7 +4662,7 @@
         <v>56</v>
       </c>
       <c r="G51">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -4628,10 +4671,10 @@
         <v>63</v>
       </c>
       <c r="J51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N51" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P51">
         <v>8</v>
@@ -4640,45 +4683,45 @@
         <v>2026</v>
       </c>
       <c r="R51">
-        <v>17222405</v>
+        <v>17398869</v>
       </c>
       <c r="S51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V51" s="1">
-        <v>46266.25161940972</v>
+        <v>46266.25077376157</v>
       </c>
       <c r="W51">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="X51" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Y51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AB51">
         <v>0</v>
       </c>
       <c r="AC51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH51" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI51" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:35">
       <c r="A52">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
         <v>50</v>
@@ -4693,7 +4736,7 @@
         <v>56</v>
       </c>
       <c r="G52">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -4702,10 +4745,10 @@
         <v>63</v>
       </c>
       <c r="J52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N52" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P52">
         <v>8</v>
@@ -4714,51 +4757,51 @@
         <v>2026</v>
       </c>
       <c r="R52">
-        <v>17941156</v>
+        <v>16962093</v>
       </c>
       <c r="S52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U52" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V52" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25004302083</v>
       </c>
       <c r="W52">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="X52" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Y52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AB52">
         <v>0</v>
       </c>
       <c r="AC52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH52" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI52" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:35">
       <c r="A53">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
@@ -4767,7 +4810,7 @@
         <v>56</v>
       </c>
       <c r="G53">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -4776,10 +4819,10 @@
         <v>63</v>
       </c>
       <c r="J53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N53" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4788,60 +4831,60 @@
         <v>2026</v>
       </c>
       <c r="R53">
-        <v>18056705</v>
+        <v>17941132</v>
       </c>
       <c r="S53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U53" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V53" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25135543982</v>
       </c>
       <c r="W53">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="X53" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="Y53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AB53">
         <v>0</v>
       </c>
       <c r="AC53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH53" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI53" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:35">
       <c r="A54">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C54" t="s">
         <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G54">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -4862,37 +4905,37 @@
         <v>2026</v>
       </c>
       <c r="R54">
-        <v>18164501</v>
+        <v>17941146</v>
       </c>
       <c r="S54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U54" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V54" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25232241898</v>
       </c>
       <c r="W54">
         <v>-8</v>
       </c>
       <c r="X54" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="Y54" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AB54">
         <v>0</v>
       </c>
       <c r="AC54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH54" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI54" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -4915,7 +4958,7 @@
         <v>57</v>
       </c>
       <c r="G55">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4936,45 +4979,45 @@
         <v>2026</v>
       </c>
       <c r="R55">
-        <v>18178138</v>
+        <v>18178132</v>
       </c>
       <c r="S55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U55" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V55" s="1">
-        <v>46266.25259008102</v>
+        <v>46266.25258784722</v>
       </c>
       <c r="W55">
         <v>-8</v>
       </c>
       <c r="X55" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y55" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AB55">
         <v>0</v>
       </c>
       <c r="AC55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH55" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI55" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:35">
       <c r="A56">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
         <v>50</v>
@@ -4989,7 +5032,7 @@
         <v>56</v>
       </c>
       <c r="G56">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -5001,7 +5044,7 @@
         <v>89</v>
       </c>
       <c r="N56" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P56">
         <v>8</v>
@@ -5010,45 +5053,45 @@
         <v>2026</v>
       </c>
       <c r="R56">
-        <v>17398883</v>
+        <v>17222405</v>
       </c>
       <c r="S56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U56" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V56" s="1">
-        <v>46266.25305</v>
+        <v>46266.25161940972</v>
       </c>
       <c r="W56">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="X56" t="s">
         <v>125</v>
       </c>
       <c r="Y56" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB56">
         <v>0</v>
       </c>
       <c r="AC56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH56" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI56" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:35">
       <c r="A57">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
         <v>50</v>
@@ -5063,7 +5106,7 @@
         <v>56</v>
       </c>
       <c r="G57">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -5075,7 +5118,7 @@
         <v>89</v>
       </c>
       <c r="N57" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P57">
         <v>8</v>
@@ -5084,60 +5127,60 @@
         <v>2026</v>
       </c>
       <c r="R57">
-        <v>16962107</v>
+        <v>17941156</v>
       </c>
       <c r="S57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U57" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V57" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25232392361</v>
       </c>
       <c r="W57">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="X57" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Y57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AB57">
         <v>0</v>
       </c>
       <c r="AC57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH57" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI57" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:35">
       <c r="A58">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C58" t="s">
         <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F58" t="s">
         <v>56</v>
       </c>
       <c r="G58">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -5149,7 +5192,7 @@
         <v>89</v>
       </c>
       <c r="N58" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P58">
         <v>8</v>
@@ -5158,60 +5201,60 @@
         <v>2026</v>
       </c>
       <c r="R58">
-        <v>17042317</v>
+        <v>18056705</v>
       </c>
       <c r="S58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U58" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V58" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W58">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="X58" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="Y58" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AB58">
         <v>0</v>
       </c>
       <c r="AC58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH58" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI58" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:35">
       <c r="A59">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G59">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -5223,7 +5266,7 @@
         <v>89</v>
       </c>
       <c r="N59" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P59">
         <v>8</v>
@@ -5232,37 +5275,37 @@
         <v>2026</v>
       </c>
       <c r="R59">
-        <v>17941166</v>
+        <v>18164501</v>
       </c>
       <c r="S59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U59" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V59" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W59">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="X59" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Y59" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AB59">
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH59" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI59" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5285,7 +5328,7 @@
         <v>57</v>
       </c>
       <c r="G60">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5297,7 +5340,7 @@
         <v>89</v>
       </c>
       <c r="N60" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P60">
         <v>8</v>
@@ -5306,37 +5349,37 @@
         <v>2026</v>
       </c>
       <c r="R60">
-        <v>18178144</v>
+        <v>18178138</v>
       </c>
       <c r="S60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U60" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V60" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25259008102</v>
       </c>
       <c r="W60">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="X60" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AB60">
         <v>0</v>
       </c>
       <c r="AC60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH60" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI60" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5359,7 +5402,7 @@
         <v>56</v>
       </c>
       <c r="G61">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5371,7 +5414,7 @@
         <v>90</v>
       </c>
       <c r="N61" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P61">
         <v>8</v>
@@ -5380,60 +5423,60 @@
         <v>2026</v>
       </c>
       <c r="R61">
-        <v>17399270</v>
+        <v>17398883</v>
       </c>
       <c r="S61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U61" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V61" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25305</v>
       </c>
       <c r="W61">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="X61" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Y61" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB61">
         <v>0</v>
       </c>
       <c r="AC61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH61" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI61" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:35">
       <c r="A62">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
         <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F62" t="s">
         <v>56</v>
       </c>
       <c r="G62">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -5445,7 +5488,7 @@
         <v>90</v>
       </c>
       <c r="N62" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P62">
         <v>8</v>
@@ -5454,45 +5497,45 @@
         <v>2026</v>
       </c>
       <c r="R62">
-        <v>17042505</v>
+        <v>16962107</v>
       </c>
       <c r="S62" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V62" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W62">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="X62" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="Y62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB62">
         <v>0</v>
       </c>
       <c r="AC62" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH62" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI62" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:35">
       <c r="A63">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
         <v>50</v>
@@ -5501,13 +5544,13 @@
         <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F63" t="s">
         <v>56</v>
       </c>
       <c r="G63">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5519,7 +5562,7 @@
         <v>90</v>
       </c>
       <c r="N63" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P63">
         <v>8</v>
@@ -5528,60 +5571,60 @@
         <v>2026</v>
       </c>
       <c r="R63">
-        <v>17952421</v>
+        <v>17042317</v>
       </c>
       <c r="S63" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U63" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V63" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W63">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="X63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AB63">
         <v>0</v>
       </c>
       <c r="AC63" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH63" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI63" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:35">
       <c r="A64">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
         <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G64">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5593,7 +5636,7 @@
         <v>90</v>
       </c>
       <c r="N64" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P64">
         <v>8</v>
@@ -5602,111 +5645,111 @@
         <v>2026</v>
       </c>
       <c r="R64">
-        <v>18178174</v>
+        <v>17941166</v>
       </c>
       <c r="S64" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U64" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V64" s="1">
-        <v>46266.25369988426</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W64">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="X64" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="Y64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB64">
         <v>0</v>
       </c>
       <c r="AC64" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH64" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AI64" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:35">
       <c r="A65">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E65" t="s">
         <v>55</v>
       </c>
       <c r="F65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G65">
-        <v>11001</v>
+        <v>953</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N65" s="1">
-        <v>46321</v>
+        <v>46290</v>
       </c>
       <c r="P65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q65">
         <v>2026</v>
       </c>
       <c r="R65">
-        <v>16962455</v>
+        <v>18178144</v>
       </c>
       <c r="S65" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="U65" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V65" s="1">
-        <v>46266.21595836805</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W65">
-        <v>-54</v>
+        <v>-23</v>
       </c>
       <c r="X65" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Y65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AB65">
         <v>0</v>
       </c>
       <c r="AC65" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="AH65" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AI65" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -5729,66 +5772,66 @@
         <v>56</v>
       </c>
       <c r="G66">
-        <v>7877</v>
+        <v>7022</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J66" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="N66" s="1">
-        <v>46321</v>
+        <v>46283</v>
       </c>
       <c r="P66">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q66">
         <v>2026</v>
       </c>
       <c r="R66">
-        <v>17399331</v>
+        <v>17399270</v>
       </c>
       <c r="S66" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="U66" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V66" s="1">
-        <v>46266.21572962963</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W66">
-        <v>-54</v>
+        <v>-16</v>
       </c>
       <c r="X66" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="Y66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="AH66" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AI66" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:35">
       <c r="A67">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
@@ -5797,72 +5840,72 @@
         <v>51</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F67" t="s">
         <v>56</v>
       </c>
       <c r="G67">
-        <v>9774</v>
+        <v>7022</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N67" s="1">
-        <v>46321</v>
+        <v>46283</v>
       </c>
       <c r="P67">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q67">
         <v>2026</v>
       </c>
       <c r="R67">
-        <v>16976322</v>
+        <v>17042505</v>
       </c>
       <c r="S67" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="U67" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V67" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W67">
-        <v>-54</v>
+        <v>-16</v>
       </c>
       <c r="X67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Y67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB67">
         <v>0</v>
       </c>
       <c r="AC67" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="AH67" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AI67" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:35">
       <c r="A68">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
@@ -5877,140 +5920,146 @@
         <v>56</v>
       </c>
       <c r="G68">
-        <v>7027</v>
+        <v>7022</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J68" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N68" s="1">
-        <v>46321</v>
+        <v>46283</v>
       </c>
       <c r="P68">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q68">
         <v>2026</v>
       </c>
       <c r="R68">
-        <v>17399291</v>
+        <v>17952421</v>
       </c>
       <c r="S68" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="U68" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V68" s="1">
-        <v>46266.00006921296</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W68">
-        <v>-54</v>
+        <v>-16</v>
       </c>
       <c r="X68" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>161</v>
       </c>
       <c r="AB68">
         <v>0</v>
       </c>
       <c r="AC68" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="AH68" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AI68" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:35">
       <c r="A69">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C69" t="s">
         <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E69" t="s">
         <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G69">
-        <v>7027</v>
+        <v>7022</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N69" s="1">
-        <v>46321</v>
+        <v>46283</v>
       </c>
       <c r="P69">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q69">
         <v>2026</v>
       </c>
       <c r="R69">
-        <v>16962349</v>
+        <v>18178174</v>
       </c>
       <c r="S69" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="U69" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V69" s="1">
-        <v>46266.00006921296</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W69">
-        <v>-54</v>
+        <v>-16</v>
       </c>
       <c r="X69" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>162</v>
       </c>
       <c r="AB69">
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="AH69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AI69" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:35">
       <c r="A70">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C70" t="s">
         <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E70" t="s">
         <v>55</v>
@@ -6019,7 +6068,7 @@
         <v>56</v>
       </c>
       <c r="G70">
-        <v>7027</v>
+        <v>11001</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -6028,46 +6077,632 @@
         <v>64</v>
       </c>
       <c r="J70" t="s">
+        <v>92</v>
+      </c>
+      <c r="N70" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P70">
+        <v>7</v>
+      </c>
+      <c r="Q70">
+        <v>2026</v>
+      </c>
+      <c r="R70">
+        <v>16962453</v>
+      </c>
+      <c r="S70" t="s">
+        <v>55</v>
+      </c>
+      <c r="U70" t="s">
+        <v>121</v>
+      </c>
+      <c r="V70" s="1">
+        <v>46267.66131466435</v>
+      </c>
+      <c r="W70">
+        <v>8</v>
+      </c>
+      <c r="X70" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="1:35">
+      <c r="A71">
+        <v>6404</v>
+      </c>
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" t="s">
+        <v>50</v>
+      </c>
+      <c r="D71" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" t="s">
+        <v>55</v>
+      </c>
+      <c r="F71" t="s">
+        <v>56</v>
+      </c>
+      <c r="G71">
+        <v>11001</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>64</v>
+      </c>
+      <c r="J71" t="s">
+        <v>92</v>
+      </c>
+      <c r="N71" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P71">
+        <v>9</v>
+      </c>
+      <c r="Q71">
+        <v>2026</v>
+      </c>
+      <c r="R71">
+        <v>16962455</v>
+      </c>
+      <c r="S71" t="s">
+        <v>55</v>
+      </c>
+      <c r="U71" t="s">
+        <v>122</v>
+      </c>
+      <c r="V71" s="1">
+        <v>46266.21595836805</v>
+      </c>
+      <c r="W71">
+        <v>-54</v>
+      </c>
+      <c r="X71" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="1:35">
+      <c r="A72">
+        <v>5417</v>
+      </c>
+      <c r="B72" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72" t="s">
+        <v>50</v>
+      </c>
+      <c r="D72" t="s">
+        <v>51</v>
+      </c>
+      <c r="E72" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" t="s">
+        <v>56</v>
+      </c>
+      <c r="G72">
+        <v>7877</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" t="s">
+        <v>64</v>
+      </c>
+      <c r="J72" t="s">
+        <v>65</v>
+      </c>
+      <c r="N72" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P72">
+        <v>7</v>
+      </c>
+      <c r="Q72">
+        <v>2026</v>
+      </c>
+      <c r="R72">
+        <v>17399329</v>
+      </c>
+      <c r="S72" t="s">
+        <v>55</v>
+      </c>
+      <c r="U72" t="s">
+        <v>121</v>
+      </c>
+      <c r="V72" s="1">
+        <v>46267.66006940972</v>
+      </c>
+      <c r="W72">
+        <v>8</v>
+      </c>
+      <c r="X72" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:35">
+      <c r="A73">
+        <v>5417</v>
+      </c>
+      <c r="B73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" t="s">
+        <v>51</v>
+      </c>
+      <c r="E73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F73" t="s">
+        <v>56</v>
+      </c>
+      <c r="G73">
+        <v>7877</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" t="s">
+        <v>64</v>
+      </c>
+      <c r="J73" t="s">
+        <v>65</v>
+      </c>
+      <c r="N73" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P73">
+        <v>9</v>
+      </c>
+      <c r="Q73">
+        <v>2026</v>
+      </c>
+      <c r="R73">
+        <v>17399331</v>
+      </c>
+      <c r="S73" t="s">
+        <v>55</v>
+      </c>
+      <c r="U73" t="s">
+        <v>122</v>
+      </c>
+      <c r="V73" s="1">
+        <v>46266.21572962963</v>
+      </c>
+      <c r="W73">
+        <v>-54</v>
+      </c>
+      <c r="X73" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI73" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="74" spans="1:35">
+      <c r="A74">
+        <v>6486</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" t="s">
+        <v>55</v>
+      </c>
+      <c r="F74" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74">
+        <v>9774</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>64</v>
+      </c>
+      <c r="J74" t="s">
         <v>93</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N74" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P74">
+        <v>7</v>
+      </c>
+      <c r="Q74">
+        <v>2026</v>
+      </c>
+      <c r="R74">
+        <v>16976320</v>
+      </c>
+      <c r="S74" t="s">
+        <v>55</v>
+      </c>
+      <c r="U74" t="s">
+        <v>121</v>
+      </c>
+      <c r="V74" s="1">
+        <v>46267.67127083334</v>
+      </c>
+      <c r="W74">
+        <v>8</v>
+      </c>
+      <c r="X74" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI74" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:35">
+      <c r="A75">
+        <v>6486</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" t="s">
+        <v>55</v>
+      </c>
+      <c r="F75" t="s">
+        <v>56</v>
+      </c>
+      <c r="G75">
+        <v>9774</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>64</v>
+      </c>
+      <c r="J75" t="s">
+        <v>93</v>
+      </c>
+      <c r="N75" s="1">
         <v>46321</v>
       </c>
-      <c r="P70">
+      <c r="P75">
         <v>9</v>
       </c>
-      <c r="Q70">
-        <v>2026</v>
-      </c>
-      <c r="R70">
+      <c r="Q75">
+        <v>2026</v>
+      </c>
+      <c r="R75">
+        <v>16976322</v>
+      </c>
+      <c r="S75" t="s">
+        <v>55</v>
+      </c>
+      <c r="U75" t="s">
+        <v>122</v>
+      </c>
+      <c r="V75" s="1">
+        <v>46266.21550011574</v>
+      </c>
+      <c r="W75">
+        <v>-54</v>
+      </c>
+      <c r="X75" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI75" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:35">
+      <c r="A76">
+        <v>5417</v>
+      </c>
+      <c r="B76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" t="s">
+        <v>55</v>
+      </c>
+      <c r="F76" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76">
+        <v>7027</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>64</v>
+      </c>
+      <c r="J76" t="s">
+        <v>94</v>
+      </c>
+      <c r="N76" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P76">
+        <v>9</v>
+      </c>
+      <c r="Q76">
+        <v>2026</v>
+      </c>
+      <c r="R76">
+        <v>17399291</v>
+      </c>
+      <c r="S76" t="s">
+        <v>55</v>
+      </c>
+      <c r="U76" t="s">
+        <v>122</v>
+      </c>
+      <c r="V76" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W76">
+        <v>-54</v>
+      </c>
+      <c r="X76" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI76" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" spans="1:35">
+      <c r="A77">
+        <v>6404</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>50</v>
+      </c>
+      <c r="D77" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" t="s">
+        <v>55</v>
+      </c>
+      <c r="F77" t="s">
+        <v>56</v>
+      </c>
+      <c r="G77">
+        <v>7027</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>64</v>
+      </c>
+      <c r="J77" t="s">
+        <v>94</v>
+      </c>
+      <c r="N77" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P77">
+        <v>9</v>
+      </c>
+      <c r="Q77">
+        <v>2026</v>
+      </c>
+      <c r="R77">
+        <v>16962349</v>
+      </c>
+      <c r="S77" t="s">
+        <v>55</v>
+      </c>
+      <c r="U77" t="s">
+        <v>122</v>
+      </c>
+      <c r="V77" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W77">
+        <v>-54</v>
+      </c>
+      <c r="X77" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI77" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="78" spans="1:35">
+      <c r="A78">
+        <v>6486</v>
+      </c>
+      <c r="B78" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" t="s">
+        <v>50</v>
+      </c>
+      <c r="D78" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" t="s">
+        <v>55</v>
+      </c>
+      <c r="F78" t="s">
+        <v>56</v>
+      </c>
+      <c r="G78">
+        <v>7027</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" t="s">
+        <v>64</v>
+      </c>
+      <c r="J78" t="s">
+        <v>94</v>
+      </c>
+      <c r="N78" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P78">
+        <v>9</v>
+      </c>
+      <c r="Q78">
+        <v>2026</v>
+      </c>
+      <c r="R78">
         <v>16976238</v>
       </c>
-      <c r="S70" t="s">
-        <v>55</v>
-      </c>
-      <c r="U70" t="s">
-        <v>118</v>
-      </c>
-      <c r="V70" s="1">
+      <c r="S78" t="s">
+        <v>55</v>
+      </c>
+      <c r="U78" t="s">
+        <v>122</v>
+      </c>
+      <c r="V78" s="1">
         <v>46266.00006921296</v>
       </c>
-      <c r="W70">
+      <c r="W78">
         <v>-54</v>
       </c>
-      <c r="X70" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH70" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>165</v>
+      <c r="X78" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="197">
   <si>
     <t>CodCliente</t>
   </si>
@@ -202,6 +202,9 @@
     <t>DP - DEPTO. PESSOAL</t>
   </si>
   <si>
+    <t>EF - INDUSTRIA</t>
+  </si>
+  <si>
     <t>EF - VAREJO</t>
   </si>
   <si>
@@ -235,6 +238,9 @@
     <t>Outras Receitas</t>
   </si>
   <si>
+    <t>Contribuição Assistencial</t>
+  </si>
+  <si>
     <t>Envio Arq. eConsignado Cliente</t>
   </si>
   <si>
@@ -253,9 +259,42 @@
     <t>Relação Bancária - Salário</t>
   </si>
   <si>
+    <t>Bloco K</t>
+  </si>
+  <si>
+    <t>Cobrança da Carta de Correção</t>
+  </si>
+  <si>
+    <t>Cobrança da Primeira NFe</t>
+  </si>
+  <si>
+    <t>Cobrança da Última NFe</t>
+  </si>
+  <si>
     <t>Cobrança de conta de energia elétrica</t>
   </si>
   <si>
+    <t>Cobrança de D.I.</t>
+  </si>
+  <si>
+    <t>Cobrança de Faturamento</t>
+  </si>
+  <si>
+    <t>Cobrança de Locação</t>
+  </si>
+  <si>
+    <t>Cobrança de NF entrada (Mensal)</t>
+  </si>
+  <si>
+    <t>Cobrança de NF saída (Mensal)</t>
+  </si>
+  <si>
+    <t>Cobrança de NF's Canceladas</t>
+  </si>
+  <si>
+    <t>Cobrança de NF's Inutilizadas</t>
+  </si>
+  <si>
     <t>Cobrança de EFD Contribuições</t>
   </si>
   <si>
@@ -304,12 +343,12 @@
     <t>01/09/2026</t>
   </si>
   <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
     <t>02/09/2026</t>
   </si>
   <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
     <t>04/09/2026</t>
   </si>
   <si>
@@ -337,6 +376,9 @@
     <t>Isabela Lemos</t>
   </si>
   <si>
+    <t>Jakeline Silva</t>
+  </si>
+  <si>
     <t>Mikael Teixeira</t>
   </si>
   <si>
@@ -346,7 +388,19 @@
     <t>Santos Karina</t>
   </si>
   <si>
-    <t>Jakeline Silva</t>
+    <t>Elaine Assis</t>
+  </si>
+  <si>
+    <t>Luan Batista</t>
+  </si>
+  <si>
+    <t>Nayara Oliveira</t>
+  </si>
+  <si>
+    <t>Rodrigo Souza</t>
+  </si>
+  <si>
+    <t>Priscila Volpe</t>
   </si>
   <si>
     <t>Cristina Leite</t>
@@ -367,15 +421,15 @@
     <t>Karina Santos</t>
   </si>
   <si>
+    <t>David Bragança</t>
+  </si>
+  <si>
     <t>Sara Cavalheiro</t>
   </si>
   <si>
     <t>Leandro Matos</t>
   </si>
   <si>
-    <t>David Bragança</t>
-  </si>
-  <si>
     <t>Ricardo Fischer</t>
   </si>
   <si>
@@ -385,6 +439,9 @@
     <t>Baixa antecipada</t>
   </si>
   <si>
+    <t>Baixada no prazo</t>
+  </si>
+  <si>
     <t xml:space="preserve">GTG </t>
   </si>
   <si>
@@ -425,6 +482,10 @@
   </si>
   <si>
     <t>Aguardando a Liberação da Gerência de Contas - Data Comentário: 31/08/2026 18:11</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/09/2026 
+Previsão: 03/09 - Data Comentário: 31/08/2026 08:37</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 01/09/2026 
@@ -446,8 +507,15 @@
 Ítalo informou que será enviado amanhã, pois está fechando as vendas/comissões hoje. Folha fecha 30. - Data Comentário: 01/09/2026 12:01</t>
   </si>
   <si>
+    <t>Atraso por parte do cliente no envio dos documentos necessários, o mesmo vem sendo cobrado diariamente e informou o envio até o fim do dia 02/09 - Data Comentário: 02/09/2026 12:36</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 04/09/2026 
 Enviado somente após finalizar a FP - Data Comentário: 28/08/2026 09:46</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/09/2026 
+Tarefa a ser realizada em: 02/09/2026 - Data Comentário: 02/09/2026 16:24</t>
   </si>
   <si>
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/09/2026 00:58</t>
@@ -879,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI78"/>
+  <dimension ref="A1:AI126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1018,7 +1086,7 @@
         <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N2" s="1">
         <v>46259</v>
@@ -1033,37 +1101,37 @@
         <v>18096486</v>
       </c>
       <c r="S2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="T2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="V2" s="1">
         <v>46266.57730150463</v>
       </c>
       <c r="W2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X2" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="Y2" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AH2" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI2" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1095,7 +1163,7 @@
         <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N3" s="1">
         <v>46259</v>
@@ -1110,37 +1178,37 @@
         <v>18254143</v>
       </c>
       <c r="S3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="U3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="V3" s="1">
         <v>46266.41668148148</v>
       </c>
       <c r="W3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="Y3" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="AB3">
         <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="AH3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI3" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1172,7 +1240,7 @@
         <v>59</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N4" s="1">
         <v>46279</v>
@@ -1187,34 +1255,34 @@
         <v>17968041</v>
       </c>
       <c r="S4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T4" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="U4" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V4" s="1">
-        <v>46267.4463130787</v>
+        <v>46267.75233784723</v>
       </c>
       <c r="W4">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X4" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="AB4">
         <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="AH4" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI4" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1246,7 +1314,7 @@
         <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N5" s="1">
         <v>46279</v>
@@ -1261,34 +1329,34 @@
         <v>17042643</v>
       </c>
       <c r="S5" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="T5" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U5" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V5" s="1">
-        <v>46267.44631975694</v>
+        <v>46267.75233927083</v>
       </c>
       <c r="W5">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X5" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="AB5">
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AH5" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI5" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1320,7 +1388,7 @@
         <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N6" s="1">
         <v>46279</v>
@@ -1335,34 +1403,34 @@
         <v>16960110</v>
       </c>
       <c r="S6" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="T6" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U6" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V6" s="1">
-        <v>46267.44632179398</v>
+        <v>46267.7523394676</v>
       </c>
       <c r="W6">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X6" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="AB6">
         <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AH6" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI6" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1394,7 +1462,7 @@
         <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1">
         <v>46279</v>
@@ -1409,34 +1477,34 @@
         <v>18163699</v>
       </c>
       <c r="S7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="T7" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U7" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V7" s="1">
-        <v>46267.44634035879</v>
+        <v>46267.75234278935</v>
       </c>
       <c r="W7">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X7" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="AB7">
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="AH7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI7" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1468,7 +1536,7 @@
         <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N8" s="1">
         <v>46279</v>
@@ -1483,34 +1551,34 @@
         <v>18178308</v>
       </c>
       <c r="S8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="T8" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="U8" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V8" s="1">
-        <v>46267.44634128473</v>
+        <v>46267.75234309028</v>
       </c>
       <c r="W8">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X8" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="AB8">
         <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="AH8" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI8" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1542,7 +1610,7 @@
         <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N9" s="1">
         <v>46279</v>
@@ -1557,34 +1625,34 @@
         <v>18187978</v>
       </c>
       <c r="S9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="T9" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U9" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V9" s="1">
-        <v>46267.44634366898</v>
+        <v>46267.75234383102</v>
       </c>
       <c r="W9">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X9" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="AB9">
         <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="AH9" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI9" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1616,7 +1684,7 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N10" s="1">
         <v>46279</v>
@@ -1631,34 +1699,34 @@
         <v>18241249</v>
       </c>
       <c r="S10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="T10" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="U10" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V10" s="1">
-        <v>46267.44634548611</v>
+        <v>46267.75234424769</v>
       </c>
       <c r="W10">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X10" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="AB10">
         <v>0</v>
       </c>
       <c r="AC10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="AH10" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI10" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1690,7 +1758,7 @@
         <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N11" s="1">
         <v>46293</v>
@@ -1705,34 +1773,34 @@
         <v>17955421</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T11" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V11" s="1">
         <v>46267.47365627315</v>
       </c>
       <c r="W11">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="X11" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB11">
         <v>0</v>
       </c>
       <c r="AC11" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH11" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI11" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -1764,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N12" s="1">
         <v>46283</v>
@@ -1779,34 +1847,34 @@
         <v>17399423</v>
       </c>
       <c r="S12" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="T12" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="U12" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V12" s="1">
         <v>46266.47620831019</v>
       </c>
       <c r="W12">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="X12" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="AB12">
         <v>0</v>
       </c>
       <c r="AC12" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="AH12" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI12" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -1838,7 +1906,7 @@
         <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N13" s="1">
         <v>46283</v>
@@ -1853,34 +1921,34 @@
         <v>18152557</v>
       </c>
       <c r="S13" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="T13" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="U13" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V13" s="1">
         <v>46267.57586420139</v>
       </c>
       <c r="W13">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="X13" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="AB13">
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="AH13" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI13" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -1912,13 +1980,13 @@
         <v>60</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N14" s="1">
         <v>46232</v>
       </c>
       <c r="O14" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -1930,28 +1998,28 @@
         <v>17688641</v>
       </c>
       <c r="U14" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="V14" s="1">
         <v>46266.44145744213</v>
       </c>
       <c r="W14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X14" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="Y14" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="AB14">
         <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="AI14" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -1983,7 +2051,7 @@
         <v>60</v>
       </c>
       <c r="J15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N15" s="1">
         <v>46290</v>
@@ -1998,25 +2066,25 @@
         <v>17688645</v>
       </c>
       <c r="U15" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V15" s="1">
         <v>46266.44156952546</v>
       </c>
       <c r="W15">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="X15" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AB15">
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="AI15" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2048,13 +2116,13 @@
         <v>60</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N16" s="1">
         <v>46260</v>
       </c>
       <c r="O16" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -2066,28 +2134,28 @@
         <v>17688891</v>
       </c>
       <c r="U16" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="V16" s="1">
         <v>46266.44152346065</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="Y16" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="AB16">
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="AI16" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2119,7 +2187,7 @@
         <v>60</v>
       </c>
       <c r="J17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N17" s="1">
         <v>46286</v>
@@ -2134,34 +2202,34 @@
         <v>16962141</v>
       </c>
       <c r="S17" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="T17" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U17" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V17" s="1">
         <v>46266.37634084491</v>
       </c>
       <c r="W17">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="X17" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="AB17">
         <v>0</v>
       </c>
       <c r="AC17" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AH17" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI17" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2193,7 +2261,7 @@
         <v>60</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N18" s="1">
         <v>46286</v>
@@ -2208,34 +2276,34 @@
         <v>17955384</v>
       </c>
       <c r="S18" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T18" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U18" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V18" s="1">
         <v>46267.47452163194</v>
       </c>
       <c r="W18">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="X18" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB18">
         <v>0</v>
       </c>
       <c r="AC18" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH18" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI18" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2267,7 +2335,7 @@
         <v>60</v>
       </c>
       <c r="J19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N19" s="1">
         <v>46286</v>
@@ -2282,34 +2350,34 @@
         <v>17955238</v>
       </c>
       <c r="S19" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T19" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U19" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V19" s="1">
         <v>46267.4745221412</v>
       </c>
       <c r="W19">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="X19" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB19">
         <v>0</v>
       </c>
       <c r="AC19" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH19" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI19" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2341,7 +2409,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N20" s="1">
         <v>46286</v>
@@ -2356,34 +2424,34 @@
         <v>18056729</v>
       </c>
       <c r="S20" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T20" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U20" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V20" s="1">
         <v>46267.47452299768</v>
       </c>
       <c r="W20">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="X20" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB20">
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH20" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI20" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2415,7 +2483,7 @@
         <v>60</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N21" s="1">
         <v>46279</v>
@@ -2430,34 +2498,34 @@
         <v>17399444</v>
       </c>
       <c r="S21" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="T21" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="U21" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V21" s="1">
-        <v>46267.4462272338</v>
+        <v>46267.75231010417</v>
       </c>
       <c r="W21">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X21" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="AH21" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI21" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2489,7 +2557,7 @@
         <v>60</v>
       </c>
       <c r="J22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N22" s="1">
         <v>46279</v>
@@ -2504,34 +2572,34 @@
         <v>17955434</v>
       </c>
       <c r="S22" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T22" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U22" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V22" s="1">
-        <v>46267.44632673611</v>
+        <v>46267.75234059028</v>
       </c>
       <c r="W22">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X22" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB22">
         <v>0</v>
       </c>
       <c r="AC22" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH22" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI22" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2563,7 +2631,7 @@
         <v>60</v>
       </c>
       <c r="J23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N23" s="1">
         <v>46279</v>
@@ -2578,34 +2646,34 @@
         <v>17955274</v>
       </c>
       <c r="S23" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T23" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U23" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V23" s="1">
-        <v>46267.44632704861</v>
+        <v>46267.7523409375</v>
       </c>
       <c r="W23">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X23" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB23">
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH23" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI23" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2637,7 +2705,7 @@
         <v>60</v>
       </c>
       <c r="J24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N24" s="1">
         <v>46279</v>
@@ -2652,111 +2720,114 @@
         <v>18056832</v>
       </c>
       <c r="S24" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T24" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U24" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V24" s="1">
-        <v>46267.44633364584</v>
+        <v>46267.75234170139</v>
       </c>
       <c r="W24">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X24" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="AH24" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI24" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:35">
       <c r="A25">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s">
         <v>56</v>
       </c>
       <c r="G25">
-        <v>11542</v>
+        <v>5859</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I25" t="s">
         <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N25" s="1">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="O25" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>2026</v>
       </c>
       <c r="R25">
-        <v>18248555</v>
+        <v>18052440</v>
       </c>
       <c r="S25" t="s">
-        <v>107</v>
+        <v>120</v>
+      </c>
+      <c r="T25" t="s">
+        <v>135</v>
       </c>
       <c r="U25" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="V25" s="1">
-        <v>46267.55838734953</v>
+        <v>46268.37896984954</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X25" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="Y25" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="AH25" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="AI25" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -2779,75 +2850,75 @@
         <v>56</v>
       </c>
       <c r="G26">
-        <v>5905</v>
+        <v>11542</v>
       </c>
       <c r="H26">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
         <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N26" s="1">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="O26" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="P26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>2026</v>
       </c>
       <c r="R26">
-        <v>17399096</v>
+        <v>18248555</v>
       </c>
       <c r="S26" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="U26" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="V26" s="1">
-        <v>46267.66088636574</v>
+        <v>46267.55838734953</v>
       </c>
       <c r="W26">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="Y26" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="AB26">
         <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AH26" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="AI26" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:35">
       <c r="A27">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
@@ -2865,13 +2936,13 @@
         <v>61</v>
       </c>
       <c r="J27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N27" s="1">
         <v>46269</v>
       </c>
       <c r="O27" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -2880,48 +2951,45 @@
         <v>2026</v>
       </c>
       <c r="R27">
-        <v>18090219</v>
+        <v>17399096</v>
       </c>
       <c r="S27" t="s">
-        <v>108</v>
-      </c>
-      <c r="T27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="U27" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V27" s="1">
-        <v>46267.64795916666</v>
+        <v>46267.66088636574</v>
       </c>
       <c r="W27">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X27" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="Y27" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="AB27">
         <v>0</v>
       </c>
       <c r="AC27" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="AI27" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:35">
       <c r="A28">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>50</v>
@@ -2930,10 +2998,10 @@
         <v>52</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28">
         <v>5905</v>
@@ -2945,13 +3013,13 @@
         <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N28" s="1">
         <v>46269</v>
       </c>
       <c r="O28" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="P28">
         <v>8</v>
@@ -2960,48 +3028,48 @@
         <v>2026</v>
       </c>
       <c r="R28">
-        <v>18179132</v>
+        <v>18090219</v>
       </c>
       <c r="S28" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="T28" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="U28" t="s">
+        <v>140</v>
+      </c>
+      <c r="V28" s="1">
+        <v>46267.64795916666</v>
+      </c>
+      <c r="W28">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="s">
         <v>122</v>
       </c>
-      <c r="V28" s="1">
-        <v>46267.4478849537</v>
-      </c>
-      <c r="W28">
-        <v>-2</v>
-      </c>
-      <c r="X28" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>109</v>
-      </c>
       <c r="AH28" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="AI28" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:35">
       <c r="A29">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
         <v>50</v>
@@ -3010,13 +3078,13 @@
         <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G29">
-        <v>5853</v>
+        <v>5905</v>
       </c>
       <c r="H29">
         <v>5784</v>
@@ -3025,10 +3093,13 @@
         <v>61</v>
       </c>
       <c r="J29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N29" s="1">
-        <v>46273</v>
+        <v>46269</v>
+      </c>
+      <c r="O29" t="s">
+        <v>111</v>
       </c>
       <c r="P29">
         <v>8</v>
@@ -3037,51 +3108,54 @@
         <v>2026</v>
       </c>
       <c r="R29">
-        <v>18090158</v>
+        <v>18179132</v>
       </c>
       <c r="S29" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="T29" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="U29" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V29" s="1">
-        <v>46267.64761306713</v>
+        <v>46267.4478849537</v>
       </c>
       <c r="W29">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="X29" t="s">
-        <v>128</v>
+        <v>145</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>160</v>
       </c>
       <c r="AB29">
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AH29" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="AI29" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:35">
       <c r="A30">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
         <v>55</v>
@@ -3090,7 +3164,7 @@
         <v>56</v>
       </c>
       <c r="G30">
-        <v>5838</v>
+        <v>5853</v>
       </c>
       <c r="H30">
         <v>5784</v>
@@ -3099,13 +3173,10 @@
         <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N30" s="1">
-        <v>46266</v>
-      </c>
-      <c r="O30" t="s">
-        <v>96</v>
+        <v>46273</v>
       </c>
       <c r="P30">
         <v>8</v>
@@ -3114,54 +3185,51 @@
         <v>2026</v>
       </c>
       <c r="R30">
-        <v>18157807</v>
+        <v>18090158</v>
       </c>
       <c r="S30" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="T30" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="U30" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="V30" s="1">
-        <v>46267.35832805555</v>
+        <v>46267.64761306713</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="X30" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AB30">
         <v>0</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AH30" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI30" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:35">
       <c r="A31">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
         <v>55</v>
@@ -3170,7 +3238,7 @@
         <v>56</v>
       </c>
       <c r="G31">
-        <v>5906</v>
+        <v>5838</v>
       </c>
       <c r="H31">
         <v>5784</v>
@@ -3179,13 +3247,13 @@
         <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N31" s="1">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="O31" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -3194,63 +3262,63 @@
         <v>2026</v>
       </c>
       <c r="R31">
-        <v>18090229</v>
+        <v>18157807</v>
       </c>
       <c r="S31" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="T31" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="U31" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="V31" s="1">
-        <v>46267.64800344907</v>
+        <v>46267.35832805555</v>
       </c>
       <c r="W31">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="Y31" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="AB31">
         <v>0</v>
       </c>
       <c r="AC31" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="AH31" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI31" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:35">
       <c r="A32">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
         <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32">
-        <v>5906</v>
+        <v>5838</v>
       </c>
       <c r="H32">
         <v>5784</v>
@@ -3259,13 +3327,13 @@
         <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N32" s="1">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="O32" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="P32">
         <v>8</v>
@@ -3274,40 +3342,40 @@
         <v>2026</v>
       </c>
       <c r="R32">
-        <v>18179139</v>
+        <v>18195915</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="T32" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="U32" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="V32" s="1">
-        <v>46267.44799793982</v>
+        <v>46267.74532275463</v>
       </c>
       <c r="W32">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="Y32" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="AB32">
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AH32" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI32" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3330,7 +3398,7 @@
         <v>56</v>
       </c>
       <c r="G33">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="H33">
         <v>5784</v>
@@ -3339,11 +3407,14 @@
         <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N33" s="1">
         <v>46273</v>
       </c>
+      <c r="O33" t="s">
+        <v>111</v>
+      </c>
       <c r="P33">
         <v>8</v>
       </c>
@@ -3351,37 +3422,40 @@
         <v>2026</v>
       </c>
       <c r="R33">
-        <v>18090239</v>
+        <v>18090229</v>
       </c>
       <c r="S33" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="T33" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="U33" t="s">
+        <v>140</v>
+      </c>
+      <c r="V33" s="1">
+        <v>46267.64800344907</v>
+      </c>
+      <c r="W33">
+        <v>-5</v>
+      </c>
+      <c r="X33" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="s">
         <v>122</v>
       </c>
-      <c r="V33" s="1">
-        <v>46267.648038125</v>
-      </c>
-      <c r="W33">
-        <v>-6</v>
-      </c>
-      <c r="X33" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>108</v>
-      </c>
       <c r="AH33" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI33" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3404,7 +3478,7 @@
         <v>57</v>
       </c>
       <c r="G34">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="H34">
         <v>5784</v>
@@ -3413,11 +3487,14 @@
         <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N34" s="1">
         <v>46273</v>
       </c>
+      <c r="O34" t="s">
+        <v>111</v>
+      </c>
       <c r="P34">
         <v>8</v>
       </c>
@@ -3425,51 +3502,54 @@
         <v>2026</v>
       </c>
       <c r="R34">
-        <v>18179146</v>
+        <v>18179139</v>
       </c>
       <c r="S34" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="T34" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="U34" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V34" s="1">
-        <v>46267.44824061343</v>
+        <v>46267.44799793982</v>
       </c>
       <c r="W34">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X34" t="s">
-        <v>126</v>
+        <v>145</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>163</v>
       </c>
       <c r="AB34">
         <v>0</v>
       </c>
       <c r="AC34" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="AH34" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI34" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:35">
       <c r="A35">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
         <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
         <v>55</v>
@@ -3478,19 +3558,19 @@
         <v>56</v>
       </c>
       <c r="G35">
-        <v>6883</v>
+        <v>5907</v>
       </c>
       <c r="H35">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N35" s="1">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3499,72 +3579,72 @@
         <v>2026</v>
       </c>
       <c r="R35">
-        <v>17399250</v>
+        <v>18090239</v>
       </c>
       <c r="S35" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="T35" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="U35" t="s">
+        <v>140</v>
+      </c>
+      <c r="V35" s="1">
+        <v>46267.648038125</v>
+      </c>
+      <c r="W35">
+        <v>-5</v>
+      </c>
+      <c r="X35" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="s">
         <v>122</v>
       </c>
-      <c r="V35" s="1">
-        <v>46266.37636392361</v>
-      </c>
-      <c r="W35">
-        <v>-8</v>
-      </c>
-      <c r="X35" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>111</v>
-      </c>
       <c r="AH35" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI35" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:35">
       <c r="A36">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G36">
-        <v>1836</v>
+        <v>5907</v>
       </c>
       <c r="H36">
-        <v>1788</v>
+        <v>5784</v>
       </c>
       <c r="I36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J36" t="s">
         <v>80</v>
       </c>
       <c r="N36" s="1">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="P36">
         <v>8</v>
@@ -3573,45 +3653,45 @@
         <v>2026</v>
       </c>
       <c r="R36">
-        <v>17398975</v>
+        <v>18179146</v>
       </c>
       <c r="S36" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="T36" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="U36" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V36" s="1">
-        <v>46266.37598834491</v>
+        <v>46267.44824061343</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="X36" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="AB36">
         <v>0</v>
       </c>
       <c r="AC36" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AH36" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI36" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:35">
       <c r="A37">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
         <v>50</v>
@@ -3626,19 +3706,19 @@
         <v>56</v>
       </c>
       <c r="G37">
-        <v>1836</v>
+        <v>11550</v>
       </c>
       <c r="H37">
-        <v>1788</v>
+        <v>1862</v>
       </c>
       <c r="I37" t="s">
         <v>62</v>
       </c>
       <c r="J37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N37" s="1">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="P37">
         <v>8</v>
@@ -3647,45 +3727,45 @@
         <v>2026</v>
       </c>
       <c r="R37">
-        <v>18085220</v>
+        <v>17988603</v>
       </c>
       <c r="S37" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="T37" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U37" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V37" s="1">
-        <v>46266.45957881944</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="X37" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="AB37">
         <v>0</v>
       </c>
       <c r="AC37" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH37" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI37" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="A38">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>50</v>
@@ -3694,16 +3774,16 @@
         <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
         <v>56</v>
       </c>
       <c r="G38">
-        <v>6802</v>
+        <v>11550</v>
       </c>
       <c r="H38">
-        <v>1788</v>
+        <v>1862</v>
       </c>
       <c r="I38" t="s">
         <v>62</v>
@@ -3712,7 +3792,7 @@
         <v>81</v>
       </c>
       <c r="N38" s="1">
-        <v>46269</v>
+        <v>46286</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3721,45 +3801,45 @@
         <v>2026</v>
       </c>
       <c r="R38">
-        <v>17399220</v>
+        <v>18048493</v>
       </c>
       <c r="S38" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="T38" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U38" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V38" s="1">
-        <v>46266.37645462963</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="W38">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="X38" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="AB38">
         <v>0</v>
       </c>
       <c r="AC38" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH38" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI38" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="A39">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
         <v>50</v>
@@ -3771,22 +3851,22 @@
         <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G39">
-        <v>6801</v>
+        <v>11550</v>
       </c>
       <c r="H39">
-        <v>1796</v>
+        <v>1862</v>
       </c>
       <c r="I39" t="s">
         <v>62</v>
       </c>
       <c r="J39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N39" s="1">
-        <v>46269</v>
+        <v>46286</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -3795,45 +3875,45 @@
         <v>2026</v>
       </c>
       <c r="R39">
-        <v>17399210</v>
+        <v>18214931</v>
       </c>
       <c r="S39" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="T39" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U39" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V39" s="1">
-        <v>46266.37649475694</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="W39">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="X39" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AB39">
         <v>0</v>
       </c>
       <c r="AC39" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="AH39" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI39" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:35">
       <c r="A40">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
         <v>50</v>
@@ -3848,19 +3928,19 @@
         <v>56</v>
       </c>
       <c r="G40">
-        <v>6014</v>
+        <v>11752</v>
       </c>
       <c r="H40">
-        <v>1788</v>
+        <v>11751</v>
       </c>
       <c r="I40" t="s">
         <v>62</v>
       </c>
       <c r="J40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N40" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -3869,45 +3949,45 @@
         <v>2026</v>
       </c>
       <c r="R40">
-        <v>17399136</v>
+        <v>18260411</v>
       </c>
       <c r="S40" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="T40" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U40" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V40" s="1">
-        <v>46266.37591180555</v>
+        <v>46267.7205502662</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X40" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="AB40">
         <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH40" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI40" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:35">
       <c r="A41">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
         <v>50</v>
@@ -3916,22 +3996,22 @@
         <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41" t="s">
         <v>56</v>
       </c>
       <c r="G41">
-        <v>6014</v>
+        <v>11752</v>
       </c>
       <c r="H41">
-        <v>1788</v>
+        <v>11751</v>
       </c>
       <c r="I41" t="s">
         <v>62</v>
       </c>
       <c r="J41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N41" s="1">
         <v>46268</v>
@@ -3943,73 +4023,76 @@
         <v>2026</v>
       </c>
       <c r="R41">
-        <v>18085231</v>
+        <v>18173143</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="T41" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U41" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V41" s="1">
-        <v>46266.45946195602</v>
+        <v>46267.79439748843</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH41" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI41" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:35">
       <c r="A42">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G42">
-        <v>6233</v>
+        <v>11752</v>
       </c>
       <c r="H42">
-        <v>6232</v>
+        <v>11751</v>
       </c>
       <c r="I42" t="s">
         <v>62</v>
       </c>
       <c r="J42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N42" s="1">
         <v>46268</v>
       </c>
+      <c r="O42" t="s">
+        <v>110</v>
+      </c>
       <c r="P42">
         <v>8</v>
       </c>
@@ -4017,69 +4100,72 @@
         <v>2026</v>
       </c>
       <c r="R42">
-        <v>17399176</v>
+        <v>18220251</v>
       </c>
       <c r="S42" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="T42" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U42" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V42" s="1">
-        <v>46266.37538684028</v>
+        <v>46267.79440011574</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="s">
-        <v>129</v>
+        <v>145</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>164</v>
       </c>
       <c r="AB42">
         <v>0</v>
       </c>
       <c r="AC42" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH42" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI42" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:35">
       <c r="A43">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
         <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G43">
-        <v>6233</v>
+        <v>11752</v>
       </c>
       <c r="H43">
-        <v>6232</v>
+        <v>11751</v>
       </c>
       <c r="I43" t="s">
         <v>62</v>
       </c>
       <c r="J43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N43" s="1">
         <v>46268</v>
@@ -4091,51 +4177,51 @@
         <v>2026</v>
       </c>
       <c r="R43">
-        <v>16962294</v>
+        <v>18214951</v>
       </c>
       <c r="S43" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="T43" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U43" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V43" s="1">
-        <v>46266.37538506944</v>
+        <v>46267.79439818287</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X43" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AB43">
         <v>0</v>
       </c>
       <c r="AC43" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="AH43" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI43" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:35">
       <c r="A44">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E44" t="s">
         <v>55</v>
@@ -4144,19 +4230,19 @@
         <v>56</v>
       </c>
       <c r="G44">
-        <v>6233</v>
+        <v>11748</v>
       </c>
       <c r="H44">
-        <v>6232</v>
+        <v>11747</v>
       </c>
       <c r="I44" t="s">
         <v>62</v>
       </c>
       <c r="J44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N44" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P44">
         <v>8</v>
@@ -4165,45 +4251,45 @@
         <v>2026</v>
       </c>
       <c r="R44">
-        <v>17948844</v>
+        <v>18260401</v>
       </c>
       <c r="S44" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="T44" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U44" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V44" s="1">
-        <v>46266.45895332176</v>
+        <v>46267.7202693287</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X44" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="AB44">
         <v>0</v>
       </c>
       <c r="AC44" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH44" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI44" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:35">
       <c r="A45">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
         <v>50</v>
@@ -4212,22 +4298,22 @@
         <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F45" t="s">
         <v>56</v>
       </c>
       <c r="G45">
-        <v>6233</v>
+        <v>11748</v>
       </c>
       <c r="H45">
-        <v>6232</v>
+        <v>11747</v>
       </c>
       <c r="I45" t="s">
         <v>62</v>
       </c>
       <c r="J45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N45" s="1">
         <v>46268</v>
@@ -4239,45 +4325,45 @@
         <v>2026</v>
       </c>
       <c r="R45">
-        <v>18085264</v>
+        <v>18173127</v>
       </c>
       <c r="S45" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="T45" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U45" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V45" s="1">
-        <v>46266.45874105324</v>
+        <v>46267.79409846065</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AB45">
         <v>0</v>
       </c>
       <c r="AC45" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH45" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI45" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:35">
       <c r="A46">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
         <v>50</v>
@@ -4286,22 +4372,22 @@
         <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F46" t="s">
         <v>56</v>
       </c>
       <c r="G46">
-        <v>6233</v>
+        <v>11748</v>
       </c>
       <c r="H46">
-        <v>6232</v>
+        <v>11747</v>
       </c>
       <c r="I46" t="s">
         <v>62</v>
       </c>
       <c r="J46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N46" s="1">
         <v>46268</v>
@@ -4313,45 +4399,45 @@
         <v>2026</v>
       </c>
       <c r="R46">
-        <v>17948989</v>
+        <v>18170386</v>
       </c>
       <c r="S46" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="T46" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U46" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V46" s="1">
-        <v>46266.45873584491</v>
+        <v>46267.79409725694</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AB46">
         <v>0</v>
       </c>
       <c r="AC46" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH46" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI46" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:35">
       <c r="A47">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
         <v>50</v>
@@ -4360,25 +4446,25 @@
         <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G47">
-        <v>11303</v>
+        <v>11748</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>11747</v>
       </c>
       <c r="I47" t="s">
         <v>62</v>
       </c>
       <c r="J47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N47" s="1">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="P47">
         <v>8</v>
@@ -4387,72 +4473,72 @@
         <v>2026</v>
       </c>
       <c r="R47">
-        <v>17949079</v>
+        <v>18220239</v>
       </c>
       <c r="S47" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="T47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U47" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V47" s="1">
-        <v>46267.44505795139</v>
+        <v>46267.79410239583</v>
       </c>
       <c r="W47">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="X47" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="AB47">
         <v>0</v>
       </c>
       <c r="AC47" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AH47" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI47" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="A48">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G48">
-        <v>945</v>
+        <v>11748</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>11747</v>
       </c>
       <c r="I48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J48" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N48" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P48">
         <v>8</v>
@@ -4461,51 +4547,51 @@
         <v>2026</v>
       </c>
       <c r="R48">
-        <v>16959938</v>
+        <v>18214939</v>
       </c>
       <c r="S48" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T48" t="s">
+        <v>126</v>
       </c>
       <c r="U48" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V48" s="1">
-        <v>46266.04180934028</v>
+        <v>46267.79409934028</v>
       </c>
       <c r="W48">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X48" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y48" t="s">
         <v>143</v>
       </c>
       <c r="AB48">
         <v>0</v>
       </c>
       <c r="AC48" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH48" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI48" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:35">
       <c r="A49">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
         <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
         <v>55</v>
@@ -4514,19 +4600,19 @@
         <v>56</v>
       </c>
       <c r="G49">
-        <v>945</v>
+        <v>11750</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>11749</v>
       </c>
       <c r="I49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N49" s="1">
-        <v>46283</v>
+        <v>46267</v>
       </c>
       <c r="P49">
         <v>8</v>
@@ -4535,72 +4621,72 @@
         <v>2026</v>
       </c>
       <c r="R49">
-        <v>18056695</v>
+        <v>18260406</v>
       </c>
       <c r="S49" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="T49" t="s">
+        <v>126</v>
       </c>
       <c r="U49" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V49" s="1">
-        <v>46266.08343295139</v>
+        <v>46267.72033356482</v>
       </c>
       <c r="W49">
-        <v>-16</v>
+        <v>1</v>
       </c>
       <c r="X49" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y49" t="s">
         <v>144</v>
       </c>
       <c r="AB49">
         <v>0</v>
       </c>
       <c r="AC49" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH49" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI49" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:35">
       <c r="A50">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C50" t="s">
         <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
         <v>54</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50">
-        <v>945</v>
+        <v>11750</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>11749</v>
       </c>
       <c r="I50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J50" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N50" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P50">
         <v>8</v>
@@ -4609,72 +4695,72 @@
         <v>2026</v>
       </c>
       <c r="R50">
-        <v>18164487</v>
+        <v>18173135</v>
       </c>
       <c r="S50" t="s">
-        <v>112</v>
+        <v>126</v>
+      </c>
+      <c r="T50" t="s">
+        <v>126</v>
       </c>
       <c r="U50" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V50" s="1">
-        <v>46266.08344398148</v>
+        <v>46267.79418105324</v>
       </c>
       <c r="W50">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X50" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="s">
         <v>126</v>
       </c>
-      <c r="Y50" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>112</v>
-      </c>
       <c r="AH50" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI50" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:35">
       <c r="A51">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F51" t="s">
         <v>56</v>
       </c>
       <c r="G51">
-        <v>946</v>
+        <v>11750</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>11749</v>
       </c>
       <c r="I51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N51" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P51">
         <v>8</v>
@@ -4683,72 +4769,72 @@
         <v>2026</v>
       </c>
       <c r="R51">
-        <v>17398869</v>
+        <v>18170394</v>
       </c>
       <c r="S51" t="s">
-        <v>112</v>
+        <v>126</v>
+      </c>
+      <c r="T51" t="s">
+        <v>126</v>
       </c>
       <c r="U51" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V51" s="1">
-        <v>46266.25077376157</v>
+        <v>46267.79418005787</v>
       </c>
       <c r="W51">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X51" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AB51">
         <v>0</v>
       </c>
       <c r="AC51" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH51" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI51" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:35">
       <c r="A52">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52">
-        <v>946</v>
+        <v>11750</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>11749</v>
       </c>
       <c r="I52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N52" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P52">
         <v>8</v>
@@ -4757,72 +4843,72 @@
         <v>2026</v>
       </c>
       <c r="R52">
-        <v>16962093</v>
+        <v>18220245</v>
       </c>
       <c r="S52" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T52" t="s">
+        <v>126</v>
       </c>
       <c r="U52" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V52" s="1">
-        <v>46266.25004302083</v>
+        <v>46267.79418379629</v>
       </c>
       <c r="W52">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X52" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AB52">
         <v>0</v>
       </c>
       <c r="AC52" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH52" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI52" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:35">
       <c r="A53">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G53">
-        <v>946</v>
+        <v>11750</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>11749</v>
       </c>
       <c r="I53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N53" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4831,51 +4917,51 @@
         <v>2026</v>
       </c>
       <c r="R53">
-        <v>17941132</v>
+        <v>18214945</v>
       </c>
       <c r="S53" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T53" t="s">
+        <v>126</v>
       </c>
       <c r="U53" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V53" s="1">
-        <v>46266.25135543982</v>
+        <v>46267.79418283565</v>
       </c>
       <c r="W53">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X53" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AB53">
         <v>0</v>
       </c>
       <c r="AC53" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH53" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI53" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:35">
       <c r="A54">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C54" t="s">
         <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
@@ -4884,19 +4970,19 @@
         <v>56</v>
       </c>
       <c r="G54">
-        <v>950</v>
+        <v>6889</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J54" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N54" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P54">
         <v>8</v>
@@ -4905,45 +4991,45 @@
         <v>2026</v>
       </c>
       <c r="R54">
-        <v>17941146</v>
+        <v>18260396</v>
       </c>
       <c r="S54" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="T54" t="s">
+        <v>126</v>
       </c>
       <c r="U54" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V54" s="1">
-        <v>46266.25232241898</v>
+        <v>46267.71937662037</v>
       </c>
       <c r="W54">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X54" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AB54">
         <v>0</v>
       </c>
       <c r="AC54" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH54" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI54" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:35">
       <c r="A55">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
         <v>50</v>
@@ -4952,25 +5038,25 @@
         <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55">
-        <v>950</v>
+        <v>6889</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J55" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N55" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P55">
         <v>8</v>
@@ -4979,45 +5065,45 @@
         <v>2026</v>
       </c>
       <c r="R55">
-        <v>18178132</v>
+        <v>18048463</v>
       </c>
       <c r="S55" t="s">
-        <v>112</v>
+        <v>126</v>
+      </c>
+      <c r="T55" t="s">
+        <v>126</v>
       </c>
       <c r="U55" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V55" s="1">
-        <v>46266.25258784722</v>
+        <v>46267.79259834491</v>
       </c>
       <c r="W55">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X55" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="AB55">
         <v>0</v>
       </c>
       <c r="AC55" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH55" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI55" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:35">
       <c r="A56">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
         <v>50</v>
@@ -5029,22 +5115,22 @@
         <v>55</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G56">
-        <v>951</v>
+        <v>6889</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J56" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N56" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P56">
         <v>8</v>
@@ -5053,45 +5139,45 @@
         <v>2026</v>
       </c>
       <c r="R56">
-        <v>17222405</v>
+        <v>18214913</v>
       </c>
       <c r="S56" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T56" t="s">
+        <v>126</v>
       </c>
       <c r="U56" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V56" s="1">
-        <v>46266.25161940972</v>
+        <v>46267.79260170139</v>
       </c>
       <c r="W56">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X56" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AB56">
         <v>0</v>
       </c>
       <c r="AC56" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH56" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI56" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:35">
       <c r="A57">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C57" t="s">
         <v>50</v>
@@ -5103,22 +5189,22 @@
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57">
-        <v>951</v>
+        <v>6889</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J57" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N57" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P57">
         <v>8</v>
@@ -5127,45 +5213,45 @@
         <v>2026</v>
       </c>
       <c r="R57">
-        <v>17941156</v>
+        <v>18187275</v>
       </c>
       <c r="S57" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T57" t="s">
+        <v>126</v>
       </c>
       <c r="U57" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V57" s="1">
-        <v>46266.25232392361</v>
+        <v>46268.37621265047</v>
       </c>
       <c r="W57">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X57" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AB57">
         <v>0</v>
       </c>
       <c r="AC57" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH57" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI57" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:35">
       <c r="A58">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
         <v>50</v>
@@ -5174,25 +5260,25 @@
         <v>52</v>
       </c>
       <c r="E58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G58">
-        <v>951</v>
+        <v>11758</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>11757</v>
       </c>
       <c r="I58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J58" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N58" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P58">
         <v>8</v>
@@ -5201,72 +5287,72 @@
         <v>2026</v>
       </c>
       <c r="R58">
-        <v>18056705</v>
+        <v>18220263</v>
       </c>
       <c r="S58" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T58" t="s">
+        <v>126</v>
       </c>
       <c r="U58" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V58" s="1">
-        <v>46266.25239591435</v>
+        <v>46267.79440636574</v>
       </c>
       <c r="W58">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X58" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AB58">
         <v>0</v>
       </c>
       <c r="AC58" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH58" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI58" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:35">
       <c r="A59">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59">
-        <v>951</v>
+        <v>11760</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N59" s="1">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="P59">
         <v>8</v>
@@ -5275,45 +5361,45 @@
         <v>2026</v>
       </c>
       <c r="R59">
-        <v>18164501</v>
+        <v>18260421</v>
       </c>
       <c r="S59" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="T59" t="s">
+        <v>126</v>
       </c>
       <c r="U59" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V59" s="1">
-        <v>46266.25258329861</v>
+        <v>46267.72037954861</v>
       </c>
       <c r="W59">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="X59" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="s">
         <v>126</v>
       </c>
-      <c r="Y59" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>112</v>
-      </c>
       <c r="AH59" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI59" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:35">
       <c r="A60">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
         <v>50</v>
@@ -5322,25 +5408,25 @@
         <v>51</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G60">
-        <v>951</v>
+        <v>11760</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J60" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N60" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P60">
         <v>8</v>
@@ -5349,72 +5435,72 @@
         <v>2026</v>
       </c>
       <c r="R60">
-        <v>18178138</v>
+        <v>18173151</v>
       </c>
       <c r="S60" t="s">
-        <v>112</v>
+        <v>126</v>
+      </c>
+      <c r="T60" t="s">
+        <v>126</v>
       </c>
       <c r="U60" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V60" s="1">
-        <v>46266.25259008102</v>
+        <v>46267.79424664352</v>
       </c>
       <c r="W60">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="X60" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="AB60">
         <v>0</v>
       </c>
       <c r="AC60" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH60" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI60" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:35">
       <c r="A61">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C61" t="s">
         <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F61" t="s">
         <v>56</v>
       </c>
       <c r="G61">
-        <v>953</v>
+        <v>11760</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J61" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N61" s="1">
-        <v>46290</v>
+        <v>46268</v>
       </c>
       <c r="P61">
         <v>8</v>
@@ -5423,72 +5509,72 @@
         <v>2026</v>
       </c>
       <c r="R61">
-        <v>17398883</v>
+        <v>18170402</v>
       </c>
       <c r="S61" t="s">
-        <v>112</v>
+        <v>126</v>
+      </c>
+      <c r="T61" t="s">
+        <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V61" s="1">
-        <v>46266.25305</v>
+        <v>46267.79424586806</v>
       </c>
       <c r="W61">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="X61" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AB61">
         <v>0</v>
       </c>
       <c r="AC61" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH61" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI61" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:35">
       <c r="A62">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C62" t="s">
         <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G62">
-        <v>953</v>
+        <v>11760</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J62" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N62" s="1">
-        <v>46290</v>
+        <v>46268</v>
       </c>
       <c r="P62">
         <v>8</v>
@@ -5497,45 +5583,45 @@
         <v>2026</v>
       </c>
       <c r="R62">
-        <v>16962107</v>
+        <v>18220269</v>
       </c>
       <c r="S62" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T62" t="s">
+        <v>126</v>
       </c>
       <c r="U62" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V62" s="1">
-        <v>46266.25270034722</v>
+        <v>46267.79424864583</v>
       </c>
       <c r="W62">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="X62" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="AB62">
         <v>0</v>
       </c>
       <c r="AC62" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH62" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI62" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:35">
       <c r="A63">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C63" t="s">
         <v>50</v>
@@ -5544,25 +5630,25 @@
         <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G63">
-        <v>953</v>
+        <v>11760</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J63" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N63" s="1">
-        <v>46290</v>
+        <v>46268</v>
       </c>
       <c r="P63">
         <v>8</v>
@@ -5571,45 +5657,45 @@
         <v>2026</v>
       </c>
       <c r="R63">
-        <v>17042317</v>
+        <v>18214963</v>
       </c>
       <c r="S63" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T63" t="s">
+        <v>126</v>
       </c>
       <c r="U63" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V63" s="1">
-        <v>46266.25274991898</v>
+        <v>46267.79424725694</v>
       </c>
       <c r="W63">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="X63" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="AB63">
         <v>0</v>
       </c>
       <c r="AC63" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH63" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI63" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:35">
       <c r="A64">
-        <v>6703</v>
+        <v>6962</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
@@ -5621,22 +5707,22 @@
         <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G64">
-        <v>953</v>
+        <v>11760</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>11759</v>
       </c>
       <c r="I64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J64" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N64" s="1">
-        <v>46290</v>
+        <v>46268</v>
       </c>
       <c r="P64">
         <v>8</v>
@@ -5645,45 +5731,45 @@
         <v>2026</v>
       </c>
       <c r="R64">
-        <v>17941166</v>
+        <v>18260057</v>
       </c>
       <c r="S64" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T64" t="s">
+        <v>126</v>
       </c>
       <c r="U64" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V64" s="1">
-        <v>46266.25364633102</v>
+        <v>46267.79425081018</v>
       </c>
       <c r="W64">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="X64" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AB64">
         <v>0</v>
       </c>
       <c r="AC64" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH64" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI64" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:35">
       <c r="A65">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
@@ -5695,22 +5781,22 @@
         <v>55</v>
       </c>
       <c r="F65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G65">
-        <v>953</v>
+        <v>11756</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>11755</v>
       </c>
       <c r="I65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J65" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N65" s="1">
-        <v>46290</v>
+        <v>46267</v>
       </c>
       <c r="P65">
         <v>8</v>
@@ -5719,72 +5805,72 @@
         <v>2026</v>
       </c>
       <c r="R65">
-        <v>18178144</v>
+        <v>18260416</v>
       </c>
       <c r="S65" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="T65" t="s">
+        <v>126</v>
       </c>
       <c r="U65" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V65" s="1">
-        <v>46266.25369826389</v>
+        <v>46267.71942916667</v>
       </c>
       <c r="W65">
-        <v>-23</v>
+        <v>1</v>
       </c>
       <c r="X65" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AB65">
         <v>0</v>
       </c>
       <c r="AC65" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH65" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI65" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:35">
       <c r="A66">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C66" t="s">
         <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E66" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G66">
-        <v>7022</v>
+        <v>11756</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>11755</v>
       </c>
       <c r="I66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J66" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N66" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P66">
         <v>8</v>
@@ -5793,45 +5879,45 @@
         <v>2026</v>
       </c>
       <c r="R66">
-        <v>17399270</v>
+        <v>18220257</v>
       </c>
       <c r="S66" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T66" t="s">
+        <v>126</v>
       </c>
       <c r="U66" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V66" s="1">
-        <v>46266.25305112269</v>
+        <v>46267.79268530093</v>
       </c>
       <c r="W66">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X66" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="AH66" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI66" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:35">
       <c r="A67">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
@@ -5840,25 +5926,25 @@
         <v>51</v>
       </c>
       <c r="E67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G67">
-        <v>7022</v>
+        <v>11756</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>11755</v>
       </c>
       <c r="I67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J67" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N67" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P67">
         <v>8</v>
@@ -5867,72 +5953,72 @@
         <v>2026</v>
       </c>
       <c r="R67">
-        <v>17042505</v>
+        <v>18214957</v>
       </c>
       <c r="S67" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T67" t="s">
+        <v>126</v>
       </c>
       <c r="U67" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V67" s="1">
-        <v>46266.25275173611</v>
+        <v>46267.79268769676</v>
       </c>
       <c r="W67">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X67" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="AB67">
         <v>0</v>
       </c>
       <c r="AC67" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH67" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI67" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:35">
       <c r="A68">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G68">
-        <v>7022</v>
+        <v>6221</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>6220</v>
       </c>
       <c r="I68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J68" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N68" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P68">
         <v>8</v>
@@ -5941,37 +6027,37 @@
         <v>2026</v>
       </c>
       <c r="R68">
-        <v>17952421</v>
+        <v>18220209</v>
       </c>
       <c r="S68" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="T68" t="s">
+        <v>126</v>
       </c>
       <c r="U68" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V68" s="1">
-        <v>46266.25364869213</v>
+        <v>46267.79249748842</v>
       </c>
       <c r="W68">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X68" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="s">
         <v>128</v>
       </c>
-      <c r="Y68" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="s">
-        <v>112</v>
-      </c>
       <c r="AH68" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI68" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -5994,19 +6080,19 @@
         <v>57</v>
       </c>
       <c r="G69">
-        <v>7022</v>
+        <v>6221</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>6220</v>
       </c>
       <c r="I69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J69" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N69" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="P69">
         <v>8</v>
@@ -6015,51 +6101,51 @@
         <v>2026</v>
       </c>
       <c r="R69">
-        <v>18178174</v>
+        <v>18214889</v>
       </c>
       <c r="S69" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="T69" t="s">
+        <v>126</v>
       </c>
       <c r="U69" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V69" s="1">
-        <v>46266.25369988426</v>
+        <v>46267.79249788194</v>
       </c>
       <c r="W69">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="X69" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="AB69">
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AH69" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="AI69" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:35">
       <c r="A70">
-        <v>6404</v>
+        <v>6548</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C70" t="s">
         <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E70" t="s">
         <v>55</v>
@@ -6068,140 +6154,140 @@
         <v>56</v>
       </c>
       <c r="G70">
-        <v>11001</v>
+        <v>6223</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>6222</v>
       </c>
       <c r="I70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J70" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N70" s="1">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="P70">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q70">
         <v>2026</v>
       </c>
       <c r="R70">
-        <v>16962453</v>
+        <v>18260391</v>
       </c>
       <c r="S70" t="s">
-        <v>55</v>
+        <v>125</v>
+      </c>
+      <c r="T70" t="s">
+        <v>126</v>
       </c>
       <c r="U70" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="V70" s="1">
-        <v>46267.66131466435</v>
+        <v>46267.71927280092</v>
       </c>
       <c r="W70">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X70" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="AB70">
         <v>0</v>
       </c>
       <c r="AC70" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="AH70" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI70" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:35">
       <c r="A71">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
         <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G71">
-        <v>11001</v>
+        <v>6223</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>6222</v>
       </c>
       <c r="I71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J71" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N71" s="1">
-        <v>46321</v>
+        <v>46268</v>
       </c>
       <c r="P71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q71">
         <v>2026</v>
       </c>
       <c r="R71">
-        <v>16962455</v>
+        <v>18220215</v>
       </c>
       <c r="S71" t="s">
-        <v>55</v>
+        <v>128</v>
+      </c>
+      <c r="T71" t="s">
+        <v>126</v>
       </c>
       <c r="U71" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V71" s="1">
-        <v>46266.21595836805</v>
+        <v>46267.79251079861</v>
       </c>
       <c r="W71">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="X71" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="AB71">
         <v>0</v>
       </c>
       <c r="AC71" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="AH71" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI71" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:35">
       <c r="A72">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C72" t="s">
         <v>50</v>
@@ -6213,69 +6299,69 @@
         <v>55</v>
       </c>
       <c r="F72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G72">
-        <v>7877</v>
+        <v>6223</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>6222</v>
       </c>
       <c r="I72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J72" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="N72" s="1">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="P72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q72">
         <v>2026</v>
       </c>
       <c r="R72">
-        <v>17399329</v>
+        <v>18214895</v>
       </c>
       <c r="S72" t="s">
-        <v>55</v>
+        <v>127</v>
+      </c>
+      <c r="T72" t="s">
+        <v>126</v>
       </c>
       <c r="U72" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="V72" s="1">
-        <v>46267.66006940972</v>
+        <v>46267.79251038194</v>
       </c>
       <c r="W72">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X72" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="AB72">
         <v>0</v>
       </c>
       <c r="AC72" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="AH72" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI72" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:35">
       <c r="A73">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
         <v>50</v>
@@ -6290,66 +6376,66 @@
         <v>56</v>
       </c>
       <c r="G73">
-        <v>7877</v>
+        <v>11766</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>11765</v>
       </c>
       <c r="I73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J73" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="N73" s="1">
-        <v>46321</v>
+        <v>46267</v>
       </c>
       <c r="P73">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q73">
         <v>2026</v>
       </c>
       <c r="R73">
-        <v>17399331</v>
+        <v>18260426</v>
       </c>
       <c r="S73" t="s">
-        <v>55</v>
+        <v>125</v>
+      </c>
+      <c r="T73" t="s">
+        <v>126</v>
       </c>
       <c r="U73" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="V73" s="1">
-        <v>46266.21572962963</v>
+        <v>46267.72044811342</v>
       </c>
       <c r="W73">
-        <v>-54</v>
+        <v>1</v>
       </c>
       <c r="X73" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="AB73">
         <v>0</v>
       </c>
       <c r="AC73" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="AH73" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI73" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:35">
       <c r="A74">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C74" t="s">
         <v>50</v>
@@ -6358,288 +6444,294 @@
         <v>51</v>
       </c>
       <c r="E74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F74" t="s">
         <v>56</v>
       </c>
       <c r="G74">
-        <v>9774</v>
+        <v>11766</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>11765</v>
       </c>
       <c r="I74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N74" s="1">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="P74">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q74">
         <v>2026</v>
       </c>
       <c r="R74">
-        <v>16976320</v>
+        <v>18173159</v>
       </c>
       <c r="S74" t="s">
-        <v>55</v>
+        <v>126</v>
+      </c>
+      <c r="T74" t="s">
+        <v>126</v>
       </c>
       <c r="U74" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="V74" s="1">
-        <v>46267.67127083334</v>
+        <v>46267.79429737268</v>
       </c>
       <c r="W74">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X74" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="AB74">
         <v>0</v>
       </c>
       <c r="AC74" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="AH74" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI74" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:35">
       <c r="A75">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F75" t="s">
         <v>56</v>
       </c>
       <c r="G75">
-        <v>9774</v>
+        <v>11766</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>11765</v>
       </c>
       <c r="I75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J75" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N75" s="1">
-        <v>46321</v>
+        <v>46268</v>
       </c>
       <c r="P75">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q75">
         <v>2026</v>
       </c>
       <c r="R75">
-        <v>16976322</v>
+        <v>18170410</v>
       </c>
       <c r="S75" t="s">
-        <v>55</v>
+        <v>126</v>
+      </c>
+      <c r="T75" t="s">
+        <v>126</v>
       </c>
       <c r="U75" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V75" s="1">
-        <v>46266.21550011574</v>
+        <v>46267.79429603009</v>
       </c>
       <c r="W75">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="X75" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="AB75">
         <v>0</v>
       </c>
       <c r="AC75" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="AH75" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI75" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:35">
       <c r="A76">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C76" t="s">
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76">
-        <v>7027</v>
+        <v>11766</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>11765</v>
       </c>
       <c r="I76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J76" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N76" s="1">
-        <v>46321</v>
+        <v>46268</v>
       </c>
       <c r="P76">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q76">
         <v>2026</v>
       </c>
       <c r="R76">
-        <v>17399291</v>
+        <v>18220275</v>
       </c>
       <c r="S76" t="s">
-        <v>55</v>
+        <v>128</v>
+      </c>
+      <c r="T76" t="s">
+        <v>126</v>
       </c>
       <c r="U76" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V76" s="1">
-        <v>46266.00006921296</v>
+        <v>46267.79429876158</v>
       </c>
       <c r="W76">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="X76" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="AB76">
         <v>0</v>
       </c>
       <c r="AC76" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="AH76" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI76" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:35">
       <c r="A77">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
         <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E77" t="s">
         <v>55</v>
       </c>
       <c r="F77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77">
-        <v>7027</v>
+        <v>11766</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>11765</v>
       </c>
       <c r="I77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J77" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N77" s="1">
-        <v>46321</v>
+        <v>46268</v>
       </c>
       <c r="P77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q77">
         <v>2026</v>
       </c>
       <c r="R77">
-        <v>16962349</v>
+        <v>18214969</v>
       </c>
       <c r="S77" t="s">
-        <v>55</v>
+        <v>127</v>
+      </c>
+      <c r="T77" t="s">
+        <v>126</v>
       </c>
       <c r="U77" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="V77" s="1">
-        <v>46266.00006921296</v>
+        <v>46267.79429826389</v>
       </c>
       <c r="W77">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="X77" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AB77">
         <v>0</v>
       </c>
       <c r="AC77" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="AH77" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AI77" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:35">
       <c r="A78">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
         <v>50</v>
@@ -6654,55 +6746,3601 @@
         <v>56</v>
       </c>
       <c r="G78">
+        <v>11768</v>
+      </c>
+      <c r="H78">
+        <v>11767</v>
+      </c>
+      <c r="I78" t="s">
+        <v>62</v>
+      </c>
+      <c r="J78" t="s">
+        <v>92</v>
+      </c>
+      <c r="N78" s="1">
+        <v>46267</v>
+      </c>
+      <c r="P78">
+        <v>8</v>
+      </c>
+      <c r="Q78">
+        <v>2026</v>
+      </c>
+      <c r="R78">
+        <v>18260431</v>
+      </c>
+      <c r="S78" t="s">
+        <v>125</v>
+      </c>
+      <c r="T78" t="s">
+        <v>126</v>
+      </c>
+      <c r="U78" t="s">
+        <v>141</v>
+      </c>
+      <c r="V78" s="1">
+        <v>46267.72050385417</v>
+      </c>
+      <c r="W78">
+        <v>1</v>
+      </c>
+      <c r="X78" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:35">
+      <c r="A79">
+        <v>6627</v>
+      </c>
+      <c r="B79" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" t="s">
+        <v>50</v>
+      </c>
+      <c r="D79" t="s">
+        <v>51</v>
+      </c>
+      <c r="E79" t="s">
+        <v>54</v>
+      </c>
+      <c r="F79" t="s">
+        <v>56</v>
+      </c>
+      <c r="G79">
+        <v>11768</v>
+      </c>
+      <c r="H79">
+        <v>11767</v>
+      </c>
+      <c r="I79" t="s">
+        <v>62</v>
+      </c>
+      <c r="J79" t="s">
+        <v>92</v>
+      </c>
+      <c r="N79" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P79">
+        <v>8</v>
+      </c>
+      <c r="Q79">
+        <v>2026</v>
+      </c>
+      <c r="R79">
+        <v>18173167</v>
+      </c>
+      <c r="S79" t="s">
+        <v>126</v>
+      </c>
+      <c r="T79" t="s">
+        <v>126</v>
+      </c>
+      <c r="U79" t="s">
+        <v>140</v>
+      </c>
+      <c r="V79" s="1">
+        <v>46267.79434996528</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI79" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" spans="1:35">
+      <c r="A80">
+        <v>6628</v>
+      </c>
+      <c r="B80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80" t="s">
+        <v>52</v>
+      </c>
+      <c r="E80" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" t="s">
+        <v>56</v>
+      </c>
+      <c r="G80">
+        <v>11768</v>
+      </c>
+      <c r="H80">
+        <v>11767</v>
+      </c>
+      <c r="I80" t="s">
+        <v>62</v>
+      </c>
+      <c r="J80" t="s">
+        <v>92</v>
+      </c>
+      <c r="N80" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P80">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>2026</v>
+      </c>
+      <c r="R80">
+        <v>18170418</v>
+      </c>
+      <c r="S80" t="s">
+        <v>126</v>
+      </c>
+      <c r="T80" t="s">
+        <v>126</v>
+      </c>
+      <c r="U80" t="s">
+        <v>140</v>
+      </c>
+      <c r="V80" s="1">
+        <v>46267.79434864583</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI80" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="81" spans="1:35">
+      <c r="A81">
+        <v>6945</v>
+      </c>
+      <c r="B81" t="s">
+        <v>39</v>
+      </c>
+      <c r="C81" t="s">
+        <v>50</v>
+      </c>
+      <c r="D81" t="s">
+        <v>52</v>
+      </c>
+      <c r="E81" t="s">
+        <v>54</v>
+      </c>
+      <c r="F81" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81">
+        <v>11768</v>
+      </c>
+      <c r="H81">
+        <v>11767</v>
+      </c>
+      <c r="I81" t="s">
+        <v>62</v>
+      </c>
+      <c r="J81" t="s">
+        <v>92</v>
+      </c>
+      <c r="N81" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P81">
+        <v>8</v>
+      </c>
+      <c r="Q81">
+        <v>2026</v>
+      </c>
+      <c r="R81">
+        <v>18220281</v>
+      </c>
+      <c r="S81" t="s">
+        <v>128</v>
+      </c>
+      <c r="T81" t="s">
+        <v>126</v>
+      </c>
+      <c r="U81" t="s">
+        <v>140</v>
+      </c>
+      <c r="V81" s="1">
+        <v>46267.79435208334</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI81" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="82" spans="1:35">
+      <c r="A82">
+        <v>6949</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" t="s">
+        <v>50</v>
+      </c>
+      <c r="D82" t="s">
+        <v>51</v>
+      </c>
+      <c r="E82" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82">
+        <v>11768</v>
+      </c>
+      <c r="H82">
+        <v>11767</v>
+      </c>
+      <c r="I82" t="s">
+        <v>62</v>
+      </c>
+      <c r="J82" t="s">
+        <v>92</v>
+      </c>
+      <c r="N82" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P82">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>2026</v>
+      </c>
+      <c r="R82">
+        <v>18214975</v>
+      </c>
+      <c r="S82" t="s">
+        <v>127</v>
+      </c>
+      <c r="T82" t="s">
+        <v>126</v>
+      </c>
+      <c r="U82" t="s">
+        <v>140</v>
+      </c>
+      <c r="V82" s="1">
+        <v>46267.79435100695</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH82" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI82" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:35">
+      <c r="A83">
+        <v>5417</v>
+      </c>
+      <c r="B83" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" t="s">
+        <v>50</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>56</v>
+      </c>
+      <c r="G83">
+        <v>6883</v>
+      </c>
+      <c r="H83">
+        <v>1788</v>
+      </c>
+      <c r="I83" t="s">
+        <v>63</v>
+      </c>
+      <c r="J83" t="s">
+        <v>85</v>
+      </c>
+      <c r="N83" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P83">
+        <v>8</v>
+      </c>
+      <c r="Q83">
+        <v>2026</v>
+      </c>
+      <c r="R83">
+        <v>17399250</v>
+      </c>
+      <c r="S83" t="s">
+        <v>129</v>
+      </c>
+      <c r="T83" t="s">
+        <v>138</v>
+      </c>
+      <c r="U83" t="s">
+        <v>140</v>
+      </c>
+      <c r="V83" s="1">
+        <v>46266.37636392361</v>
+      </c>
+      <c r="W83">
+        <v>-7</v>
+      </c>
+      <c r="X83" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB83">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI83" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35">
+      <c r="A84">
+        <v>5417</v>
+      </c>
+      <c r="B84" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" t="s">
+        <v>50</v>
+      </c>
+      <c r="D84" t="s">
+        <v>51</v>
+      </c>
+      <c r="E84" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" t="s">
+        <v>56</v>
+      </c>
+      <c r="G84">
+        <v>1836</v>
+      </c>
+      <c r="H84">
+        <v>1788</v>
+      </c>
+      <c r="I84" t="s">
+        <v>63</v>
+      </c>
+      <c r="J84" t="s">
+        <v>93</v>
+      </c>
+      <c r="N84" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P84">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>2026</v>
+      </c>
+      <c r="R84">
+        <v>17398975</v>
+      </c>
+      <c r="S84" t="s">
+        <v>129</v>
+      </c>
+      <c r="T84" t="s">
+        <v>138</v>
+      </c>
+      <c r="U84" t="s">
+        <v>140</v>
+      </c>
+      <c r="V84" s="1">
+        <v>46266.37598834491</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI84" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85" spans="1:35">
+      <c r="A85">
+        <v>6704</v>
+      </c>
+      <c r="B85" t="s">
+        <v>42</v>
+      </c>
+      <c r="C85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" t="s">
+        <v>51</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="s">
+        <v>56</v>
+      </c>
+      <c r="G85">
+        <v>1836</v>
+      </c>
+      <c r="H85">
+        <v>1788</v>
+      </c>
+      <c r="I85" t="s">
+        <v>63</v>
+      </c>
+      <c r="J85" t="s">
+        <v>93</v>
+      </c>
+      <c r="N85" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P85">
+        <v>8</v>
+      </c>
+      <c r="Q85">
+        <v>2026</v>
+      </c>
+      <c r="R85">
+        <v>18085220</v>
+      </c>
+      <c r="S85" t="s">
+        <v>129</v>
+      </c>
+      <c r="T85" t="s">
+        <v>138</v>
+      </c>
+      <c r="U85" t="s">
+        <v>140</v>
+      </c>
+      <c r="V85" s="1">
+        <v>46266.45957881944</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH85" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI85" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="86" spans="1:35">
+      <c r="A86">
+        <v>5417</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>50</v>
+      </c>
+      <c r="D86" t="s">
+        <v>51</v>
+      </c>
+      <c r="E86" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" t="s">
+        <v>56</v>
+      </c>
+      <c r="G86">
+        <v>6802</v>
+      </c>
+      <c r="H86">
+        <v>1788</v>
+      </c>
+      <c r="I86" t="s">
+        <v>63</v>
+      </c>
+      <c r="J86" t="s">
+        <v>94</v>
+      </c>
+      <c r="N86" s="1">
+        <v>46269</v>
+      </c>
+      <c r="P86">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>2026</v>
+      </c>
+      <c r="R86">
+        <v>17399220</v>
+      </c>
+      <c r="S86" t="s">
+        <v>129</v>
+      </c>
+      <c r="T86" t="s">
+        <v>138</v>
+      </c>
+      <c r="U86" t="s">
+        <v>140</v>
+      </c>
+      <c r="V86" s="1">
+        <v>46266.37645462963</v>
+      </c>
+      <c r="W86">
+        <v>-1</v>
+      </c>
+      <c r="X86" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH86" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI86" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:35">
+      <c r="A87">
+        <v>5417</v>
+      </c>
+      <c r="B87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" t="s">
+        <v>50</v>
+      </c>
+      <c r="D87" t="s">
+        <v>51</v>
+      </c>
+      <c r="E87" t="s">
+        <v>55</v>
+      </c>
+      <c r="F87" t="s">
+        <v>56</v>
+      </c>
+      <c r="G87">
+        <v>6801</v>
+      </c>
+      <c r="H87">
+        <v>1796</v>
+      </c>
+      <c r="I87" t="s">
+        <v>63</v>
+      </c>
+      <c r="J87" t="s">
+        <v>95</v>
+      </c>
+      <c r="N87" s="1">
+        <v>46269</v>
+      </c>
+      <c r="P87">
+        <v>8</v>
+      </c>
+      <c r="Q87">
+        <v>2026</v>
+      </c>
+      <c r="R87">
+        <v>17399210</v>
+      </c>
+      <c r="S87" t="s">
+        <v>129</v>
+      </c>
+      <c r="T87" t="s">
+        <v>138</v>
+      </c>
+      <c r="U87" t="s">
+        <v>140</v>
+      </c>
+      <c r="V87" s="1">
+        <v>46266.37649475694</v>
+      </c>
+      <c r="W87">
+        <v>-1</v>
+      </c>
+      <c r="X87" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB87">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH87" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI87" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="88" spans="1:35">
+      <c r="A88">
+        <v>5417</v>
+      </c>
+      <c r="B88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D88" t="s">
+        <v>51</v>
+      </c>
+      <c r="E88" t="s">
+        <v>55</v>
+      </c>
+      <c r="F88" t="s">
+        <v>56</v>
+      </c>
+      <c r="G88">
+        <v>6014</v>
+      </c>
+      <c r="H88">
+        <v>1788</v>
+      </c>
+      <c r="I88" t="s">
+        <v>63</v>
+      </c>
+      <c r="J88" t="s">
+        <v>96</v>
+      </c>
+      <c r="N88" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P88">
+        <v>8</v>
+      </c>
+      <c r="Q88">
+        <v>2026</v>
+      </c>
+      <c r="R88">
+        <v>17399136</v>
+      </c>
+      <c r="S88" t="s">
+        <v>129</v>
+      </c>
+      <c r="T88" t="s">
+        <v>138</v>
+      </c>
+      <c r="U88" t="s">
+        <v>140</v>
+      </c>
+      <c r="V88" s="1">
+        <v>46266.37591180555</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB88">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH88" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI88" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:35">
+      <c r="A89">
+        <v>6704</v>
+      </c>
+      <c r="B89" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" t="s">
+        <v>51</v>
+      </c>
+      <c r="E89" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" t="s">
+        <v>56</v>
+      </c>
+      <c r="G89">
+        <v>6014</v>
+      </c>
+      <c r="H89">
+        <v>1788</v>
+      </c>
+      <c r="I89" t="s">
+        <v>63</v>
+      </c>
+      <c r="J89" t="s">
+        <v>96</v>
+      </c>
+      <c r="N89" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P89">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>2026</v>
+      </c>
+      <c r="R89">
+        <v>18085231</v>
+      </c>
+      <c r="S89" t="s">
+        <v>129</v>
+      </c>
+      <c r="T89" t="s">
+        <v>138</v>
+      </c>
+      <c r="U89" t="s">
+        <v>140</v>
+      </c>
+      <c r="V89" s="1">
+        <v>46266.45946195602</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH89" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI89" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:35">
+      <c r="A90">
+        <v>5417</v>
+      </c>
+      <c r="B90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" t="s">
+        <v>51</v>
+      </c>
+      <c r="E90" t="s">
+        <v>55</v>
+      </c>
+      <c r="F90" t="s">
+        <v>56</v>
+      </c>
+      <c r="G90">
+        <v>6233</v>
+      </c>
+      <c r="H90">
+        <v>6232</v>
+      </c>
+      <c r="I90" t="s">
+        <v>63</v>
+      </c>
+      <c r="J90" t="s">
+        <v>97</v>
+      </c>
+      <c r="N90" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P90">
+        <v>8</v>
+      </c>
+      <c r="Q90">
+        <v>2026</v>
+      </c>
+      <c r="R90">
+        <v>17399176</v>
+      </c>
+      <c r="S90" t="s">
+        <v>129</v>
+      </c>
+      <c r="T90" t="s">
+        <v>138</v>
+      </c>
+      <c r="U90" t="s">
+        <v>140</v>
+      </c>
+      <c r="V90" s="1">
+        <v>46266.37538684028</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI90" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:35">
+      <c r="A91">
+        <v>6404</v>
+      </c>
+      <c r="B91" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" t="s">
+        <v>50</v>
+      </c>
+      <c r="D91" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" t="s">
+        <v>55</v>
+      </c>
+      <c r="F91" t="s">
+        <v>56</v>
+      </c>
+      <c r="G91">
+        <v>6233</v>
+      </c>
+      <c r="H91">
+        <v>6232</v>
+      </c>
+      <c r="I91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J91" t="s">
+        <v>97</v>
+      </c>
+      <c r="N91" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P91">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>2026</v>
+      </c>
+      <c r="R91">
+        <v>16962294</v>
+      </c>
+      <c r="S91" t="s">
+        <v>129</v>
+      </c>
+      <c r="T91" t="s">
+        <v>138</v>
+      </c>
+      <c r="U91" t="s">
+        <v>140</v>
+      </c>
+      <c r="V91" s="1">
+        <v>46266.37538506944</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB91">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI91" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="92" spans="1:35">
+      <c r="A92">
+        <v>6703</v>
+      </c>
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92" t="s">
+        <v>50</v>
+      </c>
+      <c r="D92" t="s">
+        <v>53</v>
+      </c>
+      <c r="E92" t="s">
+        <v>55</v>
+      </c>
+      <c r="F92" t="s">
+        <v>56</v>
+      </c>
+      <c r="G92">
+        <v>6233</v>
+      </c>
+      <c r="H92">
+        <v>6232</v>
+      </c>
+      <c r="I92" t="s">
+        <v>63</v>
+      </c>
+      <c r="J92" t="s">
+        <v>97</v>
+      </c>
+      <c r="N92" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P92">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>2026</v>
+      </c>
+      <c r="R92">
+        <v>17948844</v>
+      </c>
+      <c r="S92" t="s">
+        <v>129</v>
+      </c>
+      <c r="T92" t="s">
+        <v>138</v>
+      </c>
+      <c r="U92" t="s">
+        <v>140</v>
+      </c>
+      <c r="V92" s="1">
+        <v>46266.45895332176</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB92">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH92" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI92" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="93" spans="1:35">
+      <c r="A93">
+        <v>6704</v>
+      </c>
+      <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>50</v>
+      </c>
+      <c r="D93" t="s">
+        <v>51</v>
+      </c>
+      <c r="E93" t="s">
+        <v>55</v>
+      </c>
+      <c r="F93" t="s">
+        <v>56</v>
+      </c>
+      <c r="G93">
+        <v>6233</v>
+      </c>
+      <c r="H93">
+        <v>6232</v>
+      </c>
+      <c r="I93" t="s">
+        <v>63</v>
+      </c>
+      <c r="J93" t="s">
+        <v>97</v>
+      </c>
+      <c r="N93" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P93">
+        <v>8</v>
+      </c>
+      <c r="Q93">
+        <v>2026</v>
+      </c>
+      <c r="R93">
+        <v>18085264</v>
+      </c>
+      <c r="S93" t="s">
+        <v>129</v>
+      </c>
+      <c r="T93" t="s">
+        <v>138</v>
+      </c>
+      <c r="U93" t="s">
+        <v>140</v>
+      </c>
+      <c r="V93" s="1">
+        <v>46266.45874105324</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB93">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH93" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI93" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:35">
+      <c r="A94">
+        <v>6705</v>
+      </c>
+      <c r="B94" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" t="s">
+        <v>50</v>
+      </c>
+      <c r="D94" t="s">
+        <v>52</v>
+      </c>
+      <c r="E94" t="s">
+        <v>55</v>
+      </c>
+      <c r="F94" t="s">
+        <v>56</v>
+      </c>
+      <c r="G94">
+        <v>6233</v>
+      </c>
+      <c r="H94">
+        <v>6232</v>
+      </c>
+      <c r="I94" t="s">
+        <v>63</v>
+      </c>
+      <c r="J94" t="s">
+        <v>97</v>
+      </c>
+      <c r="N94" s="1">
+        <v>46268</v>
+      </c>
+      <c r="P94">
+        <v>8</v>
+      </c>
+      <c r="Q94">
+        <v>2026</v>
+      </c>
+      <c r="R94">
+        <v>17948989</v>
+      </c>
+      <c r="S94" t="s">
+        <v>129</v>
+      </c>
+      <c r="T94" t="s">
+        <v>138</v>
+      </c>
+      <c r="U94" t="s">
+        <v>140</v>
+      </c>
+      <c r="V94" s="1">
+        <v>46266.45873584491</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+      <c r="X94" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB94">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH94" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI94" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:35">
+      <c r="A95">
+        <v>6705</v>
+      </c>
+      <c r="B95" t="s">
+        <v>47</v>
+      </c>
+      <c r="C95" t="s">
+        <v>50</v>
+      </c>
+      <c r="D95" t="s">
+        <v>52</v>
+      </c>
+      <c r="E95" t="s">
+        <v>55</v>
+      </c>
+      <c r="F95" t="s">
+        <v>56</v>
+      </c>
+      <c r="G95">
+        <v>11303</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>63</v>
+      </c>
+      <c r="J95" t="s">
+        <v>98</v>
+      </c>
+      <c r="N95" s="1">
+        <v>46279</v>
+      </c>
+      <c r="P95">
+        <v>8</v>
+      </c>
+      <c r="Q95">
+        <v>2026</v>
+      </c>
+      <c r="R95">
+        <v>17949079</v>
+      </c>
+      <c r="S95" t="s">
+        <v>129</v>
+      </c>
+      <c r="T95" t="s">
+        <v>138</v>
+      </c>
+      <c r="U95" t="s">
+        <v>140</v>
+      </c>
+      <c r="V95" s="1">
+        <v>46267.44505795139</v>
+      </c>
+      <c r="W95">
+        <v>-11</v>
+      </c>
+      <c r="X95" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB95">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH95" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI95" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="96" spans="1:35">
+      <c r="A96">
+        <v>6628</v>
+      </c>
+      <c r="B96" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" t="s">
+        <v>52</v>
+      </c>
+      <c r="E96" t="s">
+        <v>54</v>
+      </c>
+      <c r="F96" t="s">
+        <v>56</v>
+      </c>
+      <c r="G96">
+        <v>945</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96" t="s">
+        <v>64</v>
+      </c>
+      <c r="J96" t="s">
+        <v>99</v>
+      </c>
+      <c r="N96" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P96">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>2026</v>
+      </c>
+      <c r="R96">
+        <v>16959938</v>
+      </c>
+      <c r="S96" t="s">
+        <v>130</v>
+      </c>
+      <c r="U96" t="s">
+        <v>140</v>
+      </c>
+      <c r="V96" s="1">
+        <v>46266.04180934028</v>
+      </c>
+      <c r="W96">
+        <v>-15</v>
+      </c>
+      <c r="X96" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB96">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH96" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI96" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97" spans="1:35">
+      <c r="A97">
+        <v>6779</v>
+      </c>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D97" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" t="s">
+        <v>55</v>
+      </c>
+      <c r="F97" t="s">
+        <v>56</v>
+      </c>
+      <c r="G97">
+        <v>945</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97" t="s">
+        <v>64</v>
+      </c>
+      <c r="J97" t="s">
+        <v>99</v>
+      </c>
+      <c r="N97" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P97">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>2026</v>
+      </c>
+      <c r="R97">
+        <v>18056695</v>
+      </c>
+      <c r="S97" t="s">
+        <v>130</v>
+      </c>
+      <c r="U97" t="s">
+        <v>140</v>
+      </c>
+      <c r="V97" s="1">
+        <v>46266.08343295139</v>
+      </c>
+      <c r="W97">
+        <v>-15</v>
+      </c>
+      <c r="X97" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB97">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH97" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI97" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="98" spans="1:35">
+      <c r="A98">
+        <v>6945</v>
+      </c>
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" t="s">
+        <v>50</v>
+      </c>
+      <c r="D98" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" t="s">
+        <v>57</v>
+      </c>
+      <c r="G98">
+        <v>945</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98" t="s">
+        <v>64</v>
+      </c>
+      <c r="J98" t="s">
+        <v>99</v>
+      </c>
+      <c r="N98" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P98">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>2026</v>
+      </c>
+      <c r="R98">
+        <v>18164487</v>
+      </c>
+      <c r="S98" t="s">
+        <v>130</v>
+      </c>
+      <c r="U98" t="s">
+        <v>140</v>
+      </c>
+      <c r="V98" s="1">
+        <v>46266.08344398148</v>
+      </c>
+      <c r="W98">
+        <v>-15</v>
+      </c>
+      <c r="X98" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB98">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH98" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" spans="1:35">
+      <c r="A99">
+        <v>5417</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>50</v>
+      </c>
+      <c r="D99" t="s">
+        <v>51</v>
+      </c>
+      <c r="E99" t="s">
+        <v>55</v>
+      </c>
+      <c r="F99" t="s">
+        <v>56</v>
+      </c>
+      <c r="G99">
+        <v>946</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99" t="s">
+        <v>64</v>
+      </c>
+      <c r="J99" t="s">
+        <v>100</v>
+      </c>
+      <c r="N99" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P99">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>2026</v>
+      </c>
+      <c r="R99">
+        <v>17398869</v>
+      </c>
+      <c r="S99" t="s">
+        <v>130</v>
+      </c>
+      <c r="U99" t="s">
+        <v>140</v>
+      </c>
+      <c r="V99" s="1">
+        <v>46266.25077376157</v>
+      </c>
+      <c r="W99">
+        <v>-15</v>
+      </c>
+      <c r="X99" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB99">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH99" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI99" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="100" spans="1:35">
+      <c r="A100">
+        <v>6404</v>
+      </c>
+      <c r="B100" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" t="s">
+        <v>55</v>
+      </c>
+      <c r="F100" t="s">
+        <v>56</v>
+      </c>
+      <c r="G100">
+        <v>946</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100" t="s">
+        <v>64</v>
+      </c>
+      <c r="J100" t="s">
+        <v>100</v>
+      </c>
+      <c r="N100" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P100">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>2026</v>
+      </c>
+      <c r="R100">
+        <v>16962093</v>
+      </c>
+      <c r="S100" t="s">
+        <v>130</v>
+      </c>
+      <c r="U100" t="s">
+        <v>140</v>
+      </c>
+      <c r="V100" s="1">
+        <v>46266.25004302083</v>
+      </c>
+      <c r="W100">
+        <v>-15</v>
+      </c>
+      <c r="X100" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB100">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH100" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI100" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="101" spans="1:35">
+      <c r="A101">
+        <v>6703</v>
+      </c>
+      <c r="B101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" t="s">
+        <v>55</v>
+      </c>
+      <c r="F101" t="s">
+        <v>56</v>
+      </c>
+      <c r="G101">
+        <v>946</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101" t="s">
+        <v>64</v>
+      </c>
+      <c r="J101" t="s">
+        <v>100</v>
+      </c>
+      <c r="N101" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P101">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>2026</v>
+      </c>
+      <c r="R101">
+        <v>17941132</v>
+      </c>
+      <c r="S101" t="s">
+        <v>130</v>
+      </c>
+      <c r="U101" t="s">
+        <v>140</v>
+      </c>
+      <c r="V101" s="1">
+        <v>46266.25135543982</v>
+      </c>
+      <c r="W101">
+        <v>-15</v>
+      </c>
+      <c r="X101" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB101">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH101" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI101" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="102" spans="1:35">
+      <c r="A102">
+        <v>6703</v>
+      </c>
+      <c r="B102" t="s">
+        <v>49</v>
+      </c>
+      <c r="C102" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" t="s">
+        <v>55</v>
+      </c>
+      <c r="F102" t="s">
+        <v>56</v>
+      </c>
+      <c r="G102">
+        <v>950</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102" t="s">
+        <v>64</v>
+      </c>
+      <c r="J102" t="s">
+        <v>101</v>
+      </c>
+      <c r="N102" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P102">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>2026</v>
+      </c>
+      <c r="R102">
+        <v>17941146</v>
+      </c>
+      <c r="S102" t="s">
+        <v>130</v>
+      </c>
+      <c r="U102" t="s">
+        <v>140</v>
+      </c>
+      <c r="V102" s="1">
+        <v>46266.25232241898</v>
+      </c>
+      <c r="W102">
+        <v>-7</v>
+      </c>
+      <c r="X102" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB102">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH102" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI102" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" spans="1:35">
+      <c r="A103">
+        <v>6949</v>
+      </c>
+      <c r="B103" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103" t="s">
+        <v>51</v>
+      </c>
+      <c r="E103" t="s">
+        <v>55</v>
+      </c>
+      <c r="F103" t="s">
+        <v>57</v>
+      </c>
+      <c r="G103">
+        <v>950</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103" t="s">
+        <v>64</v>
+      </c>
+      <c r="J103" t="s">
+        <v>101</v>
+      </c>
+      <c r="N103" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P103">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>2026</v>
+      </c>
+      <c r="R103">
+        <v>18178132</v>
+      </c>
+      <c r="S103" t="s">
+        <v>130</v>
+      </c>
+      <c r="U103" t="s">
+        <v>140</v>
+      </c>
+      <c r="V103" s="1">
+        <v>46266.25258784722</v>
+      </c>
+      <c r="W103">
+        <v>-7</v>
+      </c>
+      <c r="X103" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB103">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH103" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI103" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="104" spans="1:35">
+      <c r="A104">
+        <v>6548</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" t="s">
+        <v>51</v>
+      </c>
+      <c r="E104" t="s">
+        <v>55</v>
+      </c>
+      <c r="F104" t="s">
+        <v>56</v>
+      </c>
+      <c r="G104">
+        <v>951</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104" t="s">
+        <v>64</v>
+      </c>
+      <c r="J104" t="s">
+        <v>102</v>
+      </c>
+      <c r="N104" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P104">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>2026</v>
+      </c>
+      <c r="R104">
+        <v>17222405</v>
+      </c>
+      <c r="S104" t="s">
+        <v>130</v>
+      </c>
+      <c r="U104" t="s">
+        <v>140</v>
+      </c>
+      <c r="V104" s="1">
+        <v>46266.25161940972</v>
+      </c>
+      <c r="W104">
+        <v>-7</v>
+      </c>
+      <c r="X104" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB104">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH104" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI104" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="105" spans="1:35">
+      <c r="A105">
+        <v>6703</v>
+      </c>
+      <c r="B105" t="s">
+        <v>49</v>
+      </c>
+      <c r="C105" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105" t="s">
+        <v>53</v>
+      </c>
+      <c r="E105" t="s">
+        <v>55</v>
+      </c>
+      <c r="F105" t="s">
+        <v>56</v>
+      </c>
+      <c r="G105">
+        <v>951</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105" t="s">
+        <v>64</v>
+      </c>
+      <c r="J105" t="s">
+        <v>102</v>
+      </c>
+      <c r="N105" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P105">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>2026</v>
+      </c>
+      <c r="R105">
+        <v>17941156</v>
+      </c>
+      <c r="S105" t="s">
+        <v>130</v>
+      </c>
+      <c r="U105" t="s">
+        <v>140</v>
+      </c>
+      <c r="V105" s="1">
+        <v>46266.25232392361</v>
+      </c>
+      <c r="W105">
+        <v>-7</v>
+      </c>
+      <c r="X105" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB105">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH105" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI105" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="106" spans="1:35">
+      <c r="A106">
+        <v>6779</v>
+      </c>
+      <c r="B106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" t="s">
+        <v>50</v>
+      </c>
+      <c r="D106" t="s">
+        <v>52</v>
+      </c>
+      <c r="E106" t="s">
+        <v>55</v>
+      </c>
+      <c r="F106" t="s">
+        <v>56</v>
+      </c>
+      <c r="G106">
+        <v>951</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106" t="s">
+        <v>64</v>
+      </c>
+      <c r="J106" t="s">
+        <v>102</v>
+      </c>
+      <c r="N106" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P106">
+        <v>8</v>
+      </c>
+      <c r="Q106">
+        <v>2026</v>
+      </c>
+      <c r="R106">
+        <v>18056705</v>
+      </c>
+      <c r="S106" t="s">
+        <v>130</v>
+      </c>
+      <c r="U106" t="s">
+        <v>140</v>
+      </c>
+      <c r="V106" s="1">
+        <v>46266.25239591435</v>
+      </c>
+      <c r="W106">
+        <v>-7</v>
+      </c>
+      <c r="X106" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB106">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH106" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="107" spans="1:35">
+      <c r="A107">
+        <v>6945</v>
+      </c>
+      <c r="B107" t="s">
+        <v>39</v>
+      </c>
+      <c r="C107" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" t="s">
+        <v>52</v>
+      </c>
+      <c r="E107" t="s">
+        <v>54</v>
+      </c>
+      <c r="F107" t="s">
+        <v>57</v>
+      </c>
+      <c r="G107">
+        <v>951</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107" t="s">
+        <v>64</v>
+      </c>
+      <c r="J107" t="s">
+        <v>102</v>
+      </c>
+      <c r="N107" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P107">
+        <v>8</v>
+      </c>
+      <c r="Q107">
+        <v>2026</v>
+      </c>
+      <c r="R107">
+        <v>18164501</v>
+      </c>
+      <c r="S107" t="s">
+        <v>130</v>
+      </c>
+      <c r="U107" t="s">
+        <v>140</v>
+      </c>
+      <c r="V107" s="1">
+        <v>46266.25258329861</v>
+      </c>
+      <c r="W107">
+        <v>-7</v>
+      </c>
+      <c r="X107" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB107">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH107" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:35">
+      <c r="A108">
+        <v>6949</v>
+      </c>
+      <c r="B108" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" t="s">
+        <v>51</v>
+      </c>
+      <c r="E108" t="s">
+        <v>55</v>
+      </c>
+      <c r="F108" t="s">
+        <v>57</v>
+      </c>
+      <c r="G108">
+        <v>951</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108" t="s">
+        <v>64</v>
+      </c>
+      <c r="J108" t="s">
+        <v>102</v>
+      </c>
+      <c r="N108" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P108">
+        <v>8</v>
+      </c>
+      <c r="Q108">
+        <v>2026</v>
+      </c>
+      <c r="R108">
+        <v>18178138</v>
+      </c>
+      <c r="S108" t="s">
+        <v>130</v>
+      </c>
+      <c r="U108" t="s">
+        <v>140</v>
+      </c>
+      <c r="V108" s="1">
+        <v>46266.25259008102</v>
+      </c>
+      <c r="W108">
+        <v>-7</v>
+      </c>
+      <c r="X108" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB108">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH108" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI108" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="109" spans="1:35">
+      <c r="A109">
+        <v>5417</v>
+      </c>
+      <c r="B109" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109" t="s">
+        <v>50</v>
+      </c>
+      <c r="D109" t="s">
+        <v>51</v>
+      </c>
+      <c r="E109" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" t="s">
+        <v>56</v>
+      </c>
+      <c r="G109">
+        <v>953</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109" t="s">
+        <v>64</v>
+      </c>
+      <c r="J109" t="s">
+        <v>103</v>
+      </c>
+      <c r="N109" s="1">
+        <v>46290</v>
+      </c>
+      <c r="P109">
+        <v>8</v>
+      </c>
+      <c r="Q109">
+        <v>2026</v>
+      </c>
+      <c r="R109">
+        <v>17398883</v>
+      </c>
+      <c r="S109" t="s">
+        <v>130</v>
+      </c>
+      <c r="U109" t="s">
+        <v>140</v>
+      </c>
+      <c r="V109" s="1">
+        <v>46266.25305</v>
+      </c>
+      <c r="W109">
+        <v>-22</v>
+      </c>
+      <c r="X109" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB109">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH109" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI109" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="110" spans="1:35">
+      <c r="A110">
+        <v>6404</v>
+      </c>
+      <c r="B110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" t="s">
+        <v>53</v>
+      </c>
+      <c r="E110" t="s">
+        <v>55</v>
+      </c>
+      <c r="F110" t="s">
+        <v>56</v>
+      </c>
+      <c r="G110">
+        <v>953</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110" t="s">
+        <v>64</v>
+      </c>
+      <c r="J110" t="s">
+        <v>103</v>
+      </c>
+      <c r="N110" s="1">
+        <v>46290</v>
+      </c>
+      <c r="P110">
+        <v>8</v>
+      </c>
+      <c r="Q110">
+        <v>2026</v>
+      </c>
+      <c r="R110">
+        <v>16962107</v>
+      </c>
+      <c r="S110" t="s">
+        <v>130</v>
+      </c>
+      <c r="U110" t="s">
+        <v>140</v>
+      </c>
+      <c r="V110" s="1">
+        <v>46266.25270034722</v>
+      </c>
+      <c r="W110">
+        <v>-22</v>
+      </c>
+      <c r="X110" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB110">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH110" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI110" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="111" spans="1:35">
+      <c r="A111">
+        <v>6627</v>
+      </c>
+      <c r="B111" t="s">
+        <v>35</v>
+      </c>
+      <c r="C111" t="s">
+        <v>50</v>
+      </c>
+      <c r="D111" t="s">
+        <v>51</v>
+      </c>
+      <c r="E111" t="s">
+        <v>54</v>
+      </c>
+      <c r="F111" t="s">
+        <v>56</v>
+      </c>
+      <c r="G111">
+        <v>953</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111" t="s">
+        <v>64</v>
+      </c>
+      <c r="J111" t="s">
+        <v>103</v>
+      </c>
+      <c r="N111" s="1">
+        <v>46290</v>
+      </c>
+      <c r="P111">
+        <v>8</v>
+      </c>
+      <c r="Q111">
+        <v>2026</v>
+      </c>
+      <c r="R111">
+        <v>17042317</v>
+      </c>
+      <c r="S111" t="s">
+        <v>130</v>
+      </c>
+      <c r="U111" t="s">
+        <v>140</v>
+      </c>
+      <c r="V111" s="1">
+        <v>46266.25274991898</v>
+      </c>
+      <c r="W111">
+        <v>-22</v>
+      </c>
+      <c r="X111" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB111">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH111" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI111" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="112" spans="1:35">
+      <c r="A112">
+        <v>6703</v>
+      </c>
+      <c r="B112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" t="s">
+        <v>50</v>
+      </c>
+      <c r="D112" t="s">
+        <v>53</v>
+      </c>
+      <c r="E112" t="s">
+        <v>55</v>
+      </c>
+      <c r="F112" t="s">
+        <v>56</v>
+      </c>
+      <c r="G112">
+        <v>953</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112" t="s">
+        <v>64</v>
+      </c>
+      <c r="J112" t="s">
+        <v>103</v>
+      </c>
+      <c r="N112" s="1">
+        <v>46290</v>
+      </c>
+      <c r="P112">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>2026</v>
+      </c>
+      <c r="R112">
+        <v>17941166</v>
+      </c>
+      <c r="S112" t="s">
+        <v>130</v>
+      </c>
+      <c r="U112" t="s">
+        <v>140</v>
+      </c>
+      <c r="V112" s="1">
+        <v>46266.25364633102</v>
+      </c>
+      <c r="W112">
+        <v>-22</v>
+      </c>
+      <c r="X112" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB112">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH112" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI112" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="113" spans="1:35">
+      <c r="A113">
+        <v>6949</v>
+      </c>
+      <c r="B113" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
+        <v>50</v>
+      </c>
+      <c r="D113" t="s">
+        <v>51</v>
+      </c>
+      <c r="E113" t="s">
+        <v>55</v>
+      </c>
+      <c r="F113" t="s">
+        <v>57</v>
+      </c>
+      <c r="G113">
+        <v>953</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113" t="s">
+        <v>64</v>
+      </c>
+      <c r="J113" t="s">
+        <v>103</v>
+      </c>
+      <c r="N113" s="1">
+        <v>46290</v>
+      </c>
+      <c r="P113">
+        <v>8</v>
+      </c>
+      <c r="Q113">
+        <v>2026</v>
+      </c>
+      <c r="R113">
+        <v>18178144</v>
+      </c>
+      <c r="S113" t="s">
+        <v>130</v>
+      </c>
+      <c r="U113" t="s">
+        <v>140</v>
+      </c>
+      <c r="V113" s="1">
+        <v>46266.25369826389</v>
+      </c>
+      <c r="W113">
+        <v>-22</v>
+      </c>
+      <c r="X113" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB113">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH113" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI113" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:35">
+      <c r="A114">
+        <v>5417</v>
+      </c>
+      <c r="B114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" t="s">
+        <v>55</v>
+      </c>
+      <c r="F114" t="s">
+        <v>56</v>
+      </c>
+      <c r="G114">
+        <v>7022</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114" t="s">
+        <v>64</v>
+      </c>
+      <c r="J114" t="s">
+        <v>104</v>
+      </c>
+      <c r="N114" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P114">
+        <v>8</v>
+      </c>
+      <c r="Q114">
+        <v>2026</v>
+      </c>
+      <c r="R114">
+        <v>17399270</v>
+      </c>
+      <c r="S114" t="s">
+        <v>130</v>
+      </c>
+      <c r="U114" t="s">
+        <v>140</v>
+      </c>
+      <c r="V114" s="1">
+        <v>46266.25305112269</v>
+      </c>
+      <c r="W114">
+        <v>-15</v>
+      </c>
+      <c r="X114" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB114">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH114" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI114" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115" spans="1:35">
+      <c r="A115">
+        <v>6627</v>
+      </c>
+      <c r="B115" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115" t="s">
+        <v>50</v>
+      </c>
+      <c r="D115" t="s">
+        <v>51</v>
+      </c>
+      <c r="E115" t="s">
+        <v>54</v>
+      </c>
+      <c r="F115" t="s">
+        <v>56</v>
+      </c>
+      <c r="G115">
+        <v>7022</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115" t="s">
+        <v>64</v>
+      </c>
+      <c r="J115" t="s">
+        <v>104</v>
+      </c>
+      <c r="N115" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P115">
+        <v>8</v>
+      </c>
+      <c r="Q115">
+        <v>2026</v>
+      </c>
+      <c r="R115">
+        <v>17042505</v>
+      </c>
+      <c r="S115" t="s">
+        <v>130</v>
+      </c>
+      <c r="U115" t="s">
+        <v>140</v>
+      </c>
+      <c r="V115" s="1">
+        <v>46266.25275173611</v>
+      </c>
+      <c r="W115">
+        <v>-15</v>
+      </c>
+      <c r="X115" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB115">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH115" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI115" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="116" spans="1:35">
+      <c r="A116">
+        <v>6704</v>
+      </c>
+      <c r="B116" t="s">
+        <v>42</v>
+      </c>
+      <c r="C116" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" t="s">
+        <v>51</v>
+      </c>
+      <c r="E116" t="s">
+        <v>55</v>
+      </c>
+      <c r="F116" t="s">
+        <v>56</v>
+      </c>
+      <c r="G116">
+        <v>7022</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116" t="s">
+        <v>64</v>
+      </c>
+      <c r="J116" t="s">
+        <v>104</v>
+      </c>
+      <c r="N116" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P116">
+        <v>8</v>
+      </c>
+      <c r="Q116">
+        <v>2026</v>
+      </c>
+      <c r="R116">
+        <v>17952421</v>
+      </c>
+      <c r="S116" t="s">
+        <v>130</v>
+      </c>
+      <c r="U116" t="s">
+        <v>140</v>
+      </c>
+      <c r="V116" s="1">
+        <v>46266.25364869213</v>
+      </c>
+      <c r="W116">
+        <v>-15</v>
+      </c>
+      <c r="X116" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB116">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH116" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI116" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" spans="1:35">
+      <c r="A117">
+        <v>6949</v>
+      </c>
+      <c r="B117" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" t="s">
+        <v>50</v>
+      </c>
+      <c r="D117" t="s">
+        <v>51</v>
+      </c>
+      <c r="E117" t="s">
+        <v>55</v>
+      </c>
+      <c r="F117" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117">
+        <v>7022</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117" t="s">
+        <v>64</v>
+      </c>
+      <c r="J117" t="s">
+        <v>104</v>
+      </c>
+      <c r="N117" s="1">
+        <v>46283</v>
+      </c>
+      <c r="P117">
+        <v>8</v>
+      </c>
+      <c r="Q117">
+        <v>2026</v>
+      </c>
+      <c r="R117">
+        <v>18178174</v>
+      </c>
+      <c r="S117" t="s">
+        <v>130</v>
+      </c>
+      <c r="U117" t="s">
+        <v>140</v>
+      </c>
+      <c r="V117" s="1">
+        <v>46266.25369988426</v>
+      </c>
+      <c r="W117">
+        <v>-15</v>
+      </c>
+      <c r="X117" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB117">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH117" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI117" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="118" spans="1:35">
+      <c r="A118">
+        <v>6404</v>
+      </c>
+      <c r="B118" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" t="s">
+        <v>53</v>
+      </c>
+      <c r="E118" t="s">
+        <v>55</v>
+      </c>
+      <c r="F118" t="s">
+        <v>56</v>
+      </c>
+      <c r="G118">
+        <v>11001</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118" t="s">
+        <v>65</v>
+      </c>
+      <c r="J118" t="s">
+        <v>105</v>
+      </c>
+      <c r="N118" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P118">
+        <v>7</v>
+      </c>
+      <c r="Q118">
+        <v>2026</v>
+      </c>
+      <c r="R118">
+        <v>16962453</v>
+      </c>
+      <c r="S118" t="s">
+        <v>55</v>
+      </c>
+      <c r="U118" t="s">
+        <v>139</v>
+      </c>
+      <c r="V118" s="1">
+        <v>46267.66131466435</v>
+      </c>
+      <c r="W118">
+        <v>9</v>
+      </c>
+      <c r="X118" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB118">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH118" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI118" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="119" spans="1:35">
+      <c r="A119">
+        <v>6404</v>
+      </c>
+      <c r="B119" t="s">
+        <v>46</v>
+      </c>
+      <c r="C119" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" t="s">
+        <v>53</v>
+      </c>
+      <c r="E119" t="s">
+        <v>55</v>
+      </c>
+      <c r="F119" t="s">
+        <v>56</v>
+      </c>
+      <c r="G119">
+        <v>11001</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119" t="s">
+        <v>65</v>
+      </c>
+      <c r="J119" t="s">
+        <v>105</v>
+      </c>
+      <c r="N119" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P119">
+        <v>9</v>
+      </c>
+      <c r="Q119">
+        <v>2026</v>
+      </c>
+      <c r="R119">
+        <v>16962455</v>
+      </c>
+      <c r="S119" t="s">
+        <v>55</v>
+      </c>
+      <c r="U119" t="s">
+        <v>140</v>
+      </c>
+      <c r="V119" s="1">
+        <v>46266.21595836805</v>
+      </c>
+      <c r="W119">
+        <v>-53</v>
+      </c>
+      <c r="X119" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB119">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH119" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI119" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="120" spans="1:35">
+      <c r="A120">
+        <v>5417</v>
+      </c>
+      <c r="B120" t="s">
+        <v>43</v>
+      </c>
+      <c r="C120" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" t="s">
+        <v>55</v>
+      </c>
+      <c r="F120" t="s">
+        <v>56</v>
+      </c>
+      <c r="G120">
+        <v>7877</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120" t="s">
+        <v>65</v>
+      </c>
+      <c r="J120" t="s">
+        <v>66</v>
+      </c>
+      <c r="N120" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P120">
+        <v>7</v>
+      </c>
+      <c r="Q120">
+        <v>2026</v>
+      </c>
+      <c r="R120">
+        <v>17399329</v>
+      </c>
+      <c r="S120" t="s">
+        <v>55</v>
+      </c>
+      <c r="U120" t="s">
+        <v>139</v>
+      </c>
+      <c r="V120" s="1">
+        <v>46267.66006940972</v>
+      </c>
+      <c r="W120">
+        <v>9</v>
+      </c>
+      <c r="X120" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB120">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH120" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI120" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="121" spans="1:35">
+      <c r="A121">
+        <v>5417</v>
+      </c>
+      <c r="B121" t="s">
+        <v>43</v>
+      </c>
+      <c r="C121" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" t="s">
+        <v>55</v>
+      </c>
+      <c r="F121" t="s">
+        <v>56</v>
+      </c>
+      <c r="G121">
+        <v>7877</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121" t="s">
+        <v>65</v>
+      </c>
+      <c r="J121" t="s">
+        <v>66</v>
+      </c>
+      <c r="N121" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P121">
+        <v>9</v>
+      </c>
+      <c r="Q121">
+        <v>2026</v>
+      </c>
+      <c r="R121">
+        <v>17399331</v>
+      </c>
+      <c r="S121" t="s">
+        <v>55</v>
+      </c>
+      <c r="U121" t="s">
+        <v>140</v>
+      </c>
+      <c r="V121" s="1">
+        <v>46266.21572962963</v>
+      </c>
+      <c r="W121">
+        <v>-53</v>
+      </c>
+      <c r="X121" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB121">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH121" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI121" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="1:35">
+      <c r="A122">
+        <v>6486</v>
+      </c>
+      <c r="B122" t="s">
+        <v>44</v>
+      </c>
+      <c r="C122" t="s">
+        <v>50</v>
+      </c>
+      <c r="D122" t="s">
+        <v>51</v>
+      </c>
+      <c r="E122" t="s">
+        <v>55</v>
+      </c>
+      <c r="F122" t="s">
+        <v>56</v>
+      </c>
+      <c r="G122">
+        <v>9774</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122" t="s">
+        <v>65</v>
+      </c>
+      <c r="J122" t="s">
+        <v>106</v>
+      </c>
+      <c r="N122" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P122">
+        <v>7</v>
+      </c>
+      <c r="Q122">
+        <v>2026</v>
+      </c>
+      <c r="R122">
+        <v>16976320</v>
+      </c>
+      <c r="S122" t="s">
+        <v>55</v>
+      </c>
+      <c r="U122" t="s">
+        <v>139</v>
+      </c>
+      <c r="V122" s="1">
+        <v>46267.67127083334</v>
+      </c>
+      <c r="W122">
+        <v>9</v>
+      </c>
+      <c r="X122" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB122">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH122" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI122" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="123" spans="1:35">
+      <c r="A123">
+        <v>6486</v>
+      </c>
+      <c r="B123" t="s">
+        <v>44</v>
+      </c>
+      <c r="C123" t="s">
+        <v>50</v>
+      </c>
+      <c r="D123" t="s">
+        <v>51</v>
+      </c>
+      <c r="E123" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" t="s">
+        <v>56</v>
+      </c>
+      <c r="G123">
+        <v>9774</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123" t="s">
+        <v>65</v>
+      </c>
+      <c r="J123" t="s">
+        <v>106</v>
+      </c>
+      <c r="N123" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P123">
+        <v>9</v>
+      </c>
+      <c r="Q123">
+        <v>2026</v>
+      </c>
+      <c r="R123">
+        <v>16976322</v>
+      </c>
+      <c r="S123" t="s">
+        <v>55</v>
+      </c>
+      <c r="U123" t="s">
+        <v>140</v>
+      </c>
+      <c r="V123" s="1">
+        <v>46266.21550011574</v>
+      </c>
+      <c r="W123">
+        <v>-53</v>
+      </c>
+      <c r="X123" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB123">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH123" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI123" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="124" spans="1:35">
+      <c r="A124">
+        <v>5417</v>
+      </c>
+      <c r="B124" t="s">
+        <v>43</v>
+      </c>
+      <c r="C124" t="s">
+        <v>50</v>
+      </c>
+      <c r="D124" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" t="s">
+        <v>55</v>
+      </c>
+      <c r="F124" t="s">
+        <v>56</v>
+      </c>
+      <c r="G124">
         <v>7027</v>
       </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78" t="s">
-        <v>64</v>
-      </c>
-      <c r="J78" t="s">
-        <v>94</v>
-      </c>
-      <c r="N78" s="1">
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124" t="s">
+        <v>65</v>
+      </c>
+      <c r="J124" t="s">
+        <v>107</v>
+      </c>
+      <c r="N124" s="1">
         <v>46321</v>
       </c>
-      <c r="P78">
+      <c r="P124">
         <v>9</v>
       </c>
-      <c r="Q78">
-        <v>2026</v>
-      </c>
-      <c r="R78">
+      <c r="Q124">
+        <v>2026</v>
+      </c>
+      <c r="R124">
+        <v>17399291</v>
+      </c>
+      <c r="S124" t="s">
+        <v>55</v>
+      </c>
+      <c r="U124" t="s">
+        <v>140</v>
+      </c>
+      <c r="V124" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W124">
+        <v>-53</v>
+      </c>
+      <c r="X124" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB124">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH124" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI124" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:35">
+      <c r="A125">
+        <v>6404</v>
+      </c>
+      <c r="B125" t="s">
+        <v>46</v>
+      </c>
+      <c r="C125" t="s">
+        <v>50</v>
+      </c>
+      <c r="D125" t="s">
+        <v>53</v>
+      </c>
+      <c r="E125" t="s">
+        <v>55</v>
+      </c>
+      <c r="F125" t="s">
+        <v>56</v>
+      </c>
+      <c r="G125">
+        <v>7027</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125" t="s">
+        <v>65</v>
+      </c>
+      <c r="J125" t="s">
+        <v>107</v>
+      </c>
+      <c r="N125" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P125">
+        <v>9</v>
+      </c>
+      <c r="Q125">
+        <v>2026</v>
+      </c>
+      <c r="R125">
+        <v>16962349</v>
+      </c>
+      <c r="S125" t="s">
+        <v>55</v>
+      </c>
+      <c r="U125" t="s">
+        <v>140</v>
+      </c>
+      <c r="V125" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W125">
+        <v>-53</v>
+      </c>
+      <c r="X125" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB125">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH125" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI125" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="126" spans="1:35">
+      <c r="A126">
+        <v>6486</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" t="s">
+        <v>50</v>
+      </c>
+      <c r="D126" t="s">
+        <v>51</v>
+      </c>
+      <c r="E126" t="s">
+        <v>55</v>
+      </c>
+      <c r="F126" t="s">
+        <v>56</v>
+      </c>
+      <c r="G126">
+        <v>7027</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126" t="s">
+        <v>65</v>
+      </c>
+      <c r="J126" t="s">
+        <v>107</v>
+      </c>
+      <c r="N126" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P126">
+        <v>9</v>
+      </c>
+      <c r="Q126">
+        <v>2026</v>
+      </c>
+      <c r="R126">
         <v>16976238</v>
       </c>
-      <c r="S78" t="s">
-        <v>55</v>
-      </c>
-      <c r="U78" t="s">
-        <v>122</v>
-      </c>
-      <c r="V78" s="1">
+      <c r="S126" t="s">
+        <v>55</v>
+      </c>
+      <c r="U126" t="s">
+        <v>140</v>
+      </c>
+      <c r="V126" s="1">
         <v>46266.00006921296</v>
       </c>
-      <c r="W78">
-        <v>-54</v>
-      </c>
-      <c r="X78" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB78">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH78" t="s">
-        <v>171</v>
-      </c>
-      <c r="AI78" t="s">
-        <v>174</v>
+      <c r="W126">
+        <v>-53</v>
+      </c>
+      <c r="X126" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB126">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH126" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI126" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="198">
   <si>
     <t>CodCliente</t>
   </si>
@@ -516,6 +516,9 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/09/2026 
 Tarefa a ser realizada em: 02/09/2026 - Data Comentário: 02/09/2026 16:24</t>
+  </si>
+  <si>
+    <t>Segundo informado pela coordenadora Nayara Oliveira, tarefa será conclupida hoje, 03/09 - Data Comentário: 03/09/2026 10:15</t>
   </si>
   <si>
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/09/2026 00:58</t>
@@ -1128,10 +1131,10 @@
         <v>112</v>
       </c>
       <c r="AH2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1205,10 +1208,10 @@
         <v>113</v>
       </c>
       <c r="AH3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1279,10 +1282,10 @@
         <v>113</v>
       </c>
       <c r="AH4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1353,10 +1356,10 @@
         <v>112</v>
       </c>
       <c r="AH5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1427,10 +1430,10 @@
         <v>112</v>
       </c>
       <c r="AH6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1501,10 +1504,10 @@
         <v>114</v>
       </c>
       <c r="AH7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1575,10 +1578,10 @@
         <v>113</v>
       </c>
       <c r="AH8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1649,10 +1652,10 @@
         <v>115</v>
       </c>
       <c r="AH9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1723,10 +1726,10 @@
         <v>115</v>
       </c>
       <c r="AH10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1797,10 +1800,10 @@
         <v>116</v>
       </c>
       <c r="AH11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -1868,13 +1871,13 @@
         <v>0</v>
       </c>
       <c r="AC12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AH12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -1942,13 +1945,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AH13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2016,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2081,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2152,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2226,10 +2229,10 @@
         <v>119</v>
       </c>
       <c r="AH17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2300,10 +2303,10 @@
         <v>116</v>
       </c>
       <c r="AH18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2374,10 +2377,10 @@
         <v>116</v>
       </c>
       <c r="AH19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2448,10 +2451,10 @@
         <v>116</v>
       </c>
       <c r="AH20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2522,10 +2525,10 @@
         <v>117</v>
       </c>
       <c r="AH21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2596,10 +2599,10 @@
         <v>116</v>
       </c>
       <c r="AH22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2670,10 +2673,10 @@
         <v>116</v>
       </c>
       <c r="AH23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2744,10 +2747,10 @@
         <v>116</v>
       </c>
       <c r="AH24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -2824,10 +2827,10 @@
         <v>120</v>
       </c>
       <c r="AH25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -2901,10 +2904,10 @@
         <v>121</v>
       </c>
       <c r="AH26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -2978,10 +2981,10 @@
         <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3058,10 +3061,10 @@
         <v>122</v>
       </c>
       <c r="AH28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3138,10 +3141,10 @@
         <v>123</v>
       </c>
       <c r="AH29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3212,10 +3215,10 @@
         <v>122</v>
       </c>
       <c r="AH30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3292,10 +3295,10 @@
         <v>120</v>
       </c>
       <c r="AH31" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3372,10 +3375,10 @@
         <v>124</v>
       </c>
       <c r="AH32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3452,10 +3455,10 @@
         <v>122</v>
       </c>
       <c r="AH33" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3532,10 +3535,10 @@
         <v>123</v>
       </c>
       <c r="AH34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3606,10 +3609,10 @@
         <v>122</v>
       </c>
       <c r="AH35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3680,10 +3683,10 @@
         <v>123</v>
       </c>
       <c r="AH36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3754,10 +3757,10 @@
         <v>126</v>
       </c>
       <c r="AH37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -3828,10 +3831,10 @@
         <v>126</v>
       </c>
       <c r="AH38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -3902,10 +3905,10 @@
         <v>127</v>
       </c>
       <c r="AH39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -3976,10 +3979,10 @@
         <v>126</v>
       </c>
       <c r="AH40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4050,10 +4053,10 @@
         <v>126</v>
       </c>
       <c r="AH41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4130,10 +4133,10 @@
         <v>126</v>
       </c>
       <c r="AH42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4204,10 +4207,10 @@
         <v>127</v>
       </c>
       <c r="AH43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4278,10 +4281,10 @@
         <v>126</v>
       </c>
       <c r="AH44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4352,10 +4355,10 @@
         <v>126</v>
       </c>
       <c r="AH45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4426,10 +4429,10 @@
         <v>126</v>
       </c>
       <c r="AH46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4500,10 +4503,10 @@
         <v>126</v>
       </c>
       <c r="AH47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4574,10 +4577,10 @@
         <v>127</v>
       </c>
       <c r="AH48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4648,10 +4651,10 @@
         <v>126</v>
       </c>
       <c r="AH49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4722,10 +4725,10 @@
         <v>126</v>
       </c>
       <c r="AH50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -4796,10 +4799,10 @@
         <v>126</v>
       </c>
       <c r="AH51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -4870,10 +4873,10 @@
         <v>126</v>
       </c>
       <c r="AH52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -4944,10 +4947,10 @@
         <v>127</v>
       </c>
       <c r="AH53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5018,10 +5021,10 @@
         <v>126</v>
       </c>
       <c r="AH54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5092,10 +5095,10 @@
         <v>126</v>
       </c>
       <c r="AH55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5166,10 +5169,10 @@
         <v>127</v>
       </c>
       <c r="AH56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5206,6 +5209,9 @@
       <c r="N57" s="1">
         <v>46268</v>
       </c>
+      <c r="O57" t="s">
+        <v>109</v>
+      </c>
       <c r="P57">
         <v>8</v>
       </c>
@@ -5233,6 +5239,9 @@
       <c r="X57" t="s">
         <v>146</v>
       </c>
+      <c r="Y57" t="s">
+        <v>165</v>
+      </c>
       <c r="AB57">
         <v>0</v>
       </c>
@@ -5240,10 +5249,10 @@
         <v>126</v>
       </c>
       <c r="AH57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5314,10 +5323,10 @@
         <v>126</v>
       </c>
       <c r="AH58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5388,10 +5397,10 @@
         <v>126</v>
       </c>
       <c r="AH59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5462,10 +5471,10 @@
         <v>126</v>
       </c>
       <c r="AH60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5536,10 +5545,10 @@
         <v>126</v>
       </c>
       <c r="AH61" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5610,10 +5619,10 @@
         <v>126</v>
       </c>
       <c r="AH62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -5684,10 +5693,10 @@
         <v>127</v>
       </c>
       <c r="AH63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -5758,10 +5767,10 @@
         <v>126</v>
       </c>
       <c r="AH64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -5832,10 +5841,10 @@
         <v>126</v>
       </c>
       <c r="AH65" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -5906,10 +5915,10 @@
         <v>126</v>
       </c>
       <c r="AH66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -5980,10 +5989,10 @@
         <v>127</v>
       </c>
       <c r="AH67" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6054,10 +6063,10 @@
         <v>128</v>
       </c>
       <c r="AH68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6128,10 +6137,10 @@
         <v>127</v>
       </c>
       <c r="AH69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6202,10 +6211,10 @@
         <v>125</v>
       </c>
       <c r="AH70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6276,10 +6285,10 @@
         <v>128</v>
       </c>
       <c r="AH71" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6350,10 +6359,10 @@
         <v>127</v>
       </c>
       <c r="AH72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6424,10 +6433,10 @@
         <v>126</v>
       </c>
       <c r="AH73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6498,10 +6507,10 @@
         <v>126</v>
       </c>
       <c r="AH74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6572,10 +6581,10 @@
         <v>126</v>
       </c>
       <c r="AH75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6646,10 +6655,10 @@
         <v>126</v>
       </c>
       <c r="AH76" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -6720,10 +6729,10 @@
         <v>127</v>
       </c>
       <c r="AH77" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -6794,10 +6803,10 @@
         <v>126</v>
       </c>
       <c r="AH78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI78" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -6868,10 +6877,10 @@
         <v>126</v>
       </c>
       <c r="AH79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -6942,10 +6951,10 @@
         <v>126</v>
       </c>
       <c r="AH80" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7016,10 +7025,10 @@
         <v>126</v>
       </c>
       <c r="AH81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7090,10 +7099,10 @@
         <v>127</v>
       </c>
       <c r="AH82" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI82" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7164,10 +7173,10 @@
         <v>129</v>
       </c>
       <c r="AH83" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI83" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7238,10 +7247,10 @@
         <v>129</v>
       </c>
       <c r="AH84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI84" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7312,10 +7321,10 @@
         <v>129</v>
       </c>
       <c r="AH85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7386,10 +7395,10 @@
         <v>129</v>
       </c>
       <c r="AH86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI86" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7460,10 +7469,10 @@
         <v>129</v>
       </c>
       <c r="AH87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI87" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7534,10 +7543,10 @@
         <v>129</v>
       </c>
       <c r="AH88" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7608,10 +7617,10 @@
         <v>129</v>
       </c>
       <c r="AH89" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI89" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -7682,10 +7691,10 @@
         <v>129</v>
       </c>
       <c r="AH90" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI90" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -7756,10 +7765,10 @@
         <v>129</v>
       </c>
       <c r="AH91" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI91" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -7830,10 +7839,10 @@
         <v>129</v>
       </c>
       <c r="AH92" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI92" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -7904,10 +7913,10 @@
         <v>129</v>
       </c>
       <c r="AH93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -7978,10 +7987,10 @@
         <v>129</v>
       </c>
       <c r="AH94" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8052,10 +8061,10 @@
         <v>129</v>
       </c>
       <c r="AH95" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8117,7 +8126,7 @@
         <v>142</v>
       </c>
       <c r="Y96" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AB96">
         <v>0</v>
@@ -8126,10 +8135,10 @@
         <v>130</v>
       </c>
       <c r="AH96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI96" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8191,7 +8200,7 @@
         <v>147</v>
       </c>
       <c r="Y97" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AB97">
         <v>0</v>
@@ -8200,10 +8209,10 @@
         <v>130</v>
       </c>
       <c r="AH97" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI97" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8265,7 +8274,7 @@
         <v>145</v>
       </c>
       <c r="Y98" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB98">
         <v>0</v>
@@ -8274,10 +8283,10 @@
         <v>130</v>
       </c>
       <c r="AH98" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8339,7 +8348,7 @@
         <v>148</v>
       </c>
       <c r="Y99" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AB99">
         <v>0</v>
@@ -8348,10 +8357,10 @@
         <v>130</v>
       </c>
       <c r="AH99" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI99" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8413,7 +8422,7 @@
         <v>151</v>
       </c>
       <c r="Y100" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB100">
         <v>0</v>
@@ -8422,10 +8431,10 @@
         <v>130</v>
       </c>
       <c r="AH100" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI100" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8487,7 +8496,7 @@
         <v>152</v>
       </c>
       <c r="Y101" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AB101">
         <v>0</v>
@@ -8496,10 +8505,10 @@
         <v>130</v>
       </c>
       <c r="AH101" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI101" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8561,7 +8570,7 @@
         <v>152</v>
       </c>
       <c r="Y102" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AB102">
         <v>0</v>
@@ -8570,10 +8579,10 @@
         <v>130</v>
       </c>
       <c r="AH102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI102" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8635,7 +8644,7 @@
         <v>143</v>
       </c>
       <c r="Y103" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AB103">
         <v>0</v>
@@ -8644,10 +8653,10 @@
         <v>130</v>
       </c>
       <c r="AH103" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI103" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -8709,7 +8718,7 @@
         <v>144</v>
       </c>
       <c r="Y104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB104">
         <v>0</v>
@@ -8718,10 +8727,10 @@
         <v>130</v>
       </c>
       <c r="AH104" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI104" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -8783,7 +8792,7 @@
         <v>152</v>
       </c>
       <c r="Y105" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB105">
         <v>0</v>
@@ -8792,10 +8801,10 @@
         <v>130</v>
       </c>
       <c r="AH105" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -8857,7 +8866,7 @@
         <v>147</v>
       </c>
       <c r="Y106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB106">
         <v>0</v>
@@ -8866,10 +8875,10 @@
         <v>130</v>
       </c>
       <c r="AH106" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI106" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -8931,7 +8940,7 @@
         <v>145</v>
       </c>
       <c r="Y107" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AB107">
         <v>0</v>
@@ -8940,10 +8949,10 @@
         <v>130</v>
       </c>
       <c r="AH107" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI107" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9005,7 +9014,7 @@
         <v>143</v>
       </c>
       <c r="Y108" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AB108">
         <v>0</v>
@@ -9014,10 +9023,10 @@
         <v>130</v>
       </c>
       <c r="AH108" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI108" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9079,7 +9088,7 @@
         <v>148</v>
       </c>
       <c r="Y109" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB109">
         <v>0</v>
@@ -9088,10 +9097,10 @@
         <v>130</v>
       </c>
       <c r="AH109" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI109" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9153,7 +9162,7 @@
         <v>151</v>
       </c>
       <c r="Y110" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AB110">
         <v>0</v>
@@ -9162,10 +9171,10 @@
         <v>130</v>
       </c>
       <c r="AH110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI110" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9227,7 +9236,7 @@
         <v>142</v>
       </c>
       <c r="Y111" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AB111">
         <v>0</v>
@@ -9236,10 +9245,10 @@
         <v>130</v>
       </c>
       <c r="AH111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9301,7 +9310,7 @@
         <v>152</v>
       </c>
       <c r="Y112" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AB112">
         <v>0</v>
@@ -9310,10 +9319,10 @@
         <v>130</v>
       </c>
       <c r="AH112" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9375,7 +9384,7 @@
         <v>143</v>
       </c>
       <c r="Y113" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -9384,10 +9393,10 @@
         <v>130</v>
       </c>
       <c r="AH113" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9449,7 +9458,7 @@
         <v>148</v>
       </c>
       <c r="Y114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AB114">
         <v>0</v>
@@ -9458,10 +9467,10 @@
         <v>130</v>
       </c>
       <c r="AH114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI114" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9523,7 +9532,7 @@
         <v>142</v>
       </c>
       <c r="Y115" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AB115">
         <v>0</v>
@@ -9532,10 +9541,10 @@
         <v>130</v>
       </c>
       <c r="AH115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI115" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9597,7 +9606,7 @@
         <v>147</v>
       </c>
       <c r="Y116" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB116">
         <v>0</v>
@@ -9606,10 +9615,10 @@
         <v>130</v>
       </c>
       <c r="AH116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI116" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -9671,7 +9680,7 @@
         <v>143</v>
       </c>
       <c r="Y117" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AB117">
         <v>0</v>
@@ -9680,10 +9689,10 @@
         <v>130</v>
       </c>
       <c r="AH117" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI117" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -9745,7 +9754,7 @@
         <v>151</v>
       </c>
       <c r="Y118" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB118">
         <v>0</v>
@@ -9754,10 +9763,10 @@
         <v>55</v>
       </c>
       <c r="AH118" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI118" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -9819,7 +9828,7 @@
         <v>151</v>
       </c>
       <c r="Y119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AB119">
         <v>0</v>
@@ -9828,10 +9837,10 @@
         <v>55</v>
       </c>
       <c r="AH119" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI119" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -9893,7 +9902,7 @@
         <v>148</v>
       </c>
       <c r="Y120" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AB120">
         <v>0</v>
@@ -9902,10 +9911,10 @@
         <v>55</v>
       </c>
       <c r="AH120" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI120" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -9967,7 +9976,7 @@
         <v>148</v>
       </c>
       <c r="Y121" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB121">
         <v>0</v>
@@ -9976,10 +9985,10 @@
         <v>55</v>
       </c>
       <c r="AH121" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI121" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10041,7 +10050,7 @@
         <v>149</v>
       </c>
       <c r="Y122" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AB122">
         <v>0</v>
@@ -10050,10 +10059,10 @@
         <v>55</v>
       </c>
       <c r="AH122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI122" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10115,7 +10124,7 @@
         <v>149</v>
       </c>
       <c r="Y123" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AB123">
         <v>0</v>
@@ -10124,10 +10133,10 @@
         <v>55</v>
       </c>
       <c r="AH123" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI123" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10195,10 +10204,10 @@
         <v>55</v>
       </c>
       <c r="AH124" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI124" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10266,10 +10275,10 @@
         <v>55</v>
       </c>
       <c r="AH125" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10337,10 +10346,10 @@
         <v>55</v>
       </c>
       <c r="AH126" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI126" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="212">
   <si>
     <t>CodCliente</t>
   </si>
@@ -536,6 +536,10 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 02/09/2026 
 Ítalo informou que será enviado amanhã, pois está fechando as vendas/comissões hoje. Folha fecha 30. - Data Comentário: 01/09/2026 12:01</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/09/2026 
+Atraso por parte do cliente no envio dos documentos necessários, o mesmo vem sendo cobrado diariamente. Informou o envio dia 01/09 e depois 02/09, porém sem sucesso. Está ciente quanto aos prazos de pagamento. - Data Comentário: 02/09/2026 17:22</t>
   </si>
   <si>
     <t>Atraso por parte do cliente no envio dos documentos necessários, o mesmo vem sendo cobrado diariamente e informou o envio até o fim do dia 02/09 - Data Comentário: 02/09/2026 12:36</t>
@@ -990,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI156"/>
+  <dimension ref="A1:AI158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1171,10 +1175,10 @@
         <v>117</v>
       </c>
       <c r="AH2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1248,10 +1252,10 @@
         <v>118</v>
       </c>
       <c r="AH3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1325,10 +1329,10 @@
         <v>117</v>
       </c>
       <c r="AH4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1399,10 +1403,10 @@
         <v>117</v>
       </c>
       <c r="AH5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1473,10 +1477,10 @@
         <v>118</v>
       </c>
       <c r="AH6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1547,10 +1551,10 @@
         <v>118</v>
       </c>
       <c r="AH7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1621,10 +1625,10 @@
         <v>119</v>
       </c>
       <c r="AH8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1695,10 +1699,10 @@
         <v>117</v>
       </c>
       <c r="AH9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1769,10 +1773,10 @@
         <v>120</v>
       </c>
       <c r="AH10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1843,10 +1847,10 @@
         <v>120</v>
       </c>
       <c r="AH11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -1917,10 +1921,10 @@
         <v>121</v>
       </c>
       <c r="AH12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -1988,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AH13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2062,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AH14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2136,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2201,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2272,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2349,10 +2353,10 @@
         <v>122</v>
       </c>
       <c r="AH18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2423,10 +2427,10 @@
         <v>124</v>
       </c>
       <c r="AH19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2497,10 +2501,10 @@
         <v>121</v>
       </c>
       <c r="AH20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2571,10 +2575,10 @@
         <v>121</v>
       </c>
       <c r="AH21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2645,10 +2649,10 @@
         <v>121</v>
       </c>
       <c r="AH22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2719,10 +2723,10 @@
         <v>122</v>
       </c>
       <c r="AH23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2793,10 +2797,10 @@
         <v>121</v>
       </c>
       <c r="AH24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -2867,10 +2871,10 @@
         <v>121</v>
       </c>
       <c r="AH25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -2941,10 +2945,10 @@
         <v>121</v>
       </c>
       <c r="AH26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3015,10 +3019,10 @@
         <v>125</v>
       </c>
       <c r="AH27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3095,10 +3099,10 @@
         <v>126</v>
       </c>
       <c r="AH28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3172,10 +3176,10 @@
         <v>127</v>
       </c>
       <c r="AH29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3249,10 +3253,10 @@
         <v>142</v>
       </c>
       <c r="AH30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3329,10 +3333,10 @@
         <v>126</v>
       </c>
       <c r="AH31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3409,10 +3413,10 @@
         <v>125</v>
       </c>
       <c r="AH32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3489,10 +3493,10 @@
         <v>128</v>
       </c>
       <c r="AH33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3569,10 +3573,10 @@
         <v>129</v>
       </c>
       <c r="AH34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3643,10 +3647,10 @@
         <v>125</v>
       </c>
       <c r="AH35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3717,10 +3721,10 @@
         <v>128</v>
       </c>
       <c r="AH36" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3797,27 +3801,27 @@
         <v>126</v>
       </c>
       <c r="AH37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:35">
       <c r="A38">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
         <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
         <v>56</v>
@@ -3838,7 +3842,7 @@
         <v>46266</v>
       </c>
       <c r="O38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3847,10 +3851,10 @@
         <v>2026</v>
       </c>
       <c r="R38">
-        <v>18195915</v>
+        <v>18157815</v>
       </c>
       <c r="S38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T38" t="s">
         <v>141</v>
@@ -3859,13 +3863,13 @@
         <v>145</v>
       </c>
       <c r="V38" s="1">
-        <v>46267.74532275463</v>
+        <v>46268.71229238426</v>
       </c>
       <c r="W38">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="Y38" t="s">
         <v>172</v>
@@ -3874,36 +3878,36 @@
         <v>0</v>
       </c>
       <c r="AC38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:35">
       <c r="A39">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
         <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
         <v>56</v>
       </c>
       <c r="G39">
-        <v>5906</v>
+        <v>5838</v>
       </c>
       <c r="H39">
         <v>5784</v>
@@ -3912,13 +3916,13 @@
         <v>61</v>
       </c>
       <c r="J39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N39" s="1">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="O39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -3927,7 +3931,7 @@
         <v>2026</v>
       </c>
       <c r="R39">
-        <v>16976096</v>
+        <v>18157798</v>
       </c>
       <c r="S39" t="s">
         <v>126</v>
@@ -3936,19 +3940,19 @@
         <v>141</v>
       </c>
       <c r="U39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V39" s="1">
-        <v>46268.45926839121</v>
+        <v>46268.71229297454</v>
       </c>
       <c r="W39">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="Y39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB39">
         <v>0</v>
@@ -3957,10 +3961,10 @@
         <v>126</v>
       </c>
       <c r="AH39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -3983,7 +3987,7 @@
         <v>56</v>
       </c>
       <c r="G40">
-        <v>5906</v>
+        <v>5838</v>
       </c>
       <c r="H40">
         <v>5784</v>
@@ -3992,13 +3996,13 @@
         <v>61</v>
       </c>
       <c r="J40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N40" s="1">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="O40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -4007,7 +4011,7 @@
         <v>2026</v>
       </c>
       <c r="R40">
-        <v>18077142</v>
+        <v>18195915</v>
       </c>
       <c r="S40" t="s">
         <v>125</v>
@@ -4016,13 +4020,13 @@
         <v>141</v>
       </c>
       <c r="U40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V40" s="1">
-        <v>46268.58922707176</v>
+        <v>46267.74532275463</v>
       </c>
       <c r="W40">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="X40" t="s">
         <v>158</v>
@@ -4037,24 +4041,24 @@
         <v>125</v>
       </c>
       <c r="AH40" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:35">
       <c r="A41">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
         <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>54</v>
@@ -4087,60 +4091,60 @@
         <v>2026</v>
       </c>
       <c r="R41">
-        <v>18090229</v>
+        <v>16976096</v>
       </c>
       <c r="S41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U41" t="s">
         <v>146</v>
       </c>
       <c r="V41" s="1">
-        <v>46267.64800344907</v>
+        <v>46268.45926839121</v>
       </c>
       <c r="W41">
         <v>-5</v>
       </c>
       <c r="X41" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AH41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:35">
       <c r="A42">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G42">
         <v>5906</v>
@@ -4167,54 +4171,54 @@
         <v>2026</v>
       </c>
       <c r="R42">
-        <v>18179139</v>
+        <v>18077142</v>
       </c>
       <c r="S42" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U42" t="s">
         <v>146</v>
       </c>
       <c r="V42" s="1">
-        <v>46267.44799793982</v>
+        <v>46268.58922707176</v>
       </c>
       <c r="W42">
         <v>-5</v>
       </c>
       <c r="X42" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Y42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB42">
         <v>0</v>
       </c>
       <c r="AC42" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AH42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:35">
       <c r="A43">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
         <v>54</v>
@@ -4223,7 +4227,7 @@
         <v>56</v>
       </c>
       <c r="G43">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="H43">
         <v>5784</v>
@@ -4232,11 +4236,14 @@
         <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N43" s="1">
         <v>46273</v>
       </c>
+      <c r="O43" t="s">
+        <v>116</v>
+      </c>
       <c r="P43">
         <v>8</v>
       </c>
@@ -4244,60 +4251,63 @@
         <v>2026</v>
       </c>
       <c r="R43">
-        <v>16976106</v>
+        <v>18090229</v>
       </c>
       <c r="S43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="T43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U43" t="s">
         <v>146</v>
       </c>
       <c r="V43" s="1">
-        <v>46268.45929986111</v>
+        <v>46267.64800344907</v>
       </c>
       <c r="W43">
         <v>-5</v>
       </c>
       <c r="X43" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>174</v>
       </c>
       <c r="AB43">
         <v>0</v>
       </c>
       <c r="AC43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:35">
       <c r="A44">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G44">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="H44">
         <v>5784</v>
@@ -4306,11 +4316,14 @@
         <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N44" s="1">
         <v>46273</v>
       </c>
+      <c r="O44" t="s">
+        <v>116</v>
+      </c>
       <c r="P44">
         <v>8</v>
       </c>
@@ -4318,51 +4331,54 @@
         <v>2026</v>
       </c>
       <c r="R44">
-        <v>18077152</v>
+        <v>18179139</v>
       </c>
       <c r="S44" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="T44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U44" t="s">
         <v>146</v>
       </c>
       <c r="V44" s="1">
-        <v>46268.58932953704</v>
+        <v>46267.44799793982</v>
       </c>
       <c r="W44">
         <v>-5</v>
       </c>
       <c r="X44" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>174</v>
       </c>
       <c r="AB44">
         <v>0</v>
       </c>
       <c r="AC44" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AH44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="1:35">
       <c r="A45">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
         <v>54</v>
@@ -4392,57 +4408,57 @@
         <v>2026</v>
       </c>
       <c r="R45">
-        <v>18090239</v>
+        <v>16976106</v>
       </c>
       <c r="S45" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U45" t="s">
         <v>146</v>
       </c>
       <c r="V45" s="1">
-        <v>46267.648038125</v>
+        <v>46268.45929986111</v>
       </c>
       <c r="W45">
         <v>-5</v>
       </c>
       <c r="X45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AB45">
         <v>0</v>
       </c>
       <c r="AC45" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AH45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI45" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:35">
       <c r="A46">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G46">
         <v>5907</v>
@@ -4466,51 +4482,51 @@
         <v>2026</v>
       </c>
       <c r="R46">
-        <v>18179146</v>
+        <v>18077152</v>
       </c>
       <c r="S46" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U46" t="s">
         <v>146</v>
       </c>
       <c r="V46" s="1">
-        <v>46267.44824061343</v>
+        <v>46268.58932953704</v>
       </c>
       <c r="W46">
         <v>-5</v>
       </c>
       <c r="X46" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AB46">
         <v>0</v>
       </c>
       <c r="AC46" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AH46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:35">
       <c r="A47">
-        <v>6548</v>
+        <v>6779</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
         <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
         <v>54</v>
@@ -4519,19 +4535,19 @@
         <v>56</v>
       </c>
       <c r="G47">
-        <v>11550</v>
+        <v>5907</v>
       </c>
       <c r="H47">
-        <v>1862</v>
+        <v>5784</v>
       </c>
       <c r="I47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N47" s="1">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="P47">
         <v>8</v>
@@ -4540,72 +4556,72 @@
         <v>2026</v>
       </c>
       <c r="R47">
-        <v>17988603</v>
+        <v>18090239</v>
       </c>
       <c r="S47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="T47" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="U47" t="s">
         <v>146</v>
       </c>
       <c r="V47" s="1">
-        <v>46267.72055925926</v>
+        <v>46267.648038125</v>
       </c>
       <c r="W47">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="X47" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AB47">
         <v>0</v>
       </c>
       <c r="AC47" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="AH47" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:35">
       <c r="A48">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
         <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G48">
-        <v>11550</v>
+        <v>5907</v>
       </c>
       <c r="H48">
-        <v>1862</v>
+        <v>5784</v>
       </c>
       <c r="I48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N48" s="1">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="P48">
         <v>8</v>
@@ -4614,45 +4630,45 @@
         <v>2026</v>
       </c>
       <c r="R48">
-        <v>18048493</v>
+        <v>18179146</v>
       </c>
       <c r="S48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T48" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="U48" t="s">
         <v>146</v>
       </c>
       <c r="V48" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.44824061343</v>
       </c>
       <c r="W48">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="X48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AB48">
         <v>0</v>
       </c>
       <c r="AC48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AH48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:35">
       <c r="A49">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
         <v>50</v>
@@ -4664,7 +4680,7 @@
         <v>54</v>
       </c>
       <c r="F49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G49">
         <v>11550</v>
@@ -4688,10 +4704,10 @@
         <v>2026</v>
       </c>
       <c r="R49">
-        <v>18214931</v>
+        <v>17988603</v>
       </c>
       <c r="S49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T49" t="s">
         <v>131</v>
@@ -4700,33 +4716,33 @@
         <v>146</v>
       </c>
       <c r="V49" s="1">
-        <v>46267.79441215278</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="W49">
         <v>-18</v>
       </c>
       <c r="X49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB49">
         <v>0</v>
       </c>
       <c r="AC49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI49" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:35">
       <c r="A50">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
         <v>50</v>
@@ -4735,25 +4751,25 @@
         <v>51</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
         <v>56</v>
       </c>
       <c r="G50">
-        <v>11752</v>
+        <v>11550</v>
       </c>
       <c r="H50">
-        <v>11751</v>
+        <v>1862</v>
       </c>
       <c r="I50" t="s">
         <v>62</v>
       </c>
       <c r="J50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N50" s="1">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="P50">
         <v>8</v>
@@ -4762,25 +4778,25 @@
         <v>2026</v>
       </c>
       <c r="R50">
-        <v>18260411</v>
+        <v>18048493</v>
       </c>
       <c r="S50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T50" t="s">
         <v>131</v>
       </c>
       <c r="U50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V50" s="1">
-        <v>46267.7205502662</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="W50">
-        <v>1</v>
+        <v>-18</v>
       </c>
       <c r="X50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB50">
         <v>0</v>
@@ -4789,18 +4805,18 @@
         <v>131</v>
       </c>
       <c r="AH50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:35">
       <c r="A51">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
         <v>50</v>
@@ -4809,25 +4825,25 @@
         <v>51</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G51">
-        <v>11752</v>
+        <v>11550</v>
       </c>
       <c r="H51">
-        <v>11751</v>
+        <v>1862</v>
       </c>
       <c r="I51" t="s">
         <v>62</v>
       </c>
       <c r="J51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N51" s="1">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="P51">
         <v>8</v>
@@ -4836,10 +4852,10 @@
         <v>2026</v>
       </c>
       <c r="R51">
-        <v>18173143</v>
+        <v>18214931</v>
       </c>
       <c r="S51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T51" t="s">
         <v>131</v>
@@ -4848,45 +4864,45 @@
         <v>146</v>
       </c>
       <c r="V51" s="1">
-        <v>46267.79439748843</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="X51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB51">
         <v>0</v>
       </c>
       <c r="AC51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI51" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:35">
       <c r="A52">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52">
         <v>11752</v>
@@ -4901,10 +4917,7 @@
         <v>83</v>
       </c>
       <c r="N52" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O52" t="s">
-        <v>115</v>
+        <v>46267</v>
       </c>
       <c r="P52">
         <v>8</v>
@@ -4913,25 +4926,25 @@
         <v>2026</v>
       </c>
       <c r="R52">
-        <v>18220251</v>
+        <v>18260411</v>
       </c>
       <c r="S52" t="s">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="T52" t="s">
+        <v>131</v>
       </c>
       <c r="U52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V52" s="1">
-        <v>46267.79440011574</v>
+        <v>46267.7205502662</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="AB52">
         <v>0</v>
@@ -4940,18 +4953,18 @@
         <v>131</v>
       </c>
       <c r="AH52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:35">
       <c r="A53">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
@@ -4960,10 +4973,10 @@
         <v>51</v>
       </c>
       <c r="E53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53">
         <v>11752</v>
@@ -4987,10 +5000,10 @@
         <v>2026</v>
       </c>
       <c r="R53">
-        <v>18214951</v>
+        <v>18173143</v>
       </c>
       <c r="S53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T53" t="s">
         <v>131</v>
@@ -4999,60 +5012,63 @@
         <v>146</v>
       </c>
       <c r="V53" s="1">
-        <v>46267.79439818287</v>
+        <v>46267.79439748843</v>
       </c>
       <c r="W53">
         <v>0</v>
       </c>
       <c r="X53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB53">
         <v>0</v>
       </c>
       <c r="AC53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH53" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI53" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:35">
       <c r="A54">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
         <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54">
-        <v>11748</v>
+        <v>11752</v>
       </c>
       <c r="H54">
-        <v>11747</v>
+        <v>11751</v>
       </c>
       <c r="I54" t="s">
         <v>62</v>
       </c>
       <c r="J54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N54" s="1">
-        <v>46267</v>
+        <v>46268</v>
+      </c>
+      <c r="O54" t="s">
+        <v>115</v>
       </c>
       <c r="P54">
         <v>8</v>
@@ -5061,25 +5077,25 @@
         <v>2026</v>
       </c>
       <c r="R54">
-        <v>18260401</v>
+        <v>18220251</v>
       </c>
       <c r="S54" t="s">
-        <v>130</v>
-      </c>
-      <c r="T54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V54" s="1">
-        <v>46267.7202693287</v>
+        <v>46267.79440011574</v>
       </c>
       <c r="W54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>175</v>
       </c>
       <c r="AB54">
         <v>0</v>
@@ -5088,18 +5104,18 @@
         <v>131</v>
       </c>
       <c r="AH54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:35">
       <c r="A55">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
         <v>50</v>
@@ -5108,22 +5124,22 @@
         <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G55">
-        <v>11748</v>
+        <v>11752</v>
       </c>
       <c r="H55">
-        <v>11747</v>
+        <v>11751</v>
       </c>
       <c r="I55" t="s">
         <v>62</v>
       </c>
       <c r="J55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N55" s="1">
         <v>46268</v>
@@ -5135,10 +5151,10 @@
         <v>2026</v>
       </c>
       <c r="R55">
-        <v>18173127</v>
+        <v>18214951</v>
       </c>
       <c r="S55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T55" t="s">
         <v>131</v>
@@ -5147,42 +5163,42 @@
         <v>146</v>
       </c>
       <c r="V55" s="1">
-        <v>46267.79409846065</v>
+        <v>46267.79439818287</v>
       </c>
       <c r="W55">
         <v>0</v>
       </c>
       <c r="X55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB55">
         <v>0</v>
       </c>
       <c r="AC55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI55" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:35">
       <c r="A56">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C56" t="s">
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F56" t="s">
         <v>56</v>
@@ -5200,7 +5216,7 @@
         <v>84</v>
       </c>
       <c r="N56" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P56">
         <v>8</v>
@@ -5209,25 +5225,25 @@
         <v>2026</v>
       </c>
       <c r="R56">
-        <v>18170386</v>
+        <v>18260401</v>
       </c>
       <c r="S56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T56" t="s">
         <v>131</v>
       </c>
       <c r="U56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V56" s="1">
-        <v>46267.79409725694</v>
+        <v>46267.7202693287</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB56">
         <v>0</v>
@@ -5236,30 +5252,30 @@
         <v>131</v>
       </c>
       <c r="AH56" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:35">
       <c r="A57">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
         <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E57" t="s">
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57">
         <v>11748</v>
@@ -5283,22 +5299,25 @@
         <v>2026</v>
       </c>
       <c r="R57">
-        <v>18220239</v>
+        <v>18173127</v>
       </c>
       <c r="S57" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="T57" t="s">
+        <v>131</v>
       </c>
       <c r="U57" t="s">
         <v>146</v>
       </c>
       <c r="V57" s="1">
-        <v>46267.79410239583</v>
+        <v>46267.79409846065</v>
       </c>
       <c r="W57">
         <v>0</v>
       </c>
       <c r="X57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB57">
         <v>0</v>
@@ -5307,30 +5326,30 @@
         <v>131</v>
       </c>
       <c r="AH57" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:35">
       <c r="A58">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
         <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G58">
         <v>11748</v>
@@ -5354,10 +5373,10 @@
         <v>2026</v>
       </c>
       <c r="R58">
-        <v>18214939</v>
+        <v>18170386</v>
       </c>
       <c r="S58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T58" t="s">
         <v>131</v>
@@ -5366,60 +5385,60 @@
         <v>146</v>
       </c>
       <c r="V58" s="1">
-        <v>46267.79409934028</v>
+        <v>46267.79409725694</v>
       </c>
       <c r="W58">
         <v>0</v>
       </c>
       <c r="X58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB58">
         <v>0</v>
       </c>
       <c r="AC58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:35">
       <c r="A59">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G59">
-        <v>11750</v>
+        <v>11748</v>
       </c>
       <c r="H59">
-        <v>11749</v>
+        <v>11747</v>
       </c>
       <c r="I59" t="s">
         <v>62</v>
       </c>
       <c r="J59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N59" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P59">
         <v>8</v>
@@ -5428,25 +5447,22 @@
         <v>2026</v>
       </c>
       <c r="R59">
-        <v>18260406</v>
+        <v>18220239</v>
       </c>
       <c r="S59" t="s">
-        <v>130</v>
-      </c>
-      <c r="T59" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V59" s="1">
-        <v>46267.72033356482</v>
+        <v>46267.79410239583</v>
       </c>
       <c r="W59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB59">
         <v>0</v>
@@ -5455,18 +5471,18 @@
         <v>131</v>
       </c>
       <c r="AH59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:35">
       <c r="A60">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
         <v>50</v>
@@ -5475,22 +5491,22 @@
         <v>51</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G60">
-        <v>11750</v>
+        <v>11748</v>
       </c>
       <c r="H60">
-        <v>11749</v>
+        <v>11747</v>
       </c>
       <c r="I60" t="s">
         <v>62</v>
       </c>
       <c r="J60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N60" s="1">
         <v>46268</v>
@@ -5502,10 +5518,10 @@
         <v>2026</v>
       </c>
       <c r="R60">
-        <v>18173135</v>
+        <v>18214939</v>
       </c>
       <c r="S60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T60" t="s">
         <v>131</v>
@@ -5514,42 +5530,42 @@
         <v>146</v>
       </c>
       <c r="V60" s="1">
-        <v>46267.79418105324</v>
+        <v>46267.79409934028</v>
       </c>
       <c r="W60">
         <v>0</v>
       </c>
       <c r="X60" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB60">
         <v>0</v>
       </c>
       <c r="AC60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:35">
       <c r="A61">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
         <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F61" t="s">
         <v>56</v>
@@ -5567,7 +5583,7 @@
         <v>85</v>
       </c>
       <c r="N61" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P61">
         <v>8</v>
@@ -5576,25 +5592,25 @@
         <v>2026</v>
       </c>
       <c r="R61">
-        <v>18170394</v>
+        <v>18260406</v>
       </c>
       <c r="S61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T61" t="s">
         <v>131</v>
       </c>
       <c r="U61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V61" s="1">
-        <v>46267.79418005787</v>
+        <v>46267.72033356482</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB61">
         <v>0</v>
@@ -5603,30 +5619,30 @@
         <v>131</v>
       </c>
       <c r="AH61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:35">
       <c r="A62">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
         <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E62" t="s">
         <v>55</v>
       </c>
       <c r="F62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62">
         <v>11750</v>
@@ -5650,22 +5666,25 @@
         <v>2026</v>
       </c>
       <c r="R62">
-        <v>18220245</v>
+        <v>18173135</v>
       </c>
       <c r="S62" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="T62" t="s">
+        <v>131</v>
       </c>
       <c r="U62" t="s">
         <v>146</v>
       </c>
       <c r="V62" s="1">
-        <v>46267.79418379629</v>
+        <v>46267.79418105324</v>
       </c>
       <c r="W62">
         <v>0</v>
       </c>
       <c r="X62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB62">
         <v>0</v>
@@ -5674,30 +5693,30 @@
         <v>131</v>
       </c>
       <c r="AH62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:35">
       <c r="A63">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G63">
         <v>11750</v>
@@ -5721,10 +5740,10 @@
         <v>2026</v>
       </c>
       <c r="R63">
-        <v>18214945</v>
+        <v>18170394</v>
       </c>
       <c r="S63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T63" t="s">
         <v>131</v>
@@ -5733,57 +5752,57 @@
         <v>146</v>
       </c>
       <c r="V63" s="1">
-        <v>46267.79418283565</v>
+        <v>46267.79418005787</v>
       </c>
       <c r="W63">
         <v>0</v>
       </c>
       <c r="X63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB63">
         <v>0</v>
       </c>
       <c r="AC63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:35">
       <c r="A64">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G64">
-        <v>6889</v>
+        <v>11750</v>
       </c>
       <c r="H64">
-        <v>1862</v>
+        <v>11749</v>
       </c>
       <c r="I64" t="s">
         <v>62</v>
       </c>
       <c r="J64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N64" s="1">
         <v>46268</v>
@@ -5795,25 +5814,22 @@
         <v>2026</v>
       </c>
       <c r="R64">
-        <v>18260396</v>
+        <v>18220245</v>
       </c>
       <c r="S64" t="s">
-        <v>130</v>
-      </c>
-      <c r="T64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U64" t="s">
         <v>146</v>
       </c>
       <c r="V64" s="1">
-        <v>46267.71937662037</v>
+        <v>46267.79418379629</v>
       </c>
       <c r="W64">
         <v>0</v>
       </c>
       <c r="X64" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB64">
         <v>0</v>
@@ -5822,18 +5838,18 @@
         <v>131</v>
       </c>
       <c r="AH64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:35">
       <c r="A65">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
@@ -5842,22 +5858,22 @@
         <v>51</v>
       </c>
       <c r="E65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G65">
-        <v>6889</v>
+        <v>11750</v>
       </c>
       <c r="H65">
-        <v>1862</v>
+        <v>11749</v>
       </c>
       <c r="I65" t="s">
         <v>62</v>
       </c>
       <c r="J65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N65" s="1">
         <v>46268</v>
@@ -5869,10 +5885,10 @@
         <v>2026</v>
       </c>
       <c r="R65">
-        <v>18048463</v>
+        <v>18214945</v>
       </c>
       <c r="S65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T65" t="s">
         <v>131</v>
@@ -5881,33 +5897,33 @@
         <v>146</v>
       </c>
       <c r="V65" s="1">
-        <v>46267.79259834491</v>
+        <v>46267.79418283565</v>
       </c>
       <c r="W65">
         <v>0</v>
       </c>
       <c r="X65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB65">
         <v>0</v>
       </c>
       <c r="AC65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" spans="1:35">
       <c r="A66">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
         <v>50</v>
@@ -5919,7 +5935,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G66">
         <v>6889</v>
@@ -5943,10 +5959,10 @@
         <v>2026</v>
       </c>
       <c r="R66">
-        <v>18214913</v>
+        <v>18260396</v>
       </c>
       <c r="S66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T66" t="s">
         <v>131</v>
@@ -5955,45 +5971,45 @@
         <v>146</v>
       </c>
       <c r="V66" s="1">
-        <v>46267.79260170139</v>
+        <v>46267.71937662037</v>
       </c>
       <c r="W66">
         <v>0</v>
       </c>
       <c r="X66" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="1:35">
       <c r="A67">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G67">
         <v>6889</v>
@@ -6010,9 +6026,6 @@
       <c r="N67" s="1">
         <v>46268</v>
       </c>
-      <c r="O67" t="s">
-        <v>114</v>
-      </c>
       <c r="P67">
         <v>8</v>
       </c>
@@ -6020,28 +6033,25 @@
         <v>2026</v>
       </c>
       <c r="R67">
-        <v>18187275</v>
+        <v>18048463</v>
       </c>
       <c r="S67" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="T67" t="s">
         <v>131</v>
       </c>
       <c r="U67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V67" s="1">
-        <v>46268.37621265047</v>
+        <v>46267.79259834491</v>
       </c>
       <c r="W67">
         <v>0</v>
       </c>
       <c r="X67" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="AB67">
         <v>0</v>
@@ -6050,42 +6060,42 @@
         <v>131</v>
       </c>
       <c r="AH67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:35">
       <c r="A68">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68" t="s">
         <v>57</v>
       </c>
       <c r="G68">
-        <v>11758</v>
+        <v>6889</v>
       </c>
       <c r="H68">
-        <v>11757</v>
+        <v>1862</v>
       </c>
       <c r="I68" t="s">
         <v>62</v>
       </c>
       <c r="J68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N68" s="1">
         <v>46268</v>
@@ -6097,69 +6107,75 @@
         <v>2026</v>
       </c>
       <c r="R68">
-        <v>18220263</v>
+        <v>18214913</v>
       </c>
       <c r="S68" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="T68" t="s">
+        <v>131</v>
       </c>
       <c r="U68" t="s">
         <v>146</v>
       </c>
       <c r="V68" s="1">
-        <v>46267.79440636574</v>
+        <v>46267.79260170139</v>
       </c>
       <c r="W68">
         <v>0</v>
       </c>
       <c r="X68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB68">
         <v>0</v>
       </c>
       <c r="AC68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="1:35">
       <c r="A69">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C69" t="s">
         <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E69" t="s">
         <v>54</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G69">
-        <v>11760</v>
+        <v>6889</v>
       </c>
       <c r="H69">
-        <v>11759</v>
+        <v>1862</v>
       </c>
       <c r="I69" t="s">
         <v>62</v>
       </c>
       <c r="J69" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N69" s="1">
-        <v>46267</v>
+        <v>46268</v>
+      </c>
+      <c r="O69" t="s">
+        <v>114</v>
       </c>
       <c r="P69">
         <v>8</v>
@@ -6168,10 +6184,10 @@
         <v>2026</v>
       </c>
       <c r="R69">
-        <v>18260421</v>
+        <v>18187275</v>
       </c>
       <c r="S69" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="T69" t="s">
         <v>131</v>
@@ -6180,13 +6196,16 @@
         <v>147</v>
       </c>
       <c r="V69" s="1">
-        <v>46267.72037954861</v>
+        <v>46268.37621265047</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>176</v>
       </c>
       <c r="AB69">
         <v>0</v>
@@ -6195,42 +6214,42 @@
         <v>131</v>
       </c>
       <c r="AH69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI69" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:35">
       <c r="A70">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C70" t="s">
         <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E70" t="s">
         <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G70">
-        <v>11760</v>
+        <v>11758</v>
       </c>
       <c r="H70">
-        <v>11759</v>
+        <v>11757</v>
       </c>
       <c r="I70" t="s">
         <v>62</v>
       </c>
       <c r="J70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N70" s="1">
         <v>46268</v>
@@ -6242,25 +6261,22 @@
         <v>2026</v>
       </c>
       <c r="R70">
-        <v>18173151</v>
+        <v>18220263</v>
       </c>
       <c r="S70" t="s">
-        <v>131</v>
-      </c>
-      <c r="T70" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U70" t="s">
         <v>146</v>
       </c>
       <c r="V70" s="1">
-        <v>46267.79424664352</v>
+        <v>46267.79440636574</v>
       </c>
       <c r="W70">
         <v>0</v>
       </c>
       <c r="X70" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AB70">
         <v>0</v>
@@ -6269,27 +6285,27 @@
         <v>131</v>
       </c>
       <c r="AH70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:35">
       <c r="A71">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
         <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F71" t="s">
         <v>56</v>
@@ -6307,7 +6323,7 @@
         <v>88</v>
       </c>
       <c r="N71" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P71">
         <v>8</v>
@@ -6316,25 +6332,25 @@
         <v>2026</v>
       </c>
       <c r="R71">
-        <v>18170402</v>
+        <v>18260421</v>
       </c>
       <c r="S71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T71" t="s">
         <v>131</v>
       </c>
       <c r="U71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V71" s="1">
-        <v>46267.79424586806</v>
+        <v>46267.72037954861</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB71">
         <v>0</v>
@@ -6343,30 +6359,30 @@
         <v>131</v>
       </c>
       <c r="AH71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:35">
       <c r="A72">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C72" t="s">
         <v>50</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E72" t="s">
         <v>55</v>
       </c>
       <c r="F72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G72">
         <v>11760</v>
@@ -6390,22 +6406,25 @@
         <v>2026</v>
       </c>
       <c r="R72">
-        <v>18220269</v>
+        <v>18173151</v>
       </c>
       <c r="S72" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="T72" t="s">
+        <v>131</v>
       </c>
       <c r="U72" t="s">
         <v>146</v>
       </c>
       <c r="V72" s="1">
-        <v>46267.79424864583</v>
+        <v>46267.79424664352</v>
       </c>
       <c r="W72">
         <v>0</v>
       </c>
       <c r="X72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB72">
         <v>0</v>
@@ -6414,30 +6433,30 @@
         <v>131</v>
       </c>
       <c r="AH72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:35">
       <c r="A73">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C73" t="s">
         <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G73">
         <v>11760</v>
@@ -6461,10 +6480,10 @@
         <v>2026</v>
       </c>
       <c r="R73">
-        <v>18214963</v>
+        <v>18170402</v>
       </c>
       <c r="S73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T73" t="s">
         <v>131</v>
@@ -6473,42 +6492,42 @@
         <v>146</v>
       </c>
       <c r="V73" s="1">
-        <v>46267.79424725694</v>
+        <v>46267.79424586806</v>
       </c>
       <c r="W73">
         <v>0</v>
       </c>
       <c r="X73" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB73">
         <v>0</v>
       </c>
       <c r="AC73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:35">
       <c r="A74">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
         <v>50</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F74" t="s">
         <v>57</v>
@@ -6535,25 +6554,22 @@
         <v>2026</v>
       </c>
       <c r="R74">
-        <v>18260057</v>
+        <v>18220269</v>
       </c>
       <c r="S74" t="s">
-        <v>134</v>
-      </c>
-      <c r="T74" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U74" t="s">
         <v>146</v>
       </c>
       <c r="V74" s="1">
-        <v>46267.79425081018</v>
+        <v>46267.79424864583</v>
       </c>
       <c r="W74">
         <v>0</v>
       </c>
       <c r="X74" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AB74">
         <v>0</v>
@@ -6562,18 +6578,18 @@
         <v>131</v>
       </c>
       <c r="AH74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:35">
       <c r="A75">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C75" t="s">
         <v>50</v>
@@ -6585,22 +6601,22 @@
         <v>54</v>
       </c>
       <c r="F75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G75">
-        <v>11756</v>
+        <v>11760</v>
       </c>
       <c r="H75">
-        <v>11755</v>
+        <v>11759</v>
       </c>
       <c r="I75" t="s">
         <v>62</v>
       </c>
       <c r="J75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N75" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P75">
         <v>8</v>
@@ -6609,69 +6625,69 @@
         <v>2026</v>
       </c>
       <c r="R75">
-        <v>18260416</v>
+        <v>18214963</v>
       </c>
       <c r="S75" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T75" t="s">
         <v>131</v>
       </c>
       <c r="U75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V75" s="1">
-        <v>46267.71942916667</v>
+        <v>46267.79424725694</v>
       </c>
       <c r="W75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X75" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AB75">
         <v>0</v>
       </c>
       <c r="AC75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:35">
       <c r="A76">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F76" t="s">
         <v>57</v>
       </c>
       <c r="G76">
-        <v>11756</v>
+        <v>11760</v>
       </c>
       <c r="H76">
-        <v>11755</v>
+        <v>11759</v>
       </c>
       <c r="I76" t="s">
         <v>62</v>
       </c>
       <c r="J76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N76" s="1">
         <v>46268</v>
@@ -6683,22 +6699,25 @@
         <v>2026</v>
       </c>
       <c r="R76">
-        <v>18220257</v>
+        <v>18260057</v>
       </c>
       <c r="S76" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="T76" t="s">
+        <v>131</v>
       </c>
       <c r="U76" t="s">
         <v>146</v>
       </c>
       <c r="V76" s="1">
-        <v>46267.79268530093</v>
+        <v>46267.79425081018</v>
       </c>
       <c r="W76">
         <v>0</v>
       </c>
       <c r="X76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB76">
         <v>0</v>
@@ -6707,18 +6726,18 @@
         <v>131</v>
       </c>
       <c r="AH76" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:35">
       <c r="A77">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
         <v>50</v>
@@ -6730,7 +6749,7 @@
         <v>54</v>
       </c>
       <c r="F77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G77">
         <v>11756</v>
@@ -6745,7 +6764,7 @@
         <v>89</v>
       </c>
       <c r="N77" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P77">
         <v>8</v>
@@ -6754,37 +6773,37 @@
         <v>2026</v>
       </c>
       <c r="R77">
-        <v>18214957</v>
+        <v>18260416</v>
       </c>
       <c r="S77" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T77" t="s">
         <v>131</v>
       </c>
       <c r="U77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V77" s="1">
-        <v>46267.79268769676</v>
+        <v>46267.71942916667</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB77">
         <v>0</v>
       </c>
       <c r="AC77" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -6807,16 +6826,16 @@
         <v>57</v>
       </c>
       <c r="G78">
-        <v>6221</v>
+        <v>11756</v>
       </c>
       <c r="H78">
-        <v>6220</v>
+        <v>11755</v>
       </c>
       <c r="I78" t="s">
         <v>62</v>
       </c>
       <c r="J78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N78" s="1">
         <v>46268</v>
@@ -6828,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="R78">
-        <v>18220209</v>
+        <v>18220257</v>
       </c>
       <c r="S78" t="s">
         <v>133</v>
@@ -6837,7 +6856,7 @@
         <v>146</v>
       </c>
       <c r="V78" s="1">
-        <v>46267.79249748842</v>
+        <v>46267.79268530093</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -6849,13 +6868,13 @@
         <v>0</v>
       </c>
       <c r="AC78" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH78" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -6878,16 +6897,16 @@
         <v>57</v>
       </c>
       <c r="G79">
-        <v>6221</v>
+        <v>11756</v>
       </c>
       <c r="H79">
-        <v>6220</v>
+        <v>11755</v>
       </c>
       <c r="I79" t="s">
         <v>62</v>
       </c>
       <c r="J79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N79" s="1">
         <v>46268</v>
@@ -6899,7 +6918,7 @@
         <v>2026</v>
       </c>
       <c r="R79">
-        <v>18214889</v>
+        <v>18214957</v>
       </c>
       <c r="S79" t="s">
         <v>132</v>
@@ -6911,7 +6930,7 @@
         <v>146</v>
       </c>
       <c r="V79" s="1">
-        <v>46267.79249788194</v>
+        <v>46267.79268769676</v>
       </c>
       <c r="W79">
         <v>0</v>
@@ -6926,45 +6945,45 @@
         <v>132</v>
       </c>
       <c r="AH79" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:35">
       <c r="A80">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
         <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G80">
-        <v>6223</v>
+        <v>6221</v>
       </c>
       <c r="H80">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="I80" t="s">
         <v>62</v>
       </c>
       <c r="J80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N80" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P80">
         <v>8</v>
@@ -6973,69 +6992,66 @@
         <v>2026</v>
       </c>
       <c r="R80">
-        <v>18260391</v>
+        <v>18220209</v>
       </c>
       <c r="S80" t="s">
-        <v>130</v>
-      </c>
-      <c r="T80" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U80" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V80" s="1">
-        <v>46267.71927280092</v>
+        <v>46267.79249748842</v>
       </c>
       <c r="W80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X80" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB80">
         <v>0</v>
       </c>
       <c r="AC80" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AH80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:35">
       <c r="A81">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
         <v>50</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F81" t="s">
         <v>57</v>
       </c>
       <c r="G81">
-        <v>6223</v>
+        <v>6221</v>
       </c>
       <c r="H81">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="I81" t="s">
         <v>62</v>
       </c>
       <c r="J81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N81" s="1">
         <v>46268</v>
@@ -7047,42 +7063,45 @@
         <v>2026</v>
       </c>
       <c r="R81">
-        <v>18220215</v>
+        <v>18214889</v>
       </c>
       <c r="S81" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="T81" t="s">
+        <v>131</v>
       </c>
       <c r="U81" t="s">
         <v>146</v>
       </c>
       <c r="V81" s="1">
-        <v>46267.79251079861</v>
+        <v>46267.79249788194</v>
       </c>
       <c r="W81">
         <v>0</v>
       </c>
       <c r="X81" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB81">
         <v>0</v>
       </c>
       <c r="AC81" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:35">
       <c r="A82">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
         <v>50</v>
@@ -7094,7 +7113,7 @@
         <v>54</v>
       </c>
       <c r="F82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G82">
         <v>6223</v>
@@ -7109,7 +7128,7 @@
         <v>91</v>
       </c>
       <c r="N82" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P82">
         <v>8</v>
@@ -7118,72 +7137,72 @@
         <v>2026</v>
       </c>
       <c r="R82">
-        <v>18214895</v>
+        <v>18260391</v>
       </c>
       <c r="S82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T82" t="s">
         <v>131</v>
       </c>
       <c r="U82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V82" s="1">
-        <v>46267.79251038194</v>
+        <v>46267.71927280092</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AB82">
         <v>0</v>
       </c>
       <c r="AC82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AH82" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:35">
       <c r="A83">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B83" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C83" t="s">
         <v>50</v>
       </c>
       <c r="D83" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G83">
-        <v>11766</v>
+        <v>6223</v>
       </c>
       <c r="H83">
-        <v>11765</v>
+        <v>6222</v>
       </c>
       <c r="I83" t="s">
         <v>62</v>
       </c>
       <c r="J83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N83" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P83">
         <v>8</v>
@@ -7192,45 +7211,42 @@
         <v>2026</v>
       </c>
       <c r="R83">
-        <v>18260426</v>
+        <v>18220215</v>
       </c>
       <c r="S83" t="s">
-        <v>130</v>
-      </c>
-      <c r="T83" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U83" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V83" s="1">
-        <v>46267.72044811342</v>
+        <v>46267.79251079861</v>
       </c>
       <c r="W83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X83" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB83">
         <v>0</v>
       </c>
       <c r="AC83" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AH83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:35">
       <c r="A84">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
         <v>50</v>
@@ -7239,22 +7255,22 @@
         <v>51</v>
       </c>
       <c r="E84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84">
-        <v>11766</v>
+        <v>6223</v>
       </c>
       <c r="H84">
-        <v>11765</v>
+        <v>6222</v>
       </c>
       <c r="I84" t="s">
         <v>62</v>
       </c>
       <c r="J84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N84" s="1">
         <v>46268</v>
@@ -7266,10 +7282,10 @@
         <v>2026</v>
       </c>
       <c r="R84">
-        <v>18173159</v>
+        <v>18214895</v>
       </c>
       <c r="S84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T84" t="s">
         <v>131</v>
@@ -7278,42 +7294,42 @@
         <v>146</v>
       </c>
       <c r="V84" s="1">
-        <v>46267.79429737268</v>
+        <v>46267.79251038194</v>
       </c>
       <c r="W84">
         <v>0</v>
       </c>
       <c r="X84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB84">
         <v>0</v>
       </c>
       <c r="AC84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:35">
       <c r="A85">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C85" t="s">
         <v>50</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F85" t="s">
         <v>56</v>
@@ -7331,7 +7347,7 @@
         <v>92</v>
       </c>
       <c r="N85" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P85">
         <v>8</v>
@@ -7340,25 +7356,25 @@
         <v>2026</v>
       </c>
       <c r="R85">
-        <v>18170410</v>
+        <v>18260426</v>
       </c>
       <c r="S85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T85" t="s">
         <v>131</v>
       </c>
       <c r="U85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V85" s="1">
-        <v>46267.79429603009</v>
+        <v>46267.72044811342</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB85">
         <v>0</v>
@@ -7367,30 +7383,30 @@
         <v>131</v>
       </c>
       <c r="AH85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:35">
       <c r="A86">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C86" t="s">
         <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E86" t="s">
         <v>55</v>
       </c>
       <c r="F86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G86">
         <v>11766</v>
@@ -7414,22 +7430,25 @@
         <v>2026</v>
       </c>
       <c r="R86">
-        <v>18220275</v>
+        <v>18173159</v>
       </c>
       <c r="S86" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="T86" t="s">
+        <v>131</v>
       </c>
       <c r="U86" t="s">
         <v>146</v>
       </c>
       <c r="V86" s="1">
-        <v>46267.79429876158</v>
+        <v>46267.79429737268</v>
       </c>
       <c r="W86">
         <v>0</v>
       </c>
       <c r="X86" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB86">
         <v>0</v>
@@ -7438,30 +7457,30 @@
         <v>131</v>
       </c>
       <c r="AH86" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:35">
       <c r="A87">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C87" t="s">
         <v>50</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E87" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F87" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G87">
         <v>11766</v>
@@ -7485,10 +7504,10 @@
         <v>2026</v>
       </c>
       <c r="R87">
-        <v>18214969</v>
+        <v>18170410</v>
       </c>
       <c r="S87" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T87" t="s">
         <v>131</v>
@@ -7497,60 +7516,60 @@
         <v>146</v>
       </c>
       <c r="V87" s="1">
-        <v>46267.79429826389</v>
+        <v>46267.79429603009</v>
       </c>
       <c r="W87">
         <v>0</v>
       </c>
       <c r="X87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB87">
         <v>0</v>
       </c>
       <c r="AC87" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH87" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:35">
       <c r="A88">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C88" t="s">
         <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E88" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G88">
-        <v>11768</v>
+        <v>11766</v>
       </c>
       <c r="H88">
-        <v>11767</v>
+        <v>11765</v>
       </c>
       <c r="I88" t="s">
         <v>62</v>
       </c>
       <c r="J88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N88" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P88">
         <v>8</v>
@@ -7559,25 +7578,22 @@
         <v>2026</v>
       </c>
       <c r="R88">
-        <v>18260431</v>
+        <v>18220275</v>
       </c>
       <c r="S88" t="s">
-        <v>130</v>
-      </c>
-      <c r="T88" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U88" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V88" s="1">
-        <v>46267.72050385417</v>
+        <v>46267.79429876158</v>
       </c>
       <c r="W88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X88" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AB88">
         <v>0</v>
@@ -7586,18 +7602,18 @@
         <v>131</v>
       </c>
       <c r="AH88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="1:35">
       <c r="A89">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
         <v>50</v>
@@ -7606,22 +7622,22 @@
         <v>51</v>
       </c>
       <c r="E89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G89">
-        <v>11768</v>
+        <v>11766</v>
       </c>
       <c r="H89">
-        <v>11767</v>
+        <v>11765</v>
       </c>
       <c r="I89" t="s">
         <v>62</v>
       </c>
       <c r="J89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N89" s="1">
         <v>46268</v>
@@ -7633,10 +7649,10 @@
         <v>2026</v>
       </c>
       <c r="R89">
-        <v>18173167</v>
+        <v>18214969</v>
       </c>
       <c r="S89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T89" t="s">
         <v>131</v>
@@ -7645,42 +7661,42 @@
         <v>146</v>
       </c>
       <c r="V89" s="1">
-        <v>46267.79434996528</v>
+        <v>46267.79429826389</v>
       </c>
       <c r="W89">
         <v>0</v>
       </c>
       <c r="X89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB89">
         <v>0</v>
       </c>
       <c r="AC89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AH89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="1:35">
       <c r="A90">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
         <v>50</v>
       </c>
       <c r="D90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F90" t="s">
         <v>56</v>
@@ -7698,7 +7714,7 @@
         <v>93</v>
       </c>
       <c r="N90" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P90">
         <v>8</v>
@@ -7707,25 +7723,25 @@
         <v>2026</v>
       </c>
       <c r="R90">
-        <v>18170418</v>
+        <v>18260431</v>
       </c>
       <c r="S90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T90" t="s">
         <v>131</v>
       </c>
       <c r="U90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V90" s="1">
-        <v>46267.79434864583</v>
+        <v>46267.72050385417</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB90">
         <v>0</v>
@@ -7734,30 +7750,30 @@
         <v>131</v>
       </c>
       <c r="AH90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:35">
       <c r="A91">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B91" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C91" t="s">
         <v>50</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
         <v>55</v>
       </c>
       <c r="F91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G91">
         <v>11768</v>
@@ -7781,22 +7797,25 @@
         <v>2026</v>
       </c>
       <c r="R91">
-        <v>18220281</v>
+        <v>18173167</v>
       </c>
       <c r="S91" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="T91" t="s">
+        <v>131</v>
       </c>
       <c r="U91" t="s">
         <v>146</v>
       </c>
       <c r="V91" s="1">
-        <v>46267.79435208334</v>
+        <v>46267.79434996528</v>
       </c>
       <c r="W91">
         <v>0</v>
       </c>
       <c r="X91" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AB91">
         <v>0</v>
@@ -7805,30 +7824,30 @@
         <v>131</v>
       </c>
       <c r="AH91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:35">
       <c r="A92">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
         <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G92">
         <v>11768</v>
@@ -7852,10 +7871,10 @@
         <v>2026</v>
       </c>
       <c r="R92">
-        <v>18214975</v>
+        <v>18170418</v>
       </c>
       <c r="S92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T92" t="s">
         <v>131</v>
@@ -7864,60 +7883,60 @@
         <v>146</v>
       </c>
       <c r="V92" s="1">
-        <v>46267.79435100695</v>
+        <v>46267.79434864583</v>
       </c>
       <c r="W92">
         <v>0</v>
       </c>
       <c r="X92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB92">
         <v>0</v>
       </c>
       <c r="AC92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AH92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:35">
       <c r="A93">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B93" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C93" t="s">
         <v>50</v>
       </c>
       <c r="D93" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G93">
-        <v>6883</v>
+        <v>11768</v>
       </c>
       <c r="H93">
-        <v>1788</v>
+        <v>11767</v>
       </c>
       <c r="I93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J93" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="N93" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P93">
         <v>8</v>
@@ -7926,45 +7945,42 @@
         <v>2026</v>
       </c>
       <c r="R93">
-        <v>17399250</v>
+        <v>18220281</v>
       </c>
       <c r="S93" t="s">
-        <v>135</v>
-      </c>
-      <c r="T93" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="U93" t="s">
         <v>146</v>
       </c>
       <c r="V93" s="1">
-        <v>46266.37636392361</v>
+        <v>46267.79435208334</v>
       </c>
       <c r="W93">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="X93" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="AB93">
         <v>0</v>
       </c>
       <c r="AC93" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AH93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:35">
       <c r="A94">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B94" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
         <v>50</v>
@@ -7976,19 +7992,19 @@
         <v>54</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G94">
-        <v>1836</v>
+        <v>11768</v>
       </c>
       <c r="H94">
-        <v>1788</v>
+        <v>11767</v>
       </c>
       <c r="I94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N94" s="1">
         <v>46268</v>
@@ -8000,45 +8016,45 @@
         <v>2026</v>
       </c>
       <c r="R94">
-        <v>17398975</v>
+        <v>18214975</v>
       </c>
       <c r="S94" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="T94" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="U94" t="s">
         <v>146</v>
       </c>
       <c r="V94" s="1">
-        <v>46266.37598834491</v>
+        <v>46267.79435100695</v>
       </c>
       <c r="W94">
         <v>0</v>
       </c>
       <c r="X94" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AB94">
         <v>0</v>
       </c>
       <c r="AC94" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AH94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:35">
       <c r="A95">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
         <v>50</v>
@@ -8053,7 +8069,7 @@
         <v>56</v>
       </c>
       <c r="G95">
-        <v>1836</v>
+        <v>6883</v>
       </c>
       <c r="H95">
         <v>1788</v>
@@ -8062,13 +8078,10 @@
         <v>63</v>
       </c>
       <c r="J95" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N95" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O95" t="s">
-        <v>114</v>
+        <v>46275</v>
       </c>
       <c r="P95">
         <v>8</v>
@@ -8077,7 +8090,7 @@
         <v>2026</v>
       </c>
       <c r="R95">
-        <v>18155318</v>
+        <v>17399250</v>
       </c>
       <c r="S95" t="s">
         <v>135</v>
@@ -8086,19 +8099,16 @@
         <v>144</v>
       </c>
       <c r="U95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V95" s="1">
-        <v>46268.45899988426</v>
+        <v>46266.37636392361</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="X95" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y95" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="AB95">
         <v>0</v>
@@ -8107,18 +8117,18 @@
         <v>135</v>
       </c>
       <c r="AH95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:35">
       <c r="A96">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C96" t="s">
         <v>50</v>
@@ -8154,7 +8164,7 @@
         <v>2026</v>
       </c>
       <c r="R96">
-        <v>18085220</v>
+        <v>17398975</v>
       </c>
       <c r="S96" t="s">
         <v>135</v>
@@ -8166,13 +8176,13 @@
         <v>146</v>
       </c>
       <c r="V96" s="1">
-        <v>46266.45957881944</v>
+        <v>46266.37598834491</v>
       </c>
       <c r="W96">
         <v>0</v>
       </c>
       <c r="X96" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB96">
         <v>0</v>
@@ -8181,18 +8191,18 @@
         <v>135</v>
       </c>
       <c r="AH96" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:35">
       <c r="A97">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
@@ -8207,7 +8217,7 @@
         <v>56</v>
       </c>
       <c r="G97">
-        <v>6802</v>
+        <v>1836</v>
       </c>
       <c r="H97">
         <v>1788</v>
@@ -8216,10 +8226,13 @@
         <v>63</v>
       </c>
       <c r="J97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N97" s="1">
-        <v>46269</v>
+        <v>46268</v>
+      </c>
+      <c r="O97" t="s">
+        <v>114</v>
       </c>
       <c r="P97">
         <v>8</v>
@@ -8228,7 +8241,7 @@
         <v>2026</v>
       </c>
       <c r="R97">
-        <v>17399220</v>
+        <v>18155318</v>
       </c>
       <c r="S97" t="s">
         <v>135</v>
@@ -8237,16 +8250,19 @@
         <v>144</v>
       </c>
       <c r="U97" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V97" s="1">
-        <v>46266.37645462963</v>
+        <v>46268.45899988426</v>
       </c>
       <c r="W97">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X97" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>177</v>
       </c>
       <c r="AB97">
         <v>0</v>
@@ -8255,18 +8271,18 @@
         <v>135</v>
       </c>
       <c r="AH97" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:35">
       <c r="A98">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C98" t="s">
         <v>50</v>
@@ -8281,19 +8297,19 @@
         <v>56</v>
       </c>
       <c r="G98">
-        <v>6801</v>
+        <v>1836</v>
       </c>
       <c r="H98">
-        <v>1796</v>
+        <v>1788</v>
       </c>
       <c r="I98" t="s">
         <v>63</v>
       </c>
       <c r="J98" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N98" s="1">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="P98">
         <v>8</v>
@@ -8302,7 +8318,7 @@
         <v>2026</v>
       </c>
       <c r="R98">
-        <v>17399210</v>
+        <v>18085220</v>
       </c>
       <c r="S98" t="s">
         <v>135</v>
@@ -8314,13 +8330,13 @@
         <v>146</v>
       </c>
       <c r="V98" s="1">
-        <v>46266.37649475694</v>
+        <v>46266.45957881944</v>
       </c>
       <c r="W98">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X98" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AB98">
         <v>0</v>
@@ -8329,10 +8345,10 @@
         <v>135</v>
       </c>
       <c r="AH98" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8355,7 +8371,7 @@
         <v>56</v>
       </c>
       <c r="G99">
-        <v>6014</v>
+        <v>6802</v>
       </c>
       <c r="H99">
         <v>1788</v>
@@ -8364,10 +8380,10 @@
         <v>63</v>
       </c>
       <c r="J99" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N99" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="P99">
         <v>8</v>
@@ -8376,7 +8392,7 @@
         <v>2026</v>
       </c>
       <c r="R99">
-        <v>17399136</v>
+        <v>17399220</v>
       </c>
       <c r="S99" t="s">
         <v>135</v>
@@ -8388,10 +8404,10 @@
         <v>146</v>
       </c>
       <c r="V99" s="1">
-        <v>46266.37591180555</v>
+        <v>46266.37645462963</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X99" t="s">
         <v>154</v>
@@ -8403,18 +8419,18 @@
         <v>135</v>
       </c>
       <c r="AH99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:35">
       <c r="A100">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B100" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C100" t="s">
         <v>50</v>
@@ -8429,22 +8445,19 @@
         <v>56</v>
       </c>
       <c r="G100">
-        <v>6014</v>
+        <v>6801</v>
       </c>
       <c r="H100">
-        <v>1788</v>
+        <v>1796</v>
       </c>
       <c r="I100" t="s">
         <v>63</v>
       </c>
       <c r="J100" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N100" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O100" t="s">
-        <v>114</v>
+        <v>46269</v>
       </c>
       <c r="P100">
         <v>8</v>
@@ -8453,7 +8466,7 @@
         <v>2026</v>
       </c>
       <c r="R100">
-        <v>18155327</v>
+        <v>17399210</v>
       </c>
       <c r="S100" t="s">
         <v>135</v>
@@ -8462,19 +8475,16 @@
         <v>144</v>
       </c>
       <c r="U100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V100" s="1">
-        <v>46268.45896508102</v>
+        <v>46266.37649475694</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X100" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y100" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="AB100">
         <v>0</v>
@@ -8483,18 +8493,18 @@
         <v>135</v>
       </c>
       <c r="AH100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:35">
       <c r="A101">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B101" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C101" t="s">
         <v>50</v>
@@ -8530,7 +8540,7 @@
         <v>2026</v>
       </c>
       <c r="R101">
-        <v>18085231</v>
+        <v>17399136</v>
       </c>
       <c r="S101" t="s">
         <v>135</v>
@@ -8542,13 +8552,13 @@
         <v>146</v>
       </c>
       <c r="V101" s="1">
-        <v>46266.45946195602</v>
+        <v>46266.37591180555</v>
       </c>
       <c r="W101">
         <v>0</v>
       </c>
       <c r="X101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB101">
         <v>0</v>
@@ -8557,18 +8567,18 @@
         <v>135</v>
       </c>
       <c r="AH101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:35">
       <c r="A102">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C102" t="s">
         <v>50</v>
@@ -8583,20 +8593,23 @@
         <v>56</v>
       </c>
       <c r="G102">
-        <v>6233</v>
+        <v>6014</v>
       </c>
       <c r="H102">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I102" t="s">
         <v>63</v>
       </c>
       <c r="J102" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N102" s="1">
         <v>46268</v>
       </c>
+      <c r="O102" t="s">
+        <v>114</v>
+      </c>
       <c r="P102">
         <v>8</v>
       </c>
@@ -8604,7 +8617,7 @@
         <v>2026</v>
       </c>
       <c r="R102">
-        <v>17399176</v>
+        <v>18155327</v>
       </c>
       <c r="S102" t="s">
         <v>135</v>
@@ -8613,16 +8626,19 @@
         <v>144</v>
       </c>
       <c r="U102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V102" s="1">
-        <v>46266.37538684028</v>
+        <v>46268.45896508102</v>
       </c>
       <c r="W102">
         <v>0</v>
       </c>
       <c r="X102" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>177</v>
       </c>
       <c r="AB102">
         <v>0</v>
@@ -8631,24 +8647,24 @@
         <v>135</v>
       </c>
       <c r="AH102" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:35">
       <c r="A103">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C103" t="s">
         <v>50</v>
       </c>
       <c r="D103" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E103" t="s">
         <v>54</v>
@@ -8657,16 +8673,16 @@
         <v>56</v>
       </c>
       <c r="G103">
-        <v>6233</v>
+        <v>6014</v>
       </c>
       <c r="H103">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I103" t="s">
         <v>63</v>
       </c>
       <c r="J103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N103" s="1">
         <v>46268</v>
@@ -8678,7 +8694,7 @@
         <v>2026</v>
       </c>
       <c r="R103">
-        <v>16962294</v>
+        <v>18085231</v>
       </c>
       <c r="S103" t="s">
         <v>135</v>
@@ -8690,13 +8706,13 @@
         <v>146</v>
       </c>
       <c r="V103" s="1">
-        <v>46266.37538506944</v>
+        <v>46266.45946195602</v>
       </c>
       <c r="W103">
         <v>0</v>
       </c>
       <c r="X103" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AB103">
         <v>0</v>
@@ -8705,18 +8721,18 @@
         <v>135</v>
       </c>
       <c r="AH103" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="1:35">
       <c r="A104">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C104" t="s">
         <v>50</v>
@@ -8745,9 +8761,6 @@
       <c r="N104" s="1">
         <v>46268</v>
       </c>
-      <c r="O104" t="s">
-        <v>114</v>
-      </c>
       <c r="P104">
         <v>8</v>
       </c>
@@ -8755,7 +8768,7 @@
         <v>2026</v>
       </c>
       <c r="R104">
-        <v>16976156</v>
+        <v>17399176</v>
       </c>
       <c r="S104" t="s">
         <v>135</v>
@@ -8764,19 +8777,16 @@
         <v>144</v>
       </c>
       <c r="U104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V104" s="1">
-        <v>46268.45881820602</v>
+        <v>46266.37538684028</v>
       </c>
       <c r="W104">
         <v>0</v>
       </c>
       <c r="X104" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="AB104">
         <v>0</v>
@@ -8785,18 +8795,18 @@
         <v>135</v>
       </c>
       <c r="AH104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:35">
       <c r="A105">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B105" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C105" t="s">
         <v>50</v>
@@ -8832,7 +8842,7 @@
         <v>2026</v>
       </c>
       <c r="R105">
-        <v>17948844</v>
+        <v>16962294</v>
       </c>
       <c r="S105" t="s">
         <v>135</v>
@@ -8844,13 +8854,13 @@
         <v>146</v>
       </c>
       <c r="V105" s="1">
-        <v>46266.45895332176</v>
+        <v>46266.37538506944</v>
       </c>
       <c r="W105">
         <v>0</v>
       </c>
       <c r="X105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB105">
         <v>0</v>
@@ -8859,18 +8869,18 @@
         <v>135</v>
       </c>
       <c r="AH105" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="1:35">
       <c r="A106">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B106" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C106" t="s">
         <v>50</v>
@@ -8899,6 +8909,9 @@
       <c r="N106" s="1">
         <v>46268</v>
       </c>
+      <c r="O106" t="s">
+        <v>114</v>
+      </c>
       <c r="P106">
         <v>8</v>
       </c>
@@ -8906,7 +8919,7 @@
         <v>2026</v>
       </c>
       <c r="R106">
-        <v>18085264</v>
+        <v>16976156</v>
       </c>
       <c r="S106" t="s">
         <v>135</v>
@@ -8915,16 +8928,19 @@
         <v>144</v>
       </c>
       <c r="U106" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V106" s="1">
-        <v>46266.45874105324</v>
+        <v>46268.45881820602</v>
       </c>
       <c r="W106">
         <v>0</v>
       </c>
       <c r="X106" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>177</v>
       </c>
       <c r="AB106">
         <v>0</v>
@@ -8933,24 +8949,24 @@
         <v>135</v>
       </c>
       <c r="AH106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI106" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:35">
       <c r="A107">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B107" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C107" t="s">
         <v>50</v>
       </c>
       <c r="D107" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E107" t="s">
         <v>54</v>
@@ -8980,7 +8996,7 @@
         <v>2026</v>
       </c>
       <c r="R107">
-        <v>17948989</v>
+        <v>17948844</v>
       </c>
       <c r="S107" t="s">
         <v>135</v>
@@ -8992,13 +9008,13 @@
         <v>146</v>
       </c>
       <c r="V107" s="1">
-        <v>46266.45873584491</v>
+        <v>46266.45895332176</v>
       </c>
       <c r="W107">
         <v>0</v>
       </c>
       <c r="X107" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AB107">
         <v>0</v>
@@ -9007,18 +9023,18 @@
         <v>135</v>
       </c>
       <c r="AH107" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="1:35">
       <c r="A108">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C108" t="s">
         <v>50</v>
@@ -9033,22 +9049,19 @@
         <v>56</v>
       </c>
       <c r="G108">
-        <v>11359</v>
+        <v>6233</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I108" t="s">
         <v>63</v>
       </c>
       <c r="J108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N108" s="1">
-        <v>46267</v>
-      </c>
-      <c r="O108" t="s">
-        <v>114</v>
+        <v>46268</v>
       </c>
       <c r="P108">
         <v>8</v>
@@ -9057,7 +9070,7 @@
         <v>2026</v>
       </c>
       <c r="R108">
-        <v>18155345</v>
+        <v>18085264</v>
       </c>
       <c r="S108" t="s">
         <v>135</v>
@@ -9066,19 +9079,16 @@
         <v>144</v>
       </c>
       <c r="U108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V108" s="1">
-        <v>46268.45898549769</v>
+        <v>46266.45874105324</v>
       </c>
       <c r="W108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X108" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y108" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="AB108">
         <v>0</v>
@@ -9087,24 +9097,24 @@
         <v>135</v>
       </c>
       <c r="AH108" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI108" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="109" spans="1:35">
       <c r="A109">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C109" t="s">
         <v>50</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" t="s">
         <v>54</v>
@@ -9113,19 +9123,19 @@
         <v>56</v>
       </c>
       <c r="G109">
-        <v>6884</v>
+        <v>6233</v>
       </c>
       <c r="H109">
-        <v>1788</v>
+        <v>6232</v>
       </c>
       <c r="I109" t="s">
         <v>63</v>
       </c>
       <c r="J109" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N109" s="1">
-        <v>46273</v>
+        <v>46268</v>
       </c>
       <c r="P109">
         <v>8</v>
@@ -9134,7 +9144,7 @@
         <v>2026</v>
       </c>
       <c r="R109">
-        <v>16976207</v>
+        <v>17948989</v>
       </c>
       <c r="S109" t="s">
         <v>135</v>
@@ -9146,13 +9156,13 @@
         <v>146</v>
       </c>
       <c r="V109" s="1">
-        <v>46268.45915543981</v>
+        <v>46266.45873584491</v>
       </c>
       <c r="W109">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X109" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AB109">
         <v>0</v>
@@ -9161,24 +9171,24 @@
         <v>135</v>
       </c>
       <c r="AH109" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI109" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:35">
       <c r="A110">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C110" t="s">
         <v>50</v>
       </c>
       <c r="D110" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E110" t="s">
         <v>54</v>
@@ -9187,7 +9197,7 @@
         <v>56</v>
       </c>
       <c r="G110">
-        <v>11303</v>
+        <v>11359</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -9196,10 +9206,13 @@
         <v>63</v>
       </c>
       <c r="J110" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N110" s="1">
-        <v>46279</v>
+        <v>46267</v>
+      </c>
+      <c r="O110" t="s">
+        <v>114</v>
       </c>
       <c r="P110">
         <v>8</v>
@@ -9208,7 +9221,7 @@
         <v>2026</v>
       </c>
       <c r="R110">
-        <v>17949079</v>
+        <v>18155345</v>
       </c>
       <c r="S110" t="s">
         <v>135</v>
@@ -9217,16 +9230,19 @@
         <v>144</v>
       </c>
       <c r="U110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V110" s="1">
-        <v>46267.44505795139</v>
+        <v>46268.45898549769</v>
       </c>
       <c r="W110">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="X110" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>178</v>
       </c>
       <c r="AB110">
         <v>0</v>
@@ -9235,45 +9251,45 @@
         <v>135</v>
       </c>
       <c r="AH110" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI110" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:35">
       <c r="A111">
-        <v>6628</v>
+        <v>6486</v>
       </c>
       <c r="B111" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C111" t="s">
         <v>50</v>
       </c>
       <c r="D111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E111" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F111" t="s">
         <v>56</v>
       </c>
       <c r="G111">
-        <v>945</v>
+        <v>6884</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J111" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N111" s="1">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="P111">
         <v>8</v>
@@ -9282,45 +9298,45 @@
         <v>2026</v>
       </c>
       <c r="R111">
-        <v>16959938</v>
+        <v>16976207</v>
       </c>
       <c r="S111" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="T111" t="s">
+        <v>144</v>
       </c>
       <c r="U111" t="s">
         <v>146</v>
       </c>
       <c r="V111" s="1">
-        <v>46266.04180934028</v>
+        <v>46268.45915543981</v>
       </c>
       <c r="W111">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="X111" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y111" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="AB111">
         <v>0</v>
       </c>
       <c r="AC111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH111" t="s">
         <v>208</v>
       </c>
       <c r="AI111" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:35">
       <c r="A112">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C112" t="s">
         <v>50</v>
@@ -9335,19 +9351,19 @@
         <v>56</v>
       </c>
       <c r="G112">
-        <v>945</v>
+        <v>11303</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J112" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N112" s="1">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="P112">
         <v>8</v>
@@ -9356,45 +9372,45 @@
         <v>2026</v>
       </c>
       <c r="R112">
-        <v>18056695</v>
+        <v>17949079</v>
       </c>
       <c r="S112" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="T112" t="s">
+        <v>144</v>
       </c>
       <c r="U112" t="s">
         <v>146</v>
       </c>
       <c r="V112" s="1">
-        <v>46266.08343295139</v>
+        <v>46267.44505795139</v>
       </c>
       <c r="W112">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="X112" t="s">
         <v>153</v>
       </c>
-      <c r="Y112" t="s">
-        <v>179</v>
-      </c>
       <c r="AB112">
         <v>0</v>
       </c>
       <c r="AC112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH112" t="s">
         <v>208</v>
       </c>
       <c r="AI112" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:35">
       <c r="A113">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C113" t="s">
         <v>50</v>
@@ -9406,7 +9422,7 @@
         <v>55</v>
       </c>
       <c r="F113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G113">
         <v>945</v>
@@ -9430,7 +9446,7 @@
         <v>2026</v>
       </c>
       <c r="R113">
-        <v>18164487</v>
+        <v>16959938</v>
       </c>
       <c r="S113" t="s">
         <v>136</v>
@@ -9439,16 +9455,16 @@
         <v>146</v>
       </c>
       <c r="V113" s="1">
-        <v>46266.08344398148</v>
+        <v>46266.04180934028</v>
       </c>
       <c r="W113">
         <v>-15</v>
       </c>
       <c r="X113" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Y113" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -9457,24 +9473,24 @@
         <v>136</v>
       </c>
       <c r="AH113" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:35">
       <c r="A114">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B114" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C114" t="s">
         <v>50</v>
       </c>
       <c r="D114" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" t="s">
         <v>54</v>
@@ -9483,7 +9499,7 @@
         <v>56</v>
       </c>
       <c r="G114">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -9492,7 +9508,7 @@
         <v>64</v>
       </c>
       <c r="J114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N114" s="1">
         <v>46283</v>
@@ -9504,7 +9520,7 @@
         <v>2026</v>
       </c>
       <c r="R114">
-        <v>17398869</v>
+        <v>18056695</v>
       </c>
       <c r="S114" t="s">
         <v>136</v>
@@ -9513,16 +9529,16 @@
         <v>146</v>
       </c>
       <c r="V114" s="1">
-        <v>46266.25077376157</v>
+        <v>46266.08343295139</v>
       </c>
       <c r="W114">
         <v>-15</v>
       </c>
       <c r="X114" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y114" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB114">
         <v>0</v>
@@ -9531,33 +9547,33 @@
         <v>136</v>
       </c>
       <c r="AH114" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI114" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:35">
       <c r="A115">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C115" t="s">
         <v>50</v>
       </c>
       <c r="D115" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E115" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G115">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -9566,7 +9582,7 @@
         <v>64</v>
       </c>
       <c r="J115" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N115" s="1">
         <v>46283</v>
@@ -9578,7 +9594,7 @@
         <v>2026</v>
       </c>
       <c r="R115">
-        <v>16962093</v>
+        <v>18164487</v>
       </c>
       <c r="S115" t="s">
         <v>136</v>
@@ -9587,16 +9603,16 @@
         <v>146</v>
       </c>
       <c r="V115" s="1">
-        <v>46266.25004302083</v>
+        <v>46266.08344398148</v>
       </c>
       <c r="W115">
         <v>-15</v>
       </c>
       <c r="X115" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y115" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AB115">
         <v>0</v>
@@ -9605,24 +9621,24 @@
         <v>136</v>
       </c>
       <c r="AH115" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:35">
       <c r="A116">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C116" t="s">
         <v>50</v>
       </c>
       <c r="D116" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E116" t="s">
         <v>54</v>
@@ -9652,7 +9668,7 @@
         <v>2026</v>
       </c>
       <c r="R116">
-        <v>17941132</v>
+        <v>17398869</v>
       </c>
       <c r="S116" t="s">
         <v>136</v>
@@ -9661,16 +9677,16 @@
         <v>146</v>
       </c>
       <c r="V116" s="1">
-        <v>46266.25135543982</v>
+        <v>46266.25077376157</v>
       </c>
       <c r="W116">
         <v>-15</v>
       </c>
       <c r="X116" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y116" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB116">
         <v>0</v>
@@ -9679,18 +9695,18 @@
         <v>136</v>
       </c>
       <c r="AH116" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI116" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="1:35">
       <c r="A117">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C117" t="s">
         <v>50</v>
@@ -9705,7 +9721,7 @@
         <v>56</v>
       </c>
       <c r="G117">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -9714,10 +9730,10 @@
         <v>64</v>
       </c>
       <c r="J117" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N117" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P117">
         <v>8</v>
@@ -9726,7 +9742,7 @@
         <v>2026</v>
       </c>
       <c r="R117">
-        <v>17941146</v>
+        <v>16962093</v>
       </c>
       <c r="S117" t="s">
         <v>136</v>
@@ -9735,16 +9751,16 @@
         <v>146</v>
       </c>
       <c r="V117" s="1">
-        <v>46266.25232241898</v>
+        <v>46266.25004302083</v>
       </c>
       <c r="W117">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="X117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y117" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB117">
         <v>0</v>
@@ -9753,33 +9769,33 @@
         <v>136</v>
       </c>
       <c r="AH117" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI117" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="1:35">
       <c r="A118">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B118" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C118" t="s">
         <v>50</v>
       </c>
       <c r="D118" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E118" t="s">
         <v>54</v>
       </c>
       <c r="F118" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G118">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -9788,10 +9804,10 @@
         <v>64</v>
       </c>
       <c r="J118" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N118" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P118">
         <v>8</v>
@@ -9800,7 +9816,7 @@
         <v>2026</v>
       </c>
       <c r="R118">
-        <v>18178132</v>
+        <v>17941132</v>
       </c>
       <c r="S118" t="s">
         <v>136</v>
@@ -9809,16 +9825,16 @@
         <v>146</v>
       </c>
       <c r="V118" s="1">
-        <v>46266.25258784722</v>
+        <v>46266.25135543982</v>
       </c>
       <c r="W118">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="X118" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Y118" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AB118">
         <v>0</v>
@@ -9827,24 +9843,24 @@
         <v>136</v>
       </c>
       <c r="AH118" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI118" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="1:35">
       <c r="A119">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C119" t="s">
         <v>50</v>
       </c>
       <c r="D119" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E119" t="s">
         <v>54</v>
@@ -9853,7 +9869,7 @@
         <v>56</v>
       </c>
       <c r="G119">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -9862,7 +9878,7 @@
         <v>64</v>
       </c>
       <c r="J119" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N119" s="1">
         <v>46275</v>
@@ -9874,7 +9890,7 @@
         <v>2026</v>
       </c>
       <c r="R119">
-        <v>17222405</v>
+        <v>17941146</v>
       </c>
       <c r="S119" t="s">
         <v>136</v>
@@ -9883,16 +9899,16 @@
         <v>146</v>
       </c>
       <c r="V119" s="1">
-        <v>46266.25161940972</v>
+        <v>46266.25232241898</v>
       </c>
       <c r="W119">
         <v>-7</v>
       </c>
       <c r="X119" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="Y119" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AB119">
         <v>0</v>
@@ -9901,33 +9917,33 @@
         <v>136</v>
       </c>
       <c r="AH119" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI119" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:35">
       <c r="A120">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C120" t="s">
         <v>50</v>
       </c>
       <c r="D120" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E120" t="s">
         <v>54</v>
       </c>
       <c r="F120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G120">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -9936,7 +9952,7 @@
         <v>64</v>
       </c>
       <c r="J120" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N120" s="1">
         <v>46275</v>
@@ -9948,7 +9964,7 @@
         <v>2026</v>
       </c>
       <c r="R120">
-        <v>17941156</v>
+        <v>18178132</v>
       </c>
       <c r="S120" t="s">
         <v>136</v>
@@ -9957,16 +9973,16 @@
         <v>146</v>
       </c>
       <c r="V120" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25258784722</v>
       </c>
       <c r="W120">
         <v>-7</v>
       </c>
       <c r="X120" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="Y120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AB120">
         <v>0</v>
@@ -9975,24 +9991,24 @@
         <v>136</v>
       </c>
       <c r="AH120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:35">
       <c r="A121">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B121" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C121" t="s">
         <v>50</v>
       </c>
       <c r="D121" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E121" t="s">
         <v>54</v>
@@ -10022,7 +10038,7 @@
         <v>2026</v>
       </c>
       <c r="R121">
-        <v>18056705</v>
+        <v>17222405</v>
       </c>
       <c r="S121" t="s">
         <v>136</v>
@@ -10031,13 +10047,13 @@
         <v>146</v>
       </c>
       <c r="V121" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25161940972</v>
       </c>
       <c r="W121">
         <v>-7</v>
       </c>
       <c r="X121" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="Y121" t="s">
         <v>187</v>
@@ -10049,30 +10065,30 @@
         <v>136</v>
       </c>
       <c r="AH121" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:35">
       <c r="A122">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C122" t="s">
         <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E122" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G122">
         <v>951</v>
@@ -10096,7 +10112,7 @@
         <v>2026</v>
       </c>
       <c r="R122">
-        <v>18164501</v>
+        <v>17941156</v>
       </c>
       <c r="S122" t="s">
         <v>136</v>
@@ -10105,13 +10121,13 @@
         <v>146</v>
       </c>
       <c r="V122" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25232392361</v>
       </c>
       <c r="W122">
         <v>-7</v>
       </c>
       <c r="X122" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Y122" t="s">
         <v>188</v>
@@ -10123,30 +10139,30 @@
         <v>136</v>
       </c>
       <c r="AH122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI122" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="123" spans="1:35">
       <c r="A123">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C123" t="s">
         <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E123" t="s">
         <v>54</v>
       </c>
       <c r="F123" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G123">
         <v>951</v>
@@ -10170,7 +10186,7 @@
         <v>2026</v>
       </c>
       <c r="R123">
-        <v>18178138</v>
+        <v>18056705</v>
       </c>
       <c r="S123" t="s">
         <v>136</v>
@@ -10179,13 +10195,13 @@
         <v>146</v>
       </c>
       <c r="V123" s="1">
-        <v>46266.25259008102</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W123">
         <v>-7</v>
       </c>
       <c r="X123" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Y123" t="s">
         <v>188</v>
@@ -10197,33 +10213,33 @@
         <v>136</v>
       </c>
       <c r="AH123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="1:35">
       <c r="A124">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B124" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C124" t="s">
         <v>50</v>
       </c>
       <c r="D124" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E124" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G124">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -10232,10 +10248,10 @@
         <v>64</v>
       </c>
       <c r="J124" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N124" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P124">
         <v>8</v>
@@ -10244,7 +10260,7 @@
         <v>2026</v>
       </c>
       <c r="R124">
-        <v>17398883</v>
+        <v>18164501</v>
       </c>
       <c r="S124" t="s">
         <v>136</v>
@@ -10253,13 +10269,13 @@
         <v>146</v>
       </c>
       <c r="V124" s="1">
-        <v>46266.25305</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W124">
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="X124" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y124" t="s">
         <v>189</v>
@@ -10271,33 +10287,33 @@
         <v>136</v>
       </c>
       <c r="AH124" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:35">
       <c r="A125">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B125" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C125" t="s">
         <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E125" t="s">
         <v>54</v>
       </c>
       <c r="F125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G125">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -10306,10 +10322,10 @@
         <v>64</v>
       </c>
       <c r="J125" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N125" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P125">
         <v>8</v>
@@ -10318,7 +10334,7 @@
         <v>2026</v>
       </c>
       <c r="R125">
-        <v>16962107</v>
+        <v>18178138</v>
       </c>
       <c r="S125" t="s">
         <v>136</v>
@@ -10327,16 +10343,16 @@
         <v>146</v>
       </c>
       <c r="V125" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25259008102</v>
       </c>
       <c r="W125">
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="X125" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="Y125" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AB125">
         <v>0</v>
@@ -10345,18 +10361,18 @@
         <v>136</v>
       </c>
       <c r="AH125" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI125" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="126" spans="1:35">
       <c r="A126">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C126" t="s">
         <v>50</v>
@@ -10365,7 +10381,7 @@
         <v>51</v>
       </c>
       <c r="E126" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F126" t="s">
         <v>56</v>
@@ -10392,7 +10408,7 @@
         <v>2026</v>
       </c>
       <c r="R126">
-        <v>17042317</v>
+        <v>17398883</v>
       </c>
       <c r="S126" t="s">
         <v>136</v>
@@ -10401,16 +10417,16 @@
         <v>146</v>
       </c>
       <c r="V126" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25305</v>
       </c>
       <c r="W126">
         <v>-22</v>
       </c>
       <c r="X126" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="Y126" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AB126">
         <v>0</v>
@@ -10419,18 +10435,18 @@
         <v>136</v>
       </c>
       <c r="AH126" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI126" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="127" spans="1:35">
       <c r="A127">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C127" t="s">
         <v>50</v>
@@ -10466,7 +10482,7 @@
         <v>2026</v>
       </c>
       <c r="R127">
-        <v>17941166</v>
+        <v>16962107</v>
       </c>
       <c r="S127" t="s">
         <v>136</v>
@@ -10475,16 +10491,16 @@
         <v>146</v>
       </c>
       <c r="V127" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W127">
         <v>-22</v>
       </c>
       <c r="X127" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y127" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AB127">
         <v>0</v>
@@ -10493,18 +10509,18 @@
         <v>136</v>
       </c>
       <c r="AH127" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI127" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:35">
       <c r="A128">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B128" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C128" t="s">
         <v>50</v>
@@ -10513,10 +10529,10 @@
         <v>51</v>
       </c>
       <c r="E128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F128" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G128">
         <v>953</v>
@@ -10540,7 +10556,7 @@
         <v>2026</v>
       </c>
       <c r="R128">
-        <v>18178144</v>
+        <v>17042317</v>
       </c>
       <c r="S128" t="s">
         <v>136</v>
@@ -10549,16 +10565,16 @@
         <v>146</v>
       </c>
       <c r="V128" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W128">
         <v>-22</v>
       </c>
       <c r="X128" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y128" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AB128">
         <v>0</v>
@@ -10567,24 +10583,24 @@
         <v>136</v>
       </c>
       <c r="AH128" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI128" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="1:35">
       <c r="A129">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B129" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C129" t="s">
         <v>50</v>
       </c>
       <c r="D129" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E129" t="s">
         <v>54</v>
@@ -10593,7 +10609,7 @@
         <v>56</v>
       </c>
       <c r="G129">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -10602,10 +10618,10 @@
         <v>64</v>
       </c>
       <c r="J129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N129" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P129">
         <v>8</v>
@@ -10614,7 +10630,7 @@
         <v>2026</v>
       </c>
       <c r="R129">
-        <v>17399270</v>
+        <v>17941166</v>
       </c>
       <c r="S129" t="s">
         <v>136</v>
@@ -10623,16 +10639,16 @@
         <v>146</v>
       </c>
       <c r="V129" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W129">
-        <v>-15</v>
+        <v>-22</v>
       </c>
       <c r="X129" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Y129" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AB129">
         <v>0</v>
@@ -10641,18 +10657,18 @@
         <v>136</v>
       </c>
       <c r="AH129" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI129" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="130" spans="1:35">
       <c r="A130">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C130" t="s">
         <v>50</v>
@@ -10661,13 +10677,13 @@
         <v>51</v>
       </c>
       <c r="E130" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F130" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G130">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -10676,10 +10692,10 @@
         <v>64</v>
       </c>
       <c r="J130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N130" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P130">
         <v>8</v>
@@ -10688,7 +10704,7 @@
         <v>2026</v>
       </c>
       <c r="R130">
-        <v>17042505</v>
+        <v>18178144</v>
       </c>
       <c r="S130" t="s">
         <v>136</v>
@@ -10697,16 +10713,16 @@
         <v>146</v>
       </c>
       <c r="V130" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W130">
-        <v>-15</v>
+        <v>-22</v>
       </c>
       <c r="X130" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y130" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AB130">
         <v>0</v>
@@ -10715,18 +10731,18 @@
         <v>136</v>
       </c>
       <c r="AH130" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI130" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="131" spans="1:35">
       <c r="A131">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B131" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C131" t="s">
         <v>50</v>
@@ -10762,7 +10778,7 @@
         <v>2026</v>
       </c>
       <c r="R131">
-        <v>17952421</v>
+        <v>17399270</v>
       </c>
       <c r="S131" t="s">
         <v>136</v>
@@ -10771,16 +10787,16 @@
         <v>146</v>
       </c>
       <c r="V131" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W131">
         <v>-15</v>
       </c>
       <c r="X131" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y131" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AB131">
         <v>0</v>
@@ -10789,18 +10805,18 @@
         <v>136</v>
       </c>
       <c r="AH131" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI131" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="132" spans="1:35">
       <c r="A132">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C132" t="s">
         <v>50</v>
@@ -10809,10 +10825,10 @@
         <v>51</v>
       </c>
       <c r="E132" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F132" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G132">
         <v>7022</v>
@@ -10836,7 +10852,7 @@
         <v>2026</v>
       </c>
       <c r="R132">
-        <v>18178174</v>
+        <v>17042505</v>
       </c>
       <c r="S132" t="s">
         <v>136</v>
@@ -10845,16 +10861,16 @@
         <v>146</v>
       </c>
       <c r="V132" s="1">
-        <v>46266.25369988426</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W132">
         <v>-15</v>
       </c>
       <c r="X132" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AB132">
         <v>0</v>
@@ -10863,18 +10879,18 @@
         <v>136</v>
       </c>
       <c r="AH132" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AI132" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="1:35">
       <c r="A133">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B133" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C133" t="s">
         <v>50</v>
@@ -10889,7 +10905,7 @@
         <v>56</v>
       </c>
       <c r="G133">
-        <v>9085</v>
+        <v>7022</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -10898,40 +10914,37 @@
         <v>64</v>
       </c>
       <c r="J133" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N133" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O133" t="s">
-        <v>114</v>
+        <v>46283</v>
       </c>
       <c r="P133">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q133">
         <v>2026</v>
       </c>
       <c r="R133">
-        <v>17399353</v>
+        <v>17952421</v>
       </c>
       <c r="S133" t="s">
         <v>136</v>
       </c>
       <c r="U133" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V133" s="1">
-        <v>46268.62318445602</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="X133" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y133" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AB133">
         <v>0</v>
@@ -10943,30 +10956,30 @@
         <v>209</v>
       </c>
       <c r="AI133" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="134" spans="1:35">
       <c r="A134">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B134" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C134" t="s">
         <v>50</v>
       </c>
       <c r="D134" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E134" t="s">
         <v>54</v>
       </c>
       <c r="F134" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G134">
-        <v>9085</v>
+        <v>7022</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -10975,40 +10988,37 @@
         <v>64</v>
       </c>
       <c r="J134" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N134" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O134" t="s">
-        <v>114</v>
+        <v>46283</v>
       </c>
       <c r="P134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q134">
         <v>2026</v>
       </c>
       <c r="R134">
-        <v>16962370</v>
+        <v>18178174</v>
       </c>
       <c r="S134" t="s">
         <v>136</v>
       </c>
       <c r="U134" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V134" s="1">
-        <v>46268.62319864584</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="X134" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="Y134" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AB134">
         <v>0</v>
@@ -11020,15 +11030,15 @@
         <v>209</v>
       </c>
       <c r="AI134" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:35">
       <c r="A135">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B135" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C135" t="s">
         <v>50</v>
@@ -11067,7 +11077,7 @@
         <v>2026</v>
       </c>
       <c r="R135">
-        <v>16976260</v>
+        <v>17399353</v>
       </c>
       <c r="S135" t="s">
         <v>136</v>
@@ -11076,13 +11086,13 @@
         <v>147</v>
       </c>
       <c r="V135" s="1">
-        <v>46268.62320026621</v>
+        <v>46268.62318445602</v>
       </c>
       <c r="W135">
         <v>0</v>
       </c>
       <c r="X135" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Y135" t="s">
         <v>199</v>
@@ -11094,24 +11104,24 @@
         <v>136</v>
       </c>
       <c r="AH135" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI135" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="136" spans="1:35">
       <c r="A136">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C136" t="s">
         <v>50</v>
       </c>
       <c r="D136" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E136" t="s">
         <v>54</v>
@@ -11144,7 +11154,7 @@
         <v>2026</v>
       </c>
       <c r="R136">
-        <v>17222852</v>
+        <v>16962370</v>
       </c>
       <c r="S136" t="s">
         <v>136</v>
@@ -11153,16 +11163,16 @@
         <v>147</v>
       </c>
       <c r="V136" s="1">
-        <v>46268.62320177083</v>
+        <v>46268.62319864584</v>
       </c>
       <c r="W136">
         <v>0</v>
       </c>
       <c r="X136" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Y136" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB136">
         <v>0</v>
@@ -11171,18 +11181,18 @@
         <v>136</v>
       </c>
       <c r="AH136" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI136" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="137" spans="1:35">
       <c r="A137">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C137" t="s">
         <v>50</v>
@@ -11191,7 +11201,7 @@
         <v>51</v>
       </c>
       <c r="E137" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F137" t="s">
         <v>56</v>
@@ -11221,7 +11231,7 @@
         <v>2026</v>
       </c>
       <c r="R137">
-        <v>17042569</v>
+        <v>16976260</v>
       </c>
       <c r="S137" t="s">
         <v>136</v>
@@ -11230,16 +11240,16 @@
         <v>147</v>
       </c>
       <c r="V137" s="1">
-        <v>46268.62320378472</v>
+        <v>46268.62320026621</v>
       </c>
       <c r="W137">
         <v>0</v>
       </c>
       <c r="X137" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Y137" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB137">
         <v>0</v>
@@ -11248,27 +11258,27 @@
         <v>136</v>
       </c>
       <c r="AH137" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI137" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="138" spans="1:35">
       <c r="A138">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B138" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C138" t="s">
         <v>50</v>
       </c>
       <c r="D138" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E138" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F138" t="s">
         <v>56</v>
@@ -11298,7 +11308,7 @@
         <v>2026</v>
       </c>
       <c r="R138">
-        <v>16960062</v>
+        <v>17222852</v>
       </c>
       <c r="S138" t="s">
         <v>136</v>
@@ -11307,16 +11317,16 @@
         <v>147</v>
       </c>
       <c r="V138" s="1">
-        <v>46268.62320393518</v>
+        <v>46268.62320177083</v>
       </c>
       <c r="W138">
         <v>0</v>
       </c>
       <c r="X138" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y138" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB138">
         <v>0</v>
@@ -11325,27 +11335,27 @@
         <v>136</v>
       </c>
       <c r="AH138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI138" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="1:35">
       <c r="A139">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B139" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C139" t="s">
         <v>50</v>
       </c>
       <c r="D139" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F139" t="s">
         <v>56</v>
@@ -11375,7 +11385,7 @@
         <v>2026</v>
       </c>
       <c r="R139">
-        <v>17941207</v>
+        <v>17042569</v>
       </c>
       <c r="S139" t="s">
         <v>136</v>
@@ -11384,16 +11394,16 @@
         <v>147</v>
       </c>
       <c r="V139" s="1">
-        <v>46268.62320697917</v>
+        <v>46268.62320378472</v>
       </c>
       <c r="W139">
         <v>0</v>
       </c>
       <c r="X139" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="Y139" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB139">
         <v>0</v>
@@ -11402,27 +11412,27 @@
         <v>136</v>
       </c>
       <c r="AH139" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140" spans="1:35">
       <c r="A140">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C140" t="s">
         <v>50</v>
       </c>
       <c r="D140" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E140" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F140" t="s">
         <v>56</v>
@@ -11452,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="R140">
-        <v>17952433</v>
+        <v>16960062</v>
       </c>
       <c r="S140" t="s">
         <v>136</v>
@@ -11461,16 +11471,16 @@
         <v>147</v>
       </c>
       <c r="V140" s="1">
-        <v>46268.62320717592</v>
+        <v>46268.62320393518</v>
       </c>
       <c r="W140">
         <v>0</v>
       </c>
       <c r="X140" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="Y140" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB140">
         <v>0</v>
@@ -11479,24 +11489,24 @@
         <v>136</v>
       </c>
       <c r="AH140" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI140" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="141" spans="1:35">
       <c r="A141">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C141" t="s">
         <v>50</v>
       </c>
       <c r="D141" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
         <v>54</v>
@@ -11529,7 +11539,7 @@
         <v>2026</v>
       </c>
       <c r="R141">
-        <v>17952613</v>
+        <v>17941207</v>
       </c>
       <c r="S141" t="s">
         <v>136</v>
@@ -11538,16 +11548,16 @@
         <v>147</v>
       </c>
       <c r="V141" s="1">
-        <v>46268.62320732639</v>
+        <v>46268.62320697917</v>
       </c>
       <c r="W141">
         <v>0</v>
       </c>
       <c r="X141" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="Y141" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB141">
         <v>0</v>
@@ -11556,24 +11566,24 @@
         <v>136</v>
       </c>
       <c r="AH141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:35">
       <c r="A142">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C142" t="s">
         <v>50</v>
       </c>
       <c r="D142" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E142" t="s">
         <v>54</v>
@@ -11606,7 +11616,7 @@
         <v>2026</v>
       </c>
       <c r="R142">
-        <v>18056791</v>
+        <v>17952433</v>
       </c>
       <c r="S142" t="s">
         <v>136</v>
@@ -11615,7 +11625,7 @@
         <v>147</v>
       </c>
       <c r="V142" s="1">
-        <v>46268.62320810185</v>
+        <v>46268.62320717592</v>
       </c>
       <c r="W142">
         <v>0</v>
@@ -11624,7 +11634,7 @@
         <v>153</v>
       </c>
       <c r="Y142" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB142">
         <v>0</v>
@@ -11633,18 +11643,18 @@
         <v>136</v>
       </c>
       <c r="AH142" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:35">
       <c r="A143">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B143" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C143" t="s">
         <v>50</v>
@@ -11653,10 +11663,10 @@
         <v>52</v>
       </c>
       <c r="E143" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F143" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G143">
         <v>9085</v>
@@ -11683,7 +11693,7 @@
         <v>2026</v>
       </c>
       <c r="R143">
-        <v>18164544</v>
+        <v>17952613</v>
       </c>
       <c r="S143" t="s">
         <v>136</v>
@@ -11692,16 +11702,16 @@
         <v>147</v>
       </c>
       <c r="V143" s="1">
-        <v>46268.6232125</v>
+        <v>46268.62320732639</v>
       </c>
       <c r="W143">
         <v>0</v>
       </c>
       <c r="X143" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Y143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB143">
         <v>0</v>
@@ -11710,30 +11720,30 @@
         <v>136</v>
       </c>
       <c r="AH143" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI143" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="144" spans="1:35">
       <c r="A144">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B144" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C144" t="s">
         <v>50</v>
       </c>
       <c r="D144" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E144" t="s">
         <v>54</v>
       </c>
       <c r="F144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G144">
         <v>9085</v>
@@ -11760,7 +11770,7 @@
         <v>2026</v>
       </c>
       <c r="R144">
-        <v>18178181</v>
+        <v>18056791</v>
       </c>
       <c r="S144" t="s">
         <v>136</v>
@@ -11769,16 +11779,16 @@
         <v>147</v>
       </c>
       <c r="V144" s="1">
-        <v>46268.62321412037</v>
+        <v>46268.62320810185</v>
       </c>
       <c r="W144">
         <v>0</v>
       </c>
       <c r="X144" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Y144" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB144">
         <v>0</v>
@@ -11787,27 +11797,27 @@
         <v>136</v>
       </c>
       <c r="AH144" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI144" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="145" spans="1:35">
       <c r="A145">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C145" t="s">
         <v>50</v>
       </c>
       <c r="D145" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E145" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F145" t="s">
         <v>57</v>
@@ -11837,7 +11847,7 @@
         <v>2026</v>
       </c>
       <c r="R145">
-        <v>18188767</v>
+        <v>18164544</v>
       </c>
       <c r="S145" t="s">
         <v>136</v>
@@ -11846,16 +11856,16 @@
         <v>147</v>
       </c>
       <c r="V145" s="1">
-        <v>46268.6232128125</v>
+        <v>46268.6232125</v>
       </c>
       <c r="W145">
         <v>0</v>
       </c>
       <c r="X145" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y145" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB145">
         <v>0</v>
@@ -11864,24 +11874,24 @@
         <v>136</v>
       </c>
       <c r="AH145" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI145" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="146" spans="1:35">
       <c r="A146">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B146" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C146" t="s">
         <v>50</v>
       </c>
       <c r="D146" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E146" t="s">
         <v>54</v>
@@ -11914,7 +11924,7 @@
         <v>2026</v>
       </c>
       <c r="R146">
-        <v>18188673</v>
+        <v>18178181</v>
       </c>
       <c r="S146" t="s">
         <v>136</v>
@@ -11923,16 +11933,16 @@
         <v>147</v>
       </c>
       <c r="V146" s="1">
-        <v>46268.62321296296</v>
+        <v>46268.62321412037</v>
       </c>
       <c r="W146">
         <v>0</v>
       </c>
       <c r="X146" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Y146" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB146">
         <v>0</v>
@@ -11941,45 +11951,48 @@
         <v>136</v>
       </c>
       <c r="AH146" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI146" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147" spans="1:35">
       <c r="A147">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B147" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C147" t="s">
         <v>50</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E147" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F147" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G147">
-        <v>9087</v>
+        <v>9085</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J147" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N147" s="1">
-        <v>46269</v>
+        <v>46268</v>
+      </c>
+      <c r="O147" t="s">
+        <v>114</v>
       </c>
       <c r="P147">
         <v>9</v>
@@ -11988,69 +12001,75 @@
         <v>2026</v>
       </c>
       <c r="R147">
-        <v>16960086</v>
+        <v>18188767</v>
       </c>
       <c r="S147" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="U147" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V147" s="1">
-        <v>46268.62326365741</v>
+        <v>46268.6232128125</v>
       </c>
       <c r="W147">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X147" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>200</v>
       </c>
       <c r="AB147">
         <v>0</v>
       </c>
       <c r="AC147" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="AH147" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI147" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148" spans="1:35">
       <c r="A148">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B148" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C148" t="s">
         <v>50</v>
       </c>
       <c r="D148" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E148" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F148" t="s">
         <v>57</v>
       </c>
       <c r="G148">
-        <v>9087</v>
+        <v>9085</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J148" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N148" s="1">
-        <v>46269</v>
+        <v>46268</v>
+      </c>
+      <c r="O148" t="s">
+        <v>114</v>
       </c>
       <c r="P148">
         <v>9</v>
@@ -12059,57 +12078,60 @@
         <v>2026</v>
       </c>
       <c r="R148">
-        <v>18164558</v>
+        <v>18188673</v>
       </c>
       <c r="S148" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="U148" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V148" s="1">
-        <v>46268.62327121528</v>
+        <v>46268.62321296296</v>
       </c>
       <c r="W148">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X148" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>200</v>
       </c>
       <c r="AB148">
         <v>0</v>
       </c>
       <c r="AC148" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="AH148" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AI148" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="149" spans="1:35">
       <c r="A149">
-        <v>6404</v>
+        <v>6628</v>
       </c>
       <c r="B149" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C149" t="s">
         <v>50</v>
       </c>
       <c r="D149" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E149" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F149" t="s">
         <v>56</v>
       </c>
       <c r="G149">
-        <v>11001</v>
+        <v>9087</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -12118,72 +12140,69 @@
         <v>65</v>
       </c>
       <c r="J149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N149" s="1">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="P149">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q149">
         <v>2026</v>
       </c>
       <c r="R149">
-        <v>16962453</v>
+        <v>16960086</v>
       </c>
       <c r="S149" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U149" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V149" s="1">
-        <v>46267.66131466435</v>
+        <v>46268.62326365741</v>
       </c>
       <c r="W149">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="X149" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y149" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="AB149">
         <v>0</v>
       </c>
       <c r="AC149" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH149" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AI149" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="150" spans="1:35">
       <c r="A150">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B150" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C150" t="s">
         <v>50</v>
       </c>
       <c r="D150" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G150">
-        <v>11001</v>
+        <v>9087</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -12192,10 +12211,10 @@
         <v>65</v>
       </c>
       <c r="J150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N150" s="1">
-        <v>46321</v>
+        <v>46269</v>
       </c>
       <c r="P150">
         <v>9</v>
@@ -12204,51 +12223,48 @@
         <v>2026</v>
       </c>
       <c r="R150">
-        <v>16962455</v>
+        <v>18164558</v>
       </c>
       <c r="S150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U150" t="s">
         <v>146</v>
       </c>
       <c r="V150" s="1">
-        <v>46266.21595836805</v>
+        <v>46268.62327121528</v>
       </c>
       <c r="W150">
-        <v>-53</v>
+        <v>-1</v>
       </c>
       <c r="X150" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="AB150">
         <v>0</v>
       </c>
       <c r="AC150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH150" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AI150" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:35">
       <c r="A151">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B151" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C151" t="s">
         <v>50</v>
       </c>
       <c r="D151" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E151" t="s">
         <v>54</v>
@@ -12257,7 +12273,7 @@
         <v>56</v>
       </c>
       <c r="G151">
-        <v>7877</v>
+        <v>11001</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -12266,37 +12282,37 @@
         <v>65</v>
       </c>
       <c r="J151" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="N151" s="1">
-        <v>46321</v>
+        <v>46259</v>
       </c>
       <c r="P151">
+        <v>7</v>
+      </c>
+      <c r="Q151">
+        <v>2026</v>
+      </c>
+      <c r="R151">
+        <v>16962453</v>
+      </c>
+      <c r="S151" t="s">
+        <v>54</v>
+      </c>
+      <c r="U151" t="s">
+        <v>145</v>
+      </c>
+      <c r="V151" s="1">
+        <v>46267.66131466435</v>
+      </c>
+      <c r="W151">
         <v>9</v>
       </c>
-      <c r="Q151">
-        <v>2026</v>
-      </c>
-      <c r="R151">
-        <v>17399331</v>
-      </c>
-      <c r="S151" t="s">
-        <v>54</v>
-      </c>
-      <c r="U151" t="s">
-        <v>146</v>
-      </c>
-      <c r="V151" s="1">
-        <v>46266.21572962963</v>
-      </c>
-      <c r="W151">
-        <v>-53</v>
-      </c>
       <c r="X151" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y151" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AB151">
         <v>0</v>
@@ -12305,24 +12321,24 @@
         <v>54</v>
       </c>
       <c r="AH151" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI151" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" spans="1:35">
       <c r="A152">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C152" t="s">
         <v>50</v>
       </c>
       <c r="D152" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E152" t="s">
         <v>54</v>
@@ -12331,7 +12347,7 @@
         <v>56</v>
       </c>
       <c r="G152">
-        <v>9774</v>
+        <v>11001</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -12340,37 +12356,37 @@
         <v>65</v>
       </c>
       <c r="J152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N152" s="1">
-        <v>46259</v>
+        <v>46321</v>
       </c>
       <c r="P152">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q152">
         <v>2026</v>
       </c>
       <c r="R152">
-        <v>16976320</v>
+        <v>16962455</v>
       </c>
       <c r="S152" t="s">
         <v>54</v>
       </c>
       <c r="U152" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V152" s="1">
-        <v>46267.67127083334</v>
+        <v>46266.21595836805</v>
       </c>
       <c r="W152">
-        <v>9</v>
+        <v>-53</v>
       </c>
       <c r="X152" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Y152" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB152">
         <v>0</v>
@@ -12379,18 +12395,18 @@
         <v>54</v>
       </c>
       <c r="AH152" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:35">
       <c r="A153">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C153" t="s">
         <v>50</v>
@@ -12405,7 +12421,7 @@
         <v>56</v>
       </c>
       <c r="G153">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -12414,7 +12430,7 @@
         <v>65</v>
       </c>
       <c r="J153" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="N153" s="1">
         <v>46321</v>
@@ -12426,7 +12442,7 @@
         <v>2026</v>
       </c>
       <c r="R153">
-        <v>16976322</v>
+        <v>17399331</v>
       </c>
       <c r="S153" t="s">
         <v>54</v>
@@ -12435,16 +12451,16 @@
         <v>146</v>
       </c>
       <c r="V153" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.21572962963</v>
       </c>
       <c r="W153">
         <v>-53</v>
       </c>
       <c r="X153" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Y153" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB153">
         <v>0</v>
@@ -12453,18 +12469,18 @@
         <v>54</v>
       </c>
       <c r="AH153" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI153" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:35">
       <c r="A154">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B154" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C154" t="s">
         <v>50</v>
@@ -12479,7 +12495,7 @@
         <v>56</v>
       </c>
       <c r="G154">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -12488,34 +12504,37 @@
         <v>65</v>
       </c>
       <c r="J154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N154" s="1">
-        <v>46321</v>
+        <v>46259</v>
       </c>
       <c r="P154">
+        <v>7</v>
+      </c>
+      <c r="Q154">
+        <v>2026</v>
+      </c>
+      <c r="R154">
+        <v>16976320</v>
+      </c>
+      <c r="S154" t="s">
+        <v>54</v>
+      </c>
+      <c r="U154" t="s">
+        <v>145</v>
+      </c>
+      <c r="V154" s="1">
+        <v>46267.67127083334</v>
+      </c>
+      <c r="W154">
         <v>9</v>
       </c>
-      <c r="Q154">
-        <v>2026</v>
-      </c>
-      <c r="R154">
-        <v>17399291</v>
-      </c>
-      <c r="S154" t="s">
-        <v>54</v>
-      </c>
-      <c r="U154" t="s">
-        <v>146</v>
-      </c>
-      <c r="V154" s="1">
-        <v>46266.00006921296</v>
-      </c>
-      <c r="W154">
-        <v>-53</v>
-      </c>
       <c r="X154" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>204</v>
       </c>
       <c r="AB154">
         <v>0</v>
@@ -12524,24 +12543,24 @@
         <v>54</v>
       </c>
       <c r="AH154" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI154" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="155" spans="1:35">
       <c r="A155">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B155" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C155" t="s">
         <v>50</v>
       </c>
       <c r="D155" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E155" t="s">
         <v>54</v>
@@ -12550,7 +12569,7 @@
         <v>56</v>
       </c>
       <c r="G155">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -12559,7 +12578,7 @@
         <v>65</v>
       </c>
       <c r="J155" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N155" s="1">
         <v>46321</v>
@@ -12571,7 +12590,7 @@
         <v>2026</v>
       </c>
       <c r="R155">
-        <v>16962349</v>
+        <v>16976322</v>
       </c>
       <c r="S155" t="s">
         <v>54</v>
@@ -12580,13 +12599,16 @@
         <v>146</v>
       </c>
       <c r="V155" s="1">
-        <v>46266.00006921296</v>
+        <v>46266.21550011574</v>
       </c>
       <c r="W155">
         <v>-53</v>
       </c>
       <c r="X155" t="s">
-        <v>157</v>
+        <v>155</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>205</v>
       </c>
       <c r="AB155">
         <v>0</v>
@@ -12595,18 +12617,18 @@
         <v>54</v>
       </c>
       <c r="AH155" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AI155" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="156" spans="1:35">
       <c r="A156">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C156" t="s">
         <v>50</v>
@@ -12642,7 +12664,7 @@
         <v>2026</v>
       </c>
       <c r="R156">
-        <v>16976238</v>
+        <v>17399291</v>
       </c>
       <c r="S156" t="s">
         <v>54</v>
@@ -12657,19 +12679,161 @@
         <v>-53</v>
       </c>
       <c r="X156" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB156">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH156" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI156" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="157" spans="1:35">
+      <c r="A157">
+        <v>6404</v>
+      </c>
+      <c r="B157" t="s">
+        <v>46</v>
+      </c>
+      <c r="C157" t="s">
+        <v>50</v>
+      </c>
+      <c r="D157" t="s">
+        <v>53</v>
+      </c>
+      <c r="E157" t="s">
+        <v>54</v>
+      </c>
+      <c r="F157" t="s">
+        <v>56</v>
+      </c>
+      <c r="G157">
+        <v>7027</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157" t="s">
+        <v>65</v>
+      </c>
+      <c r="J157" t="s">
+        <v>112</v>
+      </c>
+      <c r="N157" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P157">
+        <v>9</v>
+      </c>
+      <c r="Q157">
+        <v>2026</v>
+      </c>
+      <c r="R157">
+        <v>16962349</v>
+      </c>
+      <c r="S157" t="s">
+        <v>54</v>
+      </c>
+      <c r="U157" t="s">
+        <v>146</v>
+      </c>
+      <c r="V157" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W157">
+        <v>-53</v>
+      </c>
+      <c r="X157" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB157">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH157" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI157" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="158" spans="1:35">
+      <c r="A158">
+        <v>6486</v>
+      </c>
+      <c r="B158" t="s">
+        <v>44</v>
+      </c>
+      <c r="C158" t="s">
+        <v>50</v>
+      </c>
+      <c r="D158" t="s">
+        <v>51</v>
+      </c>
+      <c r="E158" t="s">
+        <v>54</v>
+      </c>
+      <c r="F158" t="s">
+        <v>56</v>
+      </c>
+      <c r="G158">
+        <v>7027</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158" t="s">
+        <v>65</v>
+      </c>
+      <c r="J158" t="s">
+        <v>112</v>
+      </c>
+      <c r="N158" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P158">
+        <v>9</v>
+      </c>
+      <c r="Q158">
+        <v>2026</v>
+      </c>
+      <c r="R158">
+        <v>16976238</v>
+      </c>
+      <c r="S158" t="s">
+        <v>54</v>
+      </c>
+      <c r="U158" t="s">
+        <v>146</v>
+      </c>
+      <c r="V158" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W158">
+        <v>-53</v>
+      </c>
+      <c r="X158" t="s">
         <v>155</v>
       </c>
-      <c r="AB156">
-        <v>0</v>
-      </c>
-      <c r="AC156" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH156" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI156" t="s">
-        <v>210</v>
+      <c r="AB158">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH158" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI158" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -4456,7 +4456,7 @@
         <v>129</v>
       </c>
       <c r="AH45" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AI45" t="s">
         <v>219</v>
@@ -4536,7 +4536,7 @@
         <v>128</v>
       </c>
       <c r="AH46" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AI46" t="s">
         <v>219</v>
@@ -4616,7 +4616,7 @@
         <v>132</v>
       </c>
       <c r="AH47" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AI47" t="s">
         <v>219</v>
@@ -4696,7 +4696,7 @@
         <v>133</v>
       </c>
       <c r="AH48" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AI48" t="s">
         <v>219</v>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2840" uniqueCount="232">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1055,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI198"/>
+  <dimension ref="A1:AI199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -5378,10 +5378,10 @@
     </row>
     <row r="57" spans="1:35">
       <c r="A57">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
         <v>50</v>
@@ -5417,31 +5417,28 @@
         <v>2026</v>
       </c>
       <c r="R57">
-        <v>16976106</v>
+        <v>17399116</v>
       </c>
       <c r="S57" t="s">
-        <v>133</v>
-      </c>
-      <c r="T57" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="U57" t="s">
         <v>156</v>
       </c>
       <c r="V57" s="1">
-        <v>46268.45929986111</v>
+        <v>46269.63659284722</v>
       </c>
       <c r="W57">
         <v>-4</v>
       </c>
       <c r="X57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AB57">
         <v>0</v>
       </c>
       <c r="AC57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AH57" t="s">
         <v>228</v>
@@ -5452,10 +5449,10 @@
     </row>
     <row r="58" spans="1:35">
       <c r="A58">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C58" t="s">
         <v>50</v>
@@ -5464,7 +5461,7 @@
         <v>51</v>
       </c>
       <c r="E58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F58" t="s">
         <v>56</v>
@@ -5491,7 +5488,7 @@
         <v>2026</v>
       </c>
       <c r="R58">
-        <v>18068599</v>
+        <v>16976106</v>
       </c>
       <c r="S58" t="s">
         <v>133</v>
@@ -5503,13 +5500,13 @@
         <v>156</v>
       </c>
       <c r="V58" s="1">
-        <v>46269.5925421875</v>
+        <v>46268.45929986111</v>
       </c>
       <c r="W58">
         <v>-4</v>
       </c>
       <c r="X58" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AB58">
         <v>0</v>
@@ -5526,16 +5523,16 @@
     </row>
     <row r="59" spans="1:35">
       <c r="A59">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C59" t="s">
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
         <v>55</v>
@@ -5565,7 +5562,7 @@
         <v>2026</v>
       </c>
       <c r="R59">
-        <v>18052518</v>
+        <v>18068599</v>
       </c>
       <c r="S59" t="s">
         <v>133</v>
@@ -5577,7 +5574,7 @@
         <v>156</v>
       </c>
       <c r="V59" s="1">
-        <v>46269.59231454861</v>
+        <v>46269.5925421875</v>
       </c>
       <c r="W59">
         <v>-4</v>
@@ -5600,19 +5597,19 @@
     </row>
     <row r="60" spans="1:35">
       <c r="A60">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
         <v>56</v>
@@ -5639,10 +5636,10 @@
         <v>2026</v>
       </c>
       <c r="R60">
-        <v>18077152</v>
+        <v>18052518</v>
       </c>
       <c r="S60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T60" t="s">
         <v>151</v>
@@ -5651,19 +5648,19 @@
         <v>156</v>
       </c>
       <c r="V60" s="1">
-        <v>46268.58932953704</v>
+        <v>46269.59231454861</v>
       </c>
       <c r="W60">
         <v>-4</v>
       </c>
       <c r="X60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AB60">
         <v>0</v>
       </c>
       <c r="AC60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AH60" t="s">
         <v>228</v>
@@ -5674,16 +5671,16 @@
     </row>
     <row r="61" spans="1:35">
       <c r="A61">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C61" t="s">
         <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
         <v>54</v>
@@ -5713,31 +5710,31 @@
         <v>2026</v>
       </c>
       <c r="R61">
-        <v>18090239</v>
+        <v>18077152</v>
       </c>
       <c r="S61" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="T61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U61" t="s">
         <v>156</v>
       </c>
       <c r="V61" s="1">
-        <v>46267.648038125</v>
+        <v>46268.58932953704</v>
       </c>
       <c r="W61">
         <v>-4</v>
       </c>
       <c r="X61" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AB61">
         <v>0</v>
       </c>
       <c r="AC61" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AH61" t="s">
         <v>228</v>
@@ -5748,10 +5745,10 @@
     </row>
     <row r="62" spans="1:35">
       <c r="A62">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C62" t="s">
         <v>50</v>
@@ -5760,10 +5757,10 @@
         <v>52</v>
       </c>
       <c r="E62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62">
         <v>5907</v>
@@ -5787,31 +5784,31 @@
         <v>2026</v>
       </c>
       <c r="R62">
-        <v>18179146</v>
+        <v>18090239</v>
       </c>
       <c r="S62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="T62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U62" t="s">
         <v>156</v>
       </c>
       <c r="V62" s="1">
-        <v>46267.44824061343</v>
+        <v>46267.648038125</v>
       </c>
       <c r="W62">
         <v>-4</v>
       </c>
       <c r="X62" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AB62">
         <v>0</v>
       </c>
       <c r="AC62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH62" t="s">
         <v>228</v>
@@ -5822,19 +5819,19 @@
     </row>
     <row r="63" spans="1:35">
       <c r="A63">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
         <v>57</v>
@@ -5861,10 +5858,10 @@
         <v>2026</v>
       </c>
       <c r="R63">
-        <v>18190450</v>
+        <v>18179146</v>
       </c>
       <c r="S63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T63" t="s">
         <v>153</v>
@@ -5873,19 +5870,19 @@
         <v>156</v>
       </c>
       <c r="V63" s="1">
-        <v>46269.59082328704</v>
+        <v>46267.44824061343</v>
       </c>
       <c r="W63">
         <v>-4</v>
       </c>
       <c r="X63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB63">
         <v>0</v>
       </c>
       <c r="AC63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AH63" t="s">
         <v>228</v>
@@ -5896,10 +5893,10 @@
     </row>
     <row r="64" spans="1:35">
       <c r="A64">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
@@ -5911,22 +5908,22 @@
         <v>54</v>
       </c>
       <c r="F64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G64">
-        <v>11550</v>
+        <v>5907</v>
       </c>
       <c r="H64">
-        <v>1862</v>
+        <v>5784</v>
       </c>
       <c r="I64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N64" s="1">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="P64">
         <v>8</v>
@@ -5935,31 +5932,31 @@
         <v>2026</v>
       </c>
       <c r="R64">
-        <v>17988603</v>
+        <v>18190450</v>
       </c>
       <c r="S64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T64" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="U64" t="s">
         <v>156</v>
       </c>
       <c r="V64" s="1">
-        <v>46267.72055925926</v>
+        <v>46269.59082328704</v>
       </c>
       <c r="W64">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="X64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB64">
         <v>0</v>
       </c>
       <c r="AC64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AH64" t="s">
         <v>228</v>
@@ -5970,10 +5967,10 @@
     </row>
     <row r="65" spans="1:35">
       <c r="A65">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
@@ -5982,7 +5979,7 @@
         <v>51</v>
       </c>
       <c r="E65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F65" t="s">
         <v>56</v>
@@ -6009,10 +6006,10 @@
         <v>2026</v>
       </c>
       <c r="R65">
-        <v>18048493</v>
+        <v>17988603</v>
       </c>
       <c r="S65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T65" t="s">
         <v>140</v>
@@ -6021,13 +6018,13 @@
         <v>156</v>
       </c>
       <c r="V65" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="W65">
         <v>-17</v>
       </c>
       <c r="X65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB65">
         <v>0</v>
@@ -6044,10 +6041,10 @@
     </row>
     <row r="66" spans="1:35">
       <c r="A66">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
         <v>50</v>
@@ -6056,10 +6053,10 @@
         <v>51</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G66">
         <v>11550</v>
@@ -6083,10 +6080,10 @@
         <v>2026</v>
       </c>
       <c r="R66">
-        <v>18214931</v>
+        <v>18048493</v>
       </c>
       <c r="S66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T66" t="s">
         <v>140</v>
@@ -6095,19 +6092,19 @@
         <v>156</v>
       </c>
       <c r="V66" s="1">
-        <v>46267.79441215278</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="W66">
         <v>-17</v>
       </c>
       <c r="X66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH66" t="s">
         <v>228</v>
@@ -6118,10 +6115,10 @@
     </row>
     <row r="67" spans="1:35">
       <c r="A67">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
@@ -6133,22 +6130,22 @@
         <v>54</v>
       </c>
       <c r="F67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G67">
-        <v>11752</v>
+        <v>11550</v>
       </c>
       <c r="H67">
-        <v>11751</v>
+        <v>1862</v>
       </c>
       <c r="I67" t="s">
         <v>62</v>
       </c>
       <c r="J67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N67" s="1">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="P67">
         <v>8</v>
@@ -6157,31 +6154,31 @@
         <v>2026</v>
       </c>
       <c r="R67">
-        <v>18260411</v>
+        <v>18214931</v>
       </c>
       <c r="S67" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T67" t="s">
         <v>140</v>
       </c>
       <c r="U67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V67" s="1">
-        <v>46267.7205502662</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="W67">
-        <v>2</v>
+        <v>-17</v>
       </c>
       <c r="X67" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB67">
         <v>0</v>
       </c>
       <c r="AC67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH67" t="s">
         <v>228</v>
@@ -6192,10 +6189,10 @@
     </row>
     <row r="68" spans="1:35">
       <c r="A68">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
@@ -6204,7 +6201,7 @@
         <v>51</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68" t="s">
         <v>56</v>
@@ -6222,7 +6219,7 @@
         <v>87</v>
       </c>
       <c r="N68" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P68">
         <v>8</v>
@@ -6231,25 +6228,25 @@
         <v>2026</v>
       </c>
       <c r="R68">
-        <v>18173143</v>
+        <v>18260411</v>
       </c>
       <c r="S68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T68" t="s">
         <v>140</v>
       </c>
       <c r="U68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V68" s="1">
-        <v>46267.79439748843</v>
+        <v>46267.7205502662</v>
       </c>
       <c r="W68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB68">
         <v>0</v>
@@ -6266,22 +6263,22 @@
     </row>
     <row r="69" spans="1:35">
       <c r="A69">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C69" t="s">
         <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E69" t="s">
         <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69">
         <v>11752</v>
@@ -6298,9 +6295,6 @@
       <c r="N69" s="1">
         <v>46268</v>
       </c>
-      <c r="O69" t="s">
-        <v>121</v>
-      </c>
       <c r="P69">
         <v>8</v>
       </c>
@@ -6308,25 +6302,25 @@
         <v>2026</v>
       </c>
       <c r="R69">
-        <v>18220251</v>
+        <v>18173143</v>
       </c>
       <c r="S69" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T69" t="s">
+        <v>140</v>
       </c>
       <c r="U69" t="s">
         <v>156</v>
       </c>
       <c r="V69" s="1">
-        <v>46267.79440011574</v>
+        <v>46267.79439748843</v>
       </c>
       <c r="W69">
         <v>1</v>
       </c>
       <c r="X69" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="AB69">
         <v>0</v>
@@ -6343,19 +6337,19 @@
     </row>
     <row r="70" spans="1:35">
       <c r="A70">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C70" t="s">
         <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F70" t="s">
         <v>57</v>
@@ -6375,6 +6369,9 @@
       <c r="N70" s="1">
         <v>46268</v>
       </c>
+      <c r="O70" t="s">
+        <v>121</v>
+      </c>
       <c r="P70">
         <v>8</v>
       </c>
@@ -6382,31 +6379,31 @@
         <v>2026</v>
       </c>
       <c r="R70">
-        <v>18214951</v>
+        <v>18220251</v>
       </c>
       <c r="S70" t="s">
-        <v>141</v>
-      </c>
-      <c r="T70" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U70" t="s">
         <v>156</v>
       </c>
       <c r="V70" s="1">
-        <v>46267.79439818287</v>
+        <v>46267.79440011574</v>
       </c>
       <c r="W70">
         <v>1</v>
       </c>
       <c r="X70" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>193</v>
       </c>
       <c r="AB70">
         <v>0</v>
       </c>
       <c r="AC70" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH70" t="s">
         <v>228</v>
@@ -6417,10 +6414,10 @@
     </row>
     <row r="71" spans="1:35">
       <c r="A71">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
         <v>50</v>
@@ -6432,22 +6429,22 @@
         <v>54</v>
       </c>
       <c r="F71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G71">
-        <v>11748</v>
+        <v>11752</v>
       </c>
       <c r="H71">
-        <v>11747</v>
+        <v>11751</v>
       </c>
       <c r="I71" t="s">
         <v>62</v>
       </c>
       <c r="J71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N71" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P71">
         <v>8</v>
@@ -6456,31 +6453,31 @@
         <v>2026</v>
       </c>
       <c r="R71">
-        <v>18260401</v>
+        <v>18214951</v>
       </c>
       <c r="S71" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T71" t="s">
         <v>140</v>
       </c>
       <c r="U71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V71" s="1">
-        <v>46267.7202693287</v>
+        <v>46267.79439818287</v>
       </c>
       <c r="W71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB71">
         <v>0</v>
       </c>
       <c r="AC71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH71" t="s">
         <v>228</v>
@@ -6491,10 +6488,10 @@
     </row>
     <row r="72" spans="1:35">
       <c r="A72">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
         <v>50</v>
@@ -6503,7 +6500,7 @@
         <v>51</v>
       </c>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F72" t="s">
         <v>56</v>
@@ -6521,7 +6518,7 @@
         <v>88</v>
       </c>
       <c r="N72" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P72">
         <v>8</v>
@@ -6530,25 +6527,25 @@
         <v>2026</v>
       </c>
       <c r="R72">
-        <v>18173127</v>
+        <v>18260401</v>
       </c>
       <c r="S72" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T72" t="s">
         <v>140</v>
       </c>
       <c r="U72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V72" s="1">
-        <v>46267.79409846065</v>
+        <v>46267.7202693287</v>
       </c>
       <c r="W72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X72" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB72">
         <v>0</v>
@@ -6565,16 +6562,16 @@
     </row>
     <row r="73" spans="1:35">
       <c r="A73">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
         <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E73" t="s">
         <v>55</v>
@@ -6604,7 +6601,7 @@
         <v>2026</v>
       </c>
       <c r="R73">
-        <v>18170386</v>
+        <v>18173127</v>
       </c>
       <c r="S73" t="s">
         <v>140</v>
@@ -6616,7 +6613,7 @@
         <v>156</v>
       </c>
       <c r="V73" s="1">
-        <v>46267.79409725694</v>
+        <v>46267.79409846065</v>
       </c>
       <c r="W73">
         <v>1</v>
@@ -6639,10 +6636,10 @@
     </row>
     <row r="74" spans="1:35">
       <c r="A74">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C74" t="s">
         <v>50</v>
@@ -6654,7 +6651,7 @@
         <v>55</v>
       </c>
       <c r="F74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G74">
         <v>11748</v>
@@ -6678,22 +6675,25 @@
         <v>2026</v>
       </c>
       <c r="R74">
-        <v>18220239</v>
+        <v>18170386</v>
       </c>
       <c r="S74" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T74" t="s">
+        <v>140</v>
       </c>
       <c r="U74" t="s">
         <v>156</v>
       </c>
       <c r="V74" s="1">
-        <v>46267.79410239583</v>
+        <v>46267.79409725694</v>
       </c>
       <c r="W74">
         <v>1</v>
       </c>
       <c r="X74" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AB74">
         <v>0</v>
@@ -6710,19 +6710,19 @@
     </row>
     <row r="75" spans="1:35">
       <c r="A75">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
         <v>57</v>
@@ -6749,31 +6749,28 @@
         <v>2026</v>
       </c>
       <c r="R75">
-        <v>18214939</v>
+        <v>18220239</v>
       </c>
       <c r="S75" t="s">
-        <v>141</v>
-      </c>
-      <c r="T75" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U75" t="s">
         <v>156</v>
       </c>
       <c r="V75" s="1">
-        <v>46267.79409934028</v>
+        <v>46267.79410239583</v>
       </c>
       <c r="W75">
         <v>1</v>
       </c>
       <c r="X75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB75">
         <v>0</v>
       </c>
       <c r="AC75" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH75" t="s">
         <v>228</v>
@@ -6784,10 +6781,10 @@
     </row>
     <row r="76" spans="1:35">
       <c r="A76">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C76" t="s">
         <v>50</v>
@@ -6799,22 +6796,22 @@
         <v>54</v>
       </c>
       <c r="F76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76">
-        <v>11750</v>
+        <v>11748</v>
       </c>
       <c r="H76">
-        <v>11749</v>
+        <v>11747</v>
       </c>
       <c r="I76" t="s">
         <v>62</v>
       </c>
       <c r="J76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N76" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P76">
         <v>8</v>
@@ -6823,31 +6820,31 @@
         <v>2026</v>
       </c>
       <c r="R76">
-        <v>18260406</v>
+        <v>18214939</v>
       </c>
       <c r="S76" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T76" t="s">
         <v>140</v>
       </c>
       <c r="U76" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V76" s="1">
-        <v>46267.72033356482</v>
+        <v>46267.79409934028</v>
       </c>
       <c r="W76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X76" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB76">
         <v>0</v>
       </c>
       <c r="AC76" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH76" t="s">
         <v>228</v>
@@ -6858,10 +6855,10 @@
     </row>
     <row r="77" spans="1:35">
       <c r="A77">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
         <v>50</v>
@@ -6870,7 +6867,7 @@
         <v>51</v>
       </c>
       <c r="E77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F77" t="s">
         <v>56</v>
@@ -6888,7 +6885,7 @@
         <v>89</v>
       </c>
       <c r="N77" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P77">
         <v>8</v>
@@ -6897,25 +6894,25 @@
         <v>2026</v>
       </c>
       <c r="R77">
-        <v>18173135</v>
+        <v>18260406</v>
       </c>
       <c r="S77" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T77" t="s">
         <v>140</v>
       </c>
       <c r="U77" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V77" s="1">
-        <v>46267.79418105324</v>
+        <v>46267.72033356482</v>
       </c>
       <c r="W77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB77">
         <v>0</v>
@@ -6932,16 +6929,16 @@
     </row>
     <row r="78" spans="1:35">
       <c r="A78">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
         <v>50</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E78" t="s">
         <v>55</v>
@@ -6971,7 +6968,7 @@
         <v>2026</v>
       </c>
       <c r="R78">
-        <v>18170394</v>
+        <v>18173135</v>
       </c>
       <c r="S78" t="s">
         <v>140</v>
@@ -6983,7 +6980,7 @@
         <v>156</v>
       </c>
       <c r="V78" s="1">
-        <v>46267.79418005787</v>
+        <v>46267.79418105324</v>
       </c>
       <c r="W78">
         <v>1</v>
@@ -7006,10 +7003,10 @@
     </row>
     <row r="79" spans="1:35">
       <c r="A79">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" t="s">
         <v>50</v>
@@ -7021,7 +7018,7 @@
         <v>55</v>
       </c>
       <c r="F79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G79">
         <v>11750</v>
@@ -7045,22 +7042,25 @@
         <v>2026</v>
       </c>
       <c r="R79">
-        <v>18220245</v>
+        <v>18170394</v>
       </c>
       <c r="S79" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T79" t="s">
+        <v>140</v>
       </c>
       <c r="U79" t="s">
         <v>156</v>
       </c>
       <c r="V79" s="1">
-        <v>46267.79418379629</v>
+        <v>46267.79418005787</v>
       </c>
       <c r="W79">
         <v>1</v>
       </c>
       <c r="X79" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AB79">
         <v>0</v>
@@ -7077,19 +7077,19 @@
     </row>
     <row r="80" spans="1:35">
       <c r="A80">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
         <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F80" t="s">
         <v>57</v>
@@ -7116,31 +7116,28 @@
         <v>2026</v>
       </c>
       <c r="R80">
-        <v>18214945</v>
+        <v>18220245</v>
       </c>
       <c r="S80" t="s">
-        <v>141</v>
-      </c>
-      <c r="T80" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U80" t="s">
         <v>156</v>
       </c>
       <c r="V80" s="1">
-        <v>46267.79418283565</v>
+        <v>46267.79418379629</v>
       </c>
       <c r="W80">
         <v>1</v>
       </c>
       <c r="X80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB80">
         <v>0</v>
       </c>
       <c r="AC80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH80" t="s">
         <v>228</v>
@@ -7151,10 +7148,10 @@
     </row>
     <row r="81" spans="1:35">
       <c r="A81">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
         <v>50</v>
@@ -7166,19 +7163,19 @@
         <v>54</v>
       </c>
       <c r="F81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G81">
-        <v>6889</v>
+        <v>11750</v>
       </c>
       <c r="H81">
-        <v>1862</v>
+        <v>11749</v>
       </c>
       <c r="I81" t="s">
         <v>62</v>
       </c>
       <c r="J81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N81" s="1">
         <v>46268</v>
@@ -7190,10 +7187,10 @@
         <v>2026</v>
       </c>
       <c r="R81">
-        <v>18260396</v>
+        <v>18214945</v>
       </c>
       <c r="S81" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T81" t="s">
         <v>140</v>
@@ -7202,19 +7199,19 @@
         <v>156</v>
       </c>
       <c r="V81" s="1">
-        <v>46267.71937662037</v>
+        <v>46267.79418283565</v>
       </c>
       <c r="W81">
         <v>1</v>
       </c>
       <c r="X81" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB81">
         <v>0</v>
       </c>
       <c r="AC81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH81" t="s">
         <v>228</v>
@@ -7225,10 +7222,10 @@
     </row>
     <row r="82" spans="1:35">
       <c r="A82">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
         <v>50</v>
@@ -7237,7 +7234,7 @@
         <v>51</v>
       </c>
       <c r="E82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F82" t="s">
         <v>56</v>
@@ -7264,10 +7261,10 @@
         <v>2026</v>
       </c>
       <c r="R82">
-        <v>18048463</v>
+        <v>18260396</v>
       </c>
       <c r="S82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T82" t="s">
         <v>140</v>
@@ -7276,13 +7273,13 @@
         <v>156</v>
       </c>
       <c r="V82" s="1">
-        <v>46267.79259834491</v>
+        <v>46267.71937662037</v>
       </c>
       <c r="W82">
         <v>1</v>
       </c>
       <c r="X82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB82">
         <v>0</v>
@@ -7299,10 +7296,10 @@
     </row>
     <row r="83" spans="1:35">
       <c r="A83">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
         <v>50</v>
@@ -7311,10 +7308,10 @@
         <v>51</v>
       </c>
       <c r="E83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G83">
         <v>6889</v>
@@ -7338,10 +7335,10 @@
         <v>2026</v>
       </c>
       <c r="R83">
-        <v>18214913</v>
+        <v>18048463</v>
       </c>
       <c r="S83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T83" t="s">
         <v>140</v>
@@ -7350,19 +7347,19 @@
         <v>156</v>
       </c>
       <c r="V83" s="1">
-        <v>46267.79260170139</v>
+        <v>46267.79259834491</v>
       </c>
       <c r="W83">
         <v>1</v>
       </c>
       <c r="X83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB83">
         <v>0</v>
       </c>
       <c r="AC83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH83" t="s">
         <v>228</v>
@@ -7373,16 +7370,16 @@
     </row>
     <row r="84" spans="1:35">
       <c r="A84">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
         <v>50</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E84" t="s">
         <v>54</v>
@@ -7405,9 +7402,6 @@
       <c r="N84" s="1">
         <v>46268</v>
       </c>
-      <c r="O84" t="s">
-        <v>120</v>
-      </c>
       <c r="P84">
         <v>8</v>
       </c>
@@ -7415,34 +7409,31 @@
         <v>2026</v>
       </c>
       <c r="R84">
-        <v>18187275</v>
+        <v>18214913</v>
       </c>
       <c r="S84" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T84" t="s">
         <v>140</v>
       </c>
       <c r="U84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V84" s="1">
-        <v>46268.37621265047</v>
+        <v>46267.79260170139</v>
       </c>
       <c r="W84">
         <v>1</v>
       </c>
       <c r="X84" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y84" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="AB84">
         <v>0</v>
       </c>
       <c r="AC84" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH84" t="s">
         <v>228</v>
@@ -7453,38 +7444,41 @@
     </row>
     <row r="85" spans="1:35">
       <c r="A85">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B85" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C85" t="s">
         <v>50</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F85" t="s">
         <v>57</v>
       </c>
       <c r="G85">
-        <v>11758</v>
+        <v>6889</v>
       </c>
       <c r="H85">
-        <v>11757</v>
+        <v>1862</v>
       </c>
       <c r="I85" t="s">
         <v>62</v>
       </c>
       <c r="J85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N85" s="1">
         <v>46268</v>
       </c>
+      <c r="O85" t="s">
+        <v>120</v>
+      </c>
       <c r="P85">
         <v>8</v>
       </c>
@@ -7492,22 +7486,28 @@
         <v>2026</v>
       </c>
       <c r="R85">
-        <v>18220263</v>
+        <v>18187275</v>
       </c>
       <c r="S85" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="T85" t="s">
+        <v>140</v>
       </c>
       <c r="U85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V85" s="1">
-        <v>46267.79440636574</v>
+        <v>46268.37621265047</v>
       </c>
       <c r="W85">
         <v>1</v>
       </c>
       <c r="X85" t="s">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>194</v>
       </c>
       <c r="AB85">
         <v>0</v>
@@ -7524,37 +7524,37 @@
     </row>
     <row r="86" spans="1:35">
       <c r="A86">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C86" t="s">
         <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E86" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G86">
-        <v>11760</v>
+        <v>11758</v>
       </c>
       <c r="H86">
-        <v>11759</v>
+        <v>11757</v>
       </c>
       <c r="I86" t="s">
         <v>62</v>
       </c>
       <c r="J86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N86" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P86">
         <v>8</v>
@@ -7563,25 +7563,22 @@
         <v>2026</v>
       </c>
       <c r="R86">
-        <v>18260421</v>
+        <v>18220263</v>
       </c>
       <c r="S86" t="s">
-        <v>139</v>
-      </c>
-      <c r="T86" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U86" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V86" s="1">
-        <v>46267.72037954861</v>
+        <v>46267.79440636574</v>
       </c>
       <c r="W86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X86" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AB86">
         <v>0</v>
@@ -7598,10 +7595,10 @@
     </row>
     <row r="87" spans="1:35">
       <c r="A87">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
         <v>50</v>
@@ -7610,7 +7607,7 @@
         <v>51</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F87" t="s">
         <v>56</v>
@@ -7628,7 +7625,7 @@
         <v>92</v>
       </c>
       <c r="N87" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P87">
         <v>8</v>
@@ -7637,25 +7634,25 @@
         <v>2026</v>
       </c>
       <c r="R87">
-        <v>18173151</v>
+        <v>18260421</v>
       </c>
       <c r="S87" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T87" t="s">
         <v>140</v>
       </c>
       <c r="U87" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V87" s="1">
-        <v>46267.79424664352</v>
+        <v>46267.72037954861</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB87">
         <v>0</v>
@@ -7672,16 +7669,16 @@
     </row>
     <row r="88" spans="1:35">
       <c r="A88">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C88" t="s">
         <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E88" t="s">
         <v>55</v>
@@ -7711,7 +7708,7 @@
         <v>2026</v>
       </c>
       <c r="R88">
-        <v>18170402</v>
+        <v>18173151</v>
       </c>
       <c r="S88" t="s">
         <v>140</v>
@@ -7723,7 +7720,7 @@
         <v>156</v>
       </c>
       <c r="V88" s="1">
-        <v>46267.79424586806</v>
+        <v>46267.79424664352</v>
       </c>
       <c r="W88">
         <v>1</v>
@@ -7746,10 +7743,10 @@
     </row>
     <row r="89" spans="1:35">
       <c r="A89">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C89" t="s">
         <v>50</v>
@@ -7761,7 +7758,7 @@
         <v>55</v>
       </c>
       <c r="F89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G89">
         <v>11760</v>
@@ -7785,22 +7782,25 @@
         <v>2026</v>
       </c>
       <c r="R89">
-        <v>18220269</v>
+        <v>18170402</v>
       </c>
       <c r="S89" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T89" t="s">
+        <v>140</v>
       </c>
       <c r="U89" t="s">
         <v>156</v>
       </c>
       <c r="V89" s="1">
-        <v>46267.79424864583</v>
+        <v>46267.79424586806</v>
       </c>
       <c r="W89">
         <v>1</v>
       </c>
       <c r="X89" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AB89">
         <v>0</v>
@@ -7817,19 +7817,19 @@
     </row>
     <row r="90" spans="1:35">
       <c r="A90">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
         <v>50</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E90" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F90" t="s">
         <v>57</v>
@@ -7856,31 +7856,28 @@
         <v>2026</v>
       </c>
       <c r="R90">
-        <v>18214963</v>
+        <v>18220269</v>
       </c>
       <c r="S90" t="s">
-        <v>141</v>
-      </c>
-      <c r="T90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U90" t="s">
         <v>156</v>
       </c>
       <c r="V90" s="1">
-        <v>46267.79424725694</v>
+        <v>46267.79424864583</v>
       </c>
       <c r="W90">
         <v>1</v>
       </c>
       <c r="X90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB90">
         <v>0</v>
       </c>
       <c r="AC90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH90" t="s">
         <v>228</v>
@@ -7891,16 +7888,16 @@
     </row>
     <row r="91" spans="1:35">
       <c r="A91">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
         <v>50</v>
       </c>
       <c r="D91" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
         <v>54</v>
@@ -7930,10 +7927,10 @@
         <v>2026</v>
       </c>
       <c r="R91">
-        <v>18260057</v>
+        <v>18214963</v>
       </c>
       <c r="S91" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T91" t="s">
         <v>140</v>
@@ -7942,19 +7939,19 @@
         <v>156</v>
       </c>
       <c r="V91" s="1">
-        <v>46267.79425081018</v>
+        <v>46267.79424725694</v>
       </c>
       <c r="W91">
         <v>1</v>
       </c>
       <c r="X91" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AB91">
         <v>0</v>
       </c>
       <c r="AC91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH91" t="s">
         <v>228</v>
@@ -7965,37 +7962,37 @@
     </row>
     <row r="92" spans="1:35">
       <c r="A92">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C92" t="s">
         <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E92" t="s">
         <v>54</v>
       </c>
       <c r="F92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92">
-        <v>11756</v>
+        <v>11760</v>
       </c>
       <c r="H92">
-        <v>11755</v>
+        <v>11759</v>
       </c>
       <c r="I92" t="s">
         <v>62</v>
       </c>
       <c r="J92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N92" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P92">
         <v>8</v>
@@ -8004,25 +8001,25 @@
         <v>2026</v>
       </c>
       <c r="R92">
-        <v>18260416</v>
+        <v>18260057</v>
       </c>
       <c r="S92" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="T92" t="s">
         <v>140</v>
       </c>
       <c r="U92" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V92" s="1">
-        <v>46267.71942916667</v>
+        <v>46267.79425081018</v>
       </c>
       <c r="W92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X92" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AB92">
         <v>0</v>
@@ -8039,22 +8036,22 @@
     </row>
     <row r="93" spans="1:35">
       <c r="A93">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
         <v>50</v>
       </c>
       <c r="D93" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G93">
         <v>11756</v>
@@ -8069,7 +8066,7 @@
         <v>93</v>
       </c>
       <c r="N93" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P93">
         <v>8</v>
@@ -8078,22 +8075,25 @@
         <v>2026</v>
       </c>
       <c r="R93">
-        <v>18220257</v>
+        <v>18260416</v>
       </c>
       <c r="S93" t="s">
-        <v>142</v>
+        <v>139</v>
+      </c>
+      <c r="T93" t="s">
+        <v>140</v>
       </c>
       <c r="U93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V93" s="1">
-        <v>46267.79268530093</v>
+        <v>46267.71942916667</v>
       </c>
       <c r="W93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X93" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AB93">
         <v>0</v>
@@ -8110,19 +8110,19 @@
     </row>
     <row r="94" spans="1:35">
       <c r="A94">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C94" t="s">
         <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F94" t="s">
         <v>57</v>
@@ -8149,31 +8149,28 @@
         <v>2026</v>
       </c>
       <c r="R94">
-        <v>18214957</v>
+        <v>18220257</v>
       </c>
       <c r="S94" t="s">
-        <v>141</v>
-      </c>
-      <c r="T94" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U94" t="s">
         <v>156</v>
       </c>
       <c r="V94" s="1">
-        <v>46267.79268769676</v>
+        <v>46267.79268530093</v>
       </c>
       <c r="W94">
         <v>1</v>
       </c>
       <c r="X94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB94">
         <v>0</v>
       </c>
       <c r="AC94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH94" t="s">
         <v>228</v>
@@ -8184,34 +8181,34 @@
     </row>
     <row r="95" spans="1:35">
       <c r="A95">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
         <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F95" t="s">
         <v>57</v>
       </c>
       <c r="G95">
-        <v>6221</v>
+        <v>11756</v>
       </c>
       <c r="H95">
-        <v>6220</v>
+        <v>11755</v>
       </c>
       <c r="I95" t="s">
         <v>62</v>
       </c>
       <c r="J95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N95" s="1">
         <v>46268</v>
@@ -8223,28 +8220,31 @@
         <v>2026</v>
       </c>
       <c r="R95">
-        <v>18220209</v>
+        <v>18214957</v>
       </c>
       <c r="S95" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="T95" t="s">
+        <v>140</v>
       </c>
       <c r="U95" t="s">
         <v>156</v>
       </c>
       <c r="V95" s="1">
-        <v>46267.79249748842</v>
+        <v>46267.79268769676</v>
       </c>
       <c r="W95">
         <v>1</v>
       </c>
       <c r="X95" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AB95">
         <v>0</v>
       </c>
       <c r="AC95" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AH95" t="s">
         <v>228</v>
@@ -8255,19 +8255,19 @@
     </row>
     <row r="96" spans="1:35">
       <c r="A96">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C96" t="s">
         <v>50</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E96" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F96" t="s">
         <v>57</v>
@@ -8294,31 +8294,28 @@
         <v>2026</v>
       </c>
       <c r="R96">
-        <v>18214889</v>
+        <v>18220209</v>
       </c>
       <c r="S96" t="s">
-        <v>141</v>
-      </c>
-      <c r="T96" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U96" t="s">
         <v>156</v>
       </c>
       <c r="V96" s="1">
-        <v>46267.79249788194</v>
+        <v>46267.79249748842</v>
       </c>
       <c r="W96">
         <v>1</v>
       </c>
       <c r="X96" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB96">
         <v>0</v>
       </c>
       <c r="AC96" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH96" t="s">
         <v>228</v>
@@ -8329,10 +8326,10 @@
     </row>
     <row r="97" spans="1:35">
       <c r="A97">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
@@ -8344,22 +8341,22 @@
         <v>54</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G97">
-        <v>6223</v>
+        <v>6221</v>
       </c>
       <c r="H97">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="I97" t="s">
         <v>62</v>
       </c>
       <c r="J97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N97" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P97">
         <v>8</v>
@@ -8368,31 +8365,31 @@
         <v>2026</v>
       </c>
       <c r="R97">
-        <v>18260391</v>
+        <v>18214889</v>
       </c>
       <c r="S97" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T97" t="s">
         <v>140</v>
       </c>
       <c r="U97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V97" s="1">
-        <v>46267.71927280092</v>
+        <v>46267.79249788194</v>
       </c>
       <c r="W97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X97" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB97">
         <v>0</v>
       </c>
       <c r="AC97" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AH97" t="s">
         <v>228</v>
@@ -8403,22 +8400,22 @@
     </row>
     <row r="98" spans="1:35">
       <c r="A98">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C98" t="s">
         <v>50</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G98">
         <v>6223</v>
@@ -8433,7 +8430,7 @@
         <v>95</v>
       </c>
       <c r="N98" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P98">
         <v>8</v>
@@ -8442,28 +8439,31 @@
         <v>2026</v>
       </c>
       <c r="R98">
-        <v>18220215</v>
+        <v>18260391</v>
       </c>
       <c r="S98" t="s">
-        <v>142</v>
+        <v>139</v>
+      </c>
+      <c r="T98" t="s">
+        <v>140</v>
       </c>
       <c r="U98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V98" s="1">
-        <v>46267.79251079861</v>
+        <v>46267.71927280092</v>
       </c>
       <c r="W98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AB98">
         <v>0</v>
       </c>
       <c r="AC98" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AH98" t="s">
         <v>228</v>
@@ -8474,19 +8474,19 @@
     </row>
     <row r="99" spans="1:35">
       <c r="A99">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C99" t="s">
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F99" t="s">
         <v>57</v>
@@ -8513,31 +8513,28 @@
         <v>2026</v>
       </c>
       <c r="R99">
-        <v>18214895</v>
+        <v>18220215</v>
       </c>
       <c r="S99" t="s">
-        <v>141</v>
-      </c>
-      <c r="T99" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U99" t="s">
         <v>156</v>
       </c>
       <c r="V99" s="1">
-        <v>46267.79251038194</v>
+        <v>46267.79251079861</v>
       </c>
       <c r="W99">
         <v>1</v>
       </c>
       <c r="X99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB99">
         <v>0</v>
       </c>
       <c r="AC99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH99" t="s">
         <v>228</v>
@@ -8548,10 +8545,10 @@
     </row>
     <row r="100" spans="1:35">
       <c r="A100">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B100" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C100" t="s">
         <v>50</v>
@@ -8563,22 +8560,22 @@
         <v>54</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G100">
-        <v>11766</v>
+        <v>6223</v>
       </c>
       <c r="H100">
-        <v>11765</v>
+        <v>6222</v>
       </c>
       <c r="I100" t="s">
         <v>62</v>
       </c>
       <c r="J100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N100" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P100">
         <v>8</v>
@@ -8587,31 +8584,31 @@
         <v>2026</v>
       </c>
       <c r="R100">
-        <v>18260426</v>
+        <v>18214895</v>
       </c>
       <c r="S100" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T100" t="s">
         <v>140</v>
       </c>
       <c r="U100" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V100" s="1">
-        <v>46267.72044811342</v>
+        <v>46267.79251038194</v>
       </c>
       <c r="W100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X100" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB100">
         <v>0</v>
       </c>
       <c r="AC100" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH100" t="s">
         <v>228</v>
@@ -8622,10 +8619,10 @@
     </row>
     <row r="101" spans="1:35">
       <c r="A101">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C101" t="s">
         <v>50</v>
@@ -8634,7 +8631,7 @@
         <v>51</v>
       </c>
       <c r="E101" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F101" t="s">
         <v>56</v>
@@ -8652,7 +8649,7 @@
         <v>96</v>
       </c>
       <c r="N101" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P101">
         <v>8</v>
@@ -8661,25 +8658,25 @@
         <v>2026</v>
       </c>
       <c r="R101">
-        <v>18173159</v>
+        <v>18260426</v>
       </c>
       <c r="S101" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T101" t="s">
         <v>140</v>
       </c>
       <c r="U101" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V101" s="1">
-        <v>46267.79429737268</v>
+        <v>46267.72044811342</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X101" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB101">
         <v>0</v>
@@ -8696,16 +8693,16 @@
     </row>
     <row r="102" spans="1:35">
       <c r="A102">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C102" t="s">
         <v>50</v>
       </c>
       <c r="D102" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E102" t="s">
         <v>55</v>
@@ -8735,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="R102">
-        <v>18170410</v>
+        <v>18173159</v>
       </c>
       <c r="S102" t="s">
         <v>140</v>
@@ -8747,7 +8744,7 @@
         <v>156</v>
       </c>
       <c r="V102" s="1">
-        <v>46267.79429603009</v>
+        <v>46267.79429737268</v>
       </c>
       <c r="W102">
         <v>1</v>
@@ -8770,10 +8767,10 @@
     </row>
     <row r="103" spans="1:35">
       <c r="A103">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C103" t="s">
         <v>50</v>
@@ -8785,7 +8782,7 @@
         <v>55</v>
       </c>
       <c r="F103" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G103">
         <v>11766</v>
@@ -8809,22 +8806,25 @@
         <v>2026</v>
       </c>
       <c r="R103">
-        <v>18220275</v>
+        <v>18170410</v>
       </c>
       <c r="S103" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T103" t="s">
+        <v>140</v>
       </c>
       <c r="U103" t="s">
         <v>156</v>
       </c>
       <c r="V103" s="1">
-        <v>46267.79429876158</v>
+        <v>46267.79429603009</v>
       </c>
       <c r="W103">
         <v>1</v>
       </c>
       <c r="X103" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AB103">
         <v>0</v>
@@ -8841,19 +8841,19 @@
     </row>
     <row r="104" spans="1:35">
       <c r="A104">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C104" t="s">
         <v>50</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E104" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F104" t="s">
         <v>57</v>
@@ -8880,31 +8880,28 @@
         <v>2026</v>
       </c>
       <c r="R104">
-        <v>18214969</v>
+        <v>18220275</v>
       </c>
       <c r="S104" t="s">
-        <v>141</v>
-      </c>
-      <c r="T104" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U104" t="s">
         <v>156</v>
       </c>
       <c r="V104" s="1">
-        <v>46267.79429826389</v>
+        <v>46267.79429876158</v>
       </c>
       <c r="W104">
         <v>1</v>
       </c>
       <c r="X104" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB104">
         <v>0</v>
       </c>
       <c r="AC104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH104" t="s">
         <v>228</v>
@@ -8915,10 +8912,10 @@
     </row>
     <row r="105" spans="1:35">
       <c r="A105">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C105" t="s">
         <v>50</v>
@@ -8930,22 +8927,22 @@
         <v>54</v>
       </c>
       <c r="F105" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G105">
-        <v>11768</v>
+        <v>11766</v>
       </c>
       <c r="H105">
-        <v>11767</v>
+        <v>11765</v>
       </c>
       <c r="I105" t="s">
         <v>62</v>
       </c>
       <c r="J105" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N105" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="P105">
         <v>8</v>
@@ -8954,31 +8951,31 @@
         <v>2026</v>
       </c>
       <c r="R105">
-        <v>18260431</v>
+        <v>18214969</v>
       </c>
       <c r="S105" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T105" t="s">
         <v>140</v>
       </c>
       <c r="U105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V105" s="1">
-        <v>46267.72050385417</v>
+        <v>46267.79429826389</v>
       </c>
       <c r="W105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X105" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AB105">
         <v>0</v>
       </c>
       <c r="AC105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH105" t="s">
         <v>228</v>
@@ -8989,10 +8986,10 @@
     </row>
     <row r="106" spans="1:35">
       <c r="A106">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C106" t="s">
         <v>50</v>
@@ -9001,7 +8998,7 @@
         <v>51</v>
       </c>
       <c r="E106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F106" t="s">
         <v>56</v>
@@ -9019,7 +9016,7 @@
         <v>97</v>
       </c>
       <c r="N106" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="P106">
         <v>8</v>
@@ -9028,25 +9025,25 @@
         <v>2026</v>
       </c>
       <c r="R106">
-        <v>18173167</v>
+        <v>18260431</v>
       </c>
       <c r="S106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T106" t="s">
         <v>140</v>
       </c>
       <c r="U106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V106" s="1">
-        <v>46267.79434996528</v>
+        <v>46267.72050385417</v>
       </c>
       <c r="W106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB106">
         <v>0</v>
@@ -9063,16 +9060,16 @@
     </row>
     <row r="107" spans="1:35">
       <c r="A107">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C107" t="s">
         <v>50</v>
       </c>
       <c r="D107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E107" t="s">
         <v>55</v>
@@ -9102,7 +9099,7 @@
         <v>2026</v>
       </c>
       <c r="R107">
-        <v>18170418</v>
+        <v>18173167</v>
       </c>
       <c r="S107" t="s">
         <v>140</v>
@@ -9114,7 +9111,7 @@
         <v>156</v>
       </c>
       <c r="V107" s="1">
-        <v>46267.79434864583</v>
+        <v>46267.79434996528</v>
       </c>
       <c r="W107">
         <v>1</v>
@@ -9137,10 +9134,10 @@
     </row>
     <row r="108" spans="1:35">
       <c r="A108">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C108" t="s">
         <v>50</v>
@@ -9152,7 +9149,7 @@
         <v>55</v>
       </c>
       <c r="F108" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G108">
         <v>11768</v>
@@ -9176,22 +9173,25 @@
         <v>2026</v>
       </c>
       <c r="R108">
-        <v>18220281</v>
+        <v>18170418</v>
       </c>
       <c r="S108" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="T108" t="s">
+        <v>140</v>
       </c>
       <c r="U108" t="s">
         <v>156</v>
       </c>
       <c r="V108" s="1">
-        <v>46267.79435208334</v>
+        <v>46267.79434864583</v>
       </c>
       <c r="W108">
         <v>1</v>
       </c>
       <c r="X108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AB108">
         <v>0</v>
@@ -9208,19 +9208,19 @@
     </row>
     <row r="109" spans="1:35">
       <c r="A109">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B109" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C109" t="s">
         <v>50</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F109" t="s">
         <v>57</v>
@@ -9247,31 +9247,28 @@
         <v>2026</v>
       </c>
       <c r="R109">
-        <v>18214975</v>
+        <v>18220281</v>
       </c>
       <c r="S109" t="s">
-        <v>141</v>
-      </c>
-      <c r="T109" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U109" t="s">
         <v>156</v>
       </c>
       <c r="V109" s="1">
-        <v>46267.79435100695</v>
+        <v>46267.79435208334</v>
       </c>
       <c r="W109">
         <v>1</v>
       </c>
       <c r="X109" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB109">
         <v>0</v>
       </c>
       <c r="AC109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH109" t="s">
         <v>228</v>
@@ -9282,10 +9279,10 @@
     </row>
     <row r="110" spans="1:35">
       <c r="A110">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C110" t="s">
         <v>50</v>
@@ -9297,22 +9294,22 @@
         <v>54</v>
       </c>
       <c r="F110" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G110">
-        <v>6883</v>
+        <v>11768</v>
       </c>
       <c r="H110">
-        <v>1788</v>
+        <v>11767</v>
       </c>
       <c r="I110" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J110" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N110" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="P110">
         <v>8</v>
@@ -9321,31 +9318,31 @@
         <v>2026</v>
       </c>
       <c r="R110">
-        <v>17399250</v>
+        <v>18214975</v>
       </c>
       <c r="S110" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="T110" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="U110" t="s">
         <v>156</v>
       </c>
       <c r="V110" s="1">
-        <v>46266.37636392361</v>
+        <v>46267.79435100695</v>
       </c>
       <c r="W110">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="X110" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AB110">
         <v>0</v>
       </c>
       <c r="AC110" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AH110" t="s">
         <v>228</v>
@@ -9374,7 +9371,7 @@
         <v>56</v>
       </c>
       <c r="G111">
-        <v>1836</v>
+        <v>6883</v>
       </c>
       <c r="H111">
         <v>1788</v>
@@ -9383,10 +9380,10 @@
         <v>63</v>
       </c>
       <c r="J111" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="N111" s="1">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="P111">
         <v>8</v>
@@ -9395,7 +9392,7 @@
         <v>2026</v>
       </c>
       <c r="R111">
-        <v>17398975</v>
+        <v>17399250</v>
       </c>
       <c r="S111" t="s">
         <v>144</v>
@@ -9407,10 +9404,10 @@
         <v>156</v>
       </c>
       <c r="V111" s="1">
-        <v>46266.37598834491</v>
+        <v>46266.37636392361</v>
       </c>
       <c r="W111">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="X111" t="s">
         <v>164</v>
@@ -9430,10 +9427,10 @@
     </row>
     <row r="112" spans="1:35">
       <c r="A112">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C112" t="s">
         <v>50</v>
@@ -9462,9 +9459,6 @@
       <c r="N112" s="1">
         <v>46268</v>
       </c>
-      <c r="O112" t="s">
-        <v>120</v>
-      </c>
       <c r="P112">
         <v>8</v>
       </c>
@@ -9472,7 +9466,7 @@
         <v>2026</v>
       </c>
       <c r="R112">
-        <v>18155318</v>
+        <v>17398975</v>
       </c>
       <c r="S112" t="s">
         <v>144</v>
@@ -9481,19 +9475,16 @@
         <v>154</v>
       </c>
       <c r="U112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V112" s="1">
-        <v>46268.45899988426</v>
+        <v>46266.37598834491</v>
       </c>
       <c r="W112">
         <v>1</v>
       </c>
       <c r="X112" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y112" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="AB112">
         <v>0</v>
@@ -9510,10 +9501,10 @@
     </row>
     <row r="113" spans="1:35">
       <c r="A113">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B113" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C113" t="s">
         <v>50</v>
@@ -9542,6 +9533,9 @@
       <c r="N113" s="1">
         <v>46268</v>
       </c>
+      <c r="O113" t="s">
+        <v>120</v>
+      </c>
       <c r="P113">
         <v>8</v>
       </c>
@@ -9549,7 +9543,7 @@
         <v>2026</v>
       </c>
       <c r="R113">
-        <v>18085220</v>
+        <v>18155318</v>
       </c>
       <c r="S113" t="s">
         <v>144</v>
@@ -9558,16 +9552,19 @@
         <v>154</v>
       </c>
       <c r="U113" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V113" s="1">
-        <v>46266.45957881944</v>
+        <v>46268.45899988426</v>
       </c>
       <c r="W113">
         <v>1</v>
       </c>
       <c r="X113" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>195</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -9584,10 +9581,10 @@
     </row>
     <row r="114" spans="1:35">
       <c r="A114">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
         <v>50</v>
@@ -9602,7 +9599,7 @@
         <v>56</v>
       </c>
       <c r="G114">
-        <v>6802</v>
+        <v>1836</v>
       </c>
       <c r="H114">
         <v>1788</v>
@@ -9611,10 +9608,10 @@
         <v>63</v>
       </c>
       <c r="J114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N114" s="1">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="P114">
         <v>8</v>
@@ -9623,7 +9620,7 @@
         <v>2026</v>
       </c>
       <c r="R114">
-        <v>17399220</v>
+        <v>18085220</v>
       </c>
       <c r="S114" t="s">
         <v>144</v>
@@ -9635,13 +9632,13 @@
         <v>156</v>
       </c>
       <c r="V114" s="1">
-        <v>46266.37645462963</v>
+        <v>46266.45957881944</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB114">
         <v>0</v>
@@ -9676,16 +9673,16 @@
         <v>56</v>
       </c>
       <c r="G115">
-        <v>6801</v>
+        <v>6802</v>
       </c>
       <c r="H115">
-        <v>1796</v>
+        <v>1788</v>
       </c>
       <c r="I115" t="s">
         <v>63</v>
       </c>
       <c r="J115" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N115" s="1">
         <v>46269</v>
@@ -9697,7 +9694,7 @@
         <v>2026</v>
       </c>
       <c r="R115">
-        <v>17399210</v>
+        <v>17399220</v>
       </c>
       <c r="S115" t="s">
         <v>144</v>
@@ -9709,7 +9706,7 @@
         <v>156</v>
       </c>
       <c r="V115" s="1">
-        <v>46266.37649475694</v>
+        <v>46266.37645462963</v>
       </c>
       <c r="W115">
         <v>0</v>
@@ -9750,19 +9747,19 @@
         <v>56</v>
       </c>
       <c r="G116">
-        <v>6014</v>
+        <v>6801</v>
       </c>
       <c r="H116">
-        <v>1788</v>
+        <v>1796</v>
       </c>
       <c r="I116" t="s">
         <v>63</v>
       </c>
       <c r="J116" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N116" s="1">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="P116">
         <v>8</v>
@@ -9771,7 +9768,7 @@
         <v>2026</v>
       </c>
       <c r="R116">
-        <v>17399136</v>
+        <v>17399210</v>
       </c>
       <c r="S116" t="s">
         <v>144</v>
@@ -9783,10 +9780,10 @@
         <v>156</v>
       </c>
       <c r="V116" s="1">
-        <v>46266.37591180555</v>
+        <v>46266.37649475694</v>
       </c>
       <c r="W116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X116" t="s">
         <v>164</v>
@@ -9806,10 +9803,10 @@
     </row>
     <row r="117" spans="1:35">
       <c r="A117">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B117" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C117" t="s">
         <v>50</v>
@@ -9838,9 +9835,6 @@
       <c r="N117" s="1">
         <v>46268</v>
       </c>
-      <c r="O117" t="s">
-        <v>120</v>
-      </c>
       <c r="P117">
         <v>8</v>
       </c>
@@ -9848,7 +9842,7 @@
         <v>2026</v>
       </c>
       <c r="R117">
-        <v>18155327</v>
+        <v>17399136</v>
       </c>
       <c r="S117" t="s">
         <v>144</v>
@@ -9857,19 +9851,16 @@
         <v>154</v>
       </c>
       <c r="U117" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V117" s="1">
-        <v>46268.45896508102</v>
+        <v>46266.37591180555</v>
       </c>
       <c r="W117">
         <v>1</v>
       </c>
       <c r="X117" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="AB117">
         <v>0</v>
@@ -9886,10 +9877,10 @@
     </row>
     <row r="118" spans="1:35">
       <c r="A118">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B118" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C118" t="s">
         <v>50</v>
@@ -9918,6 +9909,9 @@
       <c r="N118" s="1">
         <v>46268</v>
       </c>
+      <c r="O118" t="s">
+        <v>120</v>
+      </c>
       <c r="P118">
         <v>8</v>
       </c>
@@ -9925,7 +9919,7 @@
         <v>2026</v>
       </c>
       <c r="R118">
-        <v>18085231</v>
+        <v>18155327</v>
       </c>
       <c r="S118" t="s">
         <v>144</v>
@@ -9934,16 +9928,19 @@
         <v>154</v>
       </c>
       <c r="U118" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V118" s="1">
-        <v>46266.45946195602</v>
+        <v>46268.45896508102</v>
       </c>
       <c r="W118">
         <v>1</v>
       </c>
       <c r="X118" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>195</v>
       </c>
       <c r="AB118">
         <v>0</v>
@@ -9960,10 +9957,10 @@
     </row>
     <row r="119" spans="1:35">
       <c r="A119">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B119" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C119" t="s">
         <v>50</v>
@@ -9978,16 +9975,16 @@
         <v>56</v>
       </c>
       <c r="G119">
-        <v>6233</v>
+        <v>6014</v>
       </c>
       <c r="H119">
-        <v>6232</v>
+        <v>1788</v>
       </c>
       <c r="I119" t="s">
         <v>63</v>
       </c>
       <c r="J119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N119" s="1">
         <v>46268</v>
@@ -9999,7 +9996,7 @@
         <v>2026</v>
       </c>
       <c r="R119">
-        <v>17399176</v>
+        <v>18085231</v>
       </c>
       <c r="S119" t="s">
         <v>144</v>
@@ -10011,13 +10008,13 @@
         <v>156</v>
       </c>
       <c r="V119" s="1">
-        <v>46266.37538684028</v>
+        <v>46266.45946195602</v>
       </c>
       <c r="W119">
         <v>1</v>
       </c>
       <c r="X119" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB119">
         <v>0</v>
@@ -10034,16 +10031,16 @@
     </row>
     <row r="120" spans="1:35">
       <c r="A120">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B120" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C120" t="s">
         <v>50</v>
       </c>
       <c r="D120" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E120" t="s">
         <v>54</v>
@@ -10073,7 +10070,7 @@
         <v>2026</v>
       </c>
       <c r="R120">
-        <v>16962294</v>
+        <v>17399176</v>
       </c>
       <c r="S120" t="s">
         <v>144</v>
@@ -10085,13 +10082,13 @@
         <v>156</v>
       </c>
       <c r="V120" s="1">
-        <v>46266.37538506944</v>
+        <v>46266.37538684028</v>
       </c>
       <c r="W120">
         <v>1</v>
       </c>
       <c r="X120" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AB120">
         <v>0</v>
@@ -10108,16 +10105,16 @@
     </row>
     <row r="121" spans="1:35">
       <c r="A121">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B121" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C121" t="s">
         <v>50</v>
       </c>
       <c r="D121" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E121" t="s">
         <v>54</v>
@@ -10140,9 +10137,6 @@
       <c r="N121" s="1">
         <v>46268</v>
       </c>
-      <c r="O121" t="s">
-        <v>120</v>
-      </c>
       <c r="P121">
         <v>8</v>
       </c>
@@ -10150,7 +10144,7 @@
         <v>2026</v>
       </c>
       <c r="R121">
-        <v>16976156</v>
+        <v>16962294</v>
       </c>
       <c r="S121" t="s">
         <v>144</v>
@@ -10159,19 +10153,16 @@
         <v>154</v>
       </c>
       <c r="U121" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V121" s="1">
-        <v>46268.45881820602</v>
+        <v>46266.37538506944</v>
       </c>
       <c r="W121">
         <v>1</v>
       </c>
       <c r="X121" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y121" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="AB121">
         <v>0</v>
@@ -10188,16 +10179,16 @@
     </row>
     <row r="122" spans="1:35">
       <c r="A122">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B122" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C122" t="s">
         <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E122" t="s">
         <v>54</v>
@@ -10220,6 +10211,9 @@
       <c r="N122" s="1">
         <v>46268</v>
       </c>
+      <c r="O122" t="s">
+        <v>120</v>
+      </c>
       <c r="P122">
         <v>8</v>
       </c>
@@ -10227,7 +10221,7 @@
         <v>2026</v>
       </c>
       <c r="R122">
-        <v>17948844</v>
+        <v>16976156</v>
       </c>
       <c r="S122" t="s">
         <v>144</v>
@@ -10236,16 +10230,19 @@
         <v>154</v>
       </c>
       <c r="U122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V122" s="1">
-        <v>46266.45895332176</v>
+        <v>46268.45881820602</v>
       </c>
       <c r="W122">
         <v>1</v>
       </c>
       <c r="X122" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>195</v>
       </c>
       <c r="AB122">
         <v>0</v>
@@ -10262,16 +10259,16 @@
     </row>
     <row r="123" spans="1:35">
       <c r="A123">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C123" t="s">
         <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E123" t="s">
         <v>54</v>
@@ -10301,7 +10298,7 @@
         <v>2026</v>
       </c>
       <c r="R123">
-        <v>18085264</v>
+        <v>17948844</v>
       </c>
       <c r="S123" t="s">
         <v>144</v>
@@ -10313,13 +10310,13 @@
         <v>156</v>
       </c>
       <c r="V123" s="1">
-        <v>46266.45874105324</v>
+        <v>46266.45895332176</v>
       </c>
       <c r="W123">
         <v>1</v>
       </c>
       <c r="X123" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AB123">
         <v>0</v>
@@ -10336,16 +10333,16 @@
     </row>
     <row r="124" spans="1:35">
       <c r="A124">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B124" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C124" t="s">
         <v>50</v>
       </c>
       <c r="D124" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E124" t="s">
         <v>54</v>
@@ -10375,7 +10372,7 @@
         <v>2026</v>
       </c>
       <c r="R124">
-        <v>17948989</v>
+        <v>18085264</v>
       </c>
       <c r="S124" t="s">
         <v>144</v>
@@ -10387,7 +10384,7 @@
         <v>156</v>
       </c>
       <c r="V124" s="1">
-        <v>46266.45873584491</v>
+        <v>46266.45874105324</v>
       </c>
       <c r="W124">
         <v>1</v>
@@ -10410,16 +10407,16 @@
     </row>
     <row r="125" spans="1:35">
       <c r="A125">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B125" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C125" t="s">
         <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E125" t="s">
         <v>54</v>
@@ -10428,22 +10425,19 @@
         <v>56</v>
       </c>
       <c r="G125">
-        <v>11359</v>
+        <v>6233</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>6232</v>
       </c>
       <c r="I125" t="s">
         <v>63</v>
       </c>
       <c r="J125" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N125" s="1">
-        <v>46267</v>
-      </c>
-      <c r="O125" t="s">
-        <v>120</v>
+        <v>46268</v>
       </c>
       <c r="P125">
         <v>8</v>
@@ -10452,7 +10446,7 @@
         <v>2026</v>
       </c>
       <c r="R125">
-        <v>18155345</v>
+        <v>17948989</v>
       </c>
       <c r="S125" t="s">
         <v>144</v>
@@ -10461,19 +10455,16 @@
         <v>154</v>
       </c>
       <c r="U125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V125" s="1">
-        <v>46268.45898549769</v>
+        <v>46266.45873584491</v>
       </c>
       <c r="W125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X125" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y125" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="AB125">
         <v>0</v>
@@ -10508,19 +10499,22 @@
         <v>56</v>
       </c>
       <c r="G126">
-        <v>6884</v>
+        <v>11359</v>
       </c>
       <c r="H126">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I126" t="s">
         <v>63</v>
       </c>
       <c r="J126" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N126" s="1">
-        <v>46273</v>
+        <v>46267</v>
+      </c>
+      <c r="O126" t="s">
+        <v>120</v>
       </c>
       <c r="P126">
         <v>8</v>
@@ -10529,7 +10523,7 @@
         <v>2026</v>
       </c>
       <c r="R126">
-        <v>16976207</v>
+        <v>18155345</v>
       </c>
       <c r="S126" t="s">
         <v>144</v>
@@ -10538,17 +10532,20 @@
         <v>154</v>
       </c>
       <c r="U126" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V126" s="1">
-        <v>46268.45915543981</v>
+        <v>46268.45898549769</v>
       </c>
       <c r="W126">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="X126" t="s">
         <v>165</v>
       </c>
+      <c r="Y126" t="s">
+        <v>196</v>
+      </c>
       <c r="AB126">
         <v>0</v>
       </c>
@@ -10564,16 +10561,16 @@
     </row>
     <row r="127" spans="1:35">
       <c r="A127">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B127" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C127" t="s">
         <v>50</v>
       </c>
       <c r="D127" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E127" t="s">
         <v>54</v>
@@ -10582,19 +10579,19 @@
         <v>56</v>
       </c>
       <c r="G127">
-        <v>11303</v>
+        <v>6884</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I127" t="s">
         <v>63</v>
       </c>
       <c r="J127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N127" s="1">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="P127">
         <v>8</v>
@@ -10603,7 +10600,7 @@
         <v>2026</v>
       </c>
       <c r="R127">
-        <v>17949079</v>
+        <v>16976207</v>
       </c>
       <c r="S127" t="s">
         <v>144</v>
@@ -10615,13 +10612,13 @@
         <v>156</v>
       </c>
       <c r="V127" s="1">
-        <v>46267.44505795139</v>
+        <v>46268.45915543981</v>
       </c>
       <c r="W127">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="X127" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AB127">
         <v>0</v>
@@ -10638,10 +10635,10 @@
     </row>
     <row r="128" spans="1:35">
       <c r="A128">
-        <v>6628</v>
+        <v>6705</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C128" t="s">
         <v>50</v>
@@ -10650,25 +10647,25 @@
         <v>52</v>
       </c>
       <c r="E128" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F128" t="s">
         <v>56</v>
       </c>
       <c r="G128">
-        <v>945</v>
+        <v>11303</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J128" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N128" s="1">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="P128">
         <v>8</v>
@@ -10677,34 +10674,34 @@
         <v>2026</v>
       </c>
       <c r="R128">
-        <v>16959938</v>
+        <v>17949079</v>
       </c>
       <c r="S128" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="T128" t="s">
+        <v>154</v>
       </c>
       <c r="U128" t="s">
         <v>156</v>
       </c>
       <c r="V128" s="1">
-        <v>46266.04180934028</v>
+        <v>46267.44505795139</v>
       </c>
       <c r="W128">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="X128" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y128" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="AB128">
         <v>0</v>
       </c>
       <c r="AC128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH128" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AI128" t="s">
         <v>231</v>
@@ -10712,10 +10709,10 @@
     </row>
     <row r="129" spans="1:35">
       <c r="A129">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
         <v>50</v>
@@ -10724,7 +10721,7 @@
         <v>52</v>
       </c>
       <c r="E129" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F129" t="s">
         <v>56</v>
@@ -10751,7 +10748,7 @@
         <v>2026</v>
       </c>
       <c r="R129">
-        <v>18056695</v>
+        <v>16959938</v>
       </c>
       <c r="S129" t="s">
         <v>145</v>
@@ -10760,16 +10757,16 @@
         <v>156</v>
       </c>
       <c r="V129" s="1">
-        <v>46266.08343295139</v>
+        <v>46266.04180934028</v>
       </c>
       <c r="W129">
         <v>-14</v>
       </c>
       <c r="X129" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y129" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AB129">
         <v>0</v>
@@ -10786,10 +10783,10 @@
     </row>
     <row r="130" spans="1:35">
       <c r="A130">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C130" t="s">
         <v>50</v>
@@ -10798,10 +10795,10 @@
         <v>52</v>
       </c>
       <c r="E130" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G130">
         <v>945</v>
@@ -10825,7 +10822,7 @@
         <v>2026</v>
       </c>
       <c r="R130">
-        <v>18164487</v>
+        <v>18056695</v>
       </c>
       <c r="S130" t="s">
         <v>145</v>
@@ -10834,16 +10831,16 @@
         <v>156</v>
       </c>
       <c r="V130" s="1">
-        <v>46266.08344398148</v>
+        <v>46266.08343295139</v>
       </c>
       <c r="W130">
         <v>-14</v>
       </c>
       <c r="X130" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y130" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AB130">
         <v>0</v>
@@ -10860,25 +10857,25 @@
     </row>
     <row r="131" spans="1:35">
       <c r="A131">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B131" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C131" t="s">
         <v>50</v>
       </c>
       <c r="D131" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E131" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G131">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -10887,7 +10884,7 @@
         <v>64</v>
       </c>
       <c r="J131" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N131" s="1">
         <v>46283</v>
@@ -10899,7 +10896,7 @@
         <v>2026</v>
       </c>
       <c r="R131">
-        <v>17398869</v>
+        <v>18164487</v>
       </c>
       <c r="S131" t="s">
         <v>145</v>
@@ -10908,16 +10905,16 @@
         <v>156</v>
       </c>
       <c r="V131" s="1">
-        <v>46266.25077376157</v>
+        <v>46266.08344398148</v>
       </c>
       <c r="W131">
         <v>-14</v>
       </c>
       <c r="X131" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Y131" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AB131">
         <v>0</v>
@@ -10934,16 +10931,16 @@
     </row>
     <row r="132" spans="1:35">
       <c r="A132">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B132" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C132" t="s">
         <v>50</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E132" t="s">
         <v>54</v>
@@ -10973,7 +10970,7 @@
         <v>2026</v>
       </c>
       <c r="R132">
-        <v>16962093</v>
+        <v>17398869</v>
       </c>
       <c r="S132" t="s">
         <v>145</v>
@@ -10982,16 +10979,16 @@
         <v>156</v>
       </c>
       <c r="V132" s="1">
-        <v>46266.25004302083</v>
+        <v>46266.25077376157</v>
       </c>
       <c r="W132">
         <v>-14</v>
       </c>
       <c r="X132" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y132" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AB132">
         <v>0</v>
@@ -11008,10 +11005,10 @@
     </row>
     <row r="133" spans="1:35">
       <c r="A133">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B133" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C133" t="s">
         <v>50</v>
@@ -11047,7 +11044,7 @@
         <v>2026</v>
       </c>
       <c r="R133">
-        <v>17941132</v>
+        <v>16962093</v>
       </c>
       <c r="S133" t="s">
         <v>145</v>
@@ -11056,16 +11053,16 @@
         <v>156</v>
       </c>
       <c r="V133" s="1">
-        <v>46266.25135543982</v>
+        <v>46266.25004302083</v>
       </c>
       <c r="W133">
         <v>-14</v>
       </c>
       <c r="X133" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Y133" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AB133">
         <v>0</v>
@@ -11100,7 +11097,7 @@
         <v>56</v>
       </c>
       <c r="G134">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -11109,10 +11106,10 @@
         <v>64</v>
       </c>
       <c r="J134" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N134" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P134">
         <v>8</v>
@@ -11121,7 +11118,7 @@
         <v>2026</v>
       </c>
       <c r="R134">
-        <v>17941146</v>
+        <v>17941132</v>
       </c>
       <c r="S134" t="s">
         <v>145</v>
@@ -11130,16 +11127,16 @@
         <v>156</v>
       </c>
       <c r="V134" s="1">
-        <v>46266.25232241898</v>
+        <v>46266.25135543982</v>
       </c>
       <c r="W134">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="X134" t="s">
         <v>167</v>
       </c>
       <c r="Y134" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB134">
         <v>0</v>
@@ -11156,22 +11153,22 @@
     </row>
     <row r="135" spans="1:35">
       <c r="A135">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B135" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C135" t="s">
         <v>50</v>
       </c>
       <c r="D135" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E135" t="s">
         <v>54</v>
       </c>
       <c r="F135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G135">
         <v>950</v>
@@ -11195,7 +11192,7 @@
         <v>2026</v>
       </c>
       <c r="R135">
-        <v>18178132</v>
+        <v>17941146</v>
       </c>
       <c r="S135" t="s">
         <v>145</v>
@@ -11204,16 +11201,16 @@
         <v>156</v>
       </c>
       <c r="V135" s="1">
-        <v>46266.25258784722</v>
+        <v>46266.25232241898</v>
       </c>
       <c r="W135">
         <v>-6</v>
       </c>
       <c r="X135" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Y135" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB135">
         <v>0</v>
@@ -11230,10 +11227,10 @@
     </row>
     <row r="136" spans="1:35">
       <c r="A136">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C136" t="s">
         <v>50</v>
@@ -11245,10 +11242,10 @@
         <v>54</v>
       </c>
       <c r="F136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G136">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -11257,7 +11254,7 @@
         <v>64</v>
       </c>
       <c r="J136" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N136" s="1">
         <v>46275</v>
@@ -11269,7 +11266,7 @@
         <v>2026</v>
       </c>
       <c r="R136">
-        <v>17222405</v>
+        <v>18178132</v>
       </c>
       <c r="S136" t="s">
         <v>145</v>
@@ -11278,16 +11275,16 @@
         <v>156</v>
       </c>
       <c r="V136" s="1">
-        <v>46266.25161940972</v>
+        <v>46266.25258784722</v>
       </c>
       <c r="W136">
         <v>-6</v>
       </c>
       <c r="X136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y136" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB136">
         <v>0</v>
@@ -11304,16 +11301,16 @@
     </row>
     <row r="137" spans="1:35">
       <c r="A137">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B137" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C137" t="s">
         <v>50</v>
       </c>
       <c r="D137" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E137" t="s">
         <v>54</v>
@@ -11343,7 +11340,7 @@
         <v>2026</v>
       </c>
       <c r="R137">
-        <v>17941156</v>
+        <v>17222405</v>
       </c>
       <c r="S137" t="s">
         <v>145</v>
@@ -11352,16 +11349,16 @@
         <v>156</v>
       </c>
       <c r="V137" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25161940972</v>
       </c>
       <c r="W137">
         <v>-6</v>
       </c>
       <c r="X137" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="Y137" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB137">
         <v>0</v>
@@ -11378,16 +11375,16 @@
     </row>
     <row r="138" spans="1:35">
       <c r="A138">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B138" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C138" t="s">
         <v>50</v>
       </c>
       <c r="D138" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E138" t="s">
         <v>54</v>
@@ -11417,7 +11414,7 @@
         <v>2026</v>
       </c>
       <c r="R138">
-        <v>18056705</v>
+        <v>17941156</v>
       </c>
       <c r="S138" t="s">
         <v>145</v>
@@ -11426,13 +11423,13 @@
         <v>156</v>
       </c>
       <c r="V138" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25232392361</v>
       </c>
       <c r="W138">
         <v>-6</v>
       </c>
       <c r="X138" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Y138" t="s">
         <v>206</v>
@@ -11452,10 +11449,10 @@
     </row>
     <row r="139" spans="1:35">
       <c r="A139">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B139" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C139" t="s">
         <v>50</v>
@@ -11464,10 +11461,10 @@
         <v>52</v>
       </c>
       <c r="E139" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G139">
         <v>951</v>
@@ -11491,7 +11488,7 @@
         <v>2026</v>
       </c>
       <c r="R139">
-        <v>18164501</v>
+        <v>18056705</v>
       </c>
       <c r="S139" t="s">
         <v>145</v>
@@ -11500,16 +11497,16 @@
         <v>156</v>
       </c>
       <c r="V139" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W139">
         <v>-6</v>
       </c>
       <c r="X139" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y139" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB139">
         <v>0</v>
@@ -11526,19 +11523,19 @@
     </row>
     <row r="140" spans="1:35">
       <c r="A140">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B140" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C140" t="s">
         <v>50</v>
       </c>
       <c r="D140" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E140" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F140" t="s">
         <v>57</v>
@@ -11565,7 +11562,7 @@
         <v>2026</v>
       </c>
       <c r="R140">
-        <v>18178138</v>
+        <v>18164501</v>
       </c>
       <c r="S140" t="s">
         <v>145</v>
@@ -11574,13 +11571,13 @@
         <v>156</v>
       </c>
       <c r="V140" s="1">
-        <v>46266.25259008102</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W140">
         <v>-6</v>
       </c>
       <c r="X140" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y140" t="s">
         <v>207</v>
@@ -11600,10 +11597,10 @@
     </row>
     <row r="141" spans="1:35">
       <c r="A141">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B141" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C141" t="s">
         <v>50</v>
@@ -11615,10 +11612,10 @@
         <v>54</v>
       </c>
       <c r="F141" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G141">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -11627,10 +11624,10 @@
         <v>64</v>
       </c>
       <c r="J141" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N141" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P141">
         <v>8</v>
@@ -11639,7 +11636,7 @@
         <v>2026</v>
       </c>
       <c r="R141">
-        <v>17398883</v>
+        <v>18178138</v>
       </c>
       <c r="S141" t="s">
         <v>145</v>
@@ -11648,16 +11645,16 @@
         <v>156</v>
       </c>
       <c r="V141" s="1">
-        <v>46266.25305</v>
+        <v>46266.25259008102</v>
       </c>
       <c r="W141">
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="X141" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Y141" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB141">
         <v>0</v>
@@ -11674,16 +11671,16 @@
     </row>
     <row r="142" spans="1:35">
       <c r="A142">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C142" t="s">
         <v>50</v>
       </c>
       <c r="D142" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E142" t="s">
         <v>54</v>
@@ -11713,7 +11710,7 @@
         <v>2026</v>
       </c>
       <c r="R142">
-        <v>16962107</v>
+        <v>17398883</v>
       </c>
       <c r="S142" t="s">
         <v>145</v>
@@ -11722,16 +11719,16 @@
         <v>156</v>
       </c>
       <c r="V142" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25305</v>
       </c>
       <c r="W142">
         <v>-21</v>
       </c>
       <c r="X142" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y142" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB142">
         <v>0</v>
@@ -11748,19 +11745,19 @@
     </row>
     <row r="143" spans="1:35">
       <c r="A143">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C143" t="s">
         <v>50</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E143" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F143" t="s">
         <v>56</v>
@@ -11787,7 +11784,7 @@
         <v>2026</v>
       </c>
       <c r="R143">
-        <v>17042317</v>
+        <v>16962107</v>
       </c>
       <c r="S143" t="s">
         <v>145</v>
@@ -11796,16 +11793,16 @@
         <v>156</v>
       </c>
       <c r="V143" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W143">
         <v>-21</v>
       </c>
       <c r="X143" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Y143" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB143">
         <v>0</v>
@@ -11822,19 +11819,19 @@
     </row>
     <row r="144" spans="1:35">
       <c r="A144">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B144" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C144" t="s">
         <v>50</v>
       </c>
       <c r="D144" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E144" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F144" t="s">
         <v>56</v>
@@ -11861,7 +11858,7 @@
         <v>2026</v>
       </c>
       <c r="R144">
-        <v>17941166</v>
+        <v>17042317</v>
       </c>
       <c r="S144" t="s">
         <v>145</v>
@@ -11870,16 +11867,16 @@
         <v>156</v>
       </c>
       <c r="V144" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W144">
         <v>-21</v>
       </c>
       <c r="X144" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Y144" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB144">
         <v>0</v>
@@ -11896,22 +11893,22 @@
     </row>
     <row r="145" spans="1:35">
       <c r="A145">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B145" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C145" t="s">
         <v>50</v>
       </c>
       <c r="D145" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E145" t="s">
         <v>54</v>
       </c>
       <c r="F145" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G145">
         <v>953</v>
@@ -11935,7 +11932,7 @@
         <v>2026</v>
       </c>
       <c r="R145">
-        <v>18178144</v>
+        <v>17941166</v>
       </c>
       <c r="S145" t="s">
         <v>145</v>
@@ -11944,16 +11941,16 @@
         <v>156</v>
       </c>
       <c r="V145" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W145">
         <v>-21</v>
       </c>
       <c r="X145" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Y145" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AB145">
         <v>0</v>
@@ -11970,10 +11967,10 @@
     </row>
     <row r="146" spans="1:35">
       <c r="A146">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B146" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C146" t="s">
         <v>50</v>
@@ -11985,10 +11982,10 @@
         <v>54</v>
       </c>
       <c r="F146" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G146">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -11997,10 +11994,10 @@
         <v>64</v>
       </c>
       <c r="J146" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N146" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P146">
         <v>8</v>
@@ -12009,7 +12006,7 @@
         <v>2026</v>
       </c>
       <c r="R146">
-        <v>17399270</v>
+        <v>18178144</v>
       </c>
       <c r="S146" t="s">
         <v>145</v>
@@ -12018,16 +12015,16 @@
         <v>156</v>
       </c>
       <c r="V146" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W146">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="X146" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Y146" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB146">
         <v>0</v>
@@ -12044,10 +12041,10 @@
     </row>
     <row r="147" spans="1:35">
       <c r="A147">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C147" t="s">
         <v>50</v>
@@ -12056,7 +12053,7 @@
         <v>51</v>
       </c>
       <c r="E147" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F147" t="s">
         <v>56</v>
@@ -12083,7 +12080,7 @@
         <v>2026</v>
       </c>
       <c r="R147">
-        <v>17042505</v>
+        <v>17399270</v>
       </c>
       <c r="S147" t="s">
         <v>145</v>
@@ -12092,16 +12089,16 @@
         <v>156</v>
       </c>
       <c r="V147" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W147">
         <v>-14</v>
       </c>
       <c r="X147" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Y147" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB147">
         <v>0</v>
@@ -12118,10 +12115,10 @@
     </row>
     <row r="148" spans="1:35">
       <c r="A148">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B148" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C148" t="s">
         <v>50</v>
@@ -12130,7 +12127,7 @@
         <v>51</v>
       </c>
       <c r="E148" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F148" t="s">
         <v>56</v>
@@ -12157,7 +12154,7 @@
         <v>2026</v>
       </c>
       <c r="R148">
-        <v>17952421</v>
+        <v>17042505</v>
       </c>
       <c r="S148" t="s">
         <v>145</v>
@@ -12166,16 +12163,16 @@
         <v>156</v>
       </c>
       <c r="V148" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W148">
         <v>-14</v>
       </c>
       <c r="X148" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y148" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB148">
         <v>0</v>
@@ -12192,10 +12189,10 @@
     </row>
     <row r="149" spans="1:35">
       <c r="A149">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B149" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C149" t="s">
         <v>50</v>
@@ -12207,7 +12204,7 @@
         <v>54</v>
       </c>
       <c r="F149" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G149">
         <v>7022</v>
@@ -12231,7 +12228,7 @@
         <v>2026</v>
       </c>
       <c r="R149">
-        <v>18178174</v>
+        <v>17952421</v>
       </c>
       <c r="S149" t="s">
         <v>145</v>
@@ -12240,16 +12237,16 @@
         <v>156</v>
       </c>
       <c r="V149" s="1">
-        <v>46266.25369988426</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W149">
         <v>-14</v>
       </c>
       <c r="X149" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y149" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB149">
         <v>0</v>
@@ -12266,10 +12263,10 @@
     </row>
     <row r="150" spans="1:35">
       <c r="A150">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C150" t="s">
         <v>50</v>
@@ -12281,10 +12278,10 @@
         <v>54</v>
       </c>
       <c r="F150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G150">
-        <v>9085</v>
+        <v>7022</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -12293,40 +12290,37 @@
         <v>64</v>
       </c>
       <c r="J150" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N150" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O150" t="s">
-        <v>120</v>
+        <v>46283</v>
       </c>
       <c r="P150">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q150">
         <v>2026</v>
       </c>
       <c r="R150">
-        <v>17399353</v>
+        <v>18178174</v>
       </c>
       <c r="S150" t="s">
         <v>145</v>
       </c>
       <c r="U150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V150" s="1">
-        <v>46268.62318445602</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W150">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="X150" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Y150" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB150">
         <v>0</v>
@@ -12335,7 +12329,7 @@
         <v>145</v>
       </c>
       <c r="AH150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AI150" t="s">
         <v>231</v>
@@ -12343,16 +12337,16 @@
     </row>
     <row r="151" spans="1:35">
       <c r="A151">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B151" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C151" t="s">
         <v>50</v>
       </c>
       <c r="D151" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E151" t="s">
         <v>54</v>
@@ -12385,7 +12379,7 @@
         <v>2026</v>
       </c>
       <c r="R151">
-        <v>16962370</v>
+        <v>17399353</v>
       </c>
       <c r="S151" t="s">
         <v>145</v>
@@ -12394,16 +12388,16 @@
         <v>157</v>
       </c>
       <c r="V151" s="1">
-        <v>46268.62319864584</v>
+        <v>46268.62318445602</v>
       </c>
       <c r="W151">
         <v>1</v>
       </c>
       <c r="X151" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y151" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AB151">
         <v>0</v>
@@ -12420,16 +12414,16 @@
     </row>
     <row r="152" spans="1:35">
       <c r="A152">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C152" t="s">
         <v>50</v>
       </c>
       <c r="D152" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E152" t="s">
         <v>54</v>
@@ -12462,7 +12456,7 @@
         <v>2026</v>
       </c>
       <c r="R152">
-        <v>16976260</v>
+        <v>16962370</v>
       </c>
       <c r="S152" t="s">
         <v>145</v>
@@ -12471,13 +12465,13 @@
         <v>157</v>
       </c>
       <c r="V152" s="1">
-        <v>46268.62320026621</v>
+        <v>46268.62319864584</v>
       </c>
       <c r="W152">
         <v>1</v>
       </c>
       <c r="X152" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Y152" t="s">
         <v>218</v>
@@ -12497,10 +12491,10 @@
     </row>
     <row r="153" spans="1:35">
       <c r="A153">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B153" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C153" t="s">
         <v>50</v>
@@ -12539,7 +12533,7 @@
         <v>2026</v>
       </c>
       <c r="R153">
-        <v>17222852</v>
+        <v>16976260</v>
       </c>
       <c r="S153" t="s">
         <v>145</v>
@@ -12548,13 +12542,13 @@
         <v>157</v>
       </c>
       <c r="V153" s="1">
-        <v>46268.62320177083</v>
+        <v>46268.62320026621</v>
       </c>
       <c r="W153">
         <v>1</v>
       </c>
       <c r="X153" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="Y153" t="s">
         <v>218</v>
@@ -12574,10 +12568,10 @@
     </row>
     <row r="154" spans="1:35">
       <c r="A154">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C154" t="s">
         <v>50</v>
@@ -12586,7 +12580,7 @@
         <v>51</v>
       </c>
       <c r="E154" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F154" t="s">
         <v>56</v>
@@ -12616,7 +12610,7 @@
         <v>2026</v>
       </c>
       <c r="R154">
-        <v>17042569</v>
+        <v>17222852</v>
       </c>
       <c r="S154" t="s">
         <v>145</v>
@@ -12625,13 +12619,13 @@
         <v>157</v>
       </c>
       <c r="V154" s="1">
-        <v>46268.62320378472</v>
+        <v>46268.62320177083</v>
       </c>
       <c r="W154">
         <v>1</v>
       </c>
       <c r="X154" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y154" t="s">
         <v>218</v>
@@ -12651,16 +12645,16 @@
     </row>
     <row r="155" spans="1:35">
       <c r="A155">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B155" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C155" t="s">
         <v>50</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E155" t="s">
         <v>55</v>
@@ -12693,7 +12687,7 @@
         <v>2026</v>
       </c>
       <c r="R155">
-        <v>16960062</v>
+        <v>17042569</v>
       </c>
       <c r="S155" t="s">
         <v>145</v>
@@ -12702,7 +12696,7 @@
         <v>157</v>
       </c>
       <c r="V155" s="1">
-        <v>46268.62320393518</v>
+        <v>46268.62320378472</v>
       </c>
       <c r="W155">
         <v>1</v>
@@ -12728,19 +12722,19 @@
     </row>
     <row r="156" spans="1:35">
       <c r="A156">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B156" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C156" t="s">
         <v>50</v>
       </c>
       <c r="D156" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E156" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F156" t="s">
         <v>56</v>
@@ -12770,7 +12764,7 @@
         <v>2026</v>
       </c>
       <c r="R156">
-        <v>17941207</v>
+        <v>16960062</v>
       </c>
       <c r="S156" t="s">
         <v>145</v>
@@ -12779,13 +12773,13 @@
         <v>157</v>
       </c>
       <c r="V156" s="1">
-        <v>46268.62320697917</v>
+        <v>46268.62320393518</v>
       </c>
       <c r="W156">
         <v>1</v>
       </c>
       <c r="X156" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Y156" t="s">
         <v>218</v>
@@ -12805,16 +12799,16 @@
     </row>
     <row r="157" spans="1:35">
       <c r="A157">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B157" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C157" t="s">
         <v>50</v>
       </c>
       <c r="D157" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E157" t="s">
         <v>54</v>
@@ -12847,7 +12841,7 @@
         <v>2026</v>
       </c>
       <c r="R157">
-        <v>17952433</v>
+        <v>17941207</v>
       </c>
       <c r="S157" t="s">
         <v>145</v>
@@ -12856,13 +12850,13 @@
         <v>157</v>
       </c>
       <c r="V157" s="1">
-        <v>46268.62320717592</v>
+        <v>46268.62320697917</v>
       </c>
       <c r="W157">
         <v>1</v>
       </c>
       <c r="X157" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Y157" t="s">
         <v>218</v>
@@ -12882,16 +12876,16 @@
     </row>
     <row r="158" spans="1:35">
       <c r="A158">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B158" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C158" t="s">
         <v>50</v>
       </c>
       <c r="D158" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E158" t="s">
         <v>54</v>
@@ -12924,7 +12918,7 @@
         <v>2026</v>
       </c>
       <c r="R158">
-        <v>17952613</v>
+        <v>17952433</v>
       </c>
       <c r="S158" t="s">
         <v>145</v>
@@ -12933,7 +12927,7 @@
         <v>157</v>
       </c>
       <c r="V158" s="1">
-        <v>46268.62320732639</v>
+        <v>46268.62320717592</v>
       </c>
       <c r="W158">
         <v>1</v>
@@ -12959,10 +12953,10 @@
     </row>
     <row r="159" spans="1:35">
       <c r="A159">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B159" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C159" t="s">
         <v>50</v>
@@ -13001,7 +12995,7 @@
         <v>2026</v>
       </c>
       <c r="R159">
-        <v>18056791</v>
+        <v>17952613</v>
       </c>
       <c r="S159" t="s">
         <v>145</v>
@@ -13010,7 +13004,7 @@
         <v>157</v>
       </c>
       <c r="V159" s="1">
-        <v>46268.62320810185</v>
+        <v>46268.62320732639</v>
       </c>
       <c r="W159">
         <v>1</v>
@@ -13036,10 +13030,10 @@
     </row>
     <row r="160" spans="1:35">
       <c r="A160">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B160" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C160" t="s">
         <v>50</v>
@@ -13048,10 +13042,10 @@
         <v>52</v>
       </c>
       <c r="E160" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F160" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G160">
         <v>9085</v>
@@ -13078,7 +13072,7 @@
         <v>2026</v>
       </c>
       <c r="R160">
-        <v>18164544</v>
+        <v>18056791</v>
       </c>
       <c r="S160" t="s">
         <v>145</v>
@@ -13087,13 +13081,13 @@
         <v>157</v>
       </c>
       <c r="V160" s="1">
-        <v>46268.6232125</v>
+        <v>46268.62320810185</v>
       </c>
       <c r="W160">
         <v>1</v>
       </c>
       <c r="X160" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y160" t="s">
         <v>218</v>
@@ -13113,19 +13107,19 @@
     </row>
     <row r="161" spans="1:35">
       <c r="A161">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B161" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C161" t="s">
         <v>50</v>
       </c>
       <c r="D161" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E161" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F161" t="s">
         <v>57</v>
@@ -13155,7 +13149,7 @@
         <v>2026</v>
       </c>
       <c r="R161">
-        <v>18178181</v>
+        <v>18164544</v>
       </c>
       <c r="S161" t="s">
         <v>145</v>
@@ -13164,13 +13158,13 @@
         <v>157</v>
       </c>
       <c r="V161" s="1">
-        <v>46268.62321412037</v>
+        <v>46268.6232125</v>
       </c>
       <c r="W161">
         <v>1</v>
       </c>
       <c r="X161" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y161" t="s">
         <v>218</v>
@@ -13190,16 +13184,16 @@
     </row>
     <row r="162" spans="1:35">
       <c r="A162">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C162" t="s">
         <v>50</v>
       </c>
       <c r="D162" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E162" t="s">
         <v>54</v>
@@ -13232,7 +13226,7 @@
         <v>2026</v>
       </c>
       <c r="R162">
-        <v>18188767</v>
+        <v>18178181</v>
       </c>
       <c r="S162" t="s">
         <v>145</v>
@@ -13241,13 +13235,13 @@
         <v>157</v>
       </c>
       <c r="V162" s="1">
-        <v>46268.6232128125</v>
+        <v>46268.62321412037</v>
       </c>
       <c r="W162">
         <v>1</v>
       </c>
       <c r="X162" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Y162" t="s">
         <v>218</v>
@@ -13267,10 +13261,10 @@
     </row>
     <row r="163" spans="1:35">
       <c r="A163">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B163" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C163" t="s">
         <v>50</v>
@@ -13309,7 +13303,7 @@
         <v>2026</v>
       </c>
       <c r="R163">
-        <v>18188673</v>
+        <v>18188767</v>
       </c>
       <c r="S163" t="s">
         <v>145</v>
@@ -13318,7 +13312,7 @@
         <v>157</v>
       </c>
       <c r="V163" s="1">
-        <v>46268.62321296296</v>
+        <v>46268.6232128125</v>
       </c>
       <c r="W163">
         <v>1</v>
@@ -13344,25 +13338,25 @@
     </row>
     <row r="164" spans="1:35">
       <c r="A164">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B164" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C164" t="s">
         <v>50</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E164" t="s">
         <v>54</v>
       </c>
       <c r="F164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G164">
-        <v>5989</v>
+        <v>9085</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -13371,10 +13365,13 @@
         <v>64</v>
       </c>
       <c r="J164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N164" s="1">
-        <v>46273</v>
+        <v>46268</v>
+      </c>
+      <c r="O164" t="s">
+        <v>120</v>
       </c>
       <c r="P164">
         <v>9</v>
@@ -13383,22 +13380,25 @@
         <v>2026</v>
       </c>
       <c r="R164">
-        <v>17399127</v>
+        <v>18188673</v>
       </c>
       <c r="S164" t="s">
         <v>145</v>
       </c>
       <c r="U164" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V164" s="1">
-        <v>46269.41908927084</v>
+        <v>46268.62321296296</v>
       </c>
       <c r="W164">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="X164" t="s">
-        <v>164</v>
+        <v>162</v>
+      </c>
+      <c r="Y164" t="s">
+        <v>218</v>
       </c>
       <c r="AB164">
         <v>0</v>
@@ -13415,16 +13415,16 @@
     </row>
     <row r="165" spans="1:35">
       <c r="A165">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B165" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C165" t="s">
         <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E165" t="s">
         <v>54</v>
@@ -13454,7 +13454,7 @@
         <v>2026</v>
       </c>
       <c r="R165">
-        <v>16962251</v>
+        <v>17399127</v>
       </c>
       <c r="S165" t="s">
         <v>145</v>
@@ -13463,13 +13463,13 @@
         <v>156</v>
       </c>
       <c r="V165" s="1">
-        <v>46269.41910457176</v>
+        <v>46269.41908927084</v>
       </c>
       <c r="W165">
         <v>-4</v>
       </c>
       <c r="X165" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AB165">
         <v>0</v>
@@ -13486,16 +13486,16 @@
     </row>
     <row r="166" spans="1:35">
       <c r="A166">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C166" t="s">
         <v>50</v>
       </c>
       <c r="D166" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E166" t="s">
         <v>54</v>
@@ -13525,7 +13525,7 @@
         <v>2026</v>
       </c>
       <c r="R166">
-        <v>16976117</v>
+        <v>16962251</v>
       </c>
       <c r="S166" t="s">
         <v>145</v>
@@ -13534,13 +13534,13 @@
         <v>156</v>
       </c>
       <c r="V166" s="1">
-        <v>46269.37885223379</v>
+        <v>46269.41910457176</v>
       </c>
       <c r="W166">
         <v>-4</v>
       </c>
       <c r="X166" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AB166">
         <v>0</v>
@@ -13557,10 +13557,10 @@
     </row>
     <row r="167" spans="1:35">
       <c r="A167">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C167" t="s">
         <v>50</v>
@@ -13596,7 +13596,7 @@
         <v>2026</v>
       </c>
       <c r="R167">
-        <v>17222714</v>
+        <v>16976117</v>
       </c>
       <c r="S167" t="s">
         <v>145</v>
@@ -13605,13 +13605,13 @@
         <v>156</v>
       </c>
       <c r="V167" s="1">
-        <v>46269.3782503125</v>
+        <v>46269.37885223379</v>
       </c>
       <c r="W167">
         <v>-4</v>
       </c>
       <c r="X167" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AB167">
         <v>0</v>
@@ -13628,10 +13628,10 @@
     </row>
     <row r="168" spans="1:35">
       <c r="A168">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B168" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C168" t="s">
         <v>50</v>
@@ -13640,7 +13640,7 @@
         <v>51</v>
       </c>
       <c r="E168" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F168" t="s">
         <v>56</v>
@@ -13667,7 +13667,7 @@
         <v>2026</v>
       </c>
       <c r="R168">
-        <v>17042423</v>
+        <v>17222714</v>
       </c>
       <c r="S168" t="s">
         <v>145</v>
@@ -13676,13 +13676,13 @@
         <v>156</v>
       </c>
       <c r="V168" s="1">
-        <v>46269.41913152778</v>
+        <v>46269.3782503125</v>
       </c>
       <c r="W168">
         <v>-4</v>
       </c>
       <c r="X168" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB168">
         <v>0</v>
@@ -13699,16 +13699,16 @@
     </row>
     <row r="169" spans="1:35">
       <c r="A169">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B169" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C169" t="s">
         <v>50</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E169" t="s">
         <v>55</v>
@@ -13738,7 +13738,7 @@
         <v>2026</v>
       </c>
       <c r="R169">
-        <v>16959989</v>
+        <v>17042423</v>
       </c>
       <c r="S169" t="s">
         <v>145</v>
@@ -13747,7 +13747,7 @@
         <v>156</v>
       </c>
       <c r="V169" s="1">
-        <v>46269.41913775463</v>
+        <v>46269.41913152778</v>
       </c>
       <c r="W169">
         <v>-4</v>
@@ -13770,37 +13770,37 @@
     </row>
     <row r="170" spans="1:35">
       <c r="A170">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B170" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C170" t="s">
         <v>50</v>
       </c>
       <c r="D170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E170" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F170" t="s">
         <v>56</v>
       </c>
       <c r="G170">
-        <v>9087</v>
+        <v>5989</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J170" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N170" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="P170">
         <v>9</v>
@@ -13809,28 +13809,28 @@
         <v>2026</v>
       </c>
       <c r="R170">
-        <v>17399373</v>
+        <v>16959989</v>
       </c>
       <c r="S170" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="U170" t="s">
         <v>156</v>
       </c>
       <c r="V170" s="1">
-        <v>46268.7596207176</v>
+        <v>46269.41913775463</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="X170" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AB170">
         <v>0</v>
       </c>
       <c r="AC170" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="AH170" t="s">
         <v>230</v>
@@ -13841,16 +13841,16 @@
     </row>
     <row r="171" spans="1:35">
       <c r="A171">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B171" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C171" t="s">
         <v>50</v>
       </c>
       <c r="D171" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E171" t="s">
         <v>54</v>
@@ -13880,7 +13880,7 @@
         <v>2026</v>
       </c>
       <c r="R171">
-        <v>16962390</v>
+        <v>17399373</v>
       </c>
       <c r="S171" t="s">
         <v>54</v>
@@ -13889,13 +13889,13 @@
         <v>156</v>
       </c>
       <c r="V171" s="1">
-        <v>46268.75963109954</v>
+        <v>46268.7596207176</v>
       </c>
       <c r="W171">
         <v>0</v>
       </c>
       <c r="X171" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AB171">
         <v>0</v>
@@ -13912,16 +13912,16 @@
     </row>
     <row r="172" spans="1:35">
       <c r="A172">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B172" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C172" t="s">
         <v>50</v>
       </c>
       <c r="D172" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E172" t="s">
         <v>54</v>
@@ -13951,7 +13951,7 @@
         <v>2026</v>
       </c>
       <c r="R172">
-        <v>16976280</v>
+        <v>16962390</v>
       </c>
       <c r="S172" t="s">
         <v>54</v>
@@ -13960,13 +13960,13 @@
         <v>156</v>
       </c>
       <c r="V172" s="1">
-        <v>46268.75963225694</v>
+        <v>46268.75963109954</v>
       </c>
       <c r="W172">
         <v>0</v>
       </c>
       <c r="X172" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AB172">
         <v>0</v>
@@ -13983,10 +13983,10 @@
     </row>
     <row r="173" spans="1:35">
       <c r="A173">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B173" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C173" t="s">
         <v>50</v>
@@ -14022,7 +14022,7 @@
         <v>2026</v>
       </c>
       <c r="R173">
-        <v>17222885</v>
+        <v>16976280</v>
       </c>
       <c r="S173" t="s">
         <v>54</v>
@@ -14031,13 +14031,13 @@
         <v>156</v>
       </c>
       <c r="V173" s="1">
-        <v>46268.75963348379</v>
+        <v>46268.75963225694</v>
       </c>
       <c r="W173">
         <v>0</v>
       </c>
       <c r="X173" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AB173">
         <v>0</v>
@@ -14054,10 +14054,10 @@
     </row>
     <row r="174" spans="1:35">
       <c r="A174">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B174" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C174" t="s">
         <v>50</v>
@@ -14066,7 +14066,7 @@
         <v>51</v>
       </c>
       <c r="E174" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F174" t="s">
         <v>56</v>
@@ -14093,28 +14093,28 @@
         <v>2026</v>
       </c>
       <c r="R174">
-        <v>17042605</v>
+        <v>17222885</v>
       </c>
       <c r="S174" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="U174" t="s">
         <v>156</v>
       </c>
       <c r="V174" s="1">
-        <v>46268.75963414352</v>
+        <v>46268.75963348379</v>
       </c>
       <c r="W174">
         <v>0</v>
       </c>
       <c r="X174" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB174">
         <v>0</v>
       </c>
       <c r="AC174" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="AH174" t="s">
         <v>230</v>
@@ -14125,16 +14125,16 @@
     </row>
     <row r="175" spans="1:35">
       <c r="A175">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B175" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C175" t="s">
         <v>50</v>
       </c>
       <c r="D175" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E175" t="s">
         <v>55</v>
@@ -14164,16 +14164,16 @@
         <v>2026</v>
       </c>
       <c r="R175">
-        <v>16960086</v>
+        <v>17042605</v>
       </c>
       <c r="S175" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="U175" t="s">
         <v>156</v>
       </c>
       <c r="V175" s="1">
-        <v>46268.62326365741</v>
+        <v>46268.75963414352</v>
       </c>
       <c r="W175">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>0</v>
       </c>
       <c r="AC175" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="AH175" t="s">
         <v>230</v>
@@ -14196,19 +14196,19 @@
     </row>
     <row r="176" spans="1:35">
       <c r="A176">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B176" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C176" t="s">
         <v>50</v>
       </c>
       <c r="D176" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E176" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F176" t="s">
         <v>56</v>
@@ -14235,28 +14235,28 @@
         <v>2026</v>
       </c>
       <c r="R176">
-        <v>17941227</v>
+        <v>16960086</v>
       </c>
       <c r="S176" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U176" t="s">
         <v>156</v>
       </c>
       <c r="V176" s="1">
-        <v>46268.75963472222</v>
+        <v>46268.62326365741</v>
       </c>
       <c r="W176">
         <v>0</v>
       </c>
       <c r="X176" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AB176">
         <v>0</v>
       </c>
       <c r="AC176" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH176" t="s">
         <v>230</v>
@@ -14267,16 +14267,16 @@
     </row>
     <row r="177" spans="1:35">
       <c r="A177">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B177" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C177" t="s">
         <v>50</v>
       </c>
       <c r="D177" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E177" t="s">
         <v>54</v>
@@ -14306,7 +14306,7 @@
         <v>2026</v>
       </c>
       <c r="R177">
-        <v>17952455</v>
+        <v>17941227</v>
       </c>
       <c r="S177" t="s">
         <v>54</v>
@@ -14315,13 +14315,13 @@
         <v>156</v>
       </c>
       <c r="V177" s="1">
-        <v>46268.75963475694</v>
+        <v>46268.75963472222</v>
       </c>
       <c r="W177">
         <v>0</v>
       </c>
       <c r="X177" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AB177">
         <v>0</v>
@@ -14338,16 +14338,16 @@
     </row>
     <row r="178" spans="1:35">
       <c r="A178">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B178" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C178" t="s">
         <v>50</v>
       </c>
       <c r="D178" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E178" t="s">
         <v>54</v>
@@ -14377,7 +14377,7 @@
         <v>2026</v>
       </c>
       <c r="R178">
-        <v>17952635</v>
+        <v>17952455</v>
       </c>
       <c r="S178" t="s">
         <v>54</v>
@@ -14386,7 +14386,7 @@
         <v>156</v>
       </c>
       <c r="V178" s="1">
-        <v>46268.75963506944</v>
+        <v>46268.75963475694</v>
       </c>
       <c r="W178">
         <v>0</v>
@@ -14409,10 +14409,10 @@
     </row>
     <row r="179" spans="1:35">
       <c r="A179">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B179" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C179" t="s">
         <v>50</v>
@@ -14448,16 +14448,16 @@
         <v>2026</v>
       </c>
       <c r="R179">
-        <v>18056811</v>
+        <v>17952635</v>
       </c>
       <c r="S179" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="U179" t="s">
         <v>156</v>
       </c>
       <c r="V179" s="1">
-        <v>46268.7596360301</v>
+        <v>46268.75963506944</v>
       </c>
       <c r="W179">
         <v>0</v>
@@ -14469,7 +14469,7 @@
         <v>0</v>
       </c>
       <c r="AC179" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="AH179" t="s">
         <v>230</v>
@@ -14480,10 +14480,10 @@
     </row>
     <row r="180" spans="1:35">
       <c r="A180">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B180" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C180" t="s">
         <v>50</v>
@@ -14492,10 +14492,10 @@
         <v>52</v>
       </c>
       <c r="E180" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F180" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G180">
         <v>9087</v>
@@ -14519,28 +14519,28 @@
         <v>2026</v>
       </c>
       <c r="R180">
-        <v>18164558</v>
+        <v>18056811</v>
       </c>
       <c r="S180" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="U180" t="s">
         <v>156</v>
       </c>
       <c r="V180" s="1">
-        <v>46268.62327121528</v>
+        <v>46268.7596360301</v>
       </c>
       <c r="W180">
         <v>0</v>
       </c>
       <c r="X180" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AB180">
         <v>0</v>
       </c>
       <c r="AC180" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="AH180" t="s">
         <v>230</v>
@@ -14551,19 +14551,19 @@
     </row>
     <row r="181" spans="1:35">
       <c r="A181">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B181" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C181" t="s">
         <v>50</v>
       </c>
       <c r="D181" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E181" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F181" t="s">
         <v>57</v>
@@ -14590,28 +14590,28 @@
         <v>2026</v>
       </c>
       <c r="R181">
-        <v>18178193</v>
+        <v>18164558</v>
       </c>
       <c r="S181" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="U181" t="s">
         <v>156</v>
       </c>
       <c r="V181" s="1">
-        <v>46268.75963931713</v>
+        <v>46268.62327121528</v>
       </c>
       <c r="W181">
         <v>0</v>
       </c>
       <c r="X181" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB181">
         <v>0</v>
       </c>
       <c r="AC181" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="AH181" t="s">
         <v>230</v>
@@ -14622,16 +14622,16 @@
     </row>
     <row r="182" spans="1:35">
       <c r="A182">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C182" t="s">
         <v>50</v>
       </c>
       <c r="D182" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E182" t="s">
         <v>54</v>
@@ -14661,28 +14661,28 @@
         <v>2026</v>
       </c>
       <c r="R182">
-        <v>18188781</v>
+        <v>18178193</v>
       </c>
       <c r="S182" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="U182" t="s">
         <v>156</v>
       </c>
       <c r="V182" s="1">
-        <v>46268.75963822917</v>
+        <v>46268.75963931713</v>
       </c>
       <c r="W182">
         <v>0</v>
       </c>
       <c r="X182" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AB182">
         <v>0</v>
       </c>
       <c r="AC182" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="AH182" t="s">
         <v>230</v>
@@ -14693,10 +14693,10 @@
     </row>
     <row r="183" spans="1:35">
       <c r="A183">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B183" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C183" t="s">
         <v>50</v>
@@ -14732,7 +14732,7 @@
         <v>2026</v>
       </c>
       <c r="R183">
-        <v>18188687</v>
+        <v>18188781</v>
       </c>
       <c r="S183" t="s">
         <v>54</v>
@@ -14741,7 +14741,7 @@
         <v>156</v>
       </c>
       <c r="V183" s="1">
-        <v>46268.75963857639</v>
+        <v>46268.75963822917</v>
       </c>
       <c r="W183">
         <v>0</v>
@@ -14764,25 +14764,25 @@
     </row>
     <row r="184" spans="1:35">
       <c r="A184">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B184" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C184" t="s">
         <v>50</v>
       </c>
       <c r="D184" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E184" t="s">
         <v>54</v>
       </c>
       <c r="F184" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G184">
-        <v>6215</v>
+        <v>9087</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -14791,10 +14791,10 @@
         <v>65</v>
       </c>
       <c r="J184" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N184" s="1">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="P184">
         <v>9</v>
@@ -14803,7 +14803,7 @@
         <v>2026</v>
       </c>
       <c r="R184">
-        <v>17399147</v>
+        <v>18188687</v>
       </c>
       <c r="S184" t="s">
         <v>54</v>
@@ -14812,13 +14812,13 @@
         <v>156</v>
       </c>
       <c r="V184" s="1">
-        <v>46269.41908901621</v>
+        <v>46268.75963857639</v>
       </c>
       <c r="W184">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X184" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AB184">
         <v>0</v>
@@ -14835,16 +14835,16 @@
     </row>
     <row r="185" spans="1:35">
       <c r="A185">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B185" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
       </c>
       <c r="D185" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E185" t="s">
         <v>54</v>
@@ -14874,7 +14874,7 @@
         <v>2026</v>
       </c>
       <c r="R185">
-        <v>16962265</v>
+        <v>17399147</v>
       </c>
       <c r="S185" t="s">
         <v>54</v>
@@ -14883,13 +14883,13 @@
         <v>156</v>
       </c>
       <c r="V185" s="1">
-        <v>46269.41910425926</v>
+        <v>46269.41908901621</v>
       </c>
       <c r="W185">
         <v>-5</v>
       </c>
       <c r="X185" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AB185">
         <v>0</v>
@@ -14906,16 +14906,16 @@
     </row>
     <row r="186" spans="1:35">
       <c r="A186">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B186" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C186" t="s">
         <v>50</v>
       </c>
       <c r="D186" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E186" t="s">
         <v>54</v>
@@ -14945,7 +14945,7 @@
         <v>2026</v>
       </c>
       <c r="R186">
-        <v>16976127</v>
+        <v>16962265</v>
       </c>
       <c r="S186" t="s">
         <v>54</v>
@@ -14954,13 +14954,13 @@
         <v>156</v>
       </c>
       <c r="V186" s="1">
-        <v>46269.37890997685</v>
+        <v>46269.41910425926</v>
       </c>
       <c r="W186">
         <v>-5</v>
       </c>
       <c r="X186" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AB186">
         <v>0</v>
@@ -14977,10 +14977,10 @@
     </row>
     <row r="187" spans="1:35">
       <c r="A187">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B187" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C187" t="s">
         <v>50</v>
@@ -15016,7 +15016,7 @@
         <v>2026</v>
       </c>
       <c r="R187">
-        <v>17222729</v>
+        <v>16976127</v>
       </c>
       <c r="S187" t="s">
         <v>54</v>
@@ -15025,13 +15025,13 @@
         <v>156</v>
       </c>
       <c r="V187" s="1">
-        <v>46269.37833320602</v>
+        <v>46269.37890997685</v>
       </c>
       <c r="W187">
         <v>-5</v>
       </c>
       <c r="X187" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AB187">
         <v>0</v>
@@ -15048,10 +15048,10 @@
     </row>
     <row r="188" spans="1:35">
       <c r="A188">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B188" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C188" t="s">
         <v>50</v>
@@ -15060,7 +15060,7 @@
         <v>51</v>
       </c>
       <c r="E188" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F188" t="s">
         <v>56</v>
@@ -15087,28 +15087,28 @@
         <v>2026</v>
       </c>
       <c r="R188">
-        <v>17042445</v>
+        <v>17222729</v>
       </c>
       <c r="S188" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="U188" t="s">
         <v>156</v>
       </c>
       <c r="V188" s="1">
-        <v>46269.41913112268</v>
+        <v>46269.37833320602</v>
       </c>
       <c r="W188">
         <v>-5</v>
       </c>
       <c r="X188" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AB188">
         <v>0</v>
       </c>
       <c r="AC188" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="AH188" t="s">
         <v>230</v>
@@ -15119,16 +15119,16 @@
     </row>
     <row r="189" spans="1:35">
       <c r="A189">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C189" t="s">
         <v>50</v>
       </c>
       <c r="D189" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E189" t="s">
         <v>55</v>
@@ -15158,16 +15158,16 @@
         <v>2026</v>
       </c>
       <c r="R189">
-        <v>16960001</v>
+        <v>17042445</v>
       </c>
       <c r="S189" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="U189" t="s">
         <v>156</v>
       </c>
       <c r="V189" s="1">
-        <v>46269.41913740741</v>
+        <v>46269.41913112268</v>
       </c>
       <c r="W189">
         <v>-5</v>
@@ -15179,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="AC189" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="AH189" t="s">
         <v>230</v>
@@ -15190,25 +15190,25 @@
     </row>
     <row r="190" spans="1:35">
       <c r="A190">
-        <v>6404</v>
+        <v>6628</v>
       </c>
       <c r="B190" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C190" t="s">
         <v>50</v>
       </c>
       <c r="D190" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E190" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F190" t="s">
         <v>56</v>
       </c>
       <c r="G190">
-        <v>11001</v>
+        <v>6215</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -15217,46 +15217,43 @@
         <v>65</v>
       </c>
       <c r="J190" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="N190" s="1">
-        <v>46259</v>
+        <v>46274</v>
       </c>
       <c r="P190">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q190">
         <v>2026</v>
       </c>
       <c r="R190">
-        <v>16962453</v>
+        <v>16960001</v>
       </c>
       <c r="S190" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U190" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V190" s="1">
-        <v>46267.66131466435</v>
+        <v>46269.41913740741</v>
       </c>
       <c r="W190">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="X190" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y190" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="AB190">
         <v>0</v>
       </c>
       <c r="AC190" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH190" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AI190" t="s">
         <v>231</v>
@@ -15294,34 +15291,34 @@
         <v>74</v>
       </c>
       <c r="N191" s="1">
-        <v>46321</v>
+        <v>46259</v>
       </c>
       <c r="P191">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q191">
         <v>2026</v>
       </c>
       <c r="R191">
-        <v>16962455</v>
+        <v>16962453</v>
       </c>
       <c r="S191" t="s">
         <v>54</v>
       </c>
       <c r="U191" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V191" s="1">
-        <v>46266.21595836805</v>
+        <v>46267.66131466435</v>
       </c>
       <c r="W191">
-        <v>-52</v>
+        <v>10</v>
       </c>
       <c r="X191" t="s">
         <v>168</v>
       </c>
       <c r="Y191" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AB191">
         <v>0</v>
@@ -15338,16 +15335,16 @@
     </row>
     <row r="192" spans="1:35">
       <c r="A192">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B192" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C192" t="s">
         <v>50</v>
       </c>
       <c r="D192" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E192" t="s">
         <v>54</v>
@@ -15356,7 +15353,7 @@
         <v>56</v>
       </c>
       <c r="G192">
-        <v>7877</v>
+        <v>11001</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -15365,7 +15362,7 @@
         <v>65</v>
       </c>
       <c r="J192" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N192" s="1">
         <v>46321</v>
@@ -15377,7 +15374,7 @@
         <v>2026</v>
       </c>
       <c r="R192">
-        <v>17399331</v>
+        <v>16962455</v>
       </c>
       <c r="S192" t="s">
         <v>54</v>
@@ -15386,16 +15383,16 @@
         <v>156</v>
       </c>
       <c r="V192" s="1">
-        <v>46266.21572962963</v>
+        <v>46266.21595836805</v>
       </c>
       <c r="W192">
         <v>-52</v>
       </c>
       <c r="X192" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Y192" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AB192">
         <v>0</v>
@@ -15412,10 +15409,10 @@
     </row>
     <row r="193" spans="1:35">
       <c r="A193">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B193" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
@@ -15430,7 +15427,7 @@
         <v>56</v>
       </c>
       <c r="G193">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -15439,7 +15436,7 @@
         <v>65</v>
       </c>
       <c r="J193" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="N193" s="1">
         <v>46321</v>
@@ -15451,7 +15448,7 @@
         <v>2026</v>
       </c>
       <c r="R193">
-        <v>16976322</v>
+        <v>17399331</v>
       </c>
       <c r="S193" t="s">
         <v>54</v>
@@ -15460,16 +15457,16 @@
         <v>156</v>
       </c>
       <c r="V193" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.21572962963</v>
       </c>
       <c r="W193">
         <v>-52</v>
       </c>
       <c r="X193" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y193" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AB193">
         <v>0</v>
@@ -15486,10 +15483,10 @@
     </row>
     <row r="194" spans="1:35">
       <c r="A194">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B194" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C194" t="s">
         <v>50</v>
@@ -15504,7 +15501,7 @@
         <v>56</v>
       </c>
       <c r="G194">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -15513,7 +15510,7 @@
         <v>65</v>
       </c>
       <c r="J194" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N194" s="1">
         <v>46321</v>
@@ -15525,7 +15522,7 @@
         <v>2026</v>
       </c>
       <c r="R194">
-        <v>17399291</v>
+        <v>16976322</v>
       </c>
       <c r="S194" t="s">
         <v>54</v>
@@ -15534,13 +15531,16 @@
         <v>156</v>
       </c>
       <c r="V194" s="1">
-        <v>46266.00006921296</v>
+        <v>46266.21550011574</v>
       </c>
       <c r="W194">
         <v>-52</v>
       </c>
       <c r="X194" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="Y194" t="s">
+        <v>222</v>
       </c>
       <c r="AB194">
         <v>0</v>
@@ -15557,16 +15557,16 @@
     </row>
     <row r="195" spans="1:35">
       <c r="A195">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B195" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C195" t="s">
         <v>50</v>
       </c>
       <c r="D195" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E195" t="s">
         <v>54</v>
@@ -15596,7 +15596,7 @@
         <v>2026</v>
       </c>
       <c r="R195">
-        <v>16962349</v>
+        <v>17399291</v>
       </c>
       <c r="S195" t="s">
         <v>54</v>
@@ -15611,7 +15611,7 @@
         <v>-52</v>
       </c>
       <c r="X195" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AB195">
         <v>0</v>
@@ -15628,16 +15628,16 @@
     </row>
     <row r="196" spans="1:35">
       <c r="A196">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B196" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C196" t="s">
         <v>50</v>
       </c>
       <c r="D196" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E196" t="s">
         <v>54</v>
@@ -15658,34 +15658,31 @@
         <v>117</v>
       </c>
       <c r="N196" s="1">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="P196">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q196">
         <v>2026</v>
       </c>
       <c r="R196">
-        <v>16976236</v>
+        <v>16962349</v>
       </c>
       <c r="S196" t="s">
         <v>54</v>
       </c>
       <c r="U196" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V196" s="1">
-        <v>46269.57097615741</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W196">
-        <v>9</v>
+        <v>-52</v>
       </c>
       <c r="X196" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y196" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="AB196">
         <v>0</v>
@@ -15732,32 +15729,35 @@
         <v>117</v>
       </c>
       <c r="N197" s="1">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="P197">
+        <v>7</v>
+      </c>
+      <c r="Q197">
+        <v>2026</v>
+      </c>
+      <c r="R197">
+        <v>16976236</v>
+      </c>
+      <c r="S197" t="s">
+        <v>54</v>
+      </c>
+      <c r="U197" t="s">
+        <v>155</v>
+      </c>
+      <c r="V197" s="1">
+        <v>46269.57097615741</v>
+      </c>
+      <c r="W197">
         <v>9</v>
-      </c>
-      <c r="Q197">
-        <v>2026</v>
-      </c>
-      <c r="R197">
-        <v>16976238</v>
-      </c>
-      <c r="S197" t="s">
-        <v>54</v>
-      </c>
-      <c r="U197" t="s">
-        <v>156</v>
-      </c>
-      <c r="V197" s="1">
-        <v>46266.00006921296</v>
-      </c>
-      <c r="W197">
-        <v>-52</v>
       </c>
       <c r="X197" t="s">
         <v>165</v>
       </c>
+      <c r="Y197" t="s">
+        <v>223</v>
+      </c>
       <c r="AB197">
         <v>0</v>
       </c>
@@ -15773,75 +15773,146 @@
     </row>
     <row r="198" spans="1:35">
       <c r="A198">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B198" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C198" t="s">
         <v>50</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F198" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G198">
-        <v>11056</v>
+        <v>7027</v>
       </c>
       <c r="H198">
         <v>0</v>
       </c>
       <c r="I198" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J198" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N198" s="1">
-        <v>46269</v>
-      </c>
-      <c r="O198" t="s">
-        <v>123</v>
+        <v>46321</v>
       </c>
       <c r="P198">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q198">
         <v>2026</v>
       </c>
       <c r="R198">
-        <v>18261776</v>
+        <v>16976238</v>
+      </c>
+      <c r="S198" t="s">
+        <v>54</v>
       </c>
       <c r="U198" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V198" s="1">
-        <v>46269.46753030093</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>-52</v>
       </c>
       <c r="X198" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y198" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="AB198">
         <v>0</v>
       </c>
       <c r="AC198" t="s">
-        <v>227</v>
+        <v>54</v>
       </c>
       <c r="AH198" t="s">
         <v>228</v>
       </c>
       <c r="AI198" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="199" spans="1:35">
+      <c r="A199">
+        <v>6945</v>
+      </c>
+      <c r="B199" t="s">
+        <v>39</v>
+      </c>
+      <c r="C199" t="s">
+        <v>50</v>
+      </c>
+      <c r="D199" t="s">
+        <v>52</v>
+      </c>
+      <c r="E199" t="s">
+        <v>55</v>
+      </c>
+      <c r="F199" t="s">
+        <v>57</v>
+      </c>
+      <c r="G199">
+        <v>11056</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199" t="s">
+        <v>66</v>
+      </c>
+      <c r="J199" t="s">
+        <v>118</v>
+      </c>
+      <c r="N199" s="1">
+        <v>46269</v>
+      </c>
+      <c r="O199" t="s">
+        <v>123</v>
+      </c>
+      <c r="P199">
+        <v>8</v>
+      </c>
+      <c r="Q199">
+        <v>2026</v>
+      </c>
+      <c r="R199">
+        <v>18261776</v>
+      </c>
+      <c r="U199" t="s">
+        <v>157</v>
+      </c>
+      <c r="V199" s="1">
+        <v>46269.46753030093</v>
+      </c>
+      <c r="W199">
+        <v>0</v>
+      </c>
+      <c r="X199" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y199" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB199">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="s">
+        <v>227</v>
+      </c>
+      <c r="AH199" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI199" t="s">
         <v>231</v>
       </c>
     </row>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3167" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3218" uniqueCount="253">
   <si>
     <t>CodCliente</t>
   </si>
@@ -451,7 +451,7 @@
     <t>Mikael Teixeira</t>
   </si>
   <si>
-    <t>Fabiane Branco</t>
+    <t>Micaele Cordeiro</t>
   </si>
   <si>
     <t>Evellin Bispo</t>
@@ -760,10 +760,16 @@
 Reunião confirmada pelo cliente - Data Comentário: 04/09/2026 11:03</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
+  </si>
+  <si>
     <t>Karen Ribeiro</t>
   </si>
   <si>
     <t>Karina Fonseca</t>
+  </si>
+  <si>
+    <t>Fabiane Branco</t>
   </si>
   <si>
     <t>Raisa Sousa</t>
@@ -1117,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI221"/>
+  <dimension ref="A1:AI225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1283,7 +1289,7 @@
         <v>46268.63953865741</v>
       </c>
       <c r="W2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X2" t="s">
         <v>167</v>
@@ -1298,10 +1304,10 @@
         <v>132</v>
       </c>
       <c r="AH2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1360,7 +1366,7 @@
         <v>46266.57730150463</v>
       </c>
       <c r="W3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X3" t="s">
         <v>168</v>
@@ -1375,10 +1381,10 @@
         <v>133</v>
       </c>
       <c r="AH3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1437,7 +1443,7 @@
         <v>46266.41668148148</v>
       </c>
       <c r="W4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X4" t="s">
         <v>169</v>
@@ -1452,10 +1458,10 @@
         <v>132</v>
       </c>
       <c r="AH4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1514,7 +1520,7 @@
         <v>46267.75233784723</v>
       </c>
       <c r="W5">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X5" t="s">
         <v>167</v>
@@ -1526,10 +1532,10 @@
         <v>132</v>
       </c>
       <c r="AH5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1588,7 +1594,7 @@
         <v>46267.75233927083</v>
       </c>
       <c r="W6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X6" t="s">
         <v>168</v>
@@ -1600,10 +1606,10 @@
         <v>133</v>
       </c>
       <c r="AH6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1662,7 +1668,7 @@
         <v>46267.7523394676</v>
       </c>
       <c r="W7">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X7" t="s">
         <v>168</v>
@@ -1674,10 +1680,10 @@
         <v>133</v>
       </c>
       <c r="AH7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1736,7 +1742,7 @@
         <v>46267.75234278935</v>
       </c>
       <c r="W8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X8" t="s">
         <v>170</v>
@@ -1748,10 +1754,10 @@
         <v>134</v>
       </c>
       <c r="AH8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1810,7 +1816,7 @@
         <v>46267.75234309028</v>
       </c>
       <c r="W9">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X9" t="s">
         <v>169</v>
@@ -1822,10 +1828,10 @@
         <v>132</v>
       </c>
       <c r="AH9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1884,7 +1890,7 @@
         <v>46267.75234383102</v>
       </c>
       <c r="W10">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X10" t="s">
         <v>171</v>
@@ -1896,10 +1902,10 @@
         <v>135</v>
       </c>
       <c r="AH10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1958,7 +1964,7 @@
         <v>46267.75234424769</v>
       </c>
       <c r="W11">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X11" t="s">
         <v>171</v>
@@ -1970,10 +1976,10 @@
         <v>135</v>
       </c>
       <c r="AH11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2032,7 +2038,7 @@
         <v>46267.47365627315</v>
       </c>
       <c r="W12">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="X12" t="s">
         <v>172</v>
@@ -2044,10 +2050,10 @@
         <v>136</v>
       </c>
       <c r="AH12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2106,7 +2112,7 @@
         <v>46266.47620831019</v>
       </c>
       <c r="W13">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X13" t="s">
         <v>173</v>
@@ -2115,13 +2121,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2180,7 +2186,7 @@
         <v>46267.57586420139</v>
       </c>
       <c r="W14">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X14" t="s">
         <v>174</v>
@@ -2189,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AH14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2251,7 +2257,7 @@
         <v>46266.44145744213</v>
       </c>
       <c r="W15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X15" t="s">
         <v>175</v>
@@ -2263,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2319,7 +2325,7 @@
         <v>46266.44156952546</v>
       </c>
       <c r="W16">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="X16" t="s">
         <v>175</v>
@@ -2328,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2387,7 +2393,7 @@
         <v>46266.44152346065</v>
       </c>
       <c r="W17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X17" t="s">
         <v>175</v>
@@ -2399,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2461,7 +2467,7 @@
         <v>46269.3962034375</v>
       </c>
       <c r="W18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X18" t="s">
         <v>176</v>
@@ -2476,10 +2482,10 @@
         <v>138</v>
       </c>
       <c r="AH18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2538,7 +2544,7 @@
         <v>46268.54759884259</v>
       </c>
       <c r="W19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X19" t="s">
         <v>173</v>
@@ -2553,10 +2559,10 @@
         <v>137</v>
       </c>
       <c r="AH19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2615,7 +2621,7 @@
         <v>46269.38216940972</v>
       </c>
       <c r="W20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X20" t="s">
         <v>174</v>
@@ -2630,10 +2636,10 @@
         <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2692,7 +2698,7 @@
         <v>46269.40844942129</v>
       </c>
       <c r="W21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X21" t="s">
         <v>172</v>
@@ -2707,10 +2713,10 @@
         <v>136</v>
       </c>
       <c r="AH21" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI21" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2769,7 +2775,7 @@
         <v>46266.37634084491</v>
       </c>
       <c r="W22">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X22" t="s">
         <v>177</v>
@@ -2781,10 +2787,10 @@
         <v>139</v>
       </c>
       <c r="AH22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2843,7 +2849,7 @@
         <v>46267.47452163194</v>
       </c>
       <c r="W23">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X23" t="s">
         <v>172</v>
@@ -2855,10 +2861,10 @@
         <v>136</v>
       </c>
       <c r="AH23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2917,7 +2923,7 @@
         <v>46267.4745221412</v>
       </c>
       <c r="W24">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X24" t="s">
         <v>172</v>
@@ -2929,10 +2935,10 @@
         <v>136</v>
       </c>
       <c r="AH24" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI24" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -2991,7 +2997,7 @@
         <v>46267.47452299768</v>
       </c>
       <c r="W25">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X25" t="s">
         <v>172</v>
@@ -3003,10 +3009,10 @@
         <v>136</v>
       </c>
       <c r="AH25" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI25" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3065,7 +3071,7 @@
         <v>46267.75231010417</v>
       </c>
       <c r="W26">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X26" t="s">
         <v>173</v>
@@ -3077,10 +3083,10 @@
         <v>137</v>
       </c>
       <c r="AH26" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3139,7 +3145,7 @@
         <v>46267.75234059028</v>
       </c>
       <c r="W27">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X27" t="s">
         <v>172</v>
@@ -3151,10 +3157,10 @@
         <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI27" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3213,7 +3219,7 @@
         <v>46267.7523409375</v>
       </c>
       <c r="W28">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X28" t="s">
         <v>172</v>
@@ -3225,10 +3231,10 @@
         <v>136</v>
       </c>
       <c r="AH28" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3287,7 +3293,7 @@
         <v>46267.75234170139</v>
       </c>
       <c r="W29">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="X29" t="s">
         <v>172</v>
@@ -3299,10 +3305,10 @@
         <v>136</v>
       </c>
       <c r="AH29" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI29" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3361,7 +3367,7 @@
         <v>46268.58940019676</v>
       </c>
       <c r="W30">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X30" t="s">
         <v>176</v>
@@ -3373,10 +3379,10 @@
         <v>140</v>
       </c>
       <c r="AH30" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI30" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3438,7 +3444,7 @@
         <v>46268.37896984954</v>
       </c>
       <c r="W31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X31" t="s">
         <v>168</v>
@@ -3453,10 +3459,10 @@
         <v>141</v>
       </c>
       <c r="AH31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3515,7 +3521,7 @@
         <v>46269.71652982639</v>
       </c>
       <c r="W32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X32" t="s">
         <v>170</v>
@@ -3527,10 +3533,10 @@
         <v>142</v>
       </c>
       <c r="AH32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI32" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3592,7 +3598,7 @@
         <v>46269.71069613426</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="s">
         <v>169</v>
@@ -3607,10 +3613,10 @@
         <v>143</v>
       </c>
       <c r="AH33" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI33" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3669,7 +3675,7 @@
         <v>46267.55838734953</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34" t="s">
         <v>173</v>
@@ -3684,10 +3690,10 @@
         <v>144</v>
       </c>
       <c r="AH34" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI34" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3749,7 +3755,7 @@
         <v>46273.59003707176</v>
       </c>
       <c r="W35">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X35" t="s">
         <v>177</v>
@@ -3761,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="AH35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI35" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3829,7 +3835,7 @@
         <v>46268.74069754629</v>
       </c>
       <c r="W36">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X36" t="s">
         <v>167</v>
@@ -3844,10 +3850,10 @@
         <v>146</v>
       </c>
       <c r="AH36" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI36" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3909,7 +3915,7 @@
         <v>46273.45940115741</v>
       </c>
       <c r="W37">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X37" t="s">
         <v>176</v>
@@ -3924,10 +3930,10 @@
         <v>140</v>
       </c>
       <c r="AH37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -3986,7 +3992,7 @@
         <v>46267.66088636574</v>
       </c>
       <c r="W38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X38" t="s">
         <v>173</v>
@@ -4001,10 +4007,10 @@
         <v>162</v>
       </c>
       <c r="AH38" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI38" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4066,7 +4072,7 @@
         <v>46268.45922827546</v>
       </c>
       <c r="W39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X39" t="s">
         <v>174</v>
@@ -4081,10 +4087,10 @@
         <v>141</v>
       </c>
       <c r="AH39" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI39" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4146,7 +4152,7 @@
         <v>46269.59248078704</v>
       </c>
       <c r="W40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X40" t="s">
         <v>168</v>
@@ -4161,10 +4167,10 @@
         <v>141</v>
       </c>
       <c r="AH40" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4226,7 +4232,7 @@
         <v>46269.59224453704</v>
       </c>
       <c r="W41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X41" t="s">
         <v>168</v>
@@ -4241,10 +4247,10 @@
         <v>141</v>
       </c>
       <c r="AH41" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI41" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4306,7 +4312,7 @@
         <v>46268.5891771875</v>
       </c>
       <c r="W42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X42" t="s">
         <v>176</v>
@@ -4321,10 +4327,10 @@
         <v>140</v>
       </c>
       <c r="AH42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI42" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4386,7 +4392,7 @@
         <v>46267.64795916666</v>
       </c>
       <c r="W43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X43" t="s">
         <v>172</v>
@@ -4401,10 +4407,10 @@
         <v>147</v>
       </c>
       <c r="AH43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI43" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4466,7 +4472,7 @@
         <v>46267.4478849537</v>
       </c>
       <c r="W44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X44" t="s">
         <v>170</v>
@@ -4481,10 +4487,10 @@
         <v>142</v>
       </c>
       <c r="AH44" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI44" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4546,7 +4552,7 @@
         <v>46269.59056300926</v>
       </c>
       <c r="W45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X45" t="s">
         <v>169</v>
@@ -4561,10 +4567,10 @@
         <v>143</v>
       </c>
       <c r="AH45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4620,7 +4626,7 @@
         <v>46273.67026252315</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="s">
         <v>173</v>
@@ -4632,10 +4638,10 @@
         <v>144</v>
       </c>
       <c r="AH46" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4694,7 +4700,7 @@
         <v>46269.677524375</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" t="s">
         <v>174</v>
@@ -4706,10 +4712,10 @@
         <v>141</v>
       </c>
       <c r="AH47" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI47" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4768,7 +4774,7 @@
         <v>46269.677525</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" t="s">
         <v>168</v>
@@ -4780,10 +4786,10 @@
         <v>141</v>
       </c>
       <c r="AH48" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI48" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4842,7 +4848,7 @@
         <v>46269.677525625</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" t="s">
         <v>168</v>
@@ -4854,10 +4860,10 @@
         <v>141</v>
       </c>
       <c r="AH49" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI49" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4916,7 +4922,7 @@
         <v>46268.58906282407</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" t="s">
         <v>176</v>
@@ -4928,10 +4934,10 @@
         <v>140</v>
       </c>
       <c r="AH50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -4990,7 +4996,7 @@
         <v>46267.64761306713</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" t="s">
         <v>172</v>
@@ -5002,10 +5008,10 @@
         <v>147</v>
       </c>
       <c r="AH51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI51" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5067,7 +5073,7 @@
         <v>46273.64957155092</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" t="s">
         <v>170</v>
@@ -5082,10 +5088,10 @@
         <v>142</v>
       </c>
       <c r="AH52" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5144,7 +5150,7 @@
         <v>46273.39871140046</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" t="s">
         <v>169</v>
@@ -5156,10 +5162,10 @@
         <v>143</v>
       </c>
       <c r="AH53" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5221,7 +5227,7 @@
         <v>46267.35832805555</v>
       </c>
       <c r="W54">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X54" t="s">
         <v>174</v>
@@ -5236,10 +5242,10 @@
         <v>141</v>
       </c>
       <c r="AH54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5301,7 +5307,7 @@
         <v>46268.71229238426</v>
       </c>
       <c r="W55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X55" t="s">
         <v>168</v>
@@ -5316,10 +5322,10 @@
         <v>141</v>
       </c>
       <c r="AH55" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5381,7 +5387,7 @@
         <v>46268.71229297454</v>
       </c>
       <c r="W56">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X56" t="s">
         <v>168</v>
@@ -5396,10 +5402,10 @@
         <v>141</v>
       </c>
       <c r="AH56" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5461,7 +5467,7 @@
         <v>46267.74532275463</v>
       </c>
       <c r="W57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X57" t="s">
         <v>176</v>
@@ -5476,10 +5482,10 @@
         <v>140</v>
       </c>
       <c r="AH57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI57" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5538,7 +5544,7 @@
         <v>46269.60160202546</v>
       </c>
       <c r="W58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X58" t="s">
         <v>173</v>
@@ -5553,10 +5559,10 @@
         <v>144</v>
       </c>
       <c r="AH58" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI58" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5618,7 +5624,7 @@
         <v>46273.64508760416</v>
       </c>
       <c r="W59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X59" t="s">
         <v>177</v>
@@ -5630,13 +5636,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="AH59" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI59" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5698,7 +5704,7 @@
         <v>46268.45926839121</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" t="s">
         <v>174</v>
@@ -5713,10 +5719,10 @@
         <v>141</v>
       </c>
       <c r="AH60" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI60" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5778,7 +5784,7 @@
         <v>46269.59250902777</v>
       </c>
       <c r="W61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X61" t="s">
         <v>168</v>
@@ -5793,10 +5799,10 @@
         <v>141</v>
       </c>
       <c r="AH61" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI61" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5858,7 +5864,7 @@
         <v>46269.5922865625</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" t="s">
         <v>168</v>
@@ -5873,10 +5879,10 @@
         <v>141</v>
       </c>
       <c r="AH62" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -5938,7 +5944,7 @@
         <v>46268.58922707176</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" t="s">
         <v>176</v>
@@ -5953,10 +5959,10 @@
         <v>140</v>
       </c>
       <c r="AH63" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI63" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6018,7 +6024,7 @@
         <v>46267.64800344907</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" t="s">
         <v>172</v>
@@ -6033,10 +6039,10 @@
         <v>147</v>
       </c>
       <c r="AH64" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI64" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6098,7 +6104,7 @@
         <v>46267.44799793982</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X65" t="s">
         <v>170</v>
@@ -6113,10 +6119,10 @@
         <v>142</v>
       </c>
       <c r="AH65" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI65" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6178,7 +6184,7 @@
         <v>46269.59070487269</v>
       </c>
       <c r="W66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X66" t="s">
         <v>169</v>
@@ -6193,10 +6199,10 @@
         <v>143</v>
       </c>
       <c r="AH66" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI66" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6258,7 +6264,7 @@
         <v>46269.49635894676</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" t="s">
         <v>174</v>
@@ -6273,10 +6279,10 @@
         <v>141</v>
       </c>
       <c r="AH67" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI67" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6332,7 +6338,7 @@
         <v>46269.63659284722</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" t="s">
         <v>173</v>
@@ -6344,10 +6350,10 @@
         <v>144</v>
       </c>
       <c r="AH68" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI68" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6406,7 +6412,7 @@
         <v>46273.64532122685</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" t="s">
         <v>177</v>
@@ -6415,13 +6421,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="AH69" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI69" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6480,7 +6486,7 @@
         <v>46268.45929986111</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" t="s">
         <v>174</v>
@@ -6492,10 +6498,10 @@
         <v>141</v>
       </c>
       <c r="AH70" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI70" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6554,7 +6560,7 @@
         <v>46269.5925421875</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" t="s">
         <v>168</v>
@@ -6566,10 +6572,10 @@
         <v>141</v>
       </c>
       <c r="AH71" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI71" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6628,7 +6634,7 @@
         <v>46269.59231454861</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" t="s">
         <v>168</v>
@@ -6640,10 +6646,10 @@
         <v>141</v>
       </c>
       <c r="AH72" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI72" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6702,7 +6708,7 @@
         <v>46268.58932953704</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" t="s">
         <v>176</v>
@@ -6714,10 +6720,10 @@
         <v>140</v>
       </c>
       <c r="AH73" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI73" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6776,7 +6782,7 @@
         <v>46267.648038125</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" t="s">
         <v>172</v>
@@ -6788,10 +6794,10 @@
         <v>147</v>
       </c>
       <c r="AH74" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI74" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6850,7 +6856,7 @@
         <v>46267.44824061343</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X75" t="s">
         <v>170</v>
@@ -6862,10 +6868,10 @@
         <v>142</v>
       </c>
       <c r="AH75" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI75" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6924,7 +6930,7 @@
         <v>46269.59082328704</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" t="s">
         <v>169</v>
@@ -6936,10 +6942,10 @@
         <v>143</v>
       </c>
       <c r="AH76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -6988,12 +6994,6 @@
       <c r="R77">
         <v>18263044</v>
       </c>
-      <c r="S77" t="s">
-        <v>143</v>
-      </c>
-      <c r="T77" t="s">
-        <v>161</v>
-      </c>
       <c r="U77" t="s">
         <v>165</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>46273.63629708334</v>
       </c>
       <c r="W77">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X77" t="s">
         <v>169</v>
@@ -7016,10 +7016,10 @@
         <v>143</v>
       </c>
       <c r="AH77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7068,12 +7068,6 @@
       <c r="R78">
         <v>18269524</v>
       </c>
-      <c r="S78" t="s">
-        <v>143</v>
-      </c>
-      <c r="T78" t="s">
-        <v>161</v>
-      </c>
       <c r="U78" t="s">
         <v>165</v>
       </c>
@@ -7081,7 +7075,7 @@
         <v>46273.64318633102</v>
       </c>
       <c r="W78">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X78" t="s">
         <v>169</v>
@@ -7096,10 +7090,10 @@
         <v>143</v>
       </c>
       <c r="AH78" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI78" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7148,12 +7142,6 @@
       <c r="R79">
         <v>18269550</v>
       </c>
-      <c r="S79" t="s">
-        <v>143</v>
-      </c>
-      <c r="T79" t="s">
-        <v>161</v>
-      </c>
       <c r="U79" t="s">
         <v>165</v>
       </c>
@@ -7161,7 +7149,7 @@
         <v>46273.64880981482</v>
       </c>
       <c r="W79">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X79" t="s">
         <v>169</v>
@@ -7176,10 +7164,10 @@
         <v>143</v>
       </c>
       <c r="AH79" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI79" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7238,7 +7226,7 @@
         <v>46267.72055925926</v>
       </c>
       <c r="W80">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X80" t="s">
         <v>167</v>
@@ -7250,10 +7238,10 @@
         <v>149</v>
       </c>
       <c r="AH80" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI80" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7312,7 +7300,7 @@
         <v>46267.79441380787</v>
       </c>
       <c r="W81">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X81" t="s">
         <v>168</v>
@@ -7324,10 +7312,10 @@
         <v>149</v>
       </c>
       <c r="AH81" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI81" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7386,7 +7374,7 @@
         <v>46267.79441215278</v>
       </c>
       <c r="W82">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="X82" t="s">
         <v>169</v>
@@ -7398,10 +7386,10 @@
         <v>150</v>
       </c>
       <c r="AH82" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI82" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7460,7 +7448,7 @@
         <v>46267.7205502662</v>
       </c>
       <c r="W83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X83" t="s">
         <v>167</v>
@@ -7472,10 +7460,10 @@
         <v>149</v>
       </c>
       <c r="AH83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI83" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7534,7 +7522,7 @@
         <v>46267.79439748843</v>
       </c>
       <c r="W84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X84" t="s">
         <v>168</v>
@@ -7546,10 +7534,10 @@
         <v>149</v>
       </c>
       <c r="AH84" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7608,7 +7596,7 @@
         <v>46267.79440011574</v>
       </c>
       <c r="W85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X85" t="s">
         <v>170</v>
@@ -7623,10 +7611,10 @@
         <v>149</v>
       </c>
       <c r="AH85" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI85" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7685,7 +7673,7 @@
         <v>46267.79439818287</v>
       </c>
       <c r="W86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X86" t="s">
         <v>169</v>
@@ -7697,10 +7685,10 @@
         <v>150</v>
       </c>
       <c r="AH86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI86" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7759,7 +7747,7 @@
         <v>46267.7202693287</v>
       </c>
       <c r="W87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X87" t="s">
         <v>167</v>
@@ -7771,10 +7759,10 @@
         <v>149</v>
       </c>
       <c r="AH87" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7833,7 +7821,7 @@
         <v>46267.79409846065</v>
       </c>
       <c r="W88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X88" t="s">
         <v>168</v>
@@ -7845,10 +7833,10 @@
         <v>149</v>
       </c>
       <c r="AH88" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI88" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7907,7 +7895,7 @@
         <v>46267.79409725694</v>
       </c>
       <c r="W89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X89" t="s">
         <v>168</v>
@@ -7919,10 +7907,10 @@
         <v>149</v>
       </c>
       <c r="AH89" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI89" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -7978,7 +7966,7 @@
         <v>46267.79410239583</v>
       </c>
       <c r="W90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X90" t="s">
         <v>170</v>
@@ -7990,10 +7978,10 @@
         <v>149</v>
       </c>
       <c r="AH90" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI90" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8052,7 +8040,7 @@
         <v>46267.79409934028</v>
       </c>
       <c r="W91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X91" t="s">
         <v>169</v>
@@ -8064,10 +8052,10 @@
         <v>150</v>
       </c>
       <c r="AH91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI91" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8126,7 +8114,7 @@
         <v>46267.72033356482</v>
       </c>
       <c r="W92">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X92" t="s">
         <v>167</v>
@@ -8138,10 +8126,10 @@
         <v>149</v>
       </c>
       <c r="AH92" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI92" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8200,7 +8188,7 @@
         <v>46267.79418105324</v>
       </c>
       <c r="W93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X93" t="s">
         <v>168</v>
@@ -8212,10 +8200,10 @@
         <v>149</v>
       </c>
       <c r="AH93" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI93" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8274,7 +8262,7 @@
         <v>46267.79418005787</v>
       </c>
       <c r="W94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X94" t="s">
         <v>168</v>
@@ -8286,10 +8274,10 @@
         <v>149</v>
       </c>
       <c r="AH94" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI94" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8345,7 +8333,7 @@
         <v>46267.79418379629</v>
       </c>
       <c r="W95">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X95" t="s">
         <v>170</v>
@@ -8357,10 +8345,10 @@
         <v>149</v>
       </c>
       <c r="AH95" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI95" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8419,7 +8407,7 @@
         <v>46267.79418283565</v>
       </c>
       <c r="W96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X96" t="s">
         <v>169</v>
@@ -8431,10 +8419,10 @@
         <v>150</v>
       </c>
       <c r="AH96" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI96" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8493,7 +8481,7 @@
         <v>46267.71937662037</v>
       </c>
       <c r="W97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X97" t="s">
         <v>167</v>
@@ -8505,10 +8493,10 @@
         <v>149</v>
       </c>
       <c r="AH97" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI97" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8567,7 +8555,7 @@
         <v>46267.79259834491</v>
       </c>
       <c r="W98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X98" t="s">
         <v>168</v>
@@ -8579,10 +8567,10 @@
         <v>149</v>
       </c>
       <c r="AH98" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI98" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8641,7 +8629,7 @@
         <v>46267.79260170139</v>
       </c>
       <c r="W99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X99" t="s">
         <v>169</v>
@@ -8653,10 +8641,10 @@
         <v>150</v>
       </c>
       <c r="AH99" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI99" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8718,7 +8706,7 @@
         <v>46268.37621265047</v>
       </c>
       <c r="W100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X100" t="s">
         <v>171</v>
@@ -8733,10 +8721,10 @@
         <v>149</v>
       </c>
       <c r="AH100" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI100" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8792,7 +8780,7 @@
         <v>46267.79440636574</v>
       </c>
       <c r="W101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X101" t="s">
         <v>170</v>
@@ -8804,10 +8792,10 @@
         <v>149</v>
       </c>
       <c r="AH101" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI101" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8866,7 +8854,7 @@
         <v>46267.72037954861</v>
       </c>
       <c r="W102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X102" t="s">
         <v>167</v>
@@ -8878,10 +8866,10 @@
         <v>149</v>
       </c>
       <c r="AH102" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI102" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8940,7 +8928,7 @@
         <v>46267.79424664352</v>
       </c>
       <c r="W103">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X103" t="s">
         <v>168</v>
@@ -8952,10 +8940,10 @@
         <v>149</v>
       </c>
       <c r="AH103" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI103" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9014,7 +9002,7 @@
         <v>46267.79424586806</v>
       </c>
       <c r="W104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X104" t="s">
         <v>168</v>
@@ -9026,10 +9014,10 @@
         <v>149</v>
       </c>
       <c r="AH104" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI104" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9085,7 +9073,7 @@
         <v>46267.79424864583</v>
       </c>
       <c r="W105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X105" t="s">
         <v>170</v>
@@ -9097,10 +9085,10 @@
         <v>149</v>
       </c>
       <c r="AH105" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI105" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9159,7 +9147,7 @@
         <v>46267.79424725694</v>
       </c>
       <c r="W106">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X106" t="s">
         <v>169</v>
@@ -9171,10 +9159,10 @@
         <v>150</v>
       </c>
       <c r="AH106" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI106" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9233,7 +9221,7 @@
         <v>46267.79425081018</v>
       </c>
       <c r="W107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X107" t="s">
         <v>171</v>
@@ -9245,10 +9233,10 @@
         <v>149</v>
       </c>
       <c r="AH107" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI107" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9307,7 +9295,7 @@
         <v>46267.71942916667</v>
       </c>
       <c r="W108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X108" t="s">
         <v>167</v>
@@ -9319,10 +9307,10 @@
         <v>149</v>
       </c>
       <c r="AH108" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI108" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9378,7 +9366,7 @@
         <v>46267.79268530093</v>
       </c>
       <c r="W109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X109" t="s">
         <v>170</v>
@@ -9390,10 +9378,10 @@
         <v>149</v>
       </c>
       <c r="AH109" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI109" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9452,7 +9440,7 @@
         <v>46267.79268769676</v>
       </c>
       <c r="W110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X110" t="s">
         <v>169</v>
@@ -9464,10 +9452,10 @@
         <v>150</v>
       </c>
       <c r="AH110" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI110" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9523,7 +9511,7 @@
         <v>46267.79249748842</v>
       </c>
       <c r="W111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X111" t="s">
         <v>170</v>
@@ -9535,10 +9523,10 @@
         <v>151</v>
       </c>
       <c r="AH111" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI111" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9597,7 +9585,7 @@
         <v>46267.79249788194</v>
       </c>
       <c r="W112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X112" t="s">
         <v>169</v>
@@ -9609,10 +9597,10 @@
         <v>150</v>
       </c>
       <c r="AH112" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI112" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9671,7 +9659,7 @@
         <v>46267.71927280092</v>
       </c>
       <c r="W113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X113" t="s">
         <v>167</v>
@@ -9683,10 +9671,10 @@
         <v>148</v>
       </c>
       <c r="AH113" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI113" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9742,7 +9730,7 @@
         <v>46267.79251079861</v>
       </c>
       <c r="W114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X114" t="s">
         <v>170</v>
@@ -9754,10 +9742,10 @@
         <v>151</v>
       </c>
       <c r="AH114" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9816,7 +9804,7 @@
         <v>46267.79251038194</v>
       </c>
       <c r="W115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X115" t="s">
         <v>169</v>
@@ -9828,10 +9816,10 @@
         <v>150</v>
       </c>
       <c r="AH115" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9890,7 +9878,7 @@
         <v>46267.72044811342</v>
       </c>
       <c r="W116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X116" t="s">
         <v>167</v>
@@ -9902,10 +9890,10 @@
         <v>149</v>
       </c>
       <c r="AH116" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI116" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -9964,7 +9952,7 @@
         <v>46267.79429737268</v>
       </c>
       <c r="W117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X117" t="s">
         <v>168</v>
@@ -9976,10 +9964,10 @@
         <v>149</v>
       </c>
       <c r="AH117" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI117" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10038,7 +10026,7 @@
         <v>46267.79429603009</v>
       </c>
       <c r="W118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X118" t="s">
         <v>168</v>
@@ -10050,10 +10038,10 @@
         <v>149</v>
       </c>
       <c r="AH118" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI118" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10109,7 +10097,7 @@
         <v>46267.79429876158</v>
       </c>
       <c r="W119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X119" t="s">
         <v>170</v>
@@ -10121,10 +10109,10 @@
         <v>149</v>
       </c>
       <c r="AH119" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI119" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10183,7 +10171,7 @@
         <v>46267.79429826389</v>
       </c>
       <c r="W120">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X120" t="s">
         <v>169</v>
@@ -10195,10 +10183,10 @@
         <v>150</v>
       </c>
       <c r="AH120" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI120" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10257,7 +10245,7 @@
         <v>46267.72050385417</v>
       </c>
       <c r="W121">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X121" t="s">
         <v>167</v>
@@ -10269,10 +10257,10 @@
         <v>149</v>
       </c>
       <c r="AH121" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI121" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10331,7 +10319,7 @@
         <v>46267.79434996528</v>
       </c>
       <c r="W122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X122" t="s">
         <v>168</v>
@@ -10343,10 +10331,10 @@
         <v>149</v>
       </c>
       <c r="AH122" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI122" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10405,7 +10393,7 @@
         <v>46267.79434864583</v>
       </c>
       <c r="W123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X123" t="s">
         <v>168</v>
@@ -10417,10 +10405,10 @@
         <v>149</v>
       </c>
       <c r="AH123" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI123" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10476,7 +10464,7 @@
         <v>46267.79435208334</v>
       </c>
       <c r="W124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X124" t="s">
         <v>170</v>
@@ -10488,10 +10476,10 @@
         <v>149</v>
       </c>
       <c r="AH124" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI124" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10550,7 +10538,7 @@
         <v>46267.79435100695</v>
       </c>
       <c r="W125">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X125" t="s">
         <v>169</v>
@@ -10562,10 +10550,10 @@
         <v>150</v>
       </c>
       <c r="AH125" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI125" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10627,7 +10615,7 @@
         <v>46273.6788224074</v>
       </c>
       <c r="W126">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X126" t="s">
         <v>169</v>
@@ -10642,10 +10630,10 @@
         <v>150</v>
       </c>
       <c r="AH126" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10707,7 +10695,7 @@
         <v>46273.67943539352</v>
       </c>
       <c r="W127">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X127" t="s">
         <v>169</v>
@@ -10722,10 +10710,10 @@
         <v>150</v>
       </c>
       <c r="AH127" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI127" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10784,7 +10772,7 @@
         <v>46266.37636392361</v>
       </c>
       <c r="W128">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X128" t="s">
         <v>173</v>
@@ -10796,10 +10784,10 @@
         <v>153</v>
       </c>
       <c r="AH128" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI128" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10858,7 +10846,7 @@
         <v>46266.37598834491</v>
       </c>
       <c r="W129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X129" t="s">
         <v>173</v>
@@ -10870,10 +10858,10 @@
         <v>153</v>
       </c>
       <c r="AH129" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI129" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10935,7 +10923,7 @@
         <v>46268.45899988426</v>
       </c>
       <c r="W130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X130" t="s">
         <v>174</v>
@@ -10950,10 +10938,10 @@
         <v>153</v>
       </c>
       <c r="AH130" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI130" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11012,7 +11000,7 @@
         <v>46266.45957881944</v>
       </c>
       <c r="W131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X131" t="s">
         <v>172</v>
@@ -11024,10 +11012,10 @@
         <v>153</v>
       </c>
       <c r="AH131" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI131" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11086,7 +11074,7 @@
         <v>46266.37645462963</v>
       </c>
       <c r="W132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X132" t="s">
         <v>173</v>
@@ -11098,10 +11086,10 @@
         <v>153</v>
       </c>
       <c r="AH132" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI132" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11160,7 +11148,7 @@
         <v>46266.37649475694</v>
       </c>
       <c r="W133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X133" t="s">
         <v>173</v>
@@ -11172,10 +11160,10 @@
         <v>153</v>
       </c>
       <c r="AH133" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI133" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11234,7 +11222,7 @@
         <v>46266.37591180555</v>
       </c>
       <c r="W134">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X134" t="s">
         <v>173</v>
@@ -11246,10 +11234,10 @@
         <v>153</v>
       </c>
       <c r="AH134" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI134" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11311,7 +11299,7 @@
         <v>46268.45896508102</v>
       </c>
       <c r="W135">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X135" t="s">
         <v>174</v>
@@ -11326,10 +11314,10 @@
         <v>153</v>
       </c>
       <c r="AH135" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI135" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11388,7 +11376,7 @@
         <v>46266.45946195602</v>
       </c>
       <c r="W136">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X136" t="s">
         <v>172</v>
@@ -11400,10 +11388,10 @@
         <v>153</v>
       </c>
       <c r="AH136" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI136" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11462,7 +11450,7 @@
         <v>46266.37538684028</v>
       </c>
       <c r="W137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X137" t="s">
         <v>173</v>
@@ -11474,10 +11462,10 @@
         <v>153</v>
       </c>
       <c r="AH137" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI137" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11536,7 +11524,7 @@
         <v>46266.37538506944</v>
       </c>
       <c r="W138">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X138" t="s">
         <v>177</v>
@@ -11548,10 +11536,10 @@
         <v>153</v>
       </c>
       <c r="AH138" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI138" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11613,7 +11601,7 @@
         <v>46268.45881820602</v>
       </c>
       <c r="W139">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X139" t="s">
         <v>174</v>
@@ -11628,10 +11616,10 @@
         <v>153</v>
       </c>
       <c r="AH139" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI139" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11690,7 +11678,7 @@
         <v>46266.45895332176</v>
       </c>
       <c r="W140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X140" t="s">
         <v>176</v>
@@ -11702,10 +11690,10 @@
         <v>153</v>
       </c>
       <c r="AH140" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI140" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11764,7 +11752,7 @@
         <v>46266.45874105324</v>
       </c>
       <c r="W141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X141" t="s">
         <v>172</v>
@@ -11776,10 +11764,10 @@
         <v>153</v>
       </c>
       <c r="AH141" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI141" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11838,7 +11826,7 @@
         <v>46266.45873584491</v>
       </c>
       <c r="W142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X142" t="s">
         <v>172</v>
@@ -11850,10 +11838,10 @@
         <v>153</v>
       </c>
       <c r="AH142" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI142" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11912,7 +11900,7 @@
         <v>46273.6799675</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X143" t="s">
         <v>172</v>
@@ -11924,10 +11912,10 @@
         <v>153</v>
       </c>
       <c r="AH143" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI143" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -11986,7 +11974,7 @@
         <v>46273.55254606481</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X144" t="s">
         <v>173</v>
@@ -11998,10 +11986,10 @@
         <v>153</v>
       </c>
       <c r="AH144" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI144" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12060,7 +12048,7 @@
         <v>46273.55252126158</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X145" t="s">
         <v>177</v>
@@ -12072,10 +12060,10 @@
         <v>153</v>
       </c>
       <c r="AH145" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI145" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12134,7 +12122,7 @@
         <v>46273.55254163194</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X146" t="s">
         <v>174</v>
@@ -12146,10 +12134,10 @@
         <v>153</v>
       </c>
       <c r="AH146" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI146" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12208,7 +12196,7 @@
         <v>46273.5525440162</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X147" t="s">
         <v>176</v>
@@ -12220,24 +12208,24 @@
         <v>153</v>
       </c>
       <c r="AH147" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI147" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="1:35">
       <c r="A148">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B148" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C148" t="s">
         <v>50</v>
       </c>
       <c r="D148" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E148" t="s">
         <v>54</v>
@@ -12267,7 +12255,7 @@
         <v>2026</v>
       </c>
       <c r="R148">
-        <v>17948969</v>
+        <v>18085242</v>
       </c>
       <c r="S148" t="s">
         <v>153</v>
@@ -12279,10 +12267,10 @@
         <v>166</v>
       </c>
       <c r="V148" s="1">
-        <v>46273.55254652778</v>
+        <v>46273.84422141204</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X148" t="s">
         <v>172</v>
@@ -12294,24 +12282,24 @@
         <v>153</v>
       </c>
       <c r="AH148" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI148" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:35">
       <c r="A149">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B149" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C149" t="s">
         <v>50</v>
       </c>
       <c r="D149" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E149" t="s">
         <v>54</v>
@@ -12320,22 +12308,19 @@
         <v>56</v>
       </c>
       <c r="G149">
-        <v>11359</v>
+        <v>6230</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I149" t="s">
         <v>63</v>
       </c>
       <c r="J149" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N149" s="1">
-        <v>46267</v>
-      </c>
-      <c r="O149" t="s">
-        <v>126</v>
+        <v>46273</v>
       </c>
       <c r="P149">
         <v>8</v>
@@ -12344,7 +12329,7 @@
         <v>2026</v>
       </c>
       <c r="R149">
-        <v>18155345</v>
+        <v>17948969</v>
       </c>
       <c r="S149" t="s">
         <v>153</v>
@@ -12353,19 +12338,16 @@
         <v>163</v>
       </c>
       <c r="U149" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="V149" s="1">
-        <v>46268.45898549769</v>
+        <v>46273.55254652778</v>
       </c>
       <c r="W149">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X149" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y149" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="AB149">
         <v>0</v>
@@ -12374,10 +12356,10 @@
         <v>153</v>
       </c>
       <c r="AH149" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI149" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12400,19 +12382,22 @@
         <v>56</v>
       </c>
       <c r="G150">
-        <v>6884</v>
+        <v>11359</v>
       </c>
       <c r="H150">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I150" t="s">
         <v>63</v>
       </c>
       <c r="J150" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N150" s="1">
-        <v>46273</v>
+        <v>46267</v>
+      </c>
+      <c r="O150" t="s">
+        <v>126</v>
       </c>
       <c r="P150">
         <v>8</v>
@@ -12421,7 +12406,7 @@
         <v>2026</v>
       </c>
       <c r="R150">
-        <v>16976207</v>
+        <v>18155345</v>
       </c>
       <c r="S150" t="s">
         <v>153</v>
@@ -12430,17 +12415,20 @@
         <v>163</v>
       </c>
       <c r="U150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V150" s="1">
-        <v>46268.45915543981</v>
+        <v>46268.45898549769</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X150" t="s">
         <v>174</v>
       </c>
+      <c r="Y150" t="s">
+        <v>215</v>
+      </c>
       <c r="AB150">
         <v>0</v>
       </c>
@@ -12448,24 +12436,24 @@
         <v>153</v>
       </c>
       <c r="AH150" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI150" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="151" spans="1:35">
       <c r="A151">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B151" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C151" t="s">
         <v>50</v>
       </c>
       <c r="D151" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E151" t="s">
         <v>54</v>
@@ -12495,7 +12483,7 @@
         <v>2026</v>
       </c>
       <c r="R151">
-        <v>17949039</v>
+        <v>16976207</v>
       </c>
       <c r="S151" t="s">
         <v>153</v>
@@ -12504,16 +12492,16 @@
         <v>163</v>
       </c>
       <c r="U151" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V151" s="1">
-        <v>46273.56305208334</v>
+        <v>46268.45915543981</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X151" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AB151">
         <v>0</v>
@@ -12522,10 +12510,10 @@
         <v>153</v>
       </c>
       <c r="AH151" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI151" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12548,19 +12536,19 @@
         <v>56</v>
       </c>
       <c r="G152">
-        <v>11303</v>
+        <v>6884</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I152" t="s">
         <v>63</v>
       </c>
       <c r="J152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N152" s="1">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="P152">
         <v>8</v>
@@ -12569,7 +12557,7 @@
         <v>2026</v>
       </c>
       <c r="R152">
-        <v>17949079</v>
+        <v>17949039</v>
       </c>
       <c r="S152" t="s">
         <v>153</v>
@@ -12578,13 +12566,13 @@
         <v>163</v>
       </c>
       <c r="U152" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V152" s="1">
-        <v>46267.44505795139</v>
+        <v>46273.56305208334</v>
       </c>
       <c r="W152">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="X152" t="s">
         <v>172</v>
@@ -12596,18 +12584,18 @@
         <v>153</v>
       </c>
       <c r="AH152" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI152" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="153" spans="1:35">
       <c r="A153">
-        <v>6628</v>
+        <v>6705</v>
       </c>
       <c r="B153" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C153" t="s">
         <v>50</v>
@@ -12616,25 +12604,25 @@
         <v>52</v>
       </c>
       <c r="E153" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F153" t="s">
         <v>56</v>
       </c>
       <c r="G153">
-        <v>945</v>
+        <v>11303</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J153" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N153" s="1">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="P153">
         <v>8</v>
@@ -12643,45 +12631,45 @@
         <v>2026</v>
       </c>
       <c r="R153">
-        <v>16959938</v>
+        <v>17949079</v>
       </c>
       <c r="S153" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="T153" t="s">
+        <v>163</v>
       </c>
       <c r="U153" t="s">
         <v>165</v>
       </c>
       <c r="V153" s="1">
-        <v>46266.04180934028</v>
+        <v>46267.44505795139</v>
       </c>
       <c r="W153">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="X153" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y153" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="AB153">
         <v>0</v>
       </c>
       <c r="AC153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AI153" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="154" spans="1:35">
       <c r="A154">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B154" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C154" t="s">
         <v>50</v>
@@ -12690,7 +12678,7 @@
         <v>52</v>
       </c>
       <c r="E154" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F154" t="s">
         <v>56</v>
@@ -12717,7 +12705,7 @@
         <v>2026</v>
       </c>
       <c r="R154">
-        <v>18056695</v>
+        <v>16959938</v>
       </c>
       <c r="S154" t="s">
         <v>154</v>
@@ -12726,16 +12714,16 @@
         <v>165</v>
       </c>
       <c r="V154" s="1">
-        <v>46266.08343295139</v>
+        <v>46266.04180934028</v>
       </c>
       <c r="W154">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X154" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y154" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB154">
         <v>0</v>
@@ -12744,18 +12732,18 @@
         <v>154</v>
       </c>
       <c r="AH154" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI154" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="155" spans="1:35">
       <c r="A155">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B155" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C155" t="s">
         <v>50</v>
@@ -12767,7 +12755,7 @@
         <v>54</v>
       </c>
       <c r="F155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G155">
         <v>945</v>
@@ -12791,7 +12779,7 @@
         <v>2026</v>
       </c>
       <c r="R155">
-        <v>18164487</v>
+        <v>18056695</v>
       </c>
       <c r="S155" t="s">
         <v>154</v>
@@ -12800,16 +12788,16 @@
         <v>165</v>
       </c>
       <c r="V155" s="1">
-        <v>46266.08344398148</v>
+        <v>46266.08343295139</v>
       </c>
       <c r="W155">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X155" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y155" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AB155">
         <v>0</v>
@@ -12818,33 +12806,33 @@
         <v>154</v>
       </c>
       <c r="AH155" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI155" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="156" spans="1:35">
       <c r="A156">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B156" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C156" t="s">
         <v>50</v>
       </c>
       <c r="D156" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E156" t="s">
         <v>54</v>
       </c>
       <c r="F156" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G156">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -12853,7 +12841,7 @@
         <v>64</v>
       </c>
       <c r="J156" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N156" s="1">
         <v>46283</v>
@@ -12865,7 +12853,7 @@
         <v>2026</v>
       </c>
       <c r="R156">
-        <v>17398869</v>
+        <v>18164487</v>
       </c>
       <c r="S156" t="s">
         <v>154</v>
@@ -12874,16 +12862,16 @@
         <v>165</v>
       </c>
       <c r="V156" s="1">
-        <v>46266.25077376157</v>
+        <v>46266.08344398148</v>
       </c>
       <c r="W156">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X156" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Y156" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AB156">
         <v>0</v>
@@ -12892,24 +12880,24 @@
         <v>154</v>
       </c>
       <c r="AH156" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI156" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="157" spans="1:35">
       <c r="A157">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B157" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C157" t="s">
         <v>50</v>
       </c>
       <c r="D157" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E157" t="s">
         <v>54</v>
@@ -12939,7 +12927,7 @@
         <v>2026</v>
       </c>
       <c r="R157">
-        <v>16962093</v>
+        <v>17398869</v>
       </c>
       <c r="S157" t="s">
         <v>154</v>
@@ -12948,16 +12936,16 @@
         <v>165</v>
       </c>
       <c r="V157" s="1">
-        <v>46266.25004302083</v>
+        <v>46266.25077376157</v>
       </c>
       <c r="W157">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X157" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y157" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AB157">
         <v>0</v>
@@ -12966,18 +12954,18 @@
         <v>154</v>
       </c>
       <c r="AH157" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI157" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="158" spans="1:35">
       <c r="A158">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B158" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C158" t="s">
         <v>50</v>
@@ -13013,7 +13001,7 @@
         <v>2026</v>
       </c>
       <c r="R158">
-        <v>17941132</v>
+        <v>16962093</v>
       </c>
       <c r="S158" t="s">
         <v>154</v>
@@ -13022,16 +13010,16 @@
         <v>165</v>
       </c>
       <c r="V158" s="1">
-        <v>46266.25135543982</v>
+        <v>46266.25004302083</v>
       </c>
       <c r="W158">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X158" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y158" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AB158">
         <v>0</v>
@@ -13040,10 +13028,10 @@
         <v>154</v>
       </c>
       <c r="AH158" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI158" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13066,7 +13054,7 @@
         <v>56</v>
       </c>
       <c r="G159">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -13075,10 +13063,10 @@
         <v>64</v>
       </c>
       <c r="J159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N159" s="1">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="P159">
         <v>8</v>
@@ -13087,7 +13075,7 @@
         <v>2026</v>
       </c>
       <c r="R159">
-        <v>17941146</v>
+        <v>17941132</v>
       </c>
       <c r="S159" t="s">
         <v>154</v>
@@ -13096,16 +13084,16 @@
         <v>165</v>
       </c>
       <c r="V159" s="1">
-        <v>46266.25232241898</v>
+        <v>46266.25135543982</v>
       </c>
       <c r="W159">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="X159" t="s">
         <v>176</v>
       </c>
       <c r="Y159" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AB159">
         <v>0</v>
@@ -13114,24 +13102,24 @@
         <v>154</v>
       </c>
       <c r="AH159" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI159" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="160" spans="1:35">
       <c r="A160">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B160" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C160" t="s">
         <v>50</v>
       </c>
       <c r="D160" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E160" t="s">
         <v>54</v>
@@ -13140,7 +13128,7 @@
         <v>56</v>
       </c>
       <c r="G160">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -13149,7 +13137,7 @@
         <v>64</v>
       </c>
       <c r="J160" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N160" s="1">
         <v>46275</v>
@@ -13161,7 +13149,7 @@
         <v>2026</v>
       </c>
       <c r="R160">
-        <v>17222405</v>
+        <v>17941146</v>
       </c>
       <c r="S160" t="s">
         <v>154</v>
@@ -13170,16 +13158,16 @@
         <v>165</v>
       </c>
       <c r="V160" s="1">
-        <v>46266.25161940972</v>
+        <v>46266.25232241898</v>
       </c>
       <c r="W160">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X160" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Y160" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AB160">
         <v>0</v>
@@ -13188,24 +13176,24 @@
         <v>154</v>
       </c>
       <c r="AH160" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI160" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="161" spans="1:35">
       <c r="A161">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
         <v>50</v>
       </c>
       <c r="D161" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E161" t="s">
         <v>54</v>
@@ -13235,7 +13223,7 @@
         <v>2026</v>
       </c>
       <c r="R161">
-        <v>17941156</v>
+        <v>17222405</v>
       </c>
       <c r="S161" t="s">
         <v>154</v>
@@ -13244,16 +13232,16 @@
         <v>165</v>
       </c>
       <c r="V161" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25161940972</v>
       </c>
       <c r="W161">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X161" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Y161" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AB161">
         <v>0</v>
@@ -13262,24 +13250,24 @@
         <v>154</v>
       </c>
       <c r="AH161" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI161" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="162" spans="1:35">
       <c r="A162">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B162" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C162" t="s">
         <v>50</v>
       </c>
       <c r="D162" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E162" t="s">
         <v>54</v>
@@ -13309,7 +13297,7 @@
         <v>2026</v>
       </c>
       <c r="R162">
-        <v>18056705</v>
+        <v>17941156</v>
       </c>
       <c r="S162" t="s">
         <v>154</v>
@@ -13318,13 +13306,13 @@
         <v>165</v>
       </c>
       <c r="V162" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25232392361</v>
       </c>
       <c r="W162">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X162" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Y162" t="s">
         <v>224</v>
@@ -13336,18 +13324,18 @@
         <v>154</v>
       </c>
       <c r="AH162" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI162" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="163" spans="1:35">
       <c r="A163">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B163" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C163" t="s">
         <v>50</v>
@@ -13359,7 +13347,7 @@
         <v>54</v>
       </c>
       <c r="F163" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G163">
         <v>951</v>
@@ -13383,7 +13371,7 @@
         <v>2026</v>
       </c>
       <c r="R163">
-        <v>18164501</v>
+        <v>18056705</v>
       </c>
       <c r="S163" t="s">
         <v>154</v>
@@ -13392,16 +13380,16 @@
         <v>165</v>
       </c>
       <c r="V163" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W163">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X163" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y163" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AB163">
         <v>0</v>
@@ -13410,33 +13398,33 @@
         <v>154</v>
       </c>
       <c r="AH163" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI163" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="164" spans="1:35">
       <c r="A164">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B164" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C164" t="s">
         <v>50</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E164" t="s">
         <v>54</v>
       </c>
       <c r="F164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G164">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -13445,10 +13433,10 @@
         <v>64</v>
       </c>
       <c r="J164" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N164" s="1">
-        <v>46290</v>
+        <v>46275</v>
       </c>
       <c r="P164">
         <v>8</v>
@@ -13457,7 +13445,7 @@
         <v>2026</v>
       </c>
       <c r="R164">
-        <v>17398883</v>
+        <v>18164501</v>
       </c>
       <c r="S164" t="s">
         <v>154</v>
@@ -13466,16 +13454,16 @@
         <v>165</v>
       </c>
       <c r="V164" s="1">
-        <v>46266.25305</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W164">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="X164" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Y164" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AB164">
         <v>0</v>
@@ -13484,24 +13472,24 @@
         <v>154</v>
       </c>
       <c r="AH164" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI164" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="165" spans="1:35">
       <c r="A165">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B165" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C165" t="s">
         <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E165" t="s">
         <v>54</v>
@@ -13531,7 +13519,7 @@
         <v>2026</v>
       </c>
       <c r="R165">
-        <v>16962107</v>
+        <v>17398883</v>
       </c>
       <c r="S165" t="s">
         <v>154</v>
@@ -13540,16 +13528,16 @@
         <v>165</v>
       </c>
       <c r="V165" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25305</v>
       </c>
       <c r="W165">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="X165" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y165" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AB165">
         <v>0</v>
@@ -13558,27 +13546,27 @@
         <v>154</v>
       </c>
       <c r="AH165" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI165" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="166" spans="1:35">
       <c r="A166">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B166" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C166" t="s">
         <v>50</v>
       </c>
       <c r="D166" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E166" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F166" t="s">
         <v>56</v>
@@ -13605,7 +13593,7 @@
         <v>2026</v>
       </c>
       <c r="R166">
-        <v>17042317</v>
+        <v>16962107</v>
       </c>
       <c r="S166" t="s">
         <v>154</v>
@@ -13614,16 +13602,16 @@
         <v>165</v>
       </c>
       <c r="V166" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W166">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="X166" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="Y166" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AB166">
         <v>0</v>
@@ -13632,27 +13620,27 @@
         <v>154</v>
       </c>
       <c r="AH166" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI166" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="167" spans="1:35">
       <c r="A167">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B167" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C167" t="s">
         <v>50</v>
       </c>
       <c r="D167" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E167" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F167" t="s">
         <v>56</v>
@@ -13679,7 +13667,7 @@
         <v>2026</v>
       </c>
       <c r="R167">
-        <v>17941166</v>
+        <v>17042317</v>
       </c>
       <c r="S167" t="s">
         <v>154</v>
@@ -13688,16 +13676,16 @@
         <v>165</v>
       </c>
       <c r="V167" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W167">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="X167" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Y167" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AB167">
         <v>0</v>
@@ -13706,30 +13694,30 @@
         <v>154</v>
       </c>
       <c r="AH167" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI167" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="168" spans="1:35">
       <c r="A168">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B168" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C168" t="s">
         <v>50</v>
       </c>
       <c r="D168" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E168" t="s">
         <v>54</v>
       </c>
       <c r="F168" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G168">
         <v>953</v>
@@ -13753,7 +13741,7 @@
         <v>2026</v>
       </c>
       <c r="R168">
-        <v>18178144</v>
+        <v>17941166</v>
       </c>
       <c r="S168" t="s">
         <v>154</v>
@@ -13762,16 +13750,16 @@
         <v>165</v>
       </c>
       <c r="V168" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W168">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="X168" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y168" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB168">
         <v>0</v>
@@ -13780,18 +13768,18 @@
         <v>154</v>
       </c>
       <c r="AH168" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI168" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="169" spans="1:35">
       <c r="A169">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B169" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C169" t="s">
         <v>50</v>
@@ -13803,10 +13791,10 @@
         <v>54</v>
       </c>
       <c r="F169" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G169">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -13815,10 +13803,10 @@
         <v>64</v>
       </c>
       <c r="J169" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N169" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="P169">
         <v>8</v>
@@ -13827,7 +13815,7 @@
         <v>2026</v>
       </c>
       <c r="R169">
-        <v>17399270</v>
+        <v>18178144</v>
       </c>
       <c r="S169" t="s">
         <v>154</v>
@@ -13836,16 +13824,16 @@
         <v>165</v>
       </c>
       <c r="V169" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W169">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="X169" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y169" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AB169">
         <v>0</v>
@@ -13854,18 +13842,18 @@
         <v>154</v>
       </c>
       <c r="AH169" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI169" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="170" spans="1:35">
       <c r="A170">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B170" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C170" t="s">
         <v>50</v>
@@ -13874,7 +13862,7 @@
         <v>51</v>
       </c>
       <c r="E170" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F170" t="s">
         <v>56</v>
@@ -13901,7 +13889,7 @@
         <v>2026</v>
       </c>
       <c r="R170">
-        <v>17042505</v>
+        <v>17399270</v>
       </c>
       <c r="S170" t="s">
         <v>154</v>
@@ -13910,16 +13898,16 @@
         <v>165</v>
       </c>
       <c r="V170" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W170">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X170" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="Y170" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AB170">
         <v>0</v>
@@ -13928,18 +13916,18 @@
         <v>154</v>
       </c>
       <c r="AH170" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI170" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="171" spans="1:35">
       <c r="A171">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B171" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C171" t="s">
         <v>50</v>
@@ -13948,7 +13936,7 @@
         <v>51</v>
       </c>
       <c r="E171" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F171" t="s">
         <v>56</v>
@@ -13975,7 +13963,7 @@
         <v>2026</v>
       </c>
       <c r="R171">
-        <v>17952421</v>
+        <v>17042505</v>
       </c>
       <c r="S171" t="s">
         <v>154</v>
@@ -13984,16 +13972,16 @@
         <v>165</v>
       </c>
       <c r="V171" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W171">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X171" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y171" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AB171">
         <v>0</v>
@@ -14002,18 +13990,18 @@
         <v>154</v>
       </c>
       <c r="AH171" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI171" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:35">
       <c r="A172">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B172" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
         <v>50</v>
@@ -14025,7 +14013,7 @@
         <v>54</v>
       </c>
       <c r="F172" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G172">
         <v>7022</v>
@@ -14049,7 +14037,7 @@
         <v>2026</v>
       </c>
       <c r="R172">
-        <v>18178174</v>
+        <v>17952421</v>
       </c>
       <c r="S172" t="s">
         <v>154</v>
@@ -14058,16 +14046,16 @@
         <v>165</v>
       </c>
       <c r="V172" s="1">
-        <v>46266.25369988426</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W172">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="X172" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y172" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB172">
         <v>0</v>
@@ -14076,18 +14064,18 @@
         <v>154</v>
       </c>
       <c r="AH172" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AI172" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="173" spans="1:35">
       <c r="A173">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B173" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C173" t="s">
         <v>50</v>
@@ -14099,10 +14087,10 @@
         <v>54</v>
       </c>
       <c r="F173" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G173">
-        <v>9085</v>
+        <v>7022</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -14111,40 +14099,37 @@
         <v>64</v>
       </c>
       <c r="J173" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N173" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O173" t="s">
-        <v>126</v>
+        <v>46283</v>
       </c>
       <c r="P173">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q173">
         <v>2026</v>
       </c>
       <c r="R173">
-        <v>17399353</v>
+        <v>18178174</v>
       </c>
       <c r="S173" t="s">
         <v>154</v>
       </c>
       <c r="U173" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V173" s="1">
-        <v>46268.62318445602</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W173">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="X173" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y173" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB173">
         <v>0</v>
@@ -14153,24 +14138,24 @@
         <v>154</v>
       </c>
       <c r="AH173" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AI173" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="174" spans="1:35">
       <c r="A174">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B174" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C174" t="s">
         <v>50</v>
       </c>
       <c r="D174" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E174" t="s">
         <v>54</v>
@@ -14203,7 +14188,7 @@
         <v>2026</v>
       </c>
       <c r="R174">
-        <v>16962370</v>
+        <v>17399353</v>
       </c>
       <c r="S174" t="s">
         <v>154</v>
@@ -14212,16 +14197,16 @@
         <v>166</v>
       </c>
       <c r="V174" s="1">
-        <v>46268.62319864584</v>
+        <v>46268.62318445602</v>
       </c>
       <c r="W174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X174" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y174" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB174">
         <v>0</v>
@@ -14230,24 +14215,24 @@
         <v>154</v>
       </c>
       <c r="AH174" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI174" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="175" spans="1:35">
       <c r="A175">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B175" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C175" t="s">
         <v>50</v>
       </c>
       <c r="D175" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E175" t="s">
         <v>54</v>
@@ -14280,7 +14265,7 @@
         <v>2026</v>
       </c>
       <c r="R175">
-        <v>16976260</v>
+        <v>16962370</v>
       </c>
       <c r="S175" t="s">
         <v>154</v>
@@ -14289,13 +14274,13 @@
         <v>166</v>
       </c>
       <c r="V175" s="1">
-        <v>46268.62320026621</v>
+        <v>46268.62319864584</v>
       </c>
       <c r="W175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X175" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Y175" t="s">
         <v>236</v>
@@ -14307,18 +14292,18 @@
         <v>154</v>
       </c>
       <c r="AH175" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI175" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:35">
       <c r="A176">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B176" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C176" t="s">
         <v>50</v>
@@ -14357,7 +14342,7 @@
         <v>2026</v>
       </c>
       <c r="R176">
-        <v>17222852</v>
+        <v>16976260</v>
       </c>
       <c r="S176" t="s">
         <v>154</v>
@@ -14366,13 +14351,13 @@
         <v>166</v>
       </c>
       <c r="V176" s="1">
-        <v>46268.62320177083</v>
+        <v>46268.62320026621</v>
       </c>
       <c r="W176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X176" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Y176" t="s">
         <v>236</v>
@@ -14384,18 +14369,18 @@
         <v>154</v>
       </c>
       <c r="AH176" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI176" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="177" spans="1:35">
       <c r="A177">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B177" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C177" t="s">
         <v>50</v>
@@ -14404,7 +14389,7 @@
         <v>51</v>
       </c>
       <c r="E177" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F177" t="s">
         <v>56</v>
@@ -14434,7 +14419,7 @@
         <v>2026</v>
       </c>
       <c r="R177">
-        <v>17042569</v>
+        <v>17222852</v>
       </c>
       <c r="S177" t="s">
         <v>154</v>
@@ -14443,13 +14428,13 @@
         <v>166</v>
       </c>
       <c r="V177" s="1">
-        <v>46268.62320378472</v>
+        <v>46268.62320177083</v>
       </c>
       <c r="W177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X177" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y177" t="s">
         <v>236</v>
@@ -14461,24 +14446,24 @@
         <v>154</v>
       </c>
       <c r="AH177" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI177" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="178" spans="1:35">
       <c r="A178">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B178" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C178" t="s">
         <v>50</v>
       </c>
       <c r="D178" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E178" t="s">
         <v>55</v>
@@ -14511,7 +14496,7 @@
         <v>2026</v>
       </c>
       <c r="R178">
-        <v>16960062</v>
+        <v>17042569</v>
       </c>
       <c r="S178" t="s">
         <v>154</v>
@@ -14520,10 +14505,10 @@
         <v>166</v>
       </c>
       <c r="V178" s="1">
-        <v>46268.62320393518</v>
+        <v>46268.62320378472</v>
       </c>
       <c r="W178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X178" t="s">
         <v>168</v>
@@ -14538,27 +14523,27 @@
         <v>154</v>
       </c>
       <c r="AH178" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI178" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="179" spans="1:35">
       <c r="A179">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B179" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C179" t="s">
         <v>50</v>
       </c>
       <c r="D179" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E179" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F179" t="s">
         <v>56</v>
@@ -14588,7 +14573,7 @@
         <v>2026</v>
       </c>
       <c r="R179">
-        <v>17941207</v>
+        <v>16960062</v>
       </c>
       <c r="S179" t="s">
         <v>154</v>
@@ -14597,13 +14582,13 @@
         <v>166</v>
       </c>
       <c r="V179" s="1">
-        <v>46268.62320697917</v>
+        <v>46268.62320393518</v>
       </c>
       <c r="W179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X179" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Y179" t="s">
         <v>236</v>
@@ -14615,24 +14600,24 @@
         <v>154</v>
       </c>
       <c r="AH179" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI179" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" spans="1:35">
       <c r="A180">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C180" t="s">
         <v>50</v>
       </c>
       <c r="D180" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E180" t="s">
         <v>54</v>
@@ -14665,7 +14650,7 @@
         <v>2026</v>
       </c>
       <c r="R180">
-        <v>17952433</v>
+        <v>17941207</v>
       </c>
       <c r="S180" t="s">
         <v>154</v>
@@ -14674,13 +14659,13 @@
         <v>166</v>
       </c>
       <c r="V180" s="1">
-        <v>46268.62320717592</v>
+        <v>46268.62320697917</v>
       </c>
       <c r="W180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X180" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Y180" t="s">
         <v>236</v>
@@ -14692,24 +14677,24 @@
         <v>154</v>
       </c>
       <c r="AH180" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI180" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="181" spans="1:35">
       <c r="A181">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B181" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C181" t="s">
         <v>50</v>
       </c>
       <c r="D181" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E181" t="s">
         <v>54</v>
@@ -14742,7 +14727,7 @@
         <v>2026</v>
       </c>
       <c r="R181">
-        <v>17952613</v>
+        <v>17952433</v>
       </c>
       <c r="S181" t="s">
         <v>154</v>
@@ -14751,10 +14736,10 @@
         <v>166</v>
       </c>
       <c r="V181" s="1">
-        <v>46268.62320732639</v>
+        <v>46268.62320717592</v>
       </c>
       <c r="W181">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X181" t="s">
         <v>172</v>
@@ -14769,18 +14754,18 @@
         <v>154</v>
       </c>
       <c r="AH181" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI181" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:35">
       <c r="A182">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C182" t="s">
         <v>50</v>
@@ -14819,7 +14804,7 @@
         <v>2026</v>
       </c>
       <c r="R182">
-        <v>18056791</v>
+        <v>17952613</v>
       </c>
       <c r="S182" t="s">
         <v>154</v>
@@ -14828,10 +14813,10 @@
         <v>166</v>
       </c>
       <c r="V182" s="1">
-        <v>46268.62320810185</v>
+        <v>46268.62320732639</v>
       </c>
       <c r="W182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X182" t="s">
         <v>172</v>
@@ -14846,18 +14831,18 @@
         <v>154</v>
       </c>
       <c r="AH182" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI182" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:35">
       <c r="A183">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B183" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C183" t="s">
         <v>50</v>
@@ -14869,7 +14854,7 @@
         <v>54</v>
       </c>
       <c r="F183" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G183">
         <v>9085</v>
@@ -14896,7 +14881,7 @@
         <v>2026</v>
       </c>
       <c r="R183">
-        <v>18164544</v>
+        <v>18056791</v>
       </c>
       <c r="S183" t="s">
         <v>154</v>
@@ -14905,13 +14890,13 @@
         <v>166</v>
       </c>
       <c r="V183" s="1">
-        <v>46268.6232125</v>
+        <v>46268.62320810185</v>
       </c>
       <c r="W183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X183" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y183" t="s">
         <v>236</v>
@@ -14923,24 +14908,24 @@
         <v>154</v>
       </c>
       <c r="AH183" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI183" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184" spans="1:35">
       <c r="A184">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B184" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C184" t="s">
         <v>50</v>
       </c>
       <c r="D184" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E184" t="s">
         <v>54</v>
@@ -14973,7 +14958,7 @@
         <v>2026</v>
       </c>
       <c r="R184">
-        <v>18178181</v>
+        <v>18164544</v>
       </c>
       <c r="S184" t="s">
         <v>154</v>
@@ -14982,13 +14967,13 @@
         <v>166</v>
       </c>
       <c r="V184" s="1">
-        <v>46268.62321412037</v>
+        <v>46268.6232125</v>
       </c>
       <c r="W184">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X184" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y184" t="s">
         <v>236</v>
@@ -15000,24 +14985,24 @@
         <v>154</v>
       </c>
       <c r="AH184" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI184" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="185" spans="1:35">
       <c r="A185">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
       </c>
       <c r="D185" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E185" t="s">
         <v>54</v>
@@ -15050,7 +15035,7 @@
         <v>2026</v>
       </c>
       <c r="R185">
-        <v>18188767</v>
+        <v>18178181</v>
       </c>
       <c r="S185" t="s">
         <v>154</v>
@@ -15059,13 +15044,13 @@
         <v>166</v>
       </c>
       <c r="V185" s="1">
-        <v>46268.6232128125</v>
+        <v>46268.62321412037</v>
       </c>
       <c r="W185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X185" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y185" t="s">
         <v>236</v>
@@ -15077,18 +15062,18 @@
         <v>154</v>
       </c>
       <c r="AH185" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI185" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="186" spans="1:35">
       <c r="A186">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C186" t="s">
         <v>50</v>
@@ -15127,7 +15112,7 @@
         <v>2026</v>
       </c>
       <c r="R186">
-        <v>18188673</v>
+        <v>18188767</v>
       </c>
       <c r="S186" t="s">
         <v>154</v>
@@ -15136,10 +15121,10 @@
         <v>166</v>
       </c>
       <c r="V186" s="1">
-        <v>46268.62321296296</v>
+        <v>46268.6232128125</v>
       </c>
       <c r="W186">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X186" t="s">
         <v>171</v>
@@ -15154,33 +15139,33 @@
         <v>154</v>
       </c>
       <c r="AH186" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI186" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="187" spans="1:35">
       <c r="A187">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C187" t="s">
         <v>50</v>
       </c>
       <c r="D187" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E187" t="s">
         <v>54</v>
       </c>
       <c r="F187" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G187">
-        <v>5989</v>
+        <v>9085</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -15189,10 +15174,13 @@
         <v>64</v>
       </c>
       <c r="J187" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N187" s="1">
-        <v>46273</v>
+        <v>46268</v>
+      </c>
+      <c r="O187" t="s">
+        <v>126</v>
       </c>
       <c r="P187">
         <v>9</v>
@@ -15201,22 +15189,25 @@
         <v>2026</v>
       </c>
       <c r="R187">
-        <v>17399127</v>
+        <v>18188673</v>
       </c>
       <c r="S187" t="s">
         <v>154</v>
       </c>
       <c r="U187" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V187" s="1">
-        <v>46269.41908927084</v>
+        <v>46268.62321296296</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X187" t="s">
-        <v>173</v>
+        <v>171</v>
+      </c>
+      <c r="Y187" t="s">
+        <v>236</v>
       </c>
       <c r="AB187">
         <v>0</v>
@@ -15225,24 +15216,24 @@
         <v>154</v>
       </c>
       <c r="AH187" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI187" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:35">
       <c r="A188">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B188" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C188" t="s">
         <v>50</v>
       </c>
       <c r="D188" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E188" t="s">
         <v>54</v>
@@ -15272,7 +15263,7 @@
         <v>2026</v>
       </c>
       <c r="R188">
-        <v>16962251</v>
+        <v>17399127</v>
       </c>
       <c r="S188" t="s">
         <v>154</v>
@@ -15281,13 +15272,13 @@
         <v>165</v>
       </c>
       <c r="V188" s="1">
-        <v>46269.41910457176</v>
+        <v>46269.41908927084</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X188" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AB188">
         <v>0</v>
@@ -15296,24 +15287,24 @@
         <v>154</v>
       </c>
       <c r="AH188" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI188" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="189" spans="1:35">
       <c r="A189">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B189" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C189" t="s">
         <v>50</v>
       </c>
       <c r="D189" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E189" t="s">
         <v>54</v>
@@ -15343,7 +15334,7 @@
         <v>2026</v>
       </c>
       <c r="R189">
-        <v>16976117</v>
+        <v>16962251</v>
       </c>
       <c r="S189" t="s">
         <v>154</v>
@@ -15352,13 +15343,13 @@
         <v>165</v>
       </c>
       <c r="V189" s="1">
-        <v>46269.37885223379</v>
+        <v>46269.41910457176</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X189" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AB189">
         <v>0</v>
@@ -15367,18 +15358,18 @@
         <v>154</v>
       </c>
       <c r="AH189" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI189" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="190" spans="1:35">
       <c r="A190">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B190" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C190" t="s">
         <v>50</v>
@@ -15414,7 +15405,7 @@
         <v>2026</v>
       </c>
       <c r="R190">
-        <v>17222714</v>
+        <v>16976117</v>
       </c>
       <c r="S190" t="s">
         <v>154</v>
@@ -15423,13 +15414,13 @@
         <v>165</v>
       </c>
       <c r="V190" s="1">
-        <v>46269.3782503125</v>
+        <v>46269.37885223379</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X190" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AB190">
         <v>0</v>
@@ -15438,18 +15429,18 @@
         <v>154</v>
       </c>
       <c r="AH190" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI190" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:35">
       <c r="A191">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B191" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C191" t="s">
         <v>50</v>
@@ -15458,7 +15449,7 @@
         <v>51</v>
       </c>
       <c r="E191" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F191" t="s">
         <v>56</v>
@@ -15485,7 +15476,7 @@
         <v>2026</v>
       </c>
       <c r="R191">
-        <v>17042423</v>
+        <v>17222714</v>
       </c>
       <c r="S191" t="s">
         <v>154</v>
@@ -15494,13 +15485,13 @@
         <v>165</v>
       </c>
       <c r="V191" s="1">
-        <v>46269.41913152778</v>
+        <v>46269.3782503125</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X191" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB191">
         <v>0</v>
@@ -15509,24 +15500,24 @@
         <v>154</v>
       </c>
       <c r="AH191" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI191" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="192" spans="1:35">
       <c r="A192">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B192" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C192" t="s">
         <v>50</v>
       </c>
       <c r="D192" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E192" t="s">
         <v>55</v>
@@ -15556,7 +15547,7 @@
         <v>2026</v>
       </c>
       <c r="R192">
-        <v>16959989</v>
+        <v>17042423</v>
       </c>
       <c r="S192" t="s">
         <v>154</v>
@@ -15565,10 +15556,10 @@
         <v>165</v>
       </c>
       <c r="V192" s="1">
-        <v>46269.41913775463</v>
+        <v>46269.41913152778</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X192" t="s">
         <v>168</v>
@@ -15580,45 +15571,45 @@
         <v>154</v>
       </c>
       <c r="AH192" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI192" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="193" spans="1:35">
       <c r="A193">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B193" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E193" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F193" t="s">
         <v>56</v>
       </c>
       <c r="G193">
-        <v>9087</v>
+        <v>5989</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J193" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N193" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="P193">
         <v>9</v>
@@ -15627,48 +15618,48 @@
         <v>2026</v>
       </c>
       <c r="R193">
-        <v>17399373</v>
+        <v>16959989</v>
       </c>
       <c r="S193" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="U193" t="s">
         <v>165</v>
       </c>
       <c r="V193" s="1">
-        <v>46268.7596207176</v>
+        <v>46269.41913775463</v>
       </c>
       <c r="W193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X193" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="AB193">
         <v>0</v>
       </c>
       <c r="AC193" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="AH193" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI193" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="194" spans="1:35">
       <c r="A194">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B194" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C194" t="s">
         <v>50</v>
       </c>
       <c r="D194" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E194" t="s">
         <v>54</v>
@@ -15698,7 +15689,7 @@
         <v>2026</v>
       </c>
       <c r="R194">
-        <v>16962390</v>
+        <v>17399373</v>
       </c>
       <c r="S194" t="s">
         <v>54</v>
@@ -15707,13 +15698,13 @@
         <v>165</v>
       </c>
       <c r="V194" s="1">
-        <v>46268.75963109954</v>
+        <v>46268.7596207176</v>
       </c>
       <c r="W194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X194" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AB194">
         <v>0</v>
@@ -15722,24 +15713,24 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI194" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="195" spans="1:35">
       <c r="A195">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C195" t="s">
         <v>50</v>
       </c>
       <c r="D195" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E195" t="s">
         <v>54</v>
@@ -15769,7 +15760,7 @@
         <v>2026</v>
       </c>
       <c r="R195">
-        <v>16976280</v>
+        <v>16962390</v>
       </c>
       <c r="S195" t="s">
         <v>54</v>
@@ -15778,13 +15769,13 @@
         <v>165</v>
       </c>
       <c r="V195" s="1">
-        <v>46268.75963225694</v>
+        <v>46268.75963109954</v>
       </c>
       <c r="W195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X195" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AB195">
         <v>0</v>
@@ -15793,18 +15784,18 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI195" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="196" spans="1:35">
       <c r="A196">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B196" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C196" t="s">
         <v>50</v>
@@ -15840,7 +15831,7 @@
         <v>2026</v>
       </c>
       <c r="R196">
-        <v>17222885</v>
+        <v>16976280</v>
       </c>
       <c r="S196" t="s">
         <v>54</v>
@@ -15849,13 +15840,13 @@
         <v>165</v>
       </c>
       <c r="V196" s="1">
-        <v>46268.75963348379</v>
+        <v>46268.75963225694</v>
       </c>
       <c r="W196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X196" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AB196">
         <v>0</v>
@@ -15864,18 +15855,18 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI196" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="197" spans="1:35">
       <c r="A197">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B197" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C197" t="s">
         <v>50</v>
@@ -15884,7 +15875,7 @@
         <v>51</v>
       </c>
       <c r="E197" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F197" t="s">
         <v>56</v>
@@ -15911,48 +15902,48 @@
         <v>2026</v>
       </c>
       <c r="R197">
-        <v>17042605</v>
+        <v>17222885</v>
       </c>
       <c r="S197" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U197" t="s">
         <v>165</v>
       </c>
       <c r="V197" s="1">
-        <v>46268.75963414352</v>
+        <v>46268.75963348379</v>
       </c>
       <c r="W197">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X197" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB197">
         <v>0</v>
       </c>
       <c r="AC197" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI197" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="198" spans="1:35">
       <c r="A198">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C198" t="s">
         <v>50</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198" t="s">
         <v>55</v>
@@ -15982,19 +15973,19 @@
         <v>2026</v>
       </c>
       <c r="R198">
-        <v>16960086</v>
+        <v>17042605</v>
       </c>
       <c r="S198" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="U198" t="s">
         <v>165</v>
       </c>
       <c r="V198" s="1">
-        <v>46268.62326365741</v>
+        <v>46268.75963414352</v>
       </c>
       <c r="W198">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X198" t="s">
         <v>168</v>
@@ -16003,30 +15994,30 @@
         <v>0</v>
       </c>
       <c r="AC198" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="AH198" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI198" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="199" spans="1:35">
       <c r="A199">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B199" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C199" t="s">
         <v>50</v>
       </c>
       <c r="D199" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E199" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F199" t="s">
         <v>56</v>
@@ -16053,48 +16044,48 @@
         <v>2026</v>
       </c>
       <c r="R199">
-        <v>17941227</v>
+        <v>16960086</v>
       </c>
       <c r="S199" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U199" t="s">
         <v>165</v>
       </c>
       <c r="V199" s="1">
-        <v>46268.75963472222</v>
+        <v>46268.62326365741</v>
       </c>
       <c r="W199">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X199" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AB199">
         <v>0</v>
       </c>
       <c r="AC199" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH199" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI199" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="200" spans="1:35">
       <c r="A200">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C200" t="s">
         <v>50</v>
       </c>
       <c r="D200" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E200" t="s">
         <v>54</v>
@@ -16124,7 +16115,7 @@
         <v>2026</v>
       </c>
       <c r="R200">
-        <v>17952455</v>
+        <v>17941227</v>
       </c>
       <c r="S200" t="s">
         <v>54</v>
@@ -16133,13 +16124,13 @@
         <v>165</v>
       </c>
       <c r="V200" s="1">
-        <v>46268.75963475694</v>
+        <v>46268.75963472222</v>
       </c>
       <c r="W200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X200" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AB200">
         <v>0</v>
@@ -16148,24 +16139,24 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI200" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:35">
       <c r="A201">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B201" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
       </c>
       <c r="D201" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E201" t="s">
         <v>54</v>
@@ -16195,7 +16186,7 @@
         <v>2026</v>
       </c>
       <c r="R201">
-        <v>17952635</v>
+        <v>17952455</v>
       </c>
       <c r="S201" t="s">
         <v>54</v>
@@ -16204,10 +16195,10 @@
         <v>165</v>
       </c>
       <c r="V201" s="1">
-        <v>46268.75963506944</v>
+        <v>46268.75963475694</v>
       </c>
       <c r="W201">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X201" t="s">
         <v>172</v>
@@ -16219,18 +16210,18 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI201" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="202" spans="1:35">
       <c r="A202">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C202" t="s">
         <v>50</v>
@@ -16266,19 +16257,19 @@
         <v>2026</v>
       </c>
       <c r="R202">
-        <v>18056811</v>
+        <v>17952635</v>
       </c>
       <c r="S202" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U202" t="s">
         <v>165</v>
       </c>
       <c r="V202" s="1">
-        <v>46268.7596360301</v>
+        <v>46268.75963506944</v>
       </c>
       <c r="W202">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X202" t="s">
         <v>172</v>
@@ -16287,21 +16278,21 @@
         <v>0</v>
       </c>
       <c r="AC202" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI202" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="203" spans="1:35">
       <c r="A203">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B203" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C203" t="s">
         <v>50</v>
@@ -16313,7 +16304,7 @@
         <v>54</v>
       </c>
       <c r="F203" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G203">
         <v>9087</v>
@@ -16337,48 +16328,48 @@
         <v>2026</v>
       </c>
       <c r="R203">
-        <v>18164558</v>
+        <v>18056811</v>
       </c>
       <c r="S203" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U203" t="s">
         <v>165</v>
       </c>
       <c r="V203" s="1">
-        <v>46268.62327121528</v>
+        <v>46268.7596360301</v>
       </c>
       <c r="W203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X203" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB203">
         <v>0</v>
       </c>
       <c r="AC203" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH203" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI203" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="204" spans="1:35">
       <c r="A204">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B204" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C204" t="s">
         <v>50</v>
       </c>
       <c r="D204" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E204" t="s">
         <v>54</v>
@@ -16408,48 +16399,48 @@
         <v>2026</v>
       </c>
       <c r="R204">
-        <v>18178193</v>
+        <v>18164558</v>
       </c>
       <c r="S204" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U204" t="s">
         <v>165</v>
       </c>
       <c r="V204" s="1">
-        <v>46268.75963931713</v>
+        <v>46268.62327121528</v>
       </c>
       <c r="W204">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X204" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB204">
         <v>0</v>
       </c>
       <c r="AC204" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI204" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="205" spans="1:35">
       <c r="A205">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B205" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C205" t="s">
         <v>50</v>
       </c>
       <c r="D205" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E205" t="s">
         <v>54</v>
@@ -16479,42 +16470,42 @@
         <v>2026</v>
       </c>
       <c r="R205">
-        <v>18188781</v>
+        <v>18178193</v>
       </c>
       <c r="S205" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U205" t="s">
         <v>165</v>
       </c>
       <c r="V205" s="1">
-        <v>46268.75963822917</v>
+        <v>46268.75963931713</v>
       </c>
       <c r="W205">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X205" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AB205">
         <v>0</v>
       </c>
       <c r="AC205" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH205" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI205" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="206" spans="1:35">
       <c r="A206">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B206" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C206" t="s">
         <v>50</v>
@@ -16550,7 +16541,7 @@
         <v>2026</v>
       </c>
       <c r="R206">
-        <v>18188687</v>
+        <v>18188781</v>
       </c>
       <c r="S206" t="s">
         <v>54</v>
@@ -16559,10 +16550,10 @@
         <v>165</v>
       </c>
       <c r="V206" s="1">
-        <v>46268.75963857639</v>
+        <v>46268.75963822917</v>
       </c>
       <c r="W206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X206" t="s">
         <v>171</v>
@@ -16574,33 +16565,33 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI206" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="207" spans="1:35">
       <c r="A207">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B207" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C207" t="s">
         <v>50</v>
       </c>
       <c r="D207" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E207" t="s">
         <v>54</v>
       </c>
       <c r="F207" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G207">
-        <v>6215</v>
+        <v>9087</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -16609,10 +16600,10 @@
         <v>65</v>
       </c>
       <c r="J207" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N207" s="1">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="P207">
         <v>9</v>
@@ -16621,7 +16612,7 @@
         <v>2026</v>
       </c>
       <c r="R207">
-        <v>17399147</v>
+        <v>18188687</v>
       </c>
       <c r="S207" t="s">
         <v>54</v>
@@ -16630,13 +16621,13 @@
         <v>165</v>
       </c>
       <c r="V207" s="1">
-        <v>46269.41908901621</v>
+        <v>46268.75963857639</v>
       </c>
       <c r="W207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X207" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AB207">
         <v>0</v>
@@ -16645,24 +16636,24 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI207" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="208" spans="1:35">
       <c r="A208">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B208" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C208" t="s">
         <v>50</v>
       </c>
       <c r="D208" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E208" t="s">
         <v>54</v>
@@ -16692,7 +16683,7 @@
         <v>2026</v>
       </c>
       <c r="R208">
-        <v>16962265</v>
+        <v>17399147</v>
       </c>
       <c r="S208" t="s">
         <v>54</v>
@@ -16701,13 +16692,13 @@
         <v>165</v>
       </c>
       <c r="V208" s="1">
-        <v>46269.41910425926</v>
+        <v>46269.41908901621</v>
       </c>
       <c r="W208">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X208" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AB208">
         <v>0</v>
@@ -16716,24 +16707,24 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI208" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="209" spans="1:35">
       <c r="A209">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C209" t="s">
         <v>50</v>
       </c>
       <c r="D209" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E209" t="s">
         <v>54</v>
@@ -16763,7 +16754,7 @@
         <v>2026</v>
       </c>
       <c r="R209">
-        <v>16976127</v>
+        <v>16962265</v>
       </c>
       <c r="S209" t="s">
         <v>54</v>
@@ -16772,13 +16763,13 @@
         <v>165</v>
       </c>
       <c r="V209" s="1">
-        <v>46269.37890997685</v>
+        <v>46269.41910425926</v>
       </c>
       <c r="W209">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X209" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AB209">
         <v>0</v>
@@ -16787,18 +16778,18 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI209" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="210" spans="1:35">
       <c r="A210">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B210" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C210" t="s">
         <v>50</v>
@@ -16834,7 +16825,7 @@
         <v>2026</v>
       </c>
       <c r="R210">
-        <v>17222729</v>
+        <v>16976127</v>
       </c>
       <c r="S210" t="s">
         <v>54</v>
@@ -16843,13 +16834,13 @@
         <v>165</v>
       </c>
       <c r="V210" s="1">
-        <v>46269.37833320602</v>
+        <v>46269.37890997685</v>
       </c>
       <c r="W210">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X210" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AB210">
         <v>0</v>
@@ -16858,18 +16849,18 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI210" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="211" spans="1:35">
       <c r="A211">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B211" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C211" t="s">
         <v>50</v>
@@ -16878,7 +16869,7 @@
         <v>51</v>
       </c>
       <c r="E211" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F211" t="s">
         <v>56</v>
@@ -16905,48 +16896,48 @@
         <v>2026</v>
       </c>
       <c r="R211">
-        <v>17042445</v>
+        <v>17222729</v>
       </c>
       <c r="S211" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U211" t="s">
         <v>165</v>
       </c>
       <c r="V211" s="1">
-        <v>46269.41913112268</v>
+        <v>46269.37833320602</v>
       </c>
       <c r="W211">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X211" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB211">
         <v>0</v>
       </c>
       <c r="AC211" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI211" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="212" spans="1:35">
       <c r="A212">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B212" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C212" t="s">
         <v>50</v>
       </c>
       <c r="D212" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E212" t="s">
         <v>55</v>
@@ -16976,19 +16967,19 @@
         <v>2026</v>
       </c>
       <c r="R212">
-        <v>16960001</v>
+        <v>17042445</v>
       </c>
       <c r="S212" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="U212" t="s">
         <v>165</v>
       </c>
       <c r="V212" s="1">
-        <v>46269.41913740741</v>
+        <v>46269.41913112268</v>
       </c>
       <c r="W212">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X212" t="s">
         <v>168</v>
@@ -16997,36 +16988,36 @@
         <v>0</v>
       </c>
       <c r="AC212" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="AH212" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AI212" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="213" spans="1:35">
       <c r="A213">
-        <v>6404</v>
+        <v>6628</v>
       </c>
       <c r="B213" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C213" t="s">
         <v>50</v>
       </c>
       <c r="D213" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E213" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F213" t="s">
         <v>56</v>
       </c>
       <c r="G213">
-        <v>11001</v>
+        <v>6215</v>
       </c>
       <c r="H213">
         <v>0</v>
@@ -17035,49 +17026,46 @@
         <v>65</v>
       </c>
       <c r="J213" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="N213" s="1">
-        <v>46259</v>
+        <v>46274</v>
       </c>
       <c r="P213">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q213">
         <v>2026</v>
       </c>
       <c r="R213">
-        <v>16962453</v>
+        <v>16960001</v>
       </c>
       <c r="S213" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U213" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V213" s="1">
-        <v>46267.66131466435</v>
+        <v>46269.41913740741</v>
       </c>
       <c r="W213">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X213" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y213" t="s">
-        <v>237</v>
+        <v>168</v>
       </c>
       <c r="AB213">
         <v>0</v>
       </c>
       <c r="AC213" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH213" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AI213" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17112,34 +17100,34 @@
         <v>74</v>
       </c>
       <c r="N214" s="1">
-        <v>46321</v>
+        <v>46259</v>
       </c>
       <c r="P214">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q214">
         <v>2026</v>
       </c>
       <c r="R214">
-        <v>16962455</v>
+        <v>16962453</v>
       </c>
       <c r="S214" t="s">
         <v>54</v>
       </c>
       <c r="U214" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V214" s="1">
-        <v>46266.21595836805</v>
+        <v>46267.66131466435</v>
       </c>
       <c r="W214">
-        <v>-48</v>
+        <v>15</v>
       </c>
       <c r="X214" t="s">
         <v>177</v>
       </c>
       <c r="Y214" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB214">
         <v>0</v>
@@ -17148,24 +17136,24 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI214" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="215" spans="1:35">
       <c r="A215">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B215" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C215" t="s">
         <v>50</v>
       </c>
       <c r="D215" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E215" t="s">
         <v>54</v>
@@ -17174,7 +17162,7 @@
         <v>56</v>
       </c>
       <c r="G215">
-        <v>7877</v>
+        <v>11001</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -17183,7 +17171,7 @@
         <v>65</v>
       </c>
       <c r="J215" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N215" s="1">
         <v>46321</v>
@@ -17195,7 +17183,7 @@
         <v>2026</v>
       </c>
       <c r="R215">
-        <v>17399331</v>
+        <v>16962455</v>
       </c>
       <c r="S215" t="s">
         <v>54</v>
@@ -17204,16 +17192,16 @@
         <v>165</v>
       </c>
       <c r="V215" s="1">
-        <v>46266.21572962963</v>
+        <v>46266.21595836805</v>
       </c>
       <c r="W215">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="X215" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Y215" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AB215">
         <v>0</v>
@@ -17222,18 +17210,18 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI215" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="216" spans="1:35">
       <c r="A216">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C216" t="s">
         <v>50</v>
@@ -17248,7 +17236,7 @@
         <v>56</v>
       </c>
       <c r="G216">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -17257,7 +17245,7 @@
         <v>65</v>
       </c>
       <c r="J216" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="N216" s="1">
         <v>46321</v>
@@ -17269,7 +17257,7 @@
         <v>2026</v>
       </c>
       <c r="R216">
-        <v>16976322</v>
+        <v>17399331</v>
       </c>
       <c r="S216" t="s">
         <v>54</v>
@@ -17278,16 +17266,16 @@
         <v>165</v>
       </c>
       <c r="V216" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.21572962963</v>
       </c>
       <c r="W216">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="X216" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y216" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB216">
         <v>0</v>
@@ -17296,18 +17284,18 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI216" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="217" spans="1:35">
       <c r="A217">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B217" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C217" t="s">
         <v>50</v>
@@ -17322,7 +17310,7 @@
         <v>56</v>
       </c>
       <c r="G217">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H217">
         <v>0</v>
@@ -17331,7 +17319,7 @@
         <v>65</v>
       </c>
       <c r="J217" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N217" s="1">
         <v>46321</v>
@@ -17343,7 +17331,7 @@
         <v>2026</v>
       </c>
       <c r="R217">
-        <v>17399291</v>
+        <v>16976322</v>
       </c>
       <c r="S217" t="s">
         <v>54</v>
@@ -17352,13 +17340,16 @@
         <v>165</v>
       </c>
       <c r="V217" s="1">
-        <v>46266.00006921296</v>
+        <v>46266.21550011574</v>
       </c>
       <c r="W217">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="X217" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="Y217" t="s">
+        <v>240</v>
       </c>
       <c r="AB217">
         <v>0</v>
@@ -17367,24 +17358,24 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI217" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="218" spans="1:35">
       <c r="A218">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C218" t="s">
         <v>50</v>
       </c>
       <c r="D218" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E218" t="s">
         <v>54</v>
@@ -17414,7 +17405,7 @@
         <v>2026</v>
       </c>
       <c r="R218">
-        <v>16962349</v>
+        <v>17399291</v>
       </c>
       <c r="S218" t="s">
         <v>54</v>
@@ -17426,10 +17417,10 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W218">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="X218" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AB218">
         <v>0</v>
@@ -17438,24 +17429,24 @@
         <v>54</v>
       </c>
       <c r="AH218" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI218" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="219" spans="1:35">
       <c r="A219">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B219" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C219" t="s">
         <v>50</v>
       </c>
       <c r="D219" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E219" t="s">
         <v>54</v>
@@ -17476,34 +17467,31 @@
         <v>123</v>
       </c>
       <c r="N219" s="1">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="P219">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q219">
         <v>2026</v>
       </c>
       <c r="R219">
-        <v>16976236</v>
+        <v>16962349</v>
       </c>
       <c r="S219" t="s">
         <v>54</v>
       </c>
       <c r="U219" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V219" s="1">
-        <v>46269.57097615741</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W219">
-        <v>13</v>
+        <v>-47</v>
       </c>
       <c r="X219" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y219" t="s">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="AB219">
         <v>0</v>
@@ -17512,10 +17500,10 @@
         <v>54</v>
       </c>
       <c r="AH219" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI219" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17550,32 +17538,35 @@
         <v>123</v>
       </c>
       <c r="N220" s="1">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="P220">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q220">
         <v>2026</v>
       </c>
       <c r="R220">
-        <v>16976238</v>
+        <v>16976236</v>
       </c>
       <c r="S220" t="s">
         <v>54</v>
       </c>
       <c r="U220" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V220" s="1">
-        <v>46266.00006921296</v>
+        <v>46269.57097615741</v>
       </c>
       <c r="W220">
-        <v>-48</v>
+        <v>14</v>
       </c>
       <c r="X220" t="s">
         <v>174</v>
       </c>
+      <c r="Y220" t="s">
+        <v>241</v>
+      </c>
       <c r="AB220">
         <v>0</v>
       </c>
@@ -17583,84 +17574,380 @@
         <v>54</v>
       </c>
       <c r="AH220" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AI220" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="221" spans="1:35">
       <c r="A221">
+        <v>6486</v>
+      </c>
+      <c r="B221" t="s">
+        <v>44</v>
+      </c>
+      <c r="C221" t="s">
+        <v>50</v>
+      </c>
+      <c r="D221" t="s">
+        <v>51</v>
+      </c>
+      <c r="E221" t="s">
+        <v>54</v>
+      </c>
+      <c r="F221" t="s">
+        <v>56</v>
+      </c>
+      <c r="G221">
+        <v>7027</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221" t="s">
+        <v>65</v>
+      </c>
+      <c r="J221" t="s">
+        <v>123</v>
+      </c>
+      <c r="N221" s="1">
+        <v>46321</v>
+      </c>
+      <c r="P221">
+        <v>9</v>
+      </c>
+      <c r="Q221">
+        <v>2026</v>
+      </c>
+      <c r="R221">
+        <v>16976238</v>
+      </c>
+      <c r="S221" t="s">
+        <v>54</v>
+      </c>
+      <c r="U221" t="s">
+        <v>165</v>
+      </c>
+      <c r="V221" s="1">
+        <v>46266.00006921296</v>
+      </c>
+      <c r="W221">
+        <v>-47</v>
+      </c>
+      <c r="X221" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB221">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH221" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI221" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="222" spans="1:35">
+      <c r="A222">
         <v>6945</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B222" t="s">
         <v>39</v>
       </c>
-      <c r="C221" t="s">
-        <v>50</v>
-      </c>
-      <c r="D221" t="s">
+      <c r="C222" t="s">
+        <v>50</v>
+      </c>
+      <c r="D222" t="s">
         <v>52</v>
       </c>
-      <c r="E221" t="s">
-        <v>54</v>
-      </c>
-      <c r="F221" t="s">
+      <c r="E222" t="s">
+        <v>54</v>
+      </c>
+      <c r="F222" t="s">
         <v>57</v>
       </c>
-      <c r="G221">
+      <c r="G222">
         <v>11056</v>
       </c>
-      <c r="H221">
-        <v>0</v>
-      </c>
-      <c r="I221" t="s">
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222" t="s">
         <v>66</v>
       </c>
-      <c r="J221" t="s">
+      <c r="J222" t="s">
         <v>124</v>
       </c>
-      <c r="N221" s="1">
+      <c r="N222" s="1">
         <v>46269</v>
       </c>
-      <c r="O221" t="s">
+      <c r="O222" t="s">
         <v>127</v>
       </c>
-      <c r="P221">
+      <c r="P222">
         <v>8</v>
       </c>
-      <c r="Q221">
-        <v>2026</v>
-      </c>
-      <c r="R221">
+      <c r="Q222">
+        <v>2026</v>
+      </c>
+      <c r="R222">
         <v>18261776</v>
       </c>
-      <c r="U221" t="s">
+      <c r="U222" t="s">
         <v>166</v>
       </c>
-      <c r="V221" s="1">
+      <c r="V222" s="1">
         <v>46269.46753030093</v>
       </c>
-      <c r="W221">
-        <v>4</v>
-      </c>
-      <c r="X221" t="s">
+      <c r="W222">
+        <v>5</v>
+      </c>
+      <c r="X222" t="s">
         <v>170</v>
       </c>
-      <c r="Y221" t="s">
+      <c r="Y222" t="s">
         <v>242</v>
       </c>
-      <c r="AB221">
-        <v>0</v>
-      </c>
-      <c r="AC221" t="s">
-        <v>245</v>
-      </c>
-      <c r="AH221" t="s">
-        <v>246</v>
-      </c>
-      <c r="AI221" t="s">
+      <c r="AB222">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="s">
+        <v>247</v>
+      </c>
+      <c r="AH222" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI222" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="223" spans="1:35">
+      <c r="A223">
+        <v>6949</v>
+      </c>
+      <c r="B223" t="s">
+        <v>37</v>
+      </c>
+      <c r="C223" t="s">
+        <v>50</v>
+      </c>
+      <c r="D223" t="s">
+        <v>51</v>
+      </c>
+      <c r="E223" t="s">
+        <v>54</v>
+      </c>
+      <c r="F223" t="s">
+        <v>57</v>
+      </c>
+      <c r="G223">
+        <v>9746</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223" t="s">
+        <v>61</v>
+      </c>
+      <c r="J223" t="s">
+        <v>80</v>
+      </c>
+      <c r="N223" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P223">
+        <v>8</v>
+      </c>
+      <c r="Q223">
+        <v>2026</v>
+      </c>
+      <c r="R223">
+        <v>18190457</v>
+      </c>
+      <c r="S223" t="s">
+        <v>143</v>
+      </c>
+      <c r="T223" t="s">
+        <v>161</v>
+      </c>
+      <c r="U223" t="s">
+        <v>165</v>
+      </c>
+      <c r="V223" s="1">
+        <v>46274.34198912037</v>
+      </c>
+      <c r="W223">
+        <v>-1</v>
+      </c>
+      <c r="X223" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB223">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH223" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI223" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="224" spans="1:35">
+      <c r="A224">
+        <v>6627</v>
+      </c>
+      <c r="B224" t="s">
+        <v>36</v>
+      </c>
+      <c r="C224" t="s">
+        <v>50</v>
+      </c>
+      <c r="D224" t="s">
+        <v>51</v>
+      </c>
+      <c r="E224" t="s">
+        <v>55</v>
+      </c>
+      <c r="F224" t="s">
+        <v>56</v>
+      </c>
+      <c r="G224">
+        <v>1866</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224" t="s">
+        <v>62</v>
+      </c>
+      <c r="J224" t="s">
+        <v>100</v>
+      </c>
+      <c r="N224" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P224">
+        <v>8</v>
+      </c>
+      <c r="Q224">
+        <v>2026</v>
+      </c>
+      <c r="R224">
+        <v>17968368</v>
+      </c>
+      <c r="S224" t="s">
+        <v>149</v>
+      </c>
+      <c r="T224" t="s">
+        <v>149</v>
+      </c>
+      <c r="U224" t="s">
+        <v>166</v>
+      </c>
+      <c r="V224" s="1">
+        <v>46274.36843923611</v>
+      </c>
+      <c r="W224">
+        <v>0</v>
+      </c>
+      <c r="X224" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y224" t="s">
+        <v>243</v>
+      </c>
+      <c r="AB224">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH224" t="s">
         <v>249</v>
+      </c>
+      <c r="AI224" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="225" spans="1:35">
+      <c r="A225">
+        <v>6627</v>
+      </c>
+      <c r="B225" t="s">
+        <v>36</v>
+      </c>
+      <c r="C225" t="s">
+        <v>50</v>
+      </c>
+      <c r="D225" t="s">
+        <v>51</v>
+      </c>
+      <c r="E225" t="s">
+        <v>55</v>
+      </c>
+      <c r="F225" t="s">
+        <v>56</v>
+      </c>
+      <c r="G225">
+        <v>1867</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225" t="s">
+        <v>62</v>
+      </c>
+      <c r="J225" t="s">
+        <v>101</v>
+      </c>
+      <c r="N225" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P225">
+        <v>8</v>
+      </c>
+      <c r="Q225">
+        <v>2026</v>
+      </c>
+      <c r="R225">
+        <v>17968379</v>
+      </c>
+      <c r="S225" t="s">
+        <v>149</v>
+      </c>
+      <c r="T225" t="s">
+        <v>149</v>
+      </c>
+      <c r="U225" t="s">
+        <v>166</v>
+      </c>
+      <c r="V225" s="1">
+        <v>46274.36695243056</v>
+      </c>
+      <c r="W225">
+        <v>0</v>
+      </c>
+      <c r="X225" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB225">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH225" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI225" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3218" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="256">
   <si>
     <t>CodCliente</t>
   </si>
@@ -760,7 +760,17 @@
 Reunião confirmada pelo cliente - Data Comentário: 04/09/2026 11:03</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 - Data Comentário: 04/09/2026 16:13</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/09/2026 
+Em processamento. - Data Comentário: 04/09/2026 08:41</t>
+  </si>
+  <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 09/09/2026 10:17:37. - Data Comentário: 09/09/2026 10:12</t>
   </si>
   <si>
     <t>Karen Ribeiro</t>
@@ -1123,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI225"/>
+  <dimension ref="A1:AI238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1304,10 +1314,10 @@
         <v>132</v>
       </c>
       <c r="AH2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1381,10 +1391,10 @@
         <v>133</v>
       </c>
       <c r="AH3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1458,10 +1468,10 @@
         <v>132</v>
       </c>
       <c r="AH4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1532,10 +1542,10 @@
         <v>132</v>
       </c>
       <c r="AH5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1606,10 +1616,10 @@
         <v>133</v>
       </c>
       <c r="AH6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1680,10 +1690,10 @@
         <v>133</v>
       </c>
       <c r="AH7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1754,10 +1764,10 @@
         <v>134</v>
       </c>
       <c r="AH8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1828,10 +1838,10 @@
         <v>132</v>
       </c>
       <c r="AH9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1902,10 +1912,10 @@
         <v>135</v>
       </c>
       <c r="AH10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI10" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1976,10 +1986,10 @@
         <v>135</v>
       </c>
       <c r="AH11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2050,10 +2060,10 @@
         <v>136</v>
       </c>
       <c r="AH12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2121,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AH13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2195,13 +2205,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AH14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2269,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2334,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2405,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2482,10 +2492,10 @@
         <v>138</v>
       </c>
       <c r="AH18" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2559,10 +2569,10 @@
         <v>137</v>
       </c>
       <c r="AH19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI19" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2636,10 +2646,10 @@
         <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2713,10 +2723,10 @@
         <v>136</v>
       </c>
       <c r="AH21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI21" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2787,10 +2797,10 @@
         <v>139</v>
       </c>
       <c r="AH22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2861,10 +2871,10 @@
         <v>136</v>
       </c>
       <c r="AH23" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI23" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2935,10 +2945,10 @@
         <v>136</v>
       </c>
       <c r="AH24" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI24" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3009,10 +3019,10 @@
         <v>136</v>
       </c>
       <c r="AH25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI25" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3083,10 +3093,10 @@
         <v>137</v>
       </c>
       <c r="AH26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI26" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3157,10 +3167,10 @@
         <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3231,10 +3241,10 @@
         <v>136</v>
       </c>
       <c r="AH28" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI28" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3305,10 +3315,10 @@
         <v>136</v>
       </c>
       <c r="AH29" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI29" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3379,10 +3389,10 @@
         <v>140</v>
       </c>
       <c r="AH30" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI30" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3459,10 +3469,10 @@
         <v>141</v>
       </c>
       <c r="AH31" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI31" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3533,10 +3543,10 @@
         <v>142</v>
       </c>
       <c r="AH32" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI32" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3613,10 +3623,10 @@
         <v>143</v>
       </c>
       <c r="AH33" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI33" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3690,10 +3700,10 @@
         <v>144</v>
       </c>
       <c r="AH34" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI34" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3767,13 +3777,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AH35" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI35" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3850,10 +3860,10 @@
         <v>146</v>
       </c>
       <c r="AH36" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI36" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3930,10 +3940,10 @@
         <v>140</v>
       </c>
       <c r="AH37" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI37" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4007,10 +4017,10 @@
         <v>162</v>
       </c>
       <c r="AH38" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI38" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4087,10 +4097,10 @@
         <v>141</v>
       </c>
       <c r="AH39" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI39" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4167,10 +4177,10 @@
         <v>141</v>
       </c>
       <c r="AH40" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4247,10 +4257,10 @@
         <v>141</v>
       </c>
       <c r="AH41" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI41" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4327,10 +4337,10 @@
         <v>140</v>
       </c>
       <c r="AH42" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI42" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4407,10 +4417,10 @@
         <v>147</v>
       </c>
       <c r="AH43" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI43" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4487,10 +4497,10 @@
         <v>142</v>
       </c>
       <c r="AH44" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI44" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4567,10 +4577,10 @@
         <v>143</v>
       </c>
       <c r="AH45" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4638,10 +4648,10 @@
         <v>144</v>
       </c>
       <c r="AH46" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI46" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4712,10 +4722,10 @@
         <v>141</v>
       </c>
       <c r="AH47" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI47" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4786,10 +4796,10 @@
         <v>141</v>
       </c>
       <c r="AH48" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI48" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4860,10 +4870,10 @@
         <v>141</v>
       </c>
       <c r="AH49" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI49" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4934,10 +4944,10 @@
         <v>140</v>
       </c>
       <c r="AH50" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI50" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5008,10 +5018,10 @@
         <v>147</v>
       </c>
       <c r="AH51" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI51" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5088,10 +5098,10 @@
         <v>142</v>
       </c>
       <c r="AH52" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI52" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5162,10 +5172,10 @@
         <v>143</v>
       </c>
       <c r="AH53" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI53" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5242,10 +5252,10 @@
         <v>141</v>
       </c>
       <c r="AH54" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI54" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5322,10 +5332,10 @@
         <v>141</v>
       </c>
       <c r="AH55" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI55" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5402,10 +5412,10 @@
         <v>141</v>
       </c>
       <c r="AH56" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI56" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5482,10 +5492,10 @@
         <v>140</v>
       </c>
       <c r="AH57" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI57" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5559,10 +5569,10 @@
         <v>144</v>
       </c>
       <c r="AH58" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI58" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5636,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AH59" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI59" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5719,10 +5729,10 @@
         <v>141</v>
       </c>
       <c r="AH60" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI60" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5799,10 +5809,10 @@
         <v>141</v>
       </c>
       <c r="AH61" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI61" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5879,10 +5889,10 @@
         <v>141</v>
       </c>
       <c r="AH62" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI62" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -5959,10 +5969,10 @@
         <v>140</v>
       </c>
       <c r="AH63" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI63" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6039,10 +6049,10 @@
         <v>147</v>
       </c>
       <c r="AH64" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI64" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6119,10 +6129,10 @@
         <v>142</v>
       </c>
       <c r="AH65" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI65" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6199,10 +6209,10 @@
         <v>143</v>
       </c>
       <c r="AH66" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI66" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6279,10 +6289,10 @@
         <v>141</v>
       </c>
       <c r="AH67" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI67" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6350,10 +6360,10 @@
         <v>144</v>
       </c>
       <c r="AH68" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI68" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6421,13 +6431,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AH69" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI69" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6498,10 +6508,10 @@
         <v>141</v>
       </c>
       <c r="AH70" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI70" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6572,10 +6582,10 @@
         <v>141</v>
       </c>
       <c r="AH71" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI71" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6646,10 +6656,10 @@
         <v>141</v>
       </c>
       <c r="AH72" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI72" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6720,10 +6730,10 @@
         <v>140</v>
       </c>
       <c r="AH73" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI73" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6794,10 +6804,10 @@
         <v>147</v>
       </c>
       <c r="AH74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI74" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6868,10 +6878,10 @@
         <v>142</v>
       </c>
       <c r="AH75" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI75" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6942,10 +6952,10 @@
         <v>143</v>
       </c>
       <c r="AH76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7016,10 +7026,10 @@
         <v>143</v>
       </c>
       <c r="AH77" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI77" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7090,10 +7100,10 @@
         <v>143</v>
       </c>
       <c r="AH78" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI78" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7164,10 +7174,10 @@
         <v>143</v>
       </c>
       <c r="AH79" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7238,10 +7248,10 @@
         <v>149</v>
       </c>
       <c r="AH80" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI80" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7312,10 +7322,10 @@
         <v>149</v>
       </c>
       <c r="AH81" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI81" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7386,10 +7396,10 @@
         <v>150</v>
       </c>
       <c r="AH82" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI82" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7460,10 +7470,10 @@
         <v>149</v>
       </c>
       <c r="AH83" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI83" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7534,10 +7544,10 @@
         <v>149</v>
       </c>
       <c r="AH84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI84" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7611,10 +7621,10 @@
         <v>149</v>
       </c>
       <c r="AH85" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI85" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7685,10 +7695,10 @@
         <v>150</v>
       </c>
       <c r="AH86" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI86" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7759,10 +7769,10 @@
         <v>149</v>
       </c>
       <c r="AH87" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI87" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7833,10 +7843,10 @@
         <v>149</v>
       </c>
       <c r="AH88" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI88" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7907,10 +7917,10 @@
         <v>149</v>
       </c>
       <c r="AH89" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI89" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -7978,10 +7988,10 @@
         <v>149</v>
       </c>
       <c r="AH90" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI90" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8052,10 +8062,10 @@
         <v>150</v>
       </c>
       <c r="AH91" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI91" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8126,10 +8136,10 @@
         <v>149</v>
       </c>
       <c r="AH92" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI92" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8200,10 +8210,10 @@
         <v>149</v>
       </c>
       <c r="AH93" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI93" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8274,10 +8284,10 @@
         <v>149</v>
       </c>
       <c r="AH94" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI94" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8345,10 +8355,10 @@
         <v>149</v>
       </c>
       <c r="AH95" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI95" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8419,10 +8429,10 @@
         <v>150</v>
       </c>
       <c r="AH96" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI96" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8493,10 +8503,10 @@
         <v>149</v>
       </c>
       <c r="AH97" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI97" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8567,10 +8577,10 @@
         <v>149</v>
       </c>
       <c r="AH98" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI98" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8641,10 +8651,10 @@
         <v>150</v>
       </c>
       <c r="AH99" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI99" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8721,10 +8731,10 @@
         <v>149</v>
       </c>
       <c r="AH100" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI100" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8792,10 +8802,10 @@
         <v>149</v>
       </c>
       <c r="AH101" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI101" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8866,10 +8876,10 @@
         <v>149</v>
       </c>
       <c r="AH102" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI102" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8940,10 +8950,10 @@
         <v>149</v>
       </c>
       <c r="AH103" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI103" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9014,10 +9024,10 @@
         <v>149</v>
       </c>
       <c r="AH104" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI104" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9085,10 +9095,10 @@
         <v>149</v>
       </c>
       <c r="AH105" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI105" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9159,10 +9169,10 @@
         <v>150</v>
       </c>
       <c r="AH106" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI106" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9233,10 +9243,10 @@
         <v>149</v>
       </c>
       <c r="AH107" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI107" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9307,10 +9317,10 @@
         <v>149</v>
       </c>
       <c r="AH108" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI108" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9378,10 +9388,10 @@
         <v>149</v>
       </c>
       <c r="AH109" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI109" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9452,10 +9462,10 @@
         <v>150</v>
       </c>
       <c r="AH110" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI110" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9523,10 +9533,10 @@
         <v>151</v>
       </c>
       <c r="AH111" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI111" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9597,10 +9607,10 @@
         <v>150</v>
       </c>
       <c r="AH112" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI112" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9671,10 +9681,10 @@
         <v>148</v>
       </c>
       <c r="AH113" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI113" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9742,10 +9752,10 @@
         <v>151</v>
       </c>
       <c r="AH114" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI114" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9816,10 +9826,10 @@
         <v>150</v>
       </c>
       <c r="AH115" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI115" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9890,10 +9900,10 @@
         <v>149</v>
       </c>
       <c r="AH116" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI116" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -9964,10 +9974,10 @@
         <v>149</v>
       </c>
       <c r="AH117" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI117" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10038,10 +10048,10 @@
         <v>149</v>
       </c>
       <c r="AH118" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI118" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10109,10 +10119,10 @@
         <v>149</v>
       </c>
       <c r="AH119" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI119" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10183,10 +10193,10 @@
         <v>150</v>
       </c>
       <c r="AH120" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI120" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10257,10 +10267,10 @@
         <v>149</v>
       </c>
       <c r="AH121" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI121" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10331,10 +10341,10 @@
         <v>149</v>
       </c>
       <c r="AH122" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI122" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10405,10 +10415,10 @@
         <v>149</v>
       </c>
       <c r="AH123" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI123" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10476,10 +10486,10 @@
         <v>149</v>
       </c>
       <c r="AH124" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI124" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10550,10 +10560,10 @@
         <v>150</v>
       </c>
       <c r="AH125" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI125" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10630,10 +10640,10 @@
         <v>150</v>
       </c>
       <c r="AH126" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI126" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10710,10 +10720,10 @@
         <v>150</v>
       </c>
       <c r="AH127" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI127" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10784,10 +10794,10 @@
         <v>153</v>
       </c>
       <c r="AH128" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI128" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10858,10 +10868,10 @@
         <v>153</v>
       </c>
       <c r="AH129" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI129" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10938,10 +10948,10 @@
         <v>153</v>
       </c>
       <c r="AH130" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI130" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11012,10 +11022,10 @@
         <v>153</v>
       </c>
       <c r="AH131" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI131" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11086,10 +11096,10 @@
         <v>153</v>
       </c>
       <c r="AH132" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI132" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11160,10 +11170,10 @@
         <v>153</v>
       </c>
       <c r="AH133" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI133" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11234,10 +11244,10 @@
         <v>153</v>
       </c>
       <c r="AH134" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI134" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11314,10 +11324,10 @@
         <v>153</v>
       </c>
       <c r="AH135" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI135" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11388,10 +11398,10 @@
         <v>153</v>
       </c>
       <c r="AH136" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI136" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11462,10 +11472,10 @@
         <v>153</v>
       </c>
       <c r="AH137" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI137" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11536,10 +11546,10 @@
         <v>153</v>
       </c>
       <c r="AH138" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI138" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11616,10 +11626,10 @@
         <v>153</v>
       </c>
       <c r="AH139" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI139" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11690,10 +11700,10 @@
         <v>153</v>
       </c>
       <c r="AH140" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI140" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11764,10 +11774,10 @@
         <v>153</v>
       </c>
       <c r="AH141" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI141" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11838,10 +11848,10 @@
         <v>153</v>
       </c>
       <c r="AH142" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI142" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11912,10 +11922,10 @@
         <v>153</v>
       </c>
       <c r="AH143" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI143" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -11986,10 +11996,10 @@
         <v>153</v>
       </c>
       <c r="AH144" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI144" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12060,10 +12070,10 @@
         <v>153</v>
       </c>
       <c r="AH145" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI145" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12134,10 +12144,10 @@
         <v>153</v>
       </c>
       <c r="AH146" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI146" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12208,10 +12218,10 @@
         <v>153</v>
       </c>
       <c r="AH147" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI147" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12282,10 +12292,10 @@
         <v>153</v>
       </c>
       <c r="AH148" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI148" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12356,10 +12366,10 @@
         <v>153</v>
       </c>
       <c r="AH149" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI149" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12436,10 +12446,10 @@
         <v>153</v>
       </c>
       <c r="AH150" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI150" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12510,10 +12520,10 @@
         <v>153</v>
       </c>
       <c r="AH151" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI151" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12584,10 +12594,10 @@
         <v>153</v>
       </c>
       <c r="AH152" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI152" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12658,10 +12668,10 @@
         <v>153</v>
       </c>
       <c r="AH153" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI153" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12732,10 +12742,10 @@
         <v>154</v>
       </c>
       <c r="AH154" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI154" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12806,10 +12816,10 @@
         <v>154</v>
       </c>
       <c r="AH155" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI155" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12880,10 +12890,10 @@
         <v>154</v>
       </c>
       <c r="AH156" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI156" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -12954,10 +12964,10 @@
         <v>154</v>
       </c>
       <c r="AH157" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI157" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13028,10 +13038,10 @@
         <v>154</v>
       </c>
       <c r="AH158" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI158" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13102,10 +13112,10 @@
         <v>154</v>
       </c>
       <c r="AH159" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI159" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13176,10 +13186,10 @@
         <v>154</v>
       </c>
       <c r="AH160" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI160" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13250,10 +13260,10 @@
         <v>154</v>
       </c>
       <c r="AH161" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI161" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13324,10 +13334,10 @@
         <v>154</v>
       </c>
       <c r="AH162" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI162" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13398,10 +13408,10 @@
         <v>154</v>
       </c>
       <c r="AH163" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI163" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13472,10 +13482,10 @@
         <v>154</v>
       </c>
       <c r="AH164" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI164" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13546,10 +13556,10 @@
         <v>154</v>
       </c>
       <c r="AH165" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI165" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13620,10 +13630,10 @@
         <v>154</v>
       </c>
       <c r="AH166" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI166" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13694,10 +13704,10 @@
         <v>154</v>
       </c>
       <c r="AH167" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI167" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13768,10 +13778,10 @@
         <v>154</v>
       </c>
       <c r="AH168" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI168" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13842,10 +13852,10 @@
         <v>154</v>
       </c>
       <c r="AH169" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI169" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13916,10 +13926,10 @@
         <v>154</v>
       </c>
       <c r="AH170" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI170" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -13990,10 +14000,10 @@
         <v>154</v>
       </c>
       <c r="AH171" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI171" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14064,10 +14074,10 @@
         <v>154</v>
       </c>
       <c r="AH172" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI172" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14138,10 +14148,10 @@
         <v>154</v>
       </c>
       <c r="AH173" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AI173" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14215,10 +14225,10 @@
         <v>154</v>
       </c>
       <c r="AH174" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI174" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14292,10 +14302,10 @@
         <v>154</v>
       </c>
       <c r="AH175" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI175" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14369,10 +14379,10 @@
         <v>154</v>
       </c>
       <c r="AH176" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI176" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14446,10 +14456,10 @@
         <v>154</v>
       </c>
       <c r="AH177" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI177" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14523,10 +14533,10 @@
         <v>154</v>
       </c>
       <c r="AH178" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI178" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14600,10 +14610,10 @@
         <v>154</v>
       </c>
       <c r="AH179" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI179" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14677,10 +14687,10 @@
         <v>154</v>
       </c>
       <c r="AH180" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI180" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14754,10 +14764,10 @@
         <v>154</v>
       </c>
       <c r="AH181" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI181" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14831,10 +14841,10 @@
         <v>154</v>
       </c>
       <c r="AH182" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI182" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14908,10 +14918,10 @@
         <v>154</v>
       </c>
       <c r="AH183" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI183" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -14985,10 +14995,10 @@
         <v>154</v>
       </c>
       <c r="AH184" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI184" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15062,10 +15072,10 @@
         <v>154</v>
       </c>
       <c r="AH185" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI185" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15139,10 +15149,10 @@
         <v>154</v>
       </c>
       <c r="AH186" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI186" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15216,10 +15226,10 @@
         <v>154</v>
       </c>
       <c r="AH187" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI187" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15287,10 +15297,10 @@
         <v>154</v>
       </c>
       <c r="AH188" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI188" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15358,10 +15368,10 @@
         <v>154</v>
       </c>
       <c r="AH189" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI189" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15429,10 +15439,10 @@
         <v>154</v>
       </c>
       <c r="AH190" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI190" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15500,10 +15510,10 @@
         <v>154</v>
       </c>
       <c r="AH191" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI191" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15571,10 +15581,10 @@
         <v>154</v>
       </c>
       <c r="AH192" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI192" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15642,10 +15652,10 @@
         <v>154</v>
       </c>
       <c r="AH193" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI193" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15713,10 +15723,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI194" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15784,10 +15794,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI195" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15855,10 +15865,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI196" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15926,10 +15936,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI197" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -15997,10 +16007,10 @@
         <v>155</v>
       </c>
       <c r="AH198" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI198" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16068,10 +16078,10 @@
         <v>55</v>
       </c>
       <c r="AH199" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI199" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16139,10 +16149,10 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI200" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16210,10 +16220,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI201" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16281,10 +16291,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI202" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16352,10 +16362,10 @@
         <v>155</v>
       </c>
       <c r="AH203" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI203" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16423,10 +16433,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI204" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16494,10 +16504,10 @@
         <v>155</v>
       </c>
       <c r="AH205" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI205" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16565,10 +16575,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI206" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16636,10 +16646,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI207" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16707,10 +16717,10 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI208" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16778,10 +16788,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI209" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16849,10 +16859,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI210" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16920,10 +16930,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI211" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -16991,10 +17001,10 @@
         <v>155</v>
       </c>
       <c r="AH212" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI212" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17062,10 +17072,10 @@
         <v>55</v>
       </c>
       <c r="AH213" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AI213" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17136,10 +17146,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI214" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17210,10 +17220,10 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI215" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17284,10 +17294,10 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI216" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17358,10 +17368,10 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI217" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17429,10 +17439,10 @@
         <v>54</v>
       </c>
       <c r="AH218" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI218" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17500,10 +17510,10 @@
         <v>54</v>
       </c>
       <c r="AH219" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI219" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17574,10 +17584,10 @@
         <v>54</v>
       </c>
       <c r="AH220" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI220" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17645,10 +17655,10 @@
         <v>54</v>
       </c>
       <c r="AH221" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI221" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17716,21 +17726,21 @@
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AH222" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI222" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B223" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
@@ -17742,7 +17752,7 @@
         <v>54</v>
       </c>
       <c r="F223" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G223">
         <v>9746</v>
@@ -17759,6 +17769,9 @@
       <c r="N223" s="1">
         <v>46275</v>
       </c>
+      <c r="O223" t="s">
+        <v>131</v>
+      </c>
       <c r="P223">
         <v>8</v>
       </c>
@@ -17766,72 +17779,78 @@
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>18190457</v>
+        <v>16976300</v>
       </c>
       <c r="S223" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T223" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U223" t="s">
         <v>165</v>
       </c>
       <c r="V223" s="1">
-        <v>46274.34198912037</v>
+        <v>46274.47210818287</v>
       </c>
       <c r="W223">
         <v>-1</v>
       </c>
       <c r="X223" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="Y223" t="s">
+        <v>243</v>
       </c>
       <c r="AB223">
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AH223" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AI223" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B224" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
       </c>
       <c r="D224" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E224" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F224" t="s">
         <v>56</v>
       </c>
       <c r="G224">
-        <v>1866</v>
+        <v>9746</v>
       </c>
       <c r="H224">
         <v>0</v>
       </c>
       <c r="I224" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J224" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N224" s="1">
-        <v>46274</v>
+        <v>46275</v>
+      </c>
+      <c r="O224" t="s">
+        <v>129</v>
       </c>
       <c r="P224">
         <v>8</v>
@@ -17840,48 +17859,48 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>17968368</v>
+        <v>18090250</v>
       </c>
       <c r="S224" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="T224" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U224" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V224" s="1">
-        <v>46274.36843923611</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X224" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y224" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AB224">
         <v>0</v>
       </c>
       <c r="AC224" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AH224" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AI224" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B225" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
@@ -17890,25 +17909,25 @@
         <v>51</v>
       </c>
       <c r="E225" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F225" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G225">
-        <v>1867</v>
+        <v>9746</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J225" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="N225" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="P225">
         <v>8</v>
@@ -17917,37 +17936,975 @@
         <v>2026</v>
       </c>
       <c r="R225">
+        <v>18190457</v>
+      </c>
+      <c r="S225" t="s">
+        <v>143</v>
+      </c>
+      <c r="T225" t="s">
+        <v>161</v>
+      </c>
+      <c r="U225" t="s">
+        <v>165</v>
+      </c>
+      <c r="V225" s="1">
+        <v>46274.34198912037</v>
+      </c>
+      <c r="W225">
+        <v>-1</v>
+      </c>
+      <c r="X225" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB225">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH225" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI225" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="226" spans="1:35">
+      <c r="A226">
+        <v>6627</v>
+      </c>
+      <c r="B226" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" t="s">
+        <v>50</v>
+      </c>
+      <c r="D226" t="s">
+        <v>51</v>
+      </c>
+      <c r="E226" t="s">
+        <v>55</v>
+      </c>
+      <c r="F226" t="s">
+        <v>56</v>
+      </c>
+      <c r="G226">
+        <v>1866</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226" t="s">
+        <v>62</v>
+      </c>
+      <c r="J226" t="s">
+        <v>100</v>
+      </c>
+      <c r="N226" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P226">
+        <v>8</v>
+      </c>
+      <c r="Q226">
+        <v>2026</v>
+      </c>
+      <c r="R226">
+        <v>17968368</v>
+      </c>
+      <c r="S226" t="s">
+        <v>149</v>
+      </c>
+      <c r="T226" t="s">
+        <v>149</v>
+      </c>
+      <c r="U226" t="s">
+        <v>166</v>
+      </c>
+      <c r="V226" s="1">
+        <v>46274.36843923611</v>
+      </c>
+      <c r="W226">
+        <v>0</v>
+      </c>
+      <c r="X226" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y226" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB226">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH226" t="s">
+        <v>252</v>
+      </c>
+      <c r="AI226" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="227" spans="1:35">
+      <c r="A227">
+        <v>6627</v>
+      </c>
+      <c r="B227" t="s">
+        <v>36</v>
+      </c>
+      <c r="C227" t="s">
+        <v>50</v>
+      </c>
+      <c r="D227" t="s">
+        <v>51</v>
+      </c>
+      <c r="E227" t="s">
+        <v>55</v>
+      </c>
+      <c r="F227" t="s">
+        <v>56</v>
+      </c>
+      <c r="G227">
+        <v>1867</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227" t="s">
+        <v>62</v>
+      </c>
+      <c r="J227" t="s">
+        <v>101</v>
+      </c>
+      <c r="N227" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P227">
+        <v>8</v>
+      </c>
+      <c r="Q227">
+        <v>2026</v>
+      </c>
+      <c r="R227">
         <v>17968379</v>
       </c>
-      <c r="S225" t="s">
+      <c r="S227" t="s">
         <v>149</v>
       </c>
-      <c r="T225" t="s">
+      <c r="T227" t="s">
         <v>149</v>
       </c>
-      <c r="U225" t="s">
+      <c r="U227" t="s">
         <v>166</v>
       </c>
-      <c r="V225" s="1">
+      <c r="V227" s="1">
         <v>46274.36695243056</v>
       </c>
-      <c r="W225">
-        <v>0</v>
-      </c>
-      <c r="X225" t="s">
+      <c r="W227">
+        <v>0</v>
+      </c>
+      <c r="X227" t="s">
         <v>168</v>
       </c>
-      <c r="AB225">
-        <v>0</v>
-      </c>
-      <c r="AC225" t="s">
+      <c r="AB227">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="s">
         <v>149</v>
       </c>
-      <c r="AH225" t="s">
-        <v>249</v>
-      </c>
-      <c r="AI225" t="s">
+      <c r="AH227" t="s">
         <v>252</v>
+      </c>
+      <c r="AI227" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="228" spans="1:35">
+      <c r="A228">
+        <v>5417</v>
+      </c>
+      <c r="B228" t="s">
+        <v>43</v>
+      </c>
+      <c r="C228" t="s">
+        <v>50</v>
+      </c>
+      <c r="D228" t="s">
+        <v>51</v>
+      </c>
+      <c r="E228" t="s">
+        <v>54</v>
+      </c>
+      <c r="F228" t="s">
+        <v>56</v>
+      </c>
+      <c r="G228">
+        <v>11303</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228" t="s">
+        <v>63</v>
+      </c>
+      <c r="J228" t="s">
+        <v>111</v>
+      </c>
+      <c r="N228" s="1">
+        <v>46279</v>
+      </c>
+      <c r="P228">
+        <v>8</v>
+      </c>
+      <c r="Q228">
+        <v>2026</v>
+      </c>
+      <c r="R228">
+        <v>17399454</v>
+      </c>
+      <c r="S228" t="s">
+        <v>153</v>
+      </c>
+      <c r="T228" t="s">
+        <v>163</v>
+      </c>
+      <c r="U228" t="s">
+        <v>165</v>
+      </c>
+      <c r="V228" s="1">
+        <v>46274.42878043981</v>
+      </c>
+      <c r="W228">
+        <v>-5</v>
+      </c>
+      <c r="X228" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y228" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB228">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH228" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI228" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="229" spans="1:35">
+      <c r="A229">
+        <v>6703</v>
+      </c>
+      <c r="B229" t="s">
+        <v>46</v>
+      </c>
+      <c r="C229" t="s">
+        <v>50</v>
+      </c>
+      <c r="D229" t="s">
+        <v>53</v>
+      </c>
+      <c r="E229" t="s">
+        <v>54</v>
+      </c>
+      <c r="F229" t="s">
+        <v>56</v>
+      </c>
+      <c r="G229">
+        <v>5989</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229" t="s">
+        <v>64</v>
+      </c>
+      <c r="J229" t="s">
+        <v>119</v>
+      </c>
+      <c r="N229" s="1">
+        <v>46273</v>
+      </c>
+      <c r="P229">
+        <v>9</v>
+      </c>
+      <c r="Q229">
+        <v>2026</v>
+      </c>
+      <c r="R229">
+        <v>17941177</v>
+      </c>
+      <c r="S229" t="s">
+        <v>154</v>
+      </c>
+      <c r="U229" t="s">
+        <v>164</v>
+      </c>
+      <c r="V229" s="1">
+        <v>46274.41771849537</v>
+      </c>
+      <c r="W229">
+        <v>1</v>
+      </c>
+      <c r="X229" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB229">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH229" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI229" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="230" spans="1:35">
+      <c r="A230">
+        <v>6704</v>
+      </c>
+      <c r="B230" t="s">
+        <v>42</v>
+      </c>
+      <c r="C230" t="s">
+        <v>50</v>
+      </c>
+      <c r="D230" t="s">
+        <v>51</v>
+      </c>
+      <c r="E230" t="s">
+        <v>54</v>
+      </c>
+      <c r="F230" t="s">
+        <v>56</v>
+      </c>
+      <c r="G230">
+        <v>5989</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230" t="s">
+        <v>64</v>
+      </c>
+      <c r="J230" t="s">
+        <v>119</v>
+      </c>
+      <c r="N230" s="1">
+        <v>46273</v>
+      </c>
+      <c r="P230">
+        <v>9</v>
+      </c>
+      <c r="Q230">
+        <v>2026</v>
+      </c>
+      <c r="R230">
+        <v>17952385</v>
+      </c>
+      <c r="S230" t="s">
+        <v>154</v>
+      </c>
+      <c r="U230" t="s">
+        <v>164</v>
+      </c>
+      <c r="V230" s="1">
+        <v>46274.41775447917</v>
+      </c>
+      <c r="W230">
+        <v>1</v>
+      </c>
+      <c r="X230" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB230">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH230" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI230" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="231" spans="1:35">
+      <c r="A231">
+        <v>6705</v>
+      </c>
+      <c r="B231" t="s">
+        <v>48</v>
+      </c>
+      <c r="C231" t="s">
+        <v>50</v>
+      </c>
+      <c r="D231" t="s">
+        <v>52</v>
+      </c>
+      <c r="E231" t="s">
+        <v>54</v>
+      </c>
+      <c r="F231" t="s">
+        <v>56</v>
+      </c>
+      <c r="G231">
+        <v>5989</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231" t="s">
+        <v>64</v>
+      </c>
+      <c r="J231" t="s">
+        <v>119</v>
+      </c>
+      <c r="N231" s="1">
+        <v>46273</v>
+      </c>
+      <c r="P231">
+        <v>9</v>
+      </c>
+      <c r="Q231">
+        <v>2026</v>
+      </c>
+      <c r="R231">
+        <v>17952569</v>
+      </c>
+      <c r="S231" t="s">
+        <v>154</v>
+      </c>
+      <c r="U231" t="s">
+        <v>164</v>
+      </c>
+      <c r="V231" s="1">
+        <v>46274.41777533565</v>
+      </c>
+      <c r="W231">
+        <v>1</v>
+      </c>
+      <c r="X231" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB231">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH231" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI231" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="232" spans="1:35">
+      <c r="A232">
+        <v>6945</v>
+      </c>
+      <c r="B232" t="s">
+        <v>39</v>
+      </c>
+      <c r="C232" t="s">
+        <v>50</v>
+      </c>
+      <c r="D232" t="s">
+        <v>52</v>
+      </c>
+      <c r="E232" t="s">
+        <v>54</v>
+      </c>
+      <c r="F232" t="s">
+        <v>57</v>
+      </c>
+      <c r="G232">
+        <v>5989</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232" t="s">
+        <v>64</v>
+      </c>
+      <c r="J232" t="s">
+        <v>119</v>
+      </c>
+      <c r="N232" s="1">
+        <v>46273</v>
+      </c>
+      <c r="P232">
+        <v>9</v>
+      </c>
+      <c r="Q232">
+        <v>2026</v>
+      </c>
+      <c r="R232">
+        <v>18164516</v>
+      </c>
+      <c r="S232" t="s">
+        <v>154</v>
+      </c>
+      <c r="U232" t="s">
+        <v>164</v>
+      </c>
+      <c r="V232" s="1">
+        <v>46274.41799166667</v>
+      </c>
+      <c r="W232">
+        <v>1</v>
+      </c>
+      <c r="X232" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB232">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH232" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI232" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="233" spans="1:35">
+      <c r="A233">
+        <v>6949</v>
+      </c>
+      <c r="B233" t="s">
+        <v>37</v>
+      </c>
+      <c r="C233" t="s">
+        <v>50</v>
+      </c>
+      <c r="D233" t="s">
+        <v>51</v>
+      </c>
+      <c r="E233" t="s">
+        <v>54</v>
+      </c>
+      <c r="F233" t="s">
+        <v>57</v>
+      </c>
+      <c r="G233">
+        <v>5989</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233" t="s">
+        <v>64</v>
+      </c>
+      <c r="J233" t="s">
+        <v>119</v>
+      </c>
+      <c r="N233" s="1">
+        <v>46273</v>
+      </c>
+      <c r="P233">
+        <v>9</v>
+      </c>
+      <c r="Q233">
+        <v>2026</v>
+      </c>
+      <c r="R233">
+        <v>18178157</v>
+      </c>
+      <c r="S233" t="s">
+        <v>154</v>
+      </c>
+      <c r="U233" t="s">
+        <v>164</v>
+      </c>
+      <c r="V233" s="1">
+        <v>46274.41800114583</v>
+      </c>
+      <c r="W233">
+        <v>1</v>
+      </c>
+      <c r="X233" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB233">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH233" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI233" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="234" spans="1:35">
+      <c r="A234">
+        <v>6703</v>
+      </c>
+      <c r="B234" t="s">
+        <v>46</v>
+      </c>
+      <c r="C234" t="s">
+        <v>50</v>
+      </c>
+      <c r="D234" t="s">
+        <v>53</v>
+      </c>
+      <c r="E234" t="s">
+        <v>54</v>
+      </c>
+      <c r="F234" t="s">
+        <v>56</v>
+      </c>
+      <c r="G234">
+        <v>6215</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234" t="s">
+        <v>65</v>
+      </c>
+      <c r="J234" t="s">
+        <v>121</v>
+      </c>
+      <c r="N234" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P234">
+        <v>9</v>
+      </c>
+      <c r="Q234">
+        <v>2026</v>
+      </c>
+      <c r="R234">
+        <v>17941187</v>
+      </c>
+      <c r="S234" t="s">
+        <v>54</v>
+      </c>
+      <c r="U234" t="s">
+        <v>166</v>
+      </c>
+      <c r="V234" s="1">
+        <v>46274.41772148148</v>
+      </c>
+      <c r="W234">
+        <v>0</v>
+      </c>
+      <c r="X234" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB234">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH234" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI234" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="235" spans="1:35">
+      <c r="A235">
+        <v>6704</v>
+      </c>
+      <c r="B235" t="s">
+        <v>42</v>
+      </c>
+      <c r="C235" t="s">
+        <v>50</v>
+      </c>
+      <c r="D235" t="s">
+        <v>51</v>
+      </c>
+      <c r="E235" t="s">
+        <v>54</v>
+      </c>
+      <c r="F235" t="s">
+        <v>56</v>
+      </c>
+      <c r="G235">
+        <v>6215</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235" t="s">
+        <v>65</v>
+      </c>
+      <c r="J235" t="s">
+        <v>121</v>
+      </c>
+      <c r="N235" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P235">
+        <v>9</v>
+      </c>
+      <c r="Q235">
+        <v>2026</v>
+      </c>
+      <c r="R235">
+        <v>17952400</v>
+      </c>
+      <c r="S235" t="s">
+        <v>54</v>
+      </c>
+      <c r="U235" t="s">
+        <v>166</v>
+      </c>
+      <c r="V235" s="1">
+        <v>46274.41773631945</v>
+      </c>
+      <c r="W235">
+        <v>0</v>
+      </c>
+      <c r="X235" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB235">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH235" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI235" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="236" spans="1:35">
+      <c r="A236">
+        <v>6705</v>
+      </c>
+      <c r="B236" t="s">
+        <v>48</v>
+      </c>
+      <c r="C236" t="s">
+        <v>50</v>
+      </c>
+      <c r="D236" t="s">
+        <v>52</v>
+      </c>
+      <c r="E236" t="s">
+        <v>54</v>
+      </c>
+      <c r="F236" t="s">
+        <v>56</v>
+      </c>
+      <c r="G236">
+        <v>6215</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236" t="s">
+        <v>65</v>
+      </c>
+      <c r="J236" t="s">
+        <v>121</v>
+      </c>
+      <c r="N236" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P236">
+        <v>9</v>
+      </c>
+      <c r="Q236">
+        <v>2026</v>
+      </c>
+      <c r="R236">
+        <v>17952580</v>
+      </c>
+      <c r="S236" t="s">
+        <v>54</v>
+      </c>
+      <c r="U236" t="s">
+        <v>166</v>
+      </c>
+      <c r="V236" s="1">
+        <v>46274.41777481481</v>
+      </c>
+      <c r="W236">
+        <v>0</v>
+      </c>
+      <c r="X236" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB236">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH236" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI236" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="237" spans="1:35">
+      <c r="A237">
+        <v>6945</v>
+      </c>
+      <c r="B237" t="s">
+        <v>39</v>
+      </c>
+      <c r="C237" t="s">
+        <v>50</v>
+      </c>
+      <c r="D237" t="s">
+        <v>52</v>
+      </c>
+      <c r="E237" t="s">
+        <v>54</v>
+      </c>
+      <c r="F237" t="s">
+        <v>57</v>
+      </c>
+      <c r="G237">
+        <v>6215</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237" t="s">
+        <v>65</v>
+      </c>
+      <c r="J237" t="s">
+        <v>121</v>
+      </c>
+      <c r="N237" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P237">
+        <v>9</v>
+      </c>
+      <c r="Q237">
+        <v>2026</v>
+      </c>
+      <c r="R237">
+        <v>18164523</v>
+      </c>
+      <c r="S237" t="s">
+        <v>54</v>
+      </c>
+      <c r="U237" t="s">
+        <v>166</v>
+      </c>
+      <c r="V237" s="1">
+        <v>46274.41799332176</v>
+      </c>
+      <c r="W237">
+        <v>0</v>
+      </c>
+      <c r="X237" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB237">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH237" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI237" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="238" spans="1:35">
+      <c r="A238">
+        <v>6949</v>
+      </c>
+      <c r="B238" t="s">
+        <v>37</v>
+      </c>
+      <c r="C238" t="s">
+        <v>50</v>
+      </c>
+      <c r="D238" t="s">
+        <v>51</v>
+      </c>
+      <c r="E238" t="s">
+        <v>54</v>
+      </c>
+      <c r="F238" t="s">
+        <v>57</v>
+      </c>
+      <c r="G238">
+        <v>6215</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238" t="s">
+        <v>65</v>
+      </c>
+      <c r="J238" t="s">
+        <v>121</v>
+      </c>
+      <c r="N238" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P238">
+        <v>9</v>
+      </c>
+      <c r="Q238">
+        <v>2026</v>
+      </c>
+      <c r="R238">
+        <v>18178163</v>
+      </c>
+      <c r="S238" t="s">
+        <v>155</v>
+      </c>
+      <c r="U238" t="s">
+        <v>166</v>
+      </c>
+      <c r="V238" s="1">
+        <v>46274.41800085648</v>
+      </c>
+      <c r="W238">
+        <v>0</v>
+      </c>
+      <c r="X238" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB238">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH238" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI238" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="258">
   <si>
     <t>CodCliente</t>
   </si>
@@ -760,11 +760,18 @@
 Reunião confirmada pelo cliente - Data Comentário: 04/09/2026 11:03</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/09/2026 
+em processamento - Data Comentário: 08/09/2026 16:10</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 - Data Comentário: 04/09/2026 16:13</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/09/2026 
 Em processamento. - Data Comentário: 04/09/2026 08:41</t>
+  </si>
+  <si>
+    <t>1. Folha em Processamento  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 15:22</t>
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
@@ -1133,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI238"/>
+  <dimension ref="A1:AI240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1314,10 +1321,10 @@
         <v>132</v>
       </c>
       <c r="AH2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1391,10 +1398,10 @@
         <v>133</v>
       </c>
       <c r="AH3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1468,10 +1475,10 @@
         <v>132</v>
       </c>
       <c r="AH4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1542,10 +1549,10 @@
         <v>132</v>
       </c>
       <c r="AH5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1616,10 +1623,10 @@
         <v>133</v>
       </c>
       <c r="AH6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1690,10 +1697,10 @@
         <v>133</v>
       </c>
       <c r="AH7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1764,10 +1771,10 @@
         <v>134</v>
       </c>
       <c r="AH8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1838,10 +1845,10 @@
         <v>132</v>
       </c>
       <c r="AH9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1912,10 +1919,10 @@
         <v>135</v>
       </c>
       <c r="AH10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1986,10 +1993,10 @@
         <v>135</v>
       </c>
       <c r="AH11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2060,10 +2067,10 @@
         <v>136</v>
       </c>
       <c r="AH12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2131,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AH13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2205,13 +2212,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AH14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2279,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2344,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI16" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2415,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2492,10 +2499,10 @@
         <v>138</v>
       </c>
       <c r="AH18" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2569,10 +2576,10 @@
         <v>137</v>
       </c>
       <c r="AH19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2646,10 +2653,10 @@
         <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2723,10 +2730,10 @@
         <v>136</v>
       </c>
       <c r="AH21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2797,10 +2804,10 @@
         <v>139</v>
       </c>
       <c r="AH22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2871,10 +2878,10 @@
         <v>136</v>
       </c>
       <c r="AH23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2945,10 +2952,10 @@
         <v>136</v>
       </c>
       <c r="AH24" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI24" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3019,10 +3026,10 @@
         <v>136</v>
       </c>
       <c r="AH25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3093,10 +3100,10 @@
         <v>137</v>
       </c>
       <c r="AH26" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI26" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3167,10 +3174,10 @@
         <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3241,10 +3248,10 @@
         <v>136</v>
       </c>
       <c r="AH28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI28" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3315,10 +3322,10 @@
         <v>136</v>
       </c>
       <c r="AH29" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3389,10 +3396,10 @@
         <v>140</v>
       </c>
       <c r="AH30" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI30" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3469,10 +3476,10 @@
         <v>141</v>
       </c>
       <c r="AH31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3543,10 +3550,10 @@
         <v>142</v>
       </c>
       <c r="AH32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI32" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3623,10 +3630,10 @@
         <v>143</v>
       </c>
       <c r="AH33" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3700,10 +3707,10 @@
         <v>144</v>
       </c>
       <c r="AH34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3777,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AH35" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI35" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3860,10 +3867,10 @@
         <v>146</v>
       </c>
       <c r="AH36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3940,10 +3947,10 @@
         <v>140</v>
       </c>
       <c r="AH37" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4017,10 +4024,10 @@
         <v>162</v>
       </c>
       <c r="AH38" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4097,10 +4104,10 @@
         <v>141</v>
       </c>
       <c r="AH39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI39" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4177,10 +4184,10 @@
         <v>141</v>
       </c>
       <c r="AH40" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI40" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4257,10 +4264,10 @@
         <v>141</v>
       </c>
       <c r="AH41" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI41" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4337,10 +4344,10 @@
         <v>140</v>
       </c>
       <c r="AH42" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI42" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4417,10 +4424,10 @@
         <v>147</v>
       </c>
       <c r="AH43" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI43" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4497,10 +4504,10 @@
         <v>142</v>
       </c>
       <c r="AH44" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI44" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4577,10 +4584,10 @@
         <v>143</v>
       </c>
       <c r="AH45" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4648,10 +4655,10 @@
         <v>144</v>
       </c>
       <c r="AH46" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4722,10 +4729,10 @@
         <v>141</v>
       </c>
       <c r="AH47" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI47" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4796,10 +4803,10 @@
         <v>141</v>
       </c>
       <c r="AH48" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI48" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4870,10 +4877,10 @@
         <v>141</v>
       </c>
       <c r="AH49" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4944,10 +4951,10 @@
         <v>140</v>
       </c>
       <c r="AH50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI50" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5018,10 +5025,10 @@
         <v>147</v>
       </c>
       <c r="AH51" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI51" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5098,10 +5105,10 @@
         <v>142</v>
       </c>
       <c r="AH52" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI52" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5172,10 +5179,10 @@
         <v>143</v>
       </c>
       <c r="AH53" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI53" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5252,10 +5259,10 @@
         <v>141</v>
       </c>
       <c r="AH54" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5332,10 +5339,10 @@
         <v>141</v>
       </c>
       <c r="AH55" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI55" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5412,10 +5419,10 @@
         <v>141</v>
       </c>
       <c r="AH56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5492,10 +5499,10 @@
         <v>140</v>
       </c>
       <c r="AH57" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI57" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5569,10 +5576,10 @@
         <v>144</v>
       </c>
       <c r="AH58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI58" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5646,13 +5653,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AH59" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI59" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5729,10 +5736,10 @@
         <v>141</v>
       </c>
       <c r="AH60" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI60" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5809,10 +5816,10 @@
         <v>141</v>
       </c>
       <c r="AH61" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI61" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5889,10 +5896,10 @@
         <v>141</v>
       </c>
       <c r="AH62" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI62" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -5969,10 +5976,10 @@
         <v>140</v>
       </c>
       <c r="AH63" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI63" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6049,10 +6056,10 @@
         <v>147</v>
       </c>
       <c r="AH64" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI64" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6129,10 +6136,10 @@
         <v>142</v>
       </c>
       <c r="AH65" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI65" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6209,10 +6216,10 @@
         <v>143</v>
       </c>
       <c r="AH66" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI66" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6289,10 +6296,10 @@
         <v>141</v>
       </c>
       <c r="AH67" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI67" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6360,10 +6367,10 @@
         <v>144</v>
       </c>
       <c r="AH68" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI68" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6431,13 +6438,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AH69" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI69" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6508,10 +6515,10 @@
         <v>141</v>
       </c>
       <c r="AH70" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI70" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6582,10 +6589,10 @@
         <v>141</v>
       </c>
       <c r="AH71" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI71" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6656,10 +6663,10 @@
         <v>141</v>
       </c>
       <c r="AH72" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI72" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6730,10 +6737,10 @@
         <v>140</v>
       </c>
       <c r="AH73" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI73" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6804,10 +6811,10 @@
         <v>147</v>
       </c>
       <c r="AH74" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI74" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6878,10 +6885,10 @@
         <v>142</v>
       </c>
       <c r="AH75" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI75" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6952,10 +6959,10 @@
         <v>143</v>
       </c>
       <c r="AH76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI76" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7026,10 +7033,10 @@
         <v>143</v>
       </c>
       <c r="AH77" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI77" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7100,10 +7107,10 @@
         <v>143</v>
       </c>
       <c r="AH78" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI78" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7174,10 +7181,10 @@
         <v>143</v>
       </c>
       <c r="AH79" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7248,10 +7255,10 @@
         <v>149</v>
       </c>
       <c r="AH80" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI80" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7322,10 +7329,10 @@
         <v>149</v>
       </c>
       <c r="AH81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7396,10 +7403,10 @@
         <v>150</v>
       </c>
       <c r="AH82" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI82" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7470,10 +7477,10 @@
         <v>149</v>
       </c>
       <c r="AH83" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI83" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7544,10 +7551,10 @@
         <v>149</v>
       </c>
       <c r="AH84" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7621,10 +7628,10 @@
         <v>149</v>
       </c>
       <c r="AH85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI85" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7695,10 +7702,10 @@
         <v>150</v>
       </c>
       <c r="AH86" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7769,10 +7776,10 @@
         <v>149</v>
       </c>
       <c r="AH87" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI87" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7843,10 +7850,10 @@
         <v>149</v>
       </c>
       <c r="AH88" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI88" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7917,10 +7924,10 @@
         <v>149</v>
       </c>
       <c r="AH89" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI89" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -7988,10 +7995,10 @@
         <v>149</v>
       </c>
       <c r="AH90" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI90" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8062,10 +8069,10 @@
         <v>150</v>
       </c>
       <c r="AH91" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI91" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8136,10 +8143,10 @@
         <v>149</v>
       </c>
       <c r="AH92" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI92" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8210,10 +8217,10 @@
         <v>149</v>
       </c>
       <c r="AH93" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI93" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8284,10 +8291,10 @@
         <v>149</v>
       </c>
       <c r="AH94" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI94" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8355,10 +8362,10 @@
         <v>149</v>
       </c>
       <c r="AH95" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI95" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8429,10 +8436,10 @@
         <v>150</v>
       </c>
       <c r="AH96" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI96" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8503,10 +8510,10 @@
         <v>149</v>
       </c>
       <c r="AH97" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI97" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8577,10 +8584,10 @@
         <v>149</v>
       </c>
       <c r="AH98" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI98" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8651,10 +8658,10 @@
         <v>150</v>
       </c>
       <c r="AH99" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI99" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8731,10 +8738,10 @@
         <v>149</v>
       </c>
       <c r="AH100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI100" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8802,10 +8809,10 @@
         <v>149</v>
       </c>
       <c r="AH101" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI101" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8876,10 +8883,10 @@
         <v>149</v>
       </c>
       <c r="AH102" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI102" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8950,10 +8957,10 @@
         <v>149</v>
       </c>
       <c r="AH103" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI103" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9024,10 +9031,10 @@
         <v>149</v>
       </c>
       <c r="AH104" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI104" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9095,10 +9102,10 @@
         <v>149</v>
       </c>
       <c r="AH105" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI105" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9169,10 +9176,10 @@
         <v>150</v>
       </c>
       <c r="AH106" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI106" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9243,10 +9250,10 @@
         <v>149</v>
       </c>
       <c r="AH107" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI107" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9317,10 +9324,10 @@
         <v>149</v>
       </c>
       <c r="AH108" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9388,10 +9395,10 @@
         <v>149</v>
       </c>
       <c r="AH109" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI109" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9462,10 +9469,10 @@
         <v>150</v>
       </c>
       <c r="AH110" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI110" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9533,10 +9540,10 @@
         <v>151</v>
       </c>
       <c r="AH111" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI111" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9607,10 +9614,10 @@
         <v>150</v>
       </c>
       <c r="AH112" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI112" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9681,10 +9688,10 @@
         <v>148</v>
       </c>
       <c r="AH113" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI113" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9752,10 +9759,10 @@
         <v>151</v>
       </c>
       <c r="AH114" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI114" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9826,10 +9833,10 @@
         <v>150</v>
       </c>
       <c r="AH115" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI115" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9900,10 +9907,10 @@
         <v>149</v>
       </c>
       <c r="AH116" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI116" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -9974,10 +9981,10 @@
         <v>149</v>
       </c>
       <c r="AH117" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI117" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10048,10 +10055,10 @@
         <v>149</v>
       </c>
       <c r="AH118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI118" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10119,10 +10126,10 @@
         <v>149</v>
       </c>
       <c r="AH119" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI119" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10193,10 +10200,10 @@
         <v>150</v>
       </c>
       <c r="AH120" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI120" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10267,10 +10274,10 @@
         <v>149</v>
       </c>
       <c r="AH121" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI121" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10341,10 +10348,10 @@
         <v>149</v>
       </c>
       <c r="AH122" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI122" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10415,10 +10422,10 @@
         <v>149</v>
       </c>
       <c r="AH123" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI123" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10486,10 +10493,10 @@
         <v>149</v>
       </c>
       <c r="AH124" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI124" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10560,10 +10567,10 @@
         <v>150</v>
       </c>
       <c r="AH125" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI125" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10640,10 +10647,10 @@
         <v>150</v>
       </c>
       <c r="AH126" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI126" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10720,10 +10727,10 @@
         <v>150</v>
       </c>
       <c r="AH127" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI127" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10794,10 +10801,10 @@
         <v>153</v>
       </c>
       <c r="AH128" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI128" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10868,10 +10875,10 @@
         <v>153</v>
       </c>
       <c r="AH129" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI129" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10948,10 +10955,10 @@
         <v>153</v>
       </c>
       <c r="AH130" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI130" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11022,10 +11029,10 @@
         <v>153</v>
       </c>
       <c r="AH131" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI131" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11096,10 +11103,10 @@
         <v>153</v>
       </c>
       <c r="AH132" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI132" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11170,10 +11177,10 @@
         <v>153</v>
       </c>
       <c r="AH133" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI133" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11244,10 +11251,10 @@
         <v>153</v>
       </c>
       <c r="AH134" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI134" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11324,10 +11331,10 @@
         <v>153</v>
       </c>
       <c r="AH135" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI135" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11398,10 +11405,10 @@
         <v>153</v>
       </c>
       <c r="AH136" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI136" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11472,10 +11479,10 @@
         <v>153</v>
       </c>
       <c r="AH137" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI137" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11546,10 +11553,10 @@
         <v>153</v>
       </c>
       <c r="AH138" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI138" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11626,10 +11633,10 @@
         <v>153</v>
       </c>
       <c r="AH139" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI139" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11700,10 +11707,10 @@
         <v>153</v>
       </c>
       <c r="AH140" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI140" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11774,10 +11781,10 @@
         <v>153</v>
       </c>
       <c r="AH141" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI141" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11848,10 +11855,10 @@
         <v>153</v>
       </c>
       <c r="AH142" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI142" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11922,10 +11929,10 @@
         <v>153</v>
       </c>
       <c r="AH143" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI143" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -11996,10 +12003,10 @@
         <v>153</v>
       </c>
       <c r="AH144" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI144" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12070,10 +12077,10 @@
         <v>153</v>
       </c>
       <c r="AH145" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI145" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12144,10 +12151,10 @@
         <v>153</v>
       </c>
       <c r="AH146" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI146" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12218,10 +12225,10 @@
         <v>153</v>
       </c>
       <c r="AH147" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI147" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12292,10 +12299,10 @@
         <v>153</v>
       </c>
       <c r="AH148" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI148" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12366,10 +12373,10 @@
         <v>153</v>
       </c>
       <c r="AH149" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI149" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12446,10 +12453,10 @@
         <v>153</v>
       </c>
       <c r="AH150" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI150" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12520,10 +12527,10 @@
         <v>153</v>
       </c>
       <c r="AH151" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI151" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12594,10 +12601,10 @@
         <v>153</v>
       </c>
       <c r="AH152" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI152" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12668,10 +12675,10 @@
         <v>153</v>
       </c>
       <c r="AH153" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI153" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12742,10 +12749,10 @@
         <v>154</v>
       </c>
       <c r="AH154" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI154" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12816,10 +12823,10 @@
         <v>154</v>
       </c>
       <c r="AH155" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI155" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12890,10 +12897,10 @@
         <v>154</v>
       </c>
       <c r="AH156" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI156" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -12964,10 +12971,10 @@
         <v>154</v>
       </c>
       <c r="AH157" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI157" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13038,10 +13045,10 @@
         <v>154</v>
       </c>
       <c r="AH158" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI158" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13112,10 +13119,10 @@
         <v>154</v>
       </c>
       <c r="AH159" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI159" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13186,10 +13193,10 @@
         <v>154</v>
       </c>
       <c r="AH160" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI160" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13260,10 +13267,10 @@
         <v>154</v>
       </c>
       <c r="AH161" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI161" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13334,10 +13341,10 @@
         <v>154</v>
       </c>
       <c r="AH162" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI162" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13408,10 +13415,10 @@
         <v>154</v>
       </c>
       <c r="AH163" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI163" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13482,10 +13489,10 @@
         <v>154</v>
       </c>
       <c r="AH164" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI164" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13556,10 +13563,10 @@
         <v>154</v>
       </c>
       <c r="AH165" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI165" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13630,10 +13637,10 @@
         <v>154</v>
       </c>
       <c r="AH166" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI166" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13704,10 +13711,10 @@
         <v>154</v>
       </c>
       <c r="AH167" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI167" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13778,10 +13785,10 @@
         <v>154</v>
       </c>
       <c r="AH168" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI168" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13852,10 +13859,10 @@
         <v>154</v>
       </c>
       <c r="AH169" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI169" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13926,10 +13933,10 @@
         <v>154</v>
       </c>
       <c r="AH170" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI170" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14000,10 +14007,10 @@
         <v>154</v>
       </c>
       <c r="AH171" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI171" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14074,10 +14081,10 @@
         <v>154</v>
       </c>
       <c r="AH172" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI172" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14148,10 +14155,10 @@
         <v>154</v>
       </c>
       <c r="AH173" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AI173" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14225,10 +14232,10 @@
         <v>154</v>
       </c>
       <c r="AH174" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI174" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14302,10 +14309,10 @@
         <v>154</v>
       </c>
       <c r="AH175" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI175" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14379,10 +14386,10 @@
         <v>154</v>
       </c>
       <c r="AH176" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI176" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14456,10 +14463,10 @@
         <v>154</v>
       </c>
       <c r="AH177" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI177" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14533,10 +14540,10 @@
         <v>154</v>
       </c>
       <c r="AH178" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI178" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14610,10 +14617,10 @@
         <v>154</v>
       </c>
       <c r="AH179" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI179" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14687,10 +14694,10 @@
         <v>154</v>
       </c>
       <c r="AH180" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI180" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14764,10 +14771,10 @@
         <v>154</v>
       </c>
       <c r="AH181" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI181" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14841,10 +14848,10 @@
         <v>154</v>
       </c>
       <c r="AH182" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI182" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14918,10 +14925,10 @@
         <v>154</v>
       </c>
       <c r="AH183" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI183" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -14995,10 +15002,10 @@
         <v>154</v>
       </c>
       <c r="AH184" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI184" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15072,10 +15079,10 @@
         <v>154</v>
       </c>
       <c r="AH185" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI185" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15149,10 +15156,10 @@
         <v>154</v>
       </c>
       <c r="AH186" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI186" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15226,10 +15233,10 @@
         <v>154</v>
       </c>
       <c r="AH187" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI187" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15297,10 +15304,10 @@
         <v>154</v>
       </c>
       <c r="AH188" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI188" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15368,10 +15375,10 @@
         <v>154</v>
       </c>
       <c r="AH189" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI189" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15439,10 +15446,10 @@
         <v>154</v>
       </c>
       <c r="AH190" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI190" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15510,10 +15517,10 @@
         <v>154</v>
       </c>
       <c r="AH191" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI191" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15581,10 +15588,10 @@
         <v>154</v>
       </c>
       <c r="AH192" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI192" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15652,10 +15659,10 @@
         <v>154</v>
       </c>
       <c r="AH193" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI193" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15723,10 +15730,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI194" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15794,10 +15801,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI195" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15865,10 +15872,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI196" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15936,10 +15943,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI197" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16007,10 +16014,10 @@
         <v>155</v>
       </c>
       <c r="AH198" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI198" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16078,10 +16085,10 @@
         <v>55</v>
       </c>
       <c r="AH199" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI199" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16149,10 +16156,10 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI200" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16220,10 +16227,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI201" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16291,10 +16298,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI202" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16362,10 +16369,10 @@
         <v>155</v>
       </c>
       <c r="AH203" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI203" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16433,10 +16440,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI204" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16504,10 +16511,10 @@
         <v>155</v>
       </c>
       <c r="AH205" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI205" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16575,10 +16582,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI206" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16646,10 +16653,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI207" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16717,10 +16724,10 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI208" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16788,10 +16795,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI209" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16859,10 +16866,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI210" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16930,10 +16937,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI211" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17001,10 +17008,10 @@
         <v>155</v>
       </c>
       <c r="AH212" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI212" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17072,10 +17079,10 @@
         <v>55</v>
       </c>
       <c r="AH213" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI213" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17146,10 +17153,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI214" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17220,10 +17227,10 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI215" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17294,10 +17301,10 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI216" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17368,10 +17375,10 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI217" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17439,10 +17446,10 @@
         <v>54</v>
       </c>
       <c r="AH218" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI218" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17510,10 +17517,10 @@
         <v>54</v>
       </c>
       <c r="AH219" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI219" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17584,10 +17591,10 @@
         <v>54</v>
       </c>
       <c r="AH220" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI220" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17655,10 +17662,10 @@
         <v>54</v>
       </c>
       <c r="AH221" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI221" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17726,21 +17733,21 @@
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AH222" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI222" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B223" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
@@ -17770,7 +17777,7 @@
         <v>46275</v>
       </c>
       <c r="O223" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P223">
         <v>8</v>
@@ -17779,25 +17786,22 @@
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>16976300</v>
+        <v>17399403</v>
       </c>
       <c r="S223" t="s">
-        <v>141</v>
-      </c>
-      <c r="T223" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="U223" t="s">
         <v>165</v>
       </c>
       <c r="V223" s="1">
-        <v>46274.47210818287</v>
+        <v>46274.60593387731</v>
       </c>
       <c r="W223">
         <v>-1</v>
       </c>
       <c r="X223" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y223" t="s">
         <v>243</v>
@@ -17806,27 +17810,27 @@
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AH223" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI223" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
       </c>
       <c r="D224" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E224" t="s">
         <v>54</v>
@@ -17850,7 +17854,7 @@
         <v>46275</v>
       </c>
       <c r="O224" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P224">
         <v>8</v>
@@ -17859,25 +17863,25 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>18090250</v>
+        <v>16976300</v>
       </c>
       <c r="S224" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="T224" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U224" t="s">
         <v>165</v>
       </c>
       <c r="V224" s="1">
-        <v>46274.48792050926</v>
+        <v>46274.47210818287</v>
       </c>
       <c r="W224">
         <v>-1</v>
       </c>
       <c r="X224" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y224" t="s">
         <v>244</v>
@@ -17886,33 +17890,33 @@
         <v>0</v>
       </c>
       <c r="AC224" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AH224" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI224" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B225" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
       </c>
       <c r="D225" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E225" t="s">
         <v>54</v>
       </c>
       <c r="F225" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G225">
         <v>9746</v>
@@ -17929,6 +17933,9 @@
       <c r="N225" s="1">
         <v>46275</v>
       </c>
+      <c r="O225" t="s">
+        <v>129</v>
+      </c>
       <c r="P225">
         <v>8</v>
       </c>
@@ -17936,72 +17943,78 @@
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>18190457</v>
+        <v>18090250</v>
       </c>
       <c r="S225" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="T225" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U225" t="s">
         <v>165</v>
       </c>
       <c r="V225" s="1">
-        <v>46274.34198912037</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W225">
         <v>-1</v>
       </c>
       <c r="X225" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="Y225" t="s">
+        <v>245</v>
       </c>
       <c r="AB225">
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AH225" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AI225" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B226" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
       </c>
       <c r="D226" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E226" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F226" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G226">
-        <v>1866</v>
+        <v>9746</v>
       </c>
       <c r="H226">
         <v>0</v>
       </c>
       <c r="I226" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J226" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N226" s="1">
-        <v>46274</v>
+        <v>46275</v>
+      </c>
+      <c r="O226" t="s">
+        <v>129</v>
       </c>
       <c r="P226">
         <v>8</v>
@@ -18010,48 +18023,48 @@
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>17968368</v>
+        <v>18179154</v>
       </c>
       <c r="S226" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="T226" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U226" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V226" s="1">
-        <v>46274.36843923611</v>
+        <v>46274.588374375</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X226" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Y226" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AB226">
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AH226" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AI226" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B227" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
@@ -18060,25 +18073,25 @@
         <v>51</v>
       </c>
       <c r="E227" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F227" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G227">
-        <v>1867</v>
+        <v>9746</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J227" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="N227" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="P227">
         <v>8</v>
@@ -18087,45 +18100,45 @@
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>17968379</v>
+        <v>18190457</v>
       </c>
       <c r="S227" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="T227" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U227" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V227" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.34198912037</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X227" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AB227">
         <v>0</v>
       </c>
       <c r="AC227" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AH227" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AI227" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B228" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
@@ -18134,25 +18147,25 @@
         <v>51</v>
       </c>
       <c r="E228" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F228" t="s">
         <v>56</v>
       </c>
       <c r="G228">
-        <v>11303</v>
+        <v>1866</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J228" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="N228" s="1">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="P228">
         <v>8</v>
@@ -18161,119 +18174,122 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>17399454</v>
+        <v>17968368</v>
       </c>
       <c r="S228" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="T228" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="U228" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V228" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W228">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X228" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="Y228" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AB228">
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH228" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AI228" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B229" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E229" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F229" t="s">
         <v>56</v>
       </c>
       <c r="G229">
-        <v>5989</v>
+        <v>1867</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J229" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="N229" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="P229">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q229">
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>17941177</v>
+        <v>17968379</v>
       </c>
       <c r="S229" t="s">
-        <v>154</v>
+        <v>149</v>
+      </c>
+      <c r="T229" t="s">
+        <v>149</v>
       </c>
       <c r="U229" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="V229" s="1">
-        <v>46274.41771849537</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X229" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AH229" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI229" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B230" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
@@ -18288,69 +18304,75 @@
         <v>56</v>
       </c>
       <c r="G230">
-        <v>5989</v>
+        <v>11303</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J230" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="N230" s="1">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="P230">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q230">
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>17952385</v>
+        <v>17399454</v>
       </c>
       <c r="S230" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="T230" t="s">
+        <v>163</v>
       </c>
       <c r="U230" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V230" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W230">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="X230" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="Y230" t="s">
+        <v>248</v>
       </c>
       <c r="AB230">
         <v>0</v>
       </c>
       <c r="AC230" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH230" t="s">
         <v>253</v>
       </c>
       <c r="AI230" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B231" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
@@ -18380,7 +18402,7 @@
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>17952569</v>
+        <v>17941177</v>
       </c>
       <c r="S231" t="s">
         <v>154</v>
@@ -18389,13 +18411,13 @@
         <v>164</v>
       </c>
       <c r="V231" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W231">
         <v>1</v>
       </c>
       <c r="X231" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AB231">
         <v>0</v>
@@ -18404,30 +18426,30 @@
         <v>154</v>
       </c>
       <c r="AH231" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI231" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B232" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
       </c>
       <c r="D232" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E232" t="s">
         <v>54</v>
       </c>
       <c r="F232" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G232">
         <v>5989</v>
@@ -18451,7 +18473,7 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>18164516</v>
+        <v>17952385</v>
       </c>
       <c r="S232" t="s">
         <v>154</v>
@@ -18460,13 +18482,13 @@
         <v>164</v>
       </c>
       <c r="V232" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W232">
         <v>1</v>
       </c>
       <c r="X232" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB232">
         <v>0</v>
@@ -18475,30 +18497,30 @@
         <v>154</v>
       </c>
       <c r="AH232" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI232" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B233" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E233" t="s">
         <v>54</v>
       </c>
       <c r="F233" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G233">
         <v>5989</v>
@@ -18522,7 +18544,7 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>18178157</v>
+        <v>17952569</v>
       </c>
       <c r="S233" t="s">
         <v>154</v>
@@ -18531,13 +18553,13 @@
         <v>164</v>
       </c>
       <c r="V233" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W233">
         <v>1</v>
       </c>
       <c r="X233" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB233">
         <v>0</v>
@@ -18546,45 +18568,45 @@
         <v>154</v>
       </c>
       <c r="AH233" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI233" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B234" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
       </c>
       <c r="D234" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
       </c>
       <c r="F234" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G234">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H234">
         <v>0</v>
       </c>
       <c r="I234" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J234" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N234" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P234">
         <v>9</v>
@@ -18593,42 +18615,42 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>17941187</v>
+        <v>18164516</v>
       </c>
       <c r="S234" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="U234" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X234" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AB234">
         <v>0</v>
       </c>
       <c r="AC234" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="AH234" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI234" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B235" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
@@ -18640,22 +18662,22 @@
         <v>54</v>
       </c>
       <c r="F235" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G235">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H235">
         <v>0</v>
       </c>
       <c r="I235" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J235" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N235" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P235">
         <v>9</v>
@@ -18664,48 +18686,48 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>17952400</v>
+        <v>18178157</v>
       </c>
       <c r="S235" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="U235" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X235" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="AB235">
         <v>0</v>
       </c>
       <c r="AC235" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="AH235" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI235" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B236" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
@@ -18735,7 +18757,7 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>17952580</v>
+        <v>17941187</v>
       </c>
       <c r="S236" t="s">
         <v>54</v>
@@ -18744,13 +18766,13 @@
         <v>166</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W236">
         <v>0</v>
       </c>
       <c r="X236" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AB236">
         <v>0</v>
@@ -18759,30 +18781,30 @@
         <v>54</v>
       </c>
       <c r="AH236" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI236" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B237" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E237" t="s">
         <v>54</v>
       </c>
       <c r="F237" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G237">
         <v>6215</v>
@@ -18806,7 +18828,7 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>18164523</v>
+        <v>17952400</v>
       </c>
       <c r="S237" t="s">
         <v>54</v>
@@ -18815,13 +18837,13 @@
         <v>166</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W237">
         <v>0</v>
       </c>
       <c r="X237" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB237">
         <v>0</v>
@@ -18830,30 +18852,30 @@
         <v>54</v>
       </c>
       <c r="AH237" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI237" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B238" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
       </c>
       <c r="D238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
       </c>
       <c r="F238" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G238">
         <v>6215</v>
@@ -18877,34 +18899,176 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>18178163</v>
+        <v>17952580</v>
       </c>
       <c r="S238" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U238" t="s">
         <v>166</v>
       </c>
       <c r="V238" s="1">
+        <v>46274.41777481481</v>
+      </c>
+      <c r="W238">
+        <v>0</v>
+      </c>
+      <c r="X238" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB238">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH238" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI238" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="239" spans="1:35">
+      <c r="A239">
+        <v>6945</v>
+      </c>
+      <c r="B239" t="s">
+        <v>39</v>
+      </c>
+      <c r="C239" t="s">
+        <v>50</v>
+      </c>
+      <c r="D239" t="s">
+        <v>52</v>
+      </c>
+      <c r="E239" t="s">
+        <v>54</v>
+      </c>
+      <c r="F239" t="s">
+        <v>57</v>
+      </c>
+      <c r="G239">
+        <v>6215</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239" t="s">
+        <v>65</v>
+      </c>
+      <c r="J239" t="s">
+        <v>121</v>
+      </c>
+      <c r="N239" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P239">
+        <v>9</v>
+      </c>
+      <c r="Q239">
+        <v>2026</v>
+      </c>
+      <c r="R239">
+        <v>18164523</v>
+      </c>
+      <c r="S239" t="s">
+        <v>54</v>
+      </c>
+      <c r="U239" t="s">
+        <v>166</v>
+      </c>
+      <c r="V239" s="1">
+        <v>46274.41799332176</v>
+      </c>
+      <c r="W239">
+        <v>0</v>
+      </c>
+      <c r="X239" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB239">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH239" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI239" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="240" spans="1:35">
+      <c r="A240">
+        <v>6949</v>
+      </c>
+      <c r="B240" t="s">
+        <v>37</v>
+      </c>
+      <c r="C240" t="s">
+        <v>50</v>
+      </c>
+      <c r="D240" t="s">
+        <v>51</v>
+      </c>
+      <c r="E240" t="s">
+        <v>54</v>
+      </c>
+      <c r="F240" t="s">
+        <v>57</v>
+      </c>
+      <c r="G240">
+        <v>6215</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240" t="s">
+        <v>65</v>
+      </c>
+      <c r="J240" t="s">
+        <v>121</v>
+      </c>
+      <c r="N240" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P240">
+        <v>9</v>
+      </c>
+      <c r="Q240">
+        <v>2026</v>
+      </c>
+      <c r="R240">
+        <v>18178163</v>
+      </c>
+      <c r="S240" t="s">
+        <v>155</v>
+      </c>
+      <c r="U240" t="s">
+        <v>166</v>
+      </c>
+      <c r="V240" s="1">
         <v>46274.41800085648</v>
       </c>
-      <c r="W238">
-        <v>0</v>
-      </c>
-      <c r="X238" t="s">
+      <c r="W240">
+        <v>0</v>
+      </c>
+      <c r="X240" t="s">
         <v>169</v>
       </c>
-      <c r="AB238">
-        <v>0</v>
-      </c>
-      <c r="AC238" t="s">
+      <c r="AB240">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="s">
         <v>155</v>
       </c>
-      <c r="AH238" t="s">
-        <v>253</v>
-      </c>
-      <c r="AI238" t="s">
+      <c r="AH240" t="s">
         <v>255</v>
+      </c>
+      <c r="AI240" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="258">
   <si>
     <t>CodCliente</t>
   </si>
@@ -699,9 +699,6 @@
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1792]. - Data Comentário: 01/09/2026 06:02</t>
   </si>
   <si>
-    <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1867]. - Data Comentário: 01/09/2026 06:01</t>
-  </si>
-  <si>
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1793]. - Data Comentário: 01/09/2026 06:02</t>
   </si>
   <si>
@@ -775,6 +772,10 @@
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 
+EM PROCESSO - Data Comentário: 08/09/2026 19:19</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 09/09/2026 10:17:37. - Data Comentário: 09/09/2026 10:12</t>
@@ -13201,16 +13202,16 @@
     </row>
     <row r="161" spans="1:35">
       <c r="A161">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B161" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C161" t="s">
         <v>50</v>
       </c>
       <c r="D161" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E161" t="s">
         <v>54</v>
@@ -13240,7 +13241,7 @@
         <v>2026</v>
       </c>
       <c r="R161">
-        <v>17222405</v>
+        <v>17941156</v>
       </c>
       <c r="S161" t="s">
         <v>154</v>
@@ -13249,13 +13250,13 @@
         <v>165</v>
       </c>
       <c r="V161" s="1">
-        <v>46266.25161940972</v>
+        <v>46266.25232392361</v>
       </c>
       <c r="W161">
         <v>-1</v>
       </c>
       <c r="X161" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Y161" t="s">
         <v>223</v>
@@ -13275,16 +13276,16 @@
     </row>
     <row r="162" spans="1:35">
       <c r="A162">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B162" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C162" t="s">
         <v>50</v>
       </c>
       <c r="D162" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E162" t="s">
         <v>54</v>
@@ -13314,7 +13315,7 @@
         <v>2026</v>
       </c>
       <c r="R162">
-        <v>17941156</v>
+        <v>18056705</v>
       </c>
       <c r="S162" t="s">
         <v>154</v>
@@ -13323,16 +13324,16 @@
         <v>165</v>
       </c>
       <c r="V162" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W162">
         <v>-1</v>
       </c>
       <c r="X162" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="Y162" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AB162">
         <v>0</v>
@@ -13349,10 +13350,10 @@
     </row>
     <row r="163" spans="1:35">
       <c r="A163">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B163" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C163" t="s">
         <v>50</v>
@@ -13364,7 +13365,7 @@
         <v>54</v>
       </c>
       <c r="F163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G163">
         <v>951</v>
@@ -13388,7 +13389,7 @@
         <v>2026</v>
       </c>
       <c r="R163">
-        <v>18056705</v>
+        <v>18164501</v>
       </c>
       <c r="S163" t="s">
         <v>154</v>
@@ -13397,13 +13398,13 @@
         <v>165</v>
       </c>
       <c r="V163" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W163">
         <v>-1</v>
       </c>
       <c r="X163" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y163" t="s">
         <v>224</v>
@@ -13423,25 +13424,25 @@
     </row>
     <row r="164" spans="1:35">
       <c r="A164">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B164" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C164" t="s">
         <v>50</v>
       </c>
       <c r="D164" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E164" t="s">
         <v>54</v>
       </c>
       <c r="F164" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G164">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -13450,10 +13451,10 @@
         <v>64</v>
       </c>
       <c r="J164" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N164" s="1">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="P164">
         <v>8</v>
@@ -13462,7 +13463,7 @@
         <v>2026</v>
       </c>
       <c r="R164">
-        <v>18164501</v>
+        <v>17398883</v>
       </c>
       <c r="S164" t="s">
         <v>154</v>
@@ -13471,13 +13472,13 @@
         <v>165</v>
       </c>
       <c r="V164" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25305</v>
       </c>
       <c r="W164">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="X164" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Y164" t="s">
         <v>225</v>
@@ -13497,16 +13498,16 @@
     </row>
     <row r="165" spans="1:35">
       <c r="A165">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B165" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C165" t="s">
         <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E165" t="s">
         <v>54</v>
@@ -13536,7 +13537,7 @@
         <v>2026</v>
       </c>
       <c r="R165">
-        <v>17398883</v>
+        <v>16962107</v>
       </c>
       <c r="S165" t="s">
         <v>154</v>
@@ -13545,13 +13546,13 @@
         <v>165</v>
       </c>
       <c r="V165" s="1">
-        <v>46266.25305</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W165">
         <v>-16</v>
       </c>
       <c r="X165" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Y165" t="s">
         <v>226</v>
@@ -13571,19 +13572,19 @@
     </row>
     <row r="166" spans="1:35">
       <c r="A166">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C166" t="s">
         <v>50</v>
       </c>
       <c r="D166" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E166" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F166" t="s">
         <v>56</v>
@@ -13610,7 +13611,7 @@
         <v>2026</v>
       </c>
       <c r="R166">
-        <v>16962107</v>
+        <v>17042317</v>
       </c>
       <c r="S166" t="s">
         <v>154</v>
@@ -13619,13 +13620,13 @@
         <v>165</v>
       </c>
       <c r="V166" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W166">
         <v>-16</v>
       </c>
       <c r="X166" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="Y166" t="s">
         <v>227</v>
@@ -13645,19 +13646,19 @@
     </row>
     <row r="167" spans="1:35">
       <c r="A167">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B167" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C167" t="s">
         <v>50</v>
       </c>
       <c r="D167" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E167" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F167" t="s">
         <v>56</v>
@@ -13684,7 +13685,7 @@
         <v>2026</v>
       </c>
       <c r="R167">
-        <v>17042317</v>
+        <v>17941166</v>
       </c>
       <c r="S167" t="s">
         <v>154</v>
@@ -13693,13 +13694,13 @@
         <v>165</v>
       </c>
       <c r="V167" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W167">
         <v>-16</v>
       </c>
       <c r="X167" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Y167" t="s">
         <v>228</v>
@@ -13719,22 +13720,22 @@
     </row>
     <row r="168" spans="1:35">
       <c r="A168">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B168" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C168" t="s">
         <v>50</v>
       </c>
       <c r="D168" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E168" t="s">
         <v>54</v>
       </c>
       <c r="F168" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G168">
         <v>953</v>
@@ -13758,7 +13759,7 @@
         <v>2026</v>
       </c>
       <c r="R168">
-        <v>17941166</v>
+        <v>18178144</v>
       </c>
       <c r="S168" t="s">
         <v>154</v>
@@ -13767,13 +13768,13 @@
         <v>165</v>
       </c>
       <c r="V168" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W168">
         <v>-16</v>
       </c>
       <c r="X168" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y168" t="s">
         <v>229</v>
@@ -13793,10 +13794,10 @@
     </row>
     <row r="169" spans="1:35">
       <c r="A169">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B169" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C169" t="s">
         <v>50</v>
@@ -13808,10 +13809,10 @@
         <v>54</v>
       </c>
       <c r="F169" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G169">
-        <v>953</v>
+        <v>7022</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -13820,10 +13821,10 @@
         <v>64</v>
       </c>
       <c r="J169" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N169" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="P169">
         <v>8</v>
@@ -13832,7 +13833,7 @@
         <v>2026</v>
       </c>
       <c r="R169">
-        <v>18178144</v>
+        <v>17399270</v>
       </c>
       <c r="S169" t="s">
         <v>154</v>
@@ -13841,13 +13842,13 @@
         <v>165</v>
       </c>
       <c r="V169" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W169">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="X169" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y169" t="s">
         <v>230</v>
@@ -13867,10 +13868,10 @@
     </row>
     <row r="170" spans="1:35">
       <c r="A170">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B170" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C170" t="s">
         <v>50</v>
@@ -13879,7 +13880,7 @@
         <v>51</v>
       </c>
       <c r="E170" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F170" t="s">
         <v>56</v>
@@ -13906,7 +13907,7 @@
         <v>2026</v>
       </c>
       <c r="R170">
-        <v>17399270</v>
+        <v>17042505</v>
       </c>
       <c r="S170" t="s">
         <v>154</v>
@@ -13915,13 +13916,13 @@
         <v>165</v>
       </c>
       <c r="V170" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W170">
         <v>-9</v>
       </c>
       <c r="X170" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="Y170" t="s">
         <v>231</v>
@@ -13941,10 +13942,10 @@
     </row>
     <row r="171" spans="1:35">
       <c r="A171">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B171" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C171" t="s">
         <v>50</v>
@@ -13953,7 +13954,7 @@
         <v>51</v>
       </c>
       <c r="E171" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F171" t="s">
         <v>56</v>
@@ -13980,7 +13981,7 @@
         <v>2026</v>
       </c>
       <c r="R171">
-        <v>17042505</v>
+        <v>17952421</v>
       </c>
       <c r="S171" t="s">
         <v>154</v>
@@ -13989,13 +13990,13 @@
         <v>165</v>
       </c>
       <c r="V171" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W171">
         <v>-9</v>
       </c>
       <c r="X171" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y171" t="s">
         <v>232</v>
@@ -14015,10 +14016,10 @@
     </row>
     <row r="172" spans="1:35">
       <c r="A172">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B172" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C172" t="s">
         <v>50</v>
@@ -14030,7 +14031,7 @@
         <v>54</v>
       </c>
       <c r="F172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G172">
         <v>7022</v>
@@ -14054,7 +14055,7 @@
         <v>2026</v>
       </c>
       <c r="R172">
-        <v>17952421</v>
+        <v>18178174</v>
       </c>
       <c r="S172" t="s">
         <v>154</v>
@@ -14063,13 +14064,13 @@
         <v>165</v>
       </c>
       <c r="V172" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W172">
         <v>-9</v>
       </c>
       <c r="X172" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Y172" t="s">
         <v>233</v>
@@ -14089,10 +14090,10 @@
     </row>
     <row r="173" spans="1:35">
       <c r="A173">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B173" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C173" t="s">
         <v>50</v>
@@ -14104,10 +14105,10 @@
         <v>54</v>
       </c>
       <c r="F173" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G173">
-        <v>7022</v>
+        <v>9085</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -14116,34 +14117,37 @@
         <v>64</v>
       </c>
       <c r="J173" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N173" s="1">
-        <v>46283</v>
+        <v>46268</v>
+      </c>
+      <c r="O173" t="s">
+        <v>126</v>
       </c>
       <c r="P173">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q173">
         <v>2026</v>
       </c>
       <c r="R173">
-        <v>18178174</v>
+        <v>17399353</v>
       </c>
       <c r="S173" t="s">
         <v>154</v>
       </c>
       <c r="U173" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V173" s="1">
-        <v>46266.25369988426</v>
+        <v>46268.62318445602</v>
       </c>
       <c r="W173">
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="X173" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y173" t="s">
         <v>234</v>
@@ -14155,7 +14159,7 @@
         <v>154</v>
       </c>
       <c r="AH173" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI173" t="s">
         <v>256</v>
@@ -14163,16 +14167,16 @@
     </row>
     <row r="174" spans="1:35">
       <c r="A174">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B174" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C174" t="s">
         <v>50</v>
       </c>
       <c r="D174" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E174" t="s">
         <v>54</v>
@@ -14205,7 +14209,7 @@
         <v>2026</v>
       </c>
       <c r="R174">
-        <v>17399353</v>
+        <v>16962370</v>
       </c>
       <c r="S174" t="s">
         <v>154</v>
@@ -14214,13 +14218,13 @@
         <v>166</v>
       </c>
       <c r="V174" s="1">
-        <v>46268.62318445602</v>
+        <v>46268.62319864584</v>
       </c>
       <c r="W174">
         <v>6</v>
       </c>
       <c r="X174" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Y174" t="s">
         <v>235</v>
@@ -14240,16 +14244,16 @@
     </row>
     <row r="175" spans="1:35">
       <c r="A175">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B175" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C175" t="s">
         <v>50</v>
       </c>
       <c r="D175" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E175" t="s">
         <v>54</v>
@@ -14282,7 +14286,7 @@
         <v>2026</v>
       </c>
       <c r="R175">
-        <v>16962370</v>
+        <v>16976260</v>
       </c>
       <c r="S175" t="s">
         <v>154</v>
@@ -14291,16 +14295,16 @@
         <v>166</v>
       </c>
       <c r="V175" s="1">
-        <v>46268.62319864584</v>
+        <v>46268.62320026621</v>
       </c>
       <c r="W175">
         <v>6</v>
       </c>
       <c r="X175" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y175" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB175">
         <v>0</v>
@@ -14317,10 +14321,10 @@
     </row>
     <row r="176" spans="1:35">
       <c r="A176">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B176" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C176" t="s">
         <v>50</v>
@@ -14359,7 +14363,7 @@
         <v>2026</v>
       </c>
       <c r="R176">
-        <v>16976260</v>
+        <v>17222852</v>
       </c>
       <c r="S176" t="s">
         <v>154</v>
@@ -14368,16 +14372,16 @@
         <v>166</v>
       </c>
       <c r="V176" s="1">
-        <v>46268.62320026621</v>
+        <v>46268.62320177083</v>
       </c>
       <c r="W176">
         <v>6</v>
       </c>
       <c r="X176" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y176" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB176">
         <v>0</v>
@@ -14394,10 +14398,10 @@
     </row>
     <row r="177" spans="1:35">
       <c r="A177">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B177" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C177" t="s">
         <v>50</v>
@@ -14406,7 +14410,7 @@
         <v>51</v>
       </c>
       <c r="E177" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F177" t="s">
         <v>56</v>
@@ -14436,7 +14440,7 @@
         <v>2026</v>
       </c>
       <c r="R177">
-        <v>17222852</v>
+        <v>17042569</v>
       </c>
       <c r="S177" t="s">
         <v>154</v>
@@ -14445,16 +14449,16 @@
         <v>166</v>
       </c>
       <c r="V177" s="1">
-        <v>46268.62320177083</v>
+        <v>46268.62320378472</v>
       </c>
       <c r="W177">
         <v>6</v>
       </c>
       <c r="X177" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Y177" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB177">
         <v>0</v>
@@ -14471,16 +14475,16 @@
     </row>
     <row r="178" spans="1:35">
       <c r="A178">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C178" t="s">
         <v>50</v>
       </c>
       <c r="D178" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E178" t="s">
         <v>55</v>
@@ -14513,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="R178">
-        <v>17042569</v>
+        <v>16960062</v>
       </c>
       <c r="S178" t="s">
         <v>154</v>
@@ -14522,7 +14526,7 @@
         <v>166</v>
       </c>
       <c r="V178" s="1">
-        <v>46268.62320378472</v>
+        <v>46268.62320393518</v>
       </c>
       <c r="W178">
         <v>6</v>
@@ -14531,7 +14535,7 @@
         <v>168</v>
       </c>
       <c r="Y178" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB178">
         <v>0</v>
@@ -14548,19 +14552,19 @@
     </row>
     <row r="179" spans="1:35">
       <c r="A179">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B179" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C179" t="s">
         <v>50</v>
       </c>
       <c r="D179" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E179" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F179" t="s">
         <v>56</v>
@@ -14590,7 +14594,7 @@
         <v>2026</v>
       </c>
       <c r="R179">
-        <v>16960062</v>
+        <v>17941207</v>
       </c>
       <c r="S179" t="s">
         <v>154</v>
@@ -14599,16 +14603,16 @@
         <v>166</v>
       </c>
       <c r="V179" s="1">
-        <v>46268.62320393518</v>
+        <v>46268.62320697917</v>
       </c>
       <c r="W179">
         <v>6</v>
       </c>
       <c r="X179" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Y179" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB179">
         <v>0</v>
@@ -14625,16 +14629,16 @@
     </row>
     <row r="180" spans="1:35">
       <c r="A180">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B180" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C180" t="s">
         <v>50</v>
       </c>
       <c r="D180" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E180" t="s">
         <v>54</v>
@@ -14667,7 +14671,7 @@
         <v>2026</v>
       </c>
       <c r="R180">
-        <v>17941207</v>
+        <v>17952433</v>
       </c>
       <c r="S180" t="s">
         <v>154</v>
@@ -14676,16 +14680,16 @@
         <v>166</v>
       </c>
       <c r="V180" s="1">
-        <v>46268.62320697917</v>
+        <v>46268.62320717592</v>
       </c>
       <c r="W180">
         <v>6</v>
       </c>
       <c r="X180" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="Y180" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB180">
         <v>0</v>
@@ -14702,16 +14706,16 @@
     </row>
     <row r="181" spans="1:35">
       <c r="A181">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B181" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C181" t="s">
         <v>50</v>
       </c>
       <c r="D181" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E181" t="s">
         <v>54</v>
@@ -14744,7 +14748,7 @@
         <v>2026</v>
       </c>
       <c r="R181">
-        <v>17952433</v>
+        <v>17952613</v>
       </c>
       <c r="S181" t="s">
         <v>154</v>
@@ -14753,7 +14757,7 @@
         <v>166</v>
       </c>
       <c r="V181" s="1">
-        <v>46268.62320717592</v>
+        <v>46268.62320732639</v>
       </c>
       <c r="W181">
         <v>6</v>
@@ -14762,7 +14766,7 @@
         <v>172</v>
       </c>
       <c r="Y181" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB181">
         <v>0</v>
@@ -14779,10 +14783,10 @@
     </row>
     <row r="182" spans="1:35">
       <c r="A182">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B182" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C182" t="s">
         <v>50</v>
@@ -14821,7 +14825,7 @@
         <v>2026</v>
       </c>
       <c r="R182">
-        <v>17952613</v>
+        <v>18056791</v>
       </c>
       <c r="S182" t="s">
         <v>154</v>
@@ -14830,7 +14834,7 @@
         <v>166</v>
       </c>
       <c r="V182" s="1">
-        <v>46268.62320732639</v>
+        <v>46268.62320810185</v>
       </c>
       <c r="W182">
         <v>6</v>
@@ -14839,7 +14843,7 @@
         <v>172</v>
       </c>
       <c r="Y182" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB182">
         <v>0</v>
@@ -14856,10 +14860,10 @@
     </row>
     <row r="183" spans="1:35">
       <c r="A183">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B183" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C183" t="s">
         <v>50</v>
@@ -14871,7 +14875,7 @@
         <v>54</v>
       </c>
       <c r="F183" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G183">
         <v>9085</v>
@@ -14898,7 +14902,7 @@
         <v>2026</v>
       </c>
       <c r="R183">
-        <v>18056791</v>
+        <v>18164544</v>
       </c>
       <c r="S183" t="s">
         <v>154</v>
@@ -14907,16 +14911,16 @@
         <v>166</v>
       </c>
       <c r="V183" s="1">
-        <v>46268.62320810185</v>
+        <v>46268.6232125</v>
       </c>
       <c r="W183">
         <v>6</v>
       </c>
       <c r="X183" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y183" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB183">
         <v>0</v>
@@ -14933,16 +14937,16 @@
     </row>
     <row r="184" spans="1:35">
       <c r="A184">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C184" t="s">
         <v>50</v>
       </c>
       <c r="D184" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E184" t="s">
         <v>54</v>
@@ -14975,7 +14979,7 @@
         <v>2026</v>
       </c>
       <c r="R184">
-        <v>18164544</v>
+        <v>18178181</v>
       </c>
       <c r="S184" t="s">
         <v>154</v>
@@ -14984,16 +14988,16 @@
         <v>166</v>
       </c>
       <c r="V184" s="1">
-        <v>46268.6232125</v>
+        <v>46268.62321412037</v>
       </c>
       <c r="W184">
         <v>6</v>
       </c>
       <c r="X184" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Y184" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB184">
         <v>0</v>
@@ -15010,16 +15014,16 @@
     </row>
     <row r="185" spans="1:35">
       <c r="A185">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B185" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
       </c>
       <c r="D185" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E185" t="s">
         <v>54</v>
@@ -15052,7 +15056,7 @@
         <v>2026</v>
       </c>
       <c r="R185">
-        <v>18178181</v>
+        <v>18188767</v>
       </c>
       <c r="S185" t="s">
         <v>154</v>
@@ -15061,16 +15065,16 @@
         <v>166</v>
       </c>
       <c r="V185" s="1">
-        <v>46268.62321412037</v>
+        <v>46268.6232128125</v>
       </c>
       <c r="W185">
         <v>6</v>
       </c>
       <c r="X185" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y185" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB185">
         <v>0</v>
@@ -15087,10 +15091,10 @@
     </row>
     <row r="186" spans="1:35">
       <c r="A186">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B186" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C186" t="s">
         <v>50</v>
@@ -15129,7 +15133,7 @@
         <v>2026</v>
       </c>
       <c r="R186">
-        <v>18188767</v>
+        <v>18188673</v>
       </c>
       <c r="S186" t="s">
         <v>154</v>
@@ -15138,7 +15142,7 @@
         <v>166</v>
       </c>
       <c r="V186" s="1">
-        <v>46268.6232128125</v>
+        <v>46268.62321296296</v>
       </c>
       <c r="W186">
         <v>6</v>
@@ -15147,7 +15151,7 @@
         <v>171</v>
       </c>
       <c r="Y186" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB186">
         <v>0</v>
@@ -15164,25 +15168,25 @@
     </row>
     <row r="187" spans="1:35">
       <c r="A187">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C187" t="s">
         <v>50</v>
       </c>
       <c r="D187" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E187" t="s">
         <v>54</v>
       </c>
       <c r="F187" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G187">
-        <v>9085</v>
+        <v>5989</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -15191,13 +15195,10 @@
         <v>64</v>
       </c>
       <c r="J187" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N187" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O187" t="s">
-        <v>126</v>
+        <v>46273</v>
       </c>
       <c r="P187">
         <v>9</v>
@@ -15206,25 +15207,22 @@
         <v>2026</v>
       </c>
       <c r="R187">
-        <v>18188673</v>
+        <v>17399127</v>
       </c>
       <c r="S187" t="s">
         <v>154</v>
       </c>
       <c r="U187" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V187" s="1">
-        <v>46268.62321296296</v>
+        <v>46269.41908927084</v>
       </c>
       <c r="W187">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X187" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y187" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="AB187">
         <v>0</v>
@@ -15241,16 +15239,16 @@
     </row>
     <row r="188" spans="1:35">
       <c r="A188">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C188" t="s">
         <v>50</v>
       </c>
       <c r="D188" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E188" t="s">
         <v>54</v>
@@ -15280,7 +15278,7 @@
         <v>2026</v>
       </c>
       <c r="R188">
-        <v>17399127</v>
+        <v>16962251</v>
       </c>
       <c r="S188" t="s">
         <v>154</v>
@@ -15289,13 +15287,13 @@
         <v>165</v>
       </c>
       <c r="V188" s="1">
-        <v>46269.41908927084</v>
+        <v>46269.41910457176</v>
       </c>
       <c r="W188">
         <v>1</v>
       </c>
       <c r="X188" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AB188">
         <v>0</v>
@@ -15312,16 +15310,16 @@
     </row>
     <row r="189" spans="1:35">
       <c r="A189">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B189" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C189" t="s">
         <v>50</v>
       </c>
       <c r="D189" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E189" t="s">
         <v>54</v>
@@ -15351,7 +15349,7 @@
         <v>2026</v>
       </c>
       <c r="R189">
-        <v>16962251</v>
+        <v>16976117</v>
       </c>
       <c r="S189" t="s">
         <v>154</v>
@@ -15360,13 +15358,13 @@
         <v>165</v>
       </c>
       <c r="V189" s="1">
-        <v>46269.41910457176</v>
+        <v>46269.37885223379</v>
       </c>
       <c r="W189">
         <v>1</v>
       </c>
       <c r="X189" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AB189">
         <v>0</v>
@@ -15383,10 +15381,10 @@
     </row>
     <row r="190" spans="1:35">
       <c r="A190">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B190" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
         <v>50</v>
@@ -15422,7 +15420,7 @@
         <v>2026</v>
       </c>
       <c r="R190">
-        <v>16976117</v>
+        <v>17222714</v>
       </c>
       <c r="S190" t="s">
         <v>154</v>
@@ -15431,13 +15429,13 @@
         <v>165</v>
       </c>
       <c r="V190" s="1">
-        <v>46269.37885223379</v>
+        <v>46269.3782503125</v>
       </c>
       <c r="W190">
         <v>1</v>
       </c>
       <c r="X190" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AB190">
         <v>0</v>
@@ -15454,10 +15452,10 @@
     </row>
     <row r="191" spans="1:35">
       <c r="A191">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B191" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C191" t="s">
         <v>50</v>
@@ -15466,7 +15464,7 @@
         <v>51</v>
       </c>
       <c r="E191" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F191" t="s">
         <v>56</v>
@@ -15493,7 +15491,7 @@
         <v>2026</v>
       </c>
       <c r="R191">
-        <v>17222714</v>
+        <v>17042423</v>
       </c>
       <c r="S191" t="s">
         <v>154</v>
@@ -15502,13 +15500,13 @@
         <v>165</v>
       </c>
       <c r="V191" s="1">
-        <v>46269.3782503125</v>
+        <v>46269.41913152778</v>
       </c>
       <c r="W191">
         <v>1</v>
       </c>
       <c r="X191" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB191">
         <v>0</v>
@@ -15525,16 +15523,16 @@
     </row>
     <row r="192" spans="1:35">
       <c r="A192">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B192" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C192" t="s">
         <v>50</v>
       </c>
       <c r="D192" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E192" t="s">
         <v>55</v>
@@ -15564,7 +15562,7 @@
         <v>2026</v>
       </c>
       <c r="R192">
-        <v>17042423</v>
+        <v>16959989</v>
       </c>
       <c r="S192" t="s">
         <v>154</v>
@@ -15573,7 +15571,7 @@
         <v>165</v>
       </c>
       <c r="V192" s="1">
-        <v>46269.41913152778</v>
+        <v>46269.41913775463</v>
       </c>
       <c r="W192">
         <v>1</v>
@@ -15596,37 +15594,37 @@
     </row>
     <row r="193" spans="1:35">
       <c r="A193">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B193" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E193" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F193" t="s">
         <v>56</v>
       </c>
       <c r="G193">
-        <v>5989</v>
+        <v>9087</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J193" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N193" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="P193">
         <v>9</v>
@@ -15635,28 +15633,28 @@
         <v>2026</v>
       </c>
       <c r="R193">
-        <v>16959989</v>
+        <v>17399373</v>
       </c>
       <c r="S193" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="U193" t="s">
         <v>165</v>
       </c>
       <c r="V193" s="1">
-        <v>46269.41913775463</v>
+        <v>46268.7596207176</v>
       </c>
       <c r="W193">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X193" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AB193">
         <v>0</v>
       </c>
       <c r="AC193" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="AH193" t="s">
         <v>255</v>
@@ -15667,16 +15665,16 @@
     </row>
     <row r="194" spans="1:35">
       <c r="A194">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B194" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C194" t="s">
         <v>50</v>
       </c>
       <c r="D194" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E194" t="s">
         <v>54</v>
@@ -15706,7 +15704,7 @@
         <v>2026</v>
       </c>
       <c r="R194">
-        <v>17399373</v>
+        <v>16962390</v>
       </c>
       <c r="S194" t="s">
         <v>54</v>
@@ -15715,13 +15713,13 @@
         <v>165</v>
       </c>
       <c r="V194" s="1">
-        <v>46268.7596207176</v>
+        <v>46268.75963109954</v>
       </c>
       <c r="W194">
         <v>5</v>
       </c>
       <c r="X194" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AB194">
         <v>0</v>
@@ -15738,16 +15736,16 @@
     </row>
     <row r="195" spans="1:35">
       <c r="A195">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B195" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C195" t="s">
         <v>50</v>
       </c>
       <c r="D195" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E195" t="s">
         <v>54</v>
@@ -15777,7 +15775,7 @@
         <v>2026</v>
       </c>
       <c r="R195">
-        <v>16962390</v>
+        <v>16976280</v>
       </c>
       <c r="S195" t="s">
         <v>54</v>
@@ -15786,13 +15784,13 @@
         <v>165</v>
       </c>
       <c r="V195" s="1">
-        <v>46268.75963109954</v>
+        <v>46268.75963225694</v>
       </c>
       <c r="W195">
         <v>5</v>
       </c>
       <c r="X195" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AB195">
         <v>0</v>
@@ -15809,10 +15807,10 @@
     </row>
     <row r="196" spans="1:35">
       <c r="A196">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B196" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C196" t="s">
         <v>50</v>
@@ -15848,7 +15846,7 @@
         <v>2026</v>
       </c>
       <c r="R196">
-        <v>16976280</v>
+        <v>17222885</v>
       </c>
       <c r="S196" t="s">
         <v>54</v>
@@ -15857,13 +15855,13 @@
         <v>165</v>
       </c>
       <c r="V196" s="1">
-        <v>46268.75963225694</v>
+        <v>46268.75963348379</v>
       </c>
       <c r="W196">
         <v>5</v>
       </c>
       <c r="X196" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AB196">
         <v>0</v>
@@ -15880,10 +15878,10 @@
     </row>
     <row r="197" spans="1:35">
       <c r="A197">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B197" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C197" t="s">
         <v>50</v>
@@ -15892,7 +15890,7 @@
         <v>51</v>
       </c>
       <c r="E197" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F197" t="s">
         <v>56</v>
@@ -15919,28 +15917,28 @@
         <v>2026</v>
       </c>
       <c r="R197">
-        <v>17222885</v>
+        <v>17042605</v>
       </c>
       <c r="S197" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U197" t="s">
         <v>165</v>
       </c>
       <c r="V197" s="1">
-        <v>46268.75963348379</v>
+        <v>46268.75963414352</v>
       </c>
       <c r="W197">
         <v>5</v>
       </c>
       <c r="X197" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB197">
         <v>0</v>
       </c>
       <c r="AC197" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH197" t="s">
         <v>255</v>
@@ -15951,16 +15949,16 @@
     </row>
     <row r="198" spans="1:35">
       <c r="A198">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B198" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C198" t="s">
         <v>50</v>
       </c>
       <c r="D198" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E198" t="s">
         <v>55</v>
@@ -15990,16 +15988,16 @@
         <v>2026</v>
       </c>
       <c r="R198">
-        <v>17042605</v>
+        <v>16960086</v>
       </c>
       <c r="S198" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="U198" t="s">
         <v>165</v>
       </c>
       <c r="V198" s="1">
-        <v>46268.75963414352</v>
+        <v>46268.62326365741</v>
       </c>
       <c r="W198">
         <v>5</v>
@@ -16011,7 +16009,7 @@
         <v>0</v>
       </c>
       <c r="AC198" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="AH198" t="s">
         <v>255</v>
@@ -16022,19 +16020,19 @@
     </row>
     <row r="199" spans="1:35">
       <c r="A199">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C199" t="s">
         <v>50</v>
       </c>
       <c r="D199" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E199" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F199" t="s">
         <v>56</v>
@@ -16061,28 +16059,28 @@
         <v>2026</v>
       </c>
       <c r="R199">
-        <v>16960086</v>
+        <v>17941227</v>
       </c>
       <c r="S199" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U199" t="s">
         <v>165</v>
       </c>
       <c r="V199" s="1">
-        <v>46268.62326365741</v>
+        <v>46268.75963472222</v>
       </c>
       <c r="W199">
         <v>5</v>
       </c>
       <c r="X199" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AB199">
         <v>0</v>
       </c>
       <c r="AC199" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH199" t="s">
         <v>255</v>
@@ -16093,16 +16091,16 @@
     </row>
     <row r="200" spans="1:35">
       <c r="A200">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B200" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C200" t="s">
         <v>50</v>
       </c>
       <c r="D200" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E200" t="s">
         <v>54</v>
@@ -16132,7 +16130,7 @@
         <v>2026</v>
       </c>
       <c r="R200">
-        <v>17941227</v>
+        <v>17952455</v>
       </c>
       <c r="S200" t="s">
         <v>54</v>
@@ -16141,13 +16139,13 @@
         <v>165</v>
       </c>
       <c r="V200" s="1">
-        <v>46268.75963472222</v>
+        <v>46268.75963475694</v>
       </c>
       <c r="W200">
         <v>5</v>
       </c>
       <c r="X200" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AB200">
         <v>0</v>
@@ -16164,16 +16162,16 @@
     </row>
     <row r="201" spans="1:35">
       <c r="A201">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
       </c>
       <c r="D201" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E201" t="s">
         <v>54</v>
@@ -16203,7 +16201,7 @@
         <v>2026</v>
       </c>
       <c r="R201">
-        <v>17952455</v>
+        <v>17952635</v>
       </c>
       <c r="S201" t="s">
         <v>54</v>
@@ -16212,7 +16210,7 @@
         <v>165</v>
       </c>
       <c r="V201" s="1">
-        <v>46268.75963475694</v>
+        <v>46268.75963506944</v>
       </c>
       <c r="W201">
         <v>5</v>
@@ -16235,10 +16233,10 @@
     </row>
     <row r="202" spans="1:35">
       <c r="A202">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B202" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C202" t="s">
         <v>50</v>
@@ -16274,16 +16272,16 @@
         <v>2026</v>
       </c>
       <c r="R202">
-        <v>17952635</v>
+        <v>18056811</v>
       </c>
       <c r="S202" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U202" t="s">
         <v>165</v>
       </c>
       <c r="V202" s="1">
-        <v>46268.75963506944</v>
+        <v>46268.7596360301</v>
       </c>
       <c r="W202">
         <v>5</v>
@@ -16295,7 +16293,7 @@
         <v>0</v>
       </c>
       <c r="AC202" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH202" t="s">
         <v>255</v>
@@ -16306,10 +16304,10 @@
     </row>
     <row r="203" spans="1:35">
       <c r="A203">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C203" t="s">
         <v>50</v>
@@ -16321,7 +16319,7 @@
         <v>54</v>
       </c>
       <c r="F203" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G203">
         <v>9087</v>
@@ -16345,28 +16343,28 @@
         <v>2026</v>
       </c>
       <c r="R203">
-        <v>18056811</v>
+        <v>18164558</v>
       </c>
       <c r="S203" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U203" t="s">
         <v>165</v>
       </c>
       <c r="V203" s="1">
-        <v>46268.7596360301</v>
+        <v>46268.62327121528</v>
       </c>
       <c r="W203">
         <v>5</v>
       </c>
       <c r="X203" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB203">
         <v>0</v>
       </c>
       <c r="AC203" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH203" t="s">
         <v>255</v>
@@ -16377,16 +16375,16 @@
     </row>
     <row r="204" spans="1:35">
       <c r="A204">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B204" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C204" t="s">
         <v>50</v>
       </c>
       <c r="D204" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E204" t="s">
         <v>54</v>
@@ -16416,28 +16414,28 @@
         <v>2026</v>
       </c>
       <c r="R204">
-        <v>18164558</v>
+        <v>18178193</v>
       </c>
       <c r="S204" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U204" t="s">
         <v>165</v>
       </c>
       <c r="V204" s="1">
-        <v>46268.62327121528</v>
+        <v>46268.75963931713</v>
       </c>
       <c r="W204">
         <v>5</v>
       </c>
       <c r="X204" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB204">
         <v>0</v>
       </c>
       <c r="AC204" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH204" t="s">
         <v>255</v>
@@ -16448,16 +16446,16 @@
     </row>
     <row r="205" spans="1:35">
       <c r="A205">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B205" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C205" t="s">
         <v>50</v>
       </c>
       <c r="D205" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E205" t="s">
         <v>54</v>
@@ -16487,28 +16485,28 @@
         <v>2026</v>
       </c>
       <c r="R205">
-        <v>18178193</v>
+        <v>18188781</v>
       </c>
       <c r="S205" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U205" t="s">
         <v>165</v>
       </c>
       <c r="V205" s="1">
-        <v>46268.75963931713</v>
+        <v>46268.75963822917</v>
       </c>
       <c r="W205">
         <v>5</v>
       </c>
       <c r="X205" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AB205">
         <v>0</v>
       </c>
       <c r="AC205" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="AH205" t="s">
         <v>255</v>
@@ -16519,10 +16517,10 @@
     </row>
     <row r="206" spans="1:35">
       <c r="A206">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B206" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C206" t="s">
         <v>50</v>
@@ -16558,7 +16556,7 @@
         <v>2026</v>
       </c>
       <c r="R206">
-        <v>18188781</v>
+        <v>18188687</v>
       </c>
       <c r="S206" t="s">
         <v>54</v>
@@ -16567,7 +16565,7 @@
         <v>165</v>
       </c>
       <c r="V206" s="1">
-        <v>46268.75963822917</v>
+        <v>46268.75963857639</v>
       </c>
       <c r="W206">
         <v>5</v>
@@ -16590,25 +16588,25 @@
     </row>
     <row r="207" spans="1:35">
       <c r="A207">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B207" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C207" t="s">
         <v>50</v>
       </c>
       <c r="D207" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E207" t="s">
         <v>54</v>
       </c>
       <c r="F207" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G207">
-        <v>9087</v>
+        <v>6215</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -16617,10 +16615,10 @@
         <v>65</v>
       </c>
       <c r="J207" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N207" s="1">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="P207">
         <v>9</v>
@@ -16629,7 +16627,7 @@
         <v>2026</v>
       </c>
       <c r="R207">
-        <v>18188687</v>
+        <v>17399147</v>
       </c>
       <c r="S207" t="s">
         <v>54</v>
@@ -16638,13 +16636,13 @@
         <v>165</v>
       </c>
       <c r="V207" s="1">
-        <v>46268.75963857639</v>
+        <v>46269.41908901621</v>
       </c>
       <c r="W207">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X207" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AB207">
         <v>0</v>
@@ -16661,16 +16659,16 @@
     </row>
     <row r="208" spans="1:35">
       <c r="A208">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B208" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C208" t="s">
         <v>50</v>
       </c>
       <c r="D208" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E208" t="s">
         <v>54</v>
@@ -16700,7 +16698,7 @@
         <v>2026</v>
       </c>
       <c r="R208">
-        <v>17399147</v>
+        <v>16962265</v>
       </c>
       <c r="S208" t="s">
         <v>54</v>
@@ -16709,13 +16707,13 @@
         <v>165</v>
       </c>
       <c r="V208" s="1">
-        <v>46269.41908901621</v>
+        <v>46269.41910425926</v>
       </c>
       <c r="W208">
         <v>0</v>
       </c>
       <c r="X208" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AB208">
         <v>0</v>
@@ -16732,16 +16730,16 @@
     </row>
     <row r="209" spans="1:35">
       <c r="A209">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B209" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C209" t="s">
         <v>50</v>
       </c>
       <c r="D209" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E209" t="s">
         <v>54</v>
@@ -16771,7 +16769,7 @@
         <v>2026</v>
       </c>
       <c r="R209">
-        <v>16962265</v>
+        <v>16976127</v>
       </c>
       <c r="S209" t="s">
         <v>54</v>
@@ -16780,13 +16778,13 @@
         <v>165</v>
       </c>
       <c r="V209" s="1">
-        <v>46269.41910425926</v>
+        <v>46269.37890997685</v>
       </c>
       <c r="W209">
         <v>0</v>
       </c>
       <c r="X209" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AB209">
         <v>0</v>
@@ -16803,10 +16801,10 @@
     </row>
     <row r="210" spans="1:35">
       <c r="A210">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B210" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C210" t="s">
         <v>50</v>
@@ -16842,7 +16840,7 @@
         <v>2026</v>
       </c>
       <c r="R210">
-        <v>16976127</v>
+        <v>17222729</v>
       </c>
       <c r="S210" t="s">
         <v>54</v>
@@ -16851,13 +16849,13 @@
         <v>165</v>
       </c>
       <c r="V210" s="1">
-        <v>46269.37890997685</v>
+        <v>46269.37833320602</v>
       </c>
       <c r="W210">
         <v>0</v>
       </c>
       <c r="X210" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AB210">
         <v>0</v>
@@ -16874,10 +16872,10 @@
     </row>
     <row r="211" spans="1:35">
       <c r="A211">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B211" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C211" t="s">
         <v>50</v>
@@ -16886,7 +16884,7 @@
         <v>51</v>
       </c>
       <c r="E211" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F211" t="s">
         <v>56</v>
@@ -16913,28 +16911,28 @@
         <v>2026</v>
       </c>
       <c r="R211">
-        <v>17222729</v>
+        <v>17042445</v>
       </c>
       <c r="S211" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="U211" t="s">
         <v>165</v>
       </c>
       <c r="V211" s="1">
-        <v>46269.37833320602</v>
+        <v>46269.41913112268</v>
       </c>
       <c r="W211">
         <v>0</v>
       </c>
       <c r="X211" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AB211">
         <v>0</v>
       </c>
       <c r="AC211" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="AH211" t="s">
         <v>255</v>
@@ -16945,16 +16943,16 @@
     </row>
     <row r="212" spans="1:35">
       <c r="A212">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B212" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C212" t="s">
         <v>50</v>
       </c>
       <c r="D212" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E212" t="s">
         <v>55</v>
@@ -16984,16 +16982,16 @@
         <v>2026</v>
       </c>
       <c r="R212">
-        <v>17042445</v>
+        <v>16960001</v>
       </c>
       <c r="S212" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="U212" t="s">
         <v>165</v>
       </c>
       <c r="V212" s="1">
-        <v>46269.41913112268</v>
+        <v>46269.41913740741</v>
       </c>
       <c r="W212">
         <v>0</v>
@@ -17005,7 +17003,7 @@
         <v>0</v>
       </c>
       <c r="AC212" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="AH212" t="s">
         <v>255</v>
@@ -17016,25 +17014,25 @@
     </row>
     <row r="213" spans="1:35">
       <c r="A213">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B213" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C213" t="s">
         <v>50</v>
       </c>
       <c r="D213" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E213" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F213" t="s">
         <v>56</v>
       </c>
       <c r="G213">
-        <v>6215</v>
+        <v>11001</v>
       </c>
       <c r="H213">
         <v>0</v>
@@ -17043,43 +17041,46 @@
         <v>65</v>
       </c>
       <c r="J213" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="N213" s="1">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="P213">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q213">
         <v>2026</v>
       </c>
       <c r="R213">
-        <v>16960001</v>
+        <v>16962453</v>
       </c>
       <c r="S213" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U213" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V213" s="1">
-        <v>46269.41913740741</v>
+        <v>46267.66131466435</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X213" t="s">
-        <v>168</v>
+        <v>177</v>
+      </c>
+      <c r="Y213" t="s">
+        <v>236</v>
       </c>
       <c r="AB213">
         <v>0</v>
       </c>
       <c r="AC213" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AI213" t="s">
         <v>256</v>
@@ -17117,28 +17118,28 @@
         <v>74</v>
       </c>
       <c r="N214" s="1">
-        <v>46259</v>
+        <v>46321</v>
       </c>
       <c r="P214">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q214">
         <v>2026</v>
       </c>
       <c r="R214">
-        <v>16962453</v>
+        <v>16962455</v>
       </c>
       <c r="S214" t="s">
         <v>54</v>
       </c>
       <c r="U214" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V214" s="1">
-        <v>46267.66131466435</v>
+        <v>46266.21595836805</v>
       </c>
       <c r="W214">
-        <v>15</v>
+        <v>-47</v>
       </c>
       <c r="X214" t="s">
         <v>177</v>
@@ -17161,16 +17162,16 @@
     </row>
     <row r="215" spans="1:35">
       <c r="A215">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B215" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C215" t="s">
         <v>50</v>
       </c>
       <c r="D215" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E215" t="s">
         <v>54</v>
@@ -17179,7 +17180,7 @@
         <v>56</v>
       </c>
       <c r="G215">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -17188,7 +17189,7 @@
         <v>65</v>
       </c>
       <c r="J215" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N215" s="1">
         <v>46321</v>
@@ -17200,7 +17201,7 @@
         <v>2026</v>
       </c>
       <c r="R215">
-        <v>16962455</v>
+        <v>17399331</v>
       </c>
       <c r="S215" t="s">
         <v>54</v>
@@ -17209,13 +17210,13 @@
         <v>165</v>
       </c>
       <c r="V215" s="1">
-        <v>46266.21595836805</v>
+        <v>46266.21572962963</v>
       </c>
       <c r="W215">
         <v>-47</v>
       </c>
       <c r="X215" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y215" t="s">
         <v>238</v>
@@ -17235,10 +17236,10 @@
     </row>
     <row r="216" spans="1:35">
       <c r="A216">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B216" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C216" t="s">
         <v>50</v>
@@ -17253,7 +17254,7 @@
         <v>56</v>
       </c>
       <c r="G216">
-        <v>7877</v>
+        <v>9774</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -17262,7 +17263,7 @@
         <v>65</v>
       </c>
       <c r="J216" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="N216" s="1">
         <v>46321</v>
@@ -17274,7 +17275,7 @@
         <v>2026</v>
       </c>
       <c r="R216">
-        <v>17399331</v>
+        <v>16976322</v>
       </c>
       <c r="S216" t="s">
         <v>54</v>
@@ -17283,13 +17284,13 @@
         <v>165</v>
       </c>
       <c r="V216" s="1">
-        <v>46266.21572962963</v>
+        <v>46266.21550011574</v>
       </c>
       <c r="W216">
         <v>-47</v>
       </c>
       <c r="X216" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y216" t="s">
         <v>239</v>
@@ -17309,10 +17310,10 @@
     </row>
     <row r="217" spans="1:35">
       <c r="A217">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B217" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C217" t="s">
         <v>50</v>
@@ -17327,7 +17328,7 @@
         <v>56</v>
       </c>
       <c r="G217">
-        <v>9774</v>
+        <v>7027</v>
       </c>
       <c r="H217">
         <v>0</v>
@@ -17336,7 +17337,7 @@
         <v>65</v>
       </c>
       <c r="J217" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N217" s="1">
         <v>46321</v>
@@ -17348,7 +17349,7 @@
         <v>2026</v>
       </c>
       <c r="R217">
-        <v>16976322</v>
+        <v>17399291</v>
       </c>
       <c r="S217" t="s">
         <v>54</v>
@@ -17357,16 +17358,13 @@
         <v>165</v>
       </c>
       <c r="V217" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W217">
         <v>-47</v>
       </c>
       <c r="X217" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y217" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="AB217">
         <v>0</v>
@@ -17383,16 +17381,16 @@
     </row>
     <row r="218" spans="1:35">
       <c r="A218">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B218" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C218" t="s">
         <v>50</v>
       </c>
       <c r="D218" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E218" t="s">
         <v>54</v>
@@ -17422,7 +17420,7 @@
         <v>2026</v>
       </c>
       <c r="R218">
-        <v>17399291</v>
+        <v>16962349</v>
       </c>
       <c r="S218" t="s">
         <v>54</v>
@@ -17437,7 +17435,7 @@
         <v>-47</v>
       </c>
       <c r="X218" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AB218">
         <v>0</v>
@@ -17454,16 +17452,16 @@
     </row>
     <row r="219" spans="1:35">
       <c r="A219">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B219" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C219" t="s">
         <v>50</v>
       </c>
       <c r="D219" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E219" t="s">
         <v>54</v>
@@ -17484,31 +17482,34 @@
         <v>123</v>
       </c>
       <c r="N219" s="1">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="P219">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q219">
         <v>2026</v>
       </c>
       <c r="R219">
-        <v>16962349</v>
+        <v>16976236</v>
       </c>
       <c r="S219" t="s">
         <v>54</v>
       </c>
       <c r="U219" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V219" s="1">
-        <v>46266.00006921296</v>
+        <v>46269.57097615741</v>
       </c>
       <c r="W219">
-        <v>-47</v>
+        <v>14</v>
       </c>
       <c r="X219" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="Y219" t="s">
+        <v>240</v>
       </c>
       <c r="AB219">
         <v>0</v>
@@ -17555,35 +17556,32 @@
         <v>123</v>
       </c>
       <c r="N220" s="1">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="P220">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q220">
         <v>2026</v>
       </c>
       <c r="R220">
-        <v>16976236</v>
+        <v>16976238</v>
       </c>
       <c r="S220" t="s">
         <v>54</v>
       </c>
       <c r="U220" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V220" s="1">
-        <v>46269.57097615741</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W220">
-        <v>14</v>
+        <v>-47</v>
       </c>
       <c r="X220" t="s">
         <v>174</v>
       </c>
-      <c r="Y220" t="s">
-        <v>241</v>
-      </c>
       <c r="AB220">
         <v>0</v>
       </c>
@@ -17599,67 +17597,70 @@
     </row>
     <row r="221" spans="1:35">
       <c r="A221">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B221" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C221" t="s">
         <v>50</v>
       </c>
       <c r="D221" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E221" t="s">
         <v>54</v>
       </c>
       <c r="F221" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G221">
-        <v>7027</v>
+        <v>11056</v>
       </c>
       <c r="H221">
         <v>0</v>
       </c>
       <c r="I221" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J221" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N221" s="1">
-        <v>46321</v>
+        <v>46269</v>
+      </c>
+      <c r="O221" t="s">
+        <v>127</v>
       </c>
       <c r="P221">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q221">
         <v>2026</v>
       </c>
       <c r="R221">
-        <v>16976238</v>
-      </c>
-      <c r="S221" t="s">
-        <v>54</v>
+        <v>18261776</v>
       </c>
       <c r="U221" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V221" s="1">
-        <v>46266.00006921296</v>
+        <v>46269.46753030093</v>
       </c>
       <c r="W221">
-        <v>-47</v>
+        <v>5</v>
       </c>
       <c r="X221" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="Y221" t="s">
+        <v>241</v>
       </c>
       <c r="AB221">
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="AH221" t="s">
         <v>253</v>
@@ -17670,40 +17671,40 @@
     </row>
     <row r="222" spans="1:35">
       <c r="A222">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B222" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C222" t="s">
         <v>50</v>
       </c>
       <c r="D222" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E222" t="s">
         <v>54</v>
       </c>
       <c r="F222" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G222">
-        <v>11056</v>
+        <v>9746</v>
       </c>
       <c r="H222">
         <v>0</v>
       </c>
       <c r="I222" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J222" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="N222" s="1">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="O222" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P222">
         <v>8</v>
@@ -17712,19 +17713,22 @@
         <v>2026</v>
       </c>
       <c r="R222">
-        <v>18261776</v>
+        <v>17399403</v>
+      </c>
+      <c r="S222" t="s">
+        <v>144</v>
       </c>
       <c r="U222" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V222" s="1">
-        <v>46269.46753030093</v>
+        <v>46274.60593387731</v>
       </c>
       <c r="W222">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="X222" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Y222" t="s">
         <v>242</v>
@@ -17733,21 +17737,21 @@
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="AH222" t="s">
         <v>253</v>
       </c>
       <c r="AI222" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B223" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
@@ -17777,7 +17781,7 @@
         <v>46275</v>
       </c>
       <c r="O223" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P223">
         <v>8</v>
@@ -17786,22 +17790,25 @@
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>17399403</v>
+        <v>16976300</v>
       </c>
       <c r="S223" t="s">
-        <v>144</v>
+        <v>141</v>
+      </c>
+      <c r="T223" t="s">
+        <v>160</v>
       </c>
       <c r="U223" t="s">
         <v>165</v>
       </c>
       <c r="V223" s="1">
-        <v>46274.60593387731</v>
+        <v>46274.47210818287</v>
       </c>
       <c r="W223">
         <v>-1</v>
       </c>
       <c r="X223" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y223" t="s">
         <v>243</v>
@@ -17810,7 +17817,7 @@
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AH223" t="s">
         <v>253</v>
@@ -17821,16 +17828,16 @@
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B224" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
       </c>
       <c r="D224" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E224" t="s">
         <v>54</v>
@@ -17854,7 +17861,7 @@
         <v>46275</v>
       </c>
       <c r="O224" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P224">
         <v>8</v>
@@ -17863,25 +17870,25 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>16976300</v>
+        <v>18090250</v>
       </c>
       <c r="S224" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="T224" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="U224" t="s">
         <v>165</v>
       </c>
       <c r="V224" s="1">
-        <v>46274.47210818287</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W224">
         <v>-1</v>
       </c>
       <c r="X224" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y224" t="s">
         <v>244</v>
@@ -17890,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="AC224" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AH224" t="s">
         <v>253</v>
@@ -17901,10 +17908,10 @@
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B225" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
@@ -17916,7 +17923,7 @@
         <v>54</v>
       </c>
       <c r="F225" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G225">
         <v>9746</v>
@@ -17943,25 +17950,25 @@
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>18090250</v>
+        <v>18179154</v>
       </c>
       <c r="S225" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="T225" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U225" t="s">
         <v>165</v>
       </c>
       <c r="V225" s="1">
-        <v>46274.48792050926</v>
+        <v>46274.588374375</v>
       </c>
       <c r="W225">
         <v>-1</v>
       </c>
       <c r="X225" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Y225" t="s">
         <v>245</v>
@@ -17970,7 +17977,7 @@
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AH225" t="s">
         <v>253</v>
@@ -17981,16 +17988,16 @@
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B226" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E226" t="s">
         <v>54</v>
@@ -18013,9 +18020,6 @@
       <c r="N226" s="1">
         <v>46275</v>
       </c>
-      <c r="O226" t="s">
-        <v>129</v>
-      </c>
       <c r="P226">
         <v>8</v>
       </c>
@@ -18023,10 +18027,10 @@
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>18179154</v>
+        <v>18190457</v>
       </c>
       <c r="S226" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="T226" t="s">
         <v>161</v>
@@ -18035,22 +18039,19 @@
         <v>165</v>
       </c>
       <c r="V226" s="1">
-        <v>46274.588374375</v>
+        <v>46274.34198912037</v>
       </c>
       <c r="W226">
         <v>-1</v>
       </c>
       <c r="X226" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y226" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="AB226">
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH226" t="s">
         <v>253</v>
@@ -18061,10 +18062,10 @@
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B227" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
@@ -18073,25 +18074,25 @@
         <v>51</v>
       </c>
       <c r="E227" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F227" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G227">
-        <v>9746</v>
+        <v>1866</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J227" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N227" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P227">
         <v>8</v>
@@ -18100,34 +18101,37 @@
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18190457</v>
+        <v>17968368</v>
       </c>
       <c r="S227" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="T227" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="U227" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V227" s="1">
-        <v>46274.34198912037</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W227">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X227" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="Y227" t="s">
+        <v>246</v>
       </c>
       <c r="AB227">
         <v>0</v>
       </c>
       <c r="AC227" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AH227" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI227" t="s">
         <v>257</v>
@@ -18135,10 +18139,10 @@
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B228" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
@@ -18147,13 +18151,13 @@
         <v>51</v>
       </c>
       <c r="E228" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F228" t="s">
         <v>56</v>
       </c>
       <c r="G228">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -18162,11 +18166,14 @@
         <v>62</v>
       </c>
       <c r="J228" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N228" s="1">
         <v>46274</v>
       </c>
+      <c r="O228" t="s">
+        <v>131</v>
+      </c>
       <c r="P228">
         <v>8</v>
       </c>
@@ -18174,10 +18181,10 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>17968368</v>
+        <v>17988543</v>
       </c>
       <c r="S228" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T228" t="s">
         <v>149</v>
@@ -18186,13 +18193,13 @@
         <v>166</v>
       </c>
       <c r="V228" s="1">
-        <v>46274.36843923611</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W228">
         <v>0</v>
       </c>
       <c r="X228" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y228" t="s">
         <v>247</v>
@@ -18201,7 +18208,7 @@
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH228" t="s">
         <v>254</v>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="259">
   <si>
     <t>CodCliente</t>
   </si>
@@ -772,6 +772,9 @@
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 15:41</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 
@@ -1141,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI240"/>
+  <dimension ref="A1:AI241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1322,10 +1325,10 @@
         <v>132</v>
       </c>
       <c r="AH2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1399,10 +1402,10 @@
         <v>133</v>
       </c>
       <c r="AH3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1476,10 +1479,10 @@
         <v>132</v>
       </c>
       <c r="AH4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1550,10 +1553,10 @@
         <v>132</v>
       </c>
       <c r="AH5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1624,10 +1627,10 @@
         <v>133</v>
       </c>
       <c r="AH6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1698,10 +1701,10 @@
         <v>133</v>
       </c>
       <c r="AH7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1772,10 +1775,10 @@
         <v>134</v>
       </c>
       <c r="AH8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1846,10 +1849,10 @@
         <v>132</v>
       </c>
       <c r="AH9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1920,10 +1923,10 @@
         <v>135</v>
       </c>
       <c r="AH10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1994,10 +1997,10 @@
         <v>135</v>
       </c>
       <c r="AH11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2068,10 +2071,10 @@
         <v>136</v>
       </c>
       <c r="AH12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2139,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AH13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2213,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AH14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2287,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2352,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2423,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2500,10 +2503,10 @@
         <v>138</v>
       </c>
       <c r="AH18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2577,10 +2580,10 @@
         <v>137</v>
       </c>
       <c r="AH19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2654,10 +2657,10 @@
         <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2731,10 +2734,10 @@
         <v>136</v>
       </c>
       <c r="AH21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2805,10 +2808,10 @@
         <v>139</v>
       </c>
       <c r="AH22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2879,10 +2882,10 @@
         <v>136</v>
       </c>
       <c r="AH23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2953,10 +2956,10 @@
         <v>136</v>
       </c>
       <c r="AH24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3027,10 +3030,10 @@
         <v>136</v>
       </c>
       <c r="AH25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3101,10 +3104,10 @@
         <v>137</v>
       </c>
       <c r="AH26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3175,10 +3178,10 @@
         <v>136</v>
       </c>
       <c r="AH27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3249,10 +3252,10 @@
         <v>136</v>
       </c>
       <c r="AH28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3323,10 +3326,10 @@
         <v>136</v>
       </c>
       <c r="AH29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3397,10 +3400,10 @@
         <v>140</v>
       </c>
       <c r="AH30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3477,10 +3480,10 @@
         <v>141</v>
       </c>
       <c r="AH31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3551,10 +3554,10 @@
         <v>142</v>
       </c>
       <c r="AH32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3631,10 +3634,10 @@
         <v>143</v>
       </c>
       <c r="AH33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3708,10 +3711,10 @@
         <v>144</v>
       </c>
       <c r="AH34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3785,13 +3788,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AH35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3868,10 +3871,10 @@
         <v>146</v>
       </c>
       <c r="AH36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3948,10 +3951,10 @@
         <v>140</v>
       </c>
       <c r="AH37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4025,10 +4028,10 @@
         <v>162</v>
       </c>
       <c r="AH38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4105,10 +4108,10 @@
         <v>141</v>
       </c>
       <c r="AH39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4185,10 +4188,10 @@
         <v>141</v>
       </c>
       <c r="AH40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4265,10 +4268,10 @@
         <v>141</v>
       </c>
       <c r="AH41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4345,10 +4348,10 @@
         <v>140</v>
       </c>
       <c r="AH42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4425,10 +4428,10 @@
         <v>147</v>
       </c>
       <c r="AH43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4505,10 +4508,10 @@
         <v>142</v>
       </c>
       <c r="AH44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4585,10 +4588,10 @@
         <v>143</v>
       </c>
       <c r="AH45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4656,10 +4659,10 @@
         <v>144</v>
       </c>
       <c r="AH46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4730,10 +4733,10 @@
         <v>141</v>
       </c>
       <c r="AH47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4804,10 +4807,10 @@
         <v>141</v>
       </c>
       <c r="AH48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4878,10 +4881,10 @@
         <v>141</v>
       </c>
       <c r="AH49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4952,10 +4955,10 @@
         <v>140</v>
       </c>
       <c r="AH50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI50" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5026,10 +5029,10 @@
         <v>147</v>
       </c>
       <c r="AH51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI51" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5106,10 +5109,10 @@
         <v>142</v>
       </c>
       <c r="AH52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5180,10 +5183,10 @@
         <v>143</v>
       </c>
       <c r="AH53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI53" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5260,10 +5263,10 @@
         <v>141</v>
       </c>
       <c r="AH54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5340,10 +5343,10 @@
         <v>141</v>
       </c>
       <c r="AH55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5420,10 +5423,10 @@
         <v>141</v>
       </c>
       <c r="AH56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5500,10 +5503,10 @@
         <v>140</v>
       </c>
       <c r="AH57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5577,10 +5580,10 @@
         <v>144</v>
       </c>
       <c r="AH58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5654,13 +5657,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AH59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5737,10 +5740,10 @@
         <v>141</v>
       </c>
       <c r="AH60" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5817,10 +5820,10 @@
         <v>141</v>
       </c>
       <c r="AH61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI61" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5897,10 +5900,10 @@
         <v>141</v>
       </c>
       <c r="AH62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI62" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -5977,10 +5980,10 @@
         <v>140</v>
       </c>
       <c r="AH63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6057,10 +6060,10 @@
         <v>147</v>
       </c>
       <c r="AH64" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6137,10 +6140,10 @@
         <v>142</v>
       </c>
       <c r="AH65" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI65" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6217,10 +6220,10 @@
         <v>143</v>
       </c>
       <c r="AH66" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI66" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6297,10 +6300,10 @@
         <v>141</v>
       </c>
       <c r="AH67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6368,10 +6371,10 @@
         <v>144</v>
       </c>
       <c r="AH68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6439,13 +6442,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AH69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6516,10 +6519,10 @@
         <v>141</v>
       </c>
       <c r="AH70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6590,10 +6593,10 @@
         <v>141</v>
       </c>
       <c r="AH71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6664,10 +6667,10 @@
         <v>141</v>
       </c>
       <c r="AH72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6738,10 +6741,10 @@
         <v>140</v>
       </c>
       <c r="AH73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI73" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6812,10 +6815,10 @@
         <v>147</v>
       </c>
       <c r="AH74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6886,10 +6889,10 @@
         <v>142</v>
       </c>
       <c r="AH75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6960,10 +6963,10 @@
         <v>143</v>
       </c>
       <c r="AH76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7034,10 +7037,10 @@
         <v>143</v>
       </c>
       <c r="AH77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7108,10 +7111,10 @@
         <v>143</v>
       </c>
       <c r="AH78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI78" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7182,10 +7185,10 @@
         <v>143</v>
       </c>
       <c r="AH79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7256,10 +7259,10 @@
         <v>149</v>
       </c>
       <c r="AH80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7330,10 +7333,10 @@
         <v>149</v>
       </c>
       <c r="AH81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7404,10 +7407,10 @@
         <v>150</v>
       </c>
       <c r="AH82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI82" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7478,10 +7481,10 @@
         <v>149</v>
       </c>
       <c r="AH83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7552,10 +7555,10 @@
         <v>149</v>
       </c>
       <c r="AH84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7629,10 +7632,10 @@
         <v>149</v>
       </c>
       <c r="AH85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7703,10 +7706,10 @@
         <v>150</v>
       </c>
       <c r="AH86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7777,10 +7780,10 @@
         <v>149</v>
       </c>
       <c r="AH87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7851,10 +7854,10 @@
         <v>149</v>
       </c>
       <c r="AH88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7925,10 +7928,10 @@
         <v>149</v>
       </c>
       <c r="AH89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -7996,10 +7999,10 @@
         <v>149</v>
       </c>
       <c r="AH90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8070,10 +8073,10 @@
         <v>150</v>
       </c>
       <c r="AH91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8144,10 +8147,10 @@
         <v>149</v>
       </c>
       <c r="AH92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8218,10 +8221,10 @@
         <v>149</v>
       </c>
       <c r="AH93" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8292,10 +8295,10 @@
         <v>149</v>
       </c>
       <c r="AH94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8363,10 +8366,10 @@
         <v>149</v>
       </c>
       <c r="AH95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8437,10 +8440,10 @@
         <v>150</v>
       </c>
       <c r="AH96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8511,10 +8514,10 @@
         <v>149</v>
       </c>
       <c r="AH97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI97" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8585,10 +8588,10 @@
         <v>149</v>
       </c>
       <c r="AH98" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8659,10 +8662,10 @@
         <v>150</v>
       </c>
       <c r="AH99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8739,10 +8742,10 @@
         <v>149</v>
       </c>
       <c r="AH100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8810,10 +8813,10 @@
         <v>149</v>
       </c>
       <c r="AH101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8884,10 +8887,10 @@
         <v>149</v>
       </c>
       <c r="AH102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8958,10 +8961,10 @@
         <v>149</v>
       </c>
       <c r="AH103" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI103" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9032,10 +9035,10 @@
         <v>149</v>
       </c>
       <c r="AH104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI104" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9103,10 +9106,10 @@
         <v>149</v>
       </c>
       <c r="AH105" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI105" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9177,10 +9180,10 @@
         <v>150</v>
       </c>
       <c r="AH106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9251,10 +9254,10 @@
         <v>149</v>
       </c>
       <c r="AH107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9325,10 +9328,10 @@
         <v>149</v>
       </c>
       <c r="AH108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9396,10 +9399,10 @@
         <v>149</v>
       </c>
       <c r="AH109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI109" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9470,10 +9473,10 @@
         <v>150</v>
       </c>
       <c r="AH110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9541,10 +9544,10 @@
         <v>151</v>
       </c>
       <c r="AH111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9615,10 +9618,10 @@
         <v>150</v>
       </c>
       <c r="AH112" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI112" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9689,10 +9692,10 @@
         <v>148</v>
       </c>
       <c r="AH113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI113" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9760,10 +9763,10 @@
         <v>151</v>
       </c>
       <c r="AH114" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9834,10 +9837,10 @@
         <v>150</v>
       </c>
       <c r="AH115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI115" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9908,10 +9911,10 @@
         <v>149</v>
       </c>
       <c r="AH116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -9982,10 +9985,10 @@
         <v>149</v>
       </c>
       <c r="AH117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10056,10 +10059,10 @@
         <v>149</v>
       </c>
       <c r="AH118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10127,10 +10130,10 @@
         <v>149</v>
       </c>
       <c r="AH119" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI119" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10201,10 +10204,10 @@
         <v>150</v>
       </c>
       <c r="AH120" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI120" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10275,10 +10278,10 @@
         <v>149</v>
       </c>
       <c r="AH121" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI121" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10349,10 +10352,10 @@
         <v>149</v>
       </c>
       <c r="AH122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI122" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10423,10 +10426,10 @@
         <v>149</v>
       </c>
       <c r="AH123" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10494,10 +10497,10 @@
         <v>149</v>
       </c>
       <c r="AH124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10568,10 +10571,10 @@
         <v>150</v>
       </c>
       <c r="AH125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI125" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10648,10 +10651,10 @@
         <v>150</v>
       </c>
       <c r="AH126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10728,10 +10731,10 @@
         <v>150</v>
       </c>
       <c r="AH127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10802,10 +10805,10 @@
         <v>153</v>
       </c>
       <c r="AH128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10876,10 +10879,10 @@
         <v>153</v>
       </c>
       <c r="AH129" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10956,10 +10959,10 @@
         <v>153</v>
       </c>
       <c r="AH130" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11030,10 +11033,10 @@
         <v>153</v>
       </c>
       <c r="AH131" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11104,10 +11107,10 @@
         <v>153</v>
       </c>
       <c r="AH132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI132" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11178,10 +11181,10 @@
         <v>153</v>
       </c>
       <c r="AH133" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11252,10 +11255,10 @@
         <v>153</v>
       </c>
       <c r="AH134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI134" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11332,10 +11335,10 @@
         <v>153</v>
       </c>
       <c r="AH135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11406,10 +11409,10 @@
         <v>153</v>
       </c>
       <c r="AH136" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI136" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11480,10 +11483,10 @@
         <v>153</v>
       </c>
       <c r="AH137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI137" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11554,10 +11557,10 @@
         <v>153</v>
       </c>
       <c r="AH138" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11634,10 +11637,10 @@
         <v>153</v>
       </c>
       <c r="AH139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11708,10 +11711,10 @@
         <v>153</v>
       </c>
       <c r="AH140" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11782,10 +11785,10 @@
         <v>153</v>
       </c>
       <c r="AH141" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI141" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11856,10 +11859,10 @@
         <v>153</v>
       </c>
       <c r="AH142" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI142" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11930,10 +11933,10 @@
         <v>153</v>
       </c>
       <c r="AH143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI143" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12004,10 +12007,10 @@
         <v>153</v>
       </c>
       <c r="AH144" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI144" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12078,10 +12081,10 @@
         <v>153</v>
       </c>
       <c r="AH145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12152,10 +12155,10 @@
         <v>153</v>
       </c>
       <c r="AH146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12226,10 +12229,10 @@
         <v>153</v>
       </c>
       <c r="AH147" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI147" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12300,10 +12303,10 @@
         <v>153</v>
       </c>
       <c r="AH148" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI148" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12374,10 +12377,10 @@
         <v>153</v>
       </c>
       <c r="AH149" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI149" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12454,10 +12457,10 @@
         <v>153</v>
       </c>
       <c r="AH150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI150" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12528,10 +12531,10 @@
         <v>153</v>
       </c>
       <c r="AH151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12602,10 +12605,10 @@
         <v>153</v>
       </c>
       <c r="AH152" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12676,10 +12679,10 @@
         <v>153</v>
       </c>
       <c r="AH153" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI153" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12750,10 +12753,10 @@
         <v>154</v>
       </c>
       <c r="AH154" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI154" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12824,10 +12827,10 @@
         <v>154</v>
       </c>
       <c r="AH155" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12898,10 +12901,10 @@
         <v>154</v>
       </c>
       <c r="AH156" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI156" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -12972,10 +12975,10 @@
         <v>154</v>
       </c>
       <c r="AH157" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI157" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13046,10 +13049,10 @@
         <v>154</v>
       </c>
       <c r="AH158" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI158" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13120,10 +13123,10 @@
         <v>154</v>
       </c>
       <c r="AH159" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI159" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13194,10 +13197,10 @@
         <v>154</v>
       </c>
       <c r="AH160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI160" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13268,10 +13271,10 @@
         <v>154</v>
       </c>
       <c r="AH161" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI161" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13342,10 +13345,10 @@
         <v>154</v>
       </c>
       <c r="AH162" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI162" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13416,10 +13419,10 @@
         <v>154</v>
       </c>
       <c r="AH163" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI163" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13490,10 +13493,10 @@
         <v>154</v>
       </c>
       <c r="AH164" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13564,10 +13567,10 @@
         <v>154</v>
       </c>
       <c r="AH165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13638,10 +13641,10 @@
         <v>154</v>
       </c>
       <c r="AH166" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI166" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13712,10 +13715,10 @@
         <v>154</v>
       </c>
       <c r="AH167" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI167" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13786,10 +13789,10 @@
         <v>154</v>
       </c>
       <c r="AH168" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI168" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13860,10 +13863,10 @@
         <v>154</v>
       </c>
       <c r="AH169" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI169" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13934,10 +13937,10 @@
         <v>154</v>
       </c>
       <c r="AH170" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI170" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14008,10 +14011,10 @@
         <v>154</v>
       </c>
       <c r="AH171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI171" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14082,10 +14085,10 @@
         <v>154</v>
       </c>
       <c r="AH172" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI172" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14159,10 +14162,10 @@
         <v>154</v>
       </c>
       <c r="AH173" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI173" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14236,10 +14239,10 @@
         <v>154</v>
       </c>
       <c r="AH174" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI174" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14313,10 +14316,10 @@
         <v>154</v>
       </c>
       <c r="AH175" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI175" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14390,10 +14393,10 @@
         <v>154</v>
       </c>
       <c r="AH176" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI176" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14467,10 +14470,10 @@
         <v>154</v>
       </c>
       <c r="AH177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI177" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14544,10 +14547,10 @@
         <v>154</v>
       </c>
       <c r="AH178" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI178" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14621,10 +14624,10 @@
         <v>154</v>
       </c>
       <c r="AH179" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI179" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14698,10 +14701,10 @@
         <v>154</v>
       </c>
       <c r="AH180" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI180" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14775,10 +14778,10 @@
         <v>154</v>
       </c>
       <c r="AH181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI181" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14852,10 +14855,10 @@
         <v>154</v>
       </c>
       <c r="AH182" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI182" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14929,10 +14932,10 @@
         <v>154</v>
       </c>
       <c r="AH183" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI183" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15006,10 +15009,10 @@
         <v>154</v>
       </c>
       <c r="AH184" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI184" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15083,10 +15086,10 @@
         <v>154</v>
       </c>
       <c r="AH185" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI185" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15160,10 +15163,10 @@
         <v>154</v>
       </c>
       <c r="AH186" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI186" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15231,10 +15234,10 @@
         <v>154</v>
       </c>
       <c r="AH187" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI187" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15302,10 +15305,10 @@
         <v>154</v>
       </c>
       <c r="AH188" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI188" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15373,10 +15376,10 @@
         <v>154</v>
       </c>
       <c r="AH189" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI189" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15444,10 +15447,10 @@
         <v>154</v>
       </c>
       <c r="AH190" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI190" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15515,10 +15518,10 @@
         <v>154</v>
       </c>
       <c r="AH191" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI191" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15586,10 +15589,10 @@
         <v>154</v>
       </c>
       <c r="AH192" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI192" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15657,10 +15660,10 @@
         <v>54</v>
       </c>
       <c r="AH193" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI193" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15728,10 +15731,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI194" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15799,10 +15802,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI195" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15870,10 +15873,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI196" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15941,10 +15944,10 @@
         <v>155</v>
       </c>
       <c r="AH197" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI197" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16012,10 +16015,10 @@
         <v>55</v>
       </c>
       <c r="AH198" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI198" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16083,10 +16086,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI199" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16154,10 +16157,10 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI200" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16225,10 +16228,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI201" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16296,10 +16299,10 @@
         <v>155</v>
       </c>
       <c r="AH202" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI202" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16367,10 +16370,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI203" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16438,10 +16441,10 @@
         <v>155</v>
       </c>
       <c r="AH204" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI204" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16509,10 +16512,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI205" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16580,10 +16583,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI206" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16651,10 +16654,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI207" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16722,10 +16725,10 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI208" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16793,10 +16796,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI209" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16864,10 +16867,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI210" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16935,10 +16938,10 @@
         <v>155</v>
       </c>
       <c r="AH211" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI211" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17006,10 +17009,10 @@
         <v>55</v>
       </c>
       <c r="AH212" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI212" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17080,10 +17083,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI213" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17154,10 +17157,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI214" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17228,10 +17231,10 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI215" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17302,10 +17305,10 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI216" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17373,10 +17376,10 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI217" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17444,10 +17447,10 @@
         <v>54</v>
       </c>
       <c r="AH218" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI218" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17518,10 +17521,10 @@
         <v>54</v>
       </c>
       <c r="AH219" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI219" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17589,10 +17592,10 @@
         <v>54</v>
       </c>
       <c r="AH220" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI220" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17660,13 +17663,13 @@
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AH221" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI221" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17740,10 +17743,10 @@
         <v>144</v>
       </c>
       <c r="AH222" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI222" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17820,10 +17823,10 @@
         <v>141</v>
       </c>
       <c r="AH223" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI223" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17900,10 +17903,10 @@
         <v>147</v>
       </c>
       <c r="AH224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI224" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -17980,10 +17983,10 @@
         <v>142</v>
       </c>
       <c r="AH225" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI225" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18054,10 +18057,10 @@
         <v>143</v>
       </c>
       <c r="AH226" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AI226" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18131,33 +18134,33 @@
         <v>149</v>
       </c>
       <c r="AH227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI227" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B228" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
       </c>
       <c r="D228" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E228" t="s">
         <v>54</v>
       </c>
       <c r="F228" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G228">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -18166,14 +18169,11 @@
         <v>62</v>
       </c>
       <c r="J228" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N228" s="1">
         <v>46274</v>
       </c>
-      <c r="O228" t="s">
-        <v>131</v>
-      </c>
       <c r="P228">
         <v>8</v>
       </c>
@@ -18181,10 +18181,10 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>17988543</v>
+        <v>18186946</v>
       </c>
       <c r="S228" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="T228" t="s">
         <v>149</v>
@@ -18193,13 +18193,13 @@
         <v>166</v>
       </c>
       <c r="V228" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W228">
         <v>0</v>
       </c>
       <c r="X228" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Y228" t="s">
         <v>247</v>
@@ -18208,21 +18208,21 @@
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AH228" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI228" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B229" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
@@ -18231,7 +18231,7 @@
         <v>51</v>
       </c>
       <c r="E229" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F229" t="s">
         <v>56</v>
@@ -18251,6 +18251,9 @@
       <c r="N229" s="1">
         <v>46274</v>
       </c>
+      <c r="O229" t="s">
+        <v>131</v>
+      </c>
       <c r="P229">
         <v>8</v>
       </c>
@@ -18258,10 +18261,10 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>17968379</v>
+        <v>17988543</v>
       </c>
       <c r="S229" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T229" t="s">
         <v>149</v>
@@ -18270,33 +18273,36 @@
         <v>166</v>
       </c>
       <c r="V229" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W229">
         <v>0</v>
       </c>
       <c r="X229" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="Y229" t="s">
+        <v>248</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AI229" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B230" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
@@ -18305,25 +18311,25 @@
         <v>51</v>
       </c>
       <c r="E230" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F230" t="s">
         <v>56</v>
       </c>
       <c r="G230">
-        <v>11303</v>
+        <v>1867</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J230" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="N230" s="1">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="P230">
         <v>8</v>
@@ -18332,54 +18338,51 @@
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>17399454</v>
+        <v>17968379</v>
       </c>
       <c r="S230" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="T230" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="U230" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V230" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W230">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X230" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y230" t="s">
-        <v>248</v>
+        <v>168</v>
       </c>
       <c r="AB230">
         <v>0</v>
       </c>
       <c r="AC230" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH230" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AI230" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B231" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
@@ -18388,69 +18391,75 @@
         <v>56</v>
       </c>
       <c r="G231">
-        <v>5989</v>
+        <v>11303</v>
       </c>
       <c r="H231">
         <v>0</v>
       </c>
       <c r="I231" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J231" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="N231" s="1">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="P231">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q231">
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>17941177</v>
+        <v>17399454</v>
       </c>
       <c r="S231" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="T231" t="s">
+        <v>163</v>
       </c>
       <c r="U231" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V231" s="1">
-        <v>46274.41771849537</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W231">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="X231" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="Y231" t="s">
+        <v>249</v>
       </c>
       <c r="AB231">
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH231" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AI231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B232" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
       </c>
       <c r="D232" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E232" t="s">
         <v>54</v>
@@ -18480,7 +18489,7 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>17952385</v>
+        <v>17941177</v>
       </c>
       <c r="S232" t="s">
         <v>154</v>
@@ -18489,13 +18498,13 @@
         <v>164</v>
       </c>
       <c r="V232" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W232">
         <v>1</v>
       </c>
       <c r="X232" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AB232">
         <v>0</v>
@@ -18504,24 +18513,24 @@
         <v>154</v>
       </c>
       <c r="AH232" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI232" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B233" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E233" t="s">
         <v>54</v>
@@ -18551,7 +18560,7 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>17952569</v>
+        <v>17952385</v>
       </c>
       <c r="S233" t="s">
         <v>154</v>
@@ -18560,7 +18569,7 @@
         <v>164</v>
       </c>
       <c r="V233" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W233">
         <v>1</v>
@@ -18575,18 +18584,18 @@
         <v>154</v>
       </c>
       <c r="AH233" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI233" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B234" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
@@ -18598,7 +18607,7 @@
         <v>54</v>
       </c>
       <c r="F234" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G234">
         <v>5989</v>
@@ -18622,7 +18631,7 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>18164516</v>
+        <v>17952569</v>
       </c>
       <c r="S234" t="s">
         <v>154</v>
@@ -18631,13 +18640,13 @@
         <v>164</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W234">
         <v>1</v>
       </c>
       <c r="X234" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB234">
         <v>0</v>
@@ -18646,24 +18655,24 @@
         <v>154</v>
       </c>
       <c r="AH234" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI234" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B235" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
       </c>
       <c r="D235" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E235" t="s">
         <v>54</v>
@@ -18693,7 +18702,7 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>18178157</v>
+        <v>18164516</v>
       </c>
       <c r="S235" t="s">
         <v>154</v>
@@ -18702,13 +18711,13 @@
         <v>164</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W235">
         <v>1</v>
       </c>
       <c r="X235" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB235">
         <v>0</v>
@@ -18717,45 +18726,45 @@
         <v>154</v>
       </c>
       <c r="AH235" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI235" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B236" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
       </c>
       <c r="F236" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G236">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J236" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N236" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P236">
         <v>9</v>
@@ -18764,48 +18773,48 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>17941187</v>
+        <v>18178157</v>
       </c>
       <c r="S236" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="U236" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X236" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AB236">
         <v>0</v>
       </c>
       <c r="AC236" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="AH236" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI236" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B237" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E237" t="s">
         <v>54</v>
@@ -18835,7 +18844,7 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>17952400</v>
+        <v>17941187</v>
       </c>
       <c r="S237" t="s">
         <v>54</v>
@@ -18844,13 +18853,13 @@
         <v>166</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W237">
         <v>0</v>
       </c>
       <c r="X237" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AB237">
         <v>0</v>
@@ -18859,24 +18868,24 @@
         <v>54</v>
       </c>
       <c r="AH237" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI237" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B238" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
       </c>
       <c r="D238" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
@@ -18906,7 +18915,7 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>17952580</v>
+        <v>17952400</v>
       </c>
       <c r="S238" t="s">
         <v>54</v>
@@ -18915,7 +18924,7 @@
         <v>166</v>
       </c>
       <c r="V238" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W238">
         <v>0</v>
@@ -18930,18 +18939,18 @@
         <v>54</v>
       </c>
       <c r="AH238" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI238" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B239" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
@@ -18953,7 +18962,7 @@
         <v>54</v>
       </c>
       <c r="F239" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G239">
         <v>6215</v>
@@ -18977,7 +18986,7 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>18164523</v>
+        <v>17952580</v>
       </c>
       <c r="S239" t="s">
         <v>54</v>
@@ -18986,13 +18995,13 @@
         <v>166</v>
       </c>
       <c r="V239" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W239">
         <v>0</v>
       </c>
       <c r="X239" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB239">
         <v>0</v>
@@ -19001,24 +19010,24 @@
         <v>54</v>
       </c>
       <c r="AH239" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AI239" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B240" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
       </c>
       <c r="D240" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E240" t="s">
         <v>54</v>
@@ -19048,34 +19057,105 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>18178163</v>
+        <v>18164523</v>
       </c>
       <c r="S240" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U240" t="s">
         <v>166</v>
       </c>
       <c r="V240" s="1">
+        <v>46274.41799332176</v>
+      </c>
+      <c r="W240">
+        <v>0</v>
+      </c>
+      <c r="X240" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB240">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH240" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI240" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="241" spans="1:35">
+      <c r="A241">
+        <v>6949</v>
+      </c>
+      <c r="B241" t="s">
+        <v>37</v>
+      </c>
+      <c r="C241" t="s">
+        <v>50</v>
+      </c>
+      <c r="D241" t="s">
+        <v>51</v>
+      </c>
+      <c r="E241" t="s">
+        <v>54</v>
+      </c>
+      <c r="F241" t="s">
+        <v>57</v>
+      </c>
+      <c r="G241">
+        <v>6215</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241" t="s">
+        <v>65</v>
+      </c>
+      <c r="J241" t="s">
+        <v>121</v>
+      </c>
+      <c r="N241" s="1">
+        <v>46274</v>
+      </c>
+      <c r="P241">
+        <v>9</v>
+      </c>
+      <c r="Q241">
+        <v>2026</v>
+      </c>
+      <c r="R241">
+        <v>18178163</v>
+      </c>
+      <c r="S241" t="s">
+        <v>155</v>
+      </c>
+      <c r="U241" t="s">
+        <v>166</v>
+      </c>
+      <c r="V241" s="1">
         <v>46274.41800085648</v>
       </c>
-      <c r="W240">
-        <v>0</v>
-      </c>
-      <c r="X240" t="s">
+      <c r="W241">
+        <v>0</v>
+      </c>
+      <c r="X241" t="s">
         <v>169</v>
       </c>
-      <c r="AB240">
-        <v>0</v>
-      </c>
-      <c r="AC240" t="s">
+      <c r="AB241">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="s">
         <v>155</v>
       </c>
-      <c r="AH240" t="s">
-        <v>255</v>
-      </c>
-      <c r="AI240" t="s">
-        <v>257</v>
+      <c r="AH241" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI241" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3721" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="272">
   <si>
     <t>CodCliente</t>
   </si>
@@ -810,6 +810,18 @@
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1866] sendo a ultima baixa feita [1866]-09/09/2026 17:52:06.. - Data Comentário: 09/09/2026 17:47</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-09/09/2026 15:33:08.. - Data Comentário: 09/09/2026 15:28</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-08/09/2026 16:18:23.. - Data Comentário: 08/09/2026 16:13</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-09/09/2026 17:27:34.. - Data Comentário: 09/09/2026 17:22</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-09/09/2026 17:53:38.. - Data Comentário: 09/09/2026 17:48</t>
   </si>
   <si>
     <t>Karen Ribeiro</t>
@@ -1172,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI261"/>
+  <dimension ref="A1:AI266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1353,10 +1365,10 @@
         <v>134</v>
       </c>
       <c r="AH2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1430,10 +1442,10 @@
         <v>135</v>
       </c>
       <c r="AH3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1507,10 +1519,10 @@
         <v>134</v>
       </c>
       <c r="AH4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1581,10 +1593,10 @@
         <v>134</v>
       </c>
       <c r="AH5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1655,10 +1667,10 @@
         <v>135</v>
       </c>
       <c r="AH6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1729,10 +1741,10 @@
         <v>135</v>
       </c>
       <c r="AH7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1803,10 +1815,10 @@
         <v>136</v>
       </c>
       <c r="AH8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1877,10 +1889,10 @@
         <v>134</v>
       </c>
       <c r="AH9" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1951,10 +1963,10 @@
         <v>137</v>
       </c>
       <c r="AH10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2025,10 +2037,10 @@
         <v>137</v>
       </c>
       <c r="AH11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2099,10 +2111,10 @@
         <v>138</v>
       </c>
       <c r="AH12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2170,13 +2182,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AH13" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI13" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2244,13 +2256,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AH14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI14" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2318,10 +2330,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2383,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI16" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2454,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI17" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2531,10 +2543,10 @@
         <v>140</v>
       </c>
       <c r="AH18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2608,10 +2620,10 @@
         <v>139</v>
       </c>
       <c r="AH19" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI19" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2685,10 +2697,10 @@
         <v>140</v>
       </c>
       <c r="AH20" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI20" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2762,10 +2774,10 @@
         <v>138</v>
       </c>
       <c r="AH21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI21" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2836,10 +2848,10 @@
         <v>141</v>
       </c>
       <c r="AH22" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2910,10 +2922,10 @@
         <v>138</v>
       </c>
       <c r="AH23" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI23" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2984,10 +2996,10 @@
         <v>138</v>
       </c>
       <c r="AH24" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI24" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3058,10 +3070,10 @@
         <v>138</v>
       </c>
       <c r="AH25" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI25" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3132,10 +3144,10 @@
         <v>139</v>
       </c>
       <c r="AH26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI26" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3206,10 +3218,10 @@
         <v>138</v>
       </c>
       <c r="AH27" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI27" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3280,10 +3292,10 @@
         <v>138</v>
       </c>
       <c r="AH28" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI28" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3354,10 +3366,10 @@
         <v>138</v>
       </c>
       <c r="AH29" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI29" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3428,10 +3440,10 @@
         <v>142</v>
       </c>
       <c r="AH30" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI30" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3508,10 +3520,10 @@
         <v>143</v>
       </c>
       <c r="AH31" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI31" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3582,10 +3594,10 @@
         <v>144</v>
       </c>
       <c r="AH32" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI32" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3662,10 +3674,10 @@
         <v>145</v>
       </c>
       <c r="AH33" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI33" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3739,10 +3751,10 @@
         <v>146</v>
       </c>
       <c r="AH34" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI34" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3816,13 +3828,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AH35" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI35" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3899,10 +3911,10 @@
         <v>148</v>
       </c>
       <c r="AH36" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI36" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3979,10 +3991,10 @@
         <v>142</v>
       </c>
       <c r="AH37" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI37" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4056,10 +4068,10 @@
         <v>164</v>
       </c>
       <c r="AH38" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI38" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4136,10 +4148,10 @@
         <v>143</v>
       </c>
       <c r="AH39" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI39" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4216,10 +4228,10 @@
         <v>143</v>
       </c>
       <c r="AH40" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI40" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4296,10 +4308,10 @@
         <v>143</v>
       </c>
       <c r="AH41" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI41" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4376,10 +4388,10 @@
         <v>142</v>
       </c>
       <c r="AH42" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI42" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4456,10 +4468,10 @@
         <v>149</v>
       </c>
       <c r="AH43" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI43" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4536,10 +4548,10 @@
         <v>144</v>
       </c>
       <c r="AH44" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI44" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4616,10 +4628,10 @@
         <v>145</v>
       </c>
       <c r="AH45" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI45" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4687,10 +4699,10 @@
         <v>146</v>
       </c>
       <c r="AH46" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI46" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4761,10 +4773,10 @@
         <v>143</v>
       </c>
       <c r="AH47" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI47" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4835,10 +4847,10 @@
         <v>143</v>
       </c>
       <c r="AH48" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI48" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4909,10 +4921,10 @@
         <v>143</v>
       </c>
       <c r="AH49" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI49" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4983,10 +4995,10 @@
         <v>142</v>
       </c>
       <c r="AH50" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI50" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5057,10 +5069,10 @@
         <v>149</v>
       </c>
       <c r="AH51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI51" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5137,10 +5149,10 @@
         <v>144</v>
       </c>
       <c r="AH52" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI52" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5211,10 +5223,10 @@
         <v>145</v>
       </c>
       <c r="AH53" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI53" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5291,10 +5303,10 @@
         <v>143</v>
       </c>
       <c r="AH54" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI54" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5371,10 +5383,10 @@
         <v>143</v>
       </c>
       <c r="AH55" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI55" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5451,10 +5463,10 @@
         <v>143</v>
       </c>
       <c r="AH56" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5531,10 +5543,10 @@
         <v>142</v>
       </c>
       <c r="AH57" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI57" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5608,10 +5620,10 @@
         <v>146</v>
       </c>
       <c r="AH58" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI58" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5685,13 +5697,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AH59" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI59" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5768,10 +5780,10 @@
         <v>143</v>
       </c>
       <c r="AH60" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI60" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5848,10 +5860,10 @@
         <v>143</v>
       </c>
       <c r="AH61" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI61" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5928,10 +5940,10 @@
         <v>143</v>
       </c>
       <c r="AH62" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI62" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6008,10 +6020,10 @@
         <v>142</v>
       </c>
       <c r="AH63" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI63" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6088,10 +6100,10 @@
         <v>149</v>
       </c>
       <c r="AH64" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI64" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6168,10 +6180,10 @@
         <v>144</v>
       </c>
       <c r="AH65" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI65" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6248,10 +6260,10 @@
         <v>145</v>
       </c>
       <c r="AH66" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI66" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6328,10 +6340,10 @@
         <v>143</v>
       </c>
       <c r="AH67" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI67" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6399,10 +6411,10 @@
         <v>146</v>
       </c>
       <c r="AH68" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI68" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6470,13 +6482,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AH69" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI69" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6547,10 +6559,10 @@
         <v>143</v>
       </c>
       <c r="AH70" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI70" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6621,10 +6633,10 @@
         <v>143</v>
       </c>
       <c r="AH71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI71" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6695,10 +6707,10 @@
         <v>143</v>
       </c>
       <c r="AH72" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI72" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6769,10 +6781,10 @@
         <v>142</v>
       </c>
       <c r="AH73" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI73" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6843,10 +6855,10 @@
         <v>149</v>
       </c>
       <c r="AH74" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI74" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6917,10 +6929,10 @@
         <v>144</v>
       </c>
       <c r="AH75" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI75" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -6991,10 +7003,10 @@
         <v>145</v>
       </c>
       <c r="AH76" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI76" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7065,10 +7077,10 @@
         <v>145</v>
       </c>
       <c r="AH77" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI77" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7139,10 +7151,10 @@
         <v>145</v>
       </c>
       <c r="AH78" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI78" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7213,10 +7225,10 @@
         <v>145</v>
       </c>
       <c r="AH79" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI79" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7287,10 +7299,10 @@
         <v>151</v>
       </c>
       <c r="AH80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI80" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7361,10 +7373,10 @@
         <v>151</v>
       </c>
       <c r="AH81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI81" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7435,10 +7447,10 @@
         <v>152</v>
       </c>
       <c r="AH82" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI82" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7509,10 +7521,10 @@
         <v>151</v>
       </c>
       <c r="AH83" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI83" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7583,10 +7595,10 @@
         <v>151</v>
       </c>
       <c r="AH84" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI84" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7660,10 +7672,10 @@
         <v>151</v>
       </c>
       <c r="AH85" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI85" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7734,10 +7746,10 @@
         <v>152</v>
       </c>
       <c r="AH86" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI86" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7808,10 +7820,10 @@
         <v>151</v>
       </c>
       <c r="AH87" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI87" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7882,10 +7894,10 @@
         <v>151</v>
       </c>
       <c r="AH88" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI88" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7956,10 +7968,10 @@
         <v>151</v>
       </c>
       <c r="AH89" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI89" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8027,10 +8039,10 @@
         <v>151</v>
       </c>
       <c r="AH90" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI90" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8101,10 +8113,10 @@
         <v>152</v>
       </c>
       <c r="AH91" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI91" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8175,10 +8187,10 @@
         <v>151</v>
       </c>
       <c r="AH92" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI92" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8249,10 +8261,10 @@
         <v>151</v>
       </c>
       <c r="AH93" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI93" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8323,10 +8335,10 @@
         <v>151</v>
       </c>
       <c r="AH94" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI94" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8394,10 +8406,10 @@
         <v>151</v>
       </c>
       <c r="AH95" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI95" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8468,10 +8480,10 @@
         <v>152</v>
       </c>
       <c r="AH96" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI96" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8542,10 +8554,10 @@
         <v>151</v>
       </c>
       <c r="AH97" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI97" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8616,10 +8628,10 @@
         <v>151</v>
       </c>
       <c r="AH98" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI98" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8690,10 +8702,10 @@
         <v>152</v>
       </c>
       <c r="AH99" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI99" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8770,10 +8782,10 @@
         <v>151</v>
       </c>
       <c r="AH100" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI100" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8841,10 +8853,10 @@
         <v>151</v>
       </c>
       <c r="AH101" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI101" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8915,10 +8927,10 @@
         <v>151</v>
       </c>
       <c r="AH102" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI102" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8989,10 +9001,10 @@
         <v>151</v>
       </c>
       <c r="AH103" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI103" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9063,10 +9075,10 @@
         <v>151</v>
       </c>
       <c r="AH104" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI104" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9134,10 +9146,10 @@
         <v>151</v>
       </c>
       <c r="AH105" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI105" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9208,10 +9220,10 @@
         <v>152</v>
       </c>
       <c r="AH106" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI106" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9282,10 +9294,10 @@
         <v>151</v>
       </c>
       <c r="AH107" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI107" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9356,10 +9368,10 @@
         <v>151</v>
       </c>
       <c r="AH108" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI108" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9427,10 +9439,10 @@
         <v>151</v>
       </c>
       <c r="AH109" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI109" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9501,10 +9513,10 @@
         <v>152</v>
       </c>
       <c r="AH110" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI110" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9572,10 +9584,10 @@
         <v>153</v>
       </c>
       <c r="AH111" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI111" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9646,10 +9658,10 @@
         <v>152</v>
       </c>
       <c r="AH112" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI112" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9720,10 +9732,10 @@
         <v>150</v>
       </c>
       <c r="AH113" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI113" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9791,10 +9803,10 @@
         <v>153</v>
       </c>
       <c r="AH114" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI114" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9865,10 +9877,10 @@
         <v>152</v>
       </c>
       <c r="AH115" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI115" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9939,10 +9951,10 @@
         <v>151</v>
       </c>
       <c r="AH116" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI116" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10013,10 +10025,10 @@
         <v>151</v>
       </c>
       <c r="AH117" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI117" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10087,10 +10099,10 @@
         <v>151</v>
       </c>
       <c r="AH118" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI118" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10158,10 +10170,10 @@
         <v>151</v>
       </c>
       <c r="AH119" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI119" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10232,10 +10244,10 @@
         <v>152</v>
       </c>
       <c r="AH120" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI120" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10306,10 +10318,10 @@
         <v>151</v>
       </c>
       <c r="AH121" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI121" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10380,10 +10392,10 @@
         <v>151</v>
       </c>
       <c r="AH122" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI122" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10454,10 +10466,10 @@
         <v>151</v>
       </c>
       <c r="AH123" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI123" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10525,10 +10537,10 @@
         <v>151</v>
       </c>
       <c r="AH124" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI124" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10599,10 +10611,10 @@
         <v>152</v>
       </c>
       <c r="AH125" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI125" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10679,10 +10691,10 @@
         <v>152</v>
       </c>
       <c r="AH126" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI126" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10759,10 +10771,10 @@
         <v>152</v>
       </c>
       <c r="AH127" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI127" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10833,10 +10845,10 @@
         <v>155</v>
       </c>
       <c r="AH128" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI128" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10907,10 +10919,10 @@
         <v>155</v>
       </c>
       <c r="AH129" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI129" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10987,10 +10999,10 @@
         <v>155</v>
       </c>
       <c r="AH130" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI130" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11061,10 +11073,10 @@
         <v>155</v>
       </c>
       <c r="AH131" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI131" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11135,10 +11147,10 @@
         <v>155</v>
       </c>
       <c r="AH132" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI132" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11209,10 +11221,10 @@
         <v>155</v>
       </c>
       <c r="AH133" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI133" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11283,10 +11295,10 @@
         <v>155</v>
       </c>
       <c r="AH134" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI134" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11363,10 +11375,10 @@
         <v>155</v>
       </c>
       <c r="AH135" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI135" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11437,10 +11449,10 @@
         <v>155</v>
       </c>
       <c r="AH136" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI136" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11511,10 +11523,10 @@
         <v>155</v>
       </c>
       <c r="AH137" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI137" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11585,10 +11597,10 @@
         <v>155</v>
       </c>
       <c r="AH138" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI138" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11665,10 +11677,10 @@
         <v>155</v>
       </c>
       <c r="AH139" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI139" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11739,10 +11751,10 @@
         <v>155</v>
       </c>
       <c r="AH140" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI140" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11813,10 +11825,10 @@
         <v>155</v>
       </c>
       <c r="AH141" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI141" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11887,10 +11899,10 @@
         <v>155</v>
       </c>
       <c r="AH142" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI142" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11961,10 +11973,10 @@
         <v>155</v>
       </c>
       <c r="AH143" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI143" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12035,10 +12047,10 @@
         <v>155</v>
       </c>
       <c r="AH144" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI144" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12109,10 +12121,10 @@
         <v>155</v>
       </c>
       <c r="AH145" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI145" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12183,10 +12195,10 @@
         <v>155</v>
       </c>
       <c r="AH146" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI146" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12257,10 +12269,10 @@
         <v>155</v>
       </c>
       <c r="AH147" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI147" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12331,10 +12343,10 @@
         <v>155</v>
       </c>
       <c r="AH148" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI148" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12405,10 +12417,10 @@
         <v>155</v>
       </c>
       <c r="AH149" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI149" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12485,10 +12497,10 @@
         <v>155</v>
       </c>
       <c r="AH150" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI150" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12559,10 +12571,10 @@
         <v>155</v>
       </c>
       <c r="AH151" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI151" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12633,10 +12645,10 @@
         <v>155</v>
       </c>
       <c r="AH152" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI152" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12707,10 +12719,10 @@
         <v>155</v>
       </c>
       <c r="AH153" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI153" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12781,10 +12793,10 @@
         <v>156</v>
       </c>
       <c r="AH154" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI154" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12855,10 +12867,10 @@
         <v>156</v>
       </c>
       <c r="AH155" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI155" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12929,10 +12941,10 @@
         <v>156</v>
       </c>
       <c r="AH156" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI156" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13003,10 +13015,10 @@
         <v>156</v>
       </c>
       <c r="AH157" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI157" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13077,10 +13089,10 @@
         <v>156</v>
       </c>
       <c r="AH158" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI158" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13151,10 +13163,10 @@
         <v>156</v>
       </c>
       <c r="AH159" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI159" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13225,10 +13237,10 @@
         <v>156</v>
       </c>
       <c r="AH160" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI160" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13299,10 +13311,10 @@
         <v>156</v>
       </c>
       <c r="AH161" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI161" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13373,10 +13385,10 @@
         <v>156</v>
       </c>
       <c r="AH162" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI162" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13447,10 +13459,10 @@
         <v>156</v>
       </c>
       <c r="AH163" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI163" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13521,10 +13533,10 @@
         <v>156</v>
       </c>
       <c r="AH164" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI164" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13595,10 +13607,10 @@
         <v>156</v>
       </c>
       <c r="AH165" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI165" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13669,10 +13681,10 @@
         <v>156</v>
       </c>
       <c r="AH166" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI166" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13743,10 +13755,10 @@
         <v>156</v>
       </c>
       <c r="AH167" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI167" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13817,10 +13829,10 @@
         <v>156</v>
       </c>
       <c r="AH168" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI168" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13891,10 +13903,10 @@
         <v>156</v>
       </c>
       <c r="AH169" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI169" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13965,10 +13977,10 @@
         <v>156</v>
       </c>
       <c r="AH170" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI170" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14039,10 +14051,10 @@
         <v>156</v>
       </c>
       <c r="AH171" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI171" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14113,10 +14125,10 @@
         <v>156</v>
       </c>
       <c r="AH172" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI172" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14190,10 +14202,10 @@
         <v>156</v>
       </c>
       <c r="AH173" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI173" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14267,10 +14279,10 @@
         <v>156</v>
       </c>
       <c r="AH174" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI174" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14344,10 +14356,10 @@
         <v>156</v>
       </c>
       <c r="AH175" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI175" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14421,10 +14433,10 @@
         <v>156</v>
       </c>
       <c r="AH176" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI176" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14498,10 +14510,10 @@
         <v>156</v>
       </c>
       <c r="AH177" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI177" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14575,10 +14587,10 @@
         <v>156</v>
       </c>
       <c r="AH178" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI178" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14652,10 +14664,10 @@
         <v>156</v>
       </c>
       <c r="AH179" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI179" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14729,10 +14741,10 @@
         <v>156</v>
       </c>
       <c r="AH180" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI180" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14806,10 +14818,10 @@
         <v>156</v>
       </c>
       <c r="AH181" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI181" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14883,10 +14895,10 @@
         <v>156</v>
       </c>
       <c r="AH182" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI182" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14960,10 +14972,10 @@
         <v>156</v>
       </c>
       <c r="AH183" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI183" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15037,10 +15049,10 @@
         <v>156</v>
       </c>
       <c r="AH184" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI184" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15114,10 +15126,10 @@
         <v>156</v>
       </c>
       <c r="AH185" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI185" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15191,10 +15203,10 @@
         <v>156</v>
       </c>
       <c r="AH186" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI186" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15262,10 +15274,10 @@
         <v>156</v>
       </c>
       <c r="AH187" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI187" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15333,10 +15345,10 @@
         <v>156</v>
       </c>
       <c r="AH188" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI188" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15404,10 +15416,10 @@
         <v>156</v>
       </c>
       <c r="AH189" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI189" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15475,10 +15487,10 @@
         <v>156</v>
       </c>
       <c r="AH190" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI190" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15546,10 +15558,10 @@
         <v>156</v>
       </c>
       <c r="AH191" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI191" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15617,10 +15629,10 @@
         <v>156</v>
       </c>
       <c r="AH192" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI192" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15688,10 +15700,10 @@
         <v>54</v>
       </c>
       <c r="AH193" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI193" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15759,10 +15771,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI194" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15830,10 +15842,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI195" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15901,10 +15913,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI196" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15972,10 +15984,10 @@
         <v>157</v>
       </c>
       <c r="AH197" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI197" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16043,10 +16055,10 @@
         <v>55</v>
       </c>
       <c r="AH198" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI198" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16114,10 +16126,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI199" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16185,10 +16197,10 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI200" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16256,10 +16268,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI201" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16327,10 +16339,10 @@
         <v>157</v>
       </c>
       <c r="AH202" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI202" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16398,10 +16410,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI203" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16469,10 +16481,10 @@
         <v>157</v>
       </c>
       <c r="AH204" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI204" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16540,10 +16552,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI205" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16611,10 +16623,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI206" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16682,10 +16694,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI207" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16753,10 +16765,10 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI208" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16824,10 +16836,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI209" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16895,10 +16907,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI210" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16966,10 +16978,10 @@
         <v>157</v>
       </c>
       <c r="AH211" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI211" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17037,10 +17049,10 @@
         <v>55</v>
       </c>
       <c r="AH212" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI212" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17111,10 +17123,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI213" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17185,10 +17197,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI214" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17259,10 +17271,10 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI215" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17333,10 +17345,10 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI216" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17404,10 +17416,10 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI217" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17475,10 +17487,10 @@
         <v>54</v>
       </c>
       <c r="AH218" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI218" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17543,10 +17555,10 @@
         <v>0</v>
       </c>
       <c r="AH219" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI219" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17608,10 +17620,10 @@
         <v>0</v>
       </c>
       <c r="AH220" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI220" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17679,13 +17691,13 @@
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AH221" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI221" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17759,10 +17771,10 @@
         <v>146</v>
       </c>
       <c r="AH222" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI222" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17839,10 +17851,10 @@
         <v>143</v>
       </c>
       <c r="AH223" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI223" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17919,10 +17931,10 @@
         <v>149</v>
       </c>
       <c r="AH224" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI224" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -17999,10 +18011,10 @@
         <v>144</v>
       </c>
       <c r="AH225" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI225" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18073,10 +18085,10 @@
         <v>145</v>
       </c>
       <c r="AH226" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI226" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18153,10 +18165,10 @@
         <v>143</v>
       </c>
       <c r="AH227" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI227" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18233,10 +18245,10 @@
         <v>143</v>
       </c>
       <c r="AH228" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI228" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18310,10 +18322,10 @@
         <v>151</v>
       </c>
       <c r="AH229" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI229" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18387,10 +18399,10 @@
         <v>154</v>
       </c>
       <c r="AH230" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI230" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18464,10 +18476,10 @@
         <v>154</v>
       </c>
       <c r="AH231" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI231" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18544,10 +18556,10 @@
         <v>150</v>
       </c>
       <c r="AH232" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI232" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18618,10 +18630,10 @@
         <v>151</v>
       </c>
       <c r="AH233" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI233" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18692,10 +18704,10 @@
         <v>154</v>
       </c>
       <c r="AH234" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI234" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18766,10 +18778,10 @@
         <v>154</v>
       </c>
       <c r="AH235" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI235" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -18840,10 +18852,10 @@
         <v>155</v>
       </c>
       <c r="AH236" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI236" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -18920,10 +18932,10 @@
         <v>155</v>
       </c>
       <c r="AH237" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI237" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19000,10 +19012,10 @@
         <v>155</v>
       </c>
       <c r="AH238" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI238" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19077,10 +19089,10 @@
         <v>155</v>
       </c>
       <c r="AH239" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI239" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19154,10 +19166,10 @@
         <v>155</v>
       </c>
       <c r="AH240" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI240" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19228,10 +19240,10 @@
         <v>156</v>
       </c>
       <c r="AH241" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI241" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19302,10 +19314,10 @@
         <v>156</v>
       </c>
       <c r="AH242" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI242" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19376,24 +19388,24 @@
         <v>156</v>
       </c>
       <c r="AH243" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AI243" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B244" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
@@ -19402,7 +19414,7 @@
         <v>56</v>
       </c>
       <c r="G244">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -19411,34 +19423,37 @@
         <v>64</v>
       </c>
       <c r="J244" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N244" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P244">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q244">
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>17941177</v>
+        <v>17222405</v>
       </c>
       <c r="S244" t="s">
         <v>156</v>
       </c>
       <c r="U244" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V244" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W244">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X244" t="s">
-        <v>178</v>
+        <v>169</v>
+      </c>
+      <c r="Y244" t="s">
+        <v>259</v>
       </c>
       <c r="AB244">
         <v>0</v>
@@ -19447,33 +19462,33 @@
         <v>156</v>
       </c>
       <c r="AH244" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AI244" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B245" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
       </c>
       <c r="D245" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E245" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F245" t="s">
         <v>56</v>
       </c>
       <c r="G245">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -19482,34 +19497,34 @@
         <v>64</v>
       </c>
       <c r="J245" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N245" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P245">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q245">
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>17952385</v>
+        <v>16959950</v>
       </c>
       <c r="S245" t="s">
         <v>156</v>
       </c>
       <c r="U245" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V245" s="1">
-        <v>46274.41775447917</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W245">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X245" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AB245">
         <v>0</v>
@@ -19518,33 +19533,33 @@
         <v>156</v>
       </c>
       <c r="AH245" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AI245" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="246" spans="1:35">
       <c r="A246">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C246" t="s">
         <v>50</v>
       </c>
       <c r="D246" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E246" t="s">
         <v>54</v>
       </c>
       <c r="F246" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G246">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -19553,34 +19568,37 @@
         <v>64</v>
       </c>
       <c r="J246" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N246" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P246">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q246">
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>17952569</v>
+        <v>18178138</v>
       </c>
       <c r="S246" t="s">
         <v>156</v>
       </c>
       <c r="U246" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V246" s="1">
-        <v>46274.41777533565</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W246">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X246" t="s">
-        <v>174</v>
+        <v>171</v>
+      </c>
+      <c r="Y246" t="s">
+        <v>260</v>
       </c>
       <c r="AB246">
         <v>0</v>
@@ -19589,24 +19607,24 @@
         <v>156</v>
       </c>
       <c r="AH246" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AI246" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B247" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19615,7 +19633,7 @@
         <v>57</v>
       </c>
       <c r="G247">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -19624,34 +19642,37 @@
         <v>64</v>
       </c>
       <c r="J247" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N247" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P247">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q247">
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>18164516</v>
+        <v>18188724</v>
       </c>
       <c r="S247" t="s">
         <v>156</v>
       </c>
       <c r="U247" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V247" s="1">
-        <v>46274.41799166667</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X247" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="Y247" t="s">
+        <v>261</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19660,24 +19681,24 @@
         <v>156</v>
       </c>
       <c r="AH247" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AI247" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B248" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
       </c>
       <c r="D248" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -19686,7 +19707,7 @@
         <v>57</v>
       </c>
       <c r="G248">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -19695,34 +19716,37 @@
         <v>64</v>
       </c>
       <c r="J248" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N248" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P248">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q248">
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>18178157</v>
+        <v>18188630</v>
       </c>
       <c r="S248" t="s">
         <v>156</v>
       </c>
       <c r="U248" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V248" s="1">
-        <v>46274.41800114583</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X248" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="Y248" t="s">
+        <v>262</v>
       </c>
       <c r="AB248">
         <v>0</v>
@@ -19731,10 +19755,10 @@
         <v>156</v>
       </c>
       <c r="AH248" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AI248" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -19757,19 +19781,19 @@
         <v>56</v>
       </c>
       <c r="G249">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H249">
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J249" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N249" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P249">
         <v>9</v>
@@ -19778,19 +19802,19 @@
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>17941187</v>
+        <v>17941177</v>
       </c>
       <c r="S249" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="U249" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V249" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X249" t="s">
         <v>178</v>
@@ -19799,13 +19823,13 @@
         <v>0</v>
       </c>
       <c r="AC249" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="AH249" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI249" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -19828,19 +19852,19 @@
         <v>56</v>
       </c>
       <c r="G250">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J250" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N250" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P250">
         <v>9</v>
@@ -19849,19 +19873,19 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>17952400</v>
+        <v>17952385</v>
       </c>
       <c r="S250" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="U250" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V250" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X250" t="s">
         <v>174</v>
@@ -19870,13 +19894,13 @@
         <v>0</v>
       </c>
       <c r="AC250" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="AH250" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI250" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -19899,19 +19923,19 @@
         <v>56</v>
       </c>
       <c r="G251">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H251">
         <v>0</v>
       </c>
       <c r="I251" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J251" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N251" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P251">
         <v>9</v>
@@ -19920,19 +19944,19 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>17952580</v>
+        <v>17952569</v>
       </c>
       <c r="S251" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="U251" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V251" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X251" t="s">
         <v>174</v>
@@ -19941,13 +19965,13 @@
         <v>0</v>
       </c>
       <c r="AC251" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="AH251" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI251" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -19970,19 +19994,19 @@
         <v>57</v>
       </c>
       <c r="G252">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H252">
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J252" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N252" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P252">
         <v>9</v>
@@ -19991,19 +20015,19 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>18164523</v>
+        <v>18164516</v>
       </c>
       <c r="S252" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="U252" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V252" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X252" t="s">
         <v>172</v>
@@ -20012,13 +20036,13 @@
         <v>0</v>
       </c>
       <c r="AC252" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="AH252" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI252" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20041,19 +20065,19 @@
         <v>57</v>
       </c>
       <c r="G253">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H253">
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J253" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N253" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P253">
         <v>9</v>
@@ -20062,19 +20086,19 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>18178163</v>
+        <v>18178157</v>
       </c>
       <c r="S253" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U253" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V253" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X253" t="s">
         <v>171</v>
@@ -20083,27 +20107,27 @@
         <v>0</v>
       </c>
       <c r="AC253" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AH253" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AI253" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
       </c>
       <c r="D254" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E254" t="s">
         <v>54</v>
@@ -20112,7 +20136,7 @@
         <v>56</v>
       </c>
       <c r="G254">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -20121,19 +20145,19 @@
         <v>65</v>
       </c>
       <c r="J254" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N254" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P254">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q254">
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>17994311</v>
+        <v>17941187</v>
       </c>
       <c r="S254" t="s">
         <v>54</v>
@@ -20142,39 +20166,39 @@
         <v>168</v>
       </c>
       <c r="V254" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X254" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AB254">
         <v>0</v>
       </c>
       <c r="AC254" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH254" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AI254" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B255" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
       </c>
       <c r="D255" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E255" t="s">
         <v>54</v>
@@ -20183,7 +20207,7 @@
         <v>56</v>
       </c>
       <c r="G255">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -20192,19 +20216,19 @@
         <v>65</v>
       </c>
       <c r="J255" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N255" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P255">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q255">
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>17994675</v>
+        <v>17952400</v>
       </c>
       <c r="S255" t="s">
         <v>54</v>
@@ -20213,39 +20237,39 @@
         <v>168</v>
       </c>
       <c r="V255" s="1">
-        <v>46275.31747032407</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X255" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AB255">
         <v>0</v>
       </c>
       <c r="AC255" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH255" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AI255" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B256" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -20254,7 +20278,7 @@
         <v>56</v>
       </c>
       <c r="G256">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -20263,19 +20287,19 @@
         <v>65</v>
       </c>
       <c r="J256" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N256" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P256">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q256">
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17994809</v>
+        <v>17952580</v>
       </c>
       <c r="S256" t="s">
         <v>54</v>
@@ -20284,48 +20308,48 @@
         <v>168</v>
       </c>
       <c r="V256" s="1">
-        <v>46275.31747981482</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X256" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AB256">
         <v>0</v>
       </c>
       <c r="AC256" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH256" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AI256" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B257" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
       </c>
       <c r="D257" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E257" t="s">
         <v>54</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G257">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -20334,19 +20358,19 @@
         <v>65</v>
       </c>
       <c r="J257" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N257" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P257">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q257">
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18006051</v>
+        <v>18164523</v>
       </c>
       <c r="S257" t="s">
         <v>54</v>
@@ -20355,48 +20379,48 @@
         <v>168</v>
       </c>
       <c r="V257" s="1">
-        <v>46275.31748724537</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X257" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB257">
         <v>0</v>
       </c>
       <c r="AC257" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH257" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AI257" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B258" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E258" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F258" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G258">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -20405,34 +20429,34 @@
         <v>65</v>
       </c>
       <c r="J258" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N258" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P258">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q258">
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>18003256</v>
+        <v>18178163</v>
       </c>
       <c r="S258" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="U258" t="s">
         <v>168</v>
       </c>
       <c r="V258" s="1">
-        <v>46275.31749535879</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X258" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AB258">
         <v>0</v>
@@ -20441,24 +20465,24 @@
         <v>157</v>
       </c>
       <c r="AH258" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AI258" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B259" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
       </c>
       <c r="D259" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -20488,7 +20512,7 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>18004017</v>
+        <v>17994311</v>
       </c>
       <c r="S259" t="s">
         <v>54</v>
@@ -20497,13 +20521,13 @@
         <v>168</v>
       </c>
       <c r="V259" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W259">
         <v>0</v>
       </c>
       <c r="X259" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AB259">
         <v>0</v>
@@ -20512,24 +20536,24 @@
         <v>157</v>
       </c>
       <c r="AH259" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI259" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B260" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E260" t="s">
         <v>54</v>
@@ -20559,7 +20583,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>17995164</v>
+        <v>17994675</v>
       </c>
       <c r="S260" t="s">
         <v>54</v>
@@ -20568,13 +20592,13 @@
         <v>168</v>
       </c>
       <c r="V260" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W260">
         <v>0</v>
       </c>
       <c r="X260" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AB260">
         <v>0</v>
@@ -20583,24 +20607,24 @@
         <v>157</v>
       </c>
       <c r="AH260" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI260" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B261" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20630,7 +20654,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>18004028</v>
+        <v>17994809</v>
       </c>
       <c r="S261" t="s">
         <v>54</v>
@@ -20639,13 +20663,13 @@
         <v>168</v>
       </c>
       <c r="V261" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W261">
         <v>0</v>
       </c>
       <c r="X261" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AB261">
         <v>0</v>
@@ -20654,10 +20678,365 @@
         <v>157</v>
       </c>
       <c r="AH261" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AI261" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="262" spans="1:35">
+      <c r="A262">
+        <v>6548</v>
+      </c>
+      <c r="B262" t="s">
+        <v>35</v>
+      </c>
+      <c r="C262" t="s">
+        <v>50</v>
+      </c>
+      <c r="D262" t="s">
+        <v>51</v>
+      </c>
+      <c r="E262" t="s">
+        <v>54</v>
+      </c>
+      <c r="F262" t="s">
+        <v>56</v>
+      </c>
+      <c r="G262">
+        <v>11746</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262" t="s">
+        <v>65</v>
+      </c>
+      <c r="J262" t="s">
+        <v>126</v>
+      </c>
+      <c r="N262" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P262">
+        <v>8</v>
+      </c>
+      <c r="Q262">
+        <v>2026</v>
+      </c>
+      <c r="R262">
+        <v>18006051</v>
+      </c>
+      <c r="S262" t="s">
+        <v>54</v>
+      </c>
+      <c r="U262" t="s">
+        <v>168</v>
+      </c>
+      <c r="V262" s="1">
+        <v>46275.31748724537</v>
+      </c>
+      <c r="W262">
+        <v>0</v>
+      </c>
+      <c r="X262" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB262">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH262" t="s">
         <v>267</v>
+      </c>
+      <c r="AI262" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="263" spans="1:35">
+      <c r="A263">
+        <v>6628</v>
+      </c>
+      <c r="B263" t="s">
+        <v>38</v>
+      </c>
+      <c r="C263" t="s">
+        <v>50</v>
+      </c>
+      <c r="D263" t="s">
+        <v>52</v>
+      </c>
+      <c r="E263" t="s">
+        <v>55</v>
+      </c>
+      <c r="F263" t="s">
+        <v>56</v>
+      </c>
+      <c r="G263">
+        <v>11746</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263" t="s">
+        <v>65</v>
+      </c>
+      <c r="J263" t="s">
+        <v>126</v>
+      </c>
+      <c r="N263" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P263">
+        <v>8</v>
+      </c>
+      <c r="Q263">
+        <v>2026</v>
+      </c>
+      <c r="R263">
+        <v>18003256</v>
+      </c>
+      <c r="S263" t="s">
+        <v>55</v>
+      </c>
+      <c r="U263" t="s">
+        <v>168</v>
+      </c>
+      <c r="V263" s="1">
+        <v>46275.31749535879</v>
+      </c>
+      <c r="W263">
+        <v>0</v>
+      </c>
+      <c r="X263" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB263">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH263" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI263" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="264" spans="1:35">
+      <c r="A264">
+        <v>6703</v>
+      </c>
+      <c r="B264" t="s">
+        <v>46</v>
+      </c>
+      <c r="C264" t="s">
+        <v>50</v>
+      </c>
+      <c r="D264" t="s">
+        <v>53</v>
+      </c>
+      <c r="E264" t="s">
+        <v>54</v>
+      </c>
+      <c r="F264" t="s">
+        <v>56</v>
+      </c>
+      <c r="G264">
+        <v>11746</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264" t="s">
+        <v>65</v>
+      </c>
+      <c r="J264" t="s">
+        <v>126</v>
+      </c>
+      <c r="N264" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P264">
+        <v>8</v>
+      </c>
+      <c r="Q264">
+        <v>2026</v>
+      </c>
+      <c r="R264">
+        <v>18004017</v>
+      </c>
+      <c r="S264" t="s">
+        <v>54</v>
+      </c>
+      <c r="U264" t="s">
+        <v>168</v>
+      </c>
+      <c r="V264" s="1">
+        <v>46275.31750491898</v>
+      </c>
+      <c r="W264">
+        <v>0</v>
+      </c>
+      <c r="X264" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB264">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH264" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI264" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="265" spans="1:35">
+      <c r="A265">
+        <v>6704</v>
+      </c>
+      <c r="B265" t="s">
+        <v>42</v>
+      </c>
+      <c r="C265" t="s">
+        <v>50</v>
+      </c>
+      <c r="D265" t="s">
+        <v>51</v>
+      </c>
+      <c r="E265" t="s">
+        <v>54</v>
+      </c>
+      <c r="F265" t="s">
+        <v>56</v>
+      </c>
+      <c r="G265">
+        <v>11746</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265" t="s">
+        <v>65</v>
+      </c>
+      <c r="J265" t="s">
+        <v>126</v>
+      </c>
+      <c r="N265" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P265">
+        <v>8</v>
+      </c>
+      <c r="Q265">
+        <v>2026</v>
+      </c>
+      <c r="R265">
+        <v>17995164</v>
+      </c>
+      <c r="S265" t="s">
+        <v>54</v>
+      </c>
+      <c r="U265" t="s">
+        <v>168</v>
+      </c>
+      <c r="V265" s="1">
+        <v>46275.31750555555</v>
+      </c>
+      <c r="W265">
+        <v>0</v>
+      </c>
+      <c r="X265" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB265">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH265" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI265" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:35">
+      <c r="A266">
+        <v>6705</v>
+      </c>
+      <c r="B266" t="s">
+        <v>48</v>
+      </c>
+      <c r="C266" t="s">
+        <v>50</v>
+      </c>
+      <c r="D266" t="s">
+        <v>52</v>
+      </c>
+      <c r="E266" t="s">
+        <v>54</v>
+      </c>
+      <c r="F266" t="s">
+        <v>56</v>
+      </c>
+      <c r="G266">
+        <v>11746</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266" t="s">
+        <v>65</v>
+      </c>
+      <c r="J266" t="s">
+        <v>126</v>
+      </c>
+      <c r="N266" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P266">
+        <v>8</v>
+      </c>
+      <c r="Q266">
+        <v>2026</v>
+      </c>
+      <c r="R266">
+        <v>18004028</v>
+      </c>
+      <c r="S266" t="s">
+        <v>54</v>
+      </c>
+      <c r="U266" t="s">
+        <v>168</v>
+      </c>
+      <c r="V266" s="1">
+        <v>46275.31750599537</v>
+      </c>
+      <c r="W266">
+        <v>0</v>
+      </c>
+      <c r="X266" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB266">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH266" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI266" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="274">
   <si>
     <t>CodCliente</t>
   </si>
@@ -822,6 +822,12 @@
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-09/09/2026 17:53:38.. - Data Comentário: 09/09/2026 17:48</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 10/09/2026 13:58:56. - Data Comentário: 10/09/2026 13:54</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 10/09/2026 13:59:39. - Data Comentário: 10/09/2026 13:54</t>
   </si>
   <si>
     <t>Karen Ribeiro</t>
@@ -1184,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI266"/>
+  <dimension ref="A1:AI269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1365,10 +1371,10 @@
         <v>134</v>
       </c>
       <c r="AH2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1442,10 +1448,10 @@
         <v>135</v>
       </c>
       <c r="AH3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1519,10 +1525,10 @@
         <v>134</v>
       </c>
       <c r="AH4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1593,10 +1599,10 @@
         <v>134</v>
       </c>
       <c r="AH5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1667,10 +1673,10 @@
         <v>135</v>
       </c>
       <c r="AH6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1741,10 +1747,10 @@
         <v>135</v>
       </c>
       <c r="AH7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1815,10 +1821,10 @@
         <v>136</v>
       </c>
       <c r="AH8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1889,10 +1895,10 @@
         <v>134</v>
       </c>
       <c r="AH9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1963,10 +1969,10 @@
         <v>137</v>
       </c>
       <c r="AH10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2037,10 +2043,10 @@
         <v>137</v>
       </c>
       <c r="AH11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2111,10 +2117,10 @@
         <v>138</v>
       </c>
       <c r="AH12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2182,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AH13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2256,13 +2262,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AH14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2330,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2395,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2466,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2543,10 +2549,10 @@
         <v>140</v>
       </c>
       <c r="AH18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2620,10 +2626,10 @@
         <v>139</v>
       </c>
       <c r="AH19" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2697,10 +2703,10 @@
         <v>140</v>
       </c>
       <c r="AH20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2774,10 +2780,10 @@
         <v>138</v>
       </c>
       <c r="AH21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2848,10 +2854,10 @@
         <v>141</v>
       </c>
       <c r="AH22" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2922,10 +2928,10 @@
         <v>138</v>
       </c>
       <c r="AH23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -2996,10 +3002,10 @@
         <v>138</v>
       </c>
       <c r="AH24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI24" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3070,10 +3076,10 @@
         <v>138</v>
       </c>
       <c r="AH25" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3144,10 +3150,10 @@
         <v>139</v>
       </c>
       <c r="AH26" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3218,10 +3224,10 @@
         <v>138</v>
       </c>
       <c r="AH27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3292,10 +3298,10 @@
         <v>138</v>
       </c>
       <c r="AH28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI28" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3366,10 +3372,10 @@
         <v>138</v>
       </c>
       <c r="AH29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI29" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3440,10 +3446,10 @@
         <v>142</v>
       </c>
       <c r="AH30" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI30" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3520,10 +3526,10 @@
         <v>143</v>
       </c>
       <c r="AH31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3594,10 +3600,10 @@
         <v>144</v>
       </c>
       <c r="AH32" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI32" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3674,10 +3680,10 @@
         <v>145</v>
       </c>
       <c r="AH33" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI33" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3751,10 +3757,10 @@
         <v>146</v>
       </c>
       <c r="AH34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI34" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3828,13 +3834,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AH35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI35" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3911,10 +3917,10 @@
         <v>148</v>
       </c>
       <c r="AH36" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI36" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -3991,10 +3997,10 @@
         <v>142</v>
       </c>
       <c r="AH37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI37" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4068,10 +4074,10 @@
         <v>164</v>
       </c>
       <c r="AH38" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI38" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4148,10 +4154,10 @@
         <v>143</v>
       </c>
       <c r="AH39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI39" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4228,10 +4234,10 @@
         <v>143</v>
       </c>
       <c r="AH40" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI40" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4308,10 +4314,10 @@
         <v>143</v>
       </c>
       <c r="AH41" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI41" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4388,10 +4394,10 @@
         <v>142</v>
       </c>
       <c r="AH42" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI42" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4468,10 +4474,10 @@
         <v>149</v>
       </c>
       <c r="AH43" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI43" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4548,10 +4554,10 @@
         <v>144</v>
       </c>
       <c r="AH44" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI44" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4628,10 +4634,10 @@
         <v>145</v>
       </c>
       <c r="AH45" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4699,10 +4705,10 @@
         <v>146</v>
       </c>
       <c r="AH46" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4773,10 +4779,10 @@
         <v>143</v>
       </c>
       <c r="AH47" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI47" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4847,10 +4853,10 @@
         <v>143</v>
       </c>
       <c r="AH48" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI48" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4921,10 +4927,10 @@
         <v>143</v>
       </c>
       <c r="AH49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI49" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -4995,10 +5001,10 @@
         <v>142</v>
       </c>
       <c r="AH50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5069,10 +5075,10 @@
         <v>149</v>
       </c>
       <c r="AH51" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI51" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5149,10 +5155,10 @@
         <v>144</v>
       </c>
       <c r="AH52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI52" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5223,10 +5229,10 @@
         <v>145</v>
       </c>
       <c r="AH53" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5303,10 +5309,10 @@
         <v>143</v>
       </c>
       <c r="AH54" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI54" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5383,10 +5389,10 @@
         <v>143</v>
       </c>
       <c r="AH55" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI55" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5463,10 +5469,10 @@
         <v>143</v>
       </c>
       <c r="AH56" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI56" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5543,10 +5549,10 @@
         <v>142</v>
       </c>
       <c r="AH57" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI57" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5620,10 +5626,10 @@
         <v>146</v>
       </c>
       <c r="AH58" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI58" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5697,13 +5703,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AH59" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI59" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5780,10 +5786,10 @@
         <v>143</v>
       </c>
       <c r="AH60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI60" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5860,10 +5866,10 @@
         <v>143</v>
       </c>
       <c r="AH61" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI61" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5940,10 +5946,10 @@
         <v>143</v>
       </c>
       <c r="AH62" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI62" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6020,10 +6026,10 @@
         <v>142</v>
       </c>
       <c r="AH63" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI63" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6100,10 +6106,10 @@
         <v>149</v>
       </c>
       <c r="AH64" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI64" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6180,10 +6186,10 @@
         <v>144</v>
       </c>
       <c r="AH65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI65" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6260,10 +6266,10 @@
         <v>145</v>
       </c>
       <c r="AH66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6340,10 +6346,10 @@
         <v>143</v>
       </c>
       <c r="AH67" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6411,10 +6417,10 @@
         <v>146</v>
       </c>
       <c r="AH68" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI68" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6482,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AH69" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6559,10 +6565,10 @@
         <v>143</v>
       </c>
       <c r="AH70" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI70" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6633,10 +6639,10 @@
         <v>143</v>
       </c>
       <c r="AH71" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI71" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6707,10 +6713,10 @@
         <v>143</v>
       </c>
       <c r="AH72" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI72" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6781,10 +6787,10 @@
         <v>142</v>
       </c>
       <c r="AH73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI73" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6855,10 +6861,10 @@
         <v>149</v>
       </c>
       <c r="AH74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI74" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6929,10 +6935,10 @@
         <v>144</v>
       </c>
       <c r="AH75" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI75" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7003,10 +7009,10 @@
         <v>145</v>
       </c>
       <c r="AH76" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI76" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7077,10 +7083,10 @@
         <v>145</v>
       </c>
       <c r="AH77" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI77" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7151,10 +7157,10 @@
         <v>145</v>
       </c>
       <c r="AH78" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI78" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7225,10 +7231,10 @@
         <v>145</v>
       </c>
       <c r="AH79" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI79" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7299,10 +7305,10 @@
         <v>151</v>
       </c>
       <c r="AH80" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI80" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7373,10 +7379,10 @@
         <v>151</v>
       </c>
       <c r="AH81" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI81" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7447,10 +7453,10 @@
         <v>152</v>
       </c>
       <c r="AH82" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI82" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7521,10 +7527,10 @@
         <v>151</v>
       </c>
       <c r="AH83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI83" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7595,10 +7601,10 @@
         <v>151</v>
       </c>
       <c r="AH84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7672,10 +7678,10 @@
         <v>151</v>
       </c>
       <c r="AH85" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI85" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7746,10 +7752,10 @@
         <v>152</v>
       </c>
       <c r="AH86" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI86" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7820,10 +7826,10 @@
         <v>151</v>
       </c>
       <c r="AH87" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI87" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7894,10 +7900,10 @@
         <v>151</v>
       </c>
       <c r="AH88" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI88" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7968,10 +7974,10 @@
         <v>151</v>
       </c>
       <c r="AH89" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI89" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8039,10 +8045,10 @@
         <v>151</v>
       </c>
       <c r="AH90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI90" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8113,10 +8119,10 @@
         <v>152</v>
       </c>
       <c r="AH91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8187,10 +8193,10 @@
         <v>151</v>
       </c>
       <c r="AH92" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI92" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8261,10 +8267,10 @@
         <v>151</v>
       </c>
       <c r="AH93" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI93" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8335,10 +8341,10 @@
         <v>151</v>
       </c>
       <c r="AH94" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI94" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8406,10 +8412,10 @@
         <v>151</v>
       </c>
       <c r="AH95" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI95" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8480,10 +8486,10 @@
         <v>152</v>
       </c>
       <c r="AH96" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI96" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8554,10 +8560,10 @@
         <v>151</v>
       </c>
       <c r="AH97" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI97" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8628,10 +8634,10 @@
         <v>151</v>
       </c>
       <c r="AH98" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI98" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8702,10 +8708,10 @@
         <v>152</v>
       </c>
       <c r="AH99" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI99" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8782,10 +8788,10 @@
         <v>151</v>
       </c>
       <c r="AH100" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI100" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8853,10 +8859,10 @@
         <v>151</v>
       </c>
       <c r="AH101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI101" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8927,10 +8933,10 @@
         <v>151</v>
       </c>
       <c r="AH102" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI102" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9001,10 +9007,10 @@
         <v>151</v>
       </c>
       <c r="AH103" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI103" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9075,10 +9081,10 @@
         <v>151</v>
       </c>
       <c r="AH104" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI104" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9146,10 +9152,10 @@
         <v>151</v>
       </c>
       <c r="AH105" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI105" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9220,10 +9226,10 @@
         <v>152</v>
       </c>
       <c r="AH106" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI106" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9294,10 +9300,10 @@
         <v>151</v>
       </c>
       <c r="AH107" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI107" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9368,10 +9374,10 @@
         <v>151</v>
       </c>
       <c r="AH108" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI108" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9439,10 +9445,10 @@
         <v>151</v>
       </c>
       <c r="AH109" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI109" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9513,10 +9519,10 @@
         <v>152</v>
       </c>
       <c r="AH110" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI110" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9584,10 +9590,10 @@
         <v>153</v>
       </c>
       <c r="AH111" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI111" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9658,10 +9664,10 @@
         <v>152</v>
       </c>
       <c r="AH112" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI112" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9732,10 +9738,10 @@
         <v>150</v>
       </c>
       <c r="AH113" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI113" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9803,10 +9809,10 @@
         <v>153</v>
       </c>
       <c r="AH114" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI114" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9877,10 +9883,10 @@
         <v>152</v>
       </c>
       <c r="AH115" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI115" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9951,10 +9957,10 @@
         <v>151</v>
       </c>
       <c r="AH116" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10025,10 +10031,10 @@
         <v>151</v>
       </c>
       <c r="AH117" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI117" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10099,10 +10105,10 @@
         <v>151</v>
       </c>
       <c r="AH118" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI118" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10170,10 +10176,10 @@
         <v>151</v>
       </c>
       <c r="AH119" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI119" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10244,10 +10250,10 @@
         <v>152</v>
       </c>
       <c r="AH120" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI120" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10318,10 +10324,10 @@
         <v>151</v>
       </c>
       <c r="AH121" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI121" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10392,10 +10398,10 @@
         <v>151</v>
       </c>
       <c r="AH122" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI122" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10466,10 +10472,10 @@
         <v>151</v>
       </c>
       <c r="AH123" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI123" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10537,10 +10543,10 @@
         <v>151</v>
       </c>
       <c r="AH124" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI124" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10611,10 +10617,10 @@
         <v>152</v>
       </c>
       <c r="AH125" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI125" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10691,10 +10697,10 @@
         <v>152</v>
       </c>
       <c r="AH126" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI126" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10771,10 +10777,10 @@
         <v>152</v>
       </c>
       <c r="AH127" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI127" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10845,10 +10851,10 @@
         <v>155</v>
       </c>
       <c r="AH128" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI128" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10919,10 +10925,10 @@
         <v>155</v>
       </c>
       <c r="AH129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI129" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10999,10 +11005,10 @@
         <v>155</v>
       </c>
       <c r="AH130" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11073,10 +11079,10 @@
         <v>155</v>
       </c>
       <c r="AH131" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI131" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11147,10 +11153,10 @@
         <v>155</v>
       </c>
       <c r="AH132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI132" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11221,10 +11227,10 @@
         <v>155</v>
       </c>
       <c r="AH133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI133" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11295,10 +11301,10 @@
         <v>155</v>
       </c>
       <c r="AH134" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI134" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11375,10 +11381,10 @@
         <v>155</v>
       </c>
       <c r="AH135" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI135" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11449,10 +11455,10 @@
         <v>155</v>
       </c>
       <c r="AH136" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI136" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11523,10 +11529,10 @@
         <v>155</v>
       </c>
       <c r="AH137" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI137" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11597,10 +11603,10 @@
         <v>155</v>
       </c>
       <c r="AH138" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI138" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11677,10 +11683,10 @@
         <v>155</v>
       </c>
       <c r="AH139" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI139" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11751,10 +11757,10 @@
         <v>155</v>
       </c>
       <c r="AH140" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI140" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11825,10 +11831,10 @@
         <v>155</v>
       </c>
       <c r="AH141" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11899,10 +11905,10 @@
         <v>155</v>
       </c>
       <c r="AH142" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI142" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11973,10 +11979,10 @@
         <v>155</v>
       </c>
       <c r="AH143" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI143" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12047,10 +12053,10 @@
         <v>155</v>
       </c>
       <c r="AH144" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI144" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12121,10 +12127,10 @@
         <v>155</v>
       </c>
       <c r="AH145" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI145" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12195,10 +12201,10 @@
         <v>155</v>
       </c>
       <c r="AH146" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI146" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12269,10 +12275,10 @@
         <v>155</v>
       </c>
       <c r="AH147" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI147" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12343,10 +12349,10 @@
         <v>155</v>
       </c>
       <c r="AH148" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI148" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12417,10 +12423,10 @@
         <v>155</v>
       </c>
       <c r="AH149" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12497,10 +12503,10 @@
         <v>155</v>
       </c>
       <c r="AH150" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI150" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12571,10 +12577,10 @@
         <v>155</v>
       </c>
       <c r="AH151" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI151" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12645,10 +12651,10 @@
         <v>155</v>
       </c>
       <c r="AH152" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI152" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12719,10 +12725,10 @@
         <v>155</v>
       </c>
       <c r="AH153" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI153" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12793,10 +12799,10 @@
         <v>156</v>
       </c>
       <c r="AH154" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI154" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12867,10 +12873,10 @@
         <v>156</v>
       </c>
       <c r="AH155" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI155" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12941,10 +12947,10 @@
         <v>156</v>
       </c>
       <c r="AH156" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI156" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13015,10 +13021,10 @@
         <v>156</v>
       </c>
       <c r="AH157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI157" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13089,10 +13095,10 @@
         <v>156</v>
       </c>
       <c r="AH158" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI158" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13163,10 +13169,10 @@
         <v>156</v>
       </c>
       <c r="AH159" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI159" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13237,24 +13243,24 @@
         <v>156</v>
       </c>
       <c r="AH160" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI160" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:35">
       <c r="A161">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C161" t="s">
         <v>50</v>
       </c>
       <c r="D161" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E161" t="s">
         <v>54</v>
@@ -13284,7 +13290,7 @@
         <v>2026</v>
       </c>
       <c r="R161">
-        <v>17941156</v>
+        <v>18056705</v>
       </c>
       <c r="S161" t="s">
         <v>156</v>
@@ -13293,13 +13299,13 @@
         <v>167</v>
       </c>
       <c r="V161" s="1">
-        <v>46266.25232392361</v>
+        <v>46266.25239591435</v>
       </c>
       <c r="W161">
         <v>0</v>
       </c>
       <c r="X161" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Y161" t="s">
         <v>225</v>
@@ -13311,18 +13317,18 @@
         <v>156</v>
       </c>
       <c r="AH161" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI161" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:35">
       <c r="A162">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B162" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C162" t="s">
         <v>50</v>
@@ -13334,7 +13340,7 @@
         <v>54</v>
       </c>
       <c r="F162" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G162">
         <v>951</v>
@@ -13358,7 +13364,7 @@
         <v>2026</v>
       </c>
       <c r="R162">
-        <v>18056705</v>
+        <v>18164501</v>
       </c>
       <c r="S162" t="s">
         <v>156</v>
@@ -13367,16 +13373,16 @@
         <v>167</v>
       </c>
       <c r="V162" s="1">
-        <v>46266.25239591435</v>
+        <v>46266.25258329861</v>
       </c>
       <c r="W162">
         <v>0</v>
       </c>
       <c r="X162" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y162" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AB162">
         <v>0</v>
@@ -13385,33 +13391,33 @@
         <v>156</v>
       </c>
       <c r="AH162" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI162" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:35">
       <c r="A163">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B163" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C163" t="s">
         <v>50</v>
       </c>
       <c r="D163" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E163" t="s">
         <v>54</v>
       </c>
       <c r="F163" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G163">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -13420,10 +13426,10 @@
         <v>64</v>
       </c>
       <c r="J163" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N163" s="1">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="P163">
         <v>8</v>
@@ -13432,7 +13438,7 @@
         <v>2026</v>
       </c>
       <c r="R163">
-        <v>18164501</v>
+        <v>17398883</v>
       </c>
       <c r="S163" t="s">
         <v>156</v>
@@ -13441,16 +13447,16 @@
         <v>167</v>
       </c>
       <c r="V163" s="1">
-        <v>46266.25258329861</v>
+        <v>46266.25305</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="X163" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Y163" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AB163">
         <v>0</v>
@@ -13459,24 +13465,24 @@
         <v>156</v>
       </c>
       <c r="AH163" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI163" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:35">
       <c r="A164">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B164" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C164" t="s">
         <v>50</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E164" t="s">
         <v>54</v>
@@ -13506,7 +13512,7 @@
         <v>2026</v>
       </c>
       <c r="R164">
-        <v>17398883</v>
+        <v>16962107</v>
       </c>
       <c r="S164" t="s">
         <v>156</v>
@@ -13515,16 +13521,16 @@
         <v>167</v>
       </c>
       <c r="V164" s="1">
-        <v>46266.25305</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="W164">
         <v>-15</v>
       </c>
       <c r="X164" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y164" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AB164">
         <v>0</v>
@@ -13533,27 +13539,27 @@
         <v>156</v>
       </c>
       <c r="AH164" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI164" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:35">
       <c r="A165">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B165" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C165" t="s">
         <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E165" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F165" t="s">
         <v>56</v>
@@ -13580,7 +13586,7 @@
         <v>2026</v>
       </c>
       <c r="R165">
-        <v>16962107</v>
+        <v>17042317</v>
       </c>
       <c r="S165" t="s">
         <v>156</v>
@@ -13589,16 +13595,16 @@
         <v>167</v>
       </c>
       <c r="V165" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="W165">
         <v>-15</v>
       </c>
       <c r="X165" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="Y165" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AB165">
         <v>0</v>
@@ -13607,27 +13613,27 @@
         <v>156</v>
       </c>
       <c r="AH165" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI165" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:35">
       <c r="A166">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B166" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C166" t="s">
         <v>50</v>
       </c>
       <c r="D166" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E166" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F166" t="s">
         <v>56</v>
@@ -13654,7 +13660,7 @@
         <v>2026</v>
       </c>
       <c r="R166">
-        <v>17042317</v>
+        <v>17941166</v>
       </c>
       <c r="S166" t="s">
         <v>156</v>
@@ -13663,16 +13669,16 @@
         <v>167</v>
       </c>
       <c r="V166" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="W166">
         <v>-15</v>
       </c>
       <c r="X166" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="Y166" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AB166">
         <v>0</v>
@@ -13681,30 +13687,30 @@
         <v>156</v>
       </c>
       <c r="AH166" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI166" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:35">
       <c r="A167">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B167" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C167" t="s">
         <v>50</v>
       </c>
       <c r="D167" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E167" t="s">
         <v>54</v>
       </c>
       <c r="F167" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G167">
         <v>953</v>
@@ -13728,7 +13734,7 @@
         <v>2026</v>
       </c>
       <c r="R167">
-        <v>17941166</v>
+        <v>18178144</v>
       </c>
       <c r="S167" t="s">
         <v>156</v>
@@ -13737,16 +13743,16 @@
         <v>167</v>
       </c>
       <c r="V167" s="1">
-        <v>46266.25364633102</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="W167">
         <v>-15</v>
       </c>
       <c r="X167" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Y167" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AB167">
         <v>0</v>
@@ -13755,18 +13761,18 @@
         <v>156</v>
       </c>
       <c r="AH167" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI167" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:35">
       <c r="A168">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B168" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C168" t="s">
         <v>50</v>
@@ -13778,10 +13784,10 @@
         <v>54</v>
       </c>
       <c r="F168" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G168">
-        <v>953</v>
+        <v>7022</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -13790,10 +13796,10 @@
         <v>64</v>
       </c>
       <c r="J168" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N168" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="P168">
         <v>8</v>
@@ -13802,7 +13808,7 @@
         <v>2026</v>
       </c>
       <c r="R168">
-        <v>18178144</v>
+        <v>17399270</v>
       </c>
       <c r="S168" t="s">
         <v>156</v>
@@ -13811,16 +13817,16 @@
         <v>167</v>
       </c>
       <c r="V168" s="1">
-        <v>46266.25369826389</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="W168">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="X168" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Y168" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB168">
         <v>0</v>
@@ -13829,18 +13835,18 @@
         <v>156</v>
       </c>
       <c r="AH168" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI168" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:35">
       <c r="A169">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B169" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C169" t="s">
         <v>50</v>
@@ -13849,7 +13855,7 @@
         <v>51</v>
       </c>
       <c r="E169" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F169" t="s">
         <v>56</v>
@@ -13876,7 +13882,7 @@
         <v>2026</v>
       </c>
       <c r="R169">
-        <v>17399270</v>
+        <v>17042505</v>
       </c>
       <c r="S169" t="s">
         <v>156</v>
@@ -13885,16 +13891,16 @@
         <v>167</v>
       </c>
       <c r="V169" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="W169">
         <v>-8</v>
       </c>
       <c r="X169" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Y169" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AB169">
         <v>0</v>
@@ -13903,18 +13909,18 @@
         <v>156</v>
       </c>
       <c r="AH169" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI169" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:35">
       <c r="A170">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B170" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C170" t="s">
         <v>50</v>
@@ -13923,7 +13929,7 @@
         <v>51</v>
       </c>
       <c r="E170" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F170" t="s">
         <v>56</v>
@@ -13950,7 +13956,7 @@
         <v>2026</v>
       </c>
       <c r="R170">
-        <v>17042505</v>
+        <v>17952421</v>
       </c>
       <c r="S170" t="s">
         <v>156</v>
@@ -13959,16 +13965,16 @@
         <v>167</v>
       </c>
       <c r="V170" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="W170">
         <v>-8</v>
       </c>
       <c r="X170" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Y170" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AB170">
         <v>0</v>
@@ -13977,18 +13983,18 @@
         <v>156</v>
       </c>
       <c r="AH170" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI170" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:35">
       <c r="A171">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B171" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C171" t="s">
         <v>50</v>
@@ -14000,7 +14006,7 @@
         <v>54</v>
       </c>
       <c r="F171" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G171">
         <v>7022</v>
@@ -14024,7 +14030,7 @@
         <v>2026</v>
       </c>
       <c r="R171">
-        <v>17952421</v>
+        <v>18178174</v>
       </c>
       <c r="S171" t="s">
         <v>156</v>
@@ -14033,16 +14039,16 @@
         <v>167</v>
       </c>
       <c r="V171" s="1">
-        <v>46266.25364869213</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="W171">
         <v>-8</v>
       </c>
       <c r="X171" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Y171" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB171">
         <v>0</v>
@@ -14051,18 +14057,18 @@
         <v>156</v>
       </c>
       <c r="AH171" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI171" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:35">
       <c r="A172">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B172" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C172" t="s">
         <v>50</v>
@@ -14074,10 +14080,10 @@
         <v>54</v>
       </c>
       <c r="F172" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G172">
-        <v>7022</v>
+        <v>9085</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -14086,37 +14092,40 @@
         <v>64</v>
       </c>
       <c r="J172" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N172" s="1">
-        <v>46283</v>
+        <v>46268</v>
+      </c>
+      <c r="O172" t="s">
+        <v>128</v>
       </c>
       <c r="P172">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q172">
         <v>2026</v>
       </c>
       <c r="R172">
-        <v>18178174</v>
+        <v>17399353</v>
       </c>
       <c r="S172" t="s">
         <v>156</v>
       </c>
       <c r="U172" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V172" s="1">
-        <v>46266.25369988426</v>
+        <v>46268.62318445602</v>
       </c>
       <c r="W172">
-        <v>-8</v>
+        <v>7</v>
       </c>
       <c r="X172" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Y172" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AB172">
         <v>0</v>
@@ -14125,24 +14134,24 @@
         <v>156</v>
       </c>
       <c r="AH172" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AI172" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:35">
       <c r="A173">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B173" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C173" t="s">
         <v>50</v>
       </c>
       <c r="D173" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E173" t="s">
         <v>54</v>
@@ -14175,7 +14184,7 @@
         <v>2026</v>
       </c>
       <c r="R173">
-        <v>17399353</v>
+        <v>16962370</v>
       </c>
       <c r="S173" t="s">
         <v>156</v>
@@ -14184,16 +14193,16 @@
         <v>168</v>
       </c>
       <c r="V173" s="1">
-        <v>46268.62318445602</v>
+        <v>46268.62319864584</v>
       </c>
       <c r="W173">
         <v>7</v>
       </c>
       <c r="X173" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y173" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AB173">
         <v>0</v>
@@ -14202,24 +14211,24 @@
         <v>156</v>
       </c>
       <c r="AH173" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI173" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="174" spans="1:35">
       <c r="A174">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B174" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C174" t="s">
         <v>50</v>
       </c>
       <c r="D174" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E174" t="s">
         <v>54</v>
@@ -14252,7 +14261,7 @@
         <v>2026</v>
       </c>
       <c r="R174">
-        <v>16962370</v>
+        <v>16976260</v>
       </c>
       <c r="S174" t="s">
         <v>156</v>
@@ -14261,13 +14270,13 @@
         <v>168</v>
       </c>
       <c r="V174" s="1">
-        <v>46268.62319864584</v>
+        <v>46268.62320026621</v>
       </c>
       <c r="W174">
         <v>7</v>
       </c>
       <c r="X174" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Y174" t="s">
         <v>237</v>
@@ -14279,18 +14288,18 @@
         <v>156</v>
       </c>
       <c r="AH174" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI174" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="175" spans="1:35">
       <c r="A175">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B175" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C175" t="s">
         <v>50</v>
@@ -14329,7 +14338,7 @@
         <v>2026</v>
       </c>
       <c r="R175">
-        <v>16976260</v>
+        <v>17222852</v>
       </c>
       <c r="S175" t="s">
         <v>156</v>
@@ -14338,13 +14347,13 @@
         <v>168</v>
       </c>
       <c r="V175" s="1">
-        <v>46268.62320026621</v>
+        <v>46268.62320177083</v>
       </c>
       <c r="W175">
         <v>7</v>
       </c>
       <c r="X175" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y175" t="s">
         <v>237</v>
@@ -14356,18 +14365,18 @@
         <v>156</v>
       </c>
       <c r="AH175" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI175" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="176" spans="1:35">
       <c r="A176">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B176" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C176" t="s">
         <v>50</v>
@@ -14376,7 +14385,7 @@
         <v>51</v>
       </c>
       <c r="E176" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F176" t="s">
         <v>56</v>
@@ -14406,7 +14415,7 @@
         <v>2026</v>
       </c>
       <c r="R176">
-        <v>17222852</v>
+        <v>17042569</v>
       </c>
       <c r="S176" t="s">
         <v>156</v>
@@ -14415,13 +14424,13 @@
         <v>168</v>
       </c>
       <c r="V176" s="1">
-        <v>46268.62320177083</v>
+        <v>46268.62320378472</v>
       </c>
       <c r="W176">
         <v>7</v>
       </c>
       <c r="X176" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y176" t="s">
         <v>237</v>
@@ -14433,24 +14442,24 @@
         <v>156</v>
       </c>
       <c r="AH176" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI176" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:35">
       <c r="A177">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B177" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C177" t="s">
         <v>50</v>
       </c>
       <c r="D177" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E177" t="s">
         <v>55</v>
@@ -14483,7 +14492,7 @@
         <v>2026</v>
       </c>
       <c r="R177">
-        <v>17042569</v>
+        <v>16960062</v>
       </c>
       <c r="S177" t="s">
         <v>156</v>
@@ -14492,7 +14501,7 @@
         <v>168</v>
       </c>
       <c r="V177" s="1">
-        <v>46268.62320378472</v>
+        <v>46268.62320393518</v>
       </c>
       <c r="W177">
         <v>7</v>
@@ -14510,27 +14519,27 @@
         <v>156</v>
       </c>
       <c r="AH177" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI177" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178" spans="1:35">
       <c r="A178">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B178" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C178" t="s">
         <v>50</v>
       </c>
       <c r="D178" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E178" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F178" t="s">
         <v>56</v>
@@ -14560,7 +14569,7 @@
         <v>2026</v>
       </c>
       <c r="R178">
-        <v>16960062</v>
+        <v>17941207</v>
       </c>
       <c r="S178" t="s">
         <v>156</v>
@@ -14569,13 +14578,13 @@
         <v>168</v>
       </c>
       <c r="V178" s="1">
-        <v>46268.62320393518</v>
+        <v>46268.62320697917</v>
       </c>
       <c r="W178">
         <v>7</v>
       </c>
       <c r="X178" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="Y178" t="s">
         <v>237</v>
@@ -14587,24 +14596,24 @@
         <v>156</v>
       </c>
       <c r="AH178" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI178" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="179" spans="1:35">
       <c r="A179">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B179" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C179" t="s">
         <v>50</v>
       </c>
       <c r="D179" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E179" t="s">
         <v>54</v>
@@ -14637,7 +14646,7 @@
         <v>2026</v>
       </c>
       <c r="R179">
-        <v>17941207</v>
+        <v>17952433</v>
       </c>
       <c r="S179" t="s">
         <v>156</v>
@@ -14646,13 +14655,13 @@
         <v>168</v>
       </c>
       <c r="V179" s="1">
-        <v>46268.62320697917</v>
+        <v>46268.62320717592</v>
       </c>
       <c r="W179">
         <v>7</v>
       </c>
       <c r="X179" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Y179" t="s">
         <v>237</v>
@@ -14664,24 +14673,24 @@
         <v>156</v>
       </c>
       <c r="AH179" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI179" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="180" spans="1:35">
       <c r="A180">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C180" t="s">
         <v>50</v>
       </c>
       <c r="D180" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E180" t="s">
         <v>54</v>
@@ -14714,7 +14723,7 @@
         <v>2026</v>
       </c>
       <c r="R180">
-        <v>17952433</v>
+        <v>17952613</v>
       </c>
       <c r="S180" t="s">
         <v>156</v>
@@ -14723,7 +14732,7 @@
         <v>168</v>
       </c>
       <c r="V180" s="1">
-        <v>46268.62320717592</v>
+        <v>46268.62320732639</v>
       </c>
       <c r="W180">
         <v>7</v>
@@ -14741,18 +14750,18 @@
         <v>156</v>
       </c>
       <c r="AH180" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI180" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="181" spans="1:35">
       <c r="A181">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B181" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C181" t="s">
         <v>50</v>
@@ -14791,7 +14800,7 @@
         <v>2026</v>
       </c>
       <c r="R181">
-        <v>17952613</v>
+        <v>18056791</v>
       </c>
       <c r="S181" t="s">
         <v>156</v>
@@ -14800,7 +14809,7 @@
         <v>168</v>
       </c>
       <c r="V181" s="1">
-        <v>46268.62320732639</v>
+        <v>46268.62320810185</v>
       </c>
       <c r="W181">
         <v>7</v>
@@ -14818,18 +14827,18 @@
         <v>156</v>
       </c>
       <c r="AH181" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI181" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="182" spans="1:35">
       <c r="A182">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C182" t="s">
         <v>50</v>
@@ -14841,7 +14850,7 @@
         <v>54</v>
       </c>
       <c r="F182" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G182">
         <v>9085</v>
@@ -14868,7 +14877,7 @@
         <v>2026</v>
       </c>
       <c r="R182">
-        <v>18056791</v>
+        <v>18164544</v>
       </c>
       <c r="S182" t="s">
         <v>156</v>
@@ -14877,13 +14886,13 @@
         <v>168</v>
       </c>
       <c r="V182" s="1">
-        <v>46268.62320810185</v>
+        <v>46268.6232125</v>
       </c>
       <c r="W182">
         <v>7</v>
       </c>
       <c r="X182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y182" t="s">
         <v>237</v>
@@ -14895,24 +14904,24 @@
         <v>156</v>
       </c>
       <c r="AH182" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI182" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="183" spans="1:35">
       <c r="A183">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B183" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C183" t="s">
         <v>50</v>
       </c>
       <c r="D183" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E183" t="s">
         <v>54</v>
@@ -14945,7 +14954,7 @@
         <v>2026</v>
       </c>
       <c r="R183">
-        <v>18164544</v>
+        <v>18178181</v>
       </c>
       <c r="S183" t="s">
         <v>156</v>
@@ -14954,13 +14963,13 @@
         <v>168</v>
       </c>
       <c r="V183" s="1">
-        <v>46268.6232125</v>
+        <v>46268.62321412037</v>
       </c>
       <c r="W183">
         <v>7</v>
       </c>
       <c r="X183" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y183" t="s">
         <v>237</v>
@@ -14972,24 +14981,24 @@
         <v>156</v>
       </c>
       <c r="AH183" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI183" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="184" spans="1:35">
       <c r="A184">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B184" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C184" t="s">
         <v>50</v>
       </c>
       <c r="D184" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E184" t="s">
         <v>54</v>
@@ -15022,7 +15031,7 @@
         <v>2026</v>
       </c>
       <c r="R184">
-        <v>18178181</v>
+        <v>18188767</v>
       </c>
       <c r="S184" t="s">
         <v>156</v>
@@ -15031,13 +15040,13 @@
         <v>168</v>
       </c>
       <c r="V184" s="1">
-        <v>46268.62321412037</v>
+        <v>46268.6232128125</v>
       </c>
       <c r="W184">
         <v>7</v>
       </c>
       <c r="X184" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Y184" t="s">
         <v>237</v>
@@ -15049,18 +15058,18 @@
         <v>156</v>
       </c>
       <c r="AH184" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI184" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="185" spans="1:35">
       <c r="A185">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
@@ -15099,7 +15108,7 @@
         <v>2026</v>
       </c>
       <c r="R185">
-        <v>18188767</v>
+        <v>18188673</v>
       </c>
       <c r="S185" t="s">
         <v>156</v>
@@ -15108,7 +15117,7 @@
         <v>168</v>
       </c>
       <c r="V185" s="1">
-        <v>46268.6232128125</v>
+        <v>46268.62321296296</v>
       </c>
       <c r="W185">
         <v>7</v>
@@ -15126,33 +15135,33 @@
         <v>156</v>
       </c>
       <c r="AH185" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI185" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" spans="1:35">
       <c r="A186">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C186" t="s">
         <v>50</v>
       </c>
       <c r="D186" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E186" t="s">
         <v>54</v>
       </c>
       <c r="F186" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G186">
-        <v>9085</v>
+        <v>5989</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -15161,13 +15170,10 @@
         <v>64</v>
       </c>
       <c r="J186" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N186" s="1">
-        <v>46268</v>
-      </c>
-      <c r="O186" t="s">
-        <v>128</v>
+        <v>46273</v>
       </c>
       <c r="P186">
         <v>9</v>
@@ -15176,25 +15182,22 @@
         <v>2026</v>
       </c>
       <c r="R186">
-        <v>18188673</v>
+        <v>17399127</v>
       </c>
       <c r="S186" t="s">
         <v>156</v>
       </c>
       <c r="U186" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V186" s="1">
-        <v>46268.62321296296</v>
+        <v>46269.41908927084</v>
       </c>
       <c r="W186">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X186" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y186" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="AB186">
         <v>0</v>
@@ -15203,24 +15206,24 @@
         <v>156</v>
       </c>
       <c r="AH186" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI186" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="187" spans="1:35">
       <c r="A187">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C187" t="s">
         <v>50</v>
       </c>
       <c r="D187" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E187" t="s">
         <v>54</v>
@@ -15250,7 +15253,7 @@
         <v>2026</v>
       </c>
       <c r="R187">
-        <v>17399127</v>
+        <v>16962251</v>
       </c>
       <c r="S187" t="s">
         <v>156</v>
@@ -15259,13 +15262,13 @@
         <v>167</v>
       </c>
       <c r="V187" s="1">
-        <v>46269.41908927084</v>
+        <v>46269.41910457176</v>
       </c>
       <c r="W187">
         <v>2</v>
       </c>
       <c r="X187" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AB187">
         <v>0</v>
@@ -15274,24 +15277,24 @@
         <v>156</v>
       </c>
       <c r="AH187" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI187" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="188" spans="1:35">
       <c r="A188">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B188" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C188" t="s">
         <v>50</v>
       </c>
       <c r="D188" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E188" t="s">
         <v>54</v>
@@ -15321,7 +15324,7 @@
         <v>2026</v>
       </c>
       <c r="R188">
-        <v>16962251</v>
+        <v>16976117</v>
       </c>
       <c r="S188" t="s">
         <v>156</v>
@@ -15330,13 +15333,13 @@
         <v>167</v>
       </c>
       <c r="V188" s="1">
-        <v>46269.41910457176</v>
+        <v>46269.37885223379</v>
       </c>
       <c r="W188">
         <v>2</v>
       </c>
       <c r="X188" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB188">
         <v>0</v>
@@ -15345,18 +15348,18 @@
         <v>156</v>
       </c>
       <c r="AH188" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI188" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="1:35">
       <c r="A189">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B189" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C189" t="s">
         <v>50</v>
@@ -15392,7 +15395,7 @@
         <v>2026</v>
       </c>
       <c r="R189">
-        <v>16976117</v>
+        <v>17222714</v>
       </c>
       <c r="S189" t="s">
         <v>156</v>
@@ -15401,13 +15404,13 @@
         <v>167</v>
       </c>
       <c r="V189" s="1">
-        <v>46269.37885223379</v>
+        <v>46269.3782503125</v>
       </c>
       <c r="W189">
         <v>2</v>
       </c>
       <c r="X189" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AB189">
         <v>0</v>
@@ -15416,18 +15419,18 @@
         <v>156</v>
       </c>
       <c r="AH189" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI189" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:35">
       <c r="A190">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B190" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C190" t="s">
         <v>50</v>
@@ -15436,7 +15439,7 @@
         <v>51</v>
       </c>
       <c r="E190" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F190" t="s">
         <v>56</v>
@@ -15463,7 +15466,7 @@
         <v>2026</v>
       </c>
       <c r="R190">
-        <v>17222714</v>
+        <v>17042423</v>
       </c>
       <c r="S190" t="s">
         <v>156</v>
@@ -15472,13 +15475,13 @@
         <v>167</v>
       </c>
       <c r="V190" s="1">
-        <v>46269.3782503125</v>
+        <v>46269.41913152778</v>
       </c>
       <c r="W190">
         <v>2</v>
       </c>
       <c r="X190" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB190">
         <v>0</v>
@@ -15487,24 +15490,24 @@
         <v>156</v>
       </c>
       <c r="AH190" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI190" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:35">
       <c r="A191">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B191" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C191" t="s">
         <v>50</v>
       </c>
       <c r="D191" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E191" t="s">
         <v>55</v>
@@ -15534,7 +15537,7 @@
         <v>2026</v>
       </c>
       <c r="R191">
-        <v>17042423</v>
+        <v>16959989</v>
       </c>
       <c r="S191" t="s">
         <v>156</v>
@@ -15543,7 +15546,7 @@
         <v>167</v>
       </c>
       <c r="V191" s="1">
-        <v>46269.41913152778</v>
+        <v>46269.41913775463</v>
       </c>
       <c r="W191">
         <v>2</v>
@@ -15558,45 +15561,45 @@
         <v>156</v>
       </c>
       <c r="AH191" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI191" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:35">
       <c r="A192">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B192" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C192" t="s">
         <v>50</v>
       </c>
       <c r="D192" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E192" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F192" t="s">
         <v>56</v>
       </c>
       <c r="G192">
-        <v>5989</v>
+        <v>9087</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J192" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N192" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="P192">
         <v>9</v>
@@ -15605,48 +15608,48 @@
         <v>2026</v>
       </c>
       <c r="R192">
-        <v>16959989</v>
+        <v>17399373</v>
       </c>
       <c r="S192" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="U192" t="s">
         <v>167</v>
       </c>
       <c r="V192" s="1">
-        <v>46269.41913775463</v>
+        <v>46268.7596207176</v>
       </c>
       <c r="W192">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X192" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AB192">
         <v>0</v>
       </c>
       <c r="AC192" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI192" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="1:35">
       <c r="A193">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B193" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E193" t="s">
         <v>54</v>
@@ -15676,7 +15679,7 @@
         <v>2026</v>
       </c>
       <c r="R193">
-        <v>17399373</v>
+        <v>16962390</v>
       </c>
       <c r="S193" t="s">
         <v>54</v>
@@ -15685,13 +15688,13 @@
         <v>167</v>
       </c>
       <c r="V193" s="1">
-        <v>46268.7596207176</v>
+        <v>46268.75963109954</v>
       </c>
       <c r="W193">
         <v>6</v>
       </c>
       <c r="X193" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AB193">
         <v>0</v>
@@ -15700,24 +15703,24 @@
         <v>54</v>
       </c>
       <c r="AH193" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI193" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="194" spans="1:35">
       <c r="A194">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B194" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C194" t="s">
         <v>50</v>
       </c>
       <c r="D194" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E194" t="s">
         <v>54</v>
@@ -15747,7 +15750,7 @@
         <v>2026</v>
       </c>
       <c r="R194">
-        <v>16962390</v>
+        <v>16976280</v>
       </c>
       <c r="S194" t="s">
         <v>54</v>
@@ -15756,13 +15759,13 @@
         <v>167</v>
       </c>
       <c r="V194" s="1">
-        <v>46268.75963109954</v>
+        <v>46268.75963225694</v>
       </c>
       <c r="W194">
         <v>6</v>
       </c>
       <c r="X194" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB194">
         <v>0</v>
@@ -15771,18 +15774,18 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI194" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="195" spans="1:35">
       <c r="A195">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C195" t="s">
         <v>50</v>
@@ -15818,7 +15821,7 @@
         <v>2026</v>
       </c>
       <c r="R195">
-        <v>16976280</v>
+        <v>17222885</v>
       </c>
       <c r="S195" t="s">
         <v>54</v>
@@ -15827,13 +15830,13 @@
         <v>167</v>
       </c>
       <c r="V195" s="1">
-        <v>46268.75963225694</v>
+        <v>46268.75963348379</v>
       </c>
       <c r="W195">
         <v>6</v>
       </c>
       <c r="X195" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AB195">
         <v>0</v>
@@ -15842,18 +15845,18 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI195" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="196" spans="1:35">
       <c r="A196">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B196" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C196" t="s">
         <v>50</v>
@@ -15862,7 +15865,7 @@
         <v>51</v>
       </c>
       <c r="E196" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F196" t="s">
         <v>56</v>
@@ -15889,48 +15892,48 @@
         <v>2026</v>
       </c>
       <c r="R196">
-        <v>17222885</v>
+        <v>17042605</v>
       </c>
       <c r="S196" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="U196" t="s">
         <v>167</v>
       </c>
       <c r="V196" s="1">
-        <v>46268.75963348379</v>
+        <v>46268.75963414352</v>
       </c>
       <c r="W196">
         <v>6</v>
       </c>
       <c r="X196" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB196">
         <v>0</v>
       </c>
       <c r="AC196" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="AH196" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI196" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:35">
       <c r="A197">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B197" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C197" t="s">
         <v>50</v>
       </c>
       <c r="D197" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E197" t="s">
         <v>55</v>
@@ -15960,16 +15963,16 @@
         <v>2026</v>
       </c>
       <c r="R197">
-        <v>17042605</v>
+        <v>16960086</v>
       </c>
       <c r="S197" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="U197" t="s">
         <v>167</v>
       </c>
       <c r="V197" s="1">
-        <v>46268.75963414352</v>
+        <v>46268.62326365741</v>
       </c>
       <c r="W197">
         <v>6</v>
@@ -15981,30 +15984,30 @@
         <v>0</v>
       </c>
       <c r="AC197" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="AH197" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI197" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="198" spans="1:35">
       <c r="A198">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C198" t="s">
         <v>50</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E198" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F198" t="s">
         <v>56</v>
@@ -16031,48 +16034,48 @@
         <v>2026</v>
       </c>
       <c r="R198">
-        <v>16960086</v>
+        <v>17941227</v>
       </c>
       <c r="S198" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U198" t="s">
         <v>167</v>
       </c>
       <c r="V198" s="1">
-        <v>46268.62326365741</v>
+        <v>46268.75963472222</v>
       </c>
       <c r="W198">
         <v>6</v>
       </c>
       <c r="X198" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="AB198">
         <v>0</v>
       </c>
       <c r="AC198" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH198" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI198" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="199" spans="1:35">
       <c r="A199">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B199" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C199" t="s">
         <v>50</v>
       </c>
       <c r="D199" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E199" t="s">
         <v>54</v>
@@ -16102,7 +16105,7 @@
         <v>2026</v>
       </c>
       <c r="R199">
-        <v>17941227</v>
+        <v>17952455</v>
       </c>
       <c r="S199" t="s">
         <v>54</v>
@@ -16111,13 +16114,13 @@
         <v>167</v>
       </c>
       <c r="V199" s="1">
-        <v>46268.75963472222</v>
+        <v>46268.75963475694</v>
       </c>
       <c r="W199">
         <v>6</v>
       </c>
       <c r="X199" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AB199">
         <v>0</v>
@@ -16126,24 +16129,24 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI199" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="200" spans="1:35">
       <c r="A200">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C200" t="s">
         <v>50</v>
       </c>
       <c r="D200" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E200" t="s">
         <v>54</v>
@@ -16173,7 +16176,7 @@
         <v>2026</v>
       </c>
       <c r="R200">
-        <v>17952455</v>
+        <v>17952635</v>
       </c>
       <c r="S200" t="s">
         <v>54</v>
@@ -16182,7 +16185,7 @@
         <v>167</v>
       </c>
       <c r="V200" s="1">
-        <v>46268.75963475694</v>
+        <v>46268.75963506944</v>
       </c>
       <c r="W200">
         <v>6</v>
@@ -16197,18 +16200,18 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI200" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201" spans="1:35">
       <c r="A201">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B201" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
@@ -16244,16 +16247,16 @@
         <v>2026</v>
       </c>
       <c r="R201">
-        <v>17952635</v>
+        <v>18056811</v>
       </c>
       <c r="S201" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="U201" t="s">
         <v>167</v>
       </c>
       <c r="V201" s="1">
-        <v>46268.75963506944</v>
+        <v>46268.7596360301</v>
       </c>
       <c r="W201">
         <v>6</v>
@@ -16265,21 +16268,21 @@
         <v>0</v>
       </c>
       <c r="AC201" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="AH201" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI201" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="202" spans="1:35">
       <c r="A202">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C202" t="s">
         <v>50</v>
@@ -16291,7 +16294,7 @@
         <v>54</v>
       </c>
       <c r="F202" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G202">
         <v>9087</v>
@@ -16315,48 +16318,48 @@
         <v>2026</v>
       </c>
       <c r="R202">
-        <v>18056811</v>
+        <v>18164558</v>
       </c>
       <c r="S202" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="U202" t="s">
         <v>167</v>
       </c>
       <c r="V202" s="1">
-        <v>46268.7596360301</v>
+        <v>46268.62327121528</v>
       </c>
       <c r="W202">
         <v>6</v>
       </c>
       <c r="X202" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AB202">
         <v>0</v>
       </c>
       <c r="AC202" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI202" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="203" spans="1:35">
       <c r="A203">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B203" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C203" t="s">
         <v>50</v>
       </c>
       <c r="D203" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E203" t="s">
         <v>54</v>
@@ -16386,48 +16389,48 @@
         <v>2026</v>
       </c>
       <c r="R203">
-        <v>18164558</v>
+        <v>18178193</v>
       </c>
       <c r="S203" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="U203" t="s">
         <v>167</v>
       </c>
       <c r="V203" s="1">
-        <v>46268.62327121528</v>
+        <v>46268.75963931713</v>
       </c>
       <c r="W203">
         <v>6</v>
       </c>
       <c r="X203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB203">
         <v>0</v>
       </c>
       <c r="AC203" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="AH203" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI203" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="204" spans="1:35">
       <c r="A204">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B204" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C204" t="s">
         <v>50</v>
       </c>
       <c r="D204" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E204" t="s">
         <v>54</v>
@@ -16457,42 +16460,42 @@
         <v>2026</v>
       </c>
       <c r="R204">
-        <v>18178193</v>
+        <v>18188781</v>
       </c>
       <c r="S204" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="U204" t="s">
         <v>167</v>
       </c>
       <c r="V204" s="1">
-        <v>46268.75963931713</v>
+        <v>46268.75963822917</v>
       </c>
       <c r="W204">
         <v>6</v>
       </c>
       <c r="X204" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AB204">
         <v>0</v>
       </c>
       <c r="AC204" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI204" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="205" spans="1:35">
       <c r="A205">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B205" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C205" t="s">
         <v>50</v>
@@ -16528,7 +16531,7 @@
         <v>2026</v>
       </c>
       <c r="R205">
-        <v>18188781</v>
+        <v>18188687</v>
       </c>
       <c r="S205" t="s">
         <v>54</v>
@@ -16537,7 +16540,7 @@
         <v>167</v>
       </c>
       <c r="V205" s="1">
-        <v>46268.75963822917</v>
+        <v>46268.75963857639</v>
       </c>
       <c r="W205">
         <v>6</v>
@@ -16552,33 +16555,33 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI205" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="206" spans="1:35">
       <c r="A206">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B206" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C206" t="s">
         <v>50</v>
       </c>
       <c r="D206" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E206" t="s">
         <v>54</v>
       </c>
       <c r="F206" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G206">
-        <v>9087</v>
+        <v>6215</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -16587,10 +16590,10 @@
         <v>65</v>
       </c>
       <c r="J206" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N206" s="1">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="P206">
         <v>9</v>
@@ -16599,7 +16602,7 @@
         <v>2026</v>
       </c>
       <c r="R206">
-        <v>18188687</v>
+        <v>17399147</v>
       </c>
       <c r="S206" t="s">
         <v>54</v>
@@ -16608,13 +16611,13 @@
         <v>167</v>
       </c>
       <c r="V206" s="1">
-        <v>46268.75963857639</v>
+        <v>46269.41908901621</v>
       </c>
       <c r="W206">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X206" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AB206">
         <v>0</v>
@@ -16623,24 +16626,24 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI206" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="207" spans="1:35">
       <c r="A207">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B207" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C207" t="s">
         <v>50</v>
       </c>
       <c r="D207" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E207" t="s">
         <v>54</v>
@@ -16670,7 +16673,7 @@
         <v>2026</v>
       </c>
       <c r="R207">
-        <v>17399147</v>
+        <v>16962265</v>
       </c>
       <c r="S207" t="s">
         <v>54</v>
@@ -16679,13 +16682,13 @@
         <v>167</v>
       </c>
       <c r="V207" s="1">
-        <v>46269.41908901621</v>
+        <v>46269.41910425926</v>
       </c>
       <c r="W207">
         <v>1</v>
       </c>
       <c r="X207" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AB207">
         <v>0</v>
@@ -16694,24 +16697,24 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI207" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="208" spans="1:35">
       <c r="A208">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B208" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C208" t="s">
         <v>50</v>
       </c>
       <c r="D208" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E208" t="s">
         <v>54</v>
@@ -16741,7 +16744,7 @@
         <v>2026</v>
       </c>
       <c r="R208">
-        <v>16962265</v>
+        <v>16976127</v>
       </c>
       <c r="S208" t="s">
         <v>54</v>
@@ -16750,13 +16753,13 @@
         <v>167</v>
       </c>
       <c r="V208" s="1">
-        <v>46269.41910425926</v>
+        <v>46269.37890997685</v>
       </c>
       <c r="W208">
         <v>1</v>
       </c>
       <c r="X208" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB208">
         <v>0</v>
@@ -16765,18 +16768,18 @@
         <v>54</v>
       </c>
       <c r="AH208" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI208" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="209" spans="1:35">
       <c r="A209">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C209" t="s">
         <v>50</v>
@@ -16812,7 +16815,7 @@
         <v>2026</v>
       </c>
       <c r="R209">
-        <v>16976127</v>
+        <v>17222729</v>
       </c>
       <c r="S209" t="s">
         <v>54</v>
@@ -16821,13 +16824,13 @@
         <v>167</v>
       </c>
       <c r="V209" s="1">
-        <v>46269.37890997685</v>
+        <v>46269.37833320602</v>
       </c>
       <c r="W209">
         <v>1</v>
       </c>
       <c r="X209" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AB209">
         <v>0</v>
@@ -16836,18 +16839,18 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI209" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="210" spans="1:35">
       <c r="A210">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B210" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C210" t="s">
         <v>50</v>
@@ -16856,7 +16859,7 @@
         <v>51</v>
       </c>
       <c r="E210" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F210" t="s">
         <v>56</v>
@@ -16883,48 +16886,48 @@
         <v>2026</v>
       </c>
       <c r="R210">
-        <v>17222729</v>
+        <v>17042445</v>
       </c>
       <c r="S210" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="U210" t="s">
         <v>167</v>
       </c>
       <c r="V210" s="1">
-        <v>46269.37833320602</v>
+        <v>46269.41913112268</v>
       </c>
       <c r="W210">
         <v>1</v>
       </c>
       <c r="X210" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB210">
         <v>0</v>
       </c>
       <c r="AC210" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="AH210" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI210" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="211" spans="1:35">
       <c r="A211">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B211" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C211" t="s">
         <v>50</v>
       </c>
       <c r="D211" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E211" t="s">
         <v>55</v>
@@ -16954,16 +16957,16 @@
         <v>2026</v>
       </c>
       <c r="R211">
-        <v>17042445</v>
+        <v>16960001</v>
       </c>
       <c r="S211" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="U211" t="s">
         <v>167</v>
       </c>
       <c r="V211" s="1">
-        <v>46269.41913112268</v>
+        <v>46269.41913740741</v>
       </c>
       <c r="W211">
         <v>1</v>
@@ -16975,36 +16978,36 @@
         <v>0</v>
       </c>
       <c r="AC211" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="AH211" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI211" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="212" spans="1:35">
       <c r="A212">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B212" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C212" t="s">
         <v>50</v>
       </c>
       <c r="D212" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E212" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F212" t="s">
         <v>56</v>
       </c>
       <c r="G212">
-        <v>6215</v>
+        <v>11001</v>
       </c>
       <c r="H212">
         <v>0</v>
@@ -17013,46 +17016,49 @@
         <v>65</v>
       </c>
       <c r="J212" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="N212" s="1">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="P212">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q212">
         <v>2026</v>
       </c>
       <c r="R212">
-        <v>16960001</v>
+        <v>16962453</v>
       </c>
       <c r="S212" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U212" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V212" s="1">
-        <v>46269.41913740741</v>
+        <v>46267.66131466435</v>
       </c>
       <c r="W212">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="X212" t="s">
-        <v>170</v>
+        <v>179</v>
+      </c>
+      <c r="Y212" t="s">
+        <v>238</v>
       </c>
       <c r="AB212">
         <v>0</v>
       </c>
       <c r="AC212" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH212" t="s">
         <v>269</v>
       </c>
       <c r="AI212" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17087,34 +17093,34 @@
         <v>74</v>
       </c>
       <c r="N213" s="1">
-        <v>46259</v>
+        <v>46321</v>
       </c>
       <c r="P213">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q213">
         <v>2026</v>
       </c>
       <c r="R213">
-        <v>16962453</v>
+        <v>16962455</v>
       </c>
       <c r="S213" t="s">
         <v>54</v>
       </c>
       <c r="U213" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V213" s="1">
-        <v>46267.66131466435</v>
+        <v>46266.21595836805</v>
       </c>
       <c r="W213">
-        <v>16</v>
+        <v>-46</v>
       </c>
       <c r="X213" t="s">
         <v>179</v>
       </c>
       <c r="Y213" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AB213">
         <v>0</v>
@@ -17123,24 +17129,24 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI213" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:35">
       <c r="A214">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B214" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C214" t="s">
         <v>50</v>
       </c>
       <c r="D214" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E214" t="s">
         <v>54</v>
@@ -17149,7 +17155,7 @@
         <v>56</v>
       </c>
       <c r="G214">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H214">
         <v>0</v>
@@ -17158,7 +17164,7 @@
         <v>65</v>
       </c>
       <c r="J214" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N214" s="1">
         <v>46321</v>
@@ -17170,7 +17176,7 @@
         <v>2026</v>
       </c>
       <c r="R214">
-        <v>16962455</v>
+        <v>17399331</v>
       </c>
       <c r="S214" t="s">
         <v>54</v>
@@ -17179,16 +17185,16 @@
         <v>167</v>
       </c>
       <c r="V214" s="1">
-        <v>46266.21595836805</v>
+        <v>46266.21572962963</v>
       </c>
       <c r="W214">
         <v>-46</v>
       </c>
       <c r="X214" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y214" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AB214">
         <v>0</v>
@@ -17197,18 +17203,18 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI214" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:35">
       <c r="A215">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B215" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C215" t="s">
         <v>50</v>
@@ -17223,7 +17229,7 @@
         <v>56</v>
       </c>
       <c r="G215">
-        <v>7877</v>
+        <v>9774</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -17232,7 +17238,7 @@
         <v>65</v>
       </c>
       <c r="J215" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="N215" s="1">
         <v>46321</v>
@@ -17244,7 +17250,7 @@
         <v>2026</v>
       </c>
       <c r="R215">
-        <v>17399331</v>
+        <v>16976322</v>
       </c>
       <c r="S215" t="s">
         <v>54</v>
@@ -17253,16 +17259,16 @@
         <v>167</v>
       </c>
       <c r="V215" s="1">
-        <v>46266.21572962963</v>
+        <v>46266.21550011574</v>
       </c>
       <c r="W215">
         <v>-46</v>
       </c>
       <c r="X215" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y215" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AB215">
         <v>0</v>
@@ -17271,18 +17277,18 @@
         <v>54</v>
       </c>
       <c r="AH215" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI215" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:35">
       <c r="A216">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C216" t="s">
         <v>50</v>
@@ -17297,7 +17303,7 @@
         <v>56</v>
       </c>
       <c r="G216">
-        <v>9774</v>
+        <v>7027</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -17306,7 +17312,7 @@
         <v>65</v>
       </c>
       <c r="J216" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N216" s="1">
         <v>46321</v>
@@ -17318,7 +17324,7 @@
         <v>2026</v>
       </c>
       <c r="R216">
-        <v>16976322</v>
+        <v>17399291</v>
       </c>
       <c r="S216" t="s">
         <v>54</v>
@@ -17327,16 +17333,13 @@
         <v>167</v>
       </c>
       <c r="V216" s="1">
-        <v>46266.21550011574</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W216">
         <v>-46</v>
       </c>
       <c r="X216" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y216" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="AB216">
         <v>0</v>
@@ -17345,24 +17348,24 @@
         <v>54</v>
       </c>
       <c r="AH216" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI216" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:35">
       <c r="A217">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B217" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C217" t="s">
         <v>50</v>
       </c>
       <c r="D217" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E217" t="s">
         <v>54</v>
@@ -17392,7 +17395,7 @@
         <v>2026</v>
       </c>
       <c r="R217">
-        <v>17399291</v>
+        <v>16962349</v>
       </c>
       <c r="S217" t="s">
         <v>54</v>
@@ -17407,7 +17410,7 @@
         <v>-46</v>
       </c>
       <c r="X217" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AB217">
         <v>0</v>
@@ -17416,24 +17419,24 @@
         <v>54</v>
       </c>
       <c r="AH217" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI217" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="218" spans="1:35">
       <c r="A218">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C218" t="s">
         <v>50</v>
       </c>
       <c r="D218" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E218" t="s">
         <v>54</v>
@@ -17454,43 +17457,40 @@
         <v>123</v>
       </c>
       <c r="N218" s="1">
-        <v>46321</v>
+        <v>46260</v>
       </c>
       <c r="P218">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q218">
         <v>2026</v>
       </c>
       <c r="R218">
-        <v>16962349</v>
-      </c>
-      <c r="S218" t="s">
-        <v>54</v>
+        <v>16976236</v>
       </c>
       <c r="U218" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V218" s="1">
-        <v>46266.00006921296</v>
+        <v>46269.57097615741</v>
       </c>
       <c r="W218">
-        <v>-46</v>
+        <v>15</v>
       </c>
       <c r="X218" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="Y218" t="s">
+        <v>242</v>
       </c>
       <c r="AB218">
         <v>0</v>
       </c>
-      <c r="AC218" t="s">
-        <v>54</v>
-      </c>
       <c r="AH218" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI218" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17525,143 +17525,149 @@
         <v>123</v>
       </c>
       <c r="N219" s="1">
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="P219">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q219">
         <v>2026</v>
       </c>
       <c r="R219">
-        <v>16976236</v>
+        <v>16976238</v>
       </c>
       <c r="U219" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V219" s="1">
-        <v>46269.57097615741</v>
+        <v>46266.00006921296</v>
       </c>
       <c r="W219">
-        <v>15</v>
+        <v>-46</v>
       </c>
       <c r="X219" t="s">
         <v>176</v>
       </c>
-      <c r="Y219" t="s">
-        <v>242</v>
-      </c>
       <c r="AB219">
         <v>0</v>
       </c>
       <c r="AH219" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI219" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:35">
       <c r="A220">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B220" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C220" t="s">
         <v>50</v>
       </c>
       <c r="D220" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E220" t="s">
         <v>54</v>
       </c>
       <c r="F220" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G220">
-        <v>7027</v>
+        <v>11056</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J220" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N220" s="1">
-        <v>46321</v>
+        <v>46269</v>
+      </c>
+      <c r="O220" t="s">
+        <v>129</v>
       </c>
       <c r="P220">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q220">
         <v>2026</v>
       </c>
       <c r="R220">
-        <v>16976238</v>
+        <v>18261776</v>
       </c>
       <c r="U220" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V220" s="1">
-        <v>46266.00006921296</v>
+        <v>46269.46753030093</v>
       </c>
       <c r="W220">
-        <v>-46</v>
+        <v>6</v>
       </c>
       <c r="X220" t="s">
-        <v>176</v>
+        <v>172</v>
+      </c>
+      <c r="Y220" t="s">
+        <v>243</v>
       </c>
       <c r="AB220">
         <v>0</v>
       </c>
+      <c r="AC220" t="s">
+        <v>268</v>
+      </c>
       <c r="AH220" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI220" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:35">
       <c r="A221">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B221" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C221" t="s">
         <v>50</v>
       </c>
       <c r="D221" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E221" t="s">
         <v>54</v>
       </c>
       <c r="F221" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G221">
-        <v>11056</v>
+        <v>9746</v>
       </c>
       <c r="H221">
         <v>0</v>
       </c>
       <c r="I221" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J221" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="N221" s="1">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="O221" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P221">
         <v>8</v>
@@ -17670,42 +17676,45 @@
         <v>2026</v>
       </c>
       <c r="R221">
-        <v>18261776</v>
+        <v>17399403</v>
+      </c>
+      <c r="S221" t="s">
+        <v>146</v>
       </c>
       <c r="U221" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V221" s="1">
-        <v>46269.46753030093</v>
+        <v>46274.60593387731</v>
       </c>
       <c r="W221">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X221" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Y221" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AB221">
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="AH221" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI221" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="222" spans="1:35">
       <c r="A222">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B222" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C222" t="s">
         <v>50</v>
@@ -17735,7 +17744,7 @@
         <v>46275</v>
       </c>
       <c r="O222" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="P222">
         <v>8</v>
@@ -17744,51 +17753,54 @@
         <v>2026</v>
       </c>
       <c r="R222">
-        <v>17399403</v>
+        <v>16976300</v>
       </c>
       <c r="S222" t="s">
-        <v>146</v>
+        <v>143</v>
+      </c>
+      <c r="T222" t="s">
+        <v>162</v>
       </c>
       <c r="U222" t="s">
         <v>167</v>
       </c>
       <c r="V222" s="1">
-        <v>46274.60593387731</v>
+        <v>46274.47210818287</v>
       </c>
       <c r="W222">
         <v>0</v>
       </c>
       <c r="X222" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y222" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AB222">
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AH222" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI222" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B223" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
       </c>
       <c r="D223" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E223" t="s">
         <v>54</v>
@@ -17812,7 +17824,7 @@
         <v>46275</v>
       </c>
       <c r="O223" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P223">
         <v>8</v>
@@ -17821,48 +17833,48 @@
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>16976300</v>
+        <v>18090250</v>
       </c>
       <c r="S223" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="T223" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U223" t="s">
         <v>167</v>
       </c>
       <c r="V223" s="1">
-        <v>46274.47210818287</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W223">
         <v>0</v>
       </c>
       <c r="X223" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Y223" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AB223">
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AH223" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI223" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
@@ -17874,7 +17886,7 @@
         <v>54</v>
       </c>
       <c r="F224" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G224">
         <v>9746</v>
@@ -17901,54 +17913,54 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>18090250</v>
+        <v>18179154</v>
       </c>
       <c r="S224" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="T224" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="U224" t="s">
         <v>167</v>
       </c>
       <c r="V224" s="1">
-        <v>46274.48792050926</v>
+        <v>46274.588374375</v>
       </c>
       <c r="W224">
         <v>0</v>
       </c>
       <c r="X224" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y224" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AB224">
         <v>0</v>
       </c>
       <c r="AC224" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AH224" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI224" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B225" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
       </c>
       <c r="D225" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E225" t="s">
         <v>54</v>
@@ -17971,9 +17983,6 @@
       <c r="N225" s="1">
         <v>46275</v>
       </c>
-      <c r="O225" t="s">
-        <v>131</v>
-      </c>
       <c r="P225">
         <v>8</v>
       </c>
@@ -17981,10 +17990,10 @@
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>18179154</v>
+        <v>18190457</v>
       </c>
       <c r="S225" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T225" t="s">
         <v>163</v>
@@ -17993,36 +18002,33 @@
         <v>167</v>
       </c>
       <c r="V225" s="1">
-        <v>46274.588374375</v>
+        <v>46274.34198912037</v>
       </c>
       <c r="W225">
         <v>0</v>
       </c>
       <c r="X225" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y225" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="AB225">
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AH225" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI225" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
@@ -18031,13 +18037,13 @@
         <v>51</v>
       </c>
       <c r="E226" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F226" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G226">
-        <v>9746</v>
+        <v>6348</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -18046,63 +18052,69 @@
         <v>61</v>
       </c>
       <c r="J226" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N226" s="1">
         <v>46275</v>
       </c>
+      <c r="O226" t="s">
+        <v>131</v>
+      </c>
       <c r="P226">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q226">
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>18190457</v>
+        <v>18261361</v>
       </c>
       <c r="S226" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="T226" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U226" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V226" s="1">
-        <v>46274.34198912037</v>
+        <v>46275.39631951389</v>
       </c>
       <c r="W226">
         <v>0</v>
       </c>
       <c r="X226" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="Y226" t="s">
+        <v>248</v>
       </c>
       <c r="AB226">
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AH226" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AI226" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B227" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
       </c>
       <c r="D227" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E227" t="s">
         <v>55</v>
@@ -18135,7 +18147,7 @@
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18261361</v>
+        <v>18261362</v>
       </c>
       <c r="S227" t="s">
         <v>143</v>
@@ -18147,7 +18159,7 @@
         <v>168</v>
       </c>
       <c r="V227" s="1">
-        <v>46275.39631951389</v>
+        <v>46275.39631994213</v>
       </c>
       <c r="W227">
         <v>0</v>
@@ -18165,24 +18177,24 @@
         <v>143</v>
       </c>
       <c r="AH227" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI227" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B228" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
       </c>
       <c r="D228" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E228" t="s">
         <v>55</v>
@@ -18191,84 +18203,81 @@
         <v>56</v>
       </c>
       <c r="G228">
-        <v>6348</v>
+        <v>1866</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J228" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="N228" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O228" t="s">
-        <v>131</v>
+        <v>46274</v>
       </c>
       <c r="P228">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q228">
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>18261362</v>
+        <v>17968368</v>
       </c>
       <c r="S228" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="T228" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="U228" t="s">
         <v>168</v>
       </c>
       <c r="V228" s="1">
-        <v>46275.39631994213</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X228" t="s">
         <v>170</v>
       </c>
       <c r="Y228" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AB228">
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AH228" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI228" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B229" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E229" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F229" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G229">
         <v>1866</v>
@@ -18292,10 +18301,10 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>17968368</v>
+        <v>18186946</v>
       </c>
       <c r="S229" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T229" t="s">
         <v>151</v>
@@ -18304,36 +18313,36 @@
         <v>168</v>
       </c>
       <c r="V229" s="1">
-        <v>46274.36843923611</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W229">
         <v>1</v>
       </c>
       <c r="X229" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Y229" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AH229" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI229" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B230" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
@@ -18369,7 +18378,7 @@
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>18186946</v>
+        <v>18187212</v>
       </c>
       <c r="S230" t="s">
         <v>154</v>
@@ -18381,7 +18390,7 @@
         <v>168</v>
       </c>
       <c r="V230" s="1">
-        <v>46274.66470667824</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W230">
         <v>1</v>
@@ -18390,7 +18399,7 @@
         <v>173</v>
       </c>
       <c r="Y230" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB230">
         <v>0</v>
@@ -18399,33 +18408,33 @@
         <v>154</v>
       </c>
       <c r="AH230" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI230" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B231" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
       </c>
       <c r="F231" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G231">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -18434,11 +18443,14 @@
         <v>62</v>
       </c>
       <c r="J231" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N231" s="1">
         <v>46274</v>
       </c>
+      <c r="O231" t="s">
+        <v>133</v>
+      </c>
       <c r="P231">
         <v>8</v>
       </c>
@@ -18446,10 +18458,10 @@
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>18187212</v>
+        <v>17988543</v>
       </c>
       <c r="S231" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="T231" t="s">
         <v>151</v>
@@ -18458,36 +18470,36 @@
         <v>168</v>
       </c>
       <c r="V231" s="1">
-        <v>46274.74452168981</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W231">
         <v>1</v>
       </c>
       <c r="X231" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y231" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AB231">
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AH231" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI231" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B232" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
@@ -18496,7 +18508,7 @@
         <v>51</v>
       </c>
       <c r="E232" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F232" t="s">
         <v>56</v>
@@ -18516,9 +18528,6 @@
       <c r="N232" s="1">
         <v>46274</v>
       </c>
-      <c r="O232" t="s">
-        <v>133</v>
-      </c>
       <c r="P232">
         <v>8</v>
       </c>
@@ -18526,10 +18535,10 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>17988543</v>
+        <v>17968379</v>
       </c>
       <c r="S232" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T232" t="s">
         <v>151</v>
@@ -18538,48 +18547,45 @@
         <v>168</v>
       </c>
       <c r="V232" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W232">
         <v>1</v>
       </c>
       <c r="X232" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y232" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="AB232">
         <v>0</v>
       </c>
       <c r="AC232" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AH232" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI232" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B233" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E233" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F233" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G233">
         <v>1867</v>
@@ -18603,10 +18609,10 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>17968379</v>
+        <v>18186953</v>
       </c>
       <c r="S233" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T233" t="s">
         <v>151</v>
@@ -18615,33 +18621,33 @@
         <v>168</v>
       </c>
       <c r="V233" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W233">
         <v>1</v>
       </c>
       <c r="X233" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AB233">
         <v>0</v>
       </c>
       <c r="AC233" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AH233" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI233" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B234" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
@@ -18677,7 +18683,7 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>18186953</v>
+        <v>18187219</v>
       </c>
       <c r="S234" t="s">
         <v>154</v>
@@ -18689,7 +18695,7 @@
         <v>168</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.7274781713</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W234">
         <v>1</v>
@@ -18704,18 +18710,18 @@
         <v>154</v>
       </c>
       <c r="AH234" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI234" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6963</v>
+        <v>6404</v>
       </c>
       <c r="B235" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
@@ -18727,22 +18733,22 @@
         <v>54</v>
       </c>
       <c r="F235" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G235">
-        <v>1867</v>
+        <v>1792</v>
       </c>
       <c r="H235">
         <v>0</v>
       </c>
       <c r="I235" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J235" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N235" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="P235">
         <v>8</v>
@@ -18751,51 +18757,51 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>18187219</v>
+        <v>16962151</v>
       </c>
       <c r="S235" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T235" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="U235" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X235" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AB235">
         <v>0</v>
       </c>
       <c r="AC235" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AH235" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI235" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B236" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
@@ -18825,7 +18831,7 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>16962151</v>
+        <v>18085143</v>
       </c>
       <c r="S236" t="s">
         <v>155</v>
@@ -18834,16 +18840,16 @@
         <v>165</v>
       </c>
       <c r="U236" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.70622837963</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W236">
         <v>0</v>
       </c>
       <c r="X236" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AB236">
         <v>0</v>
@@ -18852,24 +18858,24 @@
         <v>155</v>
       </c>
       <c r="AH236" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI236" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B237" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E237" t="s">
         <v>54</v>
@@ -18878,7 +18884,7 @@
         <v>56</v>
       </c>
       <c r="G237">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -18887,13 +18893,10 @@
         <v>63</v>
       </c>
       <c r="J237" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N237" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O237" t="s">
-        <v>133</v>
+        <v>46275</v>
       </c>
       <c r="P237">
         <v>8</v>
@@ -18902,7 +18905,7 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>17398955</v>
+        <v>17948766</v>
       </c>
       <c r="S237" t="s">
         <v>155</v>
@@ -18911,19 +18914,16 @@
         <v>165</v>
       </c>
       <c r="U237" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W237">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X237" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y237" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="AB237">
         <v>0</v>
@@ -18932,24 +18932,24 @@
         <v>155</v>
       </c>
       <c r="AH237" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AI237" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B238" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
       </c>
       <c r="D238" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
@@ -18982,7 +18982,7 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>18073098</v>
+        <v>17398955</v>
       </c>
       <c r="S238" t="s">
         <v>155</v>
@@ -18994,13 +18994,13 @@
         <v>166</v>
       </c>
       <c r="V238" s="1">
-        <v>46274.74838096065</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W238">
         <v>2</v>
       </c>
       <c r="X238" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y238" t="s">
         <v>253</v>
@@ -19012,24 +19012,24 @@
         <v>155</v>
       </c>
       <c r="AH238" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI238" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B239" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
       </c>
       <c r="D239" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E239" t="s">
         <v>54</v>
@@ -19038,7 +19038,7 @@
         <v>56</v>
       </c>
       <c r="G239">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -19047,10 +19047,13 @@
         <v>63</v>
       </c>
       <c r="J239" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="N239" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O239" t="s">
+        <v>133</v>
       </c>
       <c r="P239">
         <v>8</v>
@@ -19059,7 +19062,7 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>17399454</v>
+        <v>18073098</v>
       </c>
       <c r="S239" t="s">
         <v>155</v>
@@ -19068,19 +19071,19 @@
         <v>165</v>
       </c>
       <c r="U239" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V239" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W239">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="X239" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Y239" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB239">
         <v>0</v>
@@ -19089,18 +19092,18 @@
         <v>155</v>
       </c>
       <c r="AH239" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI239" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B240" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
@@ -19136,7 +19139,7 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>16976351</v>
+        <v>17399454</v>
       </c>
       <c r="S240" t="s">
         <v>155</v>
@@ -19148,16 +19151,16 @@
         <v>167</v>
       </c>
       <c r="V240" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W240">
         <v>-4</v>
       </c>
       <c r="X240" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y240" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AB240">
         <v>0</v>
@@ -19166,18 +19169,18 @@
         <v>155</v>
       </c>
       <c r="AH240" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI240" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:35">
       <c r="A241">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B241" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C241" t="s">
         <v>50</v>
@@ -19189,22 +19192,22 @@
         <v>54</v>
       </c>
       <c r="F241" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G241">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H241">
         <v>0</v>
       </c>
       <c r="I241" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J241" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N241" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="P241">
         <v>8</v>
@@ -19213,51 +19216,54 @@
         <v>2026</v>
       </c>
       <c r="R241">
-        <v>18178132</v>
+        <v>16976351</v>
       </c>
       <c r="S241" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="T241" t="s">
+        <v>165</v>
       </c>
       <c r="U241" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V241" s="1">
-        <v>46275.4100730787</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="X241" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Y241" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AB241">
         <v>0</v>
       </c>
       <c r="AC241" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH241" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AI241" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="1:35">
       <c r="A242">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B242" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C242" t="s">
         <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E242" t="s">
         <v>54</v>
@@ -19287,7 +19293,7 @@
         <v>2026</v>
       </c>
       <c r="R242">
-        <v>18188717</v>
+        <v>18178132</v>
       </c>
       <c r="S242" t="s">
         <v>156</v>
@@ -19296,16 +19302,16 @@
         <v>168</v>
       </c>
       <c r="V242" s="1">
-        <v>46275.40964188657</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W242">
         <v>0</v>
       </c>
       <c r="X242" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y242" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AB242">
         <v>0</v>
@@ -19314,18 +19320,18 @@
         <v>156</v>
       </c>
       <c r="AH242" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI242" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="1:35">
       <c r="A243">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B243" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C243" t="s">
         <v>50</v>
@@ -19361,7 +19367,7 @@
         <v>2026</v>
       </c>
       <c r="R243">
-        <v>18188623</v>
+        <v>18188717</v>
       </c>
       <c r="S243" t="s">
         <v>156</v>
@@ -19370,7 +19376,7 @@
         <v>168</v>
       </c>
       <c r="V243" s="1">
-        <v>46275.40964245371</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W243">
         <v>0</v>
@@ -19379,7 +19385,7 @@
         <v>173</v>
       </c>
       <c r="Y243" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AB243">
         <v>0</v>
@@ -19388,33 +19394,33 @@
         <v>156</v>
       </c>
       <c r="AH243" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI243" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B244" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
       </c>
       <c r="F244" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G244">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -19423,7 +19429,7 @@
         <v>64</v>
       </c>
       <c r="J244" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N244" s="1">
         <v>46275</v>
@@ -19435,7 +19441,7 @@
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>17222405</v>
+        <v>18188623</v>
       </c>
       <c r="S244" t="s">
         <v>156</v>
@@ -19444,16 +19450,16 @@
         <v>168</v>
       </c>
       <c r="V244" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W244">
         <v>0</v>
       </c>
       <c r="X244" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y244" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB244">
         <v>0</v>
@@ -19462,27 +19468,27 @@
         <v>156</v>
       </c>
       <c r="AH244" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI244" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B245" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
       </c>
       <c r="D245" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E245" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F245" t="s">
         <v>56</v>
@@ -19509,7 +19515,7 @@
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>16959950</v>
+        <v>17222405</v>
       </c>
       <c r="S245" t="s">
         <v>156</v>
@@ -19518,13 +19524,16 @@
         <v>168</v>
       </c>
       <c r="V245" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W245">
         <v>0</v>
       </c>
       <c r="X245" t="s">
-        <v>170</v>
+        <v>169</v>
+      </c>
+      <c r="Y245" t="s">
+        <v>259</v>
       </c>
       <c r="AB245">
         <v>0</v>
@@ -19533,30 +19542,30 @@
         <v>156</v>
       </c>
       <c r="AH245" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI245" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="246" spans="1:35">
       <c r="A246">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B246" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C246" t="s">
         <v>50</v>
       </c>
       <c r="D246" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E246" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F246" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G246">
         <v>951</v>
@@ -19580,7 +19589,7 @@
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>18178138</v>
+        <v>16959950</v>
       </c>
       <c r="S246" t="s">
         <v>156</v>
@@ -19589,16 +19598,13 @@
         <v>168</v>
       </c>
       <c r="V246" s="1">
-        <v>46275.44975668981</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W246">
         <v>0</v>
       </c>
       <c r="X246" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y246" t="s">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="AB246">
         <v>0</v>
@@ -19607,24 +19613,24 @@
         <v>156</v>
       </c>
       <c r="AH246" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI246" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B247" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19654,7 +19660,7 @@
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>18188724</v>
+        <v>18178138</v>
       </c>
       <c r="S247" t="s">
         <v>156</v>
@@ -19663,16 +19669,16 @@
         <v>168</v>
       </c>
       <c r="V247" s="1">
-        <v>46275.44933692129</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W247">
         <v>0</v>
       </c>
       <c r="X247" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y247" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19681,18 +19687,18 @@
         <v>156</v>
       </c>
       <c r="AH247" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI247" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B248" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
@@ -19728,7 +19734,7 @@
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>18188630</v>
+        <v>18188724</v>
       </c>
       <c r="S248" t="s">
         <v>156</v>
@@ -19737,7 +19743,7 @@
         <v>168</v>
       </c>
       <c r="V248" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W248">
         <v>0</v>
@@ -19746,7 +19752,7 @@
         <v>173</v>
       </c>
       <c r="Y248" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AB248">
         <v>0</v>
@@ -19755,18 +19761,18 @@
         <v>156</v>
       </c>
       <c r="AH248" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AI248" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="249" spans="1:35">
       <c r="A249">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B249" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C249" t="s">
         <v>50</v>
@@ -19778,10 +19784,10 @@
         <v>54</v>
       </c>
       <c r="F249" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G249">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -19790,34 +19796,37 @@
         <v>64</v>
       </c>
       <c r="J249" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N249" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P249">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q249">
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>17941177</v>
+        <v>18188630</v>
       </c>
       <c r="S249" t="s">
         <v>156</v>
       </c>
       <c r="U249" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V249" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X249" t="s">
-        <v>178</v>
+        <v>173</v>
+      </c>
+      <c r="Y249" t="s">
+        <v>262</v>
       </c>
       <c r="AB249">
         <v>0</v>
@@ -19826,24 +19835,24 @@
         <v>156</v>
       </c>
       <c r="AH249" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AI249" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="250" spans="1:35">
       <c r="A250">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B250" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C250" t="s">
         <v>50</v>
       </c>
       <c r="D250" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -19873,7 +19882,7 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>17952385</v>
+        <v>17941177</v>
       </c>
       <c r="S250" t="s">
         <v>156</v>
@@ -19882,13 +19891,13 @@
         <v>166</v>
       </c>
       <c r="V250" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W250">
         <v>2</v>
       </c>
       <c r="X250" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AB250">
         <v>0</v>
@@ -19897,24 +19906,24 @@
         <v>156</v>
       </c>
       <c r="AH250" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI250" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="251" spans="1:35">
       <c r="A251">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B251" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C251" t="s">
         <v>50</v>
       </c>
       <c r="D251" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E251" t="s">
         <v>54</v>
@@ -19944,7 +19953,7 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>17952569</v>
+        <v>17952385</v>
       </c>
       <c r="S251" t="s">
         <v>156</v>
@@ -19953,7 +19962,7 @@
         <v>166</v>
       </c>
       <c r="V251" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W251">
         <v>2</v>
@@ -19968,18 +19977,18 @@
         <v>156</v>
       </c>
       <c r="AH251" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI251" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B252" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
@@ -19991,7 +20000,7 @@
         <v>54</v>
       </c>
       <c r="F252" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G252">
         <v>5989</v>
@@ -20015,7 +20024,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>18164516</v>
+        <v>17952569</v>
       </c>
       <c r="S252" t="s">
         <v>156</v>
@@ -20024,13 +20033,13 @@
         <v>166</v>
       </c>
       <c r="V252" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W252">
         <v>2</v>
       </c>
       <c r="X252" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AB252">
         <v>0</v>
@@ -20039,24 +20048,24 @@
         <v>156</v>
       </c>
       <c r="AH252" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI252" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B253" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E253" t="s">
         <v>54</v>
@@ -20086,7 +20095,7 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>18178157</v>
+        <v>18164516</v>
       </c>
       <c r="S253" t="s">
         <v>156</v>
@@ -20095,13 +20104,13 @@
         <v>166</v>
       </c>
       <c r="V253" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W253">
         <v>2</v>
       </c>
       <c r="X253" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AB253">
         <v>0</v>
@@ -20110,45 +20119,45 @@
         <v>156</v>
       </c>
       <c r="AH253" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI253" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B254" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
       </c>
       <c r="D254" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E254" t="s">
         <v>54</v>
       </c>
       <c r="F254" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G254">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H254">
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J254" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N254" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P254">
         <v>9</v>
@@ -20157,48 +20166,48 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>17941187</v>
+        <v>18178157</v>
       </c>
       <c r="S254" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="U254" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V254" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X254" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AB254">
         <v>0</v>
       </c>
       <c r="AC254" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="AH254" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI254" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B255" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
       </c>
       <c r="D255" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E255" t="s">
         <v>54</v>
@@ -20228,7 +20237,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>17952400</v>
+        <v>17941187</v>
       </c>
       <c r="S255" t="s">
         <v>54</v>
@@ -20237,13 +20246,13 @@
         <v>168</v>
       </c>
       <c r="V255" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W255">
         <v>1</v>
       </c>
       <c r="X255" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AB255">
         <v>0</v>
@@ -20252,24 +20261,24 @@
         <v>54</v>
       </c>
       <c r="AH255" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI255" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -20299,7 +20308,7 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17952580</v>
+        <v>17952400</v>
       </c>
       <c r="S256" t="s">
         <v>54</v>
@@ -20308,7 +20317,7 @@
         <v>168</v>
       </c>
       <c r="V256" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W256">
         <v>1</v>
@@ -20323,18 +20332,18 @@
         <v>54</v>
       </c>
       <c r="AH256" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI256" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B257" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
@@ -20346,7 +20355,7 @@
         <v>54</v>
       </c>
       <c r="F257" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G257">
         <v>6215</v>
@@ -20370,7 +20379,7 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18164523</v>
+        <v>17952580</v>
       </c>
       <c r="S257" t="s">
         <v>54</v>
@@ -20379,13 +20388,13 @@
         <v>168</v>
       </c>
       <c r="V257" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W257">
         <v>1</v>
       </c>
       <c r="X257" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AB257">
         <v>0</v>
@@ -20394,24 +20403,24 @@
         <v>54</v>
       </c>
       <c r="AH257" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI257" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B258" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E258" t="s">
         <v>54</v>
@@ -20441,42 +20450,42 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>18178163</v>
+        <v>18164523</v>
       </c>
       <c r="S258" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="U258" t="s">
         <v>168</v>
       </c>
       <c r="V258" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W258">
         <v>1</v>
       </c>
       <c r="X258" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AB258">
         <v>0</v>
       </c>
       <c r="AC258" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="AH258" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AI258" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B259" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
@@ -20488,10 +20497,10 @@
         <v>54</v>
       </c>
       <c r="F259" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G259">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -20500,34 +20509,34 @@
         <v>65</v>
       </c>
       <c r="J259" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N259" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P259">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q259">
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>17994311</v>
+        <v>18178163</v>
       </c>
       <c r="S259" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="U259" t="s">
         <v>168</v>
       </c>
       <c r="V259" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X259" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AB259">
         <v>0</v>
@@ -20536,24 +20545,24 @@
         <v>157</v>
       </c>
       <c r="AH259" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AI259" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B260" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E260" t="s">
         <v>54</v>
@@ -20583,7 +20592,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>17994675</v>
+        <v>17994311</v>
       </c>
       <c r="S260" t="s">
         <v>54</v>
@@ -20592,13 +20601,13 @@
         <v>168</v>
       </c>
       <c r="V260" s="1">
-        <v>46275.31747032407</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W260">
         <v>0</v>
       </c>
       <c r="X260" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AB260">
         <v>0</v>
@@ -20607,24 +20616,24 @@
         <v>157</v>
       </c>
       <c r="AH260" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI260" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B261" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20654,7 +20663,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>17994809</v>
+        <v>17994675</v>
       </c>
       <c r="S261" t="s">
         <v>54</v>
@@ -20663,13 +20672,13 @@
         <v>168</v>
       </c>
       <c r="V261" s="1">
-        <v>46275.31747981482</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W261">
         <v>0</v>
       </c>
       <c r="X261" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB261">
         <v>0</v>
@@ -20678,18 +20687,18 @@
         <v>157</v>
       </c>
       <c r="AH261" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI261" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B262" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
@@ -20725,7 +20734,7 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>18006051</v>
+        <v>17994809</v>
       </c>
       <c r="S262" t="s">
         <v>54</v>
@@ -20734,13 +20743,13 @@
         <v>168</v>
       </c>
       <c r="V262" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W262">
         <v>0</v>
       </c>
       <c r="X262" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AB262">
         <v>0</v>
@@ -20749,27 +20758,27 @@
         <v>157</v>
       </c>
       <c r="AH262" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI262" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B263" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
       </c>
       <c r="D263" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E263" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F263" t="s">
         <v>56</v>
@@ -20796,22 +20805,22 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>18003256</v>
+        <v>18006051</v>
       </c>
       <c r="S263" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U263" t="s">
         <v>168</v>
       </c>
       <c r="V263" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W263">
         <v>0</v>
       </c>
       <c r="X263" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB263">
         <v>0</v>
@@ -20820,27 +20829,27 @@
         <v>157</v>
       </c>
       <c r="AH263" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI263" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B264" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E264" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F264" t="s">
         <v>56</v>
@@ -20867,22 +20876,22 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>18004017</v>
+        <v>18003256</v>
       </c>
       <c r="S264" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U264" t="s">
         <v>168</v>
       </c>
       <c r="V264" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W264">
         <v>0</v>
       </c>
       <c r="X264" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AB264">
         <v>0</v>
@@ -20891,24 +20900,24 @@
         <v>157</v>
       </c>
       <c r="AH264" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI264" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B265" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E265" t="s">
         <v>54</v>
@@ -20938,7 +20947,7 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>17995164</v>
+        <v>18004017</v>
       </c>
       <c r="S265" t="s">
         <v>54</v>
@@ -20947,13 +20956,13 @@
         <v>168</v>
       </c>
       <c r="V265" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W265">
         <v>0</v>
       </c>
       <c r="X265" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AB265">
         <v>0</v>
@@ -20962,24 +20971,24 @@
         <v>157</v>
       </c>
       <c r="AH265" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI265" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B266" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
       </c>
       <c r="D266" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E266" t="s">
         <v>54</v>
@@ -21009,7 +21018,7 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>18004028</v>
+        <v>17995164</v>
       </c>
       <c r="S266" t="s">
         <v>54</v>
@@ -21018,7 +21027,7 @@
         <v>168</v>
       </c>
       <c r="V266" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W266">
         <v>0</v>
@@ -21033,10 +21042,229 @@
         <v>157</v>
       </c>
       <c r="AH266" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AI266" t="s">
-        <v>271</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="267" spans="1:35">
+      <c r="A267">
+        <v>6705</v>
+      </c>
+      <c r="B267" t="s">
+        <v>48</v>
+      </c>
+      <c r="C267" t="s">
+        <v>50</v>
+      </c>
+      <c r="D267" t="s">
+        <v>52</v>
+      </c>
+      <c r="E267" t="s">
+        <v>54</v>
+      </c>
+      <c r="F267" t="s">
+        <v>56</v>
+      </c>
+      <c r="G267">
+        <v>11746</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267" t="s">
+        <v>65</v>
+      </c>
+      <c r="J267" t="s">
+        <v>126</v>
+      </c>
+      <c r="N267" s="1">
+        <v>46275</v>
+      </c>
+      <c r="P267">
+        <v>8</v>
+      </c>
+      <c r="Q267">
+        <v>2026</v>
+      </c>
+      <c r="R267">
+        <v>18004028</v>
+      </c>
+      <c r="S267" t="s">
+        <v>54</v>
+      </c>
+      <c r="U267" t="s">
+        <v>168</v>
+      </c>
+      <c r="V267" s="1">
+        <v>46275.31750599537</v>
+      </c>
+      <c r="W267">
+        <v>0</v>
+      </c>
+      <c r="X267" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB267">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH267" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI267" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:35">
+      <c r="A268">
+        <v>5417</v>
+      </c>
+      <c r="B268" t="s">
+        <v>43</v>
+      </c>
+      <c r="C268" t="s">
+        <v>50</v>
+      </c>
+      <c r="D268" t="s">
+        <v>51</v>
+      </c>
+      <c r="E268" t="s">
+        <v>54</v>
+      </c>
+      <c r="F268" t="s">
+        <v>56</v>
+      </c>
+      <c r="G268">
+        <v>7877</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268" t="s">
+        <v>65</v>
+      </c>
+      <c r="J268" t="s">
+        <v>67</v>
+      </c>
+      <c r="N268" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P268">
+        <v>7</v>
+      </c>
+      <c r="Q268">
+        <v>2026</v>
+      </c>
+      <c r="R268">
+        <v>17399329</v>
+      </c>
+      <c r="S268" t="s">
+        <v>54</v>
+      </c>
+      <c r="U268" t="s">
+        <v>166</v>
+      </c>
+      <c r="V268" s="1">
+        <v>46275.5810894676</v>
+      </c>
+      <c r="W268">
+        <v>16</v>
+      </c>
+      <c r="X268" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y268" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB268">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH268" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI268" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="269" spans="1:35">
+      <c r="A269">
+        <v>6486</v>
+      </c>
+      <c r="B269" t="s">
+        <v>44</v>
+      </c>
+      <c r="C269" t="s">
+        <v>50</v>
+      </c>
+      <c r="D269" t="s">
+        <v>51</v>
+      </c>
+      <c r="E269" t="s">
+        <v>54</v>
+      </c>
+      <c r="F269" t="s">
+        <v>56</v>
+      </c>
+      <c r="G269">
+        <v>9774</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269" t="s">
+        <v>65</v>
+      </c>
+      <c r="J269" t="s">
+        <v>122</v>
+      </c>
+      <c r="N269" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P269">
+        <v>7</v>
+      </c>
+      <c r="Q269">
+        <v>2026</v>
+      </c>
+      <c r="R269">
+        <v>16976320</v>
+      </c>
+      <c r="S269" t="s">
+        <v>54</v>
+      </c>
+      <c r="U269" t="s">
+        <v>166</v>
+      </c>
+      <c r="V269" s="1">
+        <v>46275.58158541666</v>
+      </c>
+      <c r="W269">
+        <v>16</v>
+      </c>
+      <c r="X269" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y269" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB269">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH269" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI269" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3954" uniqueCount="279">
   <si>
     <t>CodCliente</t>
   </si>
@@ -774,6 +774,10 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 - Data Comentário: 04/09/2026 16:13</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 
+Estamos encontrando algumas dificuldades nas validações da folha complementar de intermitentes. Como os cálculos são realizados individualmente, o processo exige uma conferência mais detalhada. Após a conclusão das validações, finalizaremos o fechamento. - Data Comentário: 10/09/2026 17:34</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/09/2026 
@@ -1203,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI278"/>
+  <dimension ref="A1:AI279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1384,10 +1388,10 @@
         <v>138</v>
       </c>
       <c r="AH2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1461,10 +1465,10 @@
         <v>139</v>
       </c>
       <c r="AH3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1538,10 +1542,10 @@
         <v>138</v>
       </c>
       <c r="AH4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1612,10 +1616,10 @@
         <v>138</v>
       </c>
       <c r="AH5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1686,10 +1690,10 @@
         <v>139</v>
       </c>
       <c r="AH6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1760,10 +1764,10 @@
         <v>139</v>
       </c>
       <c r="AH7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1834,10 +1838,10 @@
         <v>140</v>
       </c>
       <c r="AH8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1908,10 +1912,10 @@
         <v>138</v>
       </c>
       <c r="AH9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1982,10 +1986,10 @@
         <v>141</v>
       </c>
       <c r="AH10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2056,10 +2060,10 @@
         <v>141</v>
       </c>
       <c r="AH11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2130,10 +2134,10 @@
         <v>142</v>
       </c>
       <c r="AH12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2201,13 +2205,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AH13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2275,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AH14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2349,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2414,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2485,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2562,10 +2566,10 @@
         <v>144</v>
       </c>
       <c r="AH18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2639,10 +2643,10 @@
         <v>143</v>
       </c>
       <c r="AH19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2716,10 +2720,10 @@
         <v>144</v>
       </c>
       <c r="AH20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2793,10 +2797,10 @@
         <v>142</v>
       </c>
       <c r="AH21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2867,10 +2871,10 @@
         <v>145</v>
       </c>
       <c r="AH22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2941,10 +2945,10 @@
         <v>142</v>
       </c>
       <c r="AH23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3015,10 +3019,10 @@
         <v>142</v>
       </c>
       <c r="AH24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3089,10 +3093,10 @@
         <v>142</v>
       </c>
       <c r="AH25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3163,10 +3167,10 @@
         <v>143</v>
       </c>
       <c r="AH26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3237,10 +3241,10 @@
         <v>142</v>
       </c>
       <c r="AH27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3311,10 +3315,10 @@
         <v>142</v>
       </c>
       <c r="AH28" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3385,10 +3389,10 @@
         <v>142</v>
       </c>
       <c r="AH29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3459,10 +3463,10 @@
         <v>146</v>
       </c>
       <c r="AH30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3539,10 +3543,10 @@
         <v>147</v>
       </c>
       <c r="AH31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3613,10 +3617,10 @@
         <v>148</v>
       </c>
       <c r="AH32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI32" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3693,10 +3697,10 @@
         <v>149</v>
       </c>
       <c r="AH33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3770,10 +3774,10 @@
         <v>150</v>
       </c>
       <c r="AH34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3847,13 +3851,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH35" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3930,10 +3934,10 @@
         <v>152</v>
       </c>
       <c r="AH36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4010,10 +4014,10 @@
         <v>146</v>
       </c>
       <c r="AH37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4087,10 +4091,10 @@
         <v>169</v>
       </c>
       <c r="AH38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4167,10 +4171,10 @@
         <v>147</v>
       </c>
       <c r="AH39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4247,10 +4251,10 @@
         <v>147</v>
       </c>
       <c r="AH40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4327,10 +4331,10 @@
         <v>147</v>
       </c>
       <c r="AH41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4407,10 +4411,10 @@
         <v>146</v>
       </c>
       <c r="AH42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4487,10 +4491,10 @@
         <v>153</v>
       </c>
       <c r="AH43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4567,10 +4571,10 @@
         <v>148</v>
       </c>
       <c r="AH44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4647,10 +4651,10 @@
         <v>149</v>
       </c>
       <c r="AH45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4718,10 +4722,10 @@
         <v>150</v>
       </c>
       <c r="AH46" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4792,10 +4796,10 @@
         <v>147</v>
       </c>
       <c r="AH47" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4866,10 +4870,10 @@
         <v>147</v>
       </c>
       <c r="AH48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4940,10 +4944,10 @@
         <v>147</v>
       </c>
       <c r="AH49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5014,10 +5018,10 @@
         <v>146</v>
       </c>
       <c r="AH50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5088,10 +5092,10 @@
         <v>153</v>
       </c>
       <c r="AH51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5168,10 +5172,10 @@
         <v>148</v>
       </c>
       <c r="AH52" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5242,10 +5246,10 @@
         <v>149</v>
       </c>
       <c r="AH53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5322,10 +5326,10 @@
         <v>147</v>
       </c>
       <c r="AH54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI54" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5402,10 +5406,10 @@
         <v>147</v>
       </c>
       <c r="AH55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5482,10 +5486,10 @@
         <v>147</v>
       </c>
       <c r="AH56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5562,10 +5566,10 @@
         <v>146</v>
       </c>
       <c r="AH57" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5639,10 +5643,10 @@
         <v>150</v>
       </c>
       <c r="AH58" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5716,13 +5720,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH59" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI59" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5799,10 +5803,10 @@
         <v>147</v>
       </c>
       <c r="AH60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI60" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5879,10 +5883,10 @@
         <v>147</v>
       </c>
       <c r="AH61" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5959,10 +5963,10 @@
         <v>147</v>
       </c>
       <c r="AH62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6039,10 +6043,10 @@
         <v>146</v>
       </c>
       <c r="AH63" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6119,10 +6123,10 @@
         <v>153</v>
       </c>
       <c r="AH64" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI64" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6199,10 +6203,10 @@
         <v>148</v>
       </c>
       <c r="AH65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6279,10 +6283,10 @@
         <v>149</v>
       </c>
       <c r="AH66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6359,10 +6363,10 @@
         <v>147</v>
       </c>
       <c r="AH67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6430,10 +6434,10 @@
         <v>150</v>
       </c>
       <c r="AH68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6501,13 +6505,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6578,10 +6582,10 @@
         <v>147</v>
       </c>
       <c r="AH70" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6652,10 +6656,10 @@
         <v>147</v>
       </c>
       <c r="AH71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6726,10 +6730,10 @@
         <v>147</v>
       </c>
       <c r="AH72" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI72" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6800,10 +6804,10 @@
         <v>146</v>
       </c>
       <c r="AH73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6874,10 +6878,10 @@
         <v>153</v>
       </c>
       <c r="AH74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6948,10 +6952,10 @@
         <v>148</v>
       </c>
       <c r="AH75" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI75" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7022,10 +7026,10 @@
         <v>149</v>
       </c>
       <c r="AH76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI76" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7096,10 +7100,10 @@
         <v>149</v>
       </c>
       <c r="AH77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7170,10 +7174,10 @@
         <v>149</v>
       </c>
       <c r="AH78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7244,10 +7248,10 @@
         <v>149</v>
       </c>
       <c r="AH79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI79" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7318,10 +7322,10 @@
         <v>155</v>
       </c>
       <c r="AH80" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7392,10 +7396,10 @@
         <v>155</v>
       </c>
       <c r="AH81" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7466,10 +7470,10 @@
         <v>156</v>
       </c>
       <c r="AH82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI82" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7540,10 +7544,10 @@
         <v>155</v>
       </c>
       <c r="AH83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7614,10 +7618,10 @@
         <v>155</v>
       </c>
       <c r="AH84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7688,10 +7692,10 @@
         <v>155</v>
       </c>
       <c r="AH85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI85" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7756,10 +7760,10 @@
         <v>156</v>
       </c>
       <c r="AH86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7830,10 +7834,10 @@
         <v>155</v>
       </c>
       <c r="AH87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7904,10 +7908,10 @@
         <v>155</v>
       </c>
       <c r="AH88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI88" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7978,10 +7982,10 @@
         <v>155</v>
       </c>
       <c r="AH89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI89" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8046,10 +8050,10 @@
         <v>155</v>
       </c>
       <c r="AH90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8114,10 +8118,10 @@
         <v>156</v>
       </c>
       <c r="AH91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8188,10 +8192,10 @@
         <v>155</v>
       </c>
       <c r="AH92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8262,10 +8266,10 @@
         <v>155</v>
       </c>
       <c r="AH93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8336,10 +8340,10 @@
         <v>155</v>
       </c>
       <c r="AH94" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8404,10 +8408,10 @@
         <v>155</v>
       </c>
       <c r="AH95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8472,10 +8476,10 @@
         <v>156</v>
       </c>
       <c r="AH96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8546,10 +8550,10 @@
         <v>155</v>
       </c>
       <c r="AH97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8620,10 +8624,10 @@
         <v>155</v>
       </c>
       <c r="AH98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8694,10 +8698,10 @@
         <v>156</v>
       </c>
       <c r="AH99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8774,10 +8778,10 @@
         <v>155</v>
       </c>
       <c r="AH100" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8845,10 +8849,10 @@
         <v>155</v>
       </c>
       <c r="AH101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8919,10 +8923,10 @@
         <v>155</v>
       </c>
       <c r="AH102" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI102" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -8993,10 +8997,10 @@
         <v>155</v>
       </c>
       <c r="AH103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI103" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9067,10 +9071,10 @@
         <v>155</v>
       </c>
       <c r="AH104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI104" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9135,10 +9139,10 @@
         <v>155</v>
       </c>
       <c r="AH105" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9203,10 +9207,10 @@
         <v>156</v>
       </c>
       <c r="AH106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9277,10 +9281,10 @@
         <v>155</v>
       </c>
       <c r="AH107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI107" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9351,10 +9355,10 @@
         <v>155</v>
       </c>
       <c r="AH108" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9422,10 +9426,10 @@
         <v>155</v>
       </c>
       <c r="AH109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9496,10 +9500,10 @@
         <v>156</v>
       </c>
       <c r="AH110" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9567,10 +9571,10 @@
         <v>158</v>
       </c>
       <c r="AH111" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9641,10 +9645,10 @@
         <v>156</v>
       </c>
       <c r="AH112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI112" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9715,10 +9719,10 @@
         <v>154</v>
       </c>
       <c r="AH113" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9786,10 +9790,10 @@
         <v>158</v>
       </c>
       <c r="AH114" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI114" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9860,10 +9864,10 @@
         <v>156</v>
       </c>
       <c r="AH115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI115" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9934,10 +9938,10 @@
         <v>155</v>
       </c>
       <c r="AH116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10008,10 +10012,10 @@
         <v>155</v>
       </c>
       <c r="AH117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10082,10 +10086,10 @@
         <v>155</v>
       </c>
       <c r="AH118" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10150,10 +10154,10 @@
         <v>155</v>
       </c>
       <c r="AH119" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI119" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10218,10 +10222,10 @@
         <v>156</v>
       </c>
       <c r="AH120" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI120" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10292,10 +10296,10 @@
         <v>155</v>
       </c>
       <c r="AH121" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI121" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10366,10 +10370,10 @@
         <v>155</v>
       </c>
       <c r="AH122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10440,10 +10444,10 @@
         <v>155</v>
       </c>
       <c r="AH123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10508,10 +10512,10 @@
         <v>155</v>
       </c>
       <c r="AH124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10576,10 +10580,10 @@
         <v>156</v>
       </c>
       <c r="AH125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI125" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10656,10 +10660,10 @@
         <v>156</v>
       </c>
       <c r="AH126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI126" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10736,10 +10740,10 @@
         <v>156</v>
       </c>
       <c r="AH127" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10810,10 +10814,10 @@
         <v>159</v>
       </c>
       <c r="AH128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI128" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10884,10 +10888,10 @@
         <v>159</v>
       </c>
       <c r="AH129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10964,10 +10968,10 @@
         <v>159</v>
       </c>
       <c r="AH130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11038,10 +11042,10 @@
         <v>159</v>
       </c>
       <c r="AH131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI131" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11112,10 +11116,10 @@
         <v>159</v>
       </c>
       <c r="AH132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11186,10 +11190,10 @@
         <v>159</v>
       </c>
       <c r="AH133" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11260,10 +11264,10 @@
         <v>159</v>
       </c>
       <c r="AH134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11340,10 +11344,10 @@
         <v>159</v>
       </c>
       <c r="AH135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI135" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11414,10 +11418,10 @@
         <v>159</v>
       </c>
       <c r="AH136" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI136" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11488,10 +11492,10 @@
         <v>159</v>
       </c>
       <c r="AH137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11562,10 +11566,10 @@
         <v>159</v>
       </c>
       <c r="AH138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI138" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11642,10 +11646,10 @@
         <v>159</v>
       </c>
       <c r="AH139" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI139" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11716,10 +11720,10 @@
         <v>159</v>
       </c>
       <c r="AH140" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI140" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11790,10 +11794,10 @@
         <v>159</v>
       </c>
       <c r="AH141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11864,10 +11868,10 @@
         <v>159</v>
       </c>
       <c r="AH142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI142" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11938,10 +11942,10 @@
         <v>159</v>
       </c>
       <c r="AH143" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12012,10 +12016,10 @@
         <v>159</v>
       </c>
       <c r="AH144" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12086,10 +12090,10 @@
         <v>159</v>
       </c>
       <c r="AH145" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI145" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12160,10 +12164,10 @@
         <v>159</v>
       </c>
       <c r="AH146" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI146" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12234,10 +12238,10 @@
         <v>159</v>
       </c>
       <c r="AH147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI147" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12308,10 +12312,10 @@
         <v>159</v>
       </c>
       <c r="AH148" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12382,10 +12386,10 @@
         <v>159</v>
       </c>
       <c r="AH149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12462,10 +12466,10 @@
         <v>159</v>
       </c>
       <c r="AH150" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12536,10 +12540,10 @@
         <v>159</v>
       </c>
       <c r="AH151" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI151" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12610,10 +12614,10 @@
         <v>159</v>
       </c>
       <c r="AH152" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12684,10 +12688,10 @@
         <v>159</v>
       </c>
       <c r="AH153" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI153" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12758,10 +12762,10 @@
         <v>160</v>
       </c>
       <c r="AH154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI154" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12832,10 +12836,10 @@
         <v>160</v>
       </c>
       <c r="AH155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI155" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12906,10 +12910,10 @@
         <v>160</v>
       </c>
       <c r="AH156" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI156" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -12980,10 +12984,10 @@
         <v>160</v>
       </c>
       <c r="AH157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI157" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13054,10 +13058,10 @@
         <v>160</v>
       </c>
       <c r="AH158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13128,10 +13132,10 @@
         <v>160</v>
       </c>
       <c r="AH159" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI159" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13202,10 +13206,10 @@
         <v>160</v>
       </c>
       <c r="AH160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI160" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13276,10 +13280,10 @@
         <v>160</v>
       </c>
       <c r="AH161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13350,10 +13354,10 @@
         <v>160</v>
       </c>
       <c r="AH162" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13424,10 +13428,10 @@
         <v>160</v>
       </c>
       <c r="AH163" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI163" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13498,10 +13502,10 @@
         <v>160</v>
       </c>
       <c r="AH164" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI164" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13572,10 +13576,10 @@
         <v>160</v>
       </c>
       <c r="AH165" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI165" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13646,10 +13650,10 @@
         <v>160</v>
       </c>
       <c r="AH166" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI166" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13720,10 +13724,10 @@
         <v>160</v>
       </c>
       <c r="AH167" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI167" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13794,10 +13798,10 @@
         <v>160</v>
       </c>
       <c r="AH168" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI168" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13871,10 +13875,10 @@
         <v>160</v>
       </c>
       <c r="AH169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI169" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13948,10 +13952,10 @@
         <v>160</v>
       </c>
       <c r="AH170" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI170" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14025,10 +14029,10 @@
         <v>160</v>
       </c>
       <c r="AH171" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI171" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14102,10 +14106,10 @@
         <v>160</v>
       </c>
       <c r="AH172" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI172" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14179,10 +14183,10 @@
         <v>160</v>
       </c>
       <c r="AH173" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI173" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14256,10 +14260,10 @@
         <v>160</v>
       </c>
       <c r="AH174" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14333,10 +14337,10 @@
         <v>160</v>
       </c>
       <c r="AH175" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI175" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14410,10 +14414,10 @@
         <v>160</v>
       </c>
       <c r="AH176" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI176" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14487,10 +14491,10 @@
         <v>160</v>
       </c>
       <c r="AH177" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI177" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14564,10 +14568,10 @@
         <v>160</v>
       </c>
       <c r="AH178" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI178" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14641,10 +14645,10 @@
         <v>160</v>
       </c>
       <c r="AH179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI179" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14718,10 +14722,10 @@
         <v>160</v>
       </c>
       <c r="AH180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14795,10 +14799,10 @@
         <v>160</v>
       </c>
       <c r="AH181" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI181" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14872,10 +14876,10 @@
         <v>160</v>
       </c>
       <c r="AH182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI182" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14943,10 +14947,10 @@
         <v>160</v>
       </c>
       <c r="AH183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15014,10 +15018,10 @@
         <v>160</v>
       </c>
       <c r="AH184" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI184" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15085,10 +15089,10 @@
         <v>160</v>
       </c>
       <c r="AH185" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI185" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15156,10 +15160,10 @@
         <v>160</v>
       </c>
       <c r="AH186" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI186" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15227,10 +15231,10 @@
         <v>160</v>
       </c>
       <c r="AH187" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI187" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15298,10 +15302,10 @@
         <v>160</v>
       </c>
       <c r="AH188" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI188" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15369,10 +15373,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI189" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15440,10 +15444,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI190" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15511,10 +15515,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI191" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15582,10 +15586,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI192" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15653,10 +15657,10 @@
         <v>161</v>
       </c>
       <c r="AH193" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI193" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15724,10 +15728,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI194" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15795,10 +15799,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI195" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15866,10 +15870,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI196" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15937,10 +15941,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI197" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16008,10 +16012,10 @@
         <v>161</v>
       </c>
       <c r="AH198" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI198" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16079,10 +16083,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI199" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16150,10 +16154,10 @@
         <v>161</v>
       </c>
       <c r="AH200" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI200" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16221,10 +16225,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI201" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16292,10 +16296,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI202" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16363,10 +16367,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI203" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16434,10 +16438,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI204" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16505,10 +16509,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI205" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16576,10 +16580,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI206" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16647,10 +16651,10 @@
         <v>161</v>
       </c>
       <c r="AH207" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI207" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16718,10 +16722,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI208" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16792,10 +16796,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI209" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16866,10 +16870,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI210" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16940,10 +16944,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI211" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17014,10 +17018,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI212" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17085,10 +17089,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI213" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17156,10 +17160,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI214" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17224,10 +17228,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI215" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17289,10 +17293,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI216" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17363,10 +17367,10 @@
         <v>162</v>
       </c>
       <c r="AH217" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI217" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17440,10 +17444,10 @@
         <v>150</v>
       </c>
       <c r="AH218" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI218" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17520,27 +17524,27 @@
         <v>147</v>
       </c>
       <c r="AH219" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI219" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:35">
       <c r="A220">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B220" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C220" t="s">
         <v>50</v>
       </c>
       <c r="D220" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E220" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F220" t="s">
         <v>56</v>
@@ -17561,7 +17565,7 @@
         <v>46275</v>
       </c>
       <c r="O220" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P220">
         <v>8</v>
@@ -17570,25 +17574,25 @@
         <v>2026</v>
       </c>
       <c r="R220">
-        <v>18090250</v>
+        <v>18068611</v>
       </c>
       <c r="S220" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="T220" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U220" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V220" s="1">
-        <v>46274.48792050926</v>
+        <v>46276.48975401621</v>
       </c>
       <c r="W220">
         <v>1</v>
       </c>
       <c r="X220" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y220" t="s">
         <v>248</v>
@@ -17597,21 +17601,21 @@
         <v>0</v>
       </c>
       <c r="AC220" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AH220" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI220" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="221" spans="1:35">
       <c r="A221">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B221" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C221" t="s">
         <v>50</v>
@@ -17623,7 +17627,7 @@
         <v>54</v>
       </c>
       <c r="F221" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G221">
         <v>9746</v>
@@ -17650,25 +17654,25 @@
         <v>2026</v>
       </c>
       <c r="R221">
-        <v>18179154</v>
+        <v>18090250</v>
       </c>
       <c r="S221" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="T221" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U221" t="s">
         <v>172</v>
       </c>
       <c r="V221" s="1">
-        <v>46274.588374375</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W221">
         <v>1</v>
       </c>
       <c r="X221" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y221" t="s">
         <v>249</v>
@@ -17677,27 +17681,27 @@
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AH221" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI221" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="222" spans="1:35">
       <c r="A222">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B222" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C222" t="s">
         <v>50</v>
       </c>
       <c r="D222" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E222" t="s">
         <v>54</v>
@@ -17720,6 +17724,9 @@
       <c r="N222" s="1">
         <v>46275</v>
       </c>
+      <c r="O222" t="s">
+        <v>133</v>
+      </c>
       <c r="P222">
         <v>8</v>
       </c>
@@ -17727,10 +17734,10 @@
         <v>2026</v>
       </c>
       <c r="R222">
-        <v>18190457</v>
+        <v>18179154</v>
       </c>
       <c r="S222" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T222" t="s">
         <v>168</v>
@@ -17739,33 +17746,36 @@
         <v>172</v>
       </c>
       <c r="V222" s="1">
-        <v>46274.34198912037</v>
+        <v>46274.588374375</v>
       </c>
       <c r="W222">
         <v>1</v>
       </c>
       <c r="X222" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="Y222" t="s">
+        <v>250</v>
       </c>
       <c r="AB222">
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH222" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI222" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B223" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
@@ -17774,13 +17784,13 @@
         <v>51</v>
       </c>
       <c r="E223" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F223" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G223">
-        <v>6348</v>
+        <v>9746</v>
       </c>
       <c r="H223">
         <v>0</v>
@@ -17789,63 +17799,63 @@
         <v>61</v>
       </c>
       <c r="J223" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N223" s="1">
         <v>46275</v>
       </c>
-      <c r="O223" t="s">
-        <v>133</v>
-      </c>
       <c r="P223">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q223">
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>18261361</v>
+        <v>18190457</v>
+      </c>
+      <c r="S223" t="s">
+        <v>149</v>
+      </c>
+      <c r="T223" t="s">
+        <v>168</v>
       </c>
       <c r="U223" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V223" s="1">
-        <v>46275.39631951389</v>
+        <v>46274.34198912037</v>
       </c>
       <c r="W223">
         <v>1</v>
       </c>
       <c r="X223" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y223" t="s">
-        <v>250</v>
+        <v>176</v>
       </c>
       <c r="AB223">
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AH223" t="s">
         <v>274</v>
       </c>
       <c r="AI223" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B224" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
       </c>
       <c r="D224" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E224" t="s">
         <v>55</v>
@@ -17878,13 +17888,13 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>18261362</v>
+        <v>18261361</v>
       </c>
       <c r="U224" t="s">
         <v>173</v>
       </c>
       <c r="V224" s="1">
-        <v>46275.39631994213</v>
+        <v>46275.39631951389</v>
       </c>
       <c r="W224">
         <v>1</v>
@@ -17893,7 +17903,7 @@
         <v>175</v>
       </c>
       <c r="Y224" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB224">
         <v>0</v>
@@ -17902,18 +17912,18 @@
         <v>147</v>
       </c>
       <c r="AH224" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI224" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B225" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
@@ -17922,84 +17932,87 @@
         <v>52</v>
       </c>
       <c r="E225" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F225" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G225">
-        <v>1862</v>
+        <v>6348</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J225" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N225" s="1">
-        <v>46281</v>
+        <v>46275</v>
+      </c>
+      <c r="O225" t="s">
+        <v>133</v>
       </c>
       <c r="P225">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q225">
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>18220176</v>
-      </c>
-      <c r="S225" t="s">
-        <v>158</v>
+        <v>18261362</v>
       </c>
       <c r="U225" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V225" s="1">
-        <v>46276.37795540509</v>
+        <v>46275.39631994213</v>
       </c>
       <c r="W225">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="X225" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="Y225" t="s">
+        <v>251</v>
       </c>
       <c r="AB225">
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AH225" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AI225" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B226" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
       </c>
       <c r="D226" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E226" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F226" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G226">
-        <v>6805</v>
+        <v>1862</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -18008,10 +18021,10 @@
         <v>62</v>
       </c>
       <c r="J226" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N226" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="P226">
         <v>8</v>
@@ -18020,57 +18033,54 @@
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>18085519</v>
+        <v>18220176</v>
       </c>
       <c r="S226" t="s">
-        <v>155</v>
-      </c>
-      <c r="T226" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="U226" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V226" s="1">
-        <v>46276.40669469907</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="X226" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB226">
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AH226" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AI226" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B227" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
       </c>
       <c r="D227" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E227" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F227" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G227">
         <v>6805</v>
@@ -18087,9 +18097,6 @@
       <c r="N227" s="1">
         <v>46276</v>
       </c>
-      <c r="O227" t="s">
-        <v>136</v>
-      </c>
       <c r="P227">
         <v>8</v>
       </c>
@@ -18097,60 +18104,60 @@
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18220221</v>
+        <v>18085519</v>
       </c>
       <c r="S227" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="T227" t="s">
+        <v>155</v>
       </c>
       <c r="U227" t="s">
         <v>173</v>
       </c>
       <c r="V227" s="1">
-        <v>46276.39101108797</v>
+        <v>46276.40669469907</v>
       </c>
       <c r="W227">
         <v>0</v>
       </c>
       <c r="X227" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y227" t="s">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="AB227">
         <v>0</v>
       </c>
       <c r="AC227" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AH227" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI227" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B228" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
       </c>
       <c r="D228" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E228" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F228" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G228">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -18159,10 +18166,13 @@
         <v>62</v>
       </c>
       <c r="J228" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="N228" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O228" t="s">
+        <v>136</v>
       </c>
       <c r="P228">
         <v>8</v>
@@ -18171,25 +18181,22 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>17968368</v>
+        <v>18220221</v>
       </c>
       <c r="S228" t="s">
-        <v>155</v>
-      </c>
-      <c r="T228" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="U228" t="s">
         <v>173</v>
       </c>
       <c r="V228" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.39101108797</v>
       </c>
       <c r="W228">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X228" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y228" t="s">
         <v>252</v>
@@ -18198,33 +18205,33 @@
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AH228" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AI228" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B229" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E229" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F229" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G229">
         <v>1866</v>
@@ -18248,10 +18255,10 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>18186946</v>
+        <v>17968368</v>
       </c>
       <c r="S229" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="T229" t="s">
         <v>155</v>
@@ -18260,13 +18267,13 @@
         <v>173</v>
       </c>
       <c r="V229" s="1">
-        <v>46274.66470667824</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W229">
         <v>2</v>
       </c>
       <c r="X229" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y229" t="s">
         <v>253</v>
@@ -18275,21 +18282,21 @@
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AH229" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI229" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B230" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
@@ -18325,7 +18332,7 @@
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>18187212</v>
+        <v>18186946</v>
       </c>
       <c r="S230" t="s">
         <v>157</v>
@@ -18337,7 +18344,7 @@
         <v>173</v>
       </c>
       <c r="V230" s="1">
-        <v>46274.74452168981</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W230">
         <v>2</v>
@@ -18355,33 +18362,33 @@
         <v>157</v>
       </c>
       <c r="AH230" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI230" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B231" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
       </c>
       <c r="F231" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G231">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -18390,14 +18397,11 @@
         <v>62</v>
       </c>
       <c r="J231" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N231" s="1">
         <v>46274</v>
       </c>
-      <c r="O231" t="s">
-        <v>135</v>
-      </c>
       <c r="P231">
         <v>8</v>
       </c>
@@ -18405,10 +18409,10 @@
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>17988543</v>
+        <v>18187212</v>
       </c>
       <c r="S231" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="T231" t="s">
         <v>155</v>
@@ -18417,13 +18421,13 @@
         <v>173</v>
       </c>
       <c r="V231" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W231">
         <v>2</v>
       </c>
       <c r="X231" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Y231" t="s">
         <v>255</v>
@@ -18432,21 +18436,21 @@
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AH231" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI231" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B232" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
@@ -18455,7 +18459,7 @@
         <v>51</v>
       </c>
       <c r="E232" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F232" t="s">
         <v>56</v>
@@ -18475,6 +18479,9 @@
       <c r="N232" s="1">
         <v>46274</v>
       </c>
+      <c r="O232" t="s">
+        <v>135</v>
+      </c>
       <c r="P232">
         <v>8</v>
       </c>
@@ -18482,10 +18489,10 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>17968379</v>
+        <v>17988543</v>
       </c>
       <c r="S232" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T232" t="s">
         <v>155</v>
@@ -18494,45 +18501,48 @@
         <v>173</v>
       </c>
       <c r="V232" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W232">
         <v>2</v>
       </c>
       <c r="X232" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="Y232" t="s">
+        <v>256</v>
       </c>
       <c r="AB232">
         <v>0</v>
       </c>
       <c r="AC232" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH232" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI232" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B233" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E233" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F233" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G233">
         <v>1867</v>
@@ -18549,9 +18559,6 @@
       <c r="N233" s="1">
         <v>46274</v>
       </c>
-      <c r="O233" t="s">
-        <v>136</v>
-      </c>
       <c r="P233">
         <v>8</v>
       </c>
@@ -18559,51 +18566,51 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>18220182</v>
+        <v>17968379</v>
       </c>
       <c r="S233" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="T233" t="s">
+        <v>155</v>
       </c>
       <c r="U233" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V233" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W233">
         <v>2</v>
       </c>
       <c r="X233" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y233" t="s">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="AB233">
         <v>0</v>
       </c>
       <c r="AC233" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AH233" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI233" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B234" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
       </c>
       <c r="D234" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
@@ -18626,6 +18633,9 @@
       <c r="N234" s="1">
         <v>46274</v>
       </c>
+      <c r="O234" t="s">
+        <v>136</v>
+      </c>
       <c r="P234">
         <v>8</v>
       </c>
@@ -18633,45 +18643,45 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>18186953</v>
+        <v>18220182</v>
       </c>
       <c r="S234" t="s">
-        <v>157</v>
-      </c>
-      <c r="T234" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="U234" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.7274781713</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W234">
         <v>2</v>
       </c>
       <c r="X234" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+      <c r="Y234" t="s">
+        <v>257</v>
       </c>
       <c r="AB234">
         <v>0</v>
       </c>
       <c r="AC234" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH234" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI234" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B235" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
@@ -18707,7 +18717,7 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>18187219</v>
+        <v>18186953</v>
       </c>
       <c r="S235" t="s">
         <v>157</v>
@@ -18719,7 +18729,7 @@
         <v>173</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W235">
         <v>2</v>
@@ -18734,24 +18744,24 @@
         <v>157</v>
       </c>
       <c r="AH235" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI235" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B236" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
@@ -18760,19 +18770,19 @@
         <v>57</v>
       </c>
       <c r="G236">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H236">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I236" t="s">
         <v>62</v>
       </c>
       <c r="J236" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N236" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P236">
         <v>8</v>
@@ -18781,10 +18791,10 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>18214907</v>
+        <v>18187219</v>
       </c>
       <c r="S236" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T236" t="s">
         <v>155</v>
@@ -18793,57 +18803,57 @@
         <v>173</v>
       </c>
       <c r="V236" s="1">
-        <v>46275.79245582176</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X236" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AB236">
         <v>0</v>
       </c>
       <c r="AC236" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AH236" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AI236" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B237" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E237" t="s">
         <v>54</v>
       </c>
       <c r="F237" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G237">
-        <v>1792</v>
+        <v>6886</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I237" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J237" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N237" s="1">
         <v>46275</v>
@@ -18855,45 +18865,45 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>16962151</v>
+        <v>18214907</v>
       </c>
       <c r="S237" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="T237" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="U237" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.70622837963</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W237">
         <v>1</v>
       </c>
       <c r="X237" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AB237">
         <v>0</v>
       </c>
       <c r="AC237" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AH237" t="s">
         <v>274</v>
       </c>
       <c r="AI237" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B238" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
@@ -18929,7 +18939,7 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>17948756</v>
+        <v>16962151</v>
       </c>
       <c r="S238" t="s">
         <v>159</v>
@@ -18938,16 +18948,16 @@
         <v>170</v>
       </c>
       <c r="U238" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V238" s="1">
-        <v>46275.71996309028</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W238">
         <v>1</v>
       </c>
       <c r="X238" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB238">
         <v>0</v>
@@ -18956,24 +18966,24 @@
         <v>159</v>
       </c>
       <c r="AH238" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI238" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B239" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
       </c>
       <c r="D239" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E239" t="s">
         <v>54</v>
@@ -19003,7 +19013,7 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>18085143</v>
+        <v>17948756</v>
       </c>
       <c r="S239" t="s">
         <v>159</v>
@@ -19015,13 +19025,13 @@
         <v>173</v>
       </c>
       <c r="V239" s="1">
-        <v>46275.54278886574</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W239">
         <v>1</v>
       </c>
       <c r="X239" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB239">
         <v>0</v>
@@ -19030,24 +19040,24 @@
         <v>159</v>
       </c>
       <c r="AH239" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI239" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B240" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
       </c>
       <c r="D240" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E240" t="s">
         <v>54</v>
@@ -19056,7 +19066,7 @@
         <v>56</v>
       </c>
       <c r="G240">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -19065,7 +19075,7 @@
         <v>63</v>
       </c>
       <c r="J240" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N240" s="1">
         <v>46275</v>
@@ -19077,7 +19087,7 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>16962161</v>
+        <v>18085143</v>
       </c>
       <c r="S240" t="s">
         <v>159</v>
@@ -19089,13 +19099,13 @@
         <v>173</v>
       </c>
       <c r="V240" s="1">
-        <v>46275.7000328588</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W240">
         <v>1</v>
       </c>
       <c r="X240" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AB240">
         <v>0</v>
@@ -19104,24 +19114,24 @@
         <v>159</v>
       </c>
       <c r="AH240" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI240" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="241" spans="1:35">
       <c r="A241">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B241" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C241" t="s">
         <v>50</v>
       </c>
       <c r="D241" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E241" t="s">
         <v>54</v>
@@ -19151,7 +19161,7 @@
         <v>2026</v>
       </c>
       <c r="R241">
-        <v>16975952</v>
+        <v>16962161</v>
       </c>
       <c r="S241" t="s">
         <v>159</v>
@@ -19163,13 +19173,13 @@
         <v>173</v>
       </c>
       <c r="V241" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W241">
         <v>1</v>
       </c>
       <c r="X241" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AB241">
         <v>0</v>
@@ -19178,24 +19188,24 @@
         <v>159</v>
       </c>
       <c r="AH241" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI241" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="242" spans="1:35">
       <c r="A242">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B242" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C242" t="s">
         <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E242" t="s">
         <v>54</v>
@@ -19225,7 +19235,7 @@
         <v>2026</v>
       </c>
       <c r="R242">
-        <v>17948766</v>
+        <v>16975952</v>
       </c>
       <c r="S242" t="s">
         <v>159</v>
@@ -19237,13 +19247,13 @@
         <v>173</v>
       </c>
       <c r="V242" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W242">
         <v>1</v>
       </c>
       <c r="X242" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AB242">
         <v>0</v>
@@ -19252,24 +19262,24 @@
         <v>159</v>
       </c>
       <c r="AH242" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI242" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="243" spans="1:35">
       <c r="A243">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B243" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C243" t="s">
         <v>50</v>
       </c>
       <c r="D243" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E243" t="s">
         <v>54</v>
@@ -19299,7 +19309,7 @@
         <v>2026</v>
       </c>
       <c r="R243">
-        <v>18085154</v>
+        <v>17948766</v>
       </c>
       <c r="S243" t="s">
         <v>159</v>
@@ -19311,13 +19321,13 @@
         <v>173</v>
       </c>
       <c r="V243" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W243">
         <v>1</v>
       </c>
       <c r="X243" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB243">
         <v>0</v>
@@ -19326,24 +19336,24 @@
         <v>159</v>
       </c>
       <c r="AH243" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI243" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B244" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
@@ -19373,7 +19383,7 @@
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>17948928</v>
+        <v>18085154</v>
       </c>
       <c r="S244" t="s">
         <v>159</v>
@@ -19385,7 +19395,7 @@
         <v>173</v>
       </c>
       <c r="V244" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W244">
         <v>1</v>
@@ -19400,18 +19410,18 @@
         <v>159</v>
       </c>
       <c r="AH244" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI244" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B245" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
@@ -19447,7 +19457,7 @@
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>18084955</v>
+        <v>17948928</v>
       </c>
       <c r="S245" t="s">
         <v>159</v>
@@ -19459,7 +19469,7 @@
         <v>173</v>
       </c>
       <c r="V245" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W245">
         <v>1</v>
@@ -19474,24 +19484,24 @@
         <v>159</v>
       </c>
       <c r="AH245" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI245" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="246" spans="1:35">
       <c r="A246">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B246" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C246" t="s">
         <v>50</v>
       </c>
       <c r="D246" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E246" t="s">
         <v>54</v>
@@ -19500,7 +19510,7 @@
         <v>56</v>
       </c>
       <c r="G246">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -19509,13 +19519,10 @@
         <v>63</v>
       </c>
       <c r="J246" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N246" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O246" t="s">
-        <v>135</v>
+        <v>46275</v>
       </c>
       <c r="P246">
         <v>8</v>
@@ -19524,7 +19531,7 @@
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>17398955</v>
+        <v>18084955</v>
       </c>
       <c r="S246" t="s">
         <v>159</v>
@@ -19533,19 +19540,16 @@
         <v>170</v>
       </c>
       <c r="U246" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V246" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W246">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X246" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y246" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="AB246">
         <v>0</v>
@@ -19554,24 +19558,24 @@
         <v>159</v>
       </c>
       <c r="AH246" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AI246" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B247" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19604,7 +19608,7 @@
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>18073098</v>
+        <v>17398955</v>
       </c>
       <c r="S247" t="s">
         <v>159</v>
@@ -19616,16 +19620,16 @@
         <v>171</v>
       </c>
       <c r="V247" s="1">
-        <v>46274.74838096065</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W247">
         <v>3</v>
       </c>
       <c r="X247" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Y247" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19634,24 +19638,24 @@
         <v>159</v>
       </c>
       <c r="AH247" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI247" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B248" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
       </c>
       <c r="D248" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -19660,7 +19664,7 @@
         <v>56</v>
       </c>
       <c r="G248">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -19669,10 +19673,13 @@
         <v>63</v>
       </c>
       <c r="J248" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="N248" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O248" t="s">
+        <v>135</v>
       </c>
       <c r="P248">
         <v>8</v>
@@ -19681,7 +19688,7 @@
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>17399454</v>
+        <v>18073098</v>
       </c>
       <c r="S248" t="s">
         <v>159</v>
@@ -19690,16 +19697,16 @@
         <v>170</v>
       </c>
       <c r="U248" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V248" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W248">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="X248" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Y248" t="s">
         <v>258</v>
@@ -19711,18 +19718,18 @@
         <v>159</v>
       </c>
       <c r="AH248" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI248" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="249" spans="1:35">
       <c r="A249">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B249" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C249" t="s">
         <v>50</v>
@@ -19758,7 +19765,7 @@
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>16976351</v>
+        <v>17399454</v>
       </c>
       <c r="S249" t="s">
         <v>159</v>
@@ -19770,13 +19777,13 @@
         <v>172</v>
       </c>
       <c r="V249" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W249">
         <v>-3</v>
       </c>
       <c r="X249" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y249" t="s">
         <v>259</v>
@@ -19788,18 +19795,18 @@
         <v>159</v>
       </c>
       <c r="AH249" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI249" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="250" spans="1:35">
       <c r="A250">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B250" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C250" t="s">
         <v>50</v>
@@ -19811,22 +19818,22 @@
         <v>54</v>
       </c>
       <c r="F250" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G250">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H250">
         <v>0</v>
       </c>
       <c r="I250" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J250" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="N250" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="P250">
         <v>8</v>
@@ -19835,22 +19842,25 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>18178132</v>
+        <v>16976351</v>
       </c>
       <c r="S250" t="s">
-        <v>160</v>
+        <v>159</v>
+      </c>
+      <c r="T250" t="s">
+        <v>170</v>
       </c>
       <c r="U250" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V250" s="1">
-        <v>46275.4100730787</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W250">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="X250" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Y250" t="s">
         <v>260</v>
@@ -19859,27 +19869,27 @@
         <v>0</v>
       </c>
       <c r="AC250" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AH250" t="s">
         <v>274</v>
       </c>
       <c r="AI250" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="251" spans="1:35">
       <c r="A251">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B251" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C251" t="s">
         <v>50</v>
       </c>
       <c r="D251" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E251" t="s">
         <v>54</v>
@@ -19909,7 +19919,7 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>18188717</v>
+        <v>18178132</v>
       </c>
       <c r="S251" t="s">
         <v>160</v>
@@ -19918,13 +19928,13 @@
         <v>173</v>
       </c>
       <c r="V251" s="1">
-        <v>46275.40964188657</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W251">
         <v>1</v>
       </c>
       <c r="X251" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y251" t="s">
         <v>261</v>
@@ -19936,18 +19946,18 @@
         <v>160</v>
       </c>
       <c r="AH251" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI251" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B252" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
@@ -19983,7 +19993,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>18188623</v>
+        <v>18188717</v>
       </c>
       <c r="S252" t="s">
         <v>160</v>
@@ -19992,7 +20002,7 @@
         <v>173</v>
       </c>
       <c r="V252" s="1">
-        <v>46275.40964245371</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W252">
         <v>1</v>
@@ -20010,33 +20020,33 @@
         <v>160</v>
       </c>
       <c r="AH252" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI252" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B253" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E253" t="s">
         <v>54</v>
       </c>
       <c r="F253" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G253">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -20045,7 +20055,7 @@
         <v>64</v>
       </c>
       <c r="J253" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N253" s="1">
         <v>46275</v>
@@ -20057,7 +20067,7 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>17222405</v>
+        <v>18188623</v>
       </c>
       <c r="S253" t="s">
         <v>160</v>
@@ -20066,13 +20076,13 @@
         <v>173</v>
       </c>
       <c r="V253" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W253">
         <v>1</v>
       </c>
       <c r="X253" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Y253" t="s">
         <v>263</v>
@@ -20084,27 +20094,27 @@
         <v>160</v>
       </c>
       <c r="AH253" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI253" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B254" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
       </c>
       <c r="D254" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E254" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F254" t="s">
         <v>56</v>
@@ -20131,7 +20141,7 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>16959950</v>
+        <v>17222405</v>
       </c>
       <c r="S254" t="s">
         <v>160</v>
@@ -20140,13 +20150,16 @@
         <v>173</v>
       </c>
       <c r="V254" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W254">
         <v>1</v>
       </c>
       <c r="X254" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="Y254" t="s">
+        <v>264</v>
       </c>
       <c r="AB254">
         <v>0</v>
@@ -20155,30 +20168,30 @@
         <v>160</v>
       </c>
       <c r="AH254" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI254" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B255" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
       </c>
       <c r="D255" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E255" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F255" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G255">
         <v>951</v>
@@ -20202,7 +20215,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>18178138</v>
+        <v>16959950</v>
       </c>
       <c r="S255" t="s">
         <v>160</v>
@@ -20211,16 +20224,13 @@
         <v>173</v>
       </c>
       <c r="V255" s="1">
-        <v>46275.44975668981</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W255">
         <v>1</v>
       </c>
       <c r="X255" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y255" t="s">
-        <v>264</v>
+        <v>175</v>
       </c>
       <c r="AB255">
         <v>0</v>
@@ -20229,24 +20239,24 @@
         <v>160</v>
       </c>
       <c r="AH255" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI255" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B256" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -20276,7 +20286,7 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>18188724</v>
+        <v>18178138</v>
       </c>
       <c r="S256" t="s">
         <v>160</v>
@@ -20285,13 +20295,13 @@
         <v>173</v>
       </c>
       <c r="V256" s="1">
-        <v>46275.44933692129</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W256">
         <v>1</v>
       </c>
       <c r="X256" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y256" t="s">
         <v>265</v>
@@ -20303,18 +20313,18 @@
         <v>160</v>
       </c>
       <c r="AH256" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI256" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B257" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
@@ -20350,7 +20360,7 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18188630</v>
+        <v>18188724</v>
       </c>
       <c r="S257" t="s">
         <v>160</v>
@@ -20359,7 +20369,7 @@
         <v>173</v>
       </c>
       <c r="V257" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W257">
         <v>1</v>
@@ -20377,18 +20387,18 @@
         <v>160</v>
       </c>
       <c r="AH257" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AI257" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B258" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
@@ -20400,10 +20410,10 @@
         <v>54</v>
       </c>
       <c r="F258" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G258">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -20412,34 +20422,37 @@
         <v>64</v>
       </c>
       <c r="J258" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="N258" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P258">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q258">
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>17941177</v>
+        <v>18188630</v>
       </c>
       <c r="S258" t="s">
         <v>160</v>
       </c>
       <c r="U258" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V258" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W258">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X258" t="s">
-        <v>183</v>
+        <v>178</v>
+      </c>
+      <c r="Y258" t="s">
+        <v>267</v>
       </c>
       <c r="AB258">
         <v>0</v>
@@ -20451,21 +20464,21 @@
         <v>275</v>
       </c>
       <c r="AI258" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B259" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
       </c>
       <c r="D259" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -20495,7 +20508,7 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>17952385</v>
+        <v>17941177</v>
       </c>
       <c r="S259" t="s">
         <v>160</v>
@@ -20504,13 +20517,13 @@
         <v>171</v>
       </c>
       <c r="V259" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W259">
         <v>3</v>
       </c>
       <c r="X259" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB259">
         <v>0</v>
@@ -20519,24 +20532,24 @@
         <v>160</v>
       </c>
       <c r="AH259" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI259" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E260" t="s">
         <v>54</v>
@@ -20566,7 +20579,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>17952569</v>
+        <v>17952385</v>
       </c>
       <c r="S260" t="s">
         <v>160</v>
@@ -20575,7 +20588,7 @@
         <v>171</v>
       </c>
       <c r="V260" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W260">
         <v>3</v>
@@ -20590,18 +20603,18 @@
         <v>160</v>
       </c>
       <c r="AH260" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI260" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B261" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
@@ -20613,7 +20626,7 @@
         <v>54</v>
       </c>
       <c r="F261" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G261">
         <v>5989</v>
@@ -20637,7 +20650,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>18164516</v>
+        <v>17952569</v>
       </c>
       <c r="S261" t="s">
         <v>160</v>
@@ -20646,13 +20659,13 @@
         <v>171</v>
       </c>
       <c r="V261" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W261">
         <v>3</v>
       </c>
       <c r="X261" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB261">
         <v>0</v>
@@ -20661,24 +20674,24 @@
         <v>160</v>
       </c>
       <c r="AH261" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI261" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B262" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
       </c>
       <c r="D262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E262" t="s">
         <v>54</v>
@@ -20708,7 +20721,7 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>18178157</v>
+        <v>18164516</v>
       </c>
       <c r="S262" t="s">
         <v>160</v>
@@ -20717,13 +20730,13 @@
         <v>171</v>
       </c>
       <c r="V262" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W262">
         <v>3</v>
       </c>
       <c r="X262" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB262">
         <v>0</v>
@@ -20732,45 +20745,45 @@
         <v>160</v>
       </c>
       <c r="AH262" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI262" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B263" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
       </c>
       <c r="D263" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E263" t="s">
         <v>54</v>
       </c>
       <c r="F263" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G263">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H263">
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J263" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N263" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P263">
         <v>9</v>
@@ -20779,48 +20792,48 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>17941187</v>
+        <v>18178157</v>
       </c>
       <c r="S263" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="U263" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V263" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W263">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X263" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AB263">
         <v>0</v>
       </c>
       <c r="AC263" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="AH263" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI263" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B264" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E264" t="s">
         <v>54</v>
@@ -20850,7 +20863,7 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>17952400</v>
+        <v>17941187</v>
       </c>
       <c r="S264" t="s">
         <v>54</v>
@@ -20859,13 +20872,13 @@
         <v>173</v>
       </c>
       <c r="V264" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W264">
         <v>2</v>
       </c>
       <c r="X264" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB264">
         <v>0</v>
@@ -20874,24 +20887,24 @@
         <v>54</v>
       </c>
       <c r="AH264" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI264" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B265" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E265" t="s">
         <v>54</v>
@@ -20921,7 +20934,7 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>17952580</v>
+        <v>17952400</v>
       </c>
       <c r="S265" t="s">
         <v>54</v>
@@ -20930,7 +20943,7 @@
         <v>173</v>
       </c>
       <c r="V265" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W265">
         <v>2</v>
@@ -20945,18 +20958,18 @@
         <v>54</v>
       </c>
       <c r="AH265" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI265" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B266" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
@@ -20968,7 +20981,7 @@
         <v>54</v>
       </c>
       <c r="F266" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G266">
         <v>6215</v>
@@ -20992,7 +21005,7 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>18164523</v>
+        <v>17952580</v>
       </c>
       <c r="S266" t="s">
         <v>54</v>
@@ -21001,13 +21014,13 @@
         <v>173</v>
       </c>
       <c r="V266" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W266">
         <v>2</v>
       </c>
       <c r="X266" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB266">
         <v>0</v>
@@ -21016,24 +21029,24 @@
         <v>54</v>
       </c>
       <c r="AH266" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI266" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B267" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
       </c>
       <c r="D267" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E267" t="s">
         <v>54</v>
@@ -21063,42 +21076,42 @@
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>18178163</v>
+        <v>18164523</v>
       </c>
       <c r="S267" t="s">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="U267" t="s">
         <v>173</v>
       </c>
       <c r="V267" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W267">
         <v>2</v>
       </c>
       <c r="X267" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB267">
         <v>0</v>
       </c>
       <c r="AC267" t="s">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="AH267" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AI267" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B268" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
@@ -21110,10 +21123,10 @@
         <v>54</v>
       </c>
       <c r="F268" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G268">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -21122,34 +21135,34 @@
         <v>65</v>
       </c>
       <c r="J268" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="N268" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P268">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q268">
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>17994311</v>
+        <v>18178163</v>
       </c>
       <c r="S268" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U268" t="s">
         <v>173</v>
       </c>
       <c r="V268" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X268" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AB268">
         <v>0</v>
@@ -21158,24 +21171,24 @@
         <v>161</v>
       </c>
       <c r="AH268" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AI268" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B269" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
       </c>
       <c r="D269" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E269" t="s">
         <v>54</v>
@@ -21205,7 +21218,7 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>17994675</v>
+        <v>17994311</v>
       </c>
       <c r="S269" t="s">
         <v>54</v>
@@ -21214,13 +21227,13 @@
         <v>173</v>
       </c>
       <c r="V269" s="1">
-        <v>46275.31747032407</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W269">
         <v>1</v>
       </c>
       <c r="X269" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21229,24 +21242,24 @@
         <v>161</v>
       </c>
       <c r="AH269" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI269" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B270" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
       </c>
       <c r="D270" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E270" t="s">
         <v>54</v>
@@ -21276,7 +21289,7 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>17994809</v>
+        <v>17994675</v>
       </c>
       <c r="S270" t="s">
         <v>54</v>
@@ -21285,13 +21298,13 @@
         <v>173</v>
       </c>
       <c r="V270" s="1">
-        <v>46275.31747981482</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W270">
         <v>1</v>
       </c>
       <c r="X270" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21300,18 +21313,18 @@
         <v>161</v>
       </c>
       <c r="AH270" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI270" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B271" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
@@ -21347,7 +21360,7 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>18006051</v>
+        <v>17994809</v>
       </c>
       <c r="S271" t="s">
         <v>54</v>
@@ -21356,13 +21369,13 @@
         <v>173</v>
       </c>
       <c r="V271" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W271">
         <v>1</v>
       </c>
       <c r="X271" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AB271">
         <v>0</v>
@@ -21371,27 +21384,27 @@
         <v>161</v>
       </c>
       <c r="AH271" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI271" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B272" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
       </c>
       <c r="D272" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E272" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F272" t="s">
         <v>56</v>
@@ -21418,22 +21431,22 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>18003256</v>
+        <v>18006051</v>
       </c>
       <c r="S272" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U272" t="s">
         <v>173</v>
       </c>
       <c r="V272" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W272">
         <v>1</v>
       </c>
       <c r="X272" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AB272">
         <v>0</v>
@@ -21442,27 +21455,27 @@
         <v>161</v>
       </c>
       <c r="AH272" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI272" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B273" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
       </c>
       <c r="D273" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E273" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F273" t="s">
         <v>56</v>
@@ -21489,22 +21502,22 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>18004017</v>
+        <v>18003256</v>
       </c>
       <c r="S273" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U273" t="s">
         <v>173</v>
       </c>
       <c r="V273" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W273">
         <v>1</v>
       </c>
       <c r="X273" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AB273">
         <v>0</v>
@@ -21513,24 +21526,24 @@
         <v>161</v>
       </c>
       <c r="AH273" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI273" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B274" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
       </c>
       <c r="D274" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E274" t="s">
         <v>54</v>
@@ -21560,7 +21573,7 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>17995164</v>
+        <v>18004017</v>
       </c>
       <c r="S274" t="s">
         <v>54</v>
@@ -21569,13 +21582,13 @@
         <v>173</v>
       </c>
       <c r="V274" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W274">
         <v>1</v>
       </c>
       <c r="X274" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB274">
         <v>0</v>
@@ -21584,24 +21597,24 @@
         <v>161</v>
       </c>
       <c r="AH274" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI274" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B275" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
       </c>
       <c r="D275" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E275" t="s">
         <v>54</v>
@@ -21631,7 +21644,7 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18004028</v>
+        <v>17995164</v>
       </c>
       <c r="S275" t="s">
         <v>54</v>
@@ -21640,7 +21653,7 @@
         <v>173</v>
       </c>
       <c r="V275" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W275">
         <v>1</v>
@@ -21655,24 +21668,24 @@
         <v>161</v>
       </c>
       <c r="AH275" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI275" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B276" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -21681,7 +21694,7 @@
         <v>56</v>
       </c>
       <c r="G276">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -21690,57 +21703,54 @@
         <v>65</v>
       </c>
       <c r="J276" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="N276" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P276">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q276">
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>17399329</v>
+        <v>18004028</v>
       </c>
       <c r="S276" t="s">
         <v>54</v>
       </c>
       <c r="U276" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750599537</v>
       </c>
       <c r="W276">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X276" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y276" t="s">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="AB276">
         <v>0</v>
       </c>
       <c r="AC276" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH276" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI276" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
@@ -21755,7 +21765,7 @@
         <v>56</v>
       </c>
       <c r="G277">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -21764,7 +21774,7 @@
         <v>65</v>
       </c>
       <c r="J277" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="N277" s="1">
         <v>46259</v>
@@ -21776,7 +21786,7 @@
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>16976320</v>
+        <v>17399329</v>
       </c>
       <c r="S277" t="s">
         <v>54</v>
@@ -21785,13 +21795,13 @@
         <v>171</v>
       </c>
       <c r="V277" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.5810894676</v>
       </c>
       <c r="W277">
         <v>17</v>
       </c>
       <c r="X277" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y277" t="s">
         <v>268</v>
@@ -21803,18 +21813,18 @@
         <v>54</v>
       </c>
       <c r="AH277" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AI277" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B278" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
@@ -21823,52 +21833,49 @@
         <v>51</v>
       </c>
       <c r="E278" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F278" t="s">
         <v>56</v>
       </c>
       <c r="G278">
-        <v>11056</v>
+        <v>9774</v>
       </c>
       <c r="H278">
         <v>0</v>
       </c>
       <c r="I278" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J278" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N278" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O278" t="s">
-        <v>137</v>
+        <v>46259</v>
       </c>
       <c r="P278">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q278">
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>18270269</v>
+        <v>16976320</v>
       </c>
       <c r="S278" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="U278" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V278" s="1">
-        <v>46276.41675075232</v>
+        <v>46275.58158541666</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X278" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="Y278" t="s">
         <v>269</v>
@@ -21877,13 +21884,90 @@
         <v>0</v>
       </c>
       <c r="AC278" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH278" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI278" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="279" spans="1:35">
+      <c r="A279">
+        <v>6627</v>
+      </c>
+      <c r="B279" t="s">
+        <v>36</v>
+      </c>
+      <c r="C279" t="s">
+        <v>50</v>
+      </c>
+      <c r="D279" t="s">
+        <v>51</v>
+      </c>
+      <c r="E279" t="s">
+        <v>55</v>
+      </c>
+      <c r="F279" t="s">
+        <v>56</v>
+      </c>
+      <c r="G279">
+        <v>11056</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279" t="s">
+        <v>66</v>
+      </c>
+      <c r="J279" t="s">
+        <v>122</v>
+      </c>
+      <c r="N279" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O279" t="s">
+        <v>137</v>
+      </c>
+      <c r="P279">
+        <v>8</v>
+      </c>
+      <c r="Q279">
+        <v>2026</v>
+      </c>
+      <c r="R279">
+        <v>18270269</v>
+      </c>
+      <c r="S279" t="s">
         <v>162</v>
       </c>
-      <c r="AH278" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI278" t="s">
-        <v>277</v>
+      <c r="U279" t="s">
+        <v>173</v>
+      </c>
+      <c r="V279" s="1">
+        <v>46276.41675075232</v>
+      </c>
+      <c r="W279">
+        <v>0</v>
+      </c>
+      <c r="X279" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y279" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB279">
+        <v>0</v>
+      </c>
+      <c r="AC279" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH279" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI279" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4103" uniqueCount="286">
   <si>
     <t>CodCliente</t>
   </si>
@@ -797,7 +797,16 @@
 Aguardando informações do cliente se haverá lançamentos para a realização dos cálculos, - Data Comentário: 09/09/2026 09:45</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 11/09/2026 08:57</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 11/09/2026 - Data Comentário: 11/09/2026 09:41</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 04/09/2026 17:02</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 04/09/2026 16:38</t>
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 09/09/2026 08:35</t>
@@ -1219,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI286"/>
+  <dimension ref="A1:AI289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1400,10 +1409,10 @@
         <v>139</v>
       </c>
       <c r="AH2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1477,10 +1486,10 @@
         <v>140</v>
       </c>
       <c r="AH3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1554,10 +1563,10 @@
         <v>139</v>
       </c>
       <c r="AH4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1628,10 +1637,10 @@
         <v>139</v>
       </c>
       <c r="AH5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1702,10 +1711,10 @@
         <v>140</v>
       </c>
       <c r="AH6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1776,10 +1785,10 @@
         <v>140</v>
       </c>
       <c r="AH7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1850,10 +1859,10 @@
         <v>141</v>
       </c>
       <c r="AH8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1924,10 +1933,10 @@
         <v>139</v>
       </c>
       <c r="AH9" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI9" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -1998,10 +2007,10 @@
         <v>142</v>
       </c>
       <c r="AH10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2072,10 +2081,10 @@
         <v>142</v>
       </c>
       <c r="AH11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2146,10 +2155,10 @@
         <v>143</v>
       </c>
       <c r="AH12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2217,13 +2226,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AH13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2291,13 +2300,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AH14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2365,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI15" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2430,10 +2439,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI16" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2501,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2578,10 +2587,10 @@
         <v>145</v>
       </c>
       <c r="AH18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2655,10 +2664,10 @@
         <v>144</v>
       </c>
       <c r="AH19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2732,10 +2741,10 @@
         <v>145</v>
       </c>
       <c r="AH20" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2809,10 +2818,10 @@
         <v>143</v>
       </c>
       <c r="AH21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2883,10 +2892,10 @@
         <v>146</v>
       </c>
       <c r="AH22" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2957,10 +2966,10 @@
         <v>143</v>
       </c>
       <c r="AH23" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI23" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3031,10 +3040,10 @@
         <v>143</v>
       </c>
       <c r="AH24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3105,10 +3114,10 @@
         <v>143</v>
       </c>
       <c r="AH25" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI25" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3179,10 +3188,10 @@
         <v>144</v>
       </c>
       <c r="AH26" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI26" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3253,10 +3262,10 @@
         <v>143</v>
       </c>
       <c r="AH27" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3327,10 +3336,10 @@
         <v>143</v>
       </c>
       <c r="AH28" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI28" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3401,10 +3410,10 @@
         <v>143</v>
       </c>
       <c r="AH29" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI29" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3475,10 +3484,10 @@
         <v>147</v>
       </c>
       <c r="AH30" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI30" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3555,10 +3564,10 @@
         <v>148</v>
       </c>
       <c r="AH31" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI31" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3629,10 +3638,10 @@
         <v>149</v>
       </c>
       <c r="AH32" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI32" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3709,10 +3718,10 @@
         <v>150</v>
       </c>
       <c r="AH33" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI33" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3786,10 +3795,10 @@
         <v>151</v>
       </c>
       <c r="AH34" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI34" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3863,13 +3872,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AH35" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI35" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3946,10 +3955,10 @@
         <v>153</v>
       </c>
       <c r="AH36" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI36" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4026,10 +4035,10 @@
         <v>147</v>
       </c>
       <c r="AH37" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI37" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4103,10 +4112,10 @@
         <v>170</v>
       </c>
       <c r="AH38" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI38" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4183,10 +4192,10 @@
         <v>148</v>
       </c>
       <c r="AH39" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI39" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4263,10 +4272,10 @@
         <v>148</v>
       </c>
       <c r="AH40" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI40" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4343,10 +4352,10 @@
         <v>148</v>
       </c>
       <c r="AH41" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI41" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4423,10 +4432,10 @@
         <v>147</v>
       </c>
       <c r="AH42" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI42" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4503,10 +4512,10 @@
         <v>154</v>
       </c>
       <c r="AH43" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI43" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4583,10 +4592,10 @@
         <v>149</v>
       </c>
       <c r="AH44" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI44" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4663,10 +4672,10 @@
         <v>150</v>
       </c>
       <c r="AH45" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI45" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4734,10 +4743,10 @@
         <v>151</v>
       </c>
       <c r="AH46" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI46" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4808,10 +4817,10 @@
         <v>148</v>
       </c>
       <c r="AH47" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI47" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4882,10 +4891,10 @@
         <v>148</v>
       </c>
       <c r="AH48" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI48" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4956,10 +4965,10 @@
         <v>148</v>
       </c>
       <c r="AH49" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI49" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5030,10 +5039,10 @@
         <v>147</v>
       </c>
       <c r="AH50" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI50" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5104,10 +5113,10 @@
         <v>154</v>
       </c>
       <c r="AH51" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI51" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5184,10 +5193,10 @@
         <v>149</v>
       </c>
       <c r="AH52" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI52" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5258,10 +5267,10 @@
         <v>150</v>
       </c>
       <c r="AH53" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI53" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5338,10 +5347,10 @@
         <v>148</v>
       </c>
       <c r="AH54" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI54" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5418,10 +5427,10 @@
         <v>148</v>
       </c>
       <c r="AH55" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI55" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5498,10 +5507,10 @@
         <v>148</v>
       </c>
       <c r="AH56" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI56" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5578,10 +5587,10 @@
         <v>147</v>
       </c>
       <c r="AH57" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI57" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5655,10 +5664,10 @@
         <v>151</v>
       </c>
       <c r="AH58" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI58" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5732,13 +5741,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AH59" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI59" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5815,10 +5824,10 @@
         <v>148</v>
       </c>
       <c r="AH60" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI60" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5895,10 +5904,10 @@
         <v>148</v>
       </c>
       <c r="AH61" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI61" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -5975,10 +5984,10 @@
         <v>148</v>
       </c>
       <c r="AH62" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI62" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6055,10 +6064,10 @@
         <v>147</v>
       </c>
       <c r="AH63" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI63" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6135,10 +6144,10 @@
         <v>154</v>
       </c>
       <c r="AH64" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI64" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6215,10 +6224,10 @@
         <v>149</v>
       </c>
       <c r="AH65" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI65" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6295,10 +6304,10 @@
         <v>150</v>
       </c>
       <c r="AH66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI66" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6375,10 +6384,10 @@
         <v>148</v>
       </c>
       <c r="AH67" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI67" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6446,10 +6455,10 @@
         <v>151</v>
       </c>
       <c r="AH68" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI68" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6517,13 +6526,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AH69" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI69" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6594,10 +6603,10 @@
         <v>148</v>
       </c>
       <c r="AH70" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI70" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6668,10 +6677,10 @@
         <v>148</v>
       </c>
       <c r="AH71" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI71" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6742,10 +6751,10 @@
         <v>148</v>
       </c>
       <c r="AH72" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI72" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6816,10 +6825,10 @@
         <v>147</v>
       </c>
       <c r="AH73" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI73" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6890,10 +6899,10 @@
         <v>154</v>
       </c>
       <c r="AH74" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI74" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6964,10 +6973,10 @@
         <v>149</v>
       </c>
       <c r="AH75" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI75" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7038,10 +7047,10 @@
         <v>150</v>
       </c>
       <c r="AH76" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI76" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7112,10 +7121,10 @@
         <v>150</v>
       </c>
       <c r="AH77" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI77" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7186,10 +7195,10 @@
         <v>150</v>
       </c>
       <c r="AH78" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI78" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7260,10 +7269,10 @@
         <v>150</v>
       </c>
       <c r="AH79" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI79" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7334,10 +7343,10 @@
         <v>156</v>
       </c>
       <c r="AH80" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI80" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7408,10 +7417,10 @@
         <v>156</v>
       </c>
       <c r="AH81" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI81" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7482,10 +7491,10 @@
         <v>157</v>
       </c>
       <c r="AH82" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI82" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7556,10 +7565,10 @@
         <v>156</v>
       </c>
       <c r="AH83" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI83" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7630,10 +7639,10 @@
         <v>156</v>
       </c>
       <c r="AH84" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI84" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7704,10 +7713,10 @@
         <v>156</v>
       </c>
       <c r="AH85" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI85" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7772,10 +7781,10 @@
         <v>157</v>
       </c>
       <c r="AH86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI86" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7846,10 +7855,10 @@
         <v>156</v>
       </c>
       <c r="AH87" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI87" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7920,10 +7929,10 @@
         <v>156</v>
       </c>
       <c r="AH88" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI88" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -7994,10 +8003,10 @@
         <v>156</v>
       </c>
       <c r="AH89" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI89" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8062,10 +8071,10 @@
         <v>156</v>
       </c>
       <c r="AH90" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI90" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8130,10 +8139,10 @@
         <v>157</v>
       </c>
       <c r="AH91" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI91" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8204,10 +8213,10 @@
         <v>156</v>
       </c>
       <c r="AH92" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI92" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8278,10 +8287,10 @@
         <v>156</v>
       </c>
       <c r="AH93" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI93" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8352,10 +8361,10 @@
         <v>156</v>
       </c>
       <c r="AH94" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI94" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8420,10 +8429,10 @@
         <v>156</v>
       </c>
       <c r="AH95" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI95" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8488,10 +8497,10 @@
         <v>157</v>
       </c>
       <c r="AH96" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI96" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8562,10 +8571,10 @@
         <v>156</v>
       </c>
       <c r="AH97" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI97" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8636,10 +8645,10 @@
         <v>156</v>
       </c>
       <c r="AH98" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI98" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8710,10 +8719,10 @@
         <v>157</v>
       </c>
       <c r="AH99" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI99" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8790,10 +8799,10 @@
         <v>156</v>
       </c>
       <c r="AH100" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI100" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8861,10 +8870,10 @@
         <v>156</v>
       </c>
       <c r="AH101" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI101" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8935,10 +8944,10 @@
         <v>156</v>
       </c>
       <c r="AH102" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI102" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9009,10 +9018,10 @@
         <v>156</v>
       </c>
       <c r="AH103" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI103" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9083,10 +9092,10 @@
         <v>156</v>
       </c>
       <c r="AH104" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI104" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9151,10 +9160,10 @@
         <v>156</v>
       </c>
       <c r="AH105" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI105" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9219,10 +9228,10 @@
         <v>157</v>
       </c>
       <c r="AH106" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI106" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9293,10 +9302,10 @@
         <v>156</v>
       </c>
       <c r="AH107" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI107" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9367,10 +9376,10 @@
         <v>156</v>
       </c>
       <c r="AH108" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI108" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9438,10 +9447,10 @@
         <v>156</v>
       </c>
       <c r="AH109" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI109" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9512,10 +9521,10 @@
         <v>157</v>
       </c>
       <c r="AH110" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI110" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9583,10 +9592,10 @@
         <v>159</v>
       </c>
       <c r="AH111" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI111" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9657,10 +9666,10 @@
         <v>157</v>
       </c>
       <c r="AH112" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI112" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9731,10 +9740,10 @@
         <v>155</v>
       </c>
       <c r="AH113" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI113" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9802,10 +9811,10 @@
         <v>159</v>
       </c>
       <c r="AH114" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI114" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9876,10 +9885,10 @@
         <v>157</v>
       </c>
       <c r="AH115" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI115" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9950,10 +9959,10 @@
         <v>156</v>
       </c>
       <c r="AH116" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI116" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10024,10 +10033,10 @@
         <v>156</v>
       </c>
       <c r="AH117" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI117" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10098,10 +10107,10 @@
         <v>156</v>
       </c>
       <c r="AH118" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI118" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10166,10 +10175,10 @@
         <v>156</v>
       </c>
       <c r="AH119" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI119" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10234,10 +10243,10 @@
         <v>157</v>
       </c>
       <c r="AH120" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI120" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10308,10 +10317,10 @@
         <v>156</v>
       </c>
       <c r="AH121" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI121" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10382,10 +10391,10 @@
         <v>156</v>
       </c>
       <c r="AH122" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI122" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10456,10 +10465,10 @@
         <v>156</v>
       </c>
       <c r="AH123" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI123" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10524,10 +10533,10 @@
         <v>156</v>
       </c>
       <c r="AH124" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI124" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10592,10 +10601,10 @@
         <v>157</v>
       </c>
       <c r="AH125" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI125" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10672,10 +10681,10 @@
         <v>157</v>
       </c>
       <c r="AH126" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI126" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10752,10 +10761,10 @@
         <v>157</v>
       </c>
       <c r="AH127" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI127" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10826,10 +10835,10 @@
         <v>160</v>
       </c>
       <c r="AH128" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI128" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10900,10 +10909,10 @@
         <v>160</v>
       </c>
       <c r="AH129" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI129" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -10980,10 +10989,10 @@
         <v>160</v>
       </c>
       <c r="AH130" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI130" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11054,10 +11063,10 @@
         <v>160</v>
       </c>
       <c r="AH131" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI131" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11128,10 +11137,10 @@
         <v>160</v>
       </c>
       <c r="AH132" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI132" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11202,10 +11211,10 @@
         <v>160</v>
       </c>
       <c r="AH133" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI133" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11276,10 +11285,10 @@
         <v>160</v>
       </c>
       <c r="AH134" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI134" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11356,10 +11365,10 @@
         <v>160</v>
       </c>
       <c r="AH135" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI135" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11430,10 +11439,10 @@
         <v>160</v>
       </c>
       <c r="AH136" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI136" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11504,10 +11513,10 @@
         <v>160</v>
       </c>
       <c r="AH137" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI137" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11578,10 +11587,10 @@
         <v>160</v>
       </c>
       <c r="AH138" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI138" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11658,10 +11667,10 @@
         <v>160</v>
       </c>
       <c r="AH139" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI139" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11732,10 +11741,10 @@
         <v>160</v>
       </c>
       <c r="AH140" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI140" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11806,10 +11815,10 @@
         <v>160</v>
       </c>
       <c r="AH141" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI141" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11880,10 +11889,10 @@
         <v>160</v>
       </c>
       <c r="AH142" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI142" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11954,10 +11963,10 @@
         <v>160</v>
       </c>
       <c r="AH143" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI143" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12028,10 +12037,10 @@
         <v>160</v>
       </c>
       <c r="AH144" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI144" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12102,10 +12111,10 @@
         <v>160</v>
       </c>
       <c r="AH145" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI145" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12176,10 +12185,10 @@
         <v>160</v>
       </c>
       <c r="AH146" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI146" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12250,10 +12259,10 @@
         <v>160</v>
       </c>
       <c r="AH147" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI147" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12324,10 +12333,10 @@
         <v>160</v>
       </c>
       <c r="AH148" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12398,10 +12407,10 @@
         <v>160</v>
       </c>
       <c r="AH149" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI149" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12478,10 +12487,10 @@
         <v>160</v>
       </c>
       <c r="AH150" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI150" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12552,10 +12561,10 @@
         <v>160</v>
       </c>
       <c r="AH151" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI151" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12626,10 +12635,10 @@
         <v>160</v>
       </c>
       <c r="AH152" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI152" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12700,10 +12709,10 @@
         <v>160</v>
       </c>
       <c r="AH153" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI153" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12774,10 +12783,10 @@
         <v>161</v>
       </c>
       <c r="AH154" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI154" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12848,10 +12857,10 @@
         <v>161</v>
       </c>
       <c r="AH155" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI155" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12922,10 +12931,10 @@
         <v>161</v>
       </c>
       <c r="AH156" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI156" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -12996,10 +13005,10 @@
         <v>161</v>
       </c>
       <c r="AH157" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI157" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13070,10 +13079,10 @@
         <v>161</v>
       </c>
       <c r="AH158" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI158" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13144,10 +13153,10 @@
         <v>161</v>
       </c>
       <c r="AH159" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI159" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13218,10 +13227,10 @@
         <v>161</v>
       </c>
       <c r="AH160" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI160" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13292,10 +13301,10 @@
         <v>161</v>
       </c>
       <c r="AH161" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI161" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13366,10 +13375,10 @@
         <v>161</v>
       </c>
       <c r="AH162" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI162" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13440,10 +13449,10 @@
         <v>161</v>
       </c>
       <c r="AH163" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI163" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13514,10 +13523,10 @@
         <v>161</v>
       </c>
       <c r="AH164" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI164" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13588,10 +13597,10 @@
         <v>161</v>
       </c>
       <c r="AH165" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI165" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13662,10 +13671,10 @@
         <v>161</v>
       </c>
       <c r="AH166" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI166" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13736,10 +13745,10 @@
         <v>161</v>
       </c>
       <c r="AH167" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI167" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13810,10 +13819,10 @@
         <v>161</v>
       </c>
       <c r="AH168" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI168" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13887,10 +13896,10 @@
         <v>161</v>
       </c>
       <c r="AH169" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI169" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13964,10 +13973,10 @@
         <v>161</v>
       </c>
       <c r="AH170" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI170" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14041,10 +14050,10 @@
         <v>161</v>
       </c>
       <c r="AH171" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI171" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14118,10 +14127,10 @@
         <v>161</v>
       </c>
       <c r="AH172" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI172" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14195,10 +14204,10 @@
         <v>161</v>
       </c>
       <c r="AH173" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI173" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14272,10 +14281,10 @@
         <v>161</v>
       </c>
       <c r="AH174" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI174" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14349,10 +14358,10 @@
         <v>161</v>
       </c>
       <c r="AH175" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI175" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14426,10 +14435,10 @@
         <v>161</v>
       </c>
       <c r="AH176" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI176" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14503,10 +14512,10 @@
         <v>161</v>
       </c>
       <c r="AH177" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI177" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14580,10 +14589,10 @@
         <v>161</v>
       </c>
       <c r="AH178" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI178" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14657,10 +14666,10 @@
         <v>161</v>
       </c>
       <c r="AH179" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI179" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14734,10 +14743,10 @@
         <v>161</v>
       </c>
       <c r="AH180" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI180" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14811,10 +14820,10 @@
         <v>161</v>
       </c>
       <c r="AH181" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI181" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14888,10 +14897,10 @@
         <v>161</v>
       </c>
       <c r="AH182" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI182" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14959,10 +14968,10 @@
         <v>161</v>
       </c>
       <c r="AH183" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI183" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15030,10 +15039,10 @@
         <v>161</v>
       </c>
       <c r="AH184" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI184" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15101,10 +15110,10 @@
         <v>161</v>
       </c>
       <c r="AH185" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI185" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15172,10 +15181,10 @@
         <v>161</v>
       </c>
       <c r="AH186" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI186" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15243,10 +15252,10 @@
         <v>161</v>
       </c>
       <c r="AH187" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI187" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15314,10 +15323,10 @@
         <v>161</v>
       </c>
       <c r="AH188" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI188" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15385,10 +15394,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI189" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15456,10 +15465,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI190" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15527,10 +15536,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI191" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15598,10 +15607,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI192" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15669,10 +15678,10 @@
         <v>162</v>
       </c>
       <c r="AH193" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI193" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15740,10 +15749,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI194" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15811,10 +15820,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI195" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15882,10 +15891,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI196" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15953,10 +15962,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI197" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16024,10 +16033,10 @@
         <v>162</v>
       </c>
       <c r="AH198" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI198" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16095,10 +16104,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI199" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16166,10 +16175,10 @@
         <v>162</v>
       </c>
       <c r="AH200" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI200" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16237,10 +16246,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI201" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16308,10 +16317,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI202" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16379,10 +16388,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI203" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16450,10 +16459,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI204" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16521,10 +16530,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI205" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16592,10 +16601,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI206" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16663,10 +16672,10 @@
         <v>162</v>
       </c>
       <c r="AH207" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI207" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16734,10 +16743,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI208" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16808,10 +16817,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI209" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16882,10 +16891,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI210" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16956,10 +16965,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI211" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17030,10 +17039,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI212" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17101,10 +17110,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI213" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17172,10 +17181,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI214" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17240,10 +17249,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI215" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17305,10 +17314,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI216" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17379,10 +17388,10 @@
         <v>163</v>
       </c>
       <c r="AH217" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI217" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17456,10 +17465,10 @@
         <v>151</v>
       </c>
       <c r="AH218" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI218" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17536,10 +17545,10 @@
         <v>148</v>
       </c>
       <c r="AH219" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI219" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17616,10 +17625,10 @@
         <v>148</v>
       </c>
       <c r="AH220" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI220" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17696,10 +17705,10 @@
         <v>154</v>
       </c>
       <c r="AH221" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI221" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17776,10 +17785,10 @@
         <v>149</v>
       </c>
       <c r="AH222" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI222" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17850,10 +17859,10 @@
         <v>150</v>
       </c>
       <c r="AH223" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI223" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17927,10 +17936,10 @@
         <v>154</v>
       </c>
       <c r="AH224" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI224" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18001,10 +18010,10 @@
         <v>148</v>
       </c>
       <c r="AH225" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI225" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18075,10 +18084,10 @@
         <v>148</v>
       </c>
       <c r="AH226" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI226" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18146,18 +18155,18 @@
         <v>159</v>
       </c>
       <c r="AH227" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI227" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B228" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
@@ -18166,7 +18175,7 @@
         <v>51</v>
       </c>
       <c r="E228" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F228" t="s">
         <v>56</v>
@@ -18186,6 +18195,9 @@
       <c r="N228" s="1">
         <v>46276</v>
       </c>
+      <c r="O228" t="s">
+        <v>137</v>
+      </c>
       <c r="P228">
         <v>8</v>
       </c>
@@ -18193,10 +18205,10 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>18085519</v>
+        <v>17222743</v>
       </c>
       <c r="S228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T228" t="s">
         <v>156</v>
@@ -18205,45 +18217,48 @@
         <v>174</v>
       </c>
       <c r="V228" s="1">
-        <v>46276.40669469907</v>
+        <v>46276.66923222222</v>
       </c>
       <c r="W228">
         <v>0</v>
       </c>
       <c r="X228" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="Y228" t="s">
+        <v>254</v>
       </c>
       <c r="AB228">
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH228" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI228" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B229" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E229" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F229" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G229">
         <v>6805</v>
@@ -18260,9 +18275,6 @@
       <c r="N229" s="1">
         <v>46276</v>
       </c>
-      <c r="O229" t="s">
-        <v>137</v>
-      </c>
       <c r="P229">
         <v>8</v>
       </c>
@@ -18270,51 +18282,51 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>18220221</v>
+        <v>18085519</v>
       </c>
       <c r="S229" t="s">
-        <v>159</v>
+        <v>156</v>
+      </c>
+      <c r="T229" t="s">
+        <v>156</v>
       </c>
       <c r="U229" t="s">
         <v>174</v>
       </c>
       <c r="V229" s="1">
-        <v>46276.39101108797</v>
+        <v>46276.40669469907</v>
       </c>
       <c r="W229">
         <v>0</v>
       </c>
       <c r="X229" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y229" t="s">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AH229" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI229" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B230" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
       </c>
       <c r="D230" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E230" t="s">
         <v>55</v>
@@ -18323,7 +18335,7 @@
         <v>56</v>
       </c>
       <c r="G230">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -18332,10 +18344,13 @@
         <v>62</v>
       </c>
       <c r="J230" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N230" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O230" t="s">
+        <v>137</v>
       </c>
       <c r="P230">
         <v>8</v>
@@ -18344,7 +18359,7 @@
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>17968368</v>
+        <v>17988709</v>
       </c>
       <c r="S230" t="s">
         <v>156</v>
@@ -18356,10 +18371,10 @@
         <v>174</v>
       </c>
       <c r="V230" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.64773491898</v>
       </c>
       <c r="W230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X230" t="s">
         <v>176</v>
@@ -18374,24 +18389,24 @@
         <v>156</v>
       </c>
       <c r="AH230" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI230" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B231" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
@@ -18400,7 +18415,7 @@
         <v>57</v>
       </c>
       <c r="G231">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -18409,10 +18424,13 @@
         <v>62</v>
       </c>
       <c r="J231" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N231" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O231" t="s">
+        <v>137</v>
       </c>
       <c r="P231">
         <v>8</v>
@@ -18421,25 +18439,22 @@
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>18186946</v>
+        <v>18220221</v>
       </c>
       <c r="S231" t="s">
-        <v>158</v>
-      </c>
-      <c r="T231" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U231" t="s">
         <v>174</v>
       </c>
       <c r="V231" s="1">
-        <v>46274.66470667824</v>
+        <v>46276.39101108797</v>
       </c>
       <c r="W231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X231" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y231" t="s">
         <v>256</v>
@@ -18448,13 +18463,13 @@
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AH231" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI231" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18477,7 +18492,7 @@
         <v>57</v>
       </c>
       <c r="G232">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -18486,10 +18501,13 @@
         <v>62</v>
       </c>
       <c r="J232" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N232" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O232" t="s">
+        <v>137</v>
       </c>
       <c r="P232">
         <v>8</v>
@@ -18498,7 +18516,7 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>18187212</v>
+        <v>18187261</v>
       </c>
       <c r="S232" t="s">
         <v>158</v>
@@ -18510,10 +18528,10 @@
         <v>174</v>
       </c>
       <c r="V232" s="1">
-        <v>46274.74452168981</v>
+        <v>46276.66651596065</v>
       </c>
       <c r="W232">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X232" t="s">
         <v>179</v>
@@ -18528,18 +18546,18 @@
         <v>158</v>
       </c>
       <c r="AH232" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI232" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B233" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
@@ -18548,13 +18566,13 @@
         <v>51</v>
       </c>
       <c r="E233" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F233" t="s">
         <v>56</v>
       </c>
       <c r="G233">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -18563,14 +18581,11 @@
         <v>62</v>
       </c>
       <c r="J233" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N233" s="1">
         <v>46274</v>
       </c>
-      <c r="O233" t="s">
-        <v>136</v>
-      </c>
       <c r="P233">
         <v>8</v>
       </c>
@@ -18578,10 +18593,10 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>17988543</v>
+        <v>17968368</v>
       </c>
       <c r="S233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T233" t="s">
         <v>156</v>
@@ -18590,13 +18605,13 @@
         <v>174</v>
       </c>
       <c r="V233" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W233">
         <v>2</v>
       </c>
       <c r="X233" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y233" t="s">
         <v>258</v>
@@ -18605,36 +18620,36 @@
         <v>0</v>
       </c>
       <c r="AC233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH233" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI233" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B234" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
       </c>
       <c r="D234" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E234" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F234" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G234">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -18643,7 +18658,7 @@
         <v>62</v>
       </c>
       <c r="J234" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N234" s="1">
         <v>46274</v>
@@ -18655,10 +18670,10 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>17968379</v>
+        <v>18186946</v>
       </c>
       <c r="S234" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="T234" t="s">
         <v>156</v>
@@ -18667,39 +18682,42 @@
         <v>174</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W234">
         <v>2</v>
       </c>
       <c r="X234" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="Y234" t="s">
+        <v>259</v>
       </c>
       <c r="AB234">
         <v>0</v>
       </c>
       <c r="AC234" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AH234" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI234" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B235" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
       </c>
       <c r="D235" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E235" t="s">
         <v>54</v>
@@ -18708,7 +18726,7 @@
         <v>57</v>
       </c>
       <c r="G235">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -18717,14 +18735,11 @@
         <v>62</v>
       </c>
       <c r="J235" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N235" s="1">
         <v>46274</v>
       </c>
-      <c r="O235" t="s">
-        <v>137</v>
-      </c>
       <c r="P235">
         <v>8</v>
       </c>
@@ -18732,57 +18747,60 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>18220182</v>
+        <v>18187212</v>
       </c>
       <c r="S235" t="s">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="T235" t="s">
+        <v>156</v>
       </c>
       <c r="U235" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V235" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W235">
         <v>2</v>
       </c>
       <c r="X235" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y235" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AB235">
         <v>0</v>
       </c>
       <c r="AC235" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AH235" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI235" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B236" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
       </c>
       <c r="F236" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G236">
         <v>1867</v>
@@ -18799,6 +18817,9 @@
       <c r="N236" s="1">
         <v>46274</v>
       </c>
+      <c r="O236" t="s">
+        <v>136</v>
+      </c>
       <c r="P236">
         <v>8</v>
       </c>
@@ -18806,10 +18827,10 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>18186953</v>
+        <v>17988543</v>
       </c>
       <c r="S236" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T236" t="s">
         <v>156</v>
@@ -18818,45 +18839,48 @@
         <v>174</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.7274781713</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W236">
         <v>2</v>
       </c>
       <c r="X236" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="Y236" t="s">
+        <v>261</v>
       </c>
       <c r="AB236">
         <v>0</v>
       </c>
       <c r="AC236" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AH236" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI236" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B237" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E237" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F237" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G237">
         <v>1867</v>
@@ -18880,10 +18904,10 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>18187219</v>
+        <v>17968379</v>
       </c>
       <c r="S237" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T237" t="s">
         <v>156</v>
@@ -18892,39 +18916,39 @@
         <v>174</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W237">
         <v>2</v>
       </c>
       <c r="X237" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB237">
         <v>0</v>
       </c>
       <c r="AC237" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH237" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI237" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B238" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
       </c>
       <c r="D238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
@@ -18933,19 +18957,22 @@
         <v>57</v>
       </c>
       <c r="G238">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H238">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I238" t="s">
         <v>62</v>
       </c>
       <c r="J238" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N238" s="1">
-        <v>46275</v>
+        <v>46274</v>
+      </c>
+      <c r="O238" t="s">
+        <v>137</v>
       </c>
       <c r="P238">
         <v>8</v>
@@ -18954,72 +18981,72 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>18214907</v>
+        <v>18220182</v>
       </c>
       <c r="S238" t="s">
-        <v>157</v>
-      </c>
-      <c r="T238" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U238" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V238" s="1">
-        <v>46275.79245582176</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X238" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="Y238" t="s">
+        <v>262</v>
       </c>
       <c r="AB238">
         <v>0</v>
       </c>
       <c r="AC238" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AH238" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI238" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B239" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
       </c>
       <c r="D239" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E239" t="s">
         <v>54</v>
       </c>
       <c r="F239" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G239">
-        <v>6806</v>
+        <v>1867</v>
       </c>
       <c r="H239">
         <v>0</v>
       </c>
       <c r="I239" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J239" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N239" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="P239">
         <v>8</v>
@@ -19028,45 +19055,45 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>17399230</v>
+        <v>18186953</v>
       </c>
       <c r="S239" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T239" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="U239" t="s">
         <v>174</v>
       </c>
       <c r="V239" s="1">
-        <v>46276.49596842592</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X239" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AB239">
         <v>0</v>
       </c>
       <c r="AC239" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH239" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AI239" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6404</v>
+        <v>6963</v>
       </c>
       <c r="B240" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
@@ -19078,22 +19105,22 @@
         <v>54</v>
       </c>
       <c r="F240" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G240">
-        <v>6806</v>
+        <v>1867</v>
       </c>
       <c r="H240">
         <v>0</v>
       </c>
       <c r="I240" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J240" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N240" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="P240">
         <v>8</v>
@@ -19102,45 +19129,45 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>16962308</v>
+        <v>18187219</v>
       </c>
       <c r="S240" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T240" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="U240" t="s">
         <v>174</v>
       </c>
       <c r="V240" s="1">
-        <v>46276.53874935185</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X240" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="AB240">
         <v>0</v>
       </c>
       <c r="AC240" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH240" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AI240" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="241" spans="1:35">
       <c r="A241">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B241" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C241" t="s">
         <v>50</v>
@@ -19152,22 +19179,22 @@
         <v>54</v>
       </c>
       <c r="F241" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G241">
-        <v>6806</v>
+        <v>6886</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I241" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J241" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N241" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="P241">
         <v>8</v>
@@ -19176,51 +19203,51 @@
         <v>2026</v>
       </c>
       <c r="R241">
-        <v>16976187</v>
+        <v>18214907</v>
       </c>
       <c r="S241" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="T241" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="U241" t="s">
         <v>174</v>
       </c>
       <c r="V241" s="1">
-        <v>46276.49597027778</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X241" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AB241">
         <v>0</v>
       </c>
       <c r="AC241" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AH241" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AI241" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="242" spans="1:35">
       <c r="A242">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B242" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C242" t="s">
         <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E242" t="s">
         <v>54</v>
@@ -19250,7 +19277,7 @@
         <v>2026</v>
       </c>
       <c r="R242">
-        <v>17948858</v>
+        <v>17399230</v>
       </c>
       <c r="S242" t="s">
         <v>160</v>
@@ -19262,13 +19289,13 @@
         <v>174</v>
       </c>
       <c r="V242" s="1">
-        <v>46276.62604146991</v>
+        <v>46276.49596842592</v>
       </c>
       <c r="W242">
         <v>0</v>
       </c>
       <c r="X242" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AB242">
         <v>0</v>
@@ -19277,10 +19304,10 @@
         <v>160</v>
       </c>
       <c r="AH242" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI242" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19303,7 +19330,7 @@
         <v>56</v>
       </c>
       <c r="G243">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -19312,10 +19339,10 @@
         <v>63</v>
       </c>
       <c r="J243" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N243" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P243">
         <v>8</v>
@@ -19324,7 +19351,7 @@
         <v>2026</v>
       </c>
       <c r="R243">
-        <v>16962151</v>
+        <v>16962308</v>
       </c>
       <c r="S243" t="s">
         <v>160</v>
@@ -19333,13 +19360,13 @@
         <v>171</v>
       </c>
       <c r="U243" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="V243" s="1">
-        <v>46274.70622837963</v>
+        <v>46276.53874935185</v>
       </c>
       <c r="W243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X243" t="s">
         <v>185</v>
@@ -19351,24 +19378,24 @@
         <v>160</v>
       </c>
       <c r="AH243" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI243" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B244" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
@@ -19377,7 +19404,7 @@
         <v>56</v>
       </c>
       <c r="G244">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -19386,10 +19413,10 @@
         <v>63</v>
       </c>
       <c r="J244" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N244" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P244">
         <v>8</v>
@@ -19398,7 +19425,7 @@
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>17948756</v>
+        <v>16976187</v>
       </c>
       <c r="S244" t="s">
         <v>160</v>
@@ -19410,13 +19437,13 @@
         <v>174</v>
       </c>
       <c r="V244" s="1">
-        <v>46275.71996309028</v>
+        <v>46276.49597027778</v>
       </c>
       <c r="W244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X244" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AB244">
         <v>0</v>
@@ -19425,24 +19452,24 @@
         <v>160</v>
       </c>
       <c r="AH244" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI244" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B245" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
       </c>
       <c r="D245" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E245" t="s">
         <v>54</v>
@@ -19451,7 +19478,7 @@
         <v>56</v>
       </c>
       <c r="G245">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -19460,10 +19487,10 @@
         <v>63</v>
       </c>
       <c r="J245" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N245" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P245">
         <v>8</v>
@@ -19472,7 +19499,7 @@
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>18085143</v>
+        <v>17948858</v>
       </c>
       <c r="S245" t="s">
         <v>160</v>
@@ -19484,13 +19511,13 @@
         <v>174</v>
       </c>
       <c r="V245" s="1">
-        <v>46275.54278886574</v>
+        <v>46276.62604146991</v>
       </c>
       <c r="W245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X245" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AB245">
         <v>0</v>
@@ -19499,10 +19526,10 @@
         <v>160</v>
       </c>
       <c r="AH245" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AI245" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19525,7 +19552,7 @@
         <v>56</v>
       </c>
       <c r="G246">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -19534,7 +19561,7 @@
         <v>63</v>
       </c>
       <c r="J246" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N246" s="1">
         <v>46275</v>
@@ -19546,7 +19573,7 @@
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>16962161</v>
+        <v>16962151</v>
       </c>
       <c r="S246" t="s">
         <v>160</v>
@@ -19555,10 +19582,10 @@
         <v>171</v>
       </c>
       <c r="U246" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V246" s="1">
-        <v>46275.7000328588</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W246">
         <v>1</v>
@@ -19573,24 +19600,24 @@
         <v>160</v>
       </c>
       <c r="AH246" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI246" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B247" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19599,7 +19626,7 @@
         <v>56</v>
       </c>
       <c r="G247">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -19608,7 +19635,7 @@
         <v>63</v>
       </c>
       <c r="J247" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N247" s="1">
         <v>46275</v>
@@ -19620,7 +19647,7 @@
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>16975952</v>
+        <v>17948756</v>
       </c>
       <c r="S247" t="s">
         <v>160</v>
@@ -19632,13 +19659,13 @@
         <v>174</v>
       </c>
       <c r="V247" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W247">
         <v>1</v>
       </c>
       <c r="X247" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19647,24 +19674,24 @@
         <v>160</v>
       </c>
       <c r="AH247" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI247" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B248" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
       </c>
       <c r="D248" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -19673,7 +19700,7 @@
         <v>56</v>
       </c>
       <c r="G248">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -19682,7 +19709,7 @@
         <v>63</v>
       </c>
       <c r="J248" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N248" s="1">
         <v>46275</v>
@@ -19694,7 +19721,7 @@
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>17948766</v>
+        <v>18085143</v>
       </c>
       <c r="S248" t="s">
         <v>160</v>
@@ -19706,13 +19733,13 @@
         <v>174</v>
       </c>
       <c r="V248" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W248">
         <v>1</v>
       </c>
       <c r="X248" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AB248">
         <v>0</v>
@@ -19721,24 +19748,24 @@
         <v>160</v>
       </c>
       <c r="AH248" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI248" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="249" spans="1:35">
       <c r="A249">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B249" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C249" t="s">
         <v>50</v>
       </c>
       <c r="D249" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E249" t="s">
         <v>54</v>
@@ -19768,7 +19795,7 @@
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>18085154</v>
+        <v>16962161</v>
       </c>
       <c r="S249" t="s">
         <v>160</v>
@@ -19780,13 +19807,13 @@
         <v>174</v>
       </c>
       <c r="V249" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W249">
         <v>1</v>
       </c>
       <c r="X249" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AB249">
         <v>0</v>
@@ -19795,24 +19822,24 @@
         <v>160</v>
       </c>
       <c r="AH249" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI249" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="250" spans="1:35">
       <c r="A250">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B250" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C250" t="s">
         <v>50</v>
       </c>
       <c r="D250" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -19842,7 +19869,7 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>17948928</v>
+        <v>16975952</v>
       </c>
       <c r="S250" t="s">
         <v>160</v>
@@ -19854,13 +19881,13 @@
         <v>174</v>
       </c>
       <c r="V250" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W250">
         <v>1</v>
       </c>
       <c r="X250" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AB250">
         <v>0</v>
@@ -19869,24 +19896,24 @@
         <v>160</v>
       </c>
       <c r="AH250" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI250" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="251" spans="1:35">
       <c r="A251">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B251" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C251" t="s">
         <v>50</v>
       </c>
       <c r="D251" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E251" t="s">
         <v>54</v>
@@ -19916,7 +19943,7 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>18084955</v>
+        <v>17948766</v>
       </c>
       <c r="S251" t="s">
         <v>160</v>
@@ -19928,13 +19955,13 @@
         <v>174</v>
       </c>
       <c r="V251" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W251">
         <v>1</v>
       </c>
       <c r="X251" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AB251">
         <v>0</v>
@@ -19943,18 +19970,18 @@
         <v>160</v>
       </c>
       <c r="AH251" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI251" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B252" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
@@ -19969,7 +19996,7 @@
         <v>56</v>
       </c>
       <c r="G252">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -19978,13 +20005,10 @@
         <v>63</v>
       </c>
       <c r="J252" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N252" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O252" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P252">
         <v>8</v>
@@ -19993,7 +20017,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>17398955</v>
+        <v>18085154</v>
       </c>
       <c r="S252" t="s">
         <v>160</v>
@@ -20002,19 +20026,16 @@
         <v>171</v>
       </c>
       <c r="U252" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V252" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W252">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X252" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y252" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="AB252">
         <v>0</v>
@@ -20023,24 +20044,24 @@
         <v>160</v>
       </c>
       <c r="AH252" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI252" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B253" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E253" t="s">
         <v>54</v>
@@ -20049,7 +20070,7 @@
         <v>56</v>
       </c>
       <c r="G253">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -20058,13 +20079,10 @@
         <v>63</v>
       </c>
       <c r="J253" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N253" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O253" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P253">
         <v>8</v>
@@ -20073,7 +20091,7 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>18073098</v>
+        <v>17948928</v>
       </c>
       <c r="S253" t="s">
         <v>160</v>
@@ -20082,19 +20100,16 @@
         <v>171</v>
       </c>
       <c r="U253" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V253" s="1">
-        <v>46274.74838096065</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W253">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X253" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y253" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="AB253">
         <v>0</v>
@@ -20103,24 +20118,24 @@
         <v>160</v>
       </c>
       <c r="AH253" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI253" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
       </c>
       <c r="D254" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E254" t="s">
         <v>54</v>
@@ -20129,7 +20144,7 @@
         <v>56</v>
       </c>
       <c r="G254">
-        <v>11303</v>
+        <v>1793</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -20138,10 +20153,10 @@
         <v>63</v>
       </c>
       <c r="J254" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="N254" s="1">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="P254">
         <v>8</v>
@@ -20150,7 +20165,7 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>17399454</v>
+        <v>18084955</v>
       </c>
       <c r="S254" t="s">
         <v>160</v>
@@ -20159,19 +20174,16 @@
         <v>171</v>
       </c>
       <c r="U254" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="V254" s="1">
-        <v>46274.42878043981</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W254">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="X254" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y254" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="AB254">
         <v>0</v>
@@ -20180,18 +20192,18 @@
         <v>160</v>
       </c>
       <c r="AH254" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI254" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B255" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
@@ -20206,7 +20218,7 @@
         <v>56</v>
       </c>
       <c r="G255">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -20215,10 +20227,13 @@
         <v>63</v>
       </c>
       <c r="J255" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="N255" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O255" t="s">
+        <v>136</v>
       </c>
       <c r="P255">
         <v>8</v>
@@ -20227,7 +20242,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>16976351</v>
+        <v>17398955</v>
       </c>
       <c r="S255" t="s">
         <v>160</v>
@@ -20236,19 +20251,19 @@
         <v>171</v>
       </c>
       <c r="U255" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V255" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W255">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="X255" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y255" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AB255">
         <v>0</v>
@@ -20257,10 +20272,10 @@
         <v>160</v>
       </c>
       <c r="AH255" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI255" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20283,22 +20298,22 @@
         <v>56</v>
       </c>
       <c r="G256">
-        <v>950</v>
+        <v>1796</v>
       </c>
       <c r="H256">
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J256" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N256" s="1">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="O256" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P256">
         <v>8</v>
@@ -20307,19 +20322,22 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17941146</v>
+        <v>18073098</v>
       </c>
       <c r="S256" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T256" t="s">
+        <v>171</v>
       </c>
       <c r="U256" t="s">
         <v>172</v>
       </c>
       <c r="V256" s="1">
-        <v>46276.52399603009</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W256">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X256" t="s">
         <v>184</v>
@@ -20331,21 +20349,21 @@
         <v>0</v>
       </c>
       <c r="AC256" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH256" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AI256" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B257" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
@@ -20360,22 +20378,19 @@
         <v>56</v>
       </c>
       <c r="G257">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H257">
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J257" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N257" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O257" t="s">
-        <v>137</v>
+        <v>46279</v>
       </c>
       <c r="P257">
         <v>8</v>
@@ -20384,22 +20399,25 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>17952340</v>
+        <v>17399454</v>
       </c>
       <c r="S257" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T257" t="s">
+        <v>171</v>
       </c>
       <c r="U257" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V257" s="1">
-        <v>46276.5240703125</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W257">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="X257" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y257" t="s">
         <v>264</v>
@@ -20408,21 +20426,21 @@
         <v>0</v>
       </c>
       <c r="AC257" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH257" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AI257" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B258" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
@@ -20434,22 +20452,22 @@
         <v>54</v>
       </c>
       <c r="F258" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G258">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H258">
         <v>0</v>
       </c>
       <c r="I258" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J258" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N258" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="P258">
         <v>8</v>
@@ -20458,22 +20476,25 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>18178132</v>
+        <v>16976351</v>
       </c>
       <c r="S258" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T258" t="s">
+        <v>171</v>
       </c>
       <c r="U258" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V258" s="1">
-        <v>46275.4100730787</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W258">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="X258" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Y258" t="s">
         <v>265</v>
@@ -20482,21 +20503,21 @@
         <v>0</v>
       </c>
       <c r="AC258" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH258" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AI258" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6962</v>
+        <v>6703</v>
       </c>
       <c r="B259" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
@@ -20508,7 +20529,7 @@
         <v>54</v>
       </c>
       <c r="F259" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G259">
         <v>950</v>
@@ -20525,6 +20546,9 @@
       <c r="N259" s="1">
         <v>46275</v>
       </c>
+      <c r="O259" t="s">
+        <v>137</v>
+      </c>
       <c r="P259">
         <v>8</v>
       </c>
@@ -20532,22 +20556,22 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>18188717</v>
+        <v>17941146</v>
       </c>
       <c r="S259" t="s">
         <v>161</v>
       </c>
       <c r="U259" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V259" s="1">
-        <v>46275.40964188657</v>
+        <v>46276.52399603009</v>
       </c>
       <c r="W259">
         <v>1</v>
       </c>
       <c r="X259" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Y259" t="s">
         <v>266</v>
@@ -20559,30 +20583,30 @@
         <v>161</v>
       </c>
       <c r="AH259" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI259" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6963</v>
+        <v>6704</v>
       </c>
       <c r="B260" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E260" t="s">
         <v>54</v>
       </c>
       <c r="F260" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G260">
         <v>950</v>
@@ -20599,6 +20623,9 @@
       <c r="N260" s="1">
         <v>46275</v>
       </c>
+      <c r="O260" t="s">
+        <v>137</v>
+      </c>
       <c r="P260">
         <v>8</v>
       </c>
@@ -20606,22 +20633,22 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>18188623</v>
+        <v>17952340</v>
       </c>
       <c r="S260" t="s">
         <v>161</v>
       </c>
       <c r="U260" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V260" s="1">
-        <v>46275.40964245371</v>
+        <v>46276.5240703125</v>
       </c>
       <c r="W260">
         <v>1</v>
       </c>
       <c r="X260" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y260" t="s">
         <v>267</v>
@@ -20633,18 +20660,18 @@
         <v>161</v>
       </c>
       <c r="AH260" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI260" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B261" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
@@ -20656,10 +20683,10 @@
         <v>54</v>
       </c>
       <c r="F261" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G261">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -20668,7 +20695,7 @@
         <v>64</v>
       </c>
       <c r="J261" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N261" s="1">
         <v>46275</v>
@@ -20680,7 +20707,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>17222405</v>
+        <v>18178132</v>
       </c>
       <c r="S261" t="s">
         <v>161</v>
@@ -20689,13 +20716,13 @@
         <v>174</v>
       </c>
       <c r="V261" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W261">
         <v>1</v>
       </c>
       <c r="X261" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y261" t="s">
         <v>268</v>
@@ -20707,33 +20734,33 @@
         <v>161</v>
       </c>
       <c r="AH261" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI261" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B262" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
       </c>
       <c r="D262" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E262" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F262" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G262">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -20742,7 +20769,7 @@
         <v>64</v>
       </c>
       <c r="J262" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N262" s="1">
         <v>46275</v>
@@ -20754,7 +20781,7 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>16959950</v>
+        <v>18188717</v>
       </c>
       <c r="S262" t="s">
         <v>161</v>
@@ -20763,13 +20790,16 @@
         <v>174</v>
       </c>
       <c r="V262" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W262">
         <v>1</v>
       </c>
       <c r="X262" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="Y262" t="s">
+        <v>269</v>
       </c>
       <c r="AB262">
         <v>0</v>
@@ -20778,24 +20808,24 @@
         <v>161</v>
       </c>
       <c r="AH262" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI262" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B263" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
       </c>
       <c r="D263" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E263" t="s">
         <v>54</v>
@@ -20804,7 +20834,7 @@
         <v>57</v>
       </c>
       <c r="G263">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -20813,7 +20843,7 @@
         <v>64</v>
       </c>
       <c r="J263" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N263" s="1">
         <v>46275</v>
@@ -20825,7 +20855,7 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>18178138</v>
+        <v>18188623</v>
       </c>
       <c r="S263" t="s">
         <v>161</v>
@@ -20834,16 +20864,16 @@
         <v>174</v>
       </c>
       <c r="V263" s="1">
-        <v>46275.44975668981</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W263">
         <v>1</v>
       </c>
       <c r="X263" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y263" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AB263">
         <v>0</v>
@@ -20852,30 +20882,30 @@
         <v>161</v>
       </c>
       <c r="AH263" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI263" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B264" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E264" t="s">
         <v>54</v>
       </c>
       <c r="F264" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G264">
         <v>951</v>
@@ -20899,7 +20929,7 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>18188724</v>
+        <v>17222405</v>
       </c>
       <c r="S264" t="s">
         <v>161</v>
@@ -20908,16 +20938,16 @@
         <v>174</v>
       </c>
       <c r="V264" s="1">
-        <v>46275.44933692129</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W264">
         <v>1</v>
       </c>
       <c r="X264" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y264" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AB264">
         <v>0</v>
@@ -20926,30 +20956,30 @@
         <v>161</v>
       </c>
       <c r="AH264" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI264" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B265" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E265" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F265" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G265">
         <v>951</v>
@@ -20973,7 +21003,7 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>18188630</v>
+        <v>16959950</v>
       </c>
       <c r="S265" t="s">
         <v>161</v>
@@ -20982,16 +21012,13 @@
         <v>174</v>
       </c>
       <c r="V265" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W265">
         <v>1</v>
       </c>
       <c r="X265" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y265" t="s">
-        <v>271</v>
+        <v>176</v>
       </c>
       <c r="AB265">
         <v>0</v>
@@ -21000,33 +21027,33 @@
         <v>161</v>
       </c>
       <c r="AH265" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AI265" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B266" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
       </c>
       <c r="D266" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E266" t="s">
         <v>54</v>
       </c>
       <c r="F266" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G266">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -21035,34 +21062,37 @@
         <v>64</v>
       </c>
       <c r="J266" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N266" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P266">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q266">
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>17941177</v>
+        <v>18178138</v>
       </c>
       <c r="S266" t="s">
         <v>161</v>
       </c>
       <c r="U266" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V266" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W266">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X266" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="Y266" t="s">
+        <v>272</v>
       </c>
       <c r="AB266">
         <v>0</v>
@@ -21071,33 +21101,33 @@
         <v>161</v>
       </c>
       <c r="AH266" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AI266" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6704</v>
+        <v>6962</v>
       </c>
       <c r="B267" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
       </c>
       <c r="D267" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E267" t="s">
         <v>54</v>
       </c>
       <c r="F267" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G267">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -21106,34 +21136,37 @@
         <v>64</v>
       </c>
       <c r="J267" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N267" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P267">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q267">
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>17952385</v>
+        <v>18188724</v>
       </c>
       <c r="S267" t="s">
         <v>161</v>
       </c>
       <c r="U267" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V267" s="1">
-        <v>46274.41775447917</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W267">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X267" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+      <c r="Y267" t="s">
+        <v>273</v>
       </c>
       <c r="AB267">
         <v>0</v>
@@ -21142,33 +21175,33 @@
         <v>161</v>
       </c>
       <c r="AH267" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AI267" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>6705</v>
+        <v>6963</v>
       </c>
       <c r="B268" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
       </c>
       <c r="D268" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E268" t="s">
         <v>54</v>
       </c>
       <c r="F268" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G268">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -21177,34 +21210,37 @@
         <v>64</v>
       </c>
       <c r="J268" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N268" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q268">
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>17952569</v>
+        <v>18188630</v>
       </c>
       <c r="S268" t="s">
         <v>161</v>
       </c>
       <c r="U268" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V268" s="1">
-        <v>46274.41777533565</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W268">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X268" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+      <c r="Y268" t="s">
+        <v>274</v>
       </c>
       <c r="AB268">
         <v>0</v>
@@ -21213,30 +21249,30 @@
         <v>161</v>
       </c>
       <c r="AH268" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AI268" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B269" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
       </c>
       <c r="D269" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E269" t="s">
         <v>54</v>
       </c>
       <c r="F269" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G269">
         <v>5989</v>
@@ -21260,7 +21296,7 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>18164516</v>
+        <v>17941177</v>
       </c>
       <c r="S269" t="s">
         <v>161</v>
@@ -21269,13 +21305,13 @@
         <v>172</v>
       </c>
       <c r="V269" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W269">
         <v>3</v>
       </c>
       <c r="X269" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21284,18 +21320,18 @@
         <v>161</v>
       </c>
       <c r="AH269" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI269" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B270" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
@@ -21307,7 +21343,7 @@
         <v>54</v>
       </c>
       <c r="F270" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G270">
         <v>5989</v>
@@ -21331,7 +21367,7 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>18178157</v>
+        <v>17952385</v>
       </c>
       <c r="S270" t="s">
         <v>161</v>
@@ -21340,13 +21376,13 @@
         <v>172</v>
       </c>
       <c r="V270" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W270">
         <v>3</v>
       </c>
       <c r="X270" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21355,24 +21391,24 @@
         <v>161</v>
       </c>
       <c r="AH270" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI270" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B271" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
       </c>
       <c r="D271" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E271" t="s">
         <v>54</v>
@@ -21381,19 +21417,19 @@
         <v>56</v>
       </c>
       <c r="G271">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H271">
         <v>0</v>
       </c>
       <c r="I271" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J271" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N271" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P271">
         <v>9</v>
@@ -21402,69 +21438,69 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>17941187</v>
+        <v>17952569</v>
       </c>
       <c r="S271" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U271" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V271" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X271" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AB271">
         <v>0</v>
       </c>
       <c r="AC271" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH271" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI271" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B272" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
       </c>
       <c r="D272" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E272" t="s">
         <v>54</v>
       </c>
       <c r="F272" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G272">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H272">
         <v>0</v>
       </c>
       <c r="I272" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J272" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N272" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P272">
         <v>9</v>
@@ -21473,69 +21509,69 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>17952400</v>
+        <v>18164516</v>
       </c>
       <c r="S272" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U272" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V272" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X272" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AB272">
         <v>0</v>
       </c>
       <c r="AC272" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH272" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI272" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B273" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
       </c>
       <c r="D273" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E273" t="s">
         <v>54</v>
       </c>
       <c r="F273" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G273">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H273">
         <v>0</v>
       </c>
       <c r="I273" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J273" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N273" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P273">
         <v>9</v>
@@ -21544,54 +21580,54 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>17952580</v>
+        <v>18178157</v>
       </c>
       <c r="S273" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U273" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V273" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X273" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AB273">
         <v>0</v>
       </c>
       <c r="AC273" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH273" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI273" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B274" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
       </c>
       <c r="D274" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E274" t="s">
         <v>54</v>
       </c>
       <c r="F274" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G274">
         <v>6215</v>
@@ -21615,7 +21651,7 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>18164523</v>
+        <v>17941187</v>
       </c>
       <c r="S274" t="s">
         <v>54</v>
@@ -21624,13 +21660,13 @@
         <v>174</v>
       </c>
       <c r="V274" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W274">
         <v>2</v>
       </c>
       <c r="X274" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AB274">
         <v>0</v>
@@ -21639,18 +21675,18 @@
         <v>54</v>
       </c>
       <c r="AH274" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI274" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B275" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
@@ -21662,7 +21698,7 @@
         <v>54</v>
       </c>
       <c r="F275" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G275">
         <v>6215</v>
@@ -21686,48 +21722,48 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18178163</v>
+        <v>17952400</v>
       </c>
       <c r="S275" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="U275" t="s">
         <v>174</v>
       </c>
       <c r="V275" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W275">
         <v>2</v>
       </c>
       <c r="X275" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AB275">
         <v>0</v>
       </c>
       <c r="AC275" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH275" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AI275" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B276" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -21736,7 +21772,7 @@
         <v>56</v>
       </c>
       <c r="G276">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -21745,19 +21781,19 @@
         <v>65</v>
       </c>
       <c r="J276" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N276" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P276">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q276">
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>17994311</v>
+        <v>17952580</v>
       </c>
       <c r="S276" t="s">
         <v>54</v>
@@ -21766,48 +21802,48 @@
         <v>174</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X276" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB276">
         <v>0</v>
       </c>
       <c r="AC276" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH276" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AI276" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B277" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
       </c>
       <c r="D277" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E277" t="s">
         <v>54</v>
       </c>
       <c r="F277" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G277">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -21816,19 +21852,19 @@
         <v>65</v>
       </c>
       <c r="J277" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N277" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P277">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q277">
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>17994675</v>
+        <v>18164523</v>
       </c>
       <c r="S277" t="s">
         <v>54</v>
@@ -21837,33 +21873,33 @@
         <v>174</v>
       </c>
       <c r="V277" s="1">
-        <v>46275.31747032407</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X277" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AB277">
         <v>0</v>
       </c>
       <c r="AC277" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH277" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AI277" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B278" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
@@ -21875,10 +21911,10 @@
         <v>54</v>
       </c>
       <c r="F278" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G278">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -21887,34 +21923,34 @@
         <v>65</v>
       </c>
       <c r="J278" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N278" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q278">
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>17994809</v>
+        <v>18178163</v>
       </c>
       <c r="S278" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="U278" t="s">
         <v>174</v>
       </c>
       <c r="V278" s="1">
-        <v>46275.31747981482</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W278">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X278" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AB278">
         <v>0</v>
@@ -21923,18 +21959,18 @@
         <v>162</v>
       </c>
       <c r="AH278" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AI278" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="279" spans="1:35">
       <c r="A279">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B279" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C279" t="s">
         <v>50</v>
@@ -21970,7 +22006,7 @@
         <v>2026</v>
       </c>
       <c r="R279">
-        <v>18006051</v>
+        <v>17994311</v>
       </c>
       <c r="S279" t="s">
         <v>54</v>
@@ -21979,13 +22015,13 @@
         <v>174</v>
       </c>
       <c r="V279" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W279">
         <v>1</v>
       </c>
       <c r="X279" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AB279">
         <v>0</v>
@@ -21994,27 +22030,27 @@
         <v>162</v>
       </c>
       <c r="AH279" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI279" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="280" spans="1:35">
       <c r="A280">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B280" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C280" t="s">
         <v>50</v>
       </c>
       <c r="D280" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E280" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F280" t="s">
         <v>56</v>
@@ -22041,22 +22077,22 @@
         <v>2026</v>
       </c>
       <c r="R280">
-        <v>18003256</v>
+        <v>17994675</v>
       </c>
       <c r="S280" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U280" t="s">
         <v>174</v>
       </c>
       <c r="V280" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W280">
         <v>1</v>
       </c>
       <c r="X280" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="AB280">
         <v>0</v>
@@ -22065,24 +22101,24 @@
         <v>162</v>
       </c>
       <c r="AH280" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI280" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="281" spans="1:35">
       <c r="A281">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B281" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C281" t="s">
         <v>50</v>
       </c>
       <c r="D281" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E281" t="s">
         <v>54</v>
@@ -22112,7 +22148,7 @@
         <v>2026</v>
       </c>
       <c r="R281">
-        <v>18004017</v>
+        <v>17994809</v>
       </c>
       <c r="S281" t="s">
         <v>54</v>
@@ -22121,13 +22157,13 @@
         <v>174</v>
       </c>
       <c r="V281" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W281">
         <v>1</v>
       </c>
       <c r="X281" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AB281">
         <v>0</v>
@@ -22136,18 +22172,18 @@
         <v>162</v>
       </c>
       <c r="AH281" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI281" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="282" spans="1:35">
       <c r="A282">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B282" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C282" t="s">
         <v>50</v>
@@ -22183,7 +22219,7 @@
         <v>2026</v>
       </c>
       <c r="R282">
-        <v>17995164</v>
+        <v>18006051</v>
       </c>
       <c r="S282" t="s">
         <v>54</v>
@@ -22192,13 +22228,13 @@
         <v>174</v>
       </c>
       <c r="V282" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W282">
         <v>1</v>
       </c>
       <c r="X282" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AB282">
         <v>0</v>
@@ -22207,18 +22243,18 @@
         <v>162</v>
       </c>
       <c r="AH282" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI282" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="283" spans="1:35">
       <c r="A283">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B283" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C283" t="s">
         <v>50</v>
@@ -22227,7 +22263,7 @@
         <v>52</v>
       </c>
       <c r="E283" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F283" t="s">
         <v>56</v>
@@ -22254,22 +22290,22 @@
         <v>2026</v>
       </c>
       <c r="R283">
-        <v>18004028</v>
+        <v>18003256</v>
       </c>
       <c r="S283" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U283" t="s">
         <v>174</v>
       </c>
       <c r="V283" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W283">
         <v>1</v>
       </c>
       <c r="X283" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AB283">
         <v>0</v>
@@ -22278,24 +22314,24 @@
         <v>162</v>
       </c>
       <c r="AH283" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI283" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="284" spans="1:35">
       <c r="A284">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B284" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C284" t="s">
         <v>50</v>
       </c>
       <c r="D284" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E284" t="s">
         <v>54</v>
@@ -22304,7 +22340,7 @@
         <v>56</v>
       </c>
       <c r="G284">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -22313,57 +22349,54 @@
         <v>65</v>
       </c>
       <c r="J284" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="N284" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P284">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q284">
         <v>2026</v>
       </c>
       <c r="R284">
-        <v>17399329</v>
+        <v>18004017</v>
       </c>
       <c r="S284" t="s">
         <v>54</v>
       </c>
       <c r="U284" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V284" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W284">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X284" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y284" t="s">
-        <v>272</v>
+        <v>184</v>
       </c>
       <c r="AB284">
         <v>0</v>
       </c>
       <c r="AC284" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH284" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI284" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="285" spans="1:35">
       <c r="A285">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C285" t="s">
         <v>50</v>
@@ -22378,7 +22411,7 @@
         <v>56</v>
       </c>
       <c r="G285">
-        <v>9774</v>
+        <v>11746</v>
       </c>
       <c r="H285">
         <v>0</v>
@@ -22387,87 +22420,81 @@
         <v>65</v>
       </c>
       <c r="J285" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N285" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P285">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q285">
         <v>2026</v>
       </c>
       <c r="R285">
-        <v>16976320</v>
+        <v>17995164</v>
       </c>
       <c r="S285" t="s">
         <v>54</v>
       </c>
       <c r="U285" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V285" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W285">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="X285" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y285" t="s">
-        <v>273</v>
+        <v>180</v>
       </c>
       <c r="AB285">
         <v>0</v>
       </c>
       <c r="AC285" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH285" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AI285" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="286" spans="1:35">
       <c r="A286">
-        <v>6627</v>
+        <v>6705</v>
       </c>
       <c r="B286" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C286" t="s">
         <v>50</v>
       </c>
       <c r="D286" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E286" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F286" t="s">
         <v>56</v>
       </c>
       <c r="G286">
-        <v>11056</v>
+        <v>11746</v>
       </c>
       <c r="H286">
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J286" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N286" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O286" t="s">
-        <v>138</v>
+        <v>46275</v>
       </c>
       <c r="P286">
         <v>8</v>
@@ -22476,37 +22503,259 @@
         <v>2026</v>
       </c>
       <c r="R286">
-        <v>18270269</v>
+        <v>18004028</v>
       </c>
       <c r="S286" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="U286" t="s">
         <v>174</v>
       </c>
       <c r="V286" s="1">
+        <v>46275.31750599537</v>
+      </c>
+      <c r="W286">
+        <v>1</v>
+      </c>
+      <c r="X286" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB286">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH286" t="s">
+        <v>281</v>
+      </c>
+      <c r="AI286" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:35">
+      <c r="A287">
+        <v>5417</v>
+      </c>
+      <c r="B287" t="s">
+        <v>43</v>
+      </c>
+      <c r="C287" t="s">
+        <v>50</v>
+      </c>
+      <c r="D287" t="s">
+        <v>51</v>
+      </c>
+      <c r="E287" t="s">
+        <v>54</v>
+      </c>
+      <c r="F287" t="s">
+        <v>56</v>
+      </c>
+      <c r="G287">
+        <v>7877</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287" t="s">
+        <v>65</v>
+      </c>
+      <c r="J287" t="s">
+        <v>67</v>
+      </c>
+      <c r="N287" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P287">
+        <v>7</v>
+      </c>
+      <c r="Q287">
+        <v>2026</v>
+      </c>
+      <c r="R287">
+        <v>17399329</v>
+      </c>
+      <c r="S287" t="s">
+        <v>54</v>
+      </c>
+      <c r="U287" t="s">
+        <v>172</v>
+      </c>
+      <c r="V287" s="1">
+        <v>46275.5810894676</v>
+      </c>
+      <c r="W287">
+        <v>17</v>
+      </c>
+      <c r="X287" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y287" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB287">
+        <v>0</v>
+      </c>
+      <c r="AC287" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH287" t="s">
+        <v>281</v>
+      </c>
+      <c r="AI287" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="288" spans="1:35">
+      <c r="A288">
+        <v>6486</v>
+      </c>
+      <c r="B288" t="s">
+        <v>44</v>
+      </c>
+      <c r="C288" t="s">
+        <v>50</v>
+      </c>
+      <c r="D288" t="s">
+        <v>51</v>
+      </c>
+      <c r="E288" t="s">
+        <v>54</v>
+      </c>
+      <c r="F288" t="s">
+        <v>56</v>
+      </c>
+      <c r="G288">
+        <v>9774</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288" t="s">
+        <v>65</v>
+      </c>
+      <c r="J288" t="s">
+        <v>120</v>
+      </c>
+      <c r="N288" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P288">
+        <v>7</v>
+      </c>
+      <c r="Q288">
+        <v>2026</v>
+      </c>
+      <c r="R288">
+        <v>16976320</v>
+      </c>
+      <c r="S288" t="s">
+        <v>54</v>
+      </c>
+      <c r="U288" t="s">
+        <v>172</v>
+      </c>
+      <c r="V288" s="1">
+        <v>46275.58158541666</v>
+      </c>
+      <c r="W288">
+        <v>17</v>
+      </c>
+      <c r="X288" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y288" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB288">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH288" t="s">
+        <v>281</v>
+      </c>
+      <c r="AI288" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="289" spans="1:35">
+      <c r="A289">
+        <v>6627</v>
+      </c>
+      <c r="B289" t="s">
+        <v>36</v>
+      </c>
+      <c r="C289" t="s">
+        <v>50</v>
+      </c>
+      <c r="D289" t="s">
+        <v>51</v>
+      </c>
+      <c r="E289" t="s">
+        <v>55</v>
+      </c>
+      <c r="F289" t="s">
+        <v>56</v>
+      </c>
+      <c r="G289">
+        <v>11056</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289" t="s">
+        <v>66</v>
+      </c>
+      <c r="J289" t="s">
+        <v>122</v>
+      </c>
+      <c r="N289" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O289" t="s">
+        <v>138</v>
+      </c>
+      <c r="P289">
+        <v>8</v>
+      </c>
+      <c r="Q289">
+        <v>2026</v>
+      </c>
+      <c r="R289">
+        <v>18270269</v>
+      </c>
+      <c r="S289" t="s">
+        <v>163</v>
+      </c>
+      <c r="U289" t="s">
+        <v>174</v>
+      </c>
+      <c r="V289" s="1">
         <v>46276.41675075232</v>
       </c>
-      <c r="W286">
-        <v>0</v>
-      </c>
-      <c r="X286" t="s">
+      <c r="W289">
+        <v>0</v>
+      </c>
+      <c r="X289" t="s">
         <v>176</v>
       </c>
-      <c r="Y286" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB286">
-        <v>0</v>
-      </c>
-      <c r="AC286" t="s">
+      <c r="Y289" t="s">
+        <v>277</v>
+      </c>
+      <c r="AB289">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="s">
         <v>163</v>
       </c>
-      <c r="AH286" t="s">
-        <v>278</v>
-      </c>
-      <c r="AI286" t="s">
-        <v>282</v>
+      <c r="AH289" t="s">
+        <v>281</v>
+      </c>
+      <c r="AI289" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
